--- a/report/NeuroGrant_ultimo.xlsx
+++ b/report/NeuroGrant_ultimo.xlsx
@@ -801,7 +801,7 @@
       </c>
       <c r="Y2" s="3" t="inlineStr">
         <is>
-          <t>For profit organizations other than small businesses; Independent school districts; Nonprofits that do not have a 501(c)(3) status with the IRS, other than institutions of higher education; County governments; Others (see text field entitled "Additional Information on Eligibility" for clarification); Special district governments; Native American tribal governments (Federally recognized); State gov</t>
+          <t>Nonprofits having a 501(c)(3) status with the IRS, other than institutions of higher education; Public housing authorities/Indian housing authorities; Special district governments; Private institutions of higher education; Nonprofits that do not have a 501(c)(3) status with the IRS, other than institutions of higher education; Native American tribal governments (Federally recognized); Native Ameri</t>
         </is>
       </c>
       <c r="Z2" s="3" t="inlineStr">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="AE2" s="4" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="AF2" s="4" t="n">
         <v>46312</v>
@@ -939,7 +939,7 @@
       </c>
       <c r="Y3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Native American tribal governments (Federally recognized); State governments; Others (see text field entitled "Additional Information on Eligibility" for clarification); Native American tribal organizations (other than Federally recognized tribal governments); Public and State controlled institutions of higher education; Private institutions of higher education; Independent school districts; City </t>
+          <t>Special district governments; Native American tribal organizations (other than Federally recognized tribal governments); Small businesses; County governments; Public housing authorities/Indian housing authorities; Nonprofits that do not have a 501(c)(3) status with the IRS, other than institutions of higher education; For profit organizations other than small businesses; City or township governmen</t>
         </is>
       </c>
       <c r="Z3" s="3" t="n"/>
@@ -964,7 +964,7 @@
         </is>
       </c>
       <c r="AE3" s="4" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="AF3" s="4" t="n">
         <v>46313</v>
@@ -974,7 +974,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>EU-HORIZON-HLTH-2027-02-DISEASE-14-two-stage</t>
+          <t>EU-HORIZON-HLTH-2027-01-STAYHLTH-01</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Sperimentazioni cliniche per promuovere interventi innovativi nelle malattie neurodegenerative</t>
+          <t>Affrontare le disabilità lungo l'arco della vita a supporto della vita indipendente e dell'inclusione</t>
         </is>
       </c>
       <c r="F4" s="4" t="n">
@@ -1026,29 +1026,29 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>Clinical trials for advancing innovative interventions for neurodegenerative diseases</t>
+          <t>Addressing disabilities through the life course to support independent living and inclusion</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Parkinson, Invecchiamento, Tecnologie riabilitazione, Altre malattie e riabilitazione</t>
+          <t>Invecchiamento, Tecnologie riabilitazione, Altre malattie e riabilitazione</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>parkinson, dementi, alzheimer, aging, wearable, rehabilitat, neurodegenerat, huntington, neurological disorder</t>
+          <t>frailty, older persons, assistive technolog, rehabilitat, disabilit, cardiovascular, obesit</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>Richiede esplicitamente l'integrazione di terapie riabilitative e training cognitivo in trial clinici per malattie neurodegenerative come Alzheimer e Parkinson.</t>
+          <t>Finanzia interventi di abilitazione, riabilitazione anche con tecnologie assistive e modelli per il recupero funzionale e la vita indipendente in persone con disabilità a lungo termine.</t>
         </is>
       </c>
       <c r="P4" s="6" t="n">
         <v>39300000</v>
       </c>
       <c r="Q4" s="6" t="n">
-        <v>10000000</v>
+        <v>8000000</v>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
@@ -1056,11 +1056,11 @@
         </is>
       </c>
       <c r="S4" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t>Bassa – 4 progetti finanziabili (stima: tasso storico non disponibile)</t>
+          <t>Media – 5 progetti finanziabili (stima: tasso storico non disponibile)</t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t>Università, centri di ricerca, ospedali, PMI, start-up, organizzazioni di pazienti e autorità sanitarie</t>
+          <t>Comunità scientifica, decisori politici, fornitori di servizi sanitari e sociali, organizzazioni per la disabilità</t>
         </is>
       </c>
       <c r="Z4" s="3" t="inlineStr">
@@ -1099,26 +1099,26 @@
       </c>
       <c r="AC4" s="7" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-HLTH-2027-02-DISEASE-14-two-stage</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-HLTH-2027-01-STAYHLTH-01</t>
         </is>
       </c>
       <c r="AD4" s="3" t="inlineStr">
         <is>
-          <t>Il bando di Horizon Europe finanzia la realizzazione di studi clinici precoci volti a verificare sicurezza ed efficacia di interventi innovativi per malattie neurodegenerative non rare come Parkinson e Alzheimer. Le proposte devono combinare un principio attivo terapeutico con approcci multidisciplinari complementari, inclusi esplicitamente terapie riabilitative, modifiche dello stile di vita e training cognitivo, oltre all'uso di tecnologie digitali per il monitoraggio a lungo termine. Possono partecipare consorzi internazionali composti da università, centri clinici, PMI, associazioni di pazienti e altri enti stabiliti negli Stati membri dell'UE o nei Paesi associati.</t>
+          <t>Il bando supporta la ricerca clinica, assistenziale e tecnologica incentrata sulle persone con disabilità fisiche, mentali, intellettive o sensoriali a lungo termine, per favorire l'inclusione comunitaria e l'autonomia lungo tutto l'arco dell'esistenza. Tra le aree prioritarie rientrano l'accesso a servizi di abilitazione e riabilitazione, compresa la riabilitazione psicologica e l'impiego di tecnologie assistive avanzate volte al miglioramento o recupero delle capacità funzionali e alla riduzione delle limitazioni nelle attività quotidiane. Si finanziano inoltre nuovi modelli di cura integrati, prevenzione della perdita di autonomia e percorsi di deistituzionalizzazione. Possono partecipare consorzi transnazionali composti da ricercatori clinici, fornitori di assistenza sociosanitaria, associazioni di disabili e università.</t>
         </is>
       </c>
       <c r="AE4" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="AF4" s="4" t="n">
         <v>46313</v>
-      </c>
-      <c r="AF4" s="4" t="n">
-        <v>46312</v>
       </c>
       <c r="AG4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>EU-HORIZON-HLTH-2027-01-STAYHLTH-01</t>
+          <t>EU-HORIZON-HLTH-2027-02-DISEASE-14-two-stage</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Affrontare le disabilità lungo l'arco della vita a supporto della vita indipendente e dell'inclusione</t>
+          <t>Sperimentazioni cliniche per promuovere interventi innovativi nelle malattie neurodegenerative</t>
         </is>
       </c>
       <c r="F5" s="4" t="n">
@@ -1170,29 +1170,29 @@
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>Addressing disabilities through the life course to support independent living and inclusion</t>
+          <t>Clinical trials for advancing innovative interventions for neurodegenerative diseases</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Invecchiamento, Tecnologie riabilitazione, Altre malattie e riabilitazione</t>
+          <t>Parkinson, Invecchiamento, Tecnologie riabilitazione, Altre malattie e riabilitazione</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>frailty, older persons, assistive technolog, rehabilitat, disabilit, cardiovascular, obesit</t>
+          <t>parkinson, dementi, alzheimer, aging, wearable, rehabilitat, neurodegenerat, huntington, neurological disorder</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>Finanzia interventi di abilitazione, riabilitazione anche con tecnologie assistive e modelli per il recupero funzionale e la vita indipendente in persone con disabilità a lungo termine.</t>
+          <t>Richiede esplicitamente l'integrazione di terapie riabilitative e training cognitivo in trial clinici per malattie neurodegenerative come Alzheimer e Parkinson.</t>
         </is>
       </c>
       <c r="P5" s="6" t="n">
         <v>39300000</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>8000000</v>
+        <v>10000000</v>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
@@ -1200,11 +1200,11 @@
         </is>
       </c>
       <c r="S5" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t>Media – 5 progetti finanziabili (stima: tasso storico non disponibile)</t>
+          <t>Bassa – 4 progetti finanziabili (stima: tasso storico non disponibile)</t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t>Comunità scientifica, decisori politici, fornitori di servizi sanitari e sociali, organizzazioni per la disabilità</t>
+          <t>Università, centri di ricerca, ospedali, PMI, start-up, organizzazioni di pazienti e autorità sanitarie</t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
@@ -1243,19 +1243,19 @@
       </c>
       <c r="AC5" s="7" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-HLTH-2027-01-STAYHLTH-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-HLTH-2027-02-DISEASE-14-two-stage</t>
         </is>
       </c>
       <c r="AD5" s="3" t="inlineStr">
         <is>
-          <t>Il bando supporta la ricerca clinica, assistenziale e tecnologica incentrata sulle persone con disabilità fisiche, mentali, intellettive o sensoriali a lungo termine, per favorire l'inclusione comunitaria e l'autonomia lungo tutto l'arco dell'esistenza. Tra le aree prioritarie rientrano l'accesso a servizi di abilitazione e riabilitazione, compresa la riabilitazione psicologica e l'impiego di tecnologie assistive avanzate volte al miglioramento o recupero delle capacità funzionali e alla riduzione delle limitazioni nelle attività quotidiane. Si finanziano inoltre nuovi modelli di cura integrati, prevenzione della perdita di autonomia e percorsi di deistituzionalizzazione. Possono partecipare consorzi transnazionali composti da ricercatori clinici, fornitori di assistenza sociosanitaria, associazioni di disabili e università.</t>
+          <t>Il bando di Horizon Europe finanzia la realizzazione di studi clinici precoci volti a verificare sicurezza ed efficacia di interventi innovativi per malattie neurodegenerative non rare come Parkinson e Alzheimer. Le proposte devono combinare un principio attivo terapeutico con approcci multidisciplinari complementari, inclusi esplicitamente terapie riabilitative, modifiche dello stile di vita e training cognitivo, oltre all'uso di tecnologie digitali per il monitoraggio a lungo termine. Possono partecipare consorzi internazionali composti da università, centri clinici, PMI, associazioni di pazienti e altri enti stabiliti negli Stati membri dell'UE o nei Paesi associati.</t>
         </is>
       </c>
       <c r="AE5" s="4" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="AF5" s="4" t="n">
-        <v>46313</v>
+        <v>46312</v>
       </c>
       <c r="AG5" s="2" t="n"/>
     </row>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t>Others (see text field entitled "Additional Information on Eligibility" for clarification); Nonprofits having a 501(c)(3) status with the IRS, other than institutions of higher education; City or township governments; For profit organizations other than small businesses; Small businesses; Nonprofits that do not have a 501(c)(3) status with the IRS, other than institutions of higher education; Nati</t>
+          <t>Private institutions of higher education; Small businesses; Public housing authorities/Indian housing authorities; Independent school districts; State governments; Special district governments; Public and State controlled institutions of higher education; For profit organizations other than small businesses; County governments; City or township governments; Others (see text field entitled "Additio</t>
         </is>
       </c>
       <c r="Z6" s="3" t="n"/>
@@ -1392,7 +1392,7 @@
         </is>
       </c>
       <c r="AE6" s="4" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="AF6" s="4" t="n">
         <v>46312</v>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t>Nonprofits having a 501(c)(3) status with the IRS, other than institutions of higher education; Independent school districts; Nonprofits that do not have a 501(c)(3) status with the IRS, other than institutions of higher education; Native American tribal organizations (other than Federally recognized tribal governments); For profit organizations other than small businesses; Small businesses; Publi</t>
+          <t>County governments; Native American tribal organizations (other than Federally recognized tribal governments); For profit organizations other than small businesses; Small businesses; Special district governments; Private institutions of higher education; Nonprofits having a 501(c)(3) status with the IRS, other than institutions of higher education; Others (see text field entitled "Additional Infor</t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="AE7" s="4" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="AF7" s="4" t="n">
         <v>46312</v>
@@ -1622,22 +1622,22 @@
         </is>
       </c>
       <c r="S8" s="2" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t>Alta – 100 progetti finanziabili (stima: tasso storico non disponibile)</t>
+          <t>Bassa – 1 progetti finanziabili (stima: tasso storico non disponibile)</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t>Interamente finanziato</t>
+          <t>Co-finanziamento richiesto (25% a carico del beneficiario)</t>
         </is>
       </c>
       <c r="V8" s="4" t="n"/>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>300 mesi</t>
+          <t>12 mesi</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t>Iniziatori di carriera NIH o entro 7 anni dalla loro designazione come iniziatori di carriera NIH</t>
+          <t>Ricercatori principali a inizio carriera (Early Stage Investigator secondo i criteri NIH o entro 7 anni dalla qualifica) titolari di grant federali statunitensi interrotti</t>
         </is>
       </c>
       <c r="Z8" s="3" t="n"/>
@@ -1672,7 +1672,7 @@
         </is>
       </c>
       <c r="AE8" s="4" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="AF8" s="4" t="n">
         <v>46312</v>
@@ -1785,7 +1785,7 @@
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Special district governments; Independent school districts; Native American tribal governments (Federally recognized); Others (see text field entitled "Additional Information on Eligibility" for clarification); For profit organizations other than small businesses; Public housing authorities/Indian housing authorities; Private institutions of higher education; County governments; Small businesses; </t>
+          <t xml:space="preserve">County governments; Nonprofits that do not have a 501(c)(3) status with the IRS, other than institutions of higher education; Independent school districts; Public and State controlled institutions of higher education; For profit organizations other than small businesses; Others (see text field entitled "Additional Information on Eligibility" for clarification); State governments; City or township </t>
         </is>
       </c>
       <c r="Z9" s="3" t="n"/>
@@ -1810,7 +1810,7 @@
         </is>
       </c>
       <c r="AE9" s="4" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="AF9" s="4" t="n">
         <v>46312</v>
@@ -1919,7 +1919,7 @@
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t>Nonprofits that do not have a 501(c)(3) status with the IRS, other than institutions of higher education; Small businesses; Native American tribal governments (Federally recognized); Private institutions of higher education; County governments; Nonprofits having a 501(c)(3) status with the IRS, other than institutions of higher education; For profit organizations other than small businesses; State</t>
+          <t>For profit organizations other than small businesses; Nonprofits that do not have a 501(c)(3) status with the IRS, other than institutions of higher education; Native American tribal organizations (other than Federally recognized tribal governments); Native American tribal governments (Federally recognized); State governments; City or township governments; Nonprofits having a 501(c)(3) status with</t>
         </is>
       </c>
       <c r="Z10" s="3" t="n"/>
@@ -1944,7 +1944,7 @@
         </is>
       </c>
       <c r="AE10" s="4" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="AF10" s="4" t="n">
         <v>46312</v>
@@ -2088,7 +2088,7 @@
         </is>
       </c>
       <c r="AE11" s="4" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="AF11" s="4" t="n">
         <v>46313</v>
@@ -2232,7 +2232,7 @@
         </is>
       </c>
       <c r="AE12" s="4" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="AF12" s="4" t="n">
         <v>46312</v>
@@ -2374,7 +2374,7 @@
         </is>
       </c>
       <c r="AE13" s="4" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="AF13" s="4" t="n">
         <v>46312</v>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t>Il bando richiede l'inserimento di un partner della comunità con esperienza in lesioni della corda spinale.</t>
+          <t>Obbligatorio almeno un partner comunitario esperto per esperienza diretta di lesione midollare; ammessa opzione a due PI con ricercatore junior.</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2516,7 +2516,7 @@
         </is>
       </c>
       <c r="AE14" s="4" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="AF14" s="4" t="n">
         <v>46313</v>
@@ -2634,7 +2634,7 @@
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t>I beneficiari devono coinvolgere almeno due partner della comunità con lesioni della corda gracile (SCI) per fornire consigli durante la pianificazione e l'esecuzione del progetto.</t>
+          <t>Obbligatori almeno 2 partner della comunità con esperienza di lesione midollare; possibile collaborazione tra 2 PI</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2658,7 +2658,7 @@
         </is>
       </c>
       <c r="AE15" s="4" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="AF15" s="4" t="n">
         <v>46313</v>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t>Applicazioni a questa convenzione devono nominare almeno due partner della comunità di lesioni spinali che forniranno consigli e consulenza durante la pianificazione e l'implementazione del progetto di ricerca.</t>
+          <t>Obbligatori almeno due partner della comunità di pazienti; opzione con due PI di cui uno a inizio carriera</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
         </is>
       </c>
       <c r="AE16" s="4" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="AF16" s="4" t="n">
         <v>46312</v>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t>Per l'opzione di partnership, almeno uno dei PI deve essere un investigatore in carriera iniziale. L'opzione permette due PI, ma solo l'initiating PI può inviare un pre-applicazione.</t>
+          <t>Opzione per due Principal Investigator (di cui almeno uno a inizio carriera)</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2942,7 +2942,7 @@
         </is>
       </c>
       <c r="AE17" s="4" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="AF17" s="4" t="n">
         <v>46313</v>
@@ -3074,7 +3074,7 @@
         </is>
       </c>
       <c r="AE18" s="4" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="AF18" s="4" t="n">
         <v>46312</v>
@@ -3324,7 +3324,7 @@
       <c r="W20" s="2" t="n"/>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>Ricerca</t>
+          <t>Dottorato / formazione / mobilità</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
@@ -3358,7 +3358,7 @@
         </is>
       </c>
       <c r="AE20" s="4" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="AF20" s="4" t="n">
         <v>46312</v>
@@ -3476,7 +3476,7 @@
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">L'opzione di Principale Investigatore Associato consente di avere più di un Principale Investigatore. Uno di essi sarà identificato come Principale Investigatore Iniziativo e sarà responsabile per la maggior parte delle attività amministrative associate alla presentazione dell'applicazione. L'altro </t>
+          <t>Possibilità di consorzio con un Initiating PI e fino a due Partnering PI multidisciplinari.</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -3500,7 +3500,7 @@
         </is>
       </c>
       <c r="AE21" s="4" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="AF21" s="4" t="n">
         <v>46312</v>
@@ -3615,7 +3615,7 @@
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t>City or township governments; Unrestricted (i.e., open to any type of entity above), subject to any clarification in text field entitled "Additional Information on Eligibility"; State governments; Native American tribal organizations (other than Federally recognized tribal governments); Private institutions of higher education; Independent school districts; County governments; Others (see text fie</t>
+          <t>Native American tribal governments (Federally recognized); Public housing authorities/Indian housing authorities; Others (see text field entitled "Additional Information on Eligibility" for clarification); Unrestricted (i.e., open to any type of entity above), subject to any clarification in text field entitled "Additional Information on Eligibility"; Public and State controlled institutions of hi</t>
         </is>
       </c>
       <c r="Z22" s="3" t="n"/>
@@ -3640,7 +3640,7 @@
         </is>
       </c>
       <c r="AE22" s="4" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="AF22" s="4" t="n">
         <v>46312</v>
@@ -3879,7 +3879,7 @@
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t>Small businesses; City or township governments; Native American tribal governments (Federally recognized); Special district governments; Public housing authorities/Indian housing authorities; For profit organizations other than small businesses; Nonprofits having a 501(c)(3) status with the IRS, other than institutions of higher education; Public and State controlled institutions of higher educati</t>
+          <t>Special district governments; Private institutions of higher education; State governments; Independent school districts; Nonprofits that do not have a 501(c)(3) status with the IRS, other than institutions of higher education; For profit organizations other than small businesses; Native American tribal governments (Federally recognized); Native American tribal organizations (other than Federally r</t>
         </is>
       </c>
       <c r="Z24" s="3" t="n"/>
@@ -3904,7 +3904,7 @@
         </is>
       </c>
       <c r="AE24" s="4" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="AF24" s="4" t="n">
         <v>46312</v>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t>Nonprofits having a 501(c)(3) status with the IRS, other than institutions of higher education; Unrestricted (i.e., open to any type of entity above), subject to any clarification in text field entitled "Additional Information on Eligibility"; Small businesses; Native American tribal governments (Federally recognized); Nonprofits that do not have a 501(c)(3) status with the IRS, other than institu</t>
+          <t>Public and State controlled institutions of higher education; State governments; Special district governments; County governments; For profit organizations other than small businesses; Private institutions of higher education; Nonprofits having a 501(c)(3) status with the IRS, other than institutions of higher education; Independent school districts; Native American tribal organizations (other tha</t>
         </is>
       </c>
       <c r="Z25" s="3" t="n"/>
@@ -4038,7 +4038,7 @@
         </is>
       </c>
       <c r="AE25" s="4" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="AF25" s="4" t="n">
         <v>46312</v>
@@ -4174,7 +4174,7 @@
         </is>
       </c>
       <c r="AE26" s="4" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="AF26" s="4" t="n">
         <v>46312</v>
@@ -9222,18 +9222,18 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>18/10/2026 14:03</t>
+          <t>19/10/2026 07:40</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Ultima esecuzione: 35 elementi esaminati, 0 pertinenti</t>
+          <t>Ultima esecuzione: 1 elementi esaminati, 0 pertinenti</t>
         </is>
       </c>
     </row>
@@ -9265,11 +9265,11 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>18/10/2026 14:12</t>
+          <t>19/10/2026 07:48</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>21</v>
@@ -9562,11 +9562,11 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18/10/2026 13:56</t>
+          <t>19/10/2026 07:34</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>105</v>
+        <v>140</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>1</v>
@@ -9648,11 +9648,11 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18/10/2026 14:03</t>
+          <t>19/10/2026 07:41</t>
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>105</v>
+        <v>140</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>0</v>
@@ -9691,11 +9691,11 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18/10/2026 14:09</t>
+          <t>19/10/2026 07:46</t>
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>105</v>
+        <v>140</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>0</v>
@@ -9734,11 +9734,11 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18/10/2026 13:48</t>
+          <t>19/10/2026 07:25</t>
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>3586</v>
+        <v>4781</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>77</v>
@@ -9777,11 +9777,11 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>18/10/2026 13:58</t>
+          <t>19/10/2026 07:36</t>
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>105</v>
+        <v>140</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>3</v>
@@ -9820,11 +9820,11 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18/10/2026 13:57</t>
+          <t>19/10/2026 07:35</t>
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>105</v>
+        <v>140</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>3</v>
@@ -9863,11 +9863,11 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18/10/2026 14:01</t>
+          <t>19/10/2026 07:39</t>
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>105</v>
+        <v>140</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>2</v>
@@ -9906,11 +9906,11 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>18/10/2026 13:55</t>
+          <t>19/10/2026 07:33</t>
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>105</v>
+        <v>140</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>2</v>
@@ -9949,11 +9949,11 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18/10/2026 14:01</t>
+          <t>19/10/2026 07:39</t>
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>105</v>
+        <v>140</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>0</v>
@@ -9992,11 +9992,11 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>18/10/2026 14:02</t>
+          <t>19/10/2026 07:40</t>
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>105</v>
+        <v>140</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>0</v>
@@ -10078,11 +10078,11 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18/10/2026 13:52</t>
+          <t>19/10/2026 07:29</t>
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>2532</v>
+        <v>3382</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>113</v>
@@ -10121,11 +10121,11 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>18/10/2026 13:53</t>
+          <t>19/10/2026 07:30</t>
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>105</v>
+        <v>140</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>0</v>
@@ -10164,11 +10164,11 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>18/10/2026 14:03</t>
+          <t>19/10/2026 07:41</t>
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>0</v>
@@ -10207,11 +10207,11 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>18/10/2026 13:54</t>
+          <t>19/10/2026 07:32</t>
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>105</v>
+        <v>140</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>0</v>
@@ -10250,11 +10250,11 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>18/10/2026 14:11</t>
+          <t>19/10/2026 07:48</t>
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>21</v>
@@ -10293,11 +10293,11 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>18/10/2026 13:52</t>
+          <t>19/10/2026 07:30</t>
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>105</v>
+        <v>140</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>0</v>
@@ -10336,11 +10336,11 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>18/10/2026 13:52</t>
+          <t>19/10/2026 07:29</t>
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H28" s="2" t="n">
         <v>0</v>
@@ -10457,11 +10457,11 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>18/10/2026 14:12</t>
+          <t>19/10/2026 07:49</t>
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>105</v>
+        <v>140</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>0</v>
@@ -10500,11 +10500,11 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>18/10/2026 14:11</t>
+          <t>19/10/2026 07:48</t>
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="H32" s="2" t="n">
         <v>8</v>
@@ -10586,11 +10586,11 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>18/10/2026 13:53</t>
+          <t>19/10/2026 07:31</t>
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>0</v>
@@ -10629,11 +10629,11 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>18/10/2026 13:54</t>
+          <t>19/10/2026 07:31</t>
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>105</v>
+        <v>140</v>
       </c>
       <c r="H35" s="2" t="n">
         <v>0</v>
@@ -10711,11 +10711,11 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>18/10/2026 14:09</t>
+          <t>19/10/2026 07:46</t>
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>0</v>
@@ -10754,11 +10754,11 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>18/10/2026 14:10</t>
+          <t>19/10/2026 07:47</t>
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>105</v>
+        <v>140</v>
       </c>
       <c r="H38" s="2" t="n">
         <v>0</v>
@@ -10797,11 +10797,11 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>18/10/2026 14:11</t>
+          <t>19/10/2026 07:47</t>
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>105</v>
+        <v>140</v>
       </c>
       <c r="H39" s="2" t="n">
         <v>0</v>
@@ -10823,7 +10823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -10881,25 +10881,25 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-18 14:17</t>
+          <t>2026-10-19 07:49</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2720</v>
+        <v>2686</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>32 non aperti all'Italia, 3 di infrastruttura, 3 preclinici, 3 non pertinenti alla riabilitazione, 1 servizi o programmi sociali</t>
+          <t>32 non aperti all'Italia, 3 di infrastruttura, 3 preclinici, 2 non pertinenti alla riabilitazione, 1 servizi o programmi sociali</t>
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
@@ -10907,62 +10907,94 @@
         </is>
       </c>
       <c r="H2" s="3" t="n">
-        <v>29.3</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-18 02:48</t>
+          <t>2026-10-18 14:17</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2925</v>
+        <v>2720</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>107</v>
-      </c>
-      <c r="E3" s="3" t="n"/>
+        <v>112</v>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>32 non aperti all'Italia, 3 di infrastruttura, 3 preclinici, 3 non pertinenti alla riabilitazione, 1 servizi o programmi sociali</t>
+        </is>
+      </c>
       <c r="F3" s="3" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>NIHR: HTTP 403; Stroke Association: HTTP 403; American Heart Association – Research: HTTP 403; NHMRC: irraggiungibile: HTTPSConnectionPool(host='www.nhmrc.gov.au', port=443): Read timed out. (read timeout=45)</t>
+          <t>Nessuno</t>
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>92.5</v>
+        <v>29.3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-17 15:58</t>
+          <t>2026-10-18 02:48</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>2819</v>
+        <v>2925</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>266</v>
+        <v>20</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="E4" s="3" t="n"/>
       <c r="F4" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>NIHR: HTTP 403; Stroke Association: HTTP 403; American Heart Association – Research: HTTP 403; NHMRC: irraggiungibile: HTTPSConnectionPool(host='www.nhmrc.gov.au', port=443): Read timed out. (read timeout=45)</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>92.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-17 15:58</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>2819</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>266</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n">
         <v>44</v>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>NIHR: HTTP 403; Stroke Association: HTTP 403; American Heart Association – Research: HTTP 403; NHMRC: irraggiungibile: HTTPSConnectionPool(host='www.nhmrc.gov.au', port=443): Read timed out. (read timeout=45)</t>
         </is>
       </c>
-      <c r="H4" s="3" t="n">
+      <c r="H5" s="3" t="n">
         <v>76.5</v>
       </c>
     </row>

--- a/report/NeuroGrant_ultimo.xlsx
+++ b/report/NeuroGrant_ultimo.xlsx
@@ -700,7 +700,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>GG-RFA-NS-26-028</t>
+          <t>EU-HORIZON-HLTH-2027-02-DISEASE-14-two-stage</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -715,16 +715,16 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Tecnologia / innovazione</t>
+          <t>Ricerca clinica</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Iniziativa HEAL: ottimizzazione dei dispositivi medici terapeutici attraverso la ricerca meccanicistica interdisciplinare (RM1)</t>
+          <t>Sperimentazioni cliniche per promuovere interventi innovativi nelle malattie neurodegenerative</t>
         </is>
       </c>
       <c r="F2" s="4" t="n">
-        <v>46325</v>
+        <v>46435</v>
       </c>
       <c r="G2" s="5">
         <f>IF(F2="","",F2-TODAY())</f>
@@ -732,49 +732,53 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>In scadenza (≤30 gg)</t>
+          <t>In apertura</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>National Institutes of Health</t>
+          <t>Commissione europea</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Grants.gov</t>
+          <t>EU Funding &amp; Tenders Portal</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>National Institutes of Health – RFA-NS-26-028</t>
+          <t>Horizon Europe – HORIZON  Research and Innovation Actions</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>HEAL Initiative: Optimization of Therapeutic Medical Devices through Team Science Mechanistic Research (RM1)</t>
+          <t>Clinical trials for advancing innovative interventions for neurodegenerative diseases</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Ictus, Altre malattie e riabilitazione</t>
+          <t>Parkinson, Invecchiamento, Tecnologie riabilitazione, Altre malattie e riabilitazione</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>stroke, neurological disorder</t>
+          <t>parkinson, dementi, alzheimer, aging, wearable, rehabilitat, neurodegenerat, huntington, neurological disorder</t>
         </is>
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>Supporta la ricerca sui meccanismi d'azione di dispositivi medici terapeutici per patologie neurologiche e dolore cronico, altamente rilevanti per la neuroriabilitazione.</t>
-        </is>
-      </c>
-      <c r="P2" s="6" t="n"/>
-      <c r="Q2" s="6" t="n"/>
+          <t>Richiede esplicitamente l'integrazione di terapie riabilitative e training cognitivo in trial clinici per malattie neurodegenerative come Alzheimer e Parkinson.</t>
+        </is>
+      </c>
+      <c r="P2" s="6" t="n">
+        <v>39300000</v>
+      </c>
+      <c r="Q2" s="6" t="n">
+        <v>10000000</v>
+      </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="S2" s="2" t="n">
@@ -791,7 +795,7 @@
         </is>
       </c>
       <c r="V2" s="4" t="n">
-        <v>46097</v>
+        <v>46324</v>
       </c>
       <c r="W2" s="2" t="n"/>
       <c r="X2" s="2" t="inlineStr">
@@ -801,17 +805,17 @@
       </c>
       <c r="Y2" s="3" t="inlineStr">
         <is>
-          <t>Nonprofits having a 501(c)(3) status with the IRS, other than institutions of higher education; Public housing authorities/Indian housing authorities; Special district governments; Private institutions of higher education; Nonprofits that do not have a 501(c)(3) status with the IRS, other than institutions of higher education; Native American tribal governments (Federally recognized); Native Ameri</t>
+          <t>Università, centri di ricerca, ospedali, PMI, start-up, organizzazioni di pazienti e autorità sanitarie</t>
         </is>
       </c>
       <c r="Z2" s="3" t="inlineStr">
         <is>
-          <t>Team scientifici interdisciplinari comprendenti competenze ingegneristiche, biologiche, computazionali e cliniche</t>
+          <t>Consorzio: min. 3 enti indipendenti da 3 paesi UE/associati (regola standard, verificare il topic)</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>Ammessi anche enti non statunitensi</t>
+          <t>Stati membri UE e paesi associati (altri paesi secondo le condizioni del topic)</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
@@ -821,16 +825,16 @@
       </c>
       <c r="AC2" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/361520</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-HLTH-2027-02-DISEASE-14-two-stage</t>
         </is>
       </c>
       <c r="AD2" s="3" t="inlineStr">
         <is>
-          <t>Il National Institute of Neurological Disorders and Stroke (NINDS), nell'ambito dell'iniziativa NIH HEAL, preannuncia un'opportunità di finanziamento destinata a indagare i meccanismi d'azione dei dispositivi medici terapeutici per ottimizzare i risultati clinici nelle patologie neurologiche e nel trattamento del dolore. La call intende finanziare team scientifici altamente interdisciplinari (con competenze che spaziano dall'ingegneria e biologia alla clinica, biostatistica, intelligenza artificiale e sperimentazioni cliniche). Le attività ammissibili comprendono studi clinici meccanicistici, modelli computazionali o simulazioni e ricerche precliniche su modelli animali, applicabili sia a dispositivi sperimentali sia a tecnologie già approvate dalla FDA e impiegate nella pratica clinica. La partecipazione è aperta anche a istituzioni di ricerca estere non statunitensi.</t>
+          <t>Il bando di Horizon Europe finanzia la realizzazione di studi clinici precoci volti a verificare sicurezza ed efficacia di interventi innovativi per malattie neurodegenerative non rare come Parkinson e Alzheimer. Le proposte devono combinare un principio attivo terapeutico con approcci multidisciplinari complementari, inclusi esplicitamente terapie riabilitative, modifiche dello stile di vita e training cognitivo, oltre all'uso di tecnologie digitali per il monitoraggio a lungo termine. Possono partecipare consorzi internazionali composti da università, centri clinici, PMI, associazioni di pazienti e altri enti stabiliti negli Stati membri dell'UE o nei Paesi associati.</t>
         </is>
       </c>
       <c r="AE2" s="4" t="n">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="AF2" s="4" t="n">
         <v>46312</v>
@@ -840,7 +844,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>GG-RFA-DA-28-011</t>
+          <t>EU-HORIZON-HLTH-2027-01-STAYHLTH-01</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -860,11 +864,11 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Iniziativa HEAL: gestione integrata del dolore cronico e del disturbo da uso di oppioidi (IMPOWR) - Centri di ricerca (RM1)</t>
+          <t>Affrontare le disabilità lungo l'arco della vita a supporto della vita indipendente e dell'inclusione</t>
         </is>
       </c>
       <c r="F3" s="4" t="n">
-        <v>46413</v>
+        <v>46435</v>
       </c>
       <c r="G3" s="5">
         <f>IF(F3="","",F3-TODAY())</f>
@@ -872,55 +876,61 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Aperto</t>
+          <t>In apertura</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>National Institutes of Health</t>
+          <t>Commissione europea</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Grants.gov</t>
+          <t>EU Funding &amp; Tenders Portal</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>National Institutes of Health – RFA-DA-28-011</t>
+          <t>Horizon Europe – HORIZON  Research and Innovation Actions</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>HEAL Initiative: Integrative Management of Chronic Pain and OUD for Whole Recovery (IMPOWR): Research Centers (RM1 Clinical Trial Required)</t>
+          <t>Addressing disabilities through the life course to support independent living and inclusion</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Altre malattie e riabilitazione</t>
+          <t>Invecchiamento, Tecnologie riabilitazione, Altre malattie e riabilitazione</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>chronic pain</t>
+          <t>frailty, older persons, assistive technolog, rehabilitat, disabilit, cardiovascular, obesit</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>È dedicato alla gestione integrata a lungo termine del dolore cronico e al recupero funzionale dei pazienti.</t>
-        </is>
-      </c>
-      <c r="P3" s="6" t="n"/>
-      <c r="Q3" s="6" t="n"/>
+          <t>Finanzia interventi di abilitazione, riabilitazione anche con tecnologie assistive e modelli per il recupero funzionale e la vita indipendente in persone con disabilità a lungo termine.</t>
+        </is>
+      </c>
+      <c r="P3" s="6" t="n">
+        <v>39300000</v>
+      </c>
+      <c r="Q3" s="6" t="n">
+        <v>8000000</v>
+      </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="S3" s="2" t="n"/>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="S3" s="2" t="n">
+        <v>5</v>
+      </c>
       <c r="T3" s="3" t="inlineStr">
         <is>
-          <t>Non stimabile – dati insufficienti</t>
+          <t>Media – 5 progetti finanziabili (stima: tasso storico non disponibile)</t>
         </is>
       </c>
       <c r="U3" s="3" t="inlineStr">
@@ -929,7 +939,7 @@
         </is>
       </c>
       <c r="V3" s="4" t="n">
-        <v>46301</v>
+        <v>46324</v>
       </c>
       <c r="W3" s="2" t="n"/>
       <c r="X3" s="2" t="inlineStr">
@@ -939,13 +949,17 @@
       </c>
       <c r="Y3" s="3" t="inlineStr">
         <is>
-          <t>Special district governments; Native American tribal organizations (other than Federally recognized tribal governments); Small businesses; County governments; Public housing authorities/Indian housing authorities; Nonprofits that do not have a 501(c)(3) status with the IRS, other than institutions of higher education; For profit organizations other than small businesses; City or township governmen</t>
-        </is>
-      </c>
-      <c r="Z3" s="3" t="n"/>
+          <t>Comunità scientifica, decisori politici, fornitori di servizi sanitari e sociali, organizzazioni per la disabilità</t>
+        </is>
+      </c>
+      <c r="Z3" s="3" t="inlineStr">
+        <is>
+          <t>Consorzio: min. 3 enti indipendenti da 3 paesi UE/associati (regola standard, verificare il topic)</t>
+        </is>
+      </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>Ammessi anche enti non statunitensi</t>
+          <t>Stati membri UE e paesi associati (altri paesi secondo le condizioni del topic)</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
@@ -955,16 +969,16 @@
       </c>
       <c r="AC3" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/360048</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-HLTH-2027-01-STAYHLTH-01</t>
         </is>
       </c>
       <c r="AD3" s="3" t="inlineStr">
         <is>
-          <t>L'avviso anticipa il rinnovo della rete di ricerca IMPOWR, parte dell'iniziativa NIH HEAL, finalizzata allo sviluppo e alla validazione di modelli integrati per la gestione del dolore cronico e del disturbo da uso di oppioidi. Il network comprenderà molteplici progetti di ricerca coordinati da un centro centrale, con l'obiettivo di condurre studi clinici per testare approcci assistenziali innovativi in grado di migliorare significativamente l'erogazione delle cure nei sistemi sanitari. Possono partecipare istituzioni universitarie, ospedaliere, enti di ricerca no-profit o profit e organizzazioni estere non statunitensi.</t>
+          <t>Il bando supporta la ricerca clinica, assistenziale e tecnologica incentrata sulle persone con disabilità fisiche, mentali, intellettive o sensoriali a lungo termine, per favorire l'inclusione comunitaria e l'autonomia lungo tutto l'arco dell'esistenza. Tra le aree prioritarie rientrano l'accesso a servizi di abilitazione e riabilitazione, compresa la riabilitazione psicologica e l'impiego di tecnologie assistive avanzate volte al miglioramento o recupero delle capacità funzionali e alla riduzione delle limitazioni nelle attività quotidiane. Si finanziano inoltre nuovi modelli di cura integrati, prevenzione della perdita di autonomia e percorsi di deistituzionalizzazione. Possono partecipare consorzi transnazionali composti da ricercatori clinici, fornitori di assistenza sociosanitaria, associazioni di disabili e università.</t>
         </is>
       </c>
       <c r="AE3" s="4" t="n">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="AF3" s="4" t="n">
         <v>46313</v>
@@ -974,7 +988,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>EU-HORIZON-HLTH-2027-01-STAYHLTH-01</t>
+          <t>GG-PAR-25-124</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -994,11 +1008,11 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Affrontare le disabilità lungo l'arco della vita a supporto della vita indipendente e dell'inclusione</t>
+          <t>Finanziamento di ricerca per ricercatori a inizio carriera NCMRR (R03 Clinical Trial facoltativo)</t>
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>46435</v>
+        <v>46759</v>
       </c>
       <c r="G4" s="5">
         <f>IF(F4="","",F4-TODAY())</f>
@@ -1006,61 +1020,61 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>In apertura</t>
+          <t>Aperto</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Commissione europea</t>
+          <t>National Institutes of Health</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>EU Funding &amp; Tenders Portal</t>
+          <t>Grants.gov</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>Horizon Europe – HORIZON  Research and Innovation Actions</t>
+          <t>National Institutes of Health – PAR-25-124</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>Addressing disabilities through the life course to support independent living and inclusion</t>
+          <t>NCMRR Early Career Research Award (R03 Clinical Trial Optional)</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Invecchiamento, Tecnologie riabilitazione, Altre malattie e riabilitazione</t>
+          <t>Altre malattie e riabilitazione</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>frailty, older persons, assistive technolog, rehabilitat, disabilit, cardiovascular, obesit</t>
+          <t>rehabilitat</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>Finanzia interventi di abilitazione, riabilitazione anche con tecnologie assistive e modelli per il recupero funzionale e la vita indipendente in persone con disabilità a lungo termine.</t>
+          <t>Bando dedicato specificamente alla ricerca di base e clinica in riabilitazione promosso dal NCMRR per ricercatori a inizio carriera.</t>
         </is>
       </c>
       <c r="P4" s="6" t="n">
-        <v>39300000</v>
+        <v>200000</v>
       </c>
       <c r="Q4" s="6" t="n">
-        <v>8000000</v>
+        <v>200000</v>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="S4" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t>Media – 5 progetti finanziabili (stima: tasso storico non disponibile)</t>
+          <t>Bassa – 1 progetti finanziabili (stima: tasso storico non disponibile)</t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr">
@@ -1069,7 +1083,7 @@
         </is>
       </c>
       <c r="V4" s="4" t="n">
-        <v>46324</v>
+        <v>45614</v>
       </c>
       <c r="W4" s="2" t="n"/>
       <c r="X4" s="2" t="inlineStr">
@@ -1079,17 +1093,13 @@
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t>Comunità scientifica, decisori politici, fornitori di servizi sanitari e sociali, organizzazioni per la disabilità</t>
-        </is>
-      </c>
-      <c r="Z4" s="3" t="inlineStr">
-        <is>
-          <t>Consorzio: min. 3 enti indipendenti da 3 paesi UE/associati (regola standard, verificare il topic)</t>
-        </is>
-      </c>
+          <t>Public housing authorities/Indian housing authorities; Others (see text field entitled "Additional Information on Eligibility" for clarification); County governments; Independent school districts; Private institutions of higher education; For profit organizations other than small businesses; Nonprofits that do not have a 501(c)(3) status with the IRS, other than institutions of higher education; N</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="n"/>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>Stati membri UE e paesi associati (altri paesi secondo le condizioni del topic)</t>
+          <t>Ammessi anche enti non statunitensi (call NIH completa)</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
@@ -1099,26 +1109,26 @@
       </c>
       <c r="AC4" s="7" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-HLTH-2027-01-STAYHLTH-01</t>
+          <t>https://www.grants.gov/search-results-detail/357206</t>
         </is>
       </c>
       <c r="AD4" s="3" t="inlineStr">
         <is>
-          <t>Il bando supporta la ricerca clinica, assistenziale e tecnologica incentrata sulle persone con disabilità fisiche, mentali, intellettive o sensoriali a lungo termine, per favorire l'inclusione comunitaria e l'autonomia lungo tutto l'arco dell'esistenza. Tra le aree prioritarie rientrano l'accesso a servizi di abilitazione e riabilitazione, compresa la riabilitazione psicologica e l'impiego di tecnologie assistive avanzate volte al miglioramento o recupero delle capacità funzionali e alla riduzione delle limitazioni nelle attività quotidiane. Si finanziano inoltre nuovi modelli di cura integrati, prevenzione della perdita di autonomia e percorsi di deistituzionalizzazione. Possono partecipare consorzi transnazionali composti da ricercatori clinici, fornitori di assistenza sociosanitaria, associazioni di disabili e università.</t>
+          <t>Il bando NCMRR Early Career Research Award (R03), promosso dal National Institutes of Health (NIH), sostiene ricercatori a inizio carriera che intendono consolidare un percorso scientifico indipendente nel campo della riabilitazione medica. L'iniziativa finanzia progetti di ricerca clinica e di base allineati al Piano di Ricerca sulla Riabilitazione del NIH, con l'obiettivo di raccogliere dati preliminari sufficienti per future proposte R01. Sono ammissibili analisi secondarie di dati preesistenti, studi pilota indipendenti, sviluppo di metodologie di ricerca, studi traslazionali, ricerca sugli esiti e lo sviluppo di nuove tecnologie. Possono candidarsi istituzioni accademiche e di ricerca, comprese organizzazioni non profit ed enti stranieri con sede al di fuori degli Stati Uniti.</t>
         </is>
       </c>
       <c r="AE4" s="4" t="n">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="AF4" s="4" t="n">
-        <v>46313</v>
+        <v>46312</v>
       </c>
       <c r="AG4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>EU-HORIZON-HLTH-2027-02-DISEASE-14-two-stage</t>
+          <t>WEB-00773cbd93aa</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -1128,7 +1138,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1138,11 +1148,11 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Sperimentazioni cliniche per promuovere interventi innovativi nelle malattie neurodegenerative</t>
+          <t>Finanziamento ponte per la ricerca interrotta sulle malattie neurodegenerative (BFDN)</t>
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>46435</v>
+        <v>46325</v>
       </c>
       <c r="G5" s="5">
         <f>IF(F5="","",F5-TODAY())</f>
@@ -1150,72 +1160,74 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>In apertura</t>
+          <t>In scadenza (≤30 gg)</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Commissione europea</t>
+          <t>Michael J. Fox Foundation</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>EU Funding &amp; Tenders Portal</t>
+          <t>Michael J. Fox Foundation</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>Horizon Europe – HORIZON  Research and Innovation Actions</t>
+          <t>Bridge Funding for Disrupted Neurodegenerative Research Grant Program (BFDN) Powering the Next Generation of Research</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>Clinical trials for advancing innovative interventions for neurodegenerative diseases</t>
+          <t>Bridge Funding for Disrupted Neurodegenerative Research Grant Program (BFDN) Powering the Next Generation of Research</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Parkinson, Invecchiamento, Tecnologie riabilitazione, Altre malattie e riabilitazione</t>
+          <t>Parkinson, Invecchiamento, Altre malattie e riabilitazione</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>parkinson, dementi, alzheimer, aging, wearable, rehabilitat, neurodegenerat, huntington, neurological disorder</t>
+          <t>parkinson, dementi, alzheimer, neurodegenerat, neurological disease</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>Richiede esplicitamente l'integrazione di terapie riabilitative e training cognitivo in trial clinici per malattie neurodegenerative come Alzheimer e Parkinson.</t>
+          <t>Finanzia la continuità di progetti di ricerca su Parkinson, Alzheimer e demenze, senza una focalizzazione specifica sulla riabilitazione.</t>
         </is>
       </c>
       <c r="P5" s="6" t="n">
-        <v>39300000</v>
+        <v>250000</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>10000000</v>
+        <v>250000</v>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="S5" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t>Bassa – 4 progetti finanziabili (stima: tasso storico non disponibile)</t>
+          <t>Bassa – 1 progetti finanziabili (stima: tasso storico non disponibile)</t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t>Interamente finanziato</t>
-        </is>
-      </c>
-      <c r="V5" s="4" t="n">
-        <v>46324</v>
-      </c>
-      <c r="W5" s="2" t="n"/>
+          <t>Co-finanziamento richiesto (25% a carico del beneficiario)</t>
+        </is>
+      </c>
+      <c r="V5" s="4" t="n"/>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
+          <t>12 mesi</t>
+        </is>
+      </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
           <t>Ricerca</t>
@@ -1223,17 +1235,13 @@
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t>Università, centri di ricerca, ospedali, PMI, start-up, organizzazioni di pazienti e autorità sanitarie</t>
-        </is>
-      </c>
-      <c r="Z5" s="3" t="inlineStr">
-        <is>
-          <t>Consorzio: min. 3 enti indipendenti da 3 paesi UE/associati (regola standard, verificare il topic)</t>
-        </is>
-      </c>
+          <t>Ricercatori principali a inizio carriera (Early Stage Investigator secondo i criteri NIH o entro 7 anni dalla qualifica) titolari di grant federali statunitensi interrotti</t>
+        </is>
+      </c>
+      <c r="Z5" s="3" t="n"/>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>Stati membri UE e paesi associati (altri paesi secondo le condizioni del topic)</t>
+          <t>Mondiale</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
@@ -1243,16 +1251,16 @@
       </c>
       <c r="AC5" s="7" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-HLTH-2027-02-DISEASE-14-two-stage</t>
+          <t>https://www.michaeljfox.org/grant/bridge-funding-disrupted-neurodegenerative-research-grant-program-bfdn-powering-next</t>
         </is>
       </c>
       <c r="AD5" s="3" t="inlineStr">
         <is>
-          <t>Il bando di Horizon Europe finanzia la realizzazione di studi clinici precoci volti a verificare sicurezza ed efficacia di interventi innovativi per malattie neurodegenerative non rare come Parkinson e Alzheimer. Le proposte devono combinare un principio attivo terapeutico con approcci multidisciplinari complementari, inclusi esplicitamente terapie riabilitative, modifiche dello stile di vita e training cognitivo, oltre all'uso di tecnologie digitali per il monitoraggio a lungo termine. Possono partecipare consorzi internazionali composti da università, centri clinici, PMI, associazioni di pazienti e altri enti stabiliti negli Stati membri dell'UE o nei Paesi associati.</t>
+          <t>Il programma congiunto promosso da Alzheimer's Association, The Michael J. Fox Foundation e Robertson Foundation fornisce finanziamenti ponte per garantire la continuità a progetti di ricerca sulle malattie neurodegenerative (morbo di Parkinson, malattia di Alzheimer, demenza frontotemporale, demenza a corpi di Lewy e parkinsonismi atipici). L'iniziativa è specificamente rivolta a ricercatori a inizio carriera (Early Stage Investigator secondo i criteri NIH o entro 7 anni da tale qualifica) i cui finanziamenti federali statunitensi abbiano subito interruzioni, ritardi o tagli per cambiamenti operativi o di priorità. Il contributo, fino a un massimo di 250.000 dollari per una durata compresa tra 3 e 12 mesi, copre stipendi e costi diretti, richiedendo un cofinanziamento istituzionale fino al 25%.</t>
         </is>
       </c>
       <c r="AE5" s="4" t="n">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="AF5" s="4" t="n">
         <v>46312</v>
@@ -1262,7 +1270,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>GG-PAR-25-124</t>
+          <t>GG-PAR-25-226</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -1272,7 +1280,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1282,11 +1290,11 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Finanziamento di ricerca per ricercatori a inizio carriera NCMRR (R03 Clinical Trial facoltativo)</t>
+          <t>Sviluppo clinico precoce integrato (fase 1-2a) di nuovi agenti terapeutici per l'Alzheimer e le demenze correlate (UG3/UH3)</t>
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>46759</v>
+        <v>46345</v>
       </c>
       <c r="G6" s="5">
         <f>IF(F6="","",F6-TODAY())</f>
@@ -1294,7 +1302,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Aperto</t>
+          <t>In scadenza (≤30 gg)</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1309,46 +1317,40 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>National Institutes of Health – PAR-25-124</t>
+          <t>National Institutes of Health – PAR-25-226</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>NCMRR Early Career Research Award (R03 Clinical Trial Optional)</t>
+          <t>Seamless Early-Stage Clinical Drug Development (Phase 1 to 2a) for Novel therapeutic Agents for the Spectrum of Alzheimer's Disease (AD) and AD-related Dementias (ADRD) (UG3/UH3 Clinical Trial Required)</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Altre malattie e riabilitazione</t>
+          <t>Invecchiamento</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>rehabilitat</t>
+          <t>dementi, alzheimer</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>Bando dedicato specificamente alla ricerca di base e clinica in riabilitazione promosso dal NCMRR per ricercatori a inizio carriera.</t>
-        </is>
-      </c>
-      <c r="P6" s="6" t="n">
-        <v>200000</v>
-      </c>
-      <c r="Q6" s="6" t="n">
-        <v>200000</v>
-      </c>
+          <t>Riguarda la malattia di Alzheimer e le demenze correlate, ma è incentrato sullo sviluppo farmacologico precoce e non su interventi riabilitativi.</t>
+        </is>
+      </c>
+      <c r="P6" s="6" t="n"/>
+      <c r="Q6" s="6" t="n"/>
       <c r="R6" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="S6" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="S6" s="2" t="n"/>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t>Bassa – 1 progetti finanziabili (stima: tasso storico non disponibile)</t>
+          <t>Non stimabile – dati insufficienti</t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
@@ -1357,7 +1359,7 @@
         </is>
       </c>
       <c r="V6" s="4" t="n">
-        <v>45614</v>
+        <v>45618</v>
       </c>
       <c r="W6" s="2" t="n"/>
       <c r="X6" s="2" t="inlineStr">
@@ -1367,13 +1369,13 @@
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t>Private institutions of higher education; Small businesses; Public housing authorities/Indian housing authorities; Independent school districts; State governments; Special district governments; Public and State controlled institutions of higher education; For profit organizations other than small businesses; County governments; City or township governments; Others (see text field entitled "Additio</t>
+          <t>County governments; Independent school districts; Others (see text field entitled "Additional Information on Eligibility" for clarification); City or township governments; Public and State controlled institutions of higher education; Native American tribal governments (Federally recognized); Private institutions of higher education; Small businesses; State governments; Special district governments</t>
         </is>
       </c>
       <c r="Z6" s="3" t="n"/>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>Ammessi anche enti non statunitensi</t>
+          <t>Ammessi anche enti non statunitensi (call NIH completa)</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
@@ -1383,16 +1385,16 @@
       </c>
       <c r="AC6" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/357206</t>
+          <t>https://www.grants.gov/search-results-detail/357343</t>
         </is>
       </c>
       <c r="AD6" s="3" t="inlineStr">
         <is>
-          <t>Il bando NCMRR Early Career Research Award (R03), promosso dal National Institutes of Health (NIH), sostiene ricercatori a inizio carriera che intendono consolidare un percorso scientifico indipendente nel campo della riabilitazione medica. L'iniziativa finanzia progetti di ricerca clinica e di base allineati al Piano di Ricerca sulla Riabilitazione del NIH, con l'obiettivo di raccogliere dati preliminari sufficienti per future proposte R01. Sono ammissibili analisi secondarie di dati preesistenti, studi pilota indipendenti, sviluppo di metodologie di ricerca, studi traslazionali, ricerca sugli esiti e lo sviluppo di nuove tecnologie. Possono candidarsi istituzioni accademiche e di ricerca, comprese organizzazioni non profit ed enti stranieri con sede al di fuori degli Stati Uniti.</t>
+          <t>Il bando invita a presentare proposte per lo sviluppo clinico precoce di nuovi agenti farmacologici non amiloidi e non tau per la malattia di Alzheimer e le demenze correlate. Tramite il meccanismo a fasi UG3/UH3, il bando unisce protocolli di sperimentazione di fase 1 con fasi 1b/2a per valutare sicurezza, tollerabilità ed efficacia su sintomi cognitivi o neuropsichiatrici in diversi stadi di malattia. L'avanzamento tra le fasi è subordinato a traguardi predefiniti. Possono partecipare istituti accademici, organizzazioni sanitarie, enti di ricerca pubblici e privati e istituzioni straniere non statunitensi.</t>
         </is>
       </c>
       <c r="AE6" s="4" t="n">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="AF6" s="4" t="n">
         <v>46312</v>
@@ -1402,7 +1404,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>GG-PAR-27-065</t>
+          <t>EU-HORIZON-HLTH-2027-02-DISEASE-01-two-stage</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -1412,7 +1414,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -1422,11 +1424,11 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Trial clinici esplorativi e di efficacia del NINDS (UG3/UH3 - Clinical Trial obbligatorio)</t>
+          <t>Interventi sanitari innovativi per le malattie non trasmissibili</t>
         </is>
       </c>
       <c r="F7" s="4" t="n">
-        <v>47186</v>
+        <v>46435</v>
       </c>
       <c r="G7" s="5">
         <f>IF(F7="","",F7-TODAY())</f>
@@ -1434,55 +1436,61 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Aperto</t>
+          <t>In apertura</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>National Institutes of Health</t>
+          <t>Commissione europea</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>Grants.gov</t>
+          <t>EU Funding &amp; Tenders Portal</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>National Institutes of Health – PAR-27-065</t>
+          <t>Horizon Europe – HORIZON  Research and Innovation Actions</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>NINDS Efficacy and Exploratory Clinical Trials (UG3/UH3 - Clinical Trial Required)</t>
+          <t>Innovative healthcare interventions for non-communicable diseases</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Ictus, Altre malattie e riabilitazione</t>
+          <t>Tecnologie riabilitazione, Altre malattie e riabilitazione</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>stroke, rehabilitat, neurological disorder</t>
+          <t>wearable, disabilit</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>Finanzia trial clinici neurologici e ammette esplicitamente terapie e interventi di riabilitazione lungo tutto l'arco della vita.</t>
-        </is>
-      </c>
-      <c r="P7" s="6" t="n"/>
-      <c r="Q7" s="6" t="n"/>
+          <t>Bando incentrato su interventi innovativi e gestione clinica di patologie croniche cardiache e respiratorie, senza focus esclusivo sulla riabilitazione.</t>
+        </is>
+      </c>
+      <c r="P7" s="6" t="n">
+        <v>63800000</v>
+      </c>
+      <c r="Q7" s="6" t="n">
+        <v>8000000</v>
+      </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="n"/>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="n">
+        <v>8</v>
+      </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t>Non stimabile – dati insufficienti</t>
+          <t>Media – 8 progetti finanziabili (stima: tasso storico non disponibile)</t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
@@ -1491,7 +1499,7 @@
         </is>
       </c>
       <c r="V7" s="4" t="n">
-        <v>46265</v>
+        <v>46324</v>
       </c>
       <c r="W7" s="2" t="n"/>
       <c r="X7" s="2" t="inlineStr">
@@ -1501,17 +1509,17 @@
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t>County governments; Native American tribal organizations (other than Federally recognized tribal governments); For profit organizations other than small businesses; Small businesses; Special district governments; Private institutions of higher education; Nonprofits having a 501(c)(3) status with the IRS, other than institutions of higher education; Others (see text field entitled "Additional Infor</t>
+          <t>Enti di ricerca, università, strutture sanitarie, PMI, startup, autorità regolatorie e organizzazioni di pazienti.</t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t>Non sono ammessi sub-accordi o subappalti a entità estere; le organizzazioni estere possono candidarsi direttamente come capofila</t>
+          <t>Consorzio: min. 3 enti indipendenti da 3 paesi UE/associati (regola standard, verificare il topic)</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>Ammessi anche enti non statunitensi</t>
+          <t>Stati membri UE e paesi associati (altri paesi secondo le condizioni del topic)</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
@@ -1521,16 +1529,16 @@
       </c>
       <c r="AC7" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/360404</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-HLTH-2027-02-DISEASE-01-two-stage</t>
         </is>
       </c>
       <c r="AD7" s="3" t="inlineStr">
         <is>
-          <t>Questa opportunità di finanziamento (UG3/UH3) promossa dal National Institute of Neurological Disorders and Stroke (NINDS) sostiene trial clinici proposti da ricercatori per affrontare quesiti coerenti con la missione dell'istituto. Il bando finanzia sperimentazioni cliniche precoci, intermedie o confermative di fase 3 e studi di efficacia comparativa su molecole, farmaci biologici, dispositivi medici o interventi chirurgici, comportamentali, dietetici e terapie riabilitative, per tutte le età. Possono partecipare enti accademici, ospedalieri e organizzazioni di ricerca, incluse entità straniere non statunitensi come capofila. Non sono tuttavia consentiti subappalti o sub-accordi finanziari internazionali verso altre entità estere nell'ambito dello stesso progetto.</t>
+          <t>Il bando punta a ridurre l'impatto di specifiche malattie croniche non trasmissibili, tra cui patologie cardiovascolari, diabete, malattie respiratorie e renali croniche. Si finanzia la realizzazione di studi clinici in fase precoce per validare interventi terapeutici o di gestione della patologia innovativi o perfezionati, supportati da prove di concetto su sicurezza ed efficacia clinica. Le proposte devono integrare tecnologie digitali (come intelligenza artificiale o dispositivi indossabili) per il monitoraggio a lungo termine a domicilio. Possono partecipare consorzi internazionali composti da università, enti di ricerca clinica, ospedali, piccole e medie imprese, startup e organizzazioni di pazienti, promuovendo anche l'inclusione di competenze socio-umanistiche e l'interazione con autorità regolatorie per favorire la futura scalabilità degli interventi.</t>
         </is>
       </c>
       <c r="AE7" s="4" t="n">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="AF7" s="4" t="n">
         <v>46312</v>
@@ -1540,7 +1548,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>WEB-00773cbd93aa</t>
+          <t>EU-HORIZON-HLTH-2027-01-DISEASE-10</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -1560,11 +1568,11 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Finanziamento ponte per la ricerca interrotta sulle malattie neurodegenerative (BFDN)</t>
+          <t>Prevenzione e gestione delle malattie croniche non trasmissibili nei bambini e nei giovani (GACD)</t>
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>46325</v>
+        <v>46435</v>
       </c>
       <c r="G8" s="5">
         <f>IF(F8="","",F8-TODAY())</f>
@@ -1572,74 +1580,72 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>In scadenza (≤30 gg)</t>
+          <t>In apertura</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Michael J. Fox Foundation</t>
+          <t>Commissione europea</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>Michael J. Fox Foundation</t>
+          <t>EU Funding &amp; Tenders Portal</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>Bridge Funding for Disrupted Neurodegenerative Research Grant Program (BFDN) Powering the Next Generation of Research</t>
+          <t>Horizon Europe – HORIZON  Research and Innovation Actions</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>Bridge Funding for Disrupted Neurodegenerative Research Grant Program (BFDN) Powering the Next Generation of Research</t>
+          <t>Prevention and management of chronic non-communicable diseases in children and young people (GACD)</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Parkinson, Invecchiamento, Altre malattie e riabilitazione</t>
+          <t>Altre malattie e riabilitazione</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>parkinson, dementi, alzheimer, neurodegenerat, neurological disease</t>
+          <t>neurological disorder, disabilit</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>Finanzia la continuità di progetti di ricerca su Parkinson, Alzheimer e demenze, senza una focalizzazione specifica sulla riabilitazione.</t>
+          <t>Finanzia la ricerca sull'implementazione per la gestione di patologie croniche non trasmissibili nei giovani, ambito che include percorsi di cura complessi ma non esclusivamente riabilitativi.</t>
         </is>
       </c>
       <c r="P8" s="6" t="n">
-        <v>250000</v>
+        <v>11800000</v>
       </c>
       <c r="Q8" s="6" t="n">
-        <v>250000</v>
+        <v>4000000</v>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="S8" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t>Bassa – 1 progetti finanziabili (stima: tasso storico non disponibile)</t>
+          <t>Bassa – 3 progetti finanziabili (stima: tasso storico non disponibile)</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t>Co-finanziamento richiesto (25% a carico del beneficiario)</t>
-        </is>
-      </c>
-      <c r="V8" s="4" t="n"/>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>12 mesi</t>
-        </is>
-      </c>
+          <t>Interamente finanziato</t>
+        </is>
+      </c>
+      <c r="V8" s="4" t="n">
+        <v>46324</v>
+      </c>
+      <c r="W8" s="2" t="n"/>
       <c r="X8" s="2" t="inlineStr">
         <is>
           <t>Ricerca</t>
@@ -1647,13 +1653,17 @@
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t>Ricercatori principali a inizio carriera (Early Stage Investigator secondo i criteri NIH o entro 7 anni dalla qualifica) titolari di grant federali statunitensi interrotti</t>
-        </is>
-      </c>
-      <c r="Z8" s="3" t="n"/>
+          <t>Ricercatori, professionisti sanitari, erogatori di servizi, decisori politici e stakeholder locali</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t>Consorzio: min. 3 enti indipendenti da 3 paesi UE/associati (regola standard, verificare il topic)</t>
+        </is>
+      </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>Mondiale</t>
+          <t>Stati membri UE e paesi associati (altri paesi secondo le condizioni del topic)</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
@@ -1663,26 +1673,26 @@
       </c>
       <c r="AC8" s="7" t="inlineStr">
         <is>
-          <t>https://www.michaeljfox.org/grant/bridge-funding-disrupted-neurodegenerative-research-grant-program-bfdn-powering-next</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-HLTH-2027-01-DISEASE-10</t>
         </is>
       </c>
       <c r="AD8" s="3" t="inlineStr">
         <is>
-          <t>Il programma congiunto promosso da Alzheimer's Association, The Michael J. Fox Foundation e Robertson Foundation fornisce finanziamenti ponte per garantire la continuità a progetti di ricerca sulle malattie neurodegenerative (morbo di Parkinson, malattia di Alzheimer, demenza frontotemporale, demenza a corpi di Lewy e parkinsonismi atipici). L'iniziativa è specificamente rivolta a ricercatori a inizio carriera (Early Stage Investigator secondo i criteri NIH o entro 7 anni da tale qualifica) i cui finanziamenti federali statunitensi abbiano subito interruzioni, ritardi o tagli per cambiamenti operativi o di priorità. Il contributo, fino a un massimo di 250.000 dollari per una durata compresa tra 3 e 12 mesi, copre stipendi e costi diretti, richiedendo un cofinanziamento istituzionale fino al 25%.</t>
+          <t>In collaborazione con la Global Alliance for Chronic Diseases (GACD), il bando sostiene la ricerca sull'implementazione di interventi evidence-based per la prevenzione, la diagnosi precoce e la gestione a lungo termine delle malattie croniche non trasmissibili in soggetti tra 1 e 24 anni. Il focus riguarda popolazioni vulnerabili in paesi a basso e medio reddito o comunità svantaggiate in paesi ad alto reddito. Si finanziano modelli di cura integrati, percorsi di transizione dall'assistenza pediatrica a quella per adulti, supporto ai caregiver e strategie costo-efficaci. Possono partecipare ricercatori, operatori sanitari e istituzioni di ricerca appartenenti a consorzi eleggibili secondo le regole di Horizon Europe.</t>
         </is>
       </c>
       <c r="AE8" s="4" t="n">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="AF8" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AG8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>GG-PAR-27-007</t>
+          <t>WEB-6768384ca0cb</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -1702,58 +1712,60 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Trial clinici e studi ancillari condotti all'interno delle reti di ricerca clinica finanziate dal NIH (UG3/UH3)</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>46336</v>
-      </c>
+          <t>Programma per lo sviluppo della pipeline terapeutica nella malattia di Parkinson</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="n"/>
       <c r="G9" s="5">
         <f>IF(F9="","",F9-TODAY())</f>
         <v/>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>In scadenza (≤30 gg)</t>
+          <t>Scadenza da verificare</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>National Institutes of Health</t>
+          <t>Michael J. Fox Foundation</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>Grants.gov</t>
+          <t>Michael J. Fox Foundation</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>National Institutes of Health – PAR-27-007</t>
+          <t>Parkinson's Disease Therapeutics Pipeline Program</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>Clinical Trials and Ancillary Studies Conducted within NIH-Funded Clinical Trial Research Networks (UG3/UH3 - Clinical Trial Required)</t>
+          <t>Parkinson's Disease Therapeutics Pipeline Program</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Ictus, Altre malattie e riabilitazione</t>
+          <t>Parkinson</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>stroke, neurological disorder</t>
+          <t>parkinson</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>Finanzia trial clinici in reti neurologiche che possono comprendere patologie di interesse riabilitativo come l'ictus, pur non focalizzandosi sulla riabilitazione.</t>
-        </is>
-      </c>
-      <c r="P9" s="6" t="n"/>
-      <c r="Q9" s="6" t="n"/>
+          <t>Focalizzato sullo sviluppo terapeutico e farmacologico preclinico e clinico per il Parkinson, senza un focus specifico sulla riabilitazione.</t>
+        </is>
+      </c>
+      <c r="P9" s="6" t="n">
+        <v>250000</v>
+      </c>
+      <c r="Q9" s="6" t="n">
+        <v>5000000</v>
+      </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1767,15 +1779,13 @@
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t>Interamente finanziato</t>
-        </is>
-      </c>
-      <c r="V9" s="4" t="n">
-        <v>46097</v>
-      </c>
+          <t>Non indicato</t>
+        </is>
+      </c>
+      <c r="V9" s="4" t="n"/>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>84 mesi</t>
+          <t>36 mesi</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
@@ -1785,13 +1795,17 @@
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">County governments; Nonprofits that do not have a 501(c)(3) status with the IRS, other than institutions of higher education; Independent school districts; Public and State controlled institutions of higher education; For profit organizations other than small businesses; Others (see text field entitled "Additional Information on Eligibility" for clarification); State governments; City or township </t>
-        </is>
-      </c>
-      <c r="Z9" s="3" t="n"/>
+          <t>Imprese biotech/pharma, partenariati accademia-industria e istituti accademici</t>
+        </is>
+      </c>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t>Aperto a collaborazioni accademia-industria, singole aziende o progetti a guida accademica</t>
+        </is>
+      </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>Ammessi anche enti non statunitensi</t>
+          <t>Mondiale</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
@@ -1801,16 +1815,16 @@
       </c>
       <c r="AC9" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/361522</t>
+          <t>https://www.michaeljfox.org/grant/parkinsons-disease-therapeutics-pipeline-program</t>
         </is>
       </c>
       <c r="AD9" s="3" t="inlineStr">
         <is>
-          <t>Il bando, promosso dal NINDS insieme ad altri istituti del NIH tramite lo schema cooperativo a due fasi UG3/UH3, intende sostenere la conduzione di studi clinici multicentrici e studi ancillari all'interno delle reti di ricerca clinica già finanziate e attive del NIH. Il programma prevede una fase iniziale di pianificazione e avvio fino a due anni (UG3), con possibile passaggio a una fase operativa fino a ulteriori cinque anni (UH3) al raggiungimento di specifici traguardi. Possono candidarsi enti di ricerca, università, organizzazioni pubbliche o private ed enti stranieri non statunitensi per testare interventi diagnostici e terapeutici in ambito neurologico.</t>
+          <t>Il Therapeutics Pipeline Program della Michael J. Fox Foundation finanzia lo sviluppo preclinico e clinico di interventi terapeutici modificanti la malattia o mirati al controllo sintomatico del Parkinson, integrando strumenti biomarcatori decisionali. Il programma supporta progetti da uno a tre anni con contributi compresi generalmente tra 250.000 e oltre 5 milioni di dollari, a seconda della fase di avanzamento. La candidatura è aperta a imprese biotech, collaborazioni accademia-industria e, in casi specifici, a gruppi esclusivamente accademici. Il processo di selezione è strutturato in due fasi: invio continuo di pre-proposte e, su invito, presentazione della proposta completa secondo scadenze cicliche periodiche. Sono esclusi studi su integratori alimentari o scoperta di target precoci.</t>
         </is>
       </c>
       <c r="AE9" s="4" t="n">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="AF9" s="4" t="n">
         <v>46312</v>
@@ -1820,31 +1834,31 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>GG-PAR-25-226</t>
+          <t>GG-RFA-NS-26-028</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Sì</t>
+          <t>Da verificare</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Ricerca clinica</t>
+          <t>Tecnologia / innovazione</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Sviluppo clinico precoce integrato (fase 1-2a) di nuovi agenti terapeutici per l'Alzheimer e le demenze correlate (UG3/UH3)</t>
+          <t>Iniziativa HEAL: ottimizzazione dei dispositivi medici terapeutici attraverso la ricerca meccanicistica interdisciplinare (RM1)</t>
         </is>
       </c>
       <c r="F10" s="4" t="n">
-        <v>46345</v>
+        <v>46325</v>
       </c>
       <c r="G10" s="5">
         <f>IF(F10="","",F10-TODAY())</f>
@@ -1852,7 +1866,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Aperto</t>
+          <t>In scadenza (≤30 gg)</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1867,27 +1881,27 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>National Institutes of Health – PAR-25-226</t>
+          <t>National Institutes of Health – RFA-NS-26-028</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>Seamless Early-Stage Clinical Drug Development (Phase 1 to 2a) for Novel therapeutic Agents for the Spectrum of Alzheimer's Disease (AD) and AD-related Dementias (ADRD) (UG3/UH3 Clinical Trial Required)</t>
+          <t>HEAL Initiative: Optimization of Therapeutic Medical Devices through Team Science Mechanistic Research (RM1)</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Invecchiamento</t>
+          <t>Ictus, Altre malattie e riabilitazione</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>dementi, alzheimer</t>
+          <t>stroke, neurological disorder</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>Riguarda la malattia di Alzheimer e le demenze correlate, ma è incentrato sullo sviluppo farmacologico precoce e non su interventi riabilitativi.</t>
+          <t>Supporta la ricerca sui meccanismi d'azione di dispositivi medici terapeutici per patologie neurologiche e dolore cronico, altamente rilevanti per la neuroriabilitazione.</t>
         </is>
       </c>
       <c r="P10" s="6" t="n"/>
@@ -1897,10 +1911,12 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="S10" s="2" t="n"/>
+      <c r="S10" s="2" t="n">
+        <v>4</v>
+      </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t>Non stimabile – dati insufficienti</t>
+          <t>Bassa – 4 progetti finanziabili (stima: tasso storico non disponibile)</t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
@@ -1909,7 +1925,7 @@
         </is>
       </c>
       <c r="V10" s="4" t="n">
-        <v>45618</v>
+        <v>46097</v>
       </c>
       <c r="W10" s="2" t="n"/>
       <c r="X10" s="2" t="inlineStr">
@@ -1919,13 +1935,17 @@
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t>For profit organizations other than small businesses; Nonprofits that do not have a 501(c)(3) status with the IRS, other than institutions of higher education; Native American tribal organizations (other than Federally recognized tribal governments); Native American tribal governments (Federally recognized); State governments; City or township governments; Nonprofits having a 501(c)(3) status with</t>
-        </is>
-      </c>
-      <c r="Z10" s="3" t="n"/>
+          <t>Small businesses; Native American tribal organizations (other than Federally recognized tribal governments); Private institutions of higher education; Native American tribal governments (Federally recognized); Nonprofits that do not have a 501(c)(3) status with the IRS, other than institutions of higher education; State governments; Others (see text field entitled "Additional Information on Eligib</t>
+        </is>
+      </c>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
+          <t>Team scientifici interdisciplinari comprendenti competenze ingegneristiche, biologiche, computazionali e cliniche</t>
+        </is>
+      </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>Ammessi anche enti non statunitensi</t>
+          <t>Enti esteri: da verificare nel bando</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
@@ -1935,16 +1955,16 @@
       </c>
       <c r="AC10" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/357343</t>
+          <t>https://www.grants.gov/search-results-detail/361520</t>
         </is>
       </c>
       <c r="AD10" s="3" t="inlineStr">
         <is>
-          <t>Il bando invita a presentare proposte per lo sviluppo clinico precoce di nuovi agenti farmacologici non amiloidi e non tau per la malattia di Alzheimer e le demenze correlate. Tramite il meccanismo a fasi UG3/UH3, il bando unisce protocolli di sperimentazione di fase 1 con fasi 1b/2a per valutare sicurezza, tollerabilità ed efficacia su sintomi cognitivi o neuropsichiatrici in diversi stadi di malattia. L'avanzamento tra le fasi è subordinato a traguardi predefiniti. Possono partecipare istituti accademici, organizzazioni sanitarie, enti di ricerca pubblici e privati e istituzioni straniere non statunitensi.</t>
+          <t>Il National Institute of Neurological Disorders and Stroke (NINDS), nell'ambito dell'iniziativa NIH HEAL, preannuncia un'opportunità di finanziamento destinata a indagare i meccanismi d'azione dei dispositivi medici terapeutici per ottimizzare i risultati clinici nelle patologie neurologiche e nel trattamento del dolore. La call intende finanziare team scientifici altamente interdisciplinari (con competenze che spaziano dall'ingegneria e biologia alla clinica, biostatistica, intelligenza artificiale e sperimentazioni cliniche). Le attività ammissibili comprendono studi clinici meccanicistici, modelli computazionali o simulazioni e ricerche precliniche su modelli animali, applicabili sia a dispositivi sperimentali sia a tecnologie già approvate dalla FDA e impiegate nella pratica clinica. La partecipazione è aperta anche a istituzioni di ricerca estere non statunitensi.</t>
         </is>
       </c>
       <c r="AE10" s="4" t="n">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="AF10" s="4" t="n">
         <v>46312</v>
@@ -1954,17 +1974,17 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>EU-HORIZON-HLTH-2027-01-DISEASE-10</t>
+          <t>GG-HT942526SCIRPTRA</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Sì</t>
+          <t>Da verificare</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1974,11 +1994,11 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Prevenzione e gestione delle malattie croniche non trasmissibili nei bambini e nei giovani (GACD)</t>
+          <t>Programma di ricerca sulle lesioni del midollo spinale del Dipartimento della Difesa: finanziamento per la ricerca traslazionale</t>
         </is>
       </c>
       <c r="F11" s="4" t="n">
-        <v>46435</v>
+        <v>46338</v>
       </c>
       <c r="G11" s="5">
         <f>IF(F11="","",F11-TODAY())</f>
@@ -1986,27 +2006,27 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>In apertura</t>
+          <t>In scadenza (≤30 gg)</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Commissione europea</t>
+          <t>Defense Health Agency Contracting Activity - DHACA</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>EU Funding &amp; Tenders Portal</t>
+          <t>Grants.gov</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>Horizon Europe – HORIZON  Research and Innovation Actions</t>
+          <t>Defense Health Agency Contracting Activity - DHACA – HT942526SCIRPTRA</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>Prevention and management of chronic non-communicable diseases in children and young people (GACD)</t>
+          <t>DoW Spinal Cord Injury, Translational Research Award</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -2016,31 +2036,29 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>neurological disorder, disabilit</t>
+          <t>spinal cord injur</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>Finanzia la ricerca sull'implementazione per la gestione di patologie croniche non trasmissibili nei giovani, ambito che include percorsi di cura complessi ma non esclusivamente riabilitativi.</t>
+          <t>Dedicato alla ricerca traslazionale per l'applicazione clinica nelle lesioni del midollo spinale, patologia cardine della riabilitazione neurologica.</t>
         </is>
       </c>
       <c r="P11" s="6" t="n">
-        <v>11800000</v>
-      </c>
-      <c r="Q11" s="6" t="n">
-        <v>4000000</v>
-      </c>
+        <v>8320000</v>
+      </c>
+      <c r="Q11" s="6" t="n"/>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="S11" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t>Bassa – 3 progetti finanziabili (stima: tasso storico non disponibile)</t>
+          <t>Bassa – 4 progetti finanziabili (stima: tasso storico non disponibile)</t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
@@ -2049,7 +2067,7 @@
         </is>
       </c>
       <c r="V11" s="4" t="n">
-        <v>46324</v>
+        <v>46147</v>
       </c>
       <c r="W11" s="2" t="n"/>
       <c r="X11" s="2" t="inlineStr">
@@ -2059,17 +2077,17 @@
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t>Ricercatori, professionisti sanitari, erogatori di servizi, decisori politici e stakeholder locali</t>
+          <t>Unrestricted (i.e., open to any type of entity above), subject to any clarification in text field entitled "Additional Information on Eligibility"</t>
         </is>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
-          <t>Consorzio: min. 3 enti indipendenti da 3 paesi UE/associati (regola standard, verificare il topic)</t>
+          <t>Obbligatorio almeno un partner comunitario esperto per esperienza diretta di lesione midollare; ammessa opzione a due PI con ricercatore junior.</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>Stati membri UE e paesi associati (altri paesi secondo le condizioni del topic)</t>
+          <t>Enti esteri: da verificare nel bando</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
@@ -2079,16 +2097,16 @@
       </c>
       <c r="AC11" s="7" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-HLTH-2027-01-DISEASE-10</t>
+          <t>https://www.grants.gov/search-results-detail/362222</t>
         </is>
       </c>
       <c r="AD11" s="3" t="inlineStr">
         <is>
-          <t>In collaborazione con la Global Alliance for Chronic Diseases (GACD), il bando sostiene la ricerca sull'implementazione di interventi evidence-based per la prevenzione, la diagnosi precoce e la gestione a lungo termine delle malattie croniche non trasmissibili in soggetti tra 1 e 24 anni. Il focus riguarda popolazioni vulnerabili in paesi a basso e medio reddito o comunità svantaggiate in paesi ad alto reddito. Si finanziano modelli di cura integrati, percorsi di transizione dall'assistenza pediatrica a quella per adulti, supporto ai caregiver e strategie costo-efficaci. Possono partecipare ricercatori, operatori sanitari e istituzioni di ricerca appartenenti a consorzi eleggibili secondo le regole di Horizon Europe.</t>
+          <t>Il Translational Research Award, nell'ambito del programma di ricerca sulle lesioni del midollo spinale (SCIRP), sostiene progetti di ricerca traslazionale mirati ad accelerare il passaggio di idee e interventi innovativi dal laboratorio alle applicazioni cliniche per pazienti con lesioni midollari. Le proposte devono includere obbligatoriamente come partner almeno un membro o consulente della comunità con lesione spinale vissuta in prima persona o un rappresentante di organizzazioni attive nel settore. È prevista l'opzione di collaborazione paritaria che consente a un ricercatore esperto di affiancare un ricercatore a inizio carriera nella guida del progetto. Possono partecipare atenei, enti ospedalieri, istituti di ricerca pubblici o privati e organizzazioni specializzate.</t>
         </is>
       </c>
       <c r="AE11" s="4" t="n">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="AF11" s="4" t="n">
         <v>46313</v>
@@ -2098,17 +2116,17 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>EU-HORIZON-HLTH-2027-02-DISEASE-01-two-stage</t>
+          <t>GG-HT942526SCIRPCTA</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Sì</t>
+          <t>Da verificare</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -2118,11 +2136,11 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Interventi sanitari innovativi per le malattie non trasmissibili</t>
+          <t>DoW Ricerca sulle lesioni del midollo spinale, finanziamento per trial clinici</t>
         </is>
       </c>
       <c r="F12" s="4" t="n">
-        <v>46435</v>
+        <v>46338</v>
       </c>
       <c r="G12" s="5">
         <f>IF(F12="","",F12-TODAY())</f>
@@ -2130,61 +2148,59 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>In apertura</t>
+          <t>In scadenza (≤30 gg)</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Commissione europea</t>
+          <t>Defense Health Agency Contracting Activity - DHACA</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>EU Funding &amp; Tenders Portal</t>
+          <t>Grants.gov</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>Horizon Europe – HORIZON  Research and Innovation Actions</t>
+          <t>Defense Health Agency Contracting Activity - DHACA – HT942526SCIRPCTA</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>Innovative healthcare interventions for non-communicable diseases</t>
+          <t>DoW Spinal Cord Injury, Clinical Trial Award</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Tecnologie riabilitazione, Altre malattie e riabilitazione</t>
+          <t>Altre malattie e riabilitazione</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>wearable, disabilit</t>
+          <t>spinal cord injur</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>Bando incentrato su interventi innovativi e gestione clinica di patologie croniche cardiache e respiratorie, senza focus esclusivo sulla riabilitazione.</t>
+          <t>Finanzia trial clinici focalizzati sul trattamento e sulla gestione funzionale delle lesioni del midollo spinale.</t>
         </is>
       </c>
       <c r="P12" s="6" t="n">
-        <v>63800000</v>
-      </c>
-      <c r="Q12" s="6" t="n">
-        <v>8000000</v>
-      </c>
+        <v>9760000</v>
+      </c>
+      <c r="Q12" s="6" t="n"/>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="S12" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t>Media – 8 progetti finanziabili (stima: tasso storico non disponibile)</t>
+          <t>Bassa – 2 progetti finanziabili (stima: tasso storico non disponibile)</t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
@@ -2193,7 +2209,7 @@
         </is>
       </c>
       <c r="V12" s="4" t="n">
-        <v>46324</v>
+        <v>46147</v>
       </c>
       <c r="W12" s="2" t="n"/>
       <c r="X12" s="2" t="inlineStr">
@@ -2203,17 +2219,17 @@
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t>Enti di ricerca, università, strutture sanitarie, PMI, startup, autorità regolatorie e organizzazioni di pazienti.</t>
+          <t>Unrestricted (i.e., open to any type of entity above), subject to any clarification in text field entitled "Additional Information on Eligibility"</t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t>Consorzio: min. 3 enti indipendenti da 3 paesi UE/associati (regola standard, verificare il topic)</t>
+          <t>Obbligatori almeno 2 partner della comunità con esperienza di lesione midollare; possibile collaborazione tra 2 PI</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>Stati membri UE e paesi associati (altri paesi secondo le condizioni del topic)</t>
+          <t>Enti esteri: da verificare nel bando</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
@@ -2223,36 +2239,36 @@
       </c>
       <c r="AC12" s="7" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-HLTH-2027-02-DISEASE-01-two-stage</t>
+          <t>https://www.grants.gov/search-results-detail/362224</t>
         </is>
       </c>
       <c r="AD12" s="3" t="inlineStr">
         <is>
-          <t>Il bando punta a ridurre l'impatto di specifiche malattie croniche non trasmissibili, tra cui patologie cardiovascolari, diabete, malattie respiratorie e renali croniche. Si finanzia la realizzazione di studi clinici in fase precoce per validare interventi terapeutici o di gestione della patologia innovativi o perfezionati, supportati da prove di concetto su sicurezza ed efficacia clinica. Le proposte devono integrare tecnologie digitali (come intelligenza artificiale o dispositivi indossabili) per il monitoraggio a lungo termine a domicilio. Possono partecipare consorzi internazionali composti da università, enti di ricerca clinica, ospedali, piccole e medie imprese, startup e organizzazioni di pazienti, promuovendo anche l'inclusione di competenze socio-umanistiche e l'interazione con autorità regolatorie per favorire la futura scalabilità degli interventi.</t>
+          <t>Il bando Clinical Trial Award del programma SCIRP (anno fiscale 2026) finanzia la rapida attuazione di studi clinici con un potenziale impatto significativo sul trattamento o sulla gestione delle persone con lesione del midollo spinale. L'opportunità include un'opzione di partenariato per ricercatori all'inizio della carriera (Early-Career Partnership Option), che consente la partecipazione di due Principal Investigator, purché almeno uno sia un ricercatore junior. Le proposte devono obbligatoriamente coinvolgere almeno due rappresentanti o partner della comunità con esperienza diretta di lesione midollare, che collaboreranno attivamente fornendo consulenza durante l'intera pianificazione e implementazione dello studio clinico.</t>
         </is>
       </c>
       <c r="AE12" s="4" t="n">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="AF12" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AG12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>WEB-6768384ca0cb</t>
+          <t>GG-HT942526SCIRPCTRA</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Sì</t>
+          <t>Da verificare</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -2262,82 +2278,82 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Programma per lo sviluppo della pipeline terapeutica nella malattia di Parkinson</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="n"/>
+          <t>DoW Ricerca sulle lesioni del midollo spinale, finanziamento per la ricerca clinica traslazionale</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>46338</v>
+      </c>
       <c r="G13" s="5">
         <f>IF(F13="","",F13-TODAY())</f>
         <v/>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Scadenza da verificare</t>
+          <t>In scadenza (≤30 gg)</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Michael J. Fox Foundation</t>
+          <t>Defense Health Agency Contracting Activity - DHACA</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>Michael J. Fox Foundation</t>
+          <t>Grants.gov</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Parkinson's Disease Therapeutics Pipeline Program</t>
+          <t>Defense Health Agency Contracting Activity - DHACA – HT942526SCIRPCTRA</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>Parkinson's Disease Therapeutics Pipeline Program</t>
+          <t>DoW Spinal Cord Injury, Clinical Translation Research Award</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Parkinson</t>
+          <t>Altre malattie e riabilitazione</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>parkinson</t>
+          <t>rehabilitat, spinal cord injur</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>Focalizzato sullo sviluppo terapeutico e farmacologico preclinico e clinico per il Parkinson, senza un focus specifico sulla riabilitazione.</t>
+          <t>Finanzia ricerca clinica traslazionale volta a identificare le opzioni più efficaci di riabilitazione e trattamento nelle lesioni midollari.</t>
         </is>
       </c>
       <c r="P13" s="6" t="n">
-        <v>250000</v>
-      </c>
-      <c r="Q13" s="6" t="n">
-        <v>5000000</v>
-      </c>
+        <v>6120000</v>
+      </c>
+      <c r="Q13" s="6" t="n"/>
       <c r="R13" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="S13" s="2" t="n"/>
+      <c r="S13" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t>Non stimabile – dati insufficienti</t>
+          <t>Bassa – 3 progetti finanziabili (stima: tasso storico non disponibile)</t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t>Non indicato</t>
-        </is>
-      </c>
-      <c r="V13" s="4" t="n"/>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>36 mesi</t>
-        </is>
-      </c>
+          <t>Interamente finanziato</t>
+        </is>
+      </c>
+      <c r="V13" s="4" t="n">
+        <v>46147</v>
+      </c>
+      <c r="W13" s="2" t="n"/>
       <c r="X13" s="2" t="inlineStr">
         <is>
           <t>Ricerca</t>
@@ -2345,17 +2361,17 @@
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t>Imprese biotech/pharma, partenariati accademia-industria e istituti accademici</t>
+          <t>Unrestricted (i.e., open to any type of entity above), subject to any clarification in text field entitled "Additional Information on Eligibility"</t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t>Aperto a collaborazioni accademia-industria, singole aziende o progetti a guida accademica</t>
+          <t>Obbligatori almeno due partner della comunità di pazienti; opzione con due PI di cui uno a inizio carriera</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>Mondiale</t>
+          <t>Enti esteri: da verificare nel bando</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
@@ -2365,16 +2381,16 @@
       </c>
       <c r="AC13" s="7" t="inlineStr">
         <is>
-          <t>https://www.michaeljfox.org/grant/parkinsons-disease-therapeutics-pipeline-program</t>
+          <t>https://www.grants.gov/search-results-detail/362225</t>
         </is>
       </c>
       <c r="AD13" s="3" t="inlineStr">
         <is>
-          <t>Il Therapeutics Pipeline Program della Michael J. Fox Foundation finanzia lo sviluppo preclinico e clinico di interventi terapeutici modificanti la malattia o mirati al controllo sintomatico del Parkinson, integrando strumenti biomarcatori decisionali. Il programma supporta progetti da uno a tre anni con contributi compresi generalmente tra 250.000 e oltre 5 milioni di dollari, a seconda della fase di avanzamento. La candidatura è aperta a imprese biotech, collaborazioni accademia-industria e, in casi specifici, a gruppi esclusivamente accademici. Il processo di selezione è strutturato in due fasi: invio continuo di pre-proposte e, su invito, presentazione della proposta completa secondo scadenze cicliche periodiche. Sono esclusi studi su integratori alimentari o scoperta di target precoci.</t>
+          <t>Il bando Clinical Translation Research Award dello SCIRP per l'anno fiscale 2026 promuove ricerche cliniche emergenti o ad alto impatto che necessitano di studi preliminari, di fattibilità o di ottimizzazione per preparare futuri trial clinici definitivi. Tra gli obiettivi principali rientrano l'accelerazione del trasferimento clinico di nuove tecniche o interventi e l'identificazione delle migliori opzioni diagnostiche, terapeutiche e riabilitative per supportare le decisioni di pazienti e clinici nell'ambito delle lesioni del midollo spinale. Il bando include un'opzione per due Principal Investigator (con almeno un ricercatore junior) e impone il coinvolgimento di almeno due partner della comunità di pazienti come consulenti del progetto.</t>
         </is>
       </c>
       <c r="AE13" s="4" t="n">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="AF13" s="4" t="n">
         <v>46312</v>
@@ -2384,7 +2400,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>GG-HT942526SCIRPTRA</t>
+          <t>GG-HT942526SCIRPIIRA</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -2404,7 +2420,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Programma di ricerca sulle lesioni del midollo spinale del Dipartimento della Difesa: finanziamento per la ricerca traslazionale</t>
+          <t>DoW Ricerca sulle lesioni del midollo spinale, finanziamento per la ricerca promossa dal ricercatore</t>
         </is>
       </c>
       <c r="F14" s="4" t="n">
@@ -2431,12 +2447,12 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>Defense Health Agency Contracting Activity - DHACA – HT942526SCIRPTRA</t>
+          <t>Defense Health Agency Contracting Activity - DHACA – HT942526SCIRPIIRA</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>DoW Spinal Cord Injury, Translational Research Award</t>
+          <t>DoW Spinal Cord Injury, Investigator-Initiated Research Award</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -2451,11 +2467,11 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>Dedicato alla ricerca traslazionale per l'applicazione clinica nelle lesioni del midollo spinale, patologia cardine della riabilitazione neurologica.</t>
+          <t>Supporta la ricerca traslazionale e clinica mirata a migliorare l'assistenza e la qualità di vita nelle lesioni midollari.</t>
         </is>
       </c>
       <c r="P14" s="6" t="n">
-        <v>8320000</v>
+        <v>4960000</v>
       </c>
       <c r="Q14" s="6" t="n"/>
       <c r="R14" s="2" t="inlineStr">
@@ -2464,11 +2480,11 @@
         </is>
       </c>
       <c r="S14" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t>Bassa – 4 progetti finanziabili (stima: tasso storico non disponibile)</t>
+          <t>Media – 6 progetti finanziabili (stima: tasso storico non disponibile)</t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr">
@@ -2492,7 +2508,7 @@
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t>Obbligatorio almeno un partner comunitario esperto per esperienza diretta di lesione midollare; ammessa opzione a due PI con ricercatore junior.</t>
+          <t>Opzione per due Principal Investigator (di cui almeno uno a inizio carriera)</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2507,16 +2523,16 @@
       </c>
       <c r="AC14" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/362222</t>
+          <t>https://www.grants.gov/search-results-detail/362226</t>
         </is>
       </c>
       <c r="AD14" s="3" t="inlineStr">
         <is>
-          <t>Il Translational Research Award, nell'ambito del programma di ricerca sulle lesioni del midollo spinale (SCIRP), sostiene progetti di ricerca traslazionale mirati ad accelerare il passaggio di idee e interventi innovativi dal laboratorio alle applicazioni cliniche per pazienti con lesioni midollari. Le proposte devono includere obbligatoriamente come partner almeno un membro o consulente della comunità con lesione spinale vissuta in prima persona o un rappresentante di organizzazioni attive nel settore. È prevista l'opzione di collaborazione paritaria che consente a un ricercatore esperto di affiancare un ricercatore a inizio carriera nella guida del progetto. Possono partecipare atenei, enti ospedalieri, istituti di ricerca pubblici o privati e organizzazioni specializzate.</t>
+          <t>Il bando Investigator-Initiated Research Award (IIRA) per l'anno fiscale 2026, promosso dal programma SCIRP, supporta studi con un impatto rilevante sulla ricerca, sulla cura clinica e sulla qualità della vita delle persone con lesioni del midollo spinale. L'opportunità finanzia progetti che spaziano dalla ricerca fondamentale alle scienze traslazionali, scoraggiando gli studi focalizzati esclusivamente sull'identificazione di bersagli farmacologici o biologici. Il bando contempla una modalità opzionale di partenariato che permette a due Principal Investigator di fare domanda congiunta con premi separati, a condizione che almeno uno dei due sia un ricercatore a inizio carriera.</t>
         </is>
       </c>
       <c r="AE14" s="4" t="n">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="AF14" s="4" t="n">
         <v>46313</v>
@@ -2526,7 +2542,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>GG-HT942526SCIRPCTA</t>
+          <t>GG-RFA-DA-28-011</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -2546,11 +2562,11 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>DoW Ricerca sulle lesioni del midollo spinale, finanziamento per trial clinici</t>
+          <t>Iniziativa HEAL: gestione integrata del dolore cronico e del disturbo da uso di oppioidi (IMPOWR) - Centri di ricerca (RM1)</t>
         </is>
       </c>
       <c r="F15" s="4" t="n">
-        <v>46338</v>
+        <v>46413</v>
       </c>
       <c r="G15" s="5">
         <f>IF(F15="","",F15-TODAY())</f>
@@ -2558,12 +2574,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>In scadenza (≤30 gg)</t>
+          <t>Aperto</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Defense Health Agency Contracting Activity - DHACA</t>
+          <t>National Institutes of Health</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2573,12 +2589,12 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>Defense Health Agency Contracting Activity - DHACA – HT942526SCIRPCTA</t>
+          <t>National Institutes of Health – RFA-DA-28-011</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>DoW Spinal Cord Injury, Clinical Trial Award</t>
+          <t>HEAL Initiative: Integrative Management of Chronic Pain and OUD for Whole Recovery (IMPOWR): Research Centers (RM1 Clinical Trial Required)</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -2588,29 +2604,25 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>spinal cord injur</t>
+          <t>chronic pain</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>Finanzia trial clinici focalizzati sul trattamento e sulla gestione funzionale delle lesioni del midollo spinale.</t>
-        </is>
-      </c>
-      <c r="P15" s="6" t="n">
-        <v>9760000</v>
-      </c>
+          <t>È dedicato alla gestione integrata a lungo termine del dolore cronico e al recupero funzionale dei pazienti.</t>
+        </is>
+      </c>
+      <c r="P15" s="6" t="n"/>
       <c r="Q15" s="6" t="n"/>
       <c r="R15" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="S15" s="2" t="n">
-        <v>2</v>
-      </c>
+      <c r="S15" s="2" t="n"/>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t>Bassa – 2 progetti finanziabili (stima: tasso storico non disponibile)</t>
+          <t>Non stimabile – dati insufficienti</t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
@@ -2619,7 +2631,7 @@
         </is>
       </c>
       <c r="V15" s="4" t="n">
-        <v>46147</v>
+        <v>46301</v>
       </c>
       <c r="W15" s="2" t="n"/>
       <c r="X15" s="2" t="inlineStr">
@@ -2629,14 +2641,10 @@
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t>Unrestricted (i.e., open to any type of entity above), subject to any clarification in text field entitled "Additional Information on Eligibility"</t>
-        </is>
-      </c>
-      <c r="Z15" s="3" t="inlineStr">
-        <is>
-          <t>Obbligatori almeno 2 partner della comunità con esperienza di lesione midollare; possibile collaborazione tra 2 PI</t>
-        </is>
-      </c>
+          <t>Native American tribal governments (Federally recognized); Nonprofits having a 501(c)(3) status with the IRS, other than institutions of higher education; City or township governments; For profit organizations other than small businesses; Public and State controlled institutions of higher education; State governments; Others (see text field entitled "Additional Information on Eligibility" for clar</t>
+        </is>
+      </c>
+      <c r="Z15" s="3" t="n"/>
       <c r="AA15" s="2" t="inlineStr">
         <is>
           <t>Enti esteri: da verificare nel bando</t>
@@ -2649,16 +2657,16 @@
       </c>
       <c r="AC15" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/362224</t>
+          <t>https://www.grants.gov/search-results-detail/360048</t>
         </is>
       </c>
       <c r="AD15" s="3" t="inlineStr">
         <is>
-          <t>Il bando Clinical Trial Award del programma SCIRP (anno fiscale 2026) finanzia la rapida attuazione di studi clinici con un potenziale impatto significativo sul trattamento o sulla gestione delle persone con lesione del midollo spinale. L'opportunità include un'opzione di partenariato per ricercatori all'inizio della carriera (Early-Career Partnership Option), che consente la partecipazione di due Principal Investigator, purché almeno uno sia un ricercatore junior. Le proposte devono obbligatoriamente coinvolgere almeno due rappresentanti o partner della comunità con esperienza diretta di lesione midollare, che collaboreranno attivamente fornendo consulenza durante l'intera pianificazione e implementazione dello studio clinico.</t>
+          <t>L'avviso anticipa il rinnovo della rete di ricerca IMPOWR, parte dell'iniziativa NIH HEAL, finalizzata allo sviluppo e alla validazione di modelli integrati per la gestione del dolore cronico e del disturbo da uso di oppioidi. Il network comprenderà molteplici progetti di ricerca coordinati da un centro centrale, con l'obiettivo di condurre studi clinici per testare approcci assistenziali innovativi in grado di migliorare significativamente l'erogazione delle cure nei sistemi sanitari. Possono partecipare istituzioni universitarie, ospedaliere, enti di ricerca no-profit o profit e organizzazioni estere non statunitensi.</t>
         </is>
       </c>
       <c r="AE15" s="4" t="n">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="AF15" s="4" t="n">
         <v>46313</v>
@@ -2668,7 +2676,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>GG-HT942526SCIRPCTRA</t>
+          <t>GG-PAR-27-065</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -2688,11 +2696,11 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>DoW Ricerca sulle lesioni del midollo spinale, finanziamento per la ricerca clinica traslazionale</t>
+          <t>Trial clinici esplorativi e di efficacia del NINDS (UG3/UH3 - Clinical Trial obbligatorio)</t>
         </is>
       </c>
       <c r="F16" s="4" t="n">
-        <v>46338</v>
+        <v>47186</v>
       </c>
       <c r="G16" s="5">
         <f>IF(F16="","",F16-TODAY())</f>
@@ -2700,12 +2708,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>In scadenza (≤30 gg)</t>
+          <t>Aperto</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Defense Health Agency Contracting Activity - DHACA</t>
+          <t>National Institutes of Health</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2715,44 +2723,40 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>Defense Health Agency Contracting Activity - DHACA – HT942526SCIRPCTRA</t>
+          <t>National Institutes of Health – PAR-27-065</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>DoW Spinal Cord Injury, Clinical Translation Research Award</t>
+          <t>NINDS Efficacy and Exploratory Clinical Trials (UG3/UH3 - Clinical Trial Required)</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Altre malattie e riabilitazione</t>
+          <t>Ictus, Altre malattie e riabilitazione</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>rehabilitat, spinal cord injur</t>
+          <t>stroke, rehabilitat, neurological disorder</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>Finanzia ricerca clinica traslazionale volta a identificare le opzioni più efficaci di riabilitazione e trattamento nelle lesioni midollari.</t>
-        </is>
-      </c>
-      <c r="P16" s="6" t="n">
-        <v>6120000</v>
-      </c>
+          <t>Finanzia trial clinici neurologici e ammette esplicitamente terapie e interventi di riabilitazione lungo tutto l'arco della vita.</t>
+        </is>
+      </c>
+      <c r="P16" s="6" t="n"/>
       <c r="Q16" s="6" t="n"/>
       <c r="R16" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="S16" s="2" t="n">
-        <v>3</v>
-      </c>
+      <c r="S16" s="2" t="n"/>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t>Bassa – 3 progetti finanziabili (stima: tasso storico non disponibile)</t>
+          <t>Non stimabile – dati insufficienti</t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
@@ -2761,7 +2765,7 @@
         </is>
       </c>
       <c r="V16" s="4" t="n">
-        <v>46147</v>
+        <v>46265</v>
       </c>
       <c r="W16" s="2" t="n"/>
       <c r="X16" s="2" t="inlineStr">
@@ -2771,12 +2775,12 @@
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t>Unrestricted (i.e., open to any type of entity above), subject to any clarification in text field entitled "Additional Information on Eligibility"</t>
+          <t>Native American tribal governments (Federally recognized); State governments; Public and State controlled institutions of higher education; Small businesses; Special district governments; Public housing authorities/Indian housing authorities; City or township governments; Independent school districts; Nonprofits that do not have a 501(c)(3) status with the IRS, other than institutions of higher ed</t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t>Obbligatori almeno due partner della comunità di pazienti; opzione con due PI di cui uno a inizio carriera</t>
+          <t>Non sono ammessi sub-accordi o subappalti a entità estere; le organizzazioni estere possono candidarsi direttamente come capofila</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2791,16 +2795,16 @@
       </c>
       <c r="AC16" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/362225</t>
+          <t>https://www.grants.gov/search-results-detail/360404</t>
         </is>
       </c>
       <c r="AD16" s="3" t="inlineStr">
         <is>
-          <t>Il bando Clinical Translation Research Award dello SCIRP per l'anno fiscale 2026 promuove ricerche cliniche emergenti o ad alto impatto che necessitano di studi preliminari, di fattibilità o di ottimizzazione per preparare futuri trial clinici definitivi. Tra gli obiettivi principali rientrano l'accelerazione del trasferimento clinico di nuove tecniche o interventi e l'identificazione delle migliori opzioni diagnostiche, terapeutiche e riabilitative per supportare le decisioni di pazienti e clinici nell'ambito delle lesioni del midollo spinale. Il bando include un'opzione per due Principal Investigator (con almeno un ricercatore junior) e impone il coinvolgimento di almeno due partner della comunità di pazienti come consulenti del progetto.</t>
+          <t>Questa opportunità di finanziamento (UG3/UH3) promossa dal National Institute of Neurological Disorders and Stroke (NINDS) sostiene trial clinici proposti da ricercatori per affrontare quesiti coerenti con la missione dell'istituto. Il bando finanzia sperimentazioni cliniche precoci, intermedie o confermative di fase 3 e studi di efficacia comparativa su molecole, farmaci biologici, dispositivi medici o interventi chirurgici, comportamentali, dietetici e terapie riabilitative, per tutte le età. Possono partecipare enti accademici, ospedalieri e organizzazioni di ricerca, incluse entità straniere non statunitensi come capofila. Non sono tuttavia consentiti subappalti o sub-accordi finanziari internazionali verso altre entità estere nell'ambito dello stesso progetto.</t>
         </is>
       </c>
       <c r="AE16" s="4" t="n">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="AF16" s="4" t="n">
         <v>46312</v>
@@ -2810,7 +2814,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>GG-HT942526SCIRPIIRA</t>
+          <t>GG-PD-26-369Y</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -2825,29 +2829,27 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Ricerca clinica</t>
+          <t>Tecnologia / innovazione</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>DoW Ricerca sulle lesioni del midollo spinale, finanziamento per la ricerca promossa dal ricercatore</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="n">
-        <v>46338</v>
-      </c>
+          <t>Ingegneria dei sistemi biologici e biomedici (EBBS)</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="n"/>
       <c r="G17" s="5">
         <f>IF(F17="","",F17-TODAY())</f>
         <v/>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>In scadenza (≤30 gg)</t>
+          <t>Scadenza da verificare</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Defense Health Agency Contracting Activity - DHACA</t>
+          <t>U.S. National Science Foundation</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2857,44 +2859,40 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>Defense Health Agency Contracting Activity - DHACA – HT942526SCIRPIIRA</t>
+          <t>U.S. National Science Foundation – PD-26-369Y</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>DoW Spinal Cord Injury, Investigator-Initiated Research Award</t>
+          <t>Engineering Biological and Biomedical Systems (EBBS)</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Altre malattie e riabilitazione</t>
+          <t>Tecnologie riabilitazione, Altre malattie e riabilitazione</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>spinal cord injur</t>
+          <t>rehabilitation engineering, rehabilitat, persons with disabilities</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>Supporta la ricerca traslazionale e clinica mirata a migliorare l'assistenza e la qualità di vita nelle lesioni midollari.</t>
-        </is>
-      </c>
-      <c r="P17" s="6" t="n">
-        <v>4960000</v>
-      </c>
+          <t>Supporta esplicitamente la ricerca fondamentale in ingegneria della riabilitazione e tecnologie per il ripristino delle funzioni e la disabilità.</t>
+        </is>
+      </c>
+      <c r="P17" s="6" t="n"/>
       <c r="Q17" s="6" t="n"/>
       <c r="R17" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="S17" s="2" t="n">
-        <v>6</v>
-      </c>
+      <c r="S17" s="2" t="n"/>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t>Media – 6 progetti finanziabili (stima: tasso storico non disponibile)</t>
+          <t>Non stimabile – dati insufficienti</t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
@@ -2903,7 +2901,7 @@
         </is>
       </c>
       <c r="V17" s="4" t="n">
-        <v>46147</v>
+        <v>46136</v>
       </c>
       <c r="W17" s="2" t="n"/>
       <c r="X17" s="2" t="inlineStr">
@@ -2916,11 +2914,7 @@
           <t>Unrestricted (i.e., open to any type of entity above), subject to any clarification in text field entitled "Additional Information on Eligibility"</t>
         </is>
       </c>
-      <c r="Z17" s="3" t="inlineStr">
-        <is>
-          <t>Opzione per due Principal Investigator (di cui almeno uno a inizio carriera)</t>
-        </is>
-      </c>
+      <c r="Z17" s="3" t="n"/>
       <c r="AA17" s="2" t="inlineStr">
         <is>
           <t>Enti esteri: da verificare nel bando</t>
@@ -2933,26 +2927,26 @@
       </c>
       <c r="AC17" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/362226</t>
+          <t>https://www.grants.gov/search-results-detail/362062</t>
         </is>
       </c>
       <c r="AD17" s="3" t="inlineStr">
         <is>
-          <t>Il bando Investigator-Initiated Research Award (IIRA) per l'anno fiscale 2026, promosso dal programma SCIRP, supporta studi con un impatto rilevante sulla ricerca, sulla cura clinica e sulla qualità della vita delle persone con lesioni del midollo spinale. L'opportunità finanzia progetti che spaziano dalla ricerca fondamentale alle scienze traslazionali, scoraggiando gli studi focalizzati esclusivamente sull'identificazione di bersagli farmacologici o biologici. Il bando contempla una modalità opzionale di partenariato che permette a due Principal Investigator di fare domanda congiunta con premi separati, a condizione che almeno uno dei due sia un ricercatore a inizio carriera.</t>
+          <t>Il programma Engineering Biological and Biomedical Systems (EBBS) della National Science Foundation statunitense sostiene progetti di ricerca ingegneristica fondamentale volti a comprendere e controllare i sistemi biologici e fisiologici per migliorare la salute umana. L'iniziativa finanzia in particolare lo sviluppo di piattaforme di biosensing, metodologie di imaging ottico, sistemi per imitare o ripristinare le funzioni di tessuti e organi, nonché progetti innovativi di ingegneria della riabilitazione guidati dalle esigenze delle persone con disabilità. Non sono supportati trial clinici né progetti dedicati unicamente alla progettazione di farmaci o alla commercializzazione immediata. Il bando incoraggia approcci interdisciplinari e collaborazioni, ma non specifica restrizioni geografiche per la candidatura diretta.</t>
         </is>
       </c>
       <c r="AE17" s="4" t="n">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="AF17" s="4" t="n">
-        <v>46313</v>
+        <v>46312</v>
       </c>
       <c r="AG17" s="2" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>GG-PD-26-369Y</t>
+          <t>WEB-03a781657bb4</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -2962,75 +2956,79 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Tecnologia / innovazione</t>
-        </is>
-      </c>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n"/>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Ingegneria dei sistemi biologici e biomedici (EBBS)</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="n"/>
+          <t>Fondamenti di appello</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>46322</v>
+      </c>
       <c r="G18" s="5">
         <f>IF(F18="","",F18-TODAY())</f>
         <v/>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Scadenza da verificare</t>
+          <t>In scadenza (≤30 gg)</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>U.S. National Science Foundation</t>
+          <t>Brain Canada</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>Grants.gov</t>
+          <t>Brain Canada</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>U.S. National Science Foundation – PD-26-369Y</t>
+          <t>Funding Opportunities</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>Engineering Biological and Biomedical Systems (EBBS)</t>
+          <t>Funding Opportunities</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Tecnologie riabilitazione, Altre malattie e riabilitazione</t>
+          <t>Parkinson, Invecchiamento</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>rehabilitation engineering, rehabilitat, persons with disabilities</t>
+          <t>parkinson, dementi, alzheimer, cognitive decline, geriatr, older persons, aging, amyotrophic lateral sclerosis, neurodegenerat, spinal cord injur, neurological condition, disabilit</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>Supporta esplicitamente la ricerca fondamentale in ingegneria della riabilitazione e tecnologie per il ripristino delle funzioni e la disabilità.</t>
-        </is>
-      </c>
-      <c r="P18" s="6" t="n"/>
-      <c r="Q18" s="6" t="n"/>
+          <t>Il bando non specifica esplicitamente riabilitazione, ictus, Parkinson, invecchiamento/demenze o tecnologie per la riabilitazione</t>
+        </is>
+      </c>
+      <c r="P18" s="6" t="n">
+        <v>100000</v>
+      </c>
+      <c r="Q18" s="6" t="n">
+        <v>100000</v>
+      </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="S18" s="2" t="n"/>
+      <c r="S18" s="2" t="n">
+        <v>4</v>
+      </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t>Non stimabile – dati insufficienti</t>
+          <t>Bassa – 4 progetti finanziabili (stima: tasso storico non disponibile)</t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
@@ -3038,10 +3036,12 @@
           <t>Interamente finanziato</t>
         </is>
       </c>
-      <c r="V18" s="4" t="n">
-        <v>46136</v>
-      </c>
-      <c r="W18" s="2" t="n"/>
+      <c r="V18" s="4" t="n"/>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>24 mesi</t>
+        </is>
+      </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
           <t>Ricerca</t>
@@ -3049,13 +3049,17 @@
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t>Unrestricted (i.e., open to any type of entity above), subject to any clarification in text field entitled "Additional Information on Eligibility"</t>
-        </is>
-      </c>
-      <c r="Z18" s="3" t="n"/>
+          <t>Ricercatori in età precoce, studenti, post-doc e ricercatori clinici</t>
+        </is>
+      </c>
+      <c r="Z18" s="3" t="inlineStr">
+        <is>
+          <t>Ricercatori in età precoce e studenti, post-doc e ricercatori clinici</t>
+        </is>
+      </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>Enti esteri: da verificare nel bando</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
@@ -3065,16 +3069,16 @@
       </c>
       <c r="AC18" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/362062</t>
+          <t>https://braincanada.ca/research/funding-opportunities</t>
         </is>
       </c>
       <c r="AD18" s="3" t="inlineStr">
         <is>
-          <t>Il programma Engineering Biological and Biomedical Systems (EBBS) della National Science Foundation statunitense sostiene progetti di ricerca ingegneristica fondamentale volti a comprendere e controllare i sistemi biologici e fisiologici per migliorare la salute umana. L'iniziativa finanzia in particolare lo sviluppo di piattaforme di biosensing, metodologie di imaging ottico, sistemi per imitare o ripristinare le funzioni di tessuti e organi, nonché progetti innovativi di ingegneria della riabilitazione guidati dalle esigenze delle persone con disabilità. Non sono supportati trial clinici né progetti dedicati unicamente alla progettazione di farmaci o alla commercializzazione immediata. Il bando incoraggia approcci interdisciplinari e collaborazioni, ma non specifica restrizioni geografiche per la candidatura diretta.</t>
+          <t>Il bando offre finanziamenti per progetti di ricerca in varie aree, tra cui neuroscienze, neurologia, neurologia del neurodesenvolvimento e salute mentale degli anziani. Il finanziamento è per un periodo di due anni e varia da 100.000 a 500.000 EUR a progetto. Il bando è aperto a ricercatori in età precoce e a studenti, post-doc e ricercatori clinici. Il finanziamento include un premio di ingresso, un Passport di formazione e due esperienze di formazione e networking.</t>
         </is>
       </c>
       <c r="AE18" s="4" t="n">
-        <v>46314</v>
+        <v>46313</v>
       </c>
       <c r="AF18" s="4" t="n">
         <v>46312</v>
@@ -3084,7 +3088,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>WEB-03a781657bb4</t>
+          <t>GG-HT942526PRPEIRA</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -3097,14 +3101,18 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="D19" s="2" t="n"/>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Formazione / fellowship</t>
+        </is>
+      </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Fondamenti di appello</t>
+          <t>Programma di ricerca sul Parkinson del Dipartimento della Difesa: bando per ricercatori a inizio carriera</t>
         </is>
       </c>
       <c r="F19" s="4" t="n">
-        <v>46322</v>
+        <v>46332</v>
       </c>
       <c r="G19" s="5">
         <f>IF(F19="","",F19-TODAY())</f>
@@ -3117,56 +3125,54 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Brain Canada</t>
+          <t>Defense Health Agency Contracting Activity - DHACA</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>Brain Canada</t>
+          <t>Grants.gov</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>Funding Opportunities</t>
+          <t>Defense Health Agency Contracting Activity - DHACA – HT942526PRPEIRA</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>Funding Opportunities</t>
+          <t>DoW Parkinson’s, Early Investigator Research Award</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>Parkinson, Invecchiamento</t>
+          <t>Parkinson</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>parkinson, dementi, alzheimer, cognitive decline, geriatr, older persons, aging, amyotrophic lateral sclerosis, neurodegenerat, spinal cord injur, neurological condition, disabilit</t>
+          <t>parkinson</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>Il bando non specifica esplicitamente riabilitazione, ictus, Parkinson, invecchiamento/demenze o tecnologie per la riabilitazione</t>
+          <t>Finanzia la ricerca sul morbo di Parkinson per ricercatori a inizio carriera, ma esclude i trial clinici e non è mirato alla riabilitazione.</t>
         </is>
       </c>
       <c r="P19" s="6" t="n">
-        <v>100000</v>
-      </c>
-      <c r="Q19" s="6" t="n">
-        <v>100000</v>
-      </c>
+        <v>4200000</v>
+      </c>
+      <c r="Q19" s="6" t="n"/>
       <c r="R19" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="S19" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t>Bassa – 4 progetti finanziabili (stima: tasso storico non disponibile)</t>
+          <t>Media – 7 progetti finanziabili (stima: tasso storico non disponibile)</t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
@@ -3174,30 +3180,28 @@
           <t>Interamente finanziato</t>
         </is>
       </c>
-      <c r="V19" s="4" t="n"/>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>24 mesi</t>
-        </is>
-      </c>
+      <c r="V19" s="4" t="n">
+        <v>46191</v>
+      </c>
+      <c r="W19" s="2" t="n"/>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>Ricerca</t>
+          <t>Dottorato / formazione / mobilità</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t>Ricercatori in età precoce, studenti, post-doc e ricercatori clinici</t>
+          <t>Unrestricted (i.e., open to any type of entity above), subject to any clarification in text field entitled "Additional Information on Eligibility"</t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t>Ricercatori in età precoce e studenti, post-doc e ricercatori clinici</t>
+          <t>Per il Livello 1 è obbligatoria la designazione di almeno un mentore con esperienza documentata nella ricerca su Parkinson.</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Enti esteri: da verificare nel bando</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
@@ -3207,16 +3211,16 @@
       </c>
       <c r="AC19" s="7" t="inlineStr">
         <is>
-          <t>https://braincanada.ca/research/funding-opportunities</t>
+          <t>https://www.grants.gov/search-results-detail/362866</t>
         </is>
       </c>
       <c r="AD19" s="3" t="inlineStr">
         <is>
-          <t>Il bando offre finanziamenti per progetti di ricerca in varie aree, tra cui neuroscienze, neurologia, neurologia del neurodesenvolvimento e salute mentale degli anziani. Il finanziamento è per un periodo di due anni e varia da 100.000 a 500.000 EUR a progetto. Il bando è aperto a ricercatori in età precoce e a studenti, post-doc e ricercatori clinici. Il finanziamento include un premio di ingresso, un Passport di formazione e due esperienze di formazione e networking.</t>
+          <t>Il bando Early Investigator Research Award, promosso nell'ambito del Parkinson’s Research Program dell'agenzia di difesa statunitense, sostiene la formazione e l'avvio di carriera di ricercatori promettenti dedicati alla ricerca sulla malattia di Parkinson. L'iniziativa prevede due livelli: il primo è destinato a borsisti o assegnisti (fellows) e richiede l'affiancamento obbligatorio di un mentore esperto per garantire un solido percorso verso l'indipendenza scientifica; il secondo è rivolto a ricercatori indipendenti junior e richiede dati preliminari comprovati. Le ricerche proposte devono rientrare nelle aree prioritarie del programma e non possono includere sperimentazioni cliniche. Possono candidarsi ricercatori a inizio carriera sostenuti dalle proprie organizzazioni di ricerca o accademiche.</t>
         </is>
       </c>
       <c r="AE19" s="4" t="n">
-        <v>46313</v>
+        <v>46316</v>
       </c>
       <c r="AF19" s="4" t="n">
         <v>46312</v>
@@ -3226,7 +3230,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>GG-HT942526PRPEIRA</t>
+          <t>GG-HT942526PRPIIRA</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -3241,12 +3245,12 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Formazione / fellowship</t>
+          <t>Ricerca clinica</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Programma di ricerca sul Parkinson del Dipartimento della Difesa: bando per ricercatori a inizio carriera</t>
+          <t>Programma di ricerca sul Parkinson del Dipartimento della Difesa: bando di ricerca promosso dal ricercatore</t>
         </is>
       </c>
       <c r="F20" s="4" t="n">
@@ -3273,12 +3277,12 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>Defense Health Agency Contracting Activity - DHACA – HT942526PRPEIRA</t>
+          <t>Defense Health Agency Contracting Activity - DHACA – HT942526PRPIIRA</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>DoW Parkinson’s, Early Investigator Research Award</t>
+          <t>DoW Parkinson’s, Investigator-Initiated Research Award</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -3293,11 +3297,11 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>Finanzia la ricerca sul morbo di Parkinson per ricercatori a inizio carriera, ma esclude i trial clinici e non è mirato alla riabilitazione.</t>
+          <t>Bando dedicato alla malattia di Parkinson che ammette trial clinici, pur senza essere focalizzato specificamente sulla riabilitazione.</t>
         </is>
       </c>
       <c r="P20" s="6" t="n">
-        <v>4200000</v>
+        <v>10000000</v>
       </c>
       <c r="Q20" s="6" t="n"/>
       <c r="R20" s="2" t="inlineStr">
@@ -3306,11 +3310,11 @@
         </is>
       </c>
       <c r="S20" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t>Media – 7 progetti finanziabili (stima: tasso storico non disponibile)</t>
+          <t>Media – 5 progetti finanziabili (stima: tasso storico non disponibile)</t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
@@ -3324,7 +3328,7 @@
       <c r="W20" s="2" t="n"/>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>Dottorato / formazione / mobilità</t>
+          <t>Ricerca</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
@@ -3334,7 +3338,7 @@
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
-          <t>Per il Livello 1 è obbligatoria la designazione di almeno un mentore con esperienza documentata nella ricerca su Parkinson.</t>
+          <t>Possibilità di consorzio con un Initiating PI e fino a due Partnering PI multidisciplinari.</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -3349,16 +3353,16 @@
       </c>
       <c r="AC20" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/362866</t>
+          <t>https://www.grants.gov/search-results-detail/362868</t>
         </is>
       </c>
       <c r="AD20" s="3" t="inlineStr">
         <is>
-          <t>Il bando Early Investigator Research Award, promosso nell'ambito del Parkinson’s Research Program dell'agenzia di difesa statunitense, sostiene la formazione e l'avvio di carriera di ricercatori promettenti dedicati alla ricerca sulla malattia di Parkinson. L'iniziativa prevede due livelli: il primo è destinato a borsisti o assegnisti (fellows) e richiede l'affiancamento obbligatorio di un mentore esperto per garantire un solido percorso verso l'indipendenza scientifica; il secondo è rivolto a ricercatori indipendenti junior e richiede dati preliminari comprovati. Le ricerche proposte devono rientrare nelle aree prioritarie del programma e non possono includere sperimentazioni cliniche. Possono candidarsi ricercatori a inizio carriera sostenuti dalle proprie organizzazioni di ricerca o accademiche.</t>
+          <t>L'Investigator-Initiated Research Award, gestito dal programma di ricerca sul Parkinson (PRP), mira a finanziare progetti di ricerca rigorosi, multidisciplinari e ad alto impatto con un rilevante potenziale innovativo nella lotta al morbo di Parkinson. Le proposte devono concentrarsi su una delle aree prioritarie stabilite per l'anno fiscale 2026 e devono essere obbligatoriamente supportate da solidi dati preliminari. A differenza di altre linee di finanziamento, questo bando consente esplicitamente la conduzione di studi clinici. È inoltre prevista un'opzione di partenariato che permette la collaborazione formale tra un ricercatore principale capofila e fino a due Principal Investigator partner. Possono candidarsi istituti universitari, centri di ricerca e organizzazioni cliniche qualificate.</t>
         </is>
       </c>
       <c r="AE20" s="4" t="n">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="AF20" s="4" t="n">
         <v>46312</v>
@@ -3368,7 +3372,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>GG-HT942526PRPIIRA</t>
+          <t>GG-PAR-27-007</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -3388,11 +3392,11 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Programma di ricerca sul Parkinson del Dipartimento della Difesa: bando di ricerca promosso dal ricercatore</t>
+          <t>Trial clinici e studi ancillari condotti all'interno delle reti di ricerca clinica finanziate dal NIH (UG3/UH3)</t>
         </is>
       </c>
       <c r="F21" s="4" t="n">
-        <v>46332</v>
+        <v>46336</v>
       </c>
       <c r="G21" s="5">
         <f>IF(F21="","",F21-TODAY())</f>
@@ -3405,7 +3409,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>Defense Health Agency Contracting Activity - DHACA</t>
+          <t>National Institutes of Health</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -3415,44 +3419,40 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>Defense Health Agency Contracting Activity - DHACA – HT942526PRPIIRA</t>
+          <t>National Institutes of Health – PAR-27-007</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>DoW Parkinson’s, Investigator-Initiated Research Award</t>
+          <t>Clinical Trials and Ancillary Studies Conducted within NIH-Funded Clinical Trial Research Networks (UG3/UH3 - Clinical Trial Required)</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Parkinson</t>
+          <t>Ictus, Altre malattie e riabilitazione</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>parkinson</t>
+          <t>stroke, neurological disorder</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>Bando dedicato alla malattia di Parkinson che ammette trial clinici, pur senza essere focalizzato specificamente sulla riabilitazione.</t>
-        </is>
-      </c>
-      <c r="P21" s="6" t="n">
-        <v>10000000</v>
-      </c>
+          <t>Finanzia trial clinici in reti neurologiche che possono comprendere patologie di interesse riabilitativo come l'ictus, pur non focalizzandosi sulla riabilitazione.</t>
+        </is>
+      </c>
+      <c r="P21" s="6" t="n"/>
       <c r="Q21" s="6" t="n"/>
       <c r="R21" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="S21" s="2" t="n">
-        <v>5</v>
-      </c>
+      <c r="S21" s="2" t="n"/>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t>Media – 5 progetti finanziabili (stima: tasso storico non disponibile)</t>
+          <t>Non stimabile – dati insufficienti</t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
@@ -3461,9 +3461,13 @@
         </is>
       </c>
       <c r="V21" s="4" t="n">
-        <v>46191</v>
-      </c>
-      <c r="W21" s="2" t="n"/>
+        <v>46097</v>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>84 mesi</t>
+        </is>
+      </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
           <t>Ricerca</t>
@@ -3471,14 +3475,10 @@
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t>Unrestricted (i.e., open to any type of entity above), subject to any clarification in text field entitled "Additional Information on Eligibility"</t>
-        </is>
-      </c>
-      <c r="Z21" s="3" t="inlineStr">
-        <is>
-          <t>Possibilità di consorzio con un Initiating PI e fino a due Partnering PI multidisciplinari.</t>
-        </is>
-      </c>
+          <t xml:space="preserve">For profit organizations other than small businesses; Others (see text field entitled "Additional Information on Eligibility" for clarification); Public and State controlled institutions of higher education; Special district governments; Native American tribal organizations (other than Federally recognized tribal governments); Public housing authorities/Indian housing authorities; Native American </t>
+        </is>
+      </c>
+      <c r="Z21" s="3" t="n"/>
       <c r="AA21" s="2" t="inlineStr">
         <is>
           <t>Enti esteri: da verificare nel bando</t>
@@ -3491,16 +3491,16 @@
       </c>
       <c r="AC21" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/362868</t>
+          <t>https://www.grants.gov/search-results-detail/361522</t>
         </is>
       </c>
       <c r="AD21" s="3" t="inlineStr">
         <is>
-          <t>L'Investigator-Initiated Research Award, gestito dal programma di ricerca sul Parkinson (PRP), mira a finanziare progetti di ricerca rigorosi, multidisciplinari e ad alto impatto con un rilevante potenziale innovativo nella lotta al morbo di Parkinson. Le proposte devono concentrarsi su una delle aree prioritarie stabilite per l'anno fiscale 2026 e devono essere obbligatoriamente supportate da solidi dati preliminari. A differenza di altre linee di finanziamento, questo bando consente esplicitamente la conduzione di studi clinici. È inoltre prevista un'opzione di partenariato che permette la collaborazione formale tra un ricercatore principale capofila e fino a due Principal Investigator partner. Possono candidarsi istituti universitari, centri di ricerca e organizzazioni cliniche qualificate.</t>
+          <t>Il bando, promosso dal NINDS insieme ad altri istituti del NIH tramite lo schema cooperativo a due fasi UG3/UH3, intende sostenere la conduzione di studi clinici multicentrici e studi ancillari all'interno delle reti di ricerca clinica già finanziate e attive del NIH. Il programma prevede una fase iniziale di pianificazione e avvio fino a due anni (UG3), con possibile passaggio a una fase operativa fino a ulteriori cinque anni (UH3) al raggiungimento di specifici traguardi. Possono candidarsi enti di ricerca, università, organizzazioni pubbliche o private ed enti stranieri non statunitensi per testare interventi diagnostici e terapeutici in ambito neurologico.</t>
         </is>
       </c>
       <c r="AE21" s="4" t="n">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="AF21" s="4" t="n">
         <v>46312</v>
@@ -3615,7 +3615,7 @@
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t>Native American tribal governments (Federally recognized); Public housing authorities/Indian housing authorities; Others (see text field entitled "Additional Information on Eligibility" for clarification); Unrestricted (i.e., open to any type of entity above), subject to any clarification in text field entitled "Additional Information on Eligibility"; Public and State controlled institutions of hi</t>
+          <t>City or township governments; Public and State controlled institutions of higher education; Private institutions of higher education; Nonprofits having a 501(c)(3) status with the IRS, other than institutions of higher education; Native American tribal governments (Federally recognized); Unrestricted (i.e., open to any type of entity above), subject to any clarification in text field entitled "Add</t>
         </is>
       </c>
       <c r="Z22" s="3" t="n"/>
@@ -3640,7 +3640,7 @@
         </is>
       </c>
       <c r="AE22" s="4" t="n">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="AF22" s="4" t="n">
         <v>46312</v>
@@ -3879,7 +3879,7 @@
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t>Special district governments; Private institutions of higher education; State governments; Independent school districts; Nonprofits that do not have a 501(c)(3) status with the IRS, other than institutions of higher education; For profit organizations other than small businesses; Native American tribal governments (Federally recognized); Native American tribal organizations (other than Federally r</t>
+          <t>State governments; Native American tribal governments (Federally recognized); County governments; Native American tribal organizations (other than Federally recognized tribal governments); Nonprofits having a 501(c)(3) status with the IRS, other than institutions of higher education; Small businesses; Independent school districts; For profit organizations other than small businesses; Public and St</t>
         </is>
       </c>
       <c r="Z24" s="3" t="n"/>
@@ -3904,7 +3904,7 @@
         </is>
       </c>
       <c r="AE24" s="4" t="n">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="AF24" s="4" t="n">
         <v>46312</v>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t>Public and State controlled institutions of higher education; State governments; Special district governments; County governments; For profit organizations other than small businesses; Private institutions of higher education; Nonprofits having a 501(c)(3) status with the IRS, other than institutions of higher education; Independent school districts; Native American tribal organizations (other tha</t>
+          <t>Independent school districts; Nonprofits that do not have a 501(c)(3) status with the IRS, other than institutions of higher education; County governments; For profit organizations other than small businesses; Special district governments; Unrestricted (i.e., open to any type of entity above), subject to any clarification in text field entitled "Additional Information on Eligibility"; State govern</t>
         </is>
       </c>
       <c r="Z25" s="3" t="n"/>
@@ -4038,7 +4038,7 @@
         </is>
       </c>
       <c r="AE25" s="4" t="n">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="AF25" s="4" t="n">
         <v>46312</v>
@@ -4068,7 +4068,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Finanziamenti per la formazione clinica nel morbo di Parkinson</t>
+          <t>Bandi per la formazione clinica della Parkinson's Foundation</t>
         </is>
       </c>
       <c r="F26" s="4" t="n"/>
@@ -4113,22 +4113,26 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>Finanzia la formazione clinica e specialistica nel morbo di Parkinson e nei disordini del movimento, senza una focalizzazione esclusiva sulla riabilitazione.</t>
+          <t>Finanzia la formazione clinica avanzata e la ricerca nella malattia di Parkinson e disturbi del movimento, ma non è focalizzato specificamente sulla riabilitazione.</t>
         </is>
       </c>
       <c r="P26" s="6" t="n">
         <v>50000</v>
       </c>
-      <c r="Q26" s="6" t="n"/>
+      <c r="Q26" s="6" t="n">
+        <v>103800</v>
+      </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="S26" s="2" t="n"/>
+      <c r="S26" s="2" t="n">
+        <v>4</v>
+      </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t>Non stimabile – dati insufficienti</t>
+          <t>Bassa – 4 progetti finanziabili (stima: tasso storico non disponibile)</t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr">
@@ -4170,11 +4174,11 @@
       </c>
       <c r="AD26" s="3" t="inlineStr">
         <is>
-          <t>La Parkinson's Foundation propone diversi programmi di finanziamento dedicati alla formazione specialistica e allo sviluppo di carriera per migliorare l'assistenza alle persone con malattia di Parkinson. Tra le opportunità offerte figurano il Mentored Clinical Research Award (fino a 50.000 dollari per progetti annuali di ricerca clinica orientata al paziente guidati da giovani ricercatori con un mentor esperto), l'Institutional Movement Disorders Fellowship (fino a 103.800 dollari all'anno per due anni a supporto della formazione specialistica biennale di neurologi nei disordini del movimento presso istituzioni del Nord America) e il Nurse Faculty Award (fino a 10.000 dollari per docenti infermieristici). Le risorse coprono stipendi, costi diretti e formazione avanzata.</t>
+          <t>La Parkinson's Foundation offre diversi programmi di finanziamento alla formazione per migliorare l'assistenza a persone affette da malattia di Parkinson e disturbi del movimento. Le opportunità includono borse biennali per istituzioni volte alla formazione specialistica di nuovi neurologi clinici (fino a 103.800 dollari/anno), il Mentored Clinical Research Award da 50.000 dollari in collaborazione con il Parkinson Study Group per giovani ricercatori entro cinque anni dal termine della specializzazione, e il Nurse Faculty Award (fino a 10.000 dollari) per docenti infermieri. I contributi coprono stipendi, costi diretti di ricerca e attività di sviluppo accademico e clinico.</t>
         </is>
       </c>
       <c r="AE26" s="4" t="n">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="AF26" s="4" t="n">
         <v>46312</v>
@@ -9222,18 +9226,18 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>19/10/2026 07:40</t>
+          <t>21/10/2026 06:06</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>72</v>
+        <v>107</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Ultima esecuzione: 1 elementi esaminati, 0 pertinenti</t>
+          <t>Ultima esecuzione: 35 elementi esaminati, 0 pertinenti</t>
         </is>
       </c>
     </row>
@@ -9265,11 +9269,11 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>19/10/2026 07:48</t>
+          <t>21/10/2026 06:15</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>21</v>
@@ -9562,11 +9566,11 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19/10/2026 07:34</t>
+          <t>21/10/2026 05:59</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>140</v>
+        <v>175</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>1</v>
@@ -9648,11 +9652,11 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19/10/2026 07:41</t>
+          <t>21/10/2026 06:06</t>
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>140</v>
+        <v>175</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>0</v>
@@ -9691,11 +9695,11 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19/10/2026 07:46</t>
+          <t>21/10/2026 06:13</t>
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>140</v>
+        <v>175</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>0</v>
@@ -9734,18 +9738,18 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19/10/2026 07:25</t>
+          <t>21/10/2026 05:49</t>
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>4781</v>
+        <v>5984</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>77</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Ultima esecuzione: 1195 elementi esaminati, 10 pertinenti</t>
+          <t>Ultima esecuzione: 1203 elementi esaminati, 10 pertinenti</t>
         </is>
       </c>
     </row>
@@ -9777,18 +9781,18 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>19/10/2026 07:36</t>
+          <t>21/10/2026 06:01</t>
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>140</v>
+        <v>174</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>3</v>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Ultima esecuzione: 35 elementi esaminati, 0 pertinenti</t>
+          <t>Ultima esecuzione: 34 elementi esaminati, 0 pertinenti</t>
         </is>
       </c>
     </row>
@@ -9820,11 +9824,11 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19/10/2026 07:35</t>
+          <t>21/10/2026 06:00</t>
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>140</v>
+        <v>175</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>3</v>
@@ -9863,11 +9867,11 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19/10/2026 07:39</t>
+          <t>21/10/2026 06:04</t>
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>140</v>
+        <v>175</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>2</v>
@@ -9906,11 +9910,11 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>19/10/2026 07:33</t>
+          <t>21/10/2026 05:58</t>
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>140</v>
+        <v>175</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>2</v>
@@ -9949,11 +9953,11 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19/10/2026 07:39</t>
+          <t>21/10/2026 06:05</t>
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>140</v>
+        <v>175</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>0</v>
@@ -9992,11 +9996,11 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>19/10/2026 07:40</t>
+          <t>21/10/2026 06:05</t>
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>140</v>
+        <v>175</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>0</v>
@@ -10078,18 +10082,18 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19/10/2026 07:29</t>
+          <t>21/10/2026 05:54</t>
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>3382</v>
+        <v>4236</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Ultima esecuzione: 850 elementi esaminati, 55 pertinenti</t>
+          <t>Ultima esecuzione: 854 elementi esaminati, 58 pertinenti</t>
         </is>
       </c>
     </row>
@@ -10121,11 +10125,11 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>19/10/2026 07:30</t>
+          <t>21/10/2026 05:56</t>
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>140</v>
+        <v>175</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>0</v>
@@ -10164,11 +10168,11 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>19/10/2026 07:41</t>
+          <t>21/10/2026 06:07</t>
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>0</v>
@@ -10207,11 +10211,11 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>19/10/2026 07:32</t>
+          <t>21/10/2026 05:57</t>
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>140</v>
+        <v>175</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>0</v>
@@ -10250,11 +10254,11 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>19/10/2026 07:48</t>
+          <t>21/10/2026 06:14</t>
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>21</v>
@@ -10293,11 +10297,11 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>19/10/2026 07:30</t>
+          <t>21/10/2026 05:55</t>
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>140</v>
+        <v>175</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>0</v>
@@ -10336,11 +10340,11 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>19/10/2026 07:29</t>
+          <t>21/10/2026 05:54</t>
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H28" s="2" t="n">
         <v>0</v>
@@ -10457,11 +10461,11 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>19/10/2026 07:49</t>
+          <t>21/10/2026 06:16</t>
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>140</v>
+        <v>175</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>0</v>
@@ -10500,11 +10504,11 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>19/10/2026 07:48</t>
+          <t>21/10/2026 06:15</t>
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="H32" s="2" t="n">
         <v>8</v>
@@ -10586,11 +10590,11 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>19/10/2026 07:31</t>
+          <t>21/10/2026 05:56</t>
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>0</v>
@@ -10629,11 +10633,11 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>19/10/2026 07:31</t>
+          <t>21/10/2026 05:56</t>
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>140</v>
+        <v>175</v>
       </c>
       <c r="H35" s="2" t="n">
         <v>0</v>
@@ -10711,11 +10715,11 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>19/10/2026 07:46</t>
+          <t>21/10/2026 06:13</t>
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>0</v>
@@ -10754,11 +10758,11 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>19/10/2026 07:47</t>
+          <t>21/10/2026 06:13</t>
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>140</v>
+        <v>175</v>
       </c>
       <c r="H38" s="2" t="n">
         <v>0</v>
@@ -10797,11 +10801,11 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>19/10/2026 07:47</t>
+          <t>21/10/2026 06:14</t>
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>140</v>
+        <v>175</v>
       </c>
       <c r="H39" s="2" t="n">
         <v>0</v>
@@ -10823,7 +10827,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -10881,11 +10885,11 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-19 07:49</t>
+          <t>2026-10-21 06:19</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2686</v>
+        <v>2731</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>0</v>
@@ -10895,11 +10899,11 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>32 non aperti all'Italia, 3 di infrastruttura, 3 preclinici, 2 non pertinenti alla riabilitazione, 1 servizi o programmi sociali</t>
+          <t>35 non aperti all'Italia, 3 di infrastruttura, 3 preclinici, 2 non pertinenti alla riabilitazione, 1 servizi o programmi sociali</t>
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
@@ -10907,31 +10911,31 @@
         </is>
       </c>
       <c r="H2" s="3" t="n">
-        <v>24.1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-18 14:17</t>
+          <t>2026-10-19 07:49</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2720</v>
+        <v>2686</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>32 non aperti all'Italia, 3 di infrastruttura, 3 preclinici, 3 non pertinenti alla riabilitazione, 1 servizi o programmi sociali</t>
+          <t>32 non aperti all'Italia, 3 di infrastruttura, 3 preclinici, 2 non pertinenti alla riabilitazione, 1 servizi o programmi sociali</t>
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -10939,62 +10943,94 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>29.3</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-18 02:48</t>
+          <t>2026-10-18 14:17</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>2925</v>
+        <v>2720</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>107</v>
-      </c>
-      <c r="E4" s="3" t="n"/>
+        <v>112</v>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>32 non aperti all'Italia, 3 di infrastruttura, 3 preclinici, 3 non pertinenti alla riabilitazione, 1 servizi o programmi sociali</t>
+        </is>
+      </c>
       <c r="F4" s="3" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>NIHR: HTTP 403; Stroke Association: HTTP 403; American Heart Association – Research: HTTP 403; NHMRC: irraggiungibile: HTTPSConnectionPool(host='www.nhmrc.gov.au', port=443): Read timed out. (read timeout=45)</t>
+          <t>Nessuno</t>
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>92.5</v>
+        <v>29.3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-17 15:58</t>
+          <t>2026-10-18 02:48</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>2819</v>
+        <v>2925</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>266</v>
+        <v>20</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="E5" s="3" t="n"/>
       <c r="F5" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>NIHR: HTTP 403; Stroke Association: HTTP 403; American Heart Association – Research: HTTP 403; NHMRC: irraggiungibile: HTTPSConnectionPool(host='www.nhmrc.gov.au', port=443): Read timed out. (read timeout=45)</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>92.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-17 15:58</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>2819</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>266</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="n">
         <v>44</v>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>NIHR: HTTP 403; Stroke Association: HTTP 403; American Heart Association – Research: HTTP 403; NHMRC: irraggiungibile: HTTPSConnectionPool(host='www.nhmrc.gov.au', port=443): Read timed out. (read timeout=45)</t>
         </is>
       </c>
-      <c r="H5" s="3" t="n">
+      <c r="H6" s="3" t="n">
         <v>76.5</v>
       </c>
     </row>

--- a/report/NeuroGrant_ultimo.xlsx
+++ b/report/NeuroGrant_ultimo.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LOG" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BANDI'!$A$1:$AG$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BANDI'!$A$1:$AG$38</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -492,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG70"/>
+  <dimension ref="A1:AG38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -844,7 +844,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>EU-HORIZON-HLTH-2027-01-STAYHLTH-01</t>
+          <t>GG-PAR-25-124</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -864,11 +864,11 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Affrontare le disabilità lungo l'arco della vita a supporto della vita indipendente e dell'inclusione</t>
+          <t>Finanziamento di ricerca per ricercatori a inizio carriera NCMRR (R03 Clinical Trial facoltativo)</t>
         </is>
       </c>
       <c r="F3" s="4" t="n">
-        <v>46435</v>
+        <v>46759</v>
       </c>
       <c r="G3" s="5">
         <f>IF(F3="","",F3-TODAY())</f>
@@ -876,61 +876,61 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>In apertura</t>
+          <t>Aperto</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Commissione europea</t>
+          <t>National Institutes of Health</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>EU Funding &amp; Tenders Portal</t>
+          <t>Grants.gov</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>Horizon Europe – HORIZON  Research and Innovation Actions</t>
+          <t>National Institutes of Health – PAR-25-124</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>Addressing disabilities through the life course to support independent living and inclusion</t>
+          <t>NCMRR Early Career Research Award (R03 Clinical Trial Optional)</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Invecchiamento, Tecnologie riabilitazione, Altre malattie e riabilitazione</t>
+          <t>Altre malattie e riabilitazione</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>frailty, older persons, assistive technolog, rehabilitat, disabilit, cardiovascular, obesit</t>
+          <t>rehabilitat</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>Finanzia interventi di abilitazione, riabilitazione anche con tecnologie assistive e modelli per il recupero funzionale e la vita indipendente in persone con disabilità a lungo termine.</t>
+          <t>Bando dedicato specificamente alla ricerca di base e clinica in riabilitazione promosso dal NCMRR per ricercatori a inizio carriera.</t>
         </is>
       </c>
       <c r="P3" s="6" t="n">
-        <v>39300000</v>
+        <v>200000</v>
       </c>
       <c r="Q3" s="6" t="n">
-        <v>8000000</v>
+        <v>200000</v>
       </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="S3" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T3" s="3" t="inlineStr">
         <is>
-          <t>Media – 5 progetti finanziabili (stima: tasso storico non disponibile)</t>
+          <t>Bassa – 1 progetti finanziabili (stima: tasso storico non disponibile)</t>
         </is>
       </c>
       <c r="U3" s="3" t="inlineStr">
@@ -939,7 +939,7 @@
         </is>
       </c>
       <c r="V3" s="4" t="n">
-        <v>46324</v>
+        <v>45614</v>
       </c>
       <c r="W3" s="2" t="n"/>
       <c r="X3" s="2" t="inlineStr">
@@ -949,17 +949,13 @@
       </c>
       <c r="Y3" s="3" t="inlineStr">
         <is>
-          <t>Comunità scientifica, decisori politici, fornitori di servizi sanitari e sociali, organizzazioni per la disabilità</t>
-        </is>
-      </c>
-      <c r="Z3" s="3" t="inlineStr">
-        <is>
-          <t>Consorzio: min. 3 enti indipendenti da 3 paesi UE/associati (regola standard, verificare il topic)</t>
-        </is>
-      </c>
+          <t>State governments; Nonprofits having a 501(c)(3) status with the IRS, other than institutions of higher education; Others (see text field entitled "Additional Information on Eligibility" for clarification); City or township governments; Nonprofits that do not have a 501(c)(3) status with the IRS, other than institutions of higher education; Private institutions of higher education; Native American</t>
+        </is>
+      </c>
+      <c r="Z3" s="3" t="n"/>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>Stati membri UE e paesi associati (altri paesi secondo le condizioni del topic)</t>
+          <t>Ammessi anche enti non statunitensi (call NIH completa)</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
@@ -969,26 +965,26 @@
       </c>
       <c r="AC3" s="7" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-HLTH-2027-01-STAYHLTH-01</t>
+          <t>https://www.grants.gov/search-results-detail/357206</t>
         </is>
       </c>
       <c r="AD3" s="3" t="inlineStr">
         <is>
-          <t>Il bando supporta la ricerca clinica, assistenziale e tecnologica incentrata sulle persone con disabilità fisiche, mentali, intellettive o sensoriali a lungo termine, per favorire l'inclusione comunitaria e l'autonomia lungo tutto l'arco dell'esistenza. Tra le aree prioritarie rientrano l'accesso a servizi di abilitazione e riabilitazione, compresa la riabilitazione psicologica e l'impiego di tecnologie assistive avanzate volte al miglioramento o recupero delle capacità funzionali e alla riduzione delle limitazioni nelle attività quotidiane. Si finanziano inoltre nuovi modelli di cura integrati, prevenzione della perdita di autonomia e percorsi di deistituzionalizzazione. Possono partecipare consorzi transnazionali composti da ricercatori clinici, fornitori di assistenza sociosanitaria, associazioni di disabili e università.</t>
+          <t>Il bando NCMRR Early Career Research Award (R03), promosso dal National Institutes of Health (NIH), sostiene ricercatori a inizio carriera che intendono consolidare un percorso scientifico indipendente nel campo della riabilitazione medica. L'iniziativa finanzia progetti di ricerca clinica e di base allineati al Piano di Ricerca sulla Riabilitazione del NIH, con l'obiettivo di raccogliere dati preliminari sufficienti per future proposte R01. Sono ammissibili analisi secondarie di dati preesistenti, studi pilota indipendenti, sviluppo di metodologie di ricerca, studi traslazionali, ricerca sugli esiti e lo sviluppo di nuove tecnologie. Possono candidarsi istituzioni accademiche e di ricerca, comprese organizzazioni non profit ed enti stranieri con sede al di fuori degli Stati Uniti.</t>
         </is>
       </c>
       <c r="AE3" s="4" t="n">
         <v>46316</v>
       </c>
       <c r="AF3" s="4" t="n">
-        <v>46313</v>
+        <v>46312</v>
       </c>
       <c r="AG3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>GG-PAR-25-124</t>
+          <t>WEB-00773cbd93aa</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -998,7 +994,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1008,11 +1004,11 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Finanziamento di ricerca per ricercatori a inizio carriera NCMRR (R03 Clinical Trial facoltativo)</t>
+          <t>Finanziamento ponte per la ricerca interrotta sulle malattie neurodegenerative (BFDN)</t>
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>46759</v>
+        <v>46325</v>
       </c>
       <c r="G4" s="5">
         <f>IF(F4="","",F4-TODAY())</f>
@@ -1020,49 +1016,49 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Aperto</t>
+          <t>In scadenza (≤30 gg)</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>National Institutes of Health</t>
+          <t>Michael J. Fox Foundation</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Grants.gov</t>
+          <t>Michael J. Fox Foundation</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>National Institutes of Health – PAR-25-124</t>
+          <t>Bridge Funding for Disrupted Neurodegenerative Research Grant Program (BFDN) Powering the Next Generation of Research</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>NCMRR Early Career Research Award (R03 Clinical Trial Optional)</t>
+          <t>Bridge Funding for Disrupted Neurodegenerative Research Grant Program (BFDN) Powering the Next Generation of Research</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Altre malattie e riabilitazione</t>
+          <t>Parkinson, Invecchiamento, Altre malattie e riabilitazione</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>rehabilitat</t>
+          <t>parkinson, dementi, alzheimer, neurodegenerat, neurological disease</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>Bando dedicato specificamente alla ricerca di base e clinica in riabilitazione promosso dal NCMRR per ricercatori a inizio carriera.</t>
+          <t>Finanzia la continuità di progetti di ricerca su Parkinson, Alzheimer e demenze, senza una focalizzazione specifica sulla riabilitazione.</t>
         </is>
       </c>
       <c r="P4" s="6" t="n">
-        <v>200000</v>
+        <v>250000</v>
       </c>
       <c r="Q4" s="6" t="n">
-        <v>200000</v>
+        <v>250000</v>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
@@ -1079,13 +1075,15 @@
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t>Interamente finanziato</t>
-        </is>
-      </c>
-      <c r="V4" s="4" t="n">
-        <v>45614</v>
-      </c>
-      <c r="W4" s="2" t="n"/>
+          <t>Co-finanziamento richiesto (25% a carico del beneficiario)</t>
+        </is>
+      </c>
+      <c r="V4" s="4" t="n"/>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
+          <t>12 mesi</t>
+        </is>
+      </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
           <t>Ricerca</t>
@@ -1093,13 +1091,13 @@
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t>Public housing authorities/Indian housing authorities; Others (see text field entitled "Additional Information on Eligibility" for clarification); County governments; Independent school districts; Private institutions of higher education; For profit organizations other than small businesses; Nonprofits that do not have a 501(c)(3) status with the IRS, other than institutions of higher education; N</t>
+          <t>Ricercatori principali a inizio carriera (Early Stage Investigator secondo i criteri NIH o entro 7 anni dalla qualifica) titolari di grant federali statunitensi interrotti</t>
         </is>
       </c>
       <c r="Z4" s="3" t="n"/>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>Ammessi anche enti non statunitensi (call NIH completa)</t>
+          <t>Mondiale</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
@@ -1109,12 +1107,12 @@
       </c>
       <c r="AC4" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/357206</t>
+          <t>https://www.michaeljfox.org/grant/bridge-funding-disrupted-neurodegenerative-research-grant-program-bfdn-powering-next</t>
         </is>
       </c>
       <c r="AD4" s="3" t="inlineStr">
         <is>
-          <t>Il bando NCMRR Early Career Research Award (R03), promosso dal National Institutes of Health (NIH), sostiene ricercatori a inizio carriera che intendono consolidare un percorso scientifico indipendente nel campo della riabilitazione medica. L'iniziativa finanzia progetti di ricerca clinica e di base allineati al Piano di Ricerca sulla Riabilitazione del NIH, con l'obiettivo di raccogliere dati preliminari sufficienti per future proposte R01. Sono ammissibili analisi secondarie di dati preesistenti, studi pilota indipendenti, sviluppo di metodologie di ricerca, studi traslazionali, ricerca sugli esiti e lo sviluppo di nuove tecnologie. Possono candidarsi istituzioni accademiche e di ricerca, comprese organizzazioni non profit ed enti stranieri con sede al di fuori degli Stati Uniti.</t>
+          <t>Il programma congiunto promosso da Alzheimer's Association, The Michael J. Fox Foundation e Robertson Foundation fornisce finanziamenti ponte per garantire la continuità a progetti di ricerca sulle malattie neurodegenerative (morbo di Parkinson, malattia di Alzheimer, demenza frontotemporale, demenza a corpi di Lewy e parkinsonismi atipici). L'iniziativa è specificamente rivolta a ricercatori a inizio carriera (Early Stage Investigator secondo i criteri NIH o entro 7 anni da tale qualifica) i cui finanziamenti federali statunitensi abbiano subito interruzioni, ritardi o tagli per cambiamenti operativi o di priorità. Il contributo, fino a un massimo di 250.000 dollari per una durata compresa tra 3 e 12 mesi, copre stipendi e costi diretti, richiedendo un cofinanziamento istituzionale fino al 25%.</t>
         </is>
       </c>
       <c r="AE4" s="4" t="n">
@@ -1128,7 +1126,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>WEB-00773cbd93aa</t>
+          <t>GG-PAR-25-226</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -1148,11 +1146,11 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Finanziamento ponte per la ricerca interrotta sulle malattie neurodegenerative (BFDN)</t>
+          <t>Sviluppo clinico precoce integrato (fase 1-2a) di nuovi agenti terapeutici per l'Alzheimer e le demenze correlate (UG3/UH3)</t>
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>46325</v>
+        <v>46345</v>
       </c>
       <c r="G5" s="5">
         <f>IF(F5="","",F5-TODAY())</f>
@@ -1165,69 +1163,61 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Michael J. Fox Foundation</t>
+          <t>National Institutes of Health</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>Michael J. Fox Foundation</t>
+          <t>Grants.gov</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>Bridge Funding for Disrupted Neurodegenerative Research Grant Program (BFDN) Powering the Next Generation of Research</t>
+          <t>National Institutes of Health – PAR-25-226</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>Bridge Funding for Disrupted Neurodegenerative Research Grant Program (BFDN) Powering the Next Generation of Research</t>
+          <t>Seamless Early-Stage Clinical Drug Development (Phase 1 to 2a) for Novel therapeutic Agents for the Spectrum of Alzheimer's Disease (AD) and AD-related Dementias (ADRD) (UG3/UH3 Clinical Trial Required)</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Parkinson, Invecchiamento, Altre malattie e riabilitazione</t>
+          <t>Invecchiamento</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>parkinson, dementi, alzheimer, neurodegenerat, neurological disease</t>
+          <t>dementi, alzheimer</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>Finanzia la continuità di progetti di ricerca su Parkinson, Alzheimer e demenze, senza una focalizzazione specifica sulla riabilitazione.</t>
-        </is>
-      </c>
-      <c r="P5" s="6" t="n">
-        <v>250000</v>
-      </c>
-      <c r="Q5" s="6" t="n">
-        <v>250000</v>
-      </c>
+          <t>Riguarda la malattia di Alzheimer e le demenze correlate, ma è incentrato sullo sviluppo farmacologico precoce e non su interventi riabilitativi.</t>
+        </is>
+      </c>
+      <c r="P5" s="6" t="n"/>
+      <c r="Q5" s="6" t="n"/>
       <c r="R5" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="S5" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="S5" s="2" t="n"/>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t>Bassa – 1 progetti finanziabili (stima: tasso storico non disponibile)</t>
+          <t>Non stimabile – dati insufficienti</t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t>Co-finanziamento richiesto (25% a carico del beneficiario)</t>
-        </is>
-      </c>
-      <c r="V5" s="4" t="n"/>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>12 mesi</t>
-        </is>
-      </c>
+          <t>Interamente finanziato</t>
+        </is>
+      </c>
+      <c r="V5" s="4" t="n">
+        <v>45618</v>
+      </c>
+      <c r="W5" s="2" t="n"/>
       <c r="X5" s="2" t="inlineStr">
         <is>
           <t>Ricerca</t>
@@ -1235,13 +1225,13 @@
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t>Ricercatori principali a inizio carriera (Early Stage Investigator secondo i criteri NIH o entro 7 anni dalla qualifica) titolari di grant federali statunitensi interrotti</t>
+          <t>Nonprofits that do not have a 501(c)(3) status with the IRS, other than institutions of higher education; County governments; City or township governments; Independent school districts; Public housing authorities/Indian housing authorities; Private institutions of higher education; For profit organizations other than small businesses; Nonprofits having a 501(c)(3) status with the IRS, other than i</t>
         </is>
       </c>
       <c r="Z5" s="3" t="n"/>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>Mondiale</t>
+          <t>Ammessi anche enti non statunitensi (call NIH completa)</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
@@ -1251,12 +1241,12 @@
       </c>
       <c r="AC5" s="7" t="inlineStr">
         <is>
-          <t>https://www.michaeljfox.org/grant/bridge-funding-disrupted-neurodegenerative-research-grant-program-bfdn-powering-next</t>
+          <t>https://www.grants.gov/search-results-detail/357343</t>
         </is>
       </c>
       <c r="AD5" s="3" t="inlineStr">
         <is>
-          <t>Il programma congiunto promosso da Alzheimer's Association, The Michael J. Fox Foundation e Robertson Foundation fornisce finanziamenti ponte per garantire la continuità a progetti di ricerca sulle malattie neurodegenerative (morbo di Parkinson, malattia di Alzheimer, demenza frontotemporale, demenza a corpi di Lewy e parkinsonismi atipici). L'iniziativa è specificamente rivolta a ricercatori a inizio carriera (Early Stage Investigator secondo i criteri NIH o entro 7 anni da tale qualifica) i cui finanziamenti federali statunitensi abbiano subito interruzioni, ritardi o tagli per cambiamenti operativi o di priorità. Il contributo, fino a un massimo di 250.000 dollari per una durata compresa tra 3 e 12 mesi, copre stipendi e costi diretti, richiedendo un cofinanziamento istituzionale fino al 25%.</t>
+          <t>Il bando invita a presentare proposte per lo sviluppo clinico precoce di nuovi agenti farmacologici non amiloidi e non tau per la malattia di Alzheimer e le demenze correlate. Tramite il meccanismo a fasi UG3/UH3, il bando unisce protocolli di sperimentazione di fase 1 con fasi 1b/2a per valutare sicurezza, tollerabilità ed efficacia su sintomi cognitivi o neuropsichiatrici in diversi stadi di malattia. L'avanzamento tra le fasi è subordinato a traguardi predefiniti. Possono partecipare istituti accademici, organizzazioni sanitarie, enti di ricerca pubblici e privati e istituzioni straniere non statunitensi.</t>
         </is>
       </c>
       <c r="AE5" s="4" t="n">
@@ -1270,7 +1260,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>GG-PAR-25-226</t>
+          <t>EU-HORIZON-HLTH-2027-02-DISEASE-01-two-stage</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -1290,11 +1280,11 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Sviluppo clinico precoce integrato (fase 1-2a) di nuovi agenti terapeutici per l'Alzheimer e le demenze correlate (UG3/UH3)</t>
+          <t>Interventi sanitari innovativi per le malattie non trasmissibili</t>
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>46345</v>
+        <v>46435</v>
       </c>
       <c r="G6" s="5">
         <f>IF(F6="","",F6-TODAY())</f>
@@ -1302,55 +1292,61 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>In scadenza (≤30 gg)</t>
+          <t>In apertura</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>National Institutes of Health</t>
+          <t>Commissione europea</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>Grants.gov</t>
+          <t>EU Funding &amp; Tenders Portal</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>National Institutes of Health – PAR-25-226</t>
+          <t>Horizon Europe – HORIZON  Research and Innovation Actions</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>Seamless Early-Stage Clinical Drug Development (Phase 1 to 2a) for Novel therapeutic Agents for the Spectrum of Alzheimer's Disease (AD) and AD-related Dementias (ADRD) (UG3/UH3 Clinical Trial Required)</t>
+          <t>Innovative healthcare interventions for non-communicable diseases</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Invecchiamento</t>
+          <t>Tecnologie riabilitazione, Altre malattie e riabilitazione</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>dementi, alzheimer</t>
+          <t>wearable, disabilit</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>Riguarda la malattia di Alzheimer e le demenze correlate, ma è incentrato sullo sviluppo farmacologico precoce e non su interventi riabilitativi.</t>
-        </is>
-      </c>
-      <c r="P6" s="6" t="n"/>
-      <c r="Q6" s="6" t="n"/>
+          <t>Bando incentrato su interventi innovativi e gestione clinica di patologie croniche cardiache e respiratorie, senza focus esclusivo sulla riabilitazione.</t>
+        </is>
+      </c>
+      <c r="P6" s="6" t="n">
+        <v>63800000</v>
+      </c>
+      <c r="Q6" s="6" t="n">
+        <v>8000000</v>
+      </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="n"/>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="n">
+        <v>8</v>
+      </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t>Non stimabile – dati insufficienti</t>
+          <t>Media – 8 progetti finanziabili (stima: tasso storico non disponibile)</t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
@@ -1359,7 +1355,7 @@
         </is>
       </c>
       <c r="V6" s="4" t="n">
-        <v>45618</v>
+        <v>46324</v>
       </c>
       <c r="W6" s="2" t="n"/>
       <c r="X6" s="2" t="inlineStr">
@@ -1369,13 +1365,17 @@
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t>County governments; Independent school districts; Others (see text field entitled "Additional Information on Eligibility" for clarification); City or township governments; Public and State controlled institutions of higher education; Native American tribal governments (Federally recognized); Private institutions of higher education; Small businesses; State governments; Special district governments</t>
-        </is>
-      </c>
-      <c r="Z6" s="3" t="n"/>
+          <t>Enti di ricerca, università, strutture sanitarie, PMI, startup, autorità regolatorie e organizzazioni di pazienti.</t>
+        </is>
+      </c>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t>Consorzio: min. 3 enti indipendenti da 3 paesi UE/associati (regola standard, verificare il topic)</t>
+        </is>
+      </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>Ammessi anche enti non statunitensi (call NIH completa)</t>
+          <t>Stati membri UE e paesi associati (altri paesi secondo le condizioni del topic)</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
@@ -1385,12 +1385,12 @@
       </c>
       <c r="AC6" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/357343</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-HLTH-2027-02-DISEASE-01-two-stage</t>
         </is>
       </c>
       <c r="AD6" s="3" t="inlineStr">
         <is>
-          <t>Il bando invita a presentare proposte per lo sviluppo clinico precoce di nuovi agenti farmacologici non amiloidi e non tau per la malattia di Alzheimer e le demenze correlate. Tramite il meccanismo a fasi UG3/UH3, il bando unisce protocolli di sperimentazione di fase 1 con fasi 1b/2a per valutare sicurezza, tollerabilità ed efficacia su sintomi cognitivi o neuropsichiatrici in diversi stadi di malattia. L'avanzamento tra le fasi è subordinato a traguardi predefiniti. Possono partecipare istituti accademici, organizzazioni sanitarie, enti di ricerca pubblici e privati e istituzioni straniere non statunitensi.</t>
+          <t>Il bando punta a ridurre l'impatto di specifiche malattie croniche non trasmissibili, tra cui patologie cardiovascolari, diabete, malattie respiratorie e renali croniche. Si finanzia la realizzazione di studi clinici in fase precoce per validare interventi terapeutici o di gestione della patologia innovativi o perfezionati, supportati da prove di concetto su sicurezza ed efficacia clinica. Le proposte devono integrare tecnologie digitali (come intelligenza artificiale o dispositivi indossabili) per il monitoraggio a lungo termine a domicilio. Possono partecipare consorzi internazionali composti da università, enti di ricerca clinica, ospedali, piccole e medie imprese, startup e organizzazioni di pazienti, promuovendo anche l'inclusione di competenze socio-umanistiche e l'interazione con autorità regolatorie per favorire la futura scalabilità degli interventi.</t>
         </is>
       </c>
       <c r="AE6" s="4" t="n">
@@ -1404,7 +1404,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>EU-HORIZON-HLTH-2027-02-DISEASE-01-two-stage</t>
+          <t>EU-HORIZON-HLTH-2027-01-DISEASE-10</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Interventi sanitari innovativi per le malattie non trasmissibili</t>
+          <t>Prevenzione e gestione delle malattie croniche non trasmissibili nei bambini e nei giovani (GACD)</t>
         </is>
       </c>
       <c r="F7" s="4" t="n">
@@ -1456,29 +1456,29 @@
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>Innovative healthcare interventions for non-communicable diseases</t>
+          <t>Prevention and management of chronic non-communicable diseases in children and young people (GACD)</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Tecnologie riabilitazione, Altre malattie e riabilitazione</t>
+          <t>Altre malattie e riabilitazione</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>wearable, disabilit</t>
+          <t>neurological disorder, disabilit</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>Bando incentrato su interventi innovativi e gestione clinica di patologie croniche cardiache e respiratorie, senza focus esclusivo sulla riabilitazione.</t>
+          <t>Finanzia la ricerca sull'implementazione per la gestione di patologie croniche non trasmissibili nei giovani, ambito che include percorsi di cura complessi ma non esclusivamente riabilitativi.</t>
         </is>
       </c>
       <c r="P7" s="6" t="n">
-        <v>63800000</v>
+        <v>11800000</v>
       </c>
       <c r="Q7" s="6" t="n">
-        <v>8000000</v>
+        <v>4000000</v>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
@@ -1486,11 +1486,11 @@
         </is>
       </c>
       <c r="S7" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t>Media – 8 progetti finanziabili (stima: tasso storico non disponibile)</t>
+          <t>Bassa – 3 progetti finanziabili (stima: tasso storico non disponibile)</t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t>Enti di ricerca, università, strutture sanitarie, PMI, startup, autorità regolatorie e organizzazioni di pazienti.</t>
+          <t>Ricercatori, professionisti sanitari, erogatori di servizi, decisori politici e stakeholder locali</t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
@@ -1529,26 +1529,26 @@
       </c>
       <c r="AC7" s="7" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-HLTH-2027-02-DISEASE-01-two-stage</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-HLTH-2027-01-DISEASE-10</t>
         </is>
       </c>
       <c r="AD7" s="3" t="inlineStr">
         <is>
-          <t>Il bando punta a ridurre l'impatto di specifiche malattie croniche non trasmissibili, tra cui patologie cardiovascolari, diabete, malattie respiratorie e renali croniche. Si finanzia la realizzazione di studi clinici in fase precoce per validare interventi terapeutici o di gestione della patologia innovativi o perfezionati, supportati da prove di concetto su sicurezza ed efficacia clinica. Le proposte devono integrare tecnologie digitali (come intelligenza artificiale o dispositivi indossabili) per il monitoraggio a lungo termine a domicilio. Possono partecipare consorzi internazionali composti da università, enti di ricerca clinica, ospedali, piccole e medie imprese, startup e organizzazioni di pazienti, promuovendo anche l'inclusione di competenze socio-umanistiche e l'interazione con autorità regolatorie per favorire la futura scalabilità degli interventi.</t>
+          <t>In collaborazione con la Global Alliance for Chronic Diseases (GACD), il bando sostiene la ricerca sull'implementazione di interventi evidence-based per la prevenzione, la diagnosi precoce e la gestione a lungo termine delle malattie croniche non trasmissibili in soggetti tra 1 e 24 anni. Il focus riguarda popolazioni vulnerabili in paesi a basso e medio reddito o comunità svantaggiate in paesi ad alto reddito. Si finanziano modelli di cura integrati, percorsi di transizione dall'assistenza pediatrica a quella per adulti, supporto ai caregiver e strategie costo-efficaci. Possono partecipare ricercatori, operatori sanitari e istituzioni di ricerca appartenenti a consorzi eleggibili secondo le regole di Horizon Europe.</t>
         </is>
       </c>
       <c r="AE7" s="4" t="n">
         <v>46316</v>
       </c>
       <c r="AF7" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AG7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>EU-HORIZON-HLTH-2027-01-DISEASE-10</t>
+          <t>WEB-6768384ca0cb</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -1568,84 +1568,82 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Prevenzione e gestione delle malattie croniche non trasmissibili nei bambini e nei giovani (GACD)</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>46435</v>
-      </c>
+          <t>Programma per lo sviluppo della pipeline terapeutica nella malattia di Parkinson</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="n"/>
       <c r="G8" s="5">
         <f>IF(F8="","",F8-TODAY())</f>
         <v/>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>In apertura</t>
+          <t>Scadenza da verificare</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Commissione europea</t>
+          <t>Michael J. Fox Foundation</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>EU Funding &amp; Tenders Portal</t>
+          <t>Michael J. Fox Foundation</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>Horizon Europe – HORIZON  Research and Innovation Actions</t>
+          <t>Parkinson's Disease Therapeutics Pipeline Program</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>Prevention and management of chronic non-communicable diseases in children and young people (GACD)</t>
+          <t>Parkinson's Disease Therapeutics Pipeline Program</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Altre malattie e riabilitazione</t>
+          <t>Parkinson</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>neurological disorder, disabilit</t>
+          <t>parkinson</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>Finanzia la ricerca sull'implementazione per la gestione di patologie croniche non trasmissibili nei giovani, ambito che include percorsi di cura complessi ma non esclusivamente riabilitativi.</t>
+          <t>Focalizzato sullo sviluppo terapeutico e farmacologico preclinico e clinico per il Parkinson, senza un focus specifico sulla riabilitazione.</t>
         </is>
       </c>
       <c r="P8" s="6" t="n">
-        <v>11800000</v>
+        <v>250000</v>
       </c>
       <c r="Q8" s="6" t="n">
-        <v>4000000</v>
+        <v>5000000</v>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="n">
-        <v>3</v>
-      </c>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="n"/>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t>Bassa – 3 progetti finanziabili (stima: tasso storico non disponibile)</t>
+          <t>Non stimabile – dati insufficienti</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t>Interamente finanziato</t>
-        </is>
-      </c>
-      <c r="V8" s="4" t="n">
-        <v>46324</v>
-      </c>
-      <c r="W8" s="2" t="n"/>
+          <t>Non indicato</t>
+        </is>
+      </c>
+      <c r="V8" s="4" t="n"/>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>36 mesi</t>
+        </is>
+      </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
           <t>Ricerca</t>
@@ -1653,17 +1651,17 @@
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t>Ricercatori, professionisti sanitari, erogatori di servizi, decisori politici e stakeholder locali</t>
+          <t>Imprese biotech/pharma, partenariati accademia-industria e istituti accademici</t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t>Consorzio: min. 3 enti indipendenti da 3 paesi UE/associati (regola standard, verificare il topic)</t>
+          <t>Aperto a collaborazioni accademia-industria, singole aziende o progetti a guida accademica</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>Stati membri UE e paesi associati (altri paesi secondo le condizioni del topic)</t>
+          <t>Mondiale</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
@@ -1673,121 +1671,119 @@
       </c>
       <c r="AC8" s="7" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-HLTH-2027-01-DISEASE-10</t>
+          <t>https://www.michaeljfox.org/grant/parkinsons-disease-therapeutics-pipeline-program</t>
         </is>
       </c>
       <c r="AD8" s="3" t="inlineStr">
         <is>
-          <t>In collaborazione con la Global Alliance for Chronic Diseases (GACD), il bando sostiene la ricerca sull'implementazione di interventi evidence-based per la prevenzione, la diagnosi precoce e la gestione a lungo termine delle malattie croniche non trasmissibili in soggetti tra 1 e 24 anni. Il focus riguarda popolazioni vulnerabili in paesi a basso e medio reddito o comunità svantaggiate in paesi ad alto reddito. Si finanziano modelli di cura integrati, percorsi di transizione dall'assistenza pediatrica a quella per adulti, supporto ai caregiver e strategie costo-efficaci. Possono partecipare ricercatori, operatori sanitari e istituzioni di ricerca appartenenti a consorzi eleggibili secondo le regole di Horizon Europe.</t>
+          <t>Il Therapeutics Pipeline Program della Michael J. Fox Foundation finanzia lo sviluppo preclinico e clinico di interventi terapeutici modificanti la malattia o mirati al controllo sintomatico del Parkinson, integrando strumenti biomarcatori decisionali. Il programma supporta progetti da uno a tre anni con contributi compresi generalmente tra 250.000 e oltre 5 milioni di dollari, a seconda della fase di avanzamento. La candidatura è aperta a imprese biotech, collaborazioni accademia-industria e, in casi specifici, a gruppi esclusivamente accademici. Il processo di selezione è strutturato in due fasi: invio continuo di pre-proposte e, su invito, presentazione della proposta completa secondo scadenze cicliche periodiche. Sono esclusi studi su integratori alimentari o scoperta di target precoci.</t>
         </is>
       </c>
       <c r="AE8" s="4" t="n">
         <v>46316</v>
       </c>
       <c r="AF8" s="4" t="n">
-        <v>46313</v>
+        <v>46312</v>
       </c>
       <c r="AG8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>WEB-6768384ca0cb</t>
+          <t>GG-RFA-NS-26-028</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Sì</t>
+          <t>Da verificare</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Ricerca clinica</t>
+          <t>Tecnologia / innovazione</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Programma per lo sviluppo della pipeline terapeutica nella malattia di Parkinson</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="n"/>
+          <t>Iniziativa HEAL: ottimizzazione dei dispositivi medici terapeutici attraverso la ricerca meccanicistica interdisciplinare (RM1)</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>46325</v>
+      </c>
       <c r="G9" s="5">
         <f>IF(F9="","",F9-TODAY())</f>
         <v/>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Scadenza da verificare</t>
+          <t>In scadenza (≤30 gg)</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Michael J. Fox Foundation</t>
+          <t>National Institutes of Health</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>Michael J. Fox Foundation</t>
+          <t>Grants.gov</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>Parkinson's Disease Therapeutics Pipeline Program</t>
+          <t>National Institutes of Health – RFA-NS-26-028</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>Parkinson's Disease Therapeutics Pipeline Program</t>
+          <t>HEAL Initiative: Optimization of Therapeutic Medical Devices through Team Science Mechanistic Research (RM1)</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Parkinson</t>
+          <t>Ictus, Altre malattie e riabilitazione</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>parkinson</t>
+          <t>stroke, neurological disorder</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>Focalizzato sullo sviluppo terapeutico e farmacologico preclinico e clinico per il Parkinson, senza un focus specifico sulla riabilitazione.</t>
-        </is>
-      </c>
-      <c r="P9" s="6" t="n">
-        <v>250000</v>
-      </c>
-      <c r="Q9" s="6" t="n">
-        <v>5000000</v>
-      </c>
+          <t>Supporta la ricerca sui meccanismi d'azione di dispositivi medici terapeutici per patologie neurologiche e dolore cronico, altamente rilevanti per la neuroriabilitazione.</t>
+        </is>
+      </c>
+      <c r="P9" s="6" t="n"/>
+      <c r="Q9" s="6" t="n"/>
       <c r="R9" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="S9" s="2" t="n"/>
+      <c r="S9" s="2" t="n">
+        <v>4</v>
+      </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t>Non stimabile – dati insufficienti</t>
+          <t>Bassa – 4 progetti finanziabili (stima: tasso storico non disponibile)</t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t>Non indicato</t>
-        </is>
-      </c>
-      <c r="V9" s="4" t="n"/>
-      <c r="W9" s="2" t="inlineStr">
-        <is>
-          <t>36 mesi</t>
-        </is>
-      </c>
+          <t>Interamente finanziato</t>
+        </is>
+      </c>
+      <c r="V9" s="4" t="n">
+        <v>46097</v>
+      </c>
+      <c r="W9" s="2" t="n"/>
       <c r="X9" s="2" t="inlineStr">
         <is>
           <t>Ricerca</t>
@@ -1795,17 +1791,17 @@
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t>Imprese biotech/pharma, partenariati accademia-industria e istituti accademici</t>
+          <t>For profit organizations other than small businesses; Public housing authorities/Indian housing authorities; Independent school districts; Small businesses; County governments; Private institutions of higher education; Others (see text field entitled "Additional Information on Eligibility" for clarification); Nonprofits having a 501(c)(3) status with the IRS, other than institutions of higher educ</t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t>Aperto a collaborazioni accademia-industria, singole aziende o progetti a guida accademica</t>
+          <t>Team scientifici interdisciplinari comprendenti competenze ingegneristiche, biologiche, computazionali e cliniche</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>Mondiale</t>
+          <t>Enti esteri: da verificare nel bando</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
@@ -1815,12 +1811,12 @@
       </c>
       <c r="AC9" s="7" t="inlineStr">
         <is>
-          <t>https://www.michaeljfox.org/grant/parkinsons-disease-therapeutics-pipeline-program</t>
+          <t>https://www.grants.gov/search-results-detail/361520</t>
         </is>
       </c>
       <c r="AD9" s="3" t="inlineStr">
         <is>
-          <t>Il Therapeutics Pipeline Program della Michael J. Fox Foundation finanzia lo sviluppo preclinico e clinico di interventi terapeutici modificanti la malattia o mirati al controllo sintomatico del Parkinson, integrando strumenti biomarcatori decisionali. Il programma supporta progetti da uno a tre anni con contributi compresi generalmente tra 250.000 e oltre 5 milioni di dollari, a seconda della fase di avanzamento. La candidatura è aperta a imprese biotech, collaborazioni accademia-industria e, in casi specifici, a gruppi esclusivamente accademici. Il processo di selezione è strutturato in due fasi: invio continuo di pre-proposte e, su invito, presentazione della proposta completa secondo scadenze cicliche periodiche. Sono esclusi studi su integratori alimentari o scoperta di target precoci.</t>
+          <t>Il National Institute of Neurological Disorders and Stroke (NINDS), nell'ambito dell'iniziativa NIH HEAL, preannuncia un'opportunità di finanziamento destinata a indagare i meccanismi d'azione dei dispositivi medici terapeutici per ottimizzare i risultati clinici nelle patologie neurologiche e nel trattamento del dolore. La call intende finanziare team scientifici altamente interdisciplinari (con competenze che spaziano dall'ingegneria e biologia alla clinica, biostatistica, intelligenza artificiale e sperimentazioni cliniche). Le attività ammissibili comprendono studi clinici meccanicistici, modelli computazionali o simulazioni e ricerche precliniche su modelli animali, applicabili sia a dispositivi sperimentali sia a tecnologie già approvate dalla FDA e impiegate nella pratica clinica. La partecipazione è aperta anche a istituzioni di ricerca estere non statunitensi.</t>
         </is>
       </c>
       <c r="AE9" s="4" t="n">
@@ -1834,7 +1830,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>GG-RFA-NS-26-028</t>
+          <t>GG-HT942526SCIRPTRA</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -1849,16 +1845,16 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Tecnologia / innovazione</t>
+          <t>Ricerca clinica</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Iniziativa HEAL: ottimizzazione dei dispositivi medici terapeutici attraverso la ricerca meccanicistica interdisciplinare (RM1)</t>
+          <t>Programma di ricerca sulle lesioni del midollo spinale del Dipartimento della Difesa: finanziamento per la ricerca traslazionale</t>
         </is>
       </c>
       <c r="F10" s="4" t="n">
-        <v>46325</v>
+        <v>46338</v>
       </c>
       <c r="G10" s="5">
         <f>IF(F10="","",F10-TODAY())</f>
@@ -1871,7 +1867,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>National Institutes of Health</t>
+          <t>Defense Health Agency Contracting Activity - DHACA</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1881,30 +1877,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>National Institutes of Health – RFA-NS-26-028</t>
+          <t>Defense Health Agency Contracting Activity - DHACA – HT942526SCIRPTRA</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>HEAL Initiative: Optimization of Therapeutic Medical Devices through Team Science Mechanistic Research (RM1)</t>
+          <t>DoW Spinal Cord Injury, Translational Research Award</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Ictus, Altre malattie e riabilitazione</t>
+          <t>Altre malattie e riabilitazione</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>stroke, neurological disorder</t>
+          <t>spinal cord injur</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>Supporta la ricerca sui meccanismi d'azione di dispositivi medici terapeutici per patologie neurologiche e dolore cronico, altamente rilevanti per la neuroriabilitazione.</t>
-        </is>
-      </c>
-      <c r="P10" s="6" t="n"/>
+          <t>Dedicato alla ricerca traslazionale per l'applicazione clinica nelle lesioni del midollo spinale, patologia cardine della riabilitazione neurologica.</t>
+        </is>
+      </c>
+      <c r="P10" s="6" t="n">
+        <v>8320000</v>
+      </c>
       <c r="Q10" s="6" t="n"/>
       <c r="R10" s="2" t="inlineStr">
         <is>
@@ -1925,7 +1923,7 @@
         </is>
       </c>
       <c r="V10" s="4" t="n">
-        <v>46097</v>
+        <v>46147</v>
       </c>
       <c r="W10" s="2" t="n"/>
       <c r="X10" s="2" t="inlineStr">
@@ -1935,12 +1933,12 @@
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t>Small businesses; Native American tribal organizations (other than Federally recognized tribal governments); Private institutions of higher education; Native American tribal governments (Federally recognized); Nonprofits that do not have a 501(c)(3) status with the IRS, other than institutions of higher education; State governments; Others (see text field entitled "Additional Information on Eligib</t>
+          <t>Unrestricted (i.e., open to any type of entity above), subject to any clarification in text field entitled "Additional Information on Eligibility"</t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t>Team scientifici interdisciplinari comprendenti competenze ingegneristiche, biologiche, computazionali e cliniche</t>
+          <t>Obbligatorio almeno un partner comunitario esperto per esperienza diretta di lesione midollare; ammessa opzione a due PI con ricercatore junior.</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1955,26 +1953,26 @@
       </c>
       <c r="AC10" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/361520</t>
+          <t>https://www.grants.gov/search-results-detail/362222</t>
         </is>
       </c>
       <c r="AD10" s="3" t="inlineStr">
         <is>
-          <t>Il National Institute of Neurological Disorders and Stroke (NINDS), nell'ambito dell'iniziativa NIH HEAL, preannuncia un'opportunità di finanziamento destinata a indagare i meccanismi d'azione dei dispositivi medici terapeutici per ottimizzare i risultati clinici nelle patologie neurologiche e nel trattamento del dolore. La call intende finanziare team scientifici altamente interdisciplinari (con competenze che spaziano dall'ingegneria e biologia alla clinica, biostatistica, intelligenza artificiale e sperimentazioni cliniche). Le attività ammissibili comprendono studi clinici meccanicistici, modelli computazionali o simulazioni e ricerche precliniche su modelli animali, applicabili sia a dispositivi sperimentali sia a tecnologie già approvate dalla FDA e impiegate nella pratica clinica. La partecipazione è aperta anche a istituzioni di ricerca estere non statunitensi.</t>
+          <t>Il Translational Research Award, nell'ambito del programma di ricerca sulle lesioni del midollo spinale (SCIRP), sostiene progetti di ricerca traslazionale mirati ad accelerare il passaggio di idee e interventi innovativi dal laboratorio alle applicazioni cliniche per pazienti con lesioni midollari. Le proposte devono includere obbligatoriamente come partner almeno un membro o consulente della comunità con lesione spinale vissuta in prima persona o un rappresentante di organizzazioni attive nel settore. È prevista l'opzione di collaborazione paritaria che consente a un ricercatore esperto di affiancare un ricercatore a inizio carriera nella guida del progetto. Possono partecipare atenei, enti ospedalieri, istituti di ricerca pubblici o privati e organizzazioni specializzate.</t>
         </is>
       </c>
       <c r="AE10" s="4" t="n">
         <v>46316</v>
       </c>
       <c r="AF10" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AG10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>GG-HT942526SCIRPTRA</t>
+          <t>GG-HT942526SCIRPCTA</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -1994,7 +1992,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Programma di ricerca sulle lesioni del midollo spinale del Dipartimento della Difesa: finanziamento per la ricerca traslazionale</t>
+          <t>DoW Ricerca sulle lesioni del midollo spinale, finanziamento per trial clinici</t>
         </is>
       </c>
       <c r="F11" s="4" t="n">
@@ -2021,12 +2019,12 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>Defense Health Agency Contracting Activity - DHACA – HT942526SCIRPTRA</t>
+          <t>Defense Health Agency Contracting Activity - DHACA – HT942526SCIRPCTA</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>DoW Spinal Cord Injury, Translational Research Award</t>
+          <t>DoW Spinal Cord Injury, Clinical Trial Award</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -2041,11 +2039,11 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>Dedicato alla ricerca traslazionale per l'applicazione clinica nelle lesioni del midollo spinale, patologia cardine della riabilitazione neurologica.</t>
+          <t>Finanzia trial clinici focalizzati sul trattamento e sulla gestione funzionale delle lesioni del midollo spinale.</t>
         </is>
       </c>
       <c r="P11" s="6" t="n">
-        <v>8320000</v>
+        <v>9760000</v>
       </c>
       <c r="Q11" s="6" t="n"/>
       <c r="R11" s="2" t="inlineStr">
@@ -2054,11 +2052,11 @@
         </is>
       </c>
       <c r="S11" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t>Bassa – 4 progetti finanziabili (stima: tasso storico non disponibile)</t>
+          <t>Bassa – 2 progetti finanziabili (stima: tasso storico non disponibile)</t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
@@ -2082,7 +2080,7 @@
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
-          <t>Obbligatorio almeno un partner comunitario esperto per esperienza diretta di lesione midollare; ammessa opzione a due PI con ricercatore junior.</t>
+          <t>Obbligatori almeno 2 partner della comunità con esperienza di lesione midollare; possibile collaborazione tra 2 PI</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -2097,12 +2095,12 @@
       </c>
       <c r="AC11" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/362222</t>
+          <t>https://www.grants.gov/search-results-detail/362224</t>
         </is>
       </c>
       <c r="AD11" s="3" t="inlineStr">
         <is>
-          <t>Il Translational Research Award, nell'ambito del programma di ricerca sulle lesioni del midollo spinale (SCIRP), sostiene progetti di ricerca traslazionale mirati ad accelerare il passaggio di idee e interventi innovativi dal laboratorio alle applicazioni cliniche per pazienti con lesioni midollari. Le proposte devono includere obbligatoriamente come partner almeno un membro o consulente della comunità con lesione spinale vissuta in prima persona o un rappresentante di organizzazioni attive nel settore. È prevista l'opzione di collaborazione paritaria che consente a un ricercatore esperto di affiancare un ricercatore a inizio carriera nella guida del progetto. Possono partecipare atenei, enti ospedalieri, istituti di ricerca pubblici o privati e organizzazioni specializzate.</t>
+          <t>Il bando Clinical Trial Award del programma SCIRP (anno fiscale 2026) finanzia la rapida attuazione di studi clinici con un potenziale impatto significativo sul trattamento o sulla gestione delle persone con lesione del midollo spinale. L'opportunità include un'opzione di partenariato per ricercatori all'inizio della carriera (Early-Career Partnership Option), che consente la partecipazione di due Principal Investigator, purché almeno uno sia un ricercatore junior. Le proposte devono obbligatoriamente coinvolgere almeno due rappresentanti o partner della comunità con esperienza diretta di lesione midollare, che collaboreranno attivamente fornendo consulenza durante l'intera pianificazione e implementazione dello studio clinico.</t>
         </is>
       </c>
       <c r="AE11" s="4" t="n">
@@ -2116,7 +2114,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>GG-HT942526SCIRPCTA</t>
+          <t>GG-HT942526SCIRPCTRA</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -2136,7 +2134,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>DoW Ricerca sulle lesioni del midollo spinale, finanziamento per trial clinici</t>
+          <t>DoW Ricerca sulle lesioni del midollo spinale, finanziamento per la ricerca clinica traslazionale</t>
         </is>
       </c>
       <c r="F12" s="4" t="n">
@@ -2163,12 +2161,12 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>Defense Health Agency Contracting Activity - DHACA – HT942526SCIRPCTA</t>
+          <t>Defense Health Agency Contracting Activity - DHACA – HT942526SCIRPCTRA</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>DoW Spinal Cord Injury, Clinical Trial Award</t>
+          <t>DoW Spinal Cord Injury, Clinical Translation Research Award</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -2178,16 +2176,16 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>spinal cord injur</t>
+          <t>rehabilitat, spinal cord injur</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>Finanzia trial clinici focalizzati sul trattamento e sulla gestione funzionale delle lesioni del midollo spinale.</t>
+          <t>Finanzia ricerca clinica traslazionale volta a identificare le opzioni più efficaci di riabilitazione e trattamento nelle lesioni midollari.</t>
         </is>
       </c>
       <c r="P12" s="6" t="n">
-        <v>9760000</v>
+        <v>6120000</v>
       </c>
       <c r="Q12" s="6" t="n"/>
       <c r="R12" s="2" t="inlineStr">
@@ -2196,11 +2194,11 @@
         </is>
       </c>
       <c r="S12" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t>Bassa – 2 progetti finanziabili (stima: tasso storico non disponibile)</t>
+          <t>Bassa – 3 progetti finanziabili (stima: tasso storico non disponibile)</t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
@@ -2224,7 +2222,7 @@
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t>Obbligatori almeno 2 partner della comunità con esperienza di lesione midollare; possibile collaborazione tra 2 PI</t>
+          <t>Obbligatori almeno due partner della comunità di pazienti; opzione con due PI di cui uno a inizio carriera</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -2239,26 +2237,26 @@
       </c>
       <c r="AC12" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/362224</t>
+          <t>https://www.grants.gov/search-results-detail/362225</t>
         </is>
       </c>
       <c r="AD12" s="3" t="inlineStr">
         <is>
-          <t>Il bando Clinical Trial Award del programma SCIRP (anno fiscale 2026) finanzia la rapida attuazione di studi clinici con un potenziale impatto significativo sul trattamento o sulla gestione delle persone con lesione del midollo spinale. L'opportunità include un'opzione di partenariato per ricercatori all'inizio della carriera (Early-Career Partnership Option), che consente la partecipazione di due Principal Investigator, purché almeno uno sia un ricercatore junior. Le proposte devono obbligatoriamente coinvolgere almeno due rappresentanti o partner della comunità con esperienza diretta di lesione midollare, che collaboreranno attivamente fornendo consulenza durante l'intera pianificazione e implementazione dello studio clinico.</t>
+          <t>Il bando Clinical Translation Research Award dello SCIRP per l'anno fiscale 2026 promuove ricerche cliniche emergenti o ad alto impatto che necessitano di studi preliminari, di fattibilità o di ottimizzazione per preparare futuri trial clinici definitivi. Tra gli obiettivi principali rientrano l'accelerazione del trasferimento clinico di nuove tecniche o interventi e l'identificazione delle migliori opzioni diagnostiche, terapeutiche e riabilitative per supportare le decisioni di pazienti e clinici nell'ambito delle lesioni del midollo spinale. Il bando include un'opzione per due Principal Investigator (con almeno un ricercatore junior) e impone il coinvolgimento di almeno due partner della comunità di pazienti come consulenti del progetto.</t>
         </is>
       </c>
       <c r="AE12" s="4" t="n">
         <v>46316</v>
       </c>
       <c r="AF12" s="4" t="n">
-        <v>46313</v>
+        <v>46312</v>
       </c>
       <c r="AG12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>GG-HT942526SCIRPCTRA</t>
+          <t>GG-HT942526SCIRPIIRA</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -2278,7 +2276,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>DoW Ricerca sulle lesioni del midollo spinale, finanziamento per la ricerca clinica traslazionale</t>
+          <t>DoW Ricerca sulle lesioni del midollo spinale, finanziamento per la ricerca promossa dal ricercatore</t>
         </is>
       </c>
       <c r="F13" s="4" t="n">
@@ -2305,12 +2303,12 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Defense Health Agency Contracting Activity - DHACA – HT942526SCIRPCTRA</t>
+          <t>Defense Health Agency Contracting Activity - DHACA – HT942526SCIRPIIRA</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>DoW Spinal Cord Injury, Clinical Translation Research Award</t>
+          <t>DoW Spinal Cord Injury, Investigator-Initiated Research Award</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -2320,16 +2318,16 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>rehabilitat, spinal cord injur</t>
+          <t>spinal cord injur</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>Finanzia ricerca clinica traslazionale volta a identificare le opzioni più efficaci di riabilitazione e trattamento nelle lesioni midollari.</t>
+          <t>Supporta la ricerca traslazionale e clinica mirata a migliorare l'assistenza e la qualità di vita nelle lesioni midollari.</t>
         </is>
       </c>
       <c r="P13" s="6" t="n">
-        <v>6120000</v>
+        <v>4960000</v>
       </c>
       <c r="Q13" s="6" t="n"/>
       <c r="R13" s="2" t="inlineStr">
@@ -2338,11 +2336,11 @@
         </is>
       </c>
       <c r="S13" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t>Bassa – 3 progetti finanziabili (stima: tasso storico non disponibile)</t>
+          <t>Media – 6 progetti finanziabili (stima: tasso storico non disponibile)</t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
@@ -2366,7 +2364,7 @@
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t>Obbligatori almeno due partner della comunità di pazienti; opzione con due PI di cui uno a inizio carriera</t>
+          <t>Opzione per due Principal Investigator (di cui almeno uno a inizio carriera)</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2381,26 +2379,26 @@
       </c>
       <c r="AC13" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/362225</t>
+          <t>https://www.grants.gov/search-results-detail/362226</t>
         </is>
       </c>
       <c r="AD13" s="3" t="inlineStr">
         <is>
-          <t>Il bando Clinical Translation Research Award dello SCIRP per l'anno fiscale 2026 promuove ricerche cliniche emergenti o ad alto impatto che necessitano di studi preliminari, di fattibilità o di ottimizzazione per preparare futuri trial clinici definitivi. Tra gli obiettivi principali rientrano l'accelerazione del trasferimento clinico di nuove tecniche o interventi e l'identificazione delle migliori opzioni diagnostiche, terapeutiche e riabilitative per supportare le decisioni di pazienti e clinici nell'ambito delle lesioni del midollo spinale. Il bando include un'opzione per due Principal Investigator (con almeno un ricercatore junior) e impone il coinvolgimento di almeno due partner della comunità di pazienti come consulenti del progetto.</t>
+          <t>Il bando Investigator-Initiated Research Award (IIRA) per l'anno fiscale 2026, promosso dal programma SCIRP, supporta studi con un impatto rilevante sulla ricerca, sulla cura clinica e sulla qualità della vita delle persone con lesioni del midollo spinale. L'opportunità finanzia progetti che spaziano dalla ricerca fondamentale alle scienze traslazionali, scoraggiando gli studi focalizzati esclusivamente sull'identificazione di bersagli farmacologici o biologici. Il bando contempla una modalità opzionale di partenariato che permette a due Principal Investigator di fare domanda congiunta con premi separati, a condizione che almeno uno dei due sia un ricercatore a inizio carriera.</t>
         </is>
       </c>
       <c r="AE13" s="4" t="n">
         <v>46316</v>
       </c>
       <c r="AF13" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AG13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>GG-HT942526SCIRPIIRA</t>
+          <t>GG-RFA-DA-28-011</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -2420,11 +2418,11 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>DoW Ricerca sulle lesioni del midollo spinale, finanziamento per la ricerca promossa dal ricercatore</t>
+          <t>Iniziativa HEAL: gestione integrata del dolore cronico e del disturbo da uso di oppioidi (IMPOWR) - Centri di ricerca (RM1)</t>
         </is>
       </c>
       <c r="F14" s="4" t="n">
-        <v>46338</v>
+        <v>46413</v>
       </c>
       <c r="G14" s="5">
         <f>IF(F14="","",F14-TODAY())</f>
@@ -2432,12 +2430,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>In scadenza (≤30 gg)</t>
+          <t>Aperto</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Defense Health Agency Contracting Activity - DHACA</t>
+          <t>National Institutes of Health</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -2447,12 +2445,12 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>Defense Health Agency Contracting Activity - DHACA – HT942526SCIRPIIRA</t>
+          <t>National Institutes of Health – RFA-DA-28-011</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>DoW Spinal Cord Injury, Investigator-Initiated Research Award</t>
+          <t>HEAL Initiative: Integrative Management of Chronic Pain and OUD for Whole Recovery (IMPOWR): Research Centers (RM1 Clinical Trial Required)</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -2462,29 +2460,25 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>spinal cord injur</t>
+          <t>chronic pain</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>Supporta la ricerca traslazionale e clinica mirata a migliorare l'assistenza e la qualità di vita nelle lesioni midollari.</t>
-        </is>
-      </c>
-      <c r="P14" s="6" t="n">
-        <v>4960000</v>
-      </c>
+          <t>È dedicato alla gestione integrata a lungo termine del dolore cronico e al recupero funzionale dei pazienti.</t>
+        </is>
+      </c>
+      <c r="P14" s="6" t="n"/>
       <c r="Q14" s="6" t="n"/>
       <c r="R14" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="S14" s="2" t="n">
-        <v>6</v>
-      </c>
+      <c r="S14" s="2" t="n"/>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t>Media – 6 progetti finanziabili (stima: tasso storico non disponibile)</t>
+          <t>Non stimabile – dati insufficienti</t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr">
@@ -2493,7 +2487,7 @@
         </is>
       </c>
       <c r="V14" s="4" t="n">
-        <v>46147</v>
+        <v>46301</v>
       </c>
       <c r="W14" s="2" t="n"/>
       <c r="X14" s="2" t="inlineStr">
@@ -2503,14 +2497,10 @@
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t>Unrestricted (i.e., open to any type of entity above), subject to any clarification in text field entitled "Additional Information on Eligibility"</t>
-        </is>
-      </c>
-      <c r="Z14" s="3" t="inlineStr">
-        <is>
-          <t>Opzione per due Principal Investigator (di cui almeno uno a inizio carriera)</t>
-        </is>
-      </c>
+          <t>Special district governments; Nonprofits that do not have a 501(c)(3) status with the IRS, other than institutions of higher education; State governments; Public and State controlled institutions of higher education; Native American tribal governments (Federally recognized); Public housing authorities/Indian housing authorities; Independent school districts; Private institutions of higher educatio</t>
+        </is>
+      </c>
+      <c r="Z14" s="3" t="n"/>
       <c r="AA14" s="2" t="inlineStr">
         <is>
           <t>Enti esteri: da verificare nel bando</t>
@@ -2523,12 +2513,12 @@
       </c>
       <c r="AC14" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/362226</t>
+          <t>https://www.grants.gov/search-results-detail/360048</t>
         </is>
       </c>
       <c r="AD14" s="3" t="inlineStr">
         <is>
-          <t>Il bando Investigator-Initiated Research Award (IIRA) per l'anno fiscale 2026, promosso dal programma SCIRP, supporta studi con un impatto rilevante sulla ricerca, sulla cura clinica e sulla qualità della vita delle persone con lesioni del midollo spinale. L'opportunità finanzia progetti che spaziano dalla ricerca fondamentale alle scienze traslazionali, scoraggiando gli studi focalizzati esclusivamente sull'identificazione di bersagli farmacologici o biologici. Il bando contempla una modalità opzionale di partenariato che permette a due Principal Investigator di fare domanda congiunta con premi separati, a condizione che almeno uno dei due sia un ricercatore a inizio carriera.</t>
+          <t>L'avviso anticipa il rinnovo della rete di ricerca IMPOWR, parte dell'iniziativa NIH HEAL, finalizzata allo sviluppo e alla validazione di modelli integrati per la gestione del dolore cronico e del disturbo da uso di oppioidi. Il network comprenderà molteplici progetti di ricerca coordinati da un centro centrale, con l'obiettivo di condurre studi clinici per testare approcci assistenziali innovativi in grado di migliorare significativamente l'erogazione delle cure nei sistemi sanitari. Possono partecipare istituzioni universitarie, ospedaliere, enti di ricerca no-profit o profit e organizzazioni estere non statunitensi.</t>
         </is>
       </c>
       <c r="AE14" s="4" t="n">
@@ -2542,7 +2532,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>GG-RFA-DA-28-011</t>
+          <t>GG-PAR-27-065</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -2562,11 +2552,11 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Iniziativa HEAL: gestione integrata del dolore cronico e del disturbo da uso di oppioidi (IMPOWR) - Centri di ricerca (RM1)</t>
+          <t>Trial clinici esplorativi e di efficacia del NINDS (UG3/UH3 - Clinical Trial obbligatorio)</t>
         </is>
       </c>
       <c r="F15" s="4" t="n">
-        <v>46413</v>
+        <v>47186</v>
       </c>
       <c r="G15" s="5">
         <f>IF(F15="","",F15-TODAY())</f>
@@ -2589,27 +2579,27 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>National Institutes of Health – RFA-DA-28-011</t>
+          <t>National Institutes of Health – PAR-27-065</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>HEAL Initiative: Integrative Management of Chronic Pain and OUD for Whole Recovery (IMPOWR): Research Centers (RM1 Clinical Trial Required)</t>
+          <t>NINDS Efficacy and Exploratory Clinical Trials (UG3/UH3 - Clinical Trial Required)</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Altre malattie e riabilitazione</t>
+          <t>Ictus, Altre malattie e riabilitazione</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>chronic pain</t>
+          <t>stroke, rehabilitat, neurological disorder</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>È dedicato alla gestione integrata a lungo termine del dolore cronico e al recupero funzionale dei pazienti.</t>
+          <t>Finanzia trial clinici neurologici e ammette esplicitamente terapie e interventi di riabilitazione lungo tutto l'arco della vita.</t>
         </is>
       </c>
       <c r="P15" s="6" t="n"/>
@@ -2631,7 +2621,7 @@
         </is>
       </c>
       <c r="V15" s="4" t="n">
-        <v>46301</v>
+        <v>46265</v>
       </c>
       <c r="W15" s="2" t="n"/>
       <c r="X15" s="2" t="inlineStr">
@@ -2641,10 +2631,14 @@
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t>Native American tribal governments (Federally recognized); Nonprofits having a 501(c)(3) status with the IRS, other than institutions of higher education; City or township governments; For profit organizations other than small businesses; Public and State controlled institutions of higher education; State governments; Others (see text field entitled "Additional Information on Eligibility" for clar</t>
-        </is>
-      </c>
-      <c r="Z15" s="3" t="n"/>
+          <t>Small businesses; Private institutions of higher education; Public and State controlled institutions of higher education; Native American tribal governments (Federally recognized); State governments; City or township governments; Independent school districts; Nonprofits having a 501(c)(3) status with the IRS, other than institutions of higher education; Nonprofits that do not have a 501(c)(3) stat</t>
+        </is>
+      </c>
+      <c r="Z15" s="3" t="inlineStr">
+        <is>
+          <t>Non sono ammessi sub-accordi o subappalti a entità estere; le organizzazioni estere possono candidarsi direttamente come capofila</t>
+        </is>
+      </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
           <t>Enti esteri: da verificare nel bando</t>
@@ -2657,26 +2651,26 @@
       </c>
       <c r="AC15" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/360048</t>
+          <t>https://www.grants.gov/search-results-detail/360404</t>
         </is>
       </c>
       <c r="AD15" s="3" t="inlineStr">
         <is>
-          <t>L'avviso anticipa il rinnovo della rete di ricerca IMPOWR, parte dell'iniziativa NIH HEAL, finalizzata allo sviluppo e alla validazione di modelli integrati per la gestione del dolore cronico e del disturbo da uso di oppioidi. Il network comprenderà molteplici progetti di ricerca coordinati da un centro centrale, con l'obiettivo di condurre studi clinici per testare approcci assistenziali innovativi in grado di migliorare significativamente l'erogazione delle cure nei sistemi sanitari. Possono partecipare istituzioni universitarie, ospedaliere, enti di ricerca no-profit o profit e organizzazioni estere non statunitensi.</t>
+          <t>Questa opportunità di finanziamento (UG3/UH3) promossa dal National Institute of Neurological Disorders and Stroke (NINDS) sostiene trial clinici proposti da ricercatori per affrontare quesiti coerenti con la missione dell'istituto. Il bando finanzia sperimentazioni cliniche precoci, intermedie o confermative di fase 3 e studi di efficacia comparativa su molecole, farmaci biologici, dispositivi medici o interventi chirurgici, comportamentali, dietetici e terapie riabilitative, per tutte le età. Possono partecipare enti accademici, ospedalieri e organizzazioni di ricerca, incluse entità straniere non statunitensi come capofila. Non sono tuttavia consentiti subappalti o sub-accordi finanziari internazionali verso altre entità estere nell'ambito dello stesso progetto.</t>
         </is>
       </c>
       <c r="AE15" s="4" t="n">
         <v>46316</v>
       </c>
       <c r="AF15" s="4" t="n">
-        <v>46313</v>
+        <v>46312</v>
       </c>
       <c r="AG15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>GG-PAR-27-065</t>
+          <t>GG-PD-26-369Y</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -2691,29 +2685,27 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Ricerca clinica</t>
+          <t>Tecnologia / innovazione</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Trial clinici esplorativi e di efficacia del NINDS (UG3/UH3 - Clinical Trial obbligatorio)</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="n">
-        <v>47186</v>
-      </c>
+          <t>Ingegneria dei sistemi biologici e biomedici (EBBS)</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="n"/>
       <c r="G16" s="5">
         <f>IF(F16="","",F16-TODAY())</f>
         <v/>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Aperto</t>
+          <t>Scadenza da verificare</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>National Institutes of Health</t>
+          <t>U.S. National Science Foundation</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2723,27 +2715,27 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>National Institutes of Health – PAR-27-065</t>
+          <t>U.S. National Science Foundation – PD-26-369Y</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>NINDS Efficacy and Exploratory Clinical Trials (UG3/UH3 - Clinical Trial Required)</t>
+          <t>Engineering Biological and Biomedical Systems (EBBS)</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Ictus, Altre malattie e riabilitazione</t>
+          <t>Tecnologie riabilitazione, Altre malattie e riabilitazione</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>stroke, rehabilitat, neurological disorder</t>
+          <t>rehabilitation engineering, rehabilitat, persons with disabilities</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>Finanzia trial clinici neurologici e ammette esplicitamente terapie e interventi di riabilitazione lungo tutto l'arco della vita.</t>
+          <t>Supporta esplicitamente la ricerca fondamentale in ingegneria della riabilitazione e tecnologie per il ripristino delle funzioni e la disabilità.</t>
         </is>
       </c>
       <c r="P16" s="6" t="n"/>
@@ -2765,7 +2757,7 @@
         </is>
       </c>
       <c r="V16" s="4" t="n">
-        <v>46265</v>
+        <v>46136</v>
       </c>
       <c r="W16" s="2" t="n"/>
       <c r="X16" s="2" t="inlineStr">
@@ -2775,14 +2767,10 @@
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t>Native American tribal governments (Federally recognized); State governments; Public and State controlled institutions of higher education; Small businesses; Special district governments; Public housing authorities/Indian housing authorities; City or township governments; Independent school districts; Nonprofits that do not have a 501(c)(3) status with the IRS, other than institutions of higher ed</t>
-        </is>
-      </c>
-      <c r="Z16" s="3" t="inlineStr">
-        <is>
-          <t>Non sono ammessi sub-accordi o subappalti a entità estere; le organizzazioni estere possono candidarsi direttamente come capofila</t>
-        </is>
-      </c>
+          <t>Unrestricted (i.e., open to any type of entity above), subject to any clarification in text field entitled "Additional Information on Eligibility"</t>
+        </is>
+      </c>
+      <c r="Z16" s="3" t="n"/>
       <c r="AA16" s="2" t="inlineStr">
         <is>
           <t>Enti esteri: da verificare nel bando</t>
@@ -2795,12 +2783,12 @@
       </c>
       <c r="AC16" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/360404</t>
+          <t>https://www.grants.gov/search-results-detail/362062</t>
         </is>
       </c>
       <c r="AD16" s="3" t="inlineStr">
         <is>
-          <t>Questa opportunità di finanziamento (UG3/UH3) promossa dal National Institute of Neurological Disorders and Stroke (NINDS) sostiene trial clinici proposti da ricercatori per affrontare quesiti coerenti con la missione dell'istituto. Il bando finanzia sperimentazioni cliniche precoci, intermedie o confermative di fase 3 e studi di efficacia comparativa su molecole, farmaci biologici, dispositivi medici o interventi chirurgici, comportamentali, dietetici e terapie riabilitative, per tutte le età. Possono partecipare enti accademici, ospedalieri e organizzazioni di ricerca, incluse entità straniere non statunitensi come capofila. Non sono tuttavia consentiti subappalti o sub-accordi finanziari internazionali verso altre entità estere nell'ambito dello stesso progetto.</t>
+          <t>Il programma Engineering Biological and Biomedical Systems (EBBS) della National Science Foundation statunitense sostiene progetti di ricerca ingegneristica fondamentale volti a comprendere e controllare i sistemi biologici e fisiologici per migliorare la salute umana. L'iniziativa finanzia in particolare lo sviluppo di piattaforme di biosensing, metodologie di imaging ottico, sistemi per imitare o ripristinare le funzioni di tessuti e organi, nonché progetti innovativi di ingegneria della riabilitazione guidati dalle esigenze delle persone con disabilità. Non sono supportati trial clinici né progetti dedicati unicamente alla progettazione di farmaci o alla commercializzazione immediata. Il bando incoraggia approcci interdisciplinari e collaborazioni, ma non specifica restrizioni geografiche per la candidatura diretta.</t>
         </is>
       </c>
       <c r="AE16" s="4" t="n">
@@ -2814,7 +2802,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>GG-PD-26-369Y</t>
+          <t>GG-HT942526PRPEIRA</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -2824,32 +2812,34 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Tecnologia / innovazione</t>
+          <t>Formazione / fellowship</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Ingegneria dei sistemi biologici e biomedici (EBBS)</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="n"/>
+          <t>Programma di ricerca sul Parkinson del Dipartimento della Difesa: bando per ricercatori a inizio carriera</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>46332</v>
+      </c>
       <c r="G17" s="5">
         <f>IF(F17="","",F17-TODAY())</f>
         <v/>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Scadenza da verificare</t>
+          <t>In scadenza (≤30 gg)</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>U.S. National Science Foundation</t>
+          <t>Defense Health Agency Contracting Activity - DHACA</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2859,40 +2849,44 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>U.S. National Science Foundation – PD-26-369Y</t>
+          <t>Defense Health Agency Contracting Activity - DHACA – HT942526PRPEIRA</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>Engineering Biological and Biomedical Systems (EBBS)</t>
+          <t>DoW Parkinson’s, Early Investigator Research Award</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Tecnologie riabilitazione, Altre malattie e riabilitazione</t>
+          <t>Parkinson</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>rehabilitation engineering, rehabilitat, persons with disabilities</t>
+          <t>parkinson</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>Supporta esplicitamente la ricerca fondamentale in ingegneria della riabilitazione e tecnologie per il ripristino delle funzioni e la disabilità.</t>
-        </is>
-      </c>
-      <c r="P17" s="6" t="n"/>
+          <t>Finanzia la ricerca sul morbo di Parkinson per ricercatori a inizio carriera, ma esclude i trial clinici e non è mirato alla riabilitazione.</t>
+        </is>
+      </c>
+      <c r="P17" s="6" t="n">
+        <v>4200000</v>
+      </c>
       <c r="Q17" s="6" t="n"/>
       <c r="R17" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="S17" s="2" t="n"/>
+      <c r="S17" s="2" t="n">
+        <v>7</v>
+      </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t>Non stimabile – dati insufficienti</t>
+          <t>Media – 7 progetti finanziabili (stima: tasso storico non disponibile)</t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
@@ -2901,12 +2895,12 @@
         </is>
       </c>
       <c r="V17" s="4" t="n">
-        <v>46136</v>
+        <v>46191</v>
       </c>
       <c r="W17" s="2" t="n"/>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>Ricerca</t>
+          <t>Dottorato / formazione / mobilità</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
@@ -2914,7 +2908,11 @@
           <t>Unrestricted (i.e., open to any type of entity above), subject to any clarification in text field entitled "Additional Information on Eligibility"</t>
         </is>
       </c>
-      <c r="Z17" s="3" t="n"/>
+      <c r="Z17" s="3" t="inlineStr">
+        <is>
+          <t>Per il Livello 1 è obbligatoria la designazione di almeno un mentore con esperienza documentata nella ricerca su Parkinson.</t>
+        </is>
+      </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
           <t>Enti esteri: da verificare nel bando</t>
@@ -2927,12 +2925,12 @@
       </c>
       <c r="AC17" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/362062</t>
+          <t>https://www.grants.gov/search-results-detail/362866</t>
         </is>
       </c>
       <c r="AD17" s="3" t="inlineStr">
         <is>
-          <t>Il programma Engineering Biological and Biomedical Systems (EBBS) della National Science Foundation statunitense sostiene progetti di ricerca ingegneristica fondamentale volti a comprendere e controllare i sistemi biologici e fisiologici per migliorare la salute umana. L'iniziativa finanzia in particolare lo sviluppo di piattaforme di biosensing, metodologie di imaging ottico, sistemi per imitare o ripristinare le funzioni di tessuti e organi, nonché progetti innovativi di ingegneria della riabilitazione guidati dalle esigenze delle persone con disabilità. Non sono supportati trial clinici né progetti dedicati unicamente alla progettazione di farmaci o alla commercializzazione immediata. Il bando incoraggia approcci interdisciplinari e collaborazioni, ma non specifica restrizioni geografiche per la candidatura diretta.</t>
+          <t>Il bando Early Investigator Research Award, promosso nell'ambito del Parkinson’s Research Program dell'agenzia di difesa statunitense, sostiene la formazione e l'avvio di carriera di ricercatori promettenti dedicati alla ricerca sulla malattia di Parkinson. L'iniziativa prevede due livelli: il primo è destinato a borsisti o assegnisti (fellows) e richiede l'affiancamento obbligatorio di un mentore esperto per garantire un solido percorso verso l'indipendenza scientifica; il secondo è rivolto a ricercatori indipendenti junior e richiede dati preliminari comprovati. Le ricerche proposte devono rientrare nelle aree prioritarie del programma e non possono includere sperimentazioni cliniche. Possono candidarsi ricercatori a inizio carriera sostenuti dalle proprie organizzazioni di ricerca o accademiche.</t>
         </is>
       </c>
       <c r="AE17" s="4" t="n">
@@ -2946,7 +2944,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>WEB-03a781657bb4</t>
+          <t>GG-HT942526PRPIIRA</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -2959,14 +2957,18 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="D18" s="2" t="n"/>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Ricerca clinica</t>
+        </is>
+      </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Fondamenti di appello</t>
+          <t>Programma di ricerca sul Parkinson del Dipartimento della Difesa: bando di ricerca promosso dal ricercatore</t>
         </is>
       </c>
       <c r="F18" s="4" t="n">
-        <v>46322</v>
+        <v>46332</v>
       </c>
       <c r="G18" s="5">
         <f>IF(F18="","",F18-TODAY())</f>
@@ -2979,56 +2981,54 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Brain Canada</t>
+          <t>Defense Health Agency Contracting Activity - DHACA</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>Brain Canada</t>
+          <t>Grants.gov</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>Funding Opportunities</t>
+          <t>Defense Health Agency Contracting Activity - DHACA – HT942526PRPIIRA</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>Funding Opportunities</t>
+          <t>DoW Parkinson’s, Investigator-Initiated Research Award</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Parkinson, Invecchiamento</t>
+          <t>Parkinson</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>parkinson, dementi, alzheimer, cognitive decline, geriatr, older persons, aging, amyotrophic lateral sclerosis, neurodegenerat, spinal cord injur, neurological condition, disabilit</t>
+          <t>parkinson</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>Il bando non specifica esplicitamente riabilitazione, ictus, Parkinson, invecchiamento/demenze o tecnologie per la riabilitazione</t>
+          <t>Bando dedicato alla malattia di Parkinson che ammette trial clinici, pur senza essere focalizzato specificamente sulla riabilitazione.</t>
         </is>
       </c>
       <c r="P18" s="6" t="n">
-        <v>100000</v>
-      </c>
-      <c r="Q18" s="6" t="n">
-        <v>100000</v>
-      </c>
+        <v>10000000</v>
+      </c>
+      <c r="Q18" s="6" t="n"/>
       <c r="R18" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="S18" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t>Bassa – 4 progetti finanziabili (stima: tasso storico non disponibile)</t>
+          <t>Media – 5 progetti finanziabili (stima: tasso storico non disponibile)</t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
@@ -3036,12 +3036,10 @@
           <t>Interamente finanziato</t>
         </is>
       </c>
-      <c r="V18" s="4" t="n"/>
-      <c r="W18" s="2" t="inlineStr">
-        <is>
-          <t>24 mesi</t>
-        </is>
-      </c>
+      <c r="V18" s="4" t="n">
+        <v>46191</v>
+      </c>
+      <c r="W18" s="2" t="n"/>
       <c r="X18" s="2" t="inlineStr">
         <is>
           <t>Ricerca</t>
@@ -3049,17 +3047,17 @@
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t>Ricercatori in età precoce, studenti, post-doc e ricercatori clinici</t>
+          <t>Unrestricted (i.e., open to any type of entity above), subject to any clarification in text field entitled "Additional Information on Eligibility"</t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t>Ricercatori in età precoce e studenti, post-doc e ricercatori clinici</t>
+          <t>Possibilità di consorzio con un Initiating PI e fino a due Partnering PI multidisciplinari.</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Enti esteri: da verificare nel bando</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
@@ -3069,16 +3067,16 @@
       </c>
       <c r="AC18" s="7" t="inlineStr">
         <is>
-          <t>https://braincanada.ca/research/funding-opportunities</t>
+          <t>https://www.grants.gov/search-results-detail/362868</t>
         </is>
       </c>
       <c r="AD18" s="3" t="inlineStr">
         <is>
-          <t>Il bando offre finanziamenti per progetti di ricerca in varie aree, tra cui neuroscienze, neurologia, neurologia del neurodesenvolvimento e salute mentale degli anziani. Il finanziamento è per un periodo di due anni e varia da 100.000 a 500.000 EUR a progetto. Il bando è aperto a ricercatori in età precoce e a studenti, post-doc e ricercatori clinici. Il finanziamento include un premio di ingresso, un Passport di formazione e due esperienze di formazione e networking.</t>
+          <t>L'Investigator-Initiated Research Award, gestito dal programma di ricerca sul Parkinson (PRP), mira a finanziare progetti di ricerca rigorosi, multidisciplinari e ad alto impatto con un rilevante potenziale innovativo nella lotta al morbo di Parkinson. Le proposte devono concentrarsi su una delle aree prioritarie stabilite per l'anno fiscale 2026 e devono essere obbligatoriamente supportate da solidi dati preliminari. A differenza di altre linee di finanziamento, questo bando consente esplicitamente la conduzione di studi clinici. È inoltre prevista un'opzione di partenariato che permette la collaborazione formale tra un ricercatore principale capofila e fino a due Principal Investigator partner. Possono candidarsi istituti universitari, centri di ricerca e organizzazioni cliniche qualificate.</t>
         </is>
       </c>
       <c r="AE18" s="4" t="n">
-        <v>46313</v>
+        <v>46316</v>
       </c>
       <c r="AF18" s="4" t="n">
         <v>46312</v>
@@ -3088,7 +3086,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>GG-HT942526PRPEIRA</t>
+          <t>GG-PAR-27-007</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -3103,16 +3101,16 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Formazione / fellowship</t>
+          <t>Ricerca clinica</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Programma di ricerca sul Parkinson del Dipartimento della Difesa: bando per ricercatori a inizio carriera</t>
+          <t>Trial clinici e studi ancillari condotti all'interno delle reti di ricerca clinica finanziate dal NIH (UG3/UH3)</t>
         </is>
       </c>
       <c r="F19" s="4" t="n">
-        <v>46332</v>
+        <v>46336</v>
       </c>
       <c r="G19" s="5">
         <f>IF(F19="","",F19-TODAY())</f>
@@ -3125,7 +3123,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Defense Health Agency Contracting Activity - DHACA</t>
+          <t>National Institutes of Health</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -3135,44 +3133,40 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>Defense Health Agency Contracting Activity - DHACA – HT942526PRPEIRA</t>
+          <t>National Institutes of Health – PAR-27-007</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>DoW Parkinson’s, Early Investigator Research Award</t>
+          <t>Clinical Trials and Ancillary Studies Conducted within NIH-Funded Clinical Trial Research Networks (UG3/UH3 - Clinical Trial Required)</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>Parkinson</t>
+          <t>Ictus, Altre malattie e riabilitazione</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>parkinson</t>
+          <t>stroke, neurological disorder</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>Finanzia la ricerca sul morbo di Parkinson per ricercatori a inizio carriera, ma esclude i trial clinici e non è mirato alla riabilitazione.</t>
-        </is>
-      </c>
-      <c r="P19" s="6" t="n">
-        <v>4200000</v>
-      </c>
+          <t>Finanzia trial clinici in reti neurologiche che possono comprendere patologie di interesse riabilitativo come l'ictus, pur non focalizzandosi sulla riabilitazione.</t>
+        </is>
+      </c>
+      <c r="P19" s="6" t="n"/>
       <c r="Q19" s="6" t="n"/>
       <c r="R19" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="S19" s="2" t="n">
-        <v>7</v>
-      </c>
+      <c r="S19" s="2" t="n"/>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t>Media – 7 progetti finanziabili (stima: tasso storico non disponibile)</t>
+          <t>Non stimabile – dati insufficienti</t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
@@ -3181,24 +3175,24 @@
         </is>
       </c>
       <c r="V19" s="4" t="n">
-        <v>46191</v>
-      </c>
-      <c r="W19" s="2" t="n"/>
+        <v>46097</v>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>84 mesi</t>
+        </is>
+      </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>Dottorato / formazione / mobilità</t>
+          <t>Ricerca</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t>Unrestricted (i.e., open to any type of entity above), subject to any clarification in text field entitled "Additional Information on Eligibility"</t>
-        </is>
-      </c>
-      <c r="Z19" s="3" t="inlineStr">
-        <is>
-          <t>Per il Livello 1 è obbligatoria la designazione di almeno un mentore con esperienza documentata nella ricerca su Parkinson.</t>
-        </is>
-      </c>
+          <t>Public housing authorities/Indian housing authorities; State governments; Special district governments; Private institutions of higher education; Independent school districts; City or township governments; Nonprofits having a 501(c)(3) status with the IRS, other than institutions of higher education; Public and State controlled institutions of higher education; Small businesses; Nonprofits that do</t>
+        </is>
+      </c>
+      <c r="Z19" s="3" t="n"/>
       <c r="AA19" s="2" t="inlineStr">
         <is>
           <t>Enti esteri: da verificare nel bando</t>
@@ -3211,12 +3205,12 @@
       </c>
       <c r="AC19" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/362866</t>
+          <t>https://www.grants.gov/search-results-detail/361522</t>
         </is>
       </c>
       <c r="AD19" s="3" t="inlineStr">
         <is>
-          <t>Il bando Early Investigator Research Award, promosso nell'ambito del Parkinson’s Research Program dell'agenzia di difesa statunitense, sostiene la formazione e l'avvio di carriera di ricercatori promettenti dedicati alla ricerca sulla malattia di Parkinson. L'iniziativa prevede due livelli: il primo è destinato a borsisti o assegnisti (fellows) e richiede l'affiancamento obbligatorio di un mentore esperto per garantire un solido percorso verso l'indipendenza scientifica; il secondo è rivolto a ricercatori indipendenti junior e richiede dati preliminari comprovati. Le ricerche proposte devono rientrare nelle aree prioritarie del programma e non possono includere sperimentazioni cliniche. Possono candidarsi ricercatori a inizio carriera sostenuti dalle proprie organizzazioni di ricerca o accademiche.</t>
+          <t>Il bando, promosso dal NINDS insieme ad altri istituti del NIH tramite lo schema cooperativo a due fasi UG3/UH3, intende sostenere la conduzione di studi clinici multicentrici e studi ancillari all'interno delle reti di ricerca clinica già finanziate e attive del NIH. Il programma prevede una fase iniziale di pianificazione e avvio fino a due anni (UG3), con possibile passaggio a una fase operativa fino a ulteriori cinque anni (UH3) al raggiungimento di specifici traguardi. Possono candidarsi enti di ricerca, università, organizzazioni pubbliche o private ed enti stranieri non statunitensi per testare interventi diagnostici e terapeutici in ambito neurologico.</t>
         </is>
       </c>
       <c r="AE19" s="4" t="n">
@@ -3230,7 +3224,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>GG-HT942526PRPIIRA</t>
+          <t>GG-RFA-TS-27-018</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -3250,11 +3244,11 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Programma di ricerca sul Parkinson del Dipartimento della Difesa: bando di ricerca promosso dal ricercatore</t>
+          <t>Identificazione e valutazione dei potenziali fattori di rischio per la sclerosi laterale amiotrofica (SLA)</t>
         </is>
       </c>
       <c r="F20" s="4" t="n">
-        <v>46332</v>
+        <v>46357</v>
       </c>
       <c r="G20" s="5">
         <f>IF(F20="","",F20-TODAY())</f>
@@ -3262,12 +3256,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>In scadenza (≤30 gg)</t>
+          <t>Aperto</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Defense Health Agency Contracting Activity - DHACA</t>
+          <t>Centers for Disease Control and Prevention - ERA</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -3277,44 +3271,46 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>Defense Health Agency Contracting Activity - DHACA – HT942526PRPIIRA</t>
+          <t>Centers for Disease Control and Prevention - ERA – RFA-TS-27-018</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>DoW Parkinson’s, Investigator-Initiated Research Award</t>
+          <t>Identify and Evaluate Potential Risk Factors for Amyotrophic Lateral Sclerosis (ALS)</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Parkinson</t>
+          <t>Altre malattie e riabilitazione</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>parkinson</t>
+          <t>amyotrophic lateral sclerosis, traumatic brain injur</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>Bando dedicato alla malattia di Parkinson che ammette trial clinici, pur senza essere focalizzato specificamente sulla riabilitazione.</t>
+          <t>Riguarda la sclerosi laterale amiotrofica (SLA) ma è incentrato sullo studio dei fattori di rischio eziologici e non sulla riabilitazione.</t>
         </is>
       </c>
       <c r="P20" s="6" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="Q20" s="6" t="n"/>
+        <v>4500000</v>
+      </c>
+      <c r="Q20" s="6" t="n">
+        <v>500000</v>
+      </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="S20" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t>Media – 5 progetti finanziabili (stima: tasso storico non disponibile)</t>
+          <t>Bassa – 3 progetti finanziabili (stima: tasso storico non disponibile)</t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
@@ -3323,7 +3319,7 @@
         </is>
       </c>
       <c r="V20" s="4" t="n">
-        <v>46191</v>
+        <v>46211</v>
       </c>
       <c r="W20" s="2" t="n"/>
       <c r="X20" s="2" t="inlineStr">
@@ -3333,14 +3329,10 @@
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t>Unrestricted (i.e., open to any type of entity above), subject to any clarification in text field entitled "Additional Information on Eligibility"</t>
-        </is>
-      </c>
-      <c r="Z20" s="3" t="inlineStr">
-        <is>
-          <t>Possibilità di consorzio con un Initiating PI e fino a due Partnering PI multidisciplinari.</t>
-        </is>
-      </c>
+          <t>City or township governments; Public and State controlled institutions of higher education; Native American tribal organizations (other than Federally recognized tribal governments); Nonprofits that do not have a 501(c)(3) status with the IRS, other than institutions of higher education; Public housing authorities/Indian housing authorities; County governments; Private institutions of higher educa</t>
+        </is>
+      </c>
+      <c r="Z20" s="3" t="n"/>
       <c r="AA20" s="2" t="inlineStr">
         <is>
           <t>Enti esteri: da verificare nel bando</t>
@@ -3353,12 +3345,12 @@
       </c>
       <c r="AC20" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/362868</t>
+          <t>https://www.grants.gov/search-results-detail/363115</t>
         </is>
       </c>
       <c r="AD20" s="3" t="inlineStr">
         <is>
-          <t>L'Investigator-Initiated Research Award, gestito dal programma di ricerca sul Parkinson (PRP), mira a finanziare progetti di ricerca rigorosi, multidisciplinari e ad alto impatto con un rilevante potenziale innovativo nella lotta al morbo di Parkinson. Le proposte devono concentrarsi su una delle aree prioritarie stabilite per l'anno fiscale 2026 e devono essere obbligatoriamente supportate da solidi dati preliminari. A differenza di altre linee di finanziamento, questo bando consente esplicitamente la conduzione di studi clinici. È inoltre prevista un'opzione di partenariato che permette la collaborazione formale tra un ricercatore principale capofila e fino a due Principal Investigator partner. Possono candidarsi istituti universitari, centri di ricerca e organizzazioni cliniche qualificate.</t>
+          <t>Il CDC e l'ATSDR finanziano progetti di ricerca dedicati all'identificazione e alla valutazione dei fattori di rischio per la sclerosi laterale amiotrofica (SLA), incoraggiando studi su servizio militare, sport di contatto, traumi cranici, neuroinfiammazione ed esposizioni ad agenti infettivi o ambientali. Il bando prevede quattro opzioni tematiche: ricerca supportata da evidenze consolidate e legami tra fattori di rischio, diagnosi e cura; studi esplorativi e innovativi su nuovi fattori; analisi del rischio in popolazioni specifiche, come i veterani militari; studio di campioni biologici del cluster di Guam per chiarire i meccanismi patologici, biomarcatori e approcci di prevenzione.</t>
         </is>
       </c>
       <c r="AE20" s="4" t="n">
@@ -3372,7 +3364,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>GG-PAR-27-007</t>
+          <t>GG-FOR-FD-25-001</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -3392,24 +3384,22 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Trial clinici e studi ancillari condotti all'interno delle reti di ricerca clinica finanziate dal NIH (UG3/UH3)</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="n">
-        <v>46336</v>
-      </c>
+          <t>Trial clinici per i bisogni insoddisfatti nelle malattie neurodegenerative rare (R01 - Clinical Trial obbligatorio)</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="n"/>
       <c r="G21" s="5">
         <f>IF(F21="","",F21-TODAY())</f>
         <v/>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>In scadenza (≤30 gg)</t>
+          <t>In apertura</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>National Institutes of Health</t>
+          <t>Food and Drug Administration</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -3419,31 +3409,33 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>National Institutes of Health – PAR-27-007</t>
+          <t>Food and Drug Administration – FOR-FD-25-001</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>Clinical Trials and Ancillary Studies Conducted within NIH-Funded Clinical Trial Research Networks (UG3/UH3 - Clinical Trial Required)</t>
+          <t>Clinical Trials Addressing Unmet Needs of Rare Neurodegenerative Diseases (R01) Clinical Trials Required</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Ictus, Altre malattie e riabilitazione</t>
+          <t>Altre malattie e riabilitazione</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>stroke, neurological disorder</t>
+          <t>neurodegenerat</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>Finanzia trial clinici in reti neurologiche che possono comprendere patologie di interesse riabilitativo come l'ictus, pur non focalizzandosi sulla riabilitazione.</t>
+          <t>Riguarda le malattie neurodegenerative rare, ma è finalizzato a trial clinici regolatori per l'approvazione o rietichettatura di farmaci.</t>
         </is>
       </c>
       <c r="P21" s="6" t="n"/>
-      <c r="Q21" s="6" t="n"/>
+      <c r="Q21" s="6" t="n">
+        <v>900000</v>
+      </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3461,13 +3453,9 @@
         </is>
       </c>
       <c r="V21" s="4" t="n">
-        <v>46097</v>
-      </c>
-      <c r="W21" s="2" t="inlineStr">
-        <is>
-          <t>84 mesi</t>
-        </is>
-      </c>
+        <v>45518</v>
+      </c>
+      <c r="W21" s="2" t="n"/>
       <c r="X21" s="2" t="inlineStr">
         <is>
           <t>Ricerca</t>
@@ -3475,7 +3463,7 @@
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">For profit organizations other than small businesses; Others (see text field entitled "Additional Information on Eligibility" for clarification); Public and State controlled institutions of higher education; Special district governments; Native American tribal organizations (other than Federally recognized tribal governments); Public housing authorities/Indian housing authorities; Native American </t>
+          <t>Public and State controlled institutions of higher education; Nonprofits that do not have a 501(c)(3) status with the IRS, other than institutions of higher education; For profit organizations other than small businesses; State governments; Small businesses; Native American tribal governments (Federally recognized); County governments; Special district governments; City or township governments; No</t>
         </is>
       </c>
       <c r="Z21" s="3" t="n"/>
@@ -3491,12 +3479,12 @@
       </c>
       <c r="AC21" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/361522</t>
+          <t>https://www.grants.gov/search-results-detail/356054</t>
         </is>
       </c>
       <c r="AD21" s="3" t="inlineStr">
         <is>
-          <t>Il bando, promosso dal NINDS insieme ad altri istituti del NIH tramite lo schema cooperativo a due fasi UG3/UH3, intende sostenere la conduzione di studi clinici multicentrici e studi ancillari all'interno delle reti di ricerca clinica già finanziate e attive del NIH. Il programma prevede una fase iniziale di pianificazione e avvio fino a due anni (UG3), con possibile passaggio a una fase operativa fino a ulteriori cinque anni (UH3) al raggiungimento di specifici traguardi. Possono candidarsi enti di ricerca, università, organizzazioni pubbliche o private ed enti stranieri non statunitensi per testare interventi diagnostici e terapeutici in ambito neurologico.</t>
+          <t>Questo bando promosso dalla Food and Drug Administration (FDA) tramite il meccanismo R01 è destinato a finanziare trial clinici dedicati a rispondere ai bisogni insoddisfatti nell'ambito delle malattie neurodegenerative rare, sia pediatriche che dell'età adulta. I progetti devono valutare l'efficacia e la sicurezza di prodotti terapeutici a supporto di nuove indicazioni cliniche o di modifiche delle indicazioni di etichettatura (labeling). L'obiettivo primario è incrementare il numero di trattamenti approvati dalle autorità regolatorie e favorire un impatto positivo e duraturo sullo sviluppo clinico di terapie per patologie rare. La presentazione di un trial clinico è requisito obbligatorio per accedere al finanziamento.</t>
         </is>
       </c>
       <c r="AE21" s="4" t="n">
@@ -3510,7 +3498,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>GG-RFA-TS-27-018</t>
+          <t>GG-FOR-FD-25-006</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -3530,24 +3518,22 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Identificazione e valutazione dei potenziali fattori di rischio per la sclerosi laterale amiotrofica (SLA)</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="n">
-        <v>46357</v>
-      </c>
+          <t>Studi rivolti alle malattie neurodegenerative rare, inclusa la SLA</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="n"/>
       <c r="G22" s="5">
         <f>IF(F22="","",F22-TODAY())</f>
         <v/>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Aperto</t>
+          <t>In apertura</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Centers for Disease Control and Prevention - ERA</t>
+          <t>Food and Drug Administration</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -3557,12 +3543,12 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>Centers for Disease Control and Prevention - ERA – RFA-TS-27-018</t>
+          <t>Food and Drug Administration – FOR-FD-25-006</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>Identify and Evaluate Potential Risk Factors for Amyotrophic Lateral Sclerosis (ALS)</t>
+          <t>Studies Addressing Rare Neurodegenerative Diseases including ALS</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -3572,31 +3558,27 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>amyotrophic lateral sclerosis, traumatic brain injur</t>
+          <t>neurodegenerat</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>Riguarda la sclerosi laterale amiotrofica (SLA) ma è incentrato sullo studio dei fattori di rischio eziologici e non sulla riabilitazione.</t>
-        </is>
-      </c>
-      <c r="P22" s="6" t="n">
-        <v>4500000</v>
-      </c>
-      <c r="Q22" s="6" t="n">
-        <v>500000</v>
-      </c>
+          <t>Riguarda la SLA e le malattie neurodegenerative rare, ma è focalizzato sullo sviluppo di prodotti medici anziché su interventi riabilitativi specifici.</t>
+        </is>
+      </c>
+      <c r="P22" s="6" t="n"/>
+      <c r="Q22" s="6" t="n"/>
       <c r="R22" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="S22" s="2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t>Bassa – 3 progetti finanziabili (stima: tasso storico non disponibile)</t>
+          <t>Media – 10 progetti finanziabili (stima: tasso storico non disponibile)</t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
@@ -3605,7 +3587,7 @@
         </is>
       </c>
       <c r="V22" s="4" t="n">
-        <v>46211</v>
+        <v>45518</v>
       </c>
       <c r="W22" s="2" t="n"/>
       <c r="X22" s="2" t="inlineStr">
@@ -3615,7 +3597,7 @@
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t>City or township governments; Public and State controlled institutions of higher education; Private institutions of higher education; Nonprofits having a 501(c)(3) status with the IRS, other than institutions of higher education; Native American tribal governments (Federally recognized); Unrestricted (i.e., open to any type of entity above), subject to any clarification in text field entitled "Add</t>
+          <t xml:space="preserve">Public and State controlled institutions of higher education; Unrestricted (i.e., open to any type of entity above), subject to any clarification in text field entitled "Additional Information on Eligibility"; County governments; Public housing authorities/Indian housing authorities; Native American tribal organizations (other than Federally recognized tribal governments); Private institutions of </t>
         </is>
       </c>
       <c r="Z22" s="3" t="n"/>
@@ -3631,12 +3613,12 @@
       </c>
       <c r="AC22" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/363115</t>
+          <t>https://www.grants.gov/search-results-detail/356046</t>
         </is>
       </c>
       <c r="AD22" s="3" t="inlineStr">
         <is>
-          <t>Il CDC e l'ATSDR finanziano progetti di ricerca dedicati all'identificazione e alla valutazione dei fattori di rischio per la sclerosi laterale amiotrofica (SLA), incoraggiando studi su servizio militare, sport di contatto, traumi cranici, neuroinfiammazione ed esposizioni ad agenti infettivi o ambientali. Il bando prevede quattro opzioni tematiche: ricerca supportata da evidenze consolidate e legami tra fattori di rischio, diagnosi e cura; studi esplorativi e innovativi su nuovi fattori; analisi del rischio in popolazioni specifiche, come i veterani militari; studio di campioni biologici del cluster di Guam per chiarire i meccanismi patologici, biomarcatori e approcci di prevenzione.</t>
+          <t>Il bando, promosso dalla Food and Drug Administration (FDA), mira a sostenere studi scientifici per far progredire lo sviluppo di prodotti medici destinati a prevenire, diagnosticare, mitigare, trattare o curare la sclerosi laterale amiotrofica (SLA) e altre malattie neurodegenerative rare, sia negli adulti che nei bambini. Attraverso questo programma, l’ente intende colmare lacune conoscitive critiche, generare un impatto significativo sulla gestione delle patologie neurodegenerative rare e fornire dati essenziali per orientare lo sviluppo regolatorio e industriale di interventi innovativi attuali e futuri. Il bando finanzia attività di ricerca volte all'avanzamento di candidati terapeutici e strumenti diagnostici. I dettagli relativi a requisiti specifici di partecipazione e contributi economici sono definiti nella documentazione ufficiale.</t>
         </is>
       </c>
       <c r="AE22" s="4" t="n">
@@ -3650,7 +3632,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>WEB-14a8635c6be7</t>
+          <t>WEB-be57b3f2011d</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -3663,72 +3645,78 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="D23" s="2" t="n"/>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Formazione / fellowship</t>
+        </is>
+      </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Promozione delle Borse di Studio per Dottorato</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="n">
-        <v>46407</v>
-      </c>
+          <t>Bandi per la formazione clinica della Parkinson's Foundation</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="n"/>
       <c r="G23" s="5">
         <f>IF(F23="","",F23-TODAY())</f>
         <v/>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Aperto</t>
+          <t>Scadenza da verificare</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Foundation for Physical Therapy Research</t>
+          <t>Parkinson's Foundation</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>Foundation for Physical Therapy Research</t>
+          <t>Parkinson's Foundation</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>Promotion of Doctoral Studies Scholarships</t>
+          <t>Clinical Training Awards</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>Promotion of Doctoral Studies Scholarships</t>
+          <t>Clinical Training Awards</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>Invecchiamento, Altre malattie e riabilitazione</t>
+          <t>Parkinson, Invecchiamento</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>geriatr, physical therap</t>
+          <t>parkinson, movement disorder, aging</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>Il bando si concentra su borse di studio per dottorato, ma non specifica temi sanitari specifici.</t>
+          <t>Finanzia la formazione clinica avanzata e la ricerca nella malattia di Parkinson e disturbi del movimento, ma non è focalizzato specificamente sulla riabilitazione.</t>
         </is>
       </c>
       <c r="P23" s="6" t="n">
-        <v>7500</v>
-      </c>
-      <c r="Q23" s="6" t="n"/>
+        <v>50000</v>
+      </c>
+      <c r="Q23" s="6" t="n">
+        <v>103800</v>
+      </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="S23" s="2" t="n"/>
+      <c r="S23" s="2" t="n">
+        <v>4</v>
+      </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t>Non stimabile – dati insufficienti</t>
+          <t>Bassa – 4 progetti finanziabili (stima: tasso storico non disponibile)</t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
@@ -3737,7 +3725,11 @@
         </is>
       </c>
       <c r="V23" s="4" t="n"/>
-      <c r="W23" s="2" t="n"/>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>24 mesi</t>
+        </is>
+      </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
           <t>Dottorato / formazione / mobilità</t>
@@ -3745,13 +3737,13 @@
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t>Fisioterapisti e fisioterapeuti assistenti APTA membri</t>
+          <t>Istituzioni accademiche/ospedaliere, giovani ricercatori e clinici entro 5 anni dal titolo, docenti di scienze infermieristiche</t>
         </is>
       </c>
       <c r="Z23" s="3" t="n"/>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Mondiale</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
@@ -3761,16 +3753,16 @@
       </c>
       <c r="AC23" s="7" t="inlineStr">
         <is>
-          <t>https://foundation4pt.org/foundation-funding-opportunities/scholarships/</t>
+          <t>https://www.parkinson.org/resources-support/professionals/clinical-training-awards</t>
         </is>
       </c>
       <c r="AD23" s="3" t="inlineStr">
         <is>
-          <t>Il bando offre borse di studio per dottorato per fisioterapisti e fisioterapeuti assistenti APTA membri. Sono offerte due fasi di borse: una per il periodo precedente la candidatura e una per il periodo di candidatura. Le borse coprono i costi di ricerca accademica. I beneficiari devono rinnovare la domanda ogni anno. Il bando è aperto fino al 20/01/2027.</t>
+          <t>La Parkinson's Foundation offre diversi programmi di finanziamento alla formazione per migliorare l'assistenza a persone affette da malattia di Parkinson e disturbi del movimento. Le opportunità includono borse biennali per istituzioni volte alla formazione specialistica di nuovi neurologi clinici (fino a 103.800 dollari/anno), il Mentored Clinical Research Award da 50.000 dollari in collaborazione con il Parkinson Study Group per giovani ricercatori entro cinque anni dal termine della specializzazione, e il Nurse Faculty Award (fino a 10.000 dollari) per docenti infermieri. I contributi coprono stipendi, costi diretti di ricerca e attività di sviluppo accademico e clinico.</t>
         </is>
       </c>
       <c r="AE23" s="4" t="n">
-        <v>46313</v>
+        <v>46316</v>
       </c>
       <c r="AF23" s="4" t="n">
         <v>46312</v>
@@ -3780,17 +3772,17 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>GG-FOR-FD-25-001</t>
+          <t>GG-PAR-25-052</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Da verificare</t>
+          <t>No</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -3800,22 +3792,24 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Trial clinici per i bisogni insoddisfatti nelle malattie neurodegenerative rare (R01 - Clinical Trial obbligatorio)</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="n"/>
+          <t>Studi clinici e studi sui biomarcatori NIH StrokeNet per il trattamento, il recupero e la prevenzione dell'ictus (UG3/UH3)</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>46345</v>
+      </c>
       <c r="G24" s="5">
         <f>IF(F24="","",F24-TODAY())</f>
         <v/>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>In apertura</t>
+          <t>In scadenza (≤30 gg)</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Food and Drug Administration</t>
+          <t>National Institutes of Health</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3825,33 +3819,31 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>Food and Drug Administration – FOR-FD-25-001</t>
+          <t>National Institutes of Health – PAR-25-052</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>Clinical Trials Addressing Unmet Needs of Rare Neurodegenerative Diseases (R01) Clinical Trials Required</t>
+          <t>NIH StrokeNet Clinical Trials and Biomarker Studies for Stroke Treatment, Recovery, and Prevention (UG3/UH3 Clinical Trial Optional)</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>Altre malattie e riabilitazione</t>
+          <t>Ictus</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>neurodegenerat</t>
+          <t>stroke</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>Riguarda le malattie neurodegenerative rare, ma è finalizzato a trial clinici regolatori per l'approvazione o rietichettatura di farmaci.</t>
+          <t>Il bando finanzia trial clinici e studi di biomarcatori dedicati al trattamento, al recupero funzionale e alla prevenzione dell'ictus.</t>
         </is>
       </c>
       <c r="P24" s="6" t="n"/>
-      <c r="Q24" s="6" t="n">
-        <v>900000</v>
-      </c>
+      <c r="Q24" s="6" t="n"/>
       <c r="R24" s="2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3869,7 +3861,7 @@
         </is>
       </c>
       <c r="V24" s="4" t="n">
-        <v>45518</v>
+        <v>45616</v>
       </c>
       <c r="W24" s="2" t="n"/>
       <c r="X24" s="2" t="inlineStr">
@@ -3879,13 +3871,17 @@
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t>State governments; Native American tribal governments (Federally recognized); County governments; Native American tribal organizations (other than Federally recognized tribal governments); Nonprofits having a 501(c)(3) status with the IRS, other than institutions of higher education; Small businesses; Independent school districts; For profit organizations other than small businesses; Public and St</t>
-        </is>
-      </c>
-      <c r="Z24" s="3" t="n"/>
+          <t>State governments; City or township governments; County governments; Native American tribal organizations (other than Federally recognized tribal governments); Public housing authorities/Indian housing authorities; Nonprofits having a 501(c)(3) status with the IRS, other than institutions of higher education; Nonprofits that do not have a 501(c)(3) status with the IRS, other than institutions of h</t>
+        </is>
+      </c>
+      <c r="Z24" s="3" t="inlineStr">
+        <is>
+          <t>Collaborazione obbligatoria all'interno della rete NIH StrokeNet con il National Coordinating Center e i siti clinici affiliati.</t>
+        </is>
+      </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>Enti esteri: da verificare nel bando</t>
+          <t>Enti esteri non ammessi (call NIH completa)</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
@@ -3895,61 +3891,63 @@
       </c>
       <c r="AC24" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/356054</t>
+          <t>https://www.grants.gov/search-results-detail/357256</t>
         </is>
       </c>
       <c r="AD24" s="3" t="inlineStr">
         <is>
-          <t>Questo bando promosso dalla Food and Drug Administration (FDA) tramite il meccanismo R01 è destinato a finanziare trial clinici dedicati a rispondere ai bisogni insoddisfatti nell'ambito delle malattie neurodegenerative rare, sia pediatriche che dell'età adulta. I progetti devono valutare l'efficacia e la sicurezza di prodotti terapeutici a supporto di nuove indicazioni cliniche o di modifiche delle indicazioni di etichettatura (labeling). L'obiettivo primario è incrementare il numero di trattamenti approvati dalle autorità regolatorie e favorire un impatto positivo e duraturo sullo sviluppo clinico di terapie per patologie rare. La presentazione di un trial clinico è requisito obbligatorio per accedere al finanziamento.</t>
+          <t>Il bando promosso dal National Institutes of Health (NIH/NINDS) sostiene la realizzazione di studi clinici multicentrici esplorativi e di conferma focalizzati su interventi terapeutici promettenti, oltre a studi di validazione di biomarcatori o misure di esito funzionale propedeutici a trial clinici nell'ambito della prevenzione, del trattamento acuto e del recupero post-ictus. I progetti selezionati saranno integrati e condotti all'interno dell'infrastruttura della rete NIH StrokeNet, collaborando con i centri nazionali di coordinamento e gestione dei dati per il reclutamento e l'implementazione del protocollo. Possono candidarsi enti statunitensi come università, istituti di ricerca, ospedali e agenzie governative ammissibili, mentre gli enti esteri non residenti negli Stati Uniti sono esplicitamente esclusi come capofila.</t>
         </is>
       </c>
       <c r="AE24" s="4" t="n">
         <v>46316</v>
       </c>
       <c r="AF24" s="4" t="n">
-        <v>46312</v>
+        <v>46316</v>
       </c>
       <c r="AG24" s="2" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>GG-FOR-FD-25-006</t>
+          <t>GG-HHS-2027-ACL-NIDILRR-ARCP-0300</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Da verificare</t>
+          <t>No</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Ricerca clinica</t>
+          <t>Formazione / fellowship</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Studi rivolti alle malattie neurodegenerative rare, inclusa la SLA</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="n"/>
+          <t>Programma di formazione avanzata nella ricerca riabilitativa (ARRT) - Vita nella comunità e partecipazione</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>46363</v>
+      </c>
       <c r="G25" s="5">
         <f>IF(F25="","",F25-TODAY())</f>
         <v/>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>In apertura</t>
+          <t>Aperto</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Food and Drug Administration</t>
+          <t>Administration for Community Living</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3959,12 +3957,12 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>Food and Drug Administration – FOR-FD-25-006</t>
+          <t>Administration for Community Living – HHS-2027-ACL-NIDILRR-ARCP-0300</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>Studies Addressing Rare Neurodegenerative Diseases including ALS</t>
+          <t>Advanced Rehabilitation Research Training (ARRT) Program - Community Living and Participation</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -3974,27 +3972,31 @@
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>neurodegenerat</t>
+          <t>rehabilitat</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>Riguarda la SLA e le malattie neurodegenerative rare, ma è focalizzato sullo sviluppo di prodotti medici anziché su interventi riabilitativi specifici.</t>
-        </is>
-      </c>
-      <c r="P25" s="6" t="n"/>
-      <c r="Q25" s="6" t="n"/>
+          <t>Finanzia programmi di formazione avanzata per ricercatori nell'ambito della riabilitazione e della disabilità.</t>
+        </is>
+      </c>
+      <c r="P25" s="6" t="n">
+        <v>250000</v>
+      </c>
+      <c r="Q25" s="6" t="n">
+        <v>250000</v>
+      </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="S25" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t>Media – 10 progetti finanziabili (stima: tasso storico non disponibile)</t>
+          <t>Bassa – 1 progetti finanziabili (stima: tasso storico non disponibile)</t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
@@ -4003,9 +4005,13 @@
         </is>
       </c>
       <c r="V25" s="4" t="n">
-        <v>45518</v>
-      </c>
-      <c r="W25" s="2" t="n"/>
+        <v>46290</v>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>36 mesi</t>
+        </is>
+      </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
           <t>Ricerca</t>
@@ -4013,13 +4019,13 @@
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t>Independent school districts; Nonprofits that do not have a 501(c)(3) status with the IRS, other than institutions of higher education; County governments; For profit organizations other than small businesses; Special district governments; Unrestricted (i.e., open to any type of entity above), subject to any clarification in text field entitled "Additional Information on Eligibility"; State govern</t>
+          <t>Private institutions of higher education; Public and State controlled institutions of higher education</t>
         </is>
       </c>
       <c r="Z25" s="3" t="n"/>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>Enti esteri: da verificare nel bando</t>
+          <t>Solo enti statunitensi</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
@@ -4029,36 +4035,36 @@
       </c>
       <c r="AC25" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/356046</t>
+          <t>https://www.grants.gov/search-results-detail/363963</t>
         </is>
       </c>
       <c r="AD25" s="3" t="inlineStr">
         <is>
-          <t>Il bando, promosso dalla Food and Drug Administration (FDA), mira a sostenere studi scientifici per far progredire lo sviluppo di prodotti medici destinati a prevenire, diagnosticare, mitigare, trattare o curare la sclerosi laterale amiotrofica (SLA) e altre malattie neurodegenerative rare, sia negli adulti che nei bambini. Attraverso questo programma, l’ente intende colmare lacune conoscitive critiche, generare un impatto significativo sulla gestione delle patologie neurodegenerative rare e fornire dati essenziali per orientare lo sviluppo regolatorio e industriale di interventi innovativi attuali e futuri. Il bando finanzia attività di ricerca volte all'avanzamento di candidati terapeutici e strumenti diagnostici. I dettagli relativi a requisiti specifici di partecipazione e contributi economici sono definiti nella documentazione ufficiale.</t>
+          <t>Il programma Advanced Rehabilitation Research Training (ARRT), gestito dal NIDILRR presso l'Administration for Community Living, si propone di fornire formazione avanzata ed esperienza scientifica a ricercatori post-dottorato nel settore della riabilitazione, compresi ricercatori con disabilità. L'obiettivo del bando è rafforzare la capacità di condurre ricerche multidisciplinari di elevata qualità focalizzate sul miglioramento della vita autonoma nella comunità e sulla partecipazione sociale delle persone con disabilità. Il finanziamento sostiene un singolo progetto triennale articolato in tre periodi di budget annuali. La candidatura è aperta esclusivamente a istituti di istruzione superiore pubblici, statali o privati con sede negli Stati Uniti, mentre gli enti stranieri non sono ammessi a partecipare né a ricevere fondi.</t>
         </is>
       </c>
       <c r="AE25" s="4" t="n">
         <v>46316</v>
       </c>
       <c r="AF25" s="4" t="n">
-        <v>46312</v>
+        <v>46316</v>
       </c>
       <c r="AG25" s="2" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>WEB-be57b3f2011d</t>
+          <t>GG-HHS-2027-ACL-NIDILRR-AREM-0301</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Da verificare</t>
+          <t>No</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -4068,59 +4074,61 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Bandi per la formazione clinica della Parkinson's Foundation</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="n"/>
+          <t>Programma di formazione avanzata nella ricerca riabilitativa (ARRT) - Occupazione</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>46363</v>
+      </c>
       <c r="G26" s="5">
         <f>IF(F26="","",F26-TODAY())</f>
         <v/>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Scadenza da verificare</t>
+          <t>Aperto</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Parkinson's Foundation</t>
+          <t>Administration for Community Living</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>Parkinson's Foundation</t>
+          <t>Grants.gov</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>Clinical Training Awards</t>
+          <t>Administration for Community Living – HHS-2027-ACL-NIDILRR-AREM-0301</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>Clinical Training Awards</t>
+          <t>Advanced Rehabilitation Research Training (ARRT) Program - Employment</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>Parkinson, Invecchiamento</t>
+          <t>Altre malattie e riabilitazione</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>parkinson, movement disorder, aging</t>
+          <t>rehabilitat</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>Finanzia la formazione clinica avanzata e la ricerca nella malattia di Parkinson e disturbi del movimento, ma non è focalizzato specificamente sulla riabilitazione.</t>
+          <t>Finanzia la formazione avanzata di ricercatori nel campo della riabilitazione e disabilità con focus sull'occupazione.</t>
         </is>
       </c>
       <c r="P26" s="6" t="n">
-        <v>50000</v>
+        <v>250000</v>
       </c>
       <c r="Q26" s="6" t="n">
-        <v>103800</v>
+        <v>250000</v>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
@@ -4128,22 +4136,24 @@
         </is>
       </c>
       <c r="S26" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t>Bassa – 4 progetti finanziabili (stima: tasso storico non disponibile)</t>
+          <t>Bassa – 1 progetti finanziabili (stima: tasso storico non disponibile)</t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t>Non indicato</t>
-        </is>
-      </c>
-      <c r="V26" s="4" t="n"/>
+          <t>Interamente finanziato</t>
+        </is>
+      </c>
+      <c r="V26" s="4" t="n">
+        <v>46290</v>
+      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>24 mesi</t>
+          <t>36 mesi</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
@@ -4153,13 +4163,13 @@
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t>Clinici, ricercatori a inizio carriera, docenti di scienze infermieristiche e istituzioni con programmi formativi nei disordini del movimento</t>
+          <t>Private institutions of higher education; Public and State controlled institutions of higher education</t>
         </is>
       </c>
       <c r="Z26" s="3" t="n"/>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>Mondiale</t>
+          <t>Solo enti statunitensi</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
@@ -4169,107 +4179,141 @@
       </c>
       <c r="AC26" s="7" t="inlineStr">
         <is>
-          <t>https://www.parkinson.org/resources-support/professionals/clinical-training-awards</t>
+          <t>https://www.grants.gov/search-results-detail/363964</t>
         </is>
       </c>
       <c r="AD26" s="3" t="inlineStr">
         <is>
-          <t>La Parkinson's Foundation offre diversi programmi di finanziamento alla formazione per migliorare l'assistenza a persone affette da malattia di Parkinson e disturbi del movimento. Le opportunità includono borse biennali per istituzioni volte alla formazione specialistica di nuovi neurologi clinici (fino a 103.800 dollari/anno), il Mentored Clinical Research Award da 50.000 dollari in collaborazione con il Parkinson Study Group per giovani ricercatori entro cinque anni dal termine della specializzazione, e il Nurse Faculty Award (fino a 10.000 dollari) per docenti infermieri. I contributi coprono stipendi, costi diretti di ricerca e attività di sviluppo accademico e clinico.</t>
+          <t>Il programma ARRT promosso dal NIDILRR (Administration for Community Living) è finalizzato a erogare formazione avanzata ed esperienza scientifica a professionisti in possesso di dottorato o titoli equivalenti nel settore della riabilitazione, incentivando la partecipazione di ricercatori con disabilità. Questa specifica opportunità si concentra sul potenziamento delle competenze per condurre studi multidisciplinari incentrati sugli esiti lavorativi e sull'inclusione occupazionale delle persone con disabilità. L'iniziativa prevede l'assegnazione di un unico finanziamento per una durata complessiva di 36 mesi, suddiviso in tre annualità di budget. Possono concorrere unicamente istituzioni di istruzione superiore pubbliche, statali o private statunitensi, mentre gli enti esteri sono esplicitamente esclusi dalla competizione e dall'assegnazione del contributo.</t>
         </is>
       </c>
       <c r="AE26" s="4" t="n">
         <v>46316</v>
       </c>
       <c r="AF26" s="4" t="n">
-        <v>46312</v>
+        <v>46316</v>
       </c>
       <c r="AG26" s="2" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>WEB-c663b3090d73</t>
+          <t>GG-HHS-2027-ACL-NIDILRR-ARHF-0302</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Da verificare</t>
+          <t>No</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Non analizzato</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="n"/>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Formazione / fellowship</t>
+        </is>
+      </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Community</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="n"/>
+          <t>Programma di formazione avanzata nella ricerca riabilitativa (ARRT) - Salute e funzionalità</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>46363</v>
+      </c>
       <c r="G27" s="5">
         <f>IF(F27="","",F27-TODAY())</f>
         <v/>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Scadenza da verificare</t>
+          <t>Aperto</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Parkinson's UK</t>
+          <t>Administration for Community Living</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>Parkinson's UK</t>
+          <t>Grants.gov</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>Community</t>
+          <t>Administration for Community Living – HHS-2027-ACL-NIDILRR-ARHF-0302</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>Community</t>
+          <t>Advanced Rehabilitation Research Training (ARRT) Program - Health and Function</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>Parkinson</t>
+          <t>Altre malattie e riabilitazione</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>parkinson</t>
-        </is>
-      </c>
-      <c r="O27" s="3" t="n"/>
-      <c r="P27" s="6" t="n"/>
-      <c r="Q27" s="6" t="n"/>
-      <c r="R27" s="2" t="n"/>
-      <c r="S27" s="2" t="n"/>
+          <t>rehabilitat</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t>Finanzia programmi di formazione avanzata per ricercatori nell'ambito della riabilitazione focalizzati su salute e funzionalità.</t>
+        </is>
+      </c>
+      <c r="P27" s="6" t="n">
+        <v>250000</v>
+      </c>
+      <c r="Q27" s="6" t="n">
+        <v>250000</v>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t>Non stimabile – dati insufficienti</t>
+          <t>Bassa – 1 progetti finanziabili (stima: tasso storico non disponibile)</t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t>Non indicato</t>
-        </is>
-      </c>
-      <c r="V27" s="4" t="n"/>
-      <c r="W27" s="2" t="n"/>
-      <c r="X27" s="2" t="n"/>
-      <c r="Y27" s="3" t="n"/>
+          <t>Interamente finanziato</t>
+        </is>
+      </c>
+      <c r="V27" s="4" t="n">
+        <v>46290</v>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>36 mesi</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>Ricerca</t>
+        </is>
+      </c>
+      <c r="Y27" s="3" t="inlineStr">
+        <is>
+          <t>Public and State controlled institutions of higher education; Private institutions of higher education</t>
+        </is>
+      </c>
       <c r="Z27" s="3" t="n"/>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>Regno Unito</t>
+          <t>Solo enti statunitensi</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
@@ -4279,88 +4323,112 @@
       </c>
       <c r="AC27" s="7" t="inlineStr">
         <is>
-          <t>https://www.parkinsons.org.uk/community</t>
-        </is>
-      </c>
-      <c r="AD27" s="3" t="n"/>
+          <t>https://www.grants.gov/search-results-detail/363965</t>
+        </is>
+      </c>
+      <c r="AD27" s="3" t="inlineStr">
+        <is>
+          <t>L'iniziativa ARRT promossa dal National Institute on Disability, Independent Living, and Rehabilitation Research (NIDILRR) sostiene programmi formativi avanzati destinati a ricercatori post-dottorato nel campo della riabilitazione, inclusi studiosi con disabilità. L'obiettivo consiste nell'accrescere le competenze metodologiche e scientifiche per sviluppare ricerche multidisciplinari mirate al miglioramento della salute, del recupero funzionale e del benessere delle persone con disabilità fisiche o cognitive. È prevista l'assegnazione di un solo finanziamento della durata di 36 mesi, articolato su tre cicli annuali di spesa. La partecipazione è riservata esclusivamente a istituti di istruzione superiore pubblici, statali o privati statunitensi; gli enti internazionali e stranieri non sono ammessi a concorrere né a ricevere il finanziamento.</t>
+        </is>
+      </c>
       <c r="AE27" s="4" t="n">
-        <v>46313</v>
+        <v>46316</v>
       </c>
       <c r="AF27" s="4" t="n">
-        <v>46312</v>
+        <v>46316</v>
       </c>
       <c r="AG27" s="2" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>WEB-0736bd22ae0a</t>
+          <t>WEB-14a8635c6be7</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Da verificare</t>
+          <t>No</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Non analizzato</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="n"/>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Formazione / fellowship</t>
+        </is>
+      </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>For Parkinson's researchers</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="n"/>
+          <t>Borse di studio per la promozione degli studi di dottorato (PODS)</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>46407</v>
+      </c>
       <c r="G28" s="5">
         <f>IF(F28="","",F28-TODAY())</f>
         <v/>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Scadenza da verificare</t>
+          <t>Aperto</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Parkinson's UK</t>
+          <t>Foundation for Physical Therapy Research</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>Parkinson's UK</t>
+          <t>Foundation for Physical Therapy Research</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>For Parkinson's researchers</t>
+          <t>Promotion of Doctoral Studies Scholarships</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>For Parkinson's researchers</t>
+          <t>Promotion of Doctoral Studies Scholarships</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>Parkinson</t>
+          <t>Invecchiamento, Altre malattie e riabilitazione</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>parkinson</t>
-        </is>
-      </c>
-      <c r="O28" s="3" t="n"/>
-      <c r="P28" s="6" t="n"/>
-      <c r="Q28" s="6" t="n"/>
-      <c r="R28" s="2" t="n"/>
-      <c r="S28" s="2" t="n"/>
+          <t>geriatr, physical therap, cardiovascular, pulmonary</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t>Finanzia borse di studio dottorali per fisioterapisti impegnati nella ricerca riabilitativa clinica e applicata.</t>
+        </is>
+      </c>
+      <c r="P28" s="6" t="n">
+        <v>7500</v>
+      </c>
+      <c r="Q28" s="6" t="n">
+        <v>15000</v>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="n">
+        <v>22</v>
+      </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t>Non stimabile – dati insufficienti</t>
+          <t>Alta – 22 progetti finanziabili (stima: tasso storico non disponibile)</t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
@@ -4369,13 +4437,25 @@
         </is>
       </c>
       <c r="V28" s="4" t="n"/>
-      <c r="W28" s="2" t="n"/>
-      <c r="X28" s="2" t="n"/>
-      <c r="Y28" s="3" t="n"/>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>12 mesi</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>Dottorato / formazione / mobilità</t>
+        </is>
+      </c>
+      <c r="Y28" s="3" t="inlineStr">
+        <is>
+          <t>Fisioterapisti e fisioterapeuti assistenti APTA membri</t>
+        </is>
+      </c>
       <c r="Z28" s="3" t="n"/>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>Regno Unito</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
@@ -4385,12 +4465,16 @@
       </c>
       <c r="AC28" s="7" t="inlineStr">
         <is>
-          <t>https://www.parkinsons.org.uk/research/researchers</t>
-        </is>
-      </c>
-      <c r="AD28" s="3" t="n"/>
+          <t>https://foundation4pt.org/foundation-funding-opportunities/scholarships/</t>
+        </is>
+      </c>
+      <c r="AD28" s="3" t="inlineStr">
+        <is>
+          <t>La Foundation for Physical Therapy Research offre borse di studio a supporto dei fisioterapisti abilitati e assistenti di fisioterapia, iscritti all'APTA, che frequentano un programma di dottorato di ricerca (PhD, EdD, DSc) con l'intento di intraprendere una carriera scientifica nella riabilitazione. Il bando prevede due fasi: pre-candidatura (PODSI), con borse annuali di 7.500 dollari per il percorso di corsi preliminari, e candidatura dottorale (PODSII), con borse annuali di 15.000 dollari per la fase di tesi e ricerca. Sono previsti finanziamenti generali e su aree specialistiche quali neurologia, geriatria, riabilitazione cardiovascolare e polmonare, pediatria e ricerca sui servizi sanitari, con un totale stimato di circa 22 borse disponibili.</t>
+        </is>
+      </c>
       <c r="AE28" s="4" t="n">
-        <v>46313</v>
+        <v>46316</v>
       </c>
       <c r="AF28" s="4" t="n">
         <v>46312</v>
@@ -4400,94 +4484,122 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>WEB-72cbdd3b13f6</t>
+          <t>GG-HHS-2027-ACL-NIDILRR-DPTB-0311</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Da verificare</t>
+          <t>No</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Non analizzato</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="n"/>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Ricerca clinica</t>
+        </is>
+      </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>We're investing over £280,000 to accelerate the development of new Parkinson's drugs</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="n"/>
+          <t>Centri modello per il sistema di cura e riabilitazione del trauma cranico encefalico</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>46478</v>
+      </c>
       <c r="G29" s="5">
         <f>IF(F29="","",F29-TODAY())</f>
         <v/>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Scadenza da verificare</t>
+          <t>Aperto</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>Parkinson's UK</t>
+          <t>Administration for Community Living</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>Parkinson's UK</t>
+          <t>Grants.gov</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>We're investing over £280,000 to accelerate the development of new Parkinson's drugs</t>
+          <t>Administration for Community Living – HHS-2027-ACL-NIDILRR-DPTB-0311</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>We're investing over £280,000 to accelerate the development of new Parkinson's drugs</t>
+          <t>Traumatic Brain Injury Model Systems Centers</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>Parkinson</t>
+          <t>Altre malattie e riabilitazione</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>parkinson</t>
-        </is>
-      </c>
-      <c r="O29" s="3" t="n"/>
+          <t>rehabilitat, traumatic brain injur</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t>Focalizzato specificamente sulla riabilitazione clinica evidence-based e il recupero funzionale nei pazienti con trauma cranico (TBI).</t>
+        </is>
+      </c>
       <c r="P29" s="6" t="n">
-        <v>280000</v>
-      </c>
-      <c r="Q29" s="6" t="n"/>
+        <v>8450000</v>
+      </c>
+      <c r="Q29" s="6" t="n">
+        <v>640000</v>
+      </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="n"/>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="n">
+        <v>14</v>
+      </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t>Non stimabile – dati insufficienti</t>
+          <t>Media – 14 progetti finanziabili (stima: tasso storico non disponibile)</t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t>Non indicato</t>
-        </is>
-      </c>
-      <c r="V29" s="4" t="n"/>
-      <c r="W29" s="2" t="n"/>
-      <c r="X29" s="2" t="n"/>
-      <c r="Y29" s="3" t="n"/>
+          <t>Interamente finanziato</t>
+        </is>
+      </c>
+      <c r="V29" s="4" t="n">
+        <v>46290</v>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>60 mesi</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>Ricerca</t>
+        </is>
+      </c>
+      <c r="Y29" s="3" t="inlineStr">
+        <is>
+          <t>City or township governments; Small businesses; State governments; Special district governments; Nonprofits that do not have a 501(c)(3) status with the IRS, other than institutions of higher education; Nonprofits having a 501(c)(3) status with the IRS, other than institutions of higher education; County governments; Public and State controlled institutions of higher education; Native American tri</t>
+        </is>
+      </c>
       <c r="Z29" s="3" t="n"/>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>Regno Unito</t>
+          <t>Solo enti statunitensi</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
@@ -4497,103 +4609,141 @@
       </c>
       <c r="AC29" s="7" t="inlineStr">
         <is>
-          <t>https://www.parkinsons.org.uk/news/2026/were-investing-over-ps280000-to-accelerate-development-new-parkinsons-drugs</t>
-        </is>
-      </c>
-      <c r="AD29" s="3" t="n"/>
+          <t>https://www.grants.gov/search-results-detail/363970</t>
+        </is>
+      </c>
+      <c r="AD29" s="3" t="inlineStr">
+        <is>
+          <t>L'iniziativa finanzia i centri TBI Model Systems (TBIMS) con lo scopo di condurre ricerche cliniche per lo sviluppo e l'accesso alla riabilitazione evidence-based nei traumi cranio-encefalici. I centri devono generare nuova conoscenza per migliorare gli esiti funzionali, l'inclusione nella comunità e l'occupazione, oltre a contribuire al database longitudinale TBIMS. Possono candidarsi esclusivamente enti dotati di un continuum multidisciplinare di cura (dall'emergenza alla riabilitazione post-acuta). Le entità estere sono escluse. Il progetto prevede una durata di 60 mesi.</t>
+        </is>
+      </c>
       <c r="AE29" s="4" t="n">
-        <v>46313</v>
+        <v>46316</v>
       </c>
       <c r="AF29" s="4" t="n">
-        <v>46312</v>
+        <v>46316</v>
       </c>
       <c r="AG29" s="2" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>WEB-cd0026aac9d1</t>
+          <t>GG-HHS-2027-ACL-NIDILRR-REGE-0312</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Da verificare</t>
+          <t>No</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Non analizzato</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="n"/>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Tecnologia / innovazione</t>
+        </is>
+      </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>The Community Awards</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="n"/>
+          <t>Centro di ricerca ingegneristica per la riabilitazione sulle tecnologie per ricreazione, sport ed esercizio nelle disabilità</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>46492</v>
+      </c>
       <c r="G30" s="5">
         <f>IF(F30="","",F30-TODAY())</f>
         <v/>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Scadenza da verificare</t>
+          <t>Aperto</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Parkinson's UK</t>
+          <t>Administration for Community Living</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>Parkinson's UK</t>
+          <t>Grants.gov</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>The Community Awards</t>
+          <t>Administration for Community Living – HHS-2027-ACL-NIDILRR-REGE-0312</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>The Community Awards</t>
+          <t>Rehabilitation Engineering Research Center on Recreational, Sport, and Exercise Technologies for People with Disabilities</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>Parkinson</t>
+          <t>Tecnologie riabilitazione, Altre malattie e riabilitazione</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>parkinson</t>
-        </is>
-      </c>
-      <c r="O30" s="3" t="n"/>
-      <c r="P30" s="6" t="n"/>
-      <c r="Q30" s="6" t="n"/>
-      <c r="R30" s="2" t="n"/>
-      <c r="S30" s="2" t="n"/>
+          <t>rehabilitation engineering, rehabilitat</t>
+        </is>
+      </c>
+      <c r="O30" s="3" t="inlineStr">
+        <is>
+          <t>Finanzia ricerca ingegneristica e sviluppo tecnologico per l'esercizio, lo sport e la riabilitazione di persone con disabilità.</t>
+        </is>
+      </c>
+      <c r="P30" s="6" t="n">
+        <v>975000</v>
+      </c>
+      <c r="Q30" s="6" t="n">
+        <v>975000</v>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t>Non stimabile – dati insufficienti</t>
+          <t>Bassa – 1 progetti finanziabili (stima: tasso storico non disponibile)</t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t>Non indicato</t>
-        </is>
-      </c>
-      <c r="V30" s="4" t="n"/>
-      <c r="W30" s="2" t="n"/>
-      <c r="X30" s="2" t="n"/>
-      <c r="Y30" s="3" t="n"/>
+          <t>Interamente finanziato</t>
+        </is>
+      </c>
+      <c r="V30" s="4" t="n">
+        <v>46290</v>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>60 mesi</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>Ricerca</t>
+        </is>
+      </c>
+      <c r="Y30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nonprofits that do not have a 501(c)(3) status with the IRS, other than institutions of higher education; Nonprofits having a 501(c)(3) status with the IRS, other than institutions of higher education; Public and State controlled institutions of higher education; Small businesses; State governments; County governments; Private institutions of higher education; City or township governments; Others </t>
+        </is>
+      </c>
       <c r="Z30" s="3" t="n"/>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>Regno Unito</t>
+          <t>Solo enti statunitensi</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
@@ -4603,109 +4753,141 @@
       </c>
       <c r="AC30" s="7" t="inlineStr">
         <is>
-          <t>https://www.parkinsons.org.uk/community/awards</t>
-        </is>
-      </c>
-      <c r="AD30" s="3" t="n"/>
+          <t>https://www.grants.gov/search-results-detail/363973</t>
+        </is>
+      </c>
+      <c r="AD30" s="3" t="inlineStr">
+        <is>
+          <t>Il bando finanzia un Rehabilitation Engineering Research Center (RERC) per condurre ricerca ingegneristica avanzata e sviluppo di tecnologie innovative dedicate a promuovere l'esercizio fisico, lo sport e la salute in persone con disabilità, eliminando le barriere ambientali. NIDILRR intende assegnare un singolo finanziamento della durata complessiva di 60 mesi (5 periodi di bilancio da 12 mesi). Possono candidarsi stati, enti pubblici e privati (compresi for-profit), atenei e organizzazioni comunitarie statunitensi; le organizzazioni estere non sono ammesse al bando.</t>
+        </is>
+      </c>
       <c r="AE30" s="4" t="n">
-        <v>46313</v>
+        <v>46316</v>
       </c>
       <c r="AF30" s="4" t="n">
-        <v>46312</v>
+        <v>46316</v>
       </c>
       <c r="AG30" s="2" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>WEB-c2a48185fa75</t>
+          <t>GG-HHS-2027-ACL-NIDILRR-REGE-0313</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Da verificare</t>
+          <t>No</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Non analizzato</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="n"/>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Tecnologia / innovazione</t>
+        </is>
+      </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Support for your research meetings</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="n"/>
+          <t>Centro di ricerca ingegneristica per la riabilitazione sulle tecnologie per persone non vedenti o ipovedenti</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>46499</v>
+      </c>
       <c r="G31" s="5">
         <f>IF(F31="","",F31-TODAY())</f>
         <v/>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Scadenza da verificare</t>
+          <t>Aperto</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Parkinson's UK</t>
+          <t>Administration for Community Living</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>Parkinson's UK</t>
+          <t>Grants.gov</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>Support for your research meetings</t>
+          <t>Administration for Community Living – HHS-2027-ACL-NIDILRR-REGE-0313</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>Support for your research meetings</t>
+          <t>Rehabilitation Engineering Research Center on Technologies for People Who are Blind or have Low Vision</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>Parkinson</t>
+          <t>Tecnologie riabilitazione</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>parkinson</t>
-        </is>
-      </c>
-      <c r="O31" s="3" t="n"/>
+          <t>rehabilitation engineering</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="inlineStr">
+        <is>
+          <t>Dedicato allo sviluppo di tecnologie e ausili per l'autonomia e la riabilitazione visiva in persone non vedenti o ipovedenti.</t>
+        </is>
+      </c>
       <c r="P31" s="6" t="n">
-        <v>2500</v>
-      </c>
-      <c r="Q31" s="6" t="n"/>
+        <v>975000</v>
+      </c>
+      <c r="Q31" s="6" t="n">
+        <v>975000</v>
+      </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="S31" s="2" t="n"/>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t>Non stimabile – dati insufficienti</t>
+          <t>Bassa – 1 progetti finanziabili (stima: tasso storico non disponibile)</t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t>Non indicato</t>
-        </is>
-      </c>
-      <c r="V31" s="4" t="n"/>
-      <c r="W31" s="2" t="n"/>
-      <c r="X31" s="2" t="n"/>
-      <c r="Y31" s="3" t="n"/>
+          <t>Interamente finanziato</t>
+        </is>
+      </c>
+      <c r="V31" s="4" t="n">
+        <v>46290</v>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>60 mesi</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>Ricerca</t>
+        </is>
+      </c>
+      <c r="Y31" s="3" t="inlineStr">
+        <is>
+          <t>Nonprofits having a 501(c)(3) status with the IRS, other than institutions of higher education; For profit organizations other than small businesses; Public and State controlled institutions of higher education; Native American tribal organizations (other than Federally recognized tribal governments); State governments; County governments; Nonprofits that do not have a 501(c)(3) status with the IR</t>
+        </is>
+      </c>
       <c r="Z31" s="3" t="n"/>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>Regno Unito</t>
+          <t>Solo enti statunitensi</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
@@ -4715,103 +4897,139 @@
       </c>
       <c r="AC31" s="7" t="inlineStr">
         <is>
-          <t>https://www.parkinsons.org.uk/research/funding-grants/support-your-research-meetings</t>
-        </is>
-      </c>
-      <c r="AD31" s="3" t="n"/>
+          <t>https://www.grants.gov/search-results-detail/363974</t>
+        </is>
+      </c>
+      <c r="AD31" s="3" t="inlineStr">
+        <is>
+          <t>Il programma Rehabilitation Engineering Research Centers (RERC) intende finanziare un centro focalizzato sulla ricerca ingegneristica e sullo sviluppo di tecnologie assistive avanzate volte a promuovere l'indipendenza funzionale e la vita nella comunità per individui non vedenti o ipovedenti. È previsto il finanziamento di un unico progetto della durata di 60 mesi. Possono partecipare atenei, enti pubblici o privati profit e no-profit con sede negli Stati Uniti. Le entità straniere non sono idonee alla candidatura né alla ricezione dei fondi.</t>
+        </is>
+      </c>
       <c r="AE31" s="4" t="n">
-        <v>46313</v>
+        <v>46316</v>
       </c>
       <c r="AF31" s="4" t="n">
-        <v>46312</v>
+        <v>46316</v>
       </c>
       <c r="AG31" s="2" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>WEB-652379f6d9fa</t>
+          <t>GG-RFA-NS-26-001</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Da verificare</t>
+          <t>No</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Non analizzato</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="n"/>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Ricerca clinica</t>
+        </is>
+      </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Support and information for grants</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="n"/>
+          <t>Accesso allargato a popolazioni intermedie di pazienti con sclerosi laterale amiotrofica (U01)</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>46336</v>
+      </c>
       <c r="G32" s="5">
         <f>IF(F32="","",F32-TODAY())</f>
         <v/>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Scadenza da verificare</t>
+          <t>In scadenza (≤30 gg)</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Parkinson's UK</t>
+          <t>National Institutes of Health</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>Parkinson's UK</t>
+          <t>Grants.gov</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>Support and information for grants</t>
+          <t>National Institutes of Health – RFA-NS-26-001</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>Support and information for grants</t>
+          <t>Amyotrophic Lateral Sclerosis (ALS) Intermediate Patient Population Expanded Access (U01 Clinical Trial Required)</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>Parkinson</t>
+          <t>Altre malattie e riabilitazione</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>parkinson</t>
-        </is>
-      </c>
-      <c r="O32" s="3" t="n"/>
-      <c r="P32" s="6" t="n"/>
+          <t>amyotrophic lateral sclerosis</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t>Riguarda la sclerosi laterale amiotrofica (SLA) nell'ambito di farmaci sperimentali in accesso allargato, non la riabilitazione.</t>
+        </is>
+      </c>
+      <c r="P32" s="6" t="n">
+        <v>40000000</v>
+      </c>
       <c r="Q32" s="6" t="n"/>
-      <c r="R32" s="2" t="n"/>
-      <c r="S32" s="2" t="n"/>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="n">
+        <v>4</v>
+      </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t>Non stimabile – dati insufficienti</t>
+          <t>Bassa – 4 progetti finanziabili (stima: tasso storico non disponibile)</t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t>Non indicato</t>
-        </is>
-      </c>
-      <c r="V32" s="4" t="n"/>
+          <t>Interamente finanziato</t>
+        </is>
+      </c>
+      <c r="V32" s="4" t="n">
+        <v>46146</v>
+      </c>
       <c r="W32" s="2" t="n"/>
-      <c r="X32" s="2" t="n"/>
-      <c r="Y32" s="3" t="n"/>
-      <c r="Z32" s="3" t="n"/>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>Ricerca</t>
+        </is>
+      </c>
+      <c r="Y32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nonprofits having a 501(c)(3) status with the IRS, other than institutions of higher education; Nonprofits that do not have a 501(c)(3) status with the IRS, other than institutions of higher education; Native American tribal governments (Federally recognized); For profit organizations other than small businesses; Public housing authorities/Indian housing authorities; Special district governments; </t>
+        </is>
+      </c>
+      <c r="Z32" s="3" t="inlineStr">
+        <is>
+          <t>Centri di sperimentazione clinica collegati a trial di fase 2/3 o 3 con sponsor di piccola impresa</t>
+        </is>
+      </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>Regno Unito</t>
+          <t>Solo enti statunitensi</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
@@ -4821,84 +5039,102 @@
       </c>
       <c r="AC32" s="7" t="inlineStr">
         <is>
-          <t>https://www.parkinsons.org.uk/research/funding-grants/policies</t>
-        </is>
-      </c>
-      <c r="AD32" s="3" t="n"/>
+          <t>https://www.grants.gov/search-results-detail/360400</t>
+        </is>
+      </c>
+      <c r="AD32" s="3" t="inlineStr">
+        <is>
+          <t>Bando promosso dal NINDS per condurre attività di ricerca clinica che utilizzano dati derivanti da programmi di accesso allargato (Expanded Access) a farmaci o prodotti biologici sperimentali per la sclerosi laterale amiotrofica (SLA). L'opportunità è indirizzata a popolazioni di pazienti di dimensioni intermedie che non risultano idonei all'arruolamento nei trial clinici convenzionali per il trattamento o la prevenzione della SLA. Possono partecipare unicamente centri clinici già coinvolti in trial registrativi di fase 2/3 o 3 sponsorizzati da piccole imprese in possesso di IND approvato dalla FDA. Il bando esclude categoricamente gli enti non statunitensi e le collaborazioni con componenti estere.</t>
+        </is>
+      </c>
       <c r="AE32" s="4" t="n">
-        <v>46313</v>
+        <v>46316</v>
       </c>
       <c r="AF32" s="4" t="n">
-        <v>46312</v>
+        <v>46316</v>
       </c>
       <c r="AG32" s="2" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>WEB-26a7ffacb785</t>
+          <t>GG-RFA-NS-28-009</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Da verificare</t>
+          <t>No</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Non analizzato</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="n"/>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Ricerca clinica</t>
+        </is>
+      </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>What research are we supporting?</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="n"/>
+          <t>Accesso allargato a popolazioni intermedie di pazienti con sclerosi laterale amiotrofica (SLA) (U01)</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>46532</v>
+      </c>
       <c r="G33" s="5">
         <f>IF(F33="","",F33-TODAY())</f>
         <v/>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Scadenza da verificare</t>
+          <t>Aperto</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>Alzheimer's Society</t>
+          <t>National Institutes of Health</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>Alzheimer's Society</t>
+          <t>Grants.gov</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>What research are we supporting?</t>
+          <t>National Institutes of Health – RFA-NS-28-009</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>What research are we supporting?</t>
+          <t>Amyotrophic Lateral Sclerosis (ALS) Intermediate Patient Population Expanded Access (U01 Clinical Trial Required)</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>Invecchiamento</t>
+          <t>Ictus, Altre malattie e riabilitazione</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>dementi, alzheimer, aging</t>
-        </is>
-      </c>
-      <c r="O33" s="3" t="n"/>
+          <t>stroke, amyotrophic lateral sclerosis, neurological disorder</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t>Riguarda la SLA ma è focalizzato su protocolli di accesso allargato a farmaci sperimentali e biomarcatori.</t>
+        </is>
+      </c>
       <c r="P33" s="6" t="n"/>
       <c r="Q33" s="6" t="n"/>
-      <c r="R33" s="2" t="n"/>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
       <c r="S33" s="2" t="n"/>
       <c r="T33" s="3" t="inlineStr">
         <is>
@@ -4907,17 +5143,27 @@
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t>Non indicato</t>
-        </is>
-      </c>
-      <c r="V33" s="4" t="n"/>
+          <t>Interamente finanziato</t>
+        </is>
+      </c>
+      <c r="V33" s="4" t="n">
+        <v>46288</v>
+      </c>
       <c r="W33" s="2" t="n"/>
-      <c r="X33" s="2" t="n"/>
-      <c r="Y33" s="3" t="n"/>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>Ricerca</t>
+        </is>
+      </c>
+      <c r="Y33" s="3" t="inlineStr">
+        <is>
+          <t>Native American tribal governments (Federally recognized); County governments; Small businesses; State governments; Nonprofits having a 501(c)(3) status with the IRS, other than institutions of higher education; Special district governments; For profit organizations other than small businesses; Others (see text field entitled "Additional Information on Eligibility" for clarification); Private inst</t>
+        </is>
+      </c>
       <c r="Z33" s="3" t="n"/>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>Regno Unito</t>
+          <t>Solo enti statunitensi</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
@@ -4927,68 +5173,78 @@
       </c>
       <c r="AC33" s="7" t="inlineStr">
         <is>
-          <t>https://www.alzheimers.org.uk/research/our-research/what-research-alzheimers-society-funding</t>
-        </is>
-      </c>
-      <c r="AD33" s="3" t="n"/>
+          <t>https://www.grants.gov/search-results-detail/363926</t>
+        </is>
+      </c>
+      <c r="AD33" s="3" t="inlineStr">
+        <is>
+          <t>Il National Institute of Neurological Disorders and Stroke (NINDS) intende sostenere la ricerca scientifica basata sui dati derivanti da protocolli di accesso allargato di dimensioni intermedie per la sclerosi laterale amiotrofica (SLA). I protocolli ammissibili devono fornire accesso a farmaci o prodotti biologici sperimentali e generare dati a supporto della ricerca su prevenzione, diagnosi o trattamento della SLA, inclusi effetti su biomarcatori, sicurezza, sopravvivenza o esiti clinici rilevanti (es. ospedalizzazione o ventilazione assistita). Possono candidarsi centri clinici partecipanti a trial di fase 2/3 o fase 3 promossi da una piccola impresa statunitense titolare dell'IND presso la FDA. Non sono ammesse organizzazioni né componenti non statunitensi.</t>
+        </is>
+      </c>
       <c r="AE33" s="4" t="n">
-        <v>46313</v>
+        <v>46316</v>
       </c>
       <c r="AF33" s="4" t="n">
-        <v>46312</v>
+        <v>46316</v>
       </c>
       <c r="AG33" s="2" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>WEB-c22a85799878</t>
+          <t>GG-RFA-AG-26-011</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Da verificare</t>
+          <t>No</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Non analizzato</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="n"/>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Formazione / fellowship</t>
+        </is>
+      </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Our Dementia Research Leaders programme</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="n"/>
+          <t>Programma estivo di formazione alla ricerca NIA per espandere gli studi su Alzheimer e demenze (R25)</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>46533</v>
+      </c>
       <c r="G34" s="5">
         <f>IF(F34="","",F34-TODAY())</f>
         <v/>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Scadenza da verificare</t>
+          <t>Aperto</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Alzheimer's Society</t>
+          <t>National Institutes of Health</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>Alzheimer's Society</t>
+          <t>Grants.gov</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>Our Dementia Research Leaders programme</t>
+          <t>National Institutes of Health – RFA-AG-26-011</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>Our Dementia Research Leaders programme</t>
+          <t>NIA Expanding Research in AD/ADRD (ERA) Summer Research Education Program (R25 Independent Clinical Trial Not Allowed)</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
@@ -5001,14 +5257,18 @@
           <t>dementi, alzheimer</t>
         </is>
       </c>
-      <c r="O34" s="3" t="n"/>
-      <c r="P34" s="6" t="n">
-        <v>550000</v>
-      </c>
-      <c r="Q34" s="6" t="n"/>
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t>Riguarda l'Alzheimer e le demenze correlate, ma è incentrato sulla formazione estiva alla ricerca per studenti.</t>
+        </is>
+      </c>
+      <c r="P34" s="6" t="n"/>
+      <c r="Q34" s="6" t="n">
+        <v>200000</v>
+      </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="S34" s="2" t="n"/>
@@ -5019,17 +5279,27 @@
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t>Non indicato</t>
-        </is>
-      </c>
-      <c r="V34" s="4" t="n"/>
+          <t>Interamente finanziato</t>
+        </is>
+      </c>
+      <c r="V34" s="4" t="n">
+        <v>45902</v>
+      </c>
       <c r="W34" s="2" t="n"/>
-      <c r="X34" s="2" t="n"/>
-      <c r="Y34" s="3" t="n"/>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>Dottorato / formazione / mobilità</t>
+        </is>
+      </c>
+      <c r="Y34" s="3" t="inlineStr">
+        <is>
+          <t>Special district governments; For profit organizations other than small businesses; State governments; Others (see text field entitled "Additional Information on Eligibility" for clarification); Native American tribal governments (Federally recognized); Native American tribal organizations (other than Federally recognized tribal governments); Small businesses; Public housing authorities/Indian hou</t>
+        </is>
+      </c>
       <c r="Z34" s="3" t="n"/>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>Regno Unito</t>
+          <t>Enti esteri non ammessi (call NIH completa)</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
@@ -5039,68 +5309,78 @@
       </c>
       <c r="AC34" s="7" t="inlineStr">
         <is>
-          <t>https://www.alzheimers.org.uk/research/researchers/our-funding-schemes/our-dementia-research-leaders-programme</t>
-        </is>
-      </c>
-      <c r="AD34" s="3" t="n"/>
+          <t>https://www.grants.gov/search-results-detail/359655</t>
+        </is>
+      </c>
+      <c r="AD34" s="3" t="inlineStr">
+        <is>
+          <t>Il National Institute on Aging (NIA) promuove lo sviluppo e l'attuazione di programmi estivi di educazione alla ricerca incentrati sulla malattia di Alzheimer e sulle demenze correlate (AD/ADRD). Il bando è rivolto a studenti delle scuole superiori, universitari o docenti di scienze, incoraggiando la partecipazione di gruppi sottorappresentati nelle scienze biomediche e comportamentali. L'obiettivo è ampliare il bacino di ricercatori qualificati fornendo esperienze intensive di ricerca estiva per favorire percorsi accademici avanzati nelle demenze. I partecipanti non possono condurre trial clinici indipendenti, ma possono maturare esperienza all'interno di sperimentazioni cliniche guidate da tutor. Le organizzazioni estere e i componenti stranieri sono esclusi.</t>
+        </is>
+      </c>
       <c r="AE34" s="4" t="n">
-        <v>46313</v>
+        <v>46316</v>
       </c>
       <c r="AF34" s="4" t="n">
-        <v>46312</v>
+        <v>46316</v>
       </c>
       <c r="AG34" s="2" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>WEB-528fe5f955ab</t>
+          <t>GG-RFA-AG-26-010</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Da verificare</t>
+          <t>No</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Non analizzato</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="n"/>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Formazione / fellowship</t>
+        </is>
+      </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>Dementia Network Plus</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="n"/>
+          <t>Programma post-laurea NIA di formazione alla ricerca per ampliare gli studi su Alzheimer e demenze (R25)</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="n">
+        <v>46533</v>
+      </c>
       <c r="G35" s="5">
         <f>IF(F35="","",F35-TODAY())</f>
         <v/>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Scadenza da verificare</t>
+          <t>Aperto</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>Alzheimer's Society</t>
+          <t>National Institutes of Health</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>Alzheimer's Society</t>
+          <t>Grants.gov</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>Dementia Network Plus</t>
+          <t>National Institutes of Health – RFA-AG-26-010</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>Dementia Network Plus</t>
+          <t>NIA Expanding Research in AD/ADRD (ERA) Postbaccalaureate Research Education Program (R25 Independent Clinical Trial Not Allowed)</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
@@ -5113,10 +5393,20 @@
           <t>dementi, alzheimer</t>
         </is>
       </c>
-      <c r="O35" s="3" t="n"/>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t>Riguarda l'Alzheimer e le demenze correlate, ma è dedicato alla formazione post-laurea triennale.</t>
+        </is>
+      </c>
       <c r="P35" s="6" t="n"/>
-      <c r="Q35" s="6" t="n"/>
-      <c r="R35" s="2" t="n"/>
+      <c r="Q35" s="6" t="n">
+        <v>400000</v>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
       <c r="S35" s="2" t="n"/>
       <c r="T35" s="3" t="inlineStr">
         <is>
@@ -5125,17 +5415,27 @@
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t>Non indicato</t>
-        </is>
-      </c>
-      <c r="V35" s="4" t="n"/>
+          <t>Interamente finanziato</t>
+        </is>
+      </c>
+      <c r="V35" s="4" t="n">
+        <v>45902</v>
+      </c>
       <c r="W35" s="2" t="n"/>
-      <c r="X35" s="2" t="n"/>
-      <c r="Y35" s="3" t="n"/>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>Dottorato / formazione / mobilità</t>
+        </is>
+      </c>
+      <c r="Y35" s="3" t="inlineStr">
+        <is>
+          <t>County governments; Special district governments; Native American tribal governments (Federally recognized); Native American tribal organizations (other than Federally recognized tribal governments); City or township governments; Nonprofits that do not have a 501(c)(3) status with the IRS, other than institutions of higher education; For profit organizations other than small businesses; Independen</t>
+        </is>
+      </c>
       <c r="Z35" s="3" t="n"/>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>Regno Unito</t>
+          <t>Enti esteri non ammessi (call NIH completa)</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
@@ -5145,68 +5445,78 @@
       </c>
       <c r="AC35" s="7" t="inlineStr">
         <is>
-          <t>https://www.alzheimers.org.uk/research/researchers/our-funding-schemes/Dementia-Network-Plus</t>
-        </is>
-      </c>
-      <c r="AD35" s="3" t="n"/>
+          <t>https://www.grants.gov/search-results-detail/359653</t>
+        </is>
+      </c>
+      <c r="AD35" s="3" t="inlineStr">
+        <is>
+          <t>Il National Institute on Aging (NIA) finanzia programmi di formazione alla ricerca per neolaureati (baccalaureate) incentrati sulla malattia di Alzheimer e sulle demenze correlate (AD/ADRD). L'iniziativa mira ad ampliare la comunità di ricercatori qualificati, includendo individui provenienti da contesti sottorappresentati nelle scienze biomediche e comportamentali, e fornendo un'esperienza precoce di ricerca nel settore. I percorsi educativi proposti dovranno offrire esperienze intensive per preparare i partecipanti al passaggio verso corsi di laurea magistrale, dottorati focalizzati sulla ricerca o carriere scientifiche nel settore privato. Non è consentito condurre trial clinici indipendenti. Le entità e le componenti estere non sono ammesse al bando.</t>
+        </is>
+      </c>
       <c r="AE35" s="4" t="n">
-        <v>46313</v>
+        <v>46316</v>
       </c>
       <c r="AF35" s="4" t="n">
-        <v>46312</v>
+        <v>46316</v>
       </c>
       <c r="AG35" s="2" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>WEB-1a27375931de</t>
+          <t>GG-PAR-24-321</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Da verificare</t>
+          <t>No</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Non analizzato</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="n"/>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Formazione / fellowship</t>
+        </is>
+      </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Marie Curie and Alzheimer’s Society partnership: end of life care in dementia</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="n"/>
+          <t>Finanziamento NIA per la leadership accademica e lo sviluppo di carriera (K07)</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>46703</v>
+      </c>
       <c r="G36" s="5">
         <f>IF(F36="","",F36-TODAY())</f>
         <v/>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Scadenza da verificare</t>
+          <t>Aperto</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Alzheimer's Society</t>
+          <t>National Institutes of Health</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>Alzheimer's Society</t>
+          <t>Grants.gov</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>Marie Curie and Alzheimer’s Society partnership: end of life care in dementia</t>
+          <t>National Institutes of Health – PAR-24-321</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>Marie Curie and Alzheimer’s Society partnership: end of life care in dementia</t>
+          <t>NIA Academic Leadership Career Award (K07 Independent Clinical Trial Not Allowed)</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
@@ -5216,17 +5526,19 @@
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>dementi, alzheimer</t>
-        </is>
-      </c>
-      <c r="O36" s="3" t="n"/>
-      <c r="P36" s="6" t="n">
-        <v>203314</v>
-      </c>
+          <t>dementi, alzheimer, aging</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="inlineStr">
+        <is>
+          <t>Tratta l'invecchiamento e le demenze ma si focalizza sullo sviluppo accademico, la mentorship e le capacità istituzionali di ricerca, non sulla riabilitazione.</t>
+        </is>
+      </c>
+      <c r="P36" s="6" t="n"/>
       <c r="Q36" s="6" t="n"/>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="S36" s="2" t="n"/>
@@ -5237,17 +5549,27 @@
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t>Non indicato</t>
-        </is>
-      </c>
-      <c r="V36" s="4" t="n"/>
+          <t>Interamente finanziato</t>
+        </is>
+      </c>
+      <c r="V36" s="4" t="n">
+        <v>45602</v>
+      </c>
       <c r="W36" s="2" t="n"/>
-      <c r="X36" s="2" t="n"/>
-      <c r="Y36" s="3" t="n"/>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>Dottorato / formazione / mobilità</t>
+        </is>
+      </c>
+      <c r="Y36" s="3" t="inlineStr">
+        <is>
+          <t>State governments; Independent school districts; Others (see text field entitled "Additional Information on Eligibility" for clarification); Native American tribal governments (Federally recognized); Nonprofits having a 501(c)(3) status with the IRS, other than institutions of higher education; Nonprofits that do not have a 501(c)(3) status with the IRS, other than institutions of higher education</t>
+        </is>
+      </c>
       <c r="Z36" s="3" t="n"/>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>Regno Unito</t>
+          <t>Enti esteri non ammessi (call NIH completa)</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
@@ -5257,84 +5579,102 @@
       </c>
       <c r="AC36" s="7" t="inlineStr">
         <is>
-          <t>https://www.alzheimers.org.uk/research/researchers/grants/marie-curie-research-grants-scheme</t>
-        </is>
-      </c>
-      <c r="AD36" s="3" t="n"/>
+          <t>https://www.grants.gov/search-results-detail/357000</t>
+        </is>
+      </c>
+      <c r="AD36" s="3" t="inlineStr">
+        <is>
+          <t>Il National Institute on Aging mette a disposizione fondi attraverso il meccanismo K07 per supportare ricercatori affermati dotati di comprovata esperienza e capacità di leadership, al fine di rafforzare la capacità di ricerca sull'invecchiamento, sulla malattia di Alzheimer e sulle demenze correlate all'interno delle loro istituzioni accademiche. Il finanziamento supporta lo sviluppo di infrastrutture formative e di ricerca, attività di mentorship, nuovi corsi curriculari e programmi pilota. Non è consentito condurre trial clinici indipendenti con questo bando. La partecipazione è riservata a docenti e ricercatori di istituzioni universitarie ed enti di ricerca situati negli Stati Uniti; le organizzazioni non statunitensi sono escluse.</t>
+        </is>
+      </c>
       <c r="AE36" s="4" t="n">
-        <v>46313</v>
+        <v>46316</v>
       </c>
       <c r="AF36" s="4" t="n">
-        <v>46312</v>
+        <v>46316</v>
       </c>
       <c r="AG36" s="2" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>WEB-680e0700594c</t>
+          <t>GG-PAR-25-024</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Da verificare</t>
+          <t>No</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Non analizzato</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="n"/>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Ricerca clinica</t>
+        </is>
+      </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Global Brain Health Institute</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="n"/>
+          <t>Sviluppo di biomarcatori o combinazioni di biomarcatori per patologie neurologiche e neuromuscolari (R61/R33)</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="n">
+        <v>46759</v>
+      </c>
       <c r="G37" s="5">
         <f>IF(F37="","",F37-TODAY())</f>
         <v/>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Scadenza da verificare</t>
+          <t>Aperto</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>Alzheimer's Society</t>
+          <t>National Institutes of Health</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>Alzheimer's Society</t>
+          <t>Grants.gov</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>Global Brain Health Institute</t>
+          <t>National Institutes of Health – PAR-25-024</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>Global Brain Health Institute</t>
+          <t>Development of Biomarkers or Composite Biomarkers for Neurological and Neuromuscular Disorders (R61/R33 - Clinical Trial Optional)</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>Invecchiamento</t>
+          <t>Altre malattie e riabilitazione</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>dementi, alzheimer, aging</t>
-        </is>
-      </c>
-      <c r="O37" s="3" t="n"/>
+          <t>neuromuscular</t>
+        </is>
+      </c>
+      <c r="O37" s="3" t="inlineStr">
+        <is>
+          <t>Il bando finanzia la ricerca di biomarcatori per patologie neurologiche e neuromuscolari senza un focus diretto su interventi di riabilitazione.</t>
+        </is>
+      </c>
       <c r="P37" s="6" t="n"/>
       <c r="Q37" s="6" t="n"/>
-      <c r="R37" s="2" t="n"/>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
       <c r="S37" s="2" t="n"/>
       <c r="T37" s="3" t="inlineStr">
         <is>
@@ -5343,17 +5683,27 @@
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t>Non indicato</t>
-        </is>
-      </c>
-      <c r="V37" s="4" t="n"/>
+          <t>Interamente finanziato</t>
+        </is>
+      </c>
+      <c r="V37" s="4" t="n">
+        <v>45593</v>
+      </c>
       <c r="W37" s="2" t="n"/>
-      <c r="X37" s="2" t="n"/>
-      <c r="Y37" s="3" t="n"/>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>Ricerca</t>
+        </is>
+      </c>
+      <c r="Y37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Native American tribal governments (Federally recognized); Public housing authorities/Indian housing authorities; Private institutions of higher education; Small businesses; City or township governments; Special district governments; Independent school districts; County governments; Native American tribal organizations (other than Federally recognized tribal governments); For profit organizations </t>
+        </is>
+      </c>
       <c r="Z37" s="3" t="n"/>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>Regno Unito</t>
+          <t>Enti esteri non ammessi (call NIH completa)</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
@@ -5363,68 +5713,78 @@
       </c>
       <c r="AC37" s="7" t="inlineStr">
         <is>
-          <t>https://www.alzheimers.org.uk/research/researchers/our-funding-schemes/GBHI</t>
-        </is>
-      </c>
-      <c r="AD37" s="3" t="n"/>
+          <t>https://www.grants.gov/search-results-detail/356874</t>
+        </is>
+      </c>
+      <c r="AD37" s="3" t="inlineStr">
+        <is>
+          <t>Questa opportunità promossa dal NIH supporta la scoperta e la valutazione preliminare di solidi biomarcatori o firme di biomarcatori mirati a facilitare lo sviluppo clinico di terapie neurologiche e il loro impiego nella pratica clinica. La call si focalizza sulla caratterizzazione biologica, analitica e clinica iniziale di marcatori per patologie neurologiche e neuromuscolari. I progetti possono includere modelli animali, ma devono obbligatoriamente prevedere una prima validazione su campioni o dataset clinici umani standardizzati. Possono concorrere università, ospedali, centri di ricerca e imprese commerciali con sede negli Stati Uniti. I soggetti esteri sono esclusi dalla candidatura come enti proponenti.</t>
+        </is>
+      </c>
       <c r="AE37" s="4" t="n">
-        <v>46313</v>
+        <v>46316</v>
       </c>
       <c r="AF37" s="4" t="n">
-        <v>46312</v>
+        <v>46316</v>
       </c>
       <c r="AG37" s="2" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>WEB-c4a20d1a25b4</t>
+          <t>GG-PAR-27-096</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Da verificare</t>
+          <t>No</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Non analizzato</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="n"/>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Ricerca clinica</t>
+        </is>
+      </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Clinical Committee</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="n"/>
+          <t>Finanziamenti per la transizione alla ricerca sull'invecchiamento per specialisti medici e chirurgici a inizio carriera (GEMSSTAR R03)</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>46950</v>
+      </c>
       <c r="G38" s="5">
         <f>IF(F38="","",F38-TODAY())</f>
         <v/>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Scadenza da verificare</t>
+          <t>Aperto</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>Alzheimer's Research UK</t>
+          <t>National Institutes of Health</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>Alzheimer's Research UK</t>
+          <t>Grants.gov</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>Clinical Committee</t>
+          <t>National Institutes of Health – PAR-27-096</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>Clinical Committee</t>
+          <t>Grants for Early Medical/Surgical Specialists' Transition to Aging Research (GEMSSTAR) (R03 Clinical Trial Optional)</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
@@ -5434,13 +5794,23 @@
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>dementi, alzheimer</t>
-        </is>
-      </c>
-      <c r="O38" s="3" t="n"/>
+          <t>geriatr, aging</t>
+        </is>
+      </c>
+      <c r="O38" s="3" t="inlineStr">
+        <is>
+          <t>Bando generale sulla ricerca geriatrica e sull'invecchiamento rivolto a medici specialisti, che può includere la riabilitazione ma non vi è specificamente dedicato.</t>
+        </is>
+      </c>
       <c r="P38" s="6" t="n"/>
-      <c r="Q38" s="6" t="n"/>
-      <c r="R38" s="2" t="n"/>
+      <c r="Q38" s="6" t="n">
+        <v>125000</v>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
       <c r="S38" s="2" t="n"/>
       <c r="T38" s="3" t="inlineStr">
         <is>
@@ -5449,17 +5819,27 @@
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t>Non indicato</t>
-        </is>
-      </c>
-      <c r="V38" s="4" t="n"/>
+          <t>Interamente finanziato</t>
+        </is>
+      </c>
+      <c r="V38" s="4" t="n">
+        <v>46266</v>
+      </c>
       <c r="W38" s="2" t="n"/>
-      <c r="X38" s="2" t="n"/>
-      <c r="Y38" s="3" t="n"/>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>Ricerca</t>
+        </is>
+      </c>
+      <c r="Y38" s="3" t="inlineStr">
+        <is>
+          <t>Native American tribal organizations (other than Federally recognized tribal governments); County governments; For profit organizations other than small businesses; State governments; Special district governments; Others (see text field entitled "Additional Information on Eligibility" for clarification); Private institutions of higher education; Native American tribal governments (Federally recogn</t>
+        </is>
+      </c>
       <c r="Z38" s="3" t="n"/>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>Regno Unito</t>
+          <t>Solo enti statunitensi</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
@@ -5469,3587 +5849,25 @@
       </c>
       <c r="AC38" s="7" t="inlineStr">
         <is>
-          <t>https://www.alzheimersresearchuk.org/research/for-researchers/grant-schemes/the-grants-review-process/clinical-committee/</t>
-        </is>
-      </c>
-      <c r="AD38" s="3" t="n"/>
+          <t>https://www.grants.gov/search-results-detail/359940</t>
+        </is>
+      </c>
+      <c r="AD38" s="3" t="inlineStr">
+        <is>
+          <t>Il programma GEMSSTAR del National Institute on Aging intende supportare medici-ricercatori a inizio carriera operanti in discipline mediche o chirurgiche per avviarli a ruoli di leadership nella ricerca sull'invecchiamento e geriatrica. Il bando finanzia progetti pilota transdisciplinari volti a generare dati preliminari per successive linee di ricerca, integrati con un piano formale di sviluppo professionale e mentorship. I candidati devono operare in un contesto clinico-accademico favorevole alla ricerca geriatrica. Possono presentare domanda esclusivamente istituzioni con sede negli Stati Uniti; le organizzazioni straniere e i sub-appalti finanziari verso istituzioni estere non sono ammessi.</t>
+        </is>
+      </c>
       <c r="AE38" s="4" t="n">
-        <v>46313</v>
+        <v>46316</v>
       </c>
       <c r="AF38" s="4" t="n">
-        <v>46313</v>
+        <v>46316</v>
       </c>
       <c r="AG38" s="2" t="n"/>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>WEB-89905577f1d9</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>Da verificare</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>Non analizzato</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="n"/>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>General Award Conditions</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="n"/>
-      <c r="G39" s="5">
-        <f>IF(F39="","",F39-TODAY())</f>
-        <v/>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>Scadenza da verificare</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>Alzheimer's Research UK</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>Alzheimer's Research UK</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>General Award Conditions</t>
-        </is>
-      </c>
-      <c r="L39" s="3" t="inlineStr">
-        <is>
-          <t>General Award Conditions</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t>Invecchiamento</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr">
-        <is>
-          <t>alzheimer</t>
-        </is>
-      </c>
-      <c r="O39" s="3" t="n"/>
-      <c r="P39" s="6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Q39" s="6" t="n"/>
-      <c r="R39" s="2" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="S39" s="2" t="n"/>
-      <c r="T39" s="3" t="inlineStr">
-        <is>
-          <t>Non stimabile – dati insufficienti</t>
-        </is>
-      </c>
-      <c r="U39" s="3" t="inlineStr">
-        <is>
-          <t>Non indicato</t>
-        </is>
-      </c>
-      <c r="V39" s="4" t="n"/>
-      <c r="W39" s="2" t="n"/>
-      <c r="X39" s="2" t="n"/>
-      <c r="Y39" s="3" t="n"/>
-      <c r="Z39" s="3" t="n"/>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>Regno Unito</t>
-        </is>
-      </c>
-      <c r="AB39" s="2" t="inlineStr">
-        <is>
-          <t>Inglese</t>
-        </is>
-      </c>
-      <c r="AC39" s="7" t="inlineStr">
-        <is>
-          <t>https://www.alzheimersresearchuk.org/wp-content/uploads/2026/03/General-Award-Conditions.pdf</t>
-        </is>
-      </c>
-      <c r="AD39" s="3" t="n"/>
-      <c r="AE39" s="4" t="n">
-        <v>46313</v>
-      </c>
-      <c r="AF39" s="4" t="n">
-        <v>46313</v>
-      </c>
-      <c r="AG39" s="2" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>WEB-d9927bbca257</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>Da verificare</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>Non analizzato</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="n"/>
-      <c r="E40" s="3" t="inlineStr">
-        <is>
-          <t>26 09 Vivensa Foundation Excellence Awards guidelines 1</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="n"/>
-      <c r="G40" s="5">
-        <f>IF(F40="","",F40-TODAY())</f>
-        <v/>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>Scadenza da verificare</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>Dunhill Medical Trust</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>Dunhill Medical Trust</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>26 09 Vivensa Foundation Excellence Awards guidelines 1</t>
-        </is>
-      </c>
-      <c r="L40" s="3" t="inlineStr">
-        <is>
-          <t>26 09 Vivensa Foundation Excellence Awards guidelines 1</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>Invecchiamento</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>older adults, ageing</t>
-        </is>
-      </c>
-      <c r="O40" s="3" t="n"/>
-      <c r="P40" s="6" t="n"/>
-      <c r="Q40" s="6" t="n"/>
-      <c r="R40" s="2" t="n"/>
-      <c r="S40" s="2" t="n"/>
-      <c r="T40" s="3" t="inlineStr">
-        <is>
-          <t>Non stimabile – dati insufficienti</t>
-        </is>
-      </c>
-      <c r="U40" s="3" t="inlineStr">
-        <is>
-          <t>Non indicato</t>
-        </is>
-      </c>
-      <c r="V40" s="4" t="n"/>
-      <c r="W40" s="2" t="n"/>
-      <c r="X40" s="2" t="n"/>
-      <c r="Y40" s="3" t="n"/>
-      <c r="Z40" s="3" t="n"/>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>Regno Unito</t>
-        </is>
-      </c>
-      <c r="AB40" s="2" t="inlineStr">
-        <is>
-          <t>Inglese</t>
-        </is>
-      </c>
-      <c r="AC40" s="7" t="inlineStr">
-        <is>
-          <t>https://vivensafoundation.org.uk/wp-content/uploads/2026/09/26-09-Vivensa-Foundation-Excellence-Awards_guidelines-1.pdf</t>
-        </is>
-      </c>
-      <c r="AD40" s="3" t="n"/>
-      <c r="AE40" s="4" t="n">
-        <v>46313</v>
-      </c>
-      <c r="AF40" s="4" t="n">
-        <v>46312</v>
-      </c>
-      <c r="AG40" s="2" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>WEB-4b4b9c8907b2</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>Da verificare</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>Non analizzato</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="n"/>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>25 09 Vivensa Foundation Excellence Awards guidelines FINAL</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="n"/>
-      <c r="G41" s="5">
-        <f>IF(F41="","",F41-TODAY())</f>
-        <v/>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>Scadenza da verificare</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>Dunhill Medical Trust</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>Dunhill Medical Trust</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>25 09 Vivensa Foundation Excellence Awards guidelines FINAL</t>
-        </is>
-      </c>
-      <c r="L41" s="3" t="inlineStr">
-        <is>
-          <t>25 09 Vivensa Foundation Excellence Awards guidelines FINAL</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>Invecchiamento</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>older people, ageing</t>
-        </is>
-      </c>
-      <c r="O41" s="3" t="n"/>
-      <c r="P41" s="6" t="n"/>
-      <c r="Q41" s="6" t="n"/>
-      <c r="R41" s="2" t="n"/>
-      <c r="S41" s="2" t="n"/>
-      <c r="T41" s="3" t="inlineStr">
-        <is>
-          <t>Non stimabile – dati insufficienti</t>
-        </is>
-      </c>
-      <c r="U41" s="3" t="inlineStr">
-        <is>
-          <t>Non indicato</t>
-        </is>
-      </c>
-      <c r="V41" s="4" t="n"/>
-      <c r="W41" s="2" t="n"/>
-      <c r="X41" s="2" t="n"/>
-      <c r="Y41" s="3" t="n"/>
-      <c r="Z41" s="3" t="n"/>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>Regno Unito</t>
-        </is>
-      </c>
-      <c r="AB41" s="2" t="inlineStr">
-        <is>
-          <t>Inglese</t>
-        </is>
-      </c>
-      <c r="AC41" s="7" t="inlineStr">
-        <is>
-          <t>https://vivensafoundation.org.uk/wp-content/uploads/2025/09/25-09-Vivensa-Foundation-Excellence-Awards_guidelines-FINAL.pdf</t>
-        </is>
-      </c>
-      <c r="AD41" s="3" t="n"/>
-      <c r="AE41" s="4" t="n">
-        <v>46313</v>
-      </c>
-      <c r="AF41" s="4" t="n">
-        <v>46312</v>
-      </c>
-      <c r="AG41" s="2" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>WEB-59cf819d69fd</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>Da verificare</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Non analizzato</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="n"/>
-      <c r="E42" s="3" t="inlineStr">
-        <is>
-          <t>Excellence Awards Rising Star self nomination template form</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="n"/>
-      <c r="G42" s="5">
-        <f>IF(F42="","",F42-TODAY())</f>
-        <v/>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>Scadenza da verificare</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>Dunhill Medical Trust</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>Dunhill Medical Trust</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>Excellence Awards Rising Star self nomination template form</t>
-        </is>
-      </c>
-      <c r="L42" s="3" t="inlineStr">
-        <is>
-          <t>Excellence Awards Rising Star self nomination template form</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>Invecchiamento</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>older people, ageing</t>
-        </is>
-      </c>
-      <c r="O42" s="3" t="n"/>
-      <c r="P42" s="6" t="n">
-        <v>120000</v>
-      </c>
-      <c r="Q42" s="6" t="n"/>
-      <c r="R42" s="2" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="S42" s="2" t="n"/>
-      <c r="T42" s="3" t="inlineStr">
-        <is>
-          <t>Non stimabile – dati insufficienti</t>
-        </is>
-      </c>
-      <c r="U42" s="3" t="inlineStr">
-        <is>
-          <t>Non indicato</t>
-        </is>
-      </c>
-      <c r="V42" s="4" t="n"/>
-      <c r="W42" s="2" t="n"/>
-      <c r="X42" s="2" t="n"/>
-      <c r="Y42" s="3" t="n"/>
-      <c r="Z42" s="3" t="n"/>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>Regno Unito</t>
-        </is>
-      </c>
-      <c r="AB42" s="2" t="inlineStr">
-        <is>
-          <t>Inglese</t>
-        </is>
-      </c>
-      <c r="AC42" s="7" t="inlineStr">
-        <is>
-          <t>https://vivensafoundation.org.uk/wp-content/uploads/2026/09/Excellence-Awards_Rising-Star_self-nomination_template-form.pdf</t>
-        </is>
-      </c>
-      <c r="AD42" s="3" t="n"/>
-      <c r="AE42" s="4" t="n">
-        <v>46313</v>
-      </c>
-      <c r="AF42" s="4" t="n">
-        <v>46312</v>
-      </c>
-      <c r="AG42" s="2" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>WEB-b133620a1e26</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>Da verificare</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>Non analizzato</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="n"/>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>Excellence Awards Senior Leader self nomination template form</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="n"/>
-      <c r="G43" s="5">
-        <f>IF(F43="","",F43-TODAY())</f>
-        <v/>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>Scadenza da verificare</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>Dunhill Medical Trust</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>Dunhill Medical Trust</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>Excellence Awards Senior Leader self nomination template form</t>
-        </is>
-      </c>
-      <c r="L43" s="3" t="inlineStr">
-        <is>
-          <t>Excellence Awards Senior Leader self nomination template form</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>Invecchiamento</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t>older people, ageing</t>
-        </is>
-      </c>
-      <c r="O43" s="3" t="n"/>
-      <c r="P43" s="6" t="n">
-        <v>120000</v>
-      </c>
-      <c r="Q43" s="6" t="n"/>
-      <c r="R43" s="2" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="S43" s="2" t="n"/>
-      <c r="T43" s="3" t="inlineStr">
-        <is>
-          <t>Non stimabile – dati insufficienti</t>
-        </is>
-      </c>
-      <c r="U43" s="3" t="inlineStr">
-        <is>
-          <t>Non indicato</t>
-        </is>
-      </c>
-      <c r="V43" s="4" t="n"/>
-      <c r="W43" s="2" t="n"/>
-      <c r="X43" s="2" t="n"/>
-      <c r="Y43" s="3" t="n"/>
-      <c r="Z43" s="3" t="n"/>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>Regno Unito</t>
-        </is>
-      </c>
-      <c r="AB43" s="2" t="inlineStr">
-        <is>
-          <t>Inglese</t>
-        </is>
-      </c>
-      <c r="AC43" s="7" t="inlineStr">
-        <is>
-          <t>https://vivensafoundation.org.uk/wp-content/uploads/2026/09/Excellence-Awards_Senior-Leader_self-nomination_template-form.pdf</t>
-        </is>
-      </c>
-      <c r="AD43" s="3" t="n"/>
-      <c r="AE43" s="4" t="n">
-        <v>46313</v>
-      </c>
-      <c r="AF43" s="4" t="n">
-        <v>46312</v>
-      </c>
-      <c r="AG43" s="2" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>WEB-66dad966a4a2</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>Da verificare</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>Non analizzato</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="n"/>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t>Excellence Awards Team self nomination template form</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="n"/>
-      <c r="G44" s="5">
-        <f>IF(F44="","",F44-TODAY())</f>
-        <v/>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>Scadenza da verificare</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>Dunhill Medical Trust</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>Dunhill Medical Trust</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>Excellence Awards Team self nomination template form</t>
-        </is>
-      </c>
-      <c r="L44" s="3" t="inlineStr">
-        <is>
-          <t>Excellence Awards Team self nomination template form</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>Invecchiamento</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>older people, ageing</t>
-        </is>
-      </c>
-      <c r="O44" s="3" t="n"/>
-      <c r="P44" s="6" t="n">
-        <v>120000</v>
-      </c>
-      <c r="Q44" s="6" t="n"/>
-      <c r="R44" s="2" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="S44" s="2" t="n"/>
-      <c r="T44" s="3" t="inlineStr">
-        <is>
-          <t>Non stimabile – dati insufficienti</t>
-        </is>
-      </c>
-      <c r="U44" s="3" t="inlineStr">
-        <is>
-          <t>Non indicato</t>
-        </is>
-      </c>
-      <c r="V44" s="4" t="n"/>
-      <c r="W44" s="2" t="n"/>
-      <c r="X44" s="2" t="n"/>
-      <c r="Y44" s="3" t="n"/>
-      <c r="Z44" s="3" t="n"/>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>Regno Unito</t>
-        </is>
-      </c>
-      <c r="AB44" s="2" t="inlineStr">
-        <is>
-          <t>Inglese</t>
-        </is>
-      </c>
-      <c r="AC44" s="7" t="inlineStr">
-        <is>
-          <t>https://vivensafoundation.org.uk/wp-content/uploads/2026/09/Excellence-Awards_Team_self-nomination_template-form.pdf</t>
-        </is>
-      </c>
-      <c r="AD44" s="3" t="n"/>
-      <c r="AE44" s="4" t="n">
-        <v>46313</v>
-      </c>
-      <c r="AF44" s="4" t="n">
-        <v>46312</v>
-      </c>
-      <c r="AG44" s="2" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>WEB-a6ef2e9b1346</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>Da verificare</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>Non analizzato</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="n"/>
-      <c r="E45" s="3" t="inlineStr">
-        <is>
-          <t>Excellence Awards Rising Star third party nomination template form</t>
-        </is>
-      </c>
-      <c r="F45" s="4" t="n"/>
-      <c r="G45" s="5">
-        <f>IF(F45="","",F45-TODAY())</f>
-        <v/>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>Scadenza da verificare</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>Dunhill Medical Trust</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>Dunhill Medical Trust</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>Excellence Awards Rising Star third party nomination template form</t>
-        </is>
-      </c>
-      <c r="L45" s="3" t="inlineStr">
-        <is>
-          <t>Excellence Awards Rising Star third party nomination template form</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t>Invecchiamento</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="inlineStr">
-        <is>
-          <t>older people, ageing</t>
-        </is>
-      </c>
-      <c r="O45" s="3" t="n"/>
-      <c r="P45" s="6" t="n">
-        <v>120000</v>
-      </c>
-      <c r="Q45" s="6" t="n"/>
-      <c r="R45" s="2" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="S45" s="2" t="n"/>
-      <c r="T45" s="3" t="inlineStr">
-        <is>
-          <t>Non stimabile – dati insufficienti</t>
-        </is>
-      </c>
-      <c r="U45" s="3" t="inlineStr">
-        <is>
-          <t>Non indicato</t>
-        </is>
-      </c>
-      <c r="V45" s="4" t="n"/>
-      <c r="W45" s="2" t="n"/>
-      <c r="X45" s="2" t="n"/>
-      <c r="Y45" s="3" t="n"/>
-      <c r="Z45" s="3" t="n"/>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>Regno Unito</t>
-        </is>
-      </c>
-      <c r="AB45" s="2" t="inlineStr">
-        <is>
-          <t>Inglese</t>
-        </is>
-      </c>
-      <c r="AC45" s="7" t="inlineStr">
-        <is>
-          <t>https://vivensafoundation.org.uk/wp-content/uploads/2026/09/Excellence-Awards_Rising-Star_third-party-nomination_template-form.pdf</t>
-        </is>
-      </c>
-      <c r="AD45" s="3" t="n"/>
-      <c r="AE45" s="4" t="n">
-        <v>46313</v>
-      </c>
-      <c r="AF45" s="4" t="n">
-        <v>46312</v>
-      </c>
-      <c r="AG45" s="2" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>WEB-fcf6c64e48ec</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>Da verificare</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>Non analizzato</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="n"/>
-      <c r="E46" s="3" t="inlineStr">
-        <is>
-          <t>Excellence Awards Senior Leader third party nomination template form</t>
-        </is>
-      </c>
-      <c r="F46" s="4" t="n"/>
-      <c r="G46" s="5">
-        <f>IF(F46="","",F46-TODAY())</f>
-        <v/>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>Scadenza da verificare</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>Dunhill Medical Trust</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>Dunhill Medical Trust</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>Excellence Awards Senior Leader third party nomination template form</t>
-        </is>
-      </c>
-      <c r="L46" s="3" t="inlineStr">
-        <is>
-          <t>Excellence Awards Senior Leader third party nomination template form</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>Invecchiamento</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="inlineStr">
-        <is>
-          <t>older people, ageing</t>
-        </is>
-      </c>
-      <c r="O46" s="3" t="n"/>
-      <c r="P46" s="6" t="n">
-        <v>120000</v>
-      </c>
-      <c r="Q46" s="6" t="n"/>
-      <c r="R46" s="2" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="S46" s="2" t="n"/>
-      <c r="T46" s="3" t="inlineStr">
-        <is>
-          <t>Non stimabile – dati insufficienti</t>
-        </is>
-      </c>
-      <c r="U46" s="3" t="inlineStr">
-        <is>
-          <t>Non indicato</t>
-        </is>
-      </c>
-      <c r="V46" s="4" t="n"/>
-      <c r="W46" s="2" t="n"/>
-      <c r="X46" s="2" t="n"/>
-      <c r="Y46" s="3" t="n"/>
-      <c r="Z46" s="3" t="n"/>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>Regno Unito</t>
-        </is>
-      </c>
-      <c r="AB46" s="2" t="inlineStr">
-        <is>
-          <t>Inglese</t>
-        </is>
-      </c>
-      <c r="AC46" s="7" t="inlineStr">
-        <is>
-          <t>https://vivensafoundation.org.uk/wp-content/uploads/2026/09/Excellence-Awards_Senior-Leader_third-party-nomination_template-form.pdf</t>
-        </is>
-      </c>
-      <c r="AD46" s="3" t="n"/>
-      <c r="AE46" s="4" t="n">
-        <v>46313</v>
-      </c>
-      <c r="AF46" s="4" t="n">
-        <v>46312</v>
-      </c>
-      <c r="AG46" s="2" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>WEB-8aded4d4999a</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>Da verificare</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>Non analizzato</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="n"/>
-      <c r="E47" s="3" t="inlineStr">
-        <is>
-          <t>Excellence Awards Team third party nomination template form</t>
-        </is>
-      </c>
-      <c r="F47" s="4" t="n"/>
-      <c r="G47" s="5">
-        <f>IF(F47="","",F47-TODAY())</f>
-        <v/>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>Scadenza da verificare</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>Dunhill Medical Trust</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>Dunhill Medical Trust</t>
-        </is>
-      </c>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t>Excellence Awards Team third party nomination template form</t>
-        </is>
-      </c>
-      <c r="L47" s="3" t="inlineStr">
-        <is>
-          <t>Excellence Awards Team third party nomination template form</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr">
-        <is>
-          <t>Invecchiamento</t>
-        </is>
-      </c>
-      <c r="N47" s="2" t="inlineStr">
-        <is>
-          <t>older people, ageing</t>
-        </is>
-      </c>
-      <c r="O47" s="3" t="n"/>
-      <c r="P47" s="6" t="n">
-        <v>120000</v>
-      </c>
-      <c r="Q47" s="6" t="n"/>
-      <c r="R47" s="2" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="S47" s="2" t="n"/>
-      <c r="T47" s="3" t="inlineStr">
-        <is>
-          <t>Non stimabile – dati insufficienti</t>
-        </is>
-      </c>
-      <c r="U47" s="3" t="inlineStr">
-        <is>
-          <t>Non indicato</t>
-        </is>
-      </c>
-      <c r="V47" s="4" t="n"/>
-      <c r="W47" s="2" t="n"/>
-      <c r="X47" s="2" t="n"/>
-      <c r="Y47" s="3" t="n"/>
-      <c r="Z47" s="3" t="n"/>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>Regno Unito</t>
-        </is>
-      </c>
-      <c r="AB47" s="2" t="inlineStr">
-        <is>
-          <t>Inglese</t>
-        </is>
-      </c>
-      <c r="AC47" s="7" t="inlineStr">
-        <is>
-          <t>https://vivensafoundation.org.uk/wp-content/uploads/2026/09/Excellence-Awards_Team_third-party-nomination_template-form.pdf</t>
-        </is>
-      </c>
-      <c r="AD47" s="3" t="n"/>
-      <c r="AE47" s="4" t="n">
-        <v>46313</v>
-      </c>
-      <c r="AF47" s="4" t="n">
-        <v>46312</v>
-      </c>
-      <c r="AG47" s="2" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>WEB-b210a942c4d8</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>Da verificare</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>Non analizzato</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="n"/>
-      <c r="E48" s="3" t="inlineStr">
-        <is>
-          <t>Research Grants</t>
-        </is>
-      </c>
-      <c r="F48" s="4" t="n"/>
-      <c r="G48" s="5">
-        <f>IF(F48="","",F48-TODAY())</f>
-        <v/>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>Scadenza da verificare</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>Foundation for Physical Therapy Research</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>Foundation for Physical Therapy Research</t>
-        </is>
-      </c>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>Research Grants</t>
-        </is>
-      </c>
-      <c r="L48" s="3" t="inlineStr">
-        <is>
-          <t>Research Grants</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr">
-        <is>
-          <t>Invecchiamento, Altre malattie e riabilitazione</t>
-        </is>
-      </c>
-      <c r="N48" s="2" t="inlineStr">
-        <is>
-          <t>geriatr, physical therap</t>
-        </is>
-      </c>
-      <c r="O48" s="3" t="n"/>
-      <c r="P48" s="6" t="n">
-        <v>40000</v>
-      </c>
-      <c r="Q48" s="6" t="n"/>
-      <c r="R48" s="2" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="S48" s="2" t="n"/>
-      <c r="T48" s="3" t="inlineStr">
-        <is>
-          <t>Non stimabile – dati insufficienti</t>
-        </is>
-      </c>
-      <c r="U48" s="3" t="inlineStr">
-        <is>
-          <t>Non indicato</t>
-        </is>
-      </c>
-      <c r="V48" s="4" t="n"/>
-      <c r="W48" s="2" t="n"/>
-      <c r="X48" s="2" t="n"/>
-      <c r="Y48" s="3" t="n"/>
-      <c r="Z48" s="3" t="n"/>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="AB48" s="2" t="inlineStr">
-        <is>
-          <t>Inglese</t>
-        </is>
-      </c>
-      <c r="AC48" s="7" t="inlineStr">
-        <is>
-          <t>https://foundation4pt.org/foundation-funding-opportunities/grants/</t>
-        </is>
-      </c>
-      <c r="AD48" s="3" t="n"/>
-      <c r="AE48" s="4" t="n">
-        <v>46313</v>
-      </c>
-      <c r="AF48" s="4" t="n">
-        <v>46312</v>
-      </c>
-      <c r="AG48" s="2" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>WEB-a5fef5cb647c</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>Da verificare</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>Non analizzato</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="n"/>
-      <c r="E49" s="3" t="inlineStr">
-        <is>
-          <t>Application Review Process</t>
-        </is>
-      </c>
-      <c r="F49" s="4" t="n"/>
-      <c r="G49" s="5">
-        <f>IF(F49="","",F49-TODAY())</f>
-        <v/>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>Scadenza da verificare</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>Foundation for Physical Therapy Research</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>Foundation for Physical Therapy Research</t>
-        </is>
-      </c>
-      <c r="K49" s="2" t="inlineStr">
-        <is>
-          <t>Application Review Process</t>
-        </is>
-      </c>
-      <c r="L49" s="3" t="inlineStr">
-        <is>
-          <t>Application Review Process</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr">
-        <is>
-          <t>Altre malattie e riabilitazione</t>
-        </is>
-      </c>
-      <c r="N49" s="2" t="inlineStr">
-        <is>
-          <t>rehabilitat, physical therap, occupational therap</t>
-        </is>
-      </c>
-      <c r="O49" s="3" t="n"/>
-      <c r="P49" s="6" t="n">
-        <v>40000</v>
-      </c>
-      <c r="Q49" s="6" t="n"/>
-      <c r="R49" s="2" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="S49" s="2" t="n"/>
-      <c r="T49" s="3" t="inlineStr">
-        <is>
-          <t>Non stimabile – dati insufficienti</t>
-        </is>
-      </c>
-      <c r="U49" s="3" t="inlineStr">
-        <is>
-          <t>Non indicato</t>
-        </is>
-      </c>
-      <c r="V49" s="4" t="n"/>
-      <c r="W49" s="2" t="n"/>
-      <c r="X49" s="2" t="n"/>
-      <c r="Y49" s="3" t="n"/>
-      <c r="Z49" s="3" t="n"/>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="AB49" s="2" t="inlineStr">
-        <is>
-          <t>Inglese</t>
-        </is>
-      </c>
-      <c r="AC49" s="7" t="inlineStr">
-        <is>
-          <t>https://foundation4pt.org/foundation-funding-opportunities/application-review-process/</t>
-        </is>
-      </c>
-      <c r="AD49" s="3" t="n"/>
-      <c r="AE49" s="4" t="n">
-        <v>46313</v>
-      </c>
-      <c r="AF49" s="4" t="n">
-        <v>46312</v>
-      </c>
-      <c r="AG49" s="2" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>WEB-fbb84ea0427d</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>Da verificare</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>Non analizzato</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="n"/>
-      <c r="E50" s="3" t="inlineStr">
-        <is>
-          <t>2018 FPTR Pediatric Grant Recipient Studies Cerebral Palsy Interventions in Early Infancy</t>
-        </is>
-      </c>
-      <c r="F50" s="4" t="n"/>
-      <c r="G50" s="5">
-        <f>IF(F50="","",F50-TODAY())</f>
-        <v/>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>Scadenza da verificare</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>Foundation for Physical Therapy Research</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>Foundation for Physical Therapy Research</t>
-        </is>
-      </c>
-      <c r="K50" s="2" t="inlineStr">
-        <is>
-          <t>2018 FPTR Pediatric Grant Recipient Studies Cerebral Palsy Interventions in Early Infancy</t>
-        </is>
-      </c>
-      <c r="L50" s="3" t="inlineStr">
-        <is>
-          <t>2018 FPTR Pediatric Grant Recipient Studies Cerebral Palsy Interventions in Early Infancy</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr">
-        <is>
-          <t>Tecnologie riabilitazione, Altre malattie e riabilitazione</t>
-        </is>
-      </c>
-      <c r="N50" s="2" t="inlineStr">
-        <is>
-          <t>telerehabilit, rehabilitat, physical therap, cerebral palsy</t>
-        </is>
-      </c>
-      <c r="O50" s="3" t="n"/>
-      <c r="P50" s="6" t="n">
-        <v>40000</v>
-      </c>
-      <c r="Q50" s="6" t="n"/>
-      <c r="R50" s="2" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="S50" s="2" t="n"/>
-      <c r="T50" s="3" t="inlineStr">
-        <is>
-          <t>Non stimabile – dati insufficienti</t>
-        </is>
-      </c>
-      <c r="U50" s="3" t="inlineStr">
-        <is>
-          <t>Non indicato</t>
-        </is>
-      </c>
-      <c r="V50" s="4" t="n"/>
-      <c r="W50" s="2" t="n"/>
-      <c r="X50" s="2" t="n"/>
-      <c r="Y50" s="3" t="n"/>
-      <c r="Z50" s="3" t="n"/>
-      <c r="AA50" s="2" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="AB50" s="2" t="inlineStr">
-        <is>
-          <t>Inglese</t>
-        </is>
-      </c>
-      <c r="AC50" s="7" t="inlineStr">
-        <is>
-          <t>https://foundation4pt.org/stories/2018-fptr-pediatric-grant-recipient-studies-cerebral-palsy-interventions-in-early-infancy/</t>
-        </is>
-      </c>
-      <c r="AD50" s="3" t="n"/>
-      <c r="AE50" s="4" t="n">
-        <v>46313</v>
-      </c>
-      <c r="AF50" s="4" t="n">
-        <v>46312</v>
-      </c>
-      <c r="AG50" s="2" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>WEB-b53bf29d9b73</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>Da verificare</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>Non analizzato</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="n"/>
-      <c r="E51" s="3" t="inlineStr">
-        <is>
-          <t>The Foundation for Physical Therapy Research Announces 2026 Service Award Recipients</t>
-        </is>
-      </c>
-      <c r="F51" s="4" t="n"/>
-      <c r="G51" s="5">
-        <f>IF(F51="","",F51-TODAY())</f>
-        <v/>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>Scadenza da verificare</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>Foundation for Physical Therapy Research</t>
-        </is>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>Foundation for Physical Therapy Research</t>
-        </is>
-      </c>
-      <c r="K51" s="2" t="inlineStr">
-        <is>
-          <t>The Foundation for Physical Therapy Research Announces 2026 Service Award Recipients</t>
-        </is>
-      </c>
-      <c r="L51" s="3" t="inlineStr">
-        <is>
-          <t>The Foundation for Physical Therapy Research Announces 2026 Service Award Recipients</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr">
-        <is>
-          <t>Altre malattie e riabilitazione</t>
-        </is>
-      </c>
-      <c r="N51" s="2" t="inlineStr">
-        <is>
-          <t>physical therap</t>
-        </is>
-      </c>
-      <c r="O51" s="3" t="n"/>
-      <c r="P51" s="6" t="n"/>
-      <c r="Q51" s="6" t="n"/>
-      <c r="R51" s="2" t="n"/>
-      <c r="S51" s="2" t="n"/>
-      <c r="T51" s="3" t="inlineStr">
-        <is>
-          <t>Non stimabile – dati insufficienti</t>
-        </is>
-      </c>
-      <c r="U51" s="3" t="inlineStr">
-        <is>
-          <t>Non indicato</t>
-        </is>
-      </c>
-      <c r="V51" s="4" t="n"/>
-      <c r="W51" s="2" t="n"/>
-      <c r="X51" s="2" t="n"/>
-      <c r="Y51" s="3" t="n"/>
-      <c r="Z51" s="3" t="n"/>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="AB51" s="2" t="inlineStr">
-        <is>
-          <t>Inglese</t>
-        </is>
-      </c>
-      <c r="AC51" s="7" t="inlineStr">
-        <is>
-          <t>https://foundation4pt.org/2026-service-award-recipients/</t>
-        </is>
-      </c>
-      <c r="AD51" s="3" t="n"/>
-      <c r="AE51" s="4" t="n">
-        <v>46313</v>
-      </c>
-      <c r="AF51" s="4" t="n">
-        <v>46312</v>
-      </c>
-      <c r="AG51" s="2" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>WEB-aead8398cbba</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>Da verificare</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>Non analizzato</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="n"/>
-      <c r="E52" s="3" t="inlineStr">
-        <is>
-          <t>Comparative Effectiveness of Telehealth vs in-Person Delivery of the Supporting Play Exploration and Early Development Intervention in Underserved Urban and Rural Populations</t>
-        </is>
-      </c>
-      <c r="F52" s="4" t="n"/>
-      <c r="G52" s="5">
-        <f>IF(F52="","",F52-TODAY())</f>
-        <v/>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>Scadenza da verificare</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>Foundation for Physical Therapy Research</t>
-        </is>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>Foundation for Physical Therapy Research</t>
-        </is>
-      </c>
-      <c r="K52" s="2" t="inlineStr">
-        <is>
-          <t>Comparative Effectiveness of Telehealth vs in-Person Delivery of the Supporting Play Exploration and Early Development Intervention in Underserved Urban and Rural Populations</t>
-        </is>
-      </c>
-      <c r="L52" s="3" t="inlineStr">
-        <is>
-          <t>Comparative Effectiveness of Telehealth vs in-Person Delivery of the Supporting Play Exploration and Early Development Intervention in Underserved Urban and Rural Populations</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr">
-        <is>
-          <t>Tecnologie riabilitazione, Altre malattie e riabilitazione</t>
-        </is>
-      </c>
-      <c r="N52" s="2" t="inlineStr">
-        <is>
-          <t>telerehabilit, physical therap</t>
-        </is>
-      </c>
-      <c r="O52" s="3" t="n"/>
-      <c r="P52" s="6" t="n">
-        <v>200000</v>
-      </c>
-      <c r="Q52" s="6" t="n"/>
-      <c r="R52" s="2" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="S52" s="2" t="n"/>
-      <c r="T52" s="3" t="inlineStr">
-        <is>
-          <t>Non stimabile – dati insufficienti</t>
-        </is>
-      </c>
-      <c r="U52" s="3" t="inlineStr">
-        <is>
-          <t>Non indicato</t>
-        </is>
-      </c>
-      <c r="V52" s="4" t="n"/>
-      <c r="W52" s="2" t="n"/>
-      <c r="X52" s="2" t="n"/>
-      <c r="Y52" s="3" t="n"/>
-      <c r="Z52" s="3" t="n"/>
-      <c r="AA52" s="2" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="AB52" s="2" t="inlineStr">
-        <is>
-          <t>Inglese</t>
-        </is>
-      </c>
-      <c r="AC52" s="7" t="inlineStr">
-        <is>
-          <t>https://foundation4pt.org/funding-database/comparative-effectiveness-of-telehealth-vs-in-person-delivery-of-the-supporting-play-exploration-and-early-development-intervention-in-underserved-urban-and-rural-populations/</t>
-        </is>
-      </c>
-      <c r="AD52" s="3" t="n"/>
-      <c r="AE52" s="4" t="n">
-        <v>46313</v>
-      </c>
-      <c r="AF52" s="4" t="n">
-        <v>46312</v>
-      </c>
-      <c r="AG52" s="2" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>WEB-a48880d5e152</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>Da verificare</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>Non analizzato</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="n"/>
-      <c r="E53" s="3" t="inlineStr">
-        <is>
-          <t>Brain-Heart-Behavior Connections: Understanding Associations Between Parent-Infant Relationships, Infant Neurodevelopment, and Parent Neurophysiology</t>
-        </is>
-      </c>
-      <c r="F53" s="4" t="n"/>
-      <c r="G53" s="5">
-        <f>IF(F53="","",F53-TODAY())</f>
-        <v/>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>Scadenza da verificare</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>Foundation for Physical Therapy Research</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>Foundation for Physical Therapy Research</t>
-        </is>
-      </c>
-      <c r="K53" s="2" t="inlineStr">
-        <is>
-          <t>Brain-Heart-Behavior Connections: Understanding Associations Between Parent-Infant Relationships, Infant Neurodevelopment, and Parent Neurophysiology</t>
-        </is>
-      </c>
-      <c r="L53" s="3" t="inlineStr">
-        <is>
-          <t>Brain-Heart-Behavior Connections: Understanding Associations Between Parent-Infant Relationships, Infant Neurodevelopment, and Parent Neurophysiology</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr">
-        <is>
-          <t>Altre malattie e riabilitazione</t>
-        </is>
-      </c>
-      <c r="N53" s="2" t="inlineStr">
-        <is>
-          <t>physical therap</t>
-        </is>
-      </c>
-      <c r="O53" s="3" t="n"/>
-      <c r="P53" s="6" t="n">
-        <v>40000</v>
-      </c>
-      <c r="Q53" s="6" t="n"/>
-      <c r="R53" s="2" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="S53" s="2" t="n"/>
-      <c r="T53" s="3" t="inlineStr">
-        <is>
-          <t>Non stimabile – dati insufficienti</t>
-        </is>
-      </c>
-      <c r="U53" s="3" t="inlineStr">
-        <is>
-          <t>Non indicato</t>
-        </is>
-      </c>
-      <c r="V53" s="4" t="n"/>
-      <c r="W53" s="2" t="n"/>
-      <c r="X53" s="2" t="n"/>
-      <c r="Y53" s="3" t="n"/>
-      <c r="Z53" s="3" t="n"/>
-      <c r="AA53" s="2" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="AB53" s="2" t="inlineStr">
-        <is>
-          <t>Inglese</t>
-        </is>
-      </c>
-      <c r="AC53" s="7" t="inlineStr">
-        <is>
-          <t>https://foundation4pt.org/funding-database/brain-heart-behavior-connections-understanding-associations-between-parent-infant-relationships-infant-neurodevelopment-and-parent-neurophysiology/</t>
-        </is>
-      </c>
-      <c r="AD53" s="3" t="n"/>
-      <c r="AE53" s="4" t="n">
-        <v>46313</v>
-      </c>
-      <c r="AF53" s="4" t="n">
-        <v>46312</v>
-      </c>
-      <c r="AG53" s="2" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>WEB-67c2739330d5</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>Da verificare</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>Non analizzato</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="n"/>
-      <c r="E54" s="3" t="inlineStr">
-        <is>
-          <t>Supraspinatus Muscle Response to Exercise in Individuals With Rotator Cuff Tears who Failed Physical Therapy</t>
-        </is>
-      </c>
-      <c r="F54" s="4" t="n"/>
-      <c r="G54" s="5">
-        <f>IF(F54="","",F54-TODAY())</f>
-        <v/>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>Scadenza da verificare</t>
-        </is>
-      </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>Foundation for Physical Therapy Research</t>
-        </is>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>Foundation for Physical Therapy Research</t>
-        </is>
-      </c>
-      <c r="K54" s="2" t="inlineStr">
-        <is>
-          <t>Supraspinatus Muscle Response to Exercise in Individuals With Rotator Cuff Tears who Failed Physical Therapy</t>
-        </is>
-      </c>
-      <c r="L54" s="3" t="inlineStr">
-        <is>
-          <t>Supraspinatus Muscle Response to Exercise in Individuals With Rotator Cuff Tears who Failed Physical Therapy</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr">
-        <is>
-          <t>Altre malattie e riabilitazione</t>
-        </is>
-      </c>
-      <c r="N54" s="2" t="inlineStr">
-        <is>
-          <t>physical therap</t>
-        </is>
-      </c>
-      <c r="O54" s="3" t="n"/>
-      <c r="P54" s="6" t="n">
-        <v>40000</v>
-      </c>
-      <c r="Q54" s="6" t="n"/>
-      <c r="R54" s="2" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="S54" s="2" t="n"/>
-      <c r="T54" s="3" t="inlineStr">
-        <is>
-          <t>Non stimabile – dati insufficienti</t>
-        </is>
-      </c>
-      <c r="U54" s="3" t="inlineStr">
-        <is>
-          <t>Non indicato</t>
-        </is>
-      </c>
-      <c r="V54" s="4" t="n"/>
-      <c r="W54" s="2" t="n"/>
-      <c r="X54" s="2" t="n"/>
-      <c r="Y54" s="3" t="n"/>
-      <c r="Z54" s="3" t="n"/>
-      <c r="AA54" s="2" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="AB54" s="2" t="inlineStr">
-        <is>
-          <t>Inglese</t>
-        </is>
-      </c>
-      <c r="AC54" s="7" t="inlineStr">
-        <is>
-          <t>https://foundation4pt.org/funding-database/supraspinatus-muscle-response-to-exercise-in-individuals-with-rotator-cuff-tears-who-failed-physical-therapy/</t>
-        </is>
-      </c>
-      <c r="AD54" s="3" t="n"/>
-      <c r="AE54" s="4" t="n">
-        <v>46313</v>
-      </c>
-      <c r="AF54" s="4" t="n">
-        <v>46312</v>
-      </c>
-      <c r="AG54" s="2" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>WEB-eaf7618a8796</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>Da verificare</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>Non analizzato</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="n"/>
-      <c r="E55" s="3" t="inlineStr">
-        <is>
-          <t>Defining and Evaluating the “Integrated Practice Unit” as a Model for Acute Care Physical Therapy Delivery</t>
-        </is>
-      </c>
-      <c r="F55" s="4" t="n"/>
-      <c r="G55" s="5">
-        <f>IF(F55="","",F55-TODAY())</f>
-        <v/>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>Scadenza da verificare</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>Foundation for Physical Therapy Research</t>
-        </is>
-      </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>Foundation for Physical Therapy Research</t>
-        </is>
-      </c>
-      <c r="K55" s="2" t="inlineStr">
-        <is>
-          <t>Defining and Evaluating the “Integrated Practice Unit” as a Model for Acute Care Physical Therapy Delivery</t>
-        </is>
-      </c>
-      <c r="L55" s="3" t="inlineStr">
-        <is>
-          <t>Defining and Evaluating the “Integrated Practice Unit” as a Model for Acute Care Physical Therapy Delivery</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr">
-        <is>
-          <t>Altre malattie e riabilitazione</t>
-        </is>
-      </c>
-      <c r="N55" s="2" t="inlineStr">
-        <is>
-          <t>physical therap</t>
-        </is>
-      </c>
-      <c r="O55" s="3" t="n"/>
-      <c r="P55" s="6" t="n">
-        <v>80000</v>
-      </c>
-      <c r="Q55" s="6" t="n"/>
-      <c r="R55" s="2" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="S55" s="2" t="n"/>
-      <c r="T55" s="3" t="inlineStr">
-        <is>
-          <t>Non stimabile – dati insufficienti</t>
-        </is>
-      </c>
-      <c r="U55" s="3" t="inlineStr">
-        <is>
-          <t>Non indicato</t>
-        </is>
-      </c>
-      <c r="V55" s="4" t="n"/>
-      <c r="W55" s="2" t="n"/>
-      <c r="X55" s="2" t="n"/>
-      <c r="Y55" s="3" t="n"/>
-      <c r="Z55" s="3" t="n"/>
-      <c r="AA55" s="2" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="AB55" s="2" t="inlineStr">
-        <is>
-          <t>Inglese</t>
-        </is>
-      </c>
-      <c r="AC55" s="7" t="inlineStr">
-        <is>
-          <t>https://foundation4pt.org/funding-database/defining-and-evaluating-the-integrated-practice-unit-as-a-model-for-acute-care-physical-therapy-delivery/</t>
-        </is>
-      </c>
-      <c r="AD55" s="3" t="n"/>
-      <c r="AE55" s="4" t="n">
-        <v>46313</v>
-      </c>
-      <c r="AF55" s="4" t="n">
-        <v>46312</v>
-      </c>
-      <c r="AG55" s="2" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>WEB-22ffc111a27f</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>Da verificare</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>Non analizzato</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="n"/>
-      <c r="E56" s="3" t="inlineStr">
-        <is>
-          <t>Intensive Physical Therapy for Young Children With Ventricular Assist Devices Prior to Heart Transplant</t>
-        </is>
-      </c>
-      <c r="F56" s="4" t="n"/>
-      <c r="G56" s="5">
-        <f>IF(F56="","",F56-TODAY())</f>
-        <v/>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>Scadenza da verificare</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>Foundation for Physical Therapy Research</t>
-        </is>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>Foundation for Physical Therapy Research</t>
-        </is>
-      </c>
-      <c r="K56" s="2" t="inlineStr">
-        <is>
-          <t>Intensive Physical Therapy for Young Children With Ventricular Assist Devices Prior to Heart Transplant</t>
-        </is>
-      </c>
-      <c r="L56" s="3" t="inlineStr">
-        <is>
-          <t>Intensive Physical Therapy for Young Children With Ventricular Assist Devices Prior to Heart Transplant</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr">
-        <is>
-          <t>Altre malattie e riabilitazione</t>
-        </is>
-      </c>
-      <c r="N56" s="2" t="inlineStr">
-        <is>
-          <t>physical therap</t>
-        </is>
-      </c>
-      <c r="O56" s="3" t="n"/>
-      <c r="P56" s="6" t="n">
-        <v>40000</v>
-      </c>
-      <c r="Q56" s="6" t="n"/>
-      <c r="R56" s="2" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="S56" s="2" t="n"/>
-      <c r="T56" s="3" t="inlineStr">
-        <is>
-          <t>Non stimabile – dati insufficienti</t>
-        </is>
-      </c>
-      <c r="U56" s="3" t="inlineStr">
-        <is>
-          <t>Non indicato</t>
-        </is>
-      </c>
-      <c r="V56" s="4" t="n"/>
-      <c r="W56" s="2" t="n"/>
-      <c r="X56" s="2" t="n"/>
-      <c r="Y56" s="3" t="n"/>
-      <c r="Z56" s="3" t="n"/>
-      <c r="AA56" s="2" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="AB56" s="2" t="inlineStr">
-        <is>
-          <t>Inglese</t>
-        </is>
-      </c>
-      <c r="AC56" s="7" t="inlineStr">
-        <is>
-          <t>https://foundation4pt.org/funding-database/intensive-physical-therapy-for-young-children-with-ventricular-assist-devices-prior-to-heart-transplant/</t>
-        </is>
-      </c>
-      <c r="AD56" s="3" t="n"/>
-      <c r="AE56" s="4" t="n">
-        <v>46313</v>
-      </c>
-      <c r="AF56" s="4" t="n">
-        <v>46312</v>
-      </c>
-      <c r="AG56" s="2" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>WEB-a4357f8df33d</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>Da verificare</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>Non analizzato</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="n"/>
-      <c r="E57" s="3" t="inlineStr">
-        <is>
-          <t>Cost-Effectiveness of Telerehabilitation for Individuals With Temporomandibular Disorders</t>
-        </is>
-      </c>
-      <c r="F57" s="4" t="n"/>
-      <c r="G57" s="5">
-        <f>IF(F57="","",F57-TODAY())</f>
-        <v/>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>Scadenza da verificare</t>
-        </is>
-      </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>Foundation for Physical Therapy Research</t>
-        </is>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>Foundation for Physical Therapy Research</t>
-        </is>
-      </c>
-      <c r="K57" s="2" t="inlineStr">
-        <is>
-          <t>Cost-Effectiveness of Telerehabilitation for Individuals With Temporomandibular Disorders</t>
-        </is>
-      </c>
-      <c r="L57" s="3" t="inlineStr">
-        <is>
-          <t>Cost-Effectiveness of Telerehabilitation for Individuals With Temporomandibular Disorders</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr">
-        <is>
-          <t>Tecnologie riabilitazione, Altre malattie e riabilitazione</t>
-        </is>
-      </c>
-      <c r="N57" s="2" t="inlineStr">
-        <is>
-          <t>telerehabilit, rehabilitat, physical therap, disabilit</t>
-        </is>
-      </c>
-      <c r="O57" s="3" t="n"/>
-      <c r="P57" s="6" t="n">
-        <v>40000</v>
-      </c>
-      <c r="Q57" s="6" t="n"/>
-      <c r="R57" s="2" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="S57" s="2" t="n"/>
-      <c r="T57" s="3" t="inlineStr">
-        <is>
-          <t>Non stimabile – dati insufficienti</t>
-        </is>
-      </c>
-      <c r="U57" s="3" t="inlineStr">
-        <is>
-          <t>Non indicato</t>
-        </is>
-      </c>
-      <c r="V57" s="4" t="n"/>
-      <c r="W57" s="2" t="n"/>
-      <c r="X57" s="2" t="n"/>
-      <c r="Y57" s="3" t="n"/>
-      <c r="Z57" s="3" t="n"/>
-      <c r="AA57" s="2" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="AB57" s="2" t="inlineStr">
-        <is>
-          <t>Inglese</t>
-        </is>
-      </c>
-      <c r="AC57" s="7" t="inlineStr">
-        <is>
-          <t>https://foundation4pt.org/funding-database/cost-effectiveness-of-telerehabilitation-for-individuals-with-temporomandibular-disorders/</t>
-        </is>
-      </c>
-      <c r="AD57" s="3" t="n"/>
-      <c r="AE57" s="4" t="n">
-        <v>46313</v>
-      </c>
-      <c r="AF57" s="4" t="n">
-        <v>46312</v>
-      </c>
-      <c r="AG57" s="2" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>WEB-89ea11473f48</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>Da verificare</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>Non analizzato</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="n"/>
-      <c r="E58" s="3" t="inlineStr">
-        <is>
-          <t>Rehabilitation-based Approaches to Prevent Mechanical Ventilation-Induced Breathing Dysfunction</t>
-        </is>
-      </c>
-      <c r="F58" s="4" t="n"/>
-      <c r="G58" s="5">
-        <f>IF(F58="","",F58-TODAY())</f>
-        <v/>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>Scadenza da verificare</t>
-        </is>
-      </c>
-      <c r="I58" s="2" t="inlineStr">
-        <is>
-          <t>Foundation for Physical Therapy Research</t>
-        </is>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>Foundation for Physical Therapy Research</t>
-        </is>
-      </c>
-      <c r="K58" s="2" t="inlineStr">
-        <is>
-          <t>Rehabilitation-based Approaches to Prevent Mechanical Ventilation-Induced Breathing Dysfunction</t>
-        </is>
-      </c>
-      <c r="L58" s="3" t="inlineStr">
-        <is>
-          <t>Rehabilitation-based Approaches to Prevent Mechanical Ventilation-Induced Breathing Dysfunction</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr">
-        <is>
-          <t>Altre malattie e riabilitazione</t>
-        </is>
-      </c>
-      <c r="N58" s="2" t="inlineStr">
-        <is>
-          <t>rehabilitat, physical therap</t>
-        </is>
-      </c>
-      <c r="O58" s="3" t="n"/>
-      <c r="P58" s="6" t="n">
-        <v>40000</v>
-      </c>
-      <c r="Q58" s="6" t="n"/>
-      <c r="R58" s="2" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="S58" s="2" t="n"/>
-      <c r="T58" s="3" t="inlineStr">
-        <is>
-          <t>Non stimabile – dati insufficienti</t>
-        </is>
-      </c>
-      <c r="U58" s="3" t="inlineStr">
-        <is>
-          <t>Non indicato</t>
-        </is>
-      </c>
-      <c r="V58" s="4" t="n"/>
-      <c r="W58" s="2" t="n"/>
-      <c r="X58" s="2" t="n"/>
-      <c r="Y58" s="3" t="n"/>
-      <c r="Z58" s="3" t="n"/>
-      <c r="AA58" s="2" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="AB58" s="2" t="inlineStr">
-        <is>
-          <t>Inglese</t>
-        </is>
-      </c>
-      <c r="AC58" s="7" t="inlineStr">
-        <is>
-          <t>https://foundation4pt.org/funding-database/rehabilitation-based-approaches-to-prevent-mechanical-ventilation-induced-breathing-dysfunction/</t>
-        </is>
-      </c>
-      <c r="AD58" s="3" t="n"/>
-      <c r="AE58" s="4" t="n">
-        <v>46313</v>
-      </c>
-      <c r="AF58" s="4" t="n">
-        <v>46312</v>
-      </c>
-      <c r="AG58" s="2" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>WEB-8d514510f24f</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>Da verificare</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>Non analizzato</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="n"/>
-      <c r="E59" s="3" t="inlineStr">
-        <is>
-          <t>Effects of Noxious vs Non-Noxious Knee Mobilization on Cortical Activity in Chronic Joint Pain</t>
-        </is>
-      </c>
-      <c r="F59" s="4" t="n"/>
-      <c r="G59" s="5">
-        <f>IF(F59="","",F59-TODAY())</f>
-        <v/>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>Scadenza da verificare</t>
-        </is>
-      </c>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>Foundation for Physical Therapy Research</t>
-        </is>
-      </c>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>Foundation for Physical Therapy Research</t>
-        </is>
-      </c>
-      <c r="K59" s="2" t="inlineStr">
-        <is>
-          <t>Effects of Noxious vs Non-Noxious Knee Mobilization on Cortical Activity in Chronic Joint Pain</t>
-        </is>
-      </c>
-      <c r="L59" s="3" t="inlineStr">
-        <is>
-          <t>Effects of Noxious vs Non-Noxious Knee Mobilization on Cortical Activity in Chronic Joint Pain</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr">
-        <is>
-          <t>Altre malattie e riabilitazione</t>
-        </is>
-      </c>
-      <c r="N59" s="2" t="inlineStr">
-        <is>
-          <t>physical therap, chronic pain</t>
-        </is>
-      </c>
-      <c r="O59" s="3" t="n"/>
-      <c r="P59" s="6" t="n">
-        <v>200000</v>
-      </c>
-      <c r="Q59" s="6" t="n"/>
-      <c r="R59" s="2" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="S59" s="2" t="n"/>
-      <c r="T59" s="3" t="inlineStr">
-        <is>
-          <t>Non stimabile – dati insufficienti</t>
-        </is>
-      </c>
-      <c r="U59" s="3" t="inlineStr">
-        <is>
-          <t>Non indicato</t>
-        </is>
-      </c>
-      <c r="V59" s="4" t="n"/>
-      <c r="W59" s="2" t="n"/>
-      <c r="X59" s="2" t="n"/>
-      <c r="Y59" s="3" t="n"/>
-      <c r="Z59" s="3" t="n"/>
-      <c r="AA59" s="2" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="AB59" s="2" t="inlineStr">
-        <is>
-          <t>Inglese</t>
-        </is>
-      </c>
-      <c r="AC59" s="7" t="inlineStr">
-        <is>
-          <t>https://foundation4pt.org/funding-database/effects-of-noxious-vs-non-noxious-knee-mobilization-on-cortical-activity-in-chronic-joint-pain/</t>
-        </is>
-      </c>
-      <c r="AD59" s="3" t="n"/>
-      <c r="AE59" s="4" t="n">
-        <v>46313</v>
-      </c>
-      <c r="AF59" s="4" t="n">
-        <v>46312</v>
-      </c>
-      <c r="AG59" s="2" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>WEB-1987665eca09</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>Da verificare</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>Non analizzato</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="n"/>
-      <c r="E60" s="3" t="inlineStr">
-        <is>
-          <t>Balance Training With Restricted Vision: Implication for Fall Prevention in Older Adults (A Pilot Study)</t>
-        </is>
-      </c>
-      <c r="F60" s="4" t="n"/>
-      <c r="G60" s="5">
-        <f>IF(F60="","",F60-TODAY())</f>
-        <v/>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>Scadenza da verificare</t>
-        </is>
-      </c>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t>Foundation for Physical Therapy Research</t>
-        </is>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>Foundation for Physical Therapy Research</t>
-        </is>
-      </c>
-      <c r="K60" s="2" t="inlineStr">
-        <is>
-          <t>Balance Training With Restricted Vision: Implication for Fall Prevention in Older Adults (A Pilot Study)</t>
-        </is>
-      </c>
-      <c r="L60" s="3" t="inlineStr">
-        <is>
-          <t>Balance Training With Restricted Vision: Implication for Fall Prevention in Older Adults (A Pilot Study)</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr">
-        <is>
-          <t>Invecchiamento, Tecnologie riabilitazione</t>
-        </is>
-      </c>
-      <c r="N60" s="2" t="inlineStr">
-        <is>
-          <t>fall prevention, older adults, aging, gait, rehabilitat, physical therap</t>
-        </is>
-      </c>
-      <c r="O60" s="3" t="n"/>
-      <c r="P60" s="6" t="n">
-        <v>40000</v>
-      </c>
-      <c r="Q60" s="6" t="n"/>
-      <c r="R60" s="2" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="S60" s="2" t="n"/>
-      <c r="T60" s="3" t="inlineStr">
-        <is>
-          <t>Non stimabile – dati insufficienti</t>
-        </is>
-      </c>
-      <c r="U60" s="3" t="inlineStr">
-        <is>
-          <t>Non indicato</t>
-        </is>
-      </c>
-      <c r="V60" s="4" t="n"/>
-      <c r="W60" s="2" t="n"/>
-      <c r="X60" s="2" t="n"/>
-      <c r="Y60" s="3" t="n"/>
-      <c r="Z60" s="3" t="n"/>
-      <c r="AA60" s="2" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="AB60" s="2" t="inlineStr">
-        <is>
-          <t>Inglese</t>
-        </is>
-      </c>
-      <c r="AC60" s="7" t="inlineStr">
-        <is>
-          <t>https://foundation4pt.org/funding-database/balance-training-with-restricted-vision-implication-for-fall-prevention-in-older-adults-a-pilot-study/</t>
-        </is>
-      </c>
-      <c r="AD60" s="3" t="n"/>
-      <c r="AE60" s="4" t="n">
-        <v>46313</v>
-      </c>
-      <c r="AF60" s="4" t="n">
-        <v>46312</v>
-      </c>
-      <c r="AG60" s="2" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>WEB-f06806eb9814</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>Da verificare</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>Non analizzato</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="n"/>
-      <c r="E61" s="3" t="inlineStr">
-        <is>
-          <t>Past Foundation Funding Recipients Recognized by 2025 APTA Honors &amp; Awards Program</t>
-        </is>
-      </c>
-      <c r="F61" s="4" t="n"/>
-      <c r="G61" s="5">
-        <f>IF(F61="","",F61-TODAY())</f>
-        <v/>
-      </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>Scadenza da verificare</t>
-        </is>
-      </c>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>Foundation for Physical Therapy Research</t>
-        </is>
-      </c>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>Foundation for Physical Therapy Research</t>
-        </is>
-      </c>
-      <c r="K61" s="2" t="inlineStr">
-        <is>
-          <t>Past Foundation Funding Recipients Recognized by 2025 APTA Honors &amp; Awards Program</t>
-        </is>
-      </c>
-      <c r="L61" s="3" t="inlineStr">
-        <is>
-          <t>Past Foundation Funding Recipients Recognized by 2025 APTA Honors &amp; Awards Program</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr">
-        <is>
-          <t>Altre malattie e riabilitazione</t>
-        </is>
-      </c>
-      <c r="N61" s="2" t="inlineStr">
-        <is>
-          <t>physical therap</t>
-        </is>
-      </c>
-      <c r="O61" s="3" t="n"/>
-      <c r="P61" s="6" t="n">
-        <v>307500</v>
-      </c>
-      <c r="Q61" s="6" t="n"/>
-      <c r="R61" s="2" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="S61" s="2" t="n"/>
-      <c r="T61" s="3" t="inlineStr">
-        <is>
-          <t>Non stimabile – dati insufficienti</t>
-        </is>
-      </c>
-      <c r="U61" s="3" t="inlineStr">
-        <is>
-          <t>Non indicato</t>
-        </is>
-      </c>
-      <c r="V61" s="4" t="n"/>
-      <c r="W61" s="2" t="n"/>
-      <c r="X61" s="2" t="n"/>
-      <c r="Y61" s="3" t="n"/>
-      <c r="Z61" s="3" t="n"/>
-      <c r="AA61" s="2" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="AB61" s="2" t="inlineStr">
-        <is>
-          <t>Inglese</t>
-        </is>
-      </c>
-      <c r="AC61" s="7" t="inlineStr">
-        <is>
-          <t>https://foundation4pt.org/past-foundation-funding-recipients-recognized-by-2025-apta-honors-awards-program-3/</t>
-        </is>
-      </c>
-      <c r="AD61" s="3" t="n"/>
-      <c r="AE61" s="4" t="n">
-        <v>46313</v>
-      </c>
-      <c r="AF61" s="4" t="n">
-        <v>46312</v>
-      </c>
-      <c r="AG61" s="2" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>WEB-d9c0e3fc00fb</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>Da verificare</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>Non analizzato</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="n"/>
-      <c r="E62" s="3" t="inlineStr">
-        <is>
-          <t>Understanding the impact of socioeconomic inequities, social support, and cognitive resilience in Alzheimer’s Disease</t>
-        </is>
-      </c>
-      <c r="F62" s="4" t="n"/>
-      <c r="G62" s="5">
-        <f>IF(F62="","",F62-TODAY())</f>
-        <v/>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>Scadenza da verificare</t>
-        </is>
-      </c>
-      <c r="I62" s="2" t="inlineStr">
-        <is>
-          <t>Brain Canada</t>
-        </is>
-      </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>Brain Canada</t>
-        </is>
-      </c>
-      <c r="K62" s="2" t="inlineStr">
-        <is>
-          <t>Understanding the impact of socioeconomic inequities, social support, and cognitive resilience in Alzheimer’s Disease</t>
-        </is>
-      </c>
-      <c r="L62" s="3" t="inlineStr">
-        <is>
-          <t>Understanding the impact of socioeconomic inequities, social support, and cognitive resilience in Alzheimer’s Disease</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr">
-        <is>
-          <t>Invecchiamento</t>
-        </is>
-      </c>
-      <c r="N62" s="2" t="inlineStr">
-        <is>
-          <t>dementi, alzheimer, older adults, neurodegenerat</t>
-        </is>
-      </c>
-      <c r="O62" s="3" t="n"/>
-      <c r="P62" s="6" t="n">
-        <v>200000</v>
-      </c>
-      <c r="Q62" s="6" t="n"/>
-      <c r="R62" s="2" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="S62" s="2" t="n"/>
-      <c r="T62" s="3" t="inlineStr">
-        <is>
-          <t>Non stimabile – dati insufficienti</t>
-        </is>
-      </c>
-      <c r="U62" s="3" t="inlineStr">
-        <is>
-          <t>Non indicato</t>
-        </is>
-      </c>
-      <c r="V62" s="4" t="n"/>
-      <c r="W62" s="2" t="n"/>
-      <c r="X62" s="2" t="n"/>
-      <c r="Y62" s="3" t="n"/>
-      <c r="Z62" s="3" t="n"/>
-      <c r="AA62" s="2" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="AB62" s="2" t="inlineStr">
-        <is>
-          <t>Inglese</t>
-        </is>
-      </c>
-      <c r="AC62" s="7" t="inlineStr">
-        <is>
-          <t>https://braincanada.ca/funded-grants/understanding-the-impact-of-socioeconomic-inequities-social-support-and-cognitive-resilience-in-alzheimer-s-disease</t>
-        </is>
-      </c>
-      <c r="AD62" s="3" t="n"/>
-      <c r="AE62" s="4" t="n">
-        <v>46313</v>
-      </c>
-      <c r="AF62" s="4" t="n">
-        <v>46312</v>
-      </c>
-      <c r="AG62" s="2" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>WEB-219789099636</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>Da verificare</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>Non analizzato</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="n"/>
-      <c r="E63" s="3" t="inlineStr">
-        <is>
-          <t>An Inclusive Approach Towards Developing Biomarkers of Subjective Cognitive Decline and Progression to Dementia</t>
-        </is>
-      </c>
-      <c r="F63" s="4" t="n"/>
-      <c r="G63" s="5">
-        <f>IF(F63="","",F63-TODAY())</f>
-        <v/>
-      </c>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t>Scadenza da verificare</t>
-        </is>
-      </c>
-      <c r="I63" s="2" t="inlineStr">
-        <is>
-          <t>Brain Canada</t>
-        </is>
-      </c>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>Brain Canada</t>
-        </is>
-      </c>
-      <c r="K63" s="2" t="inlineStr">
-        <is>
-          <t>An Inclusive Approach Towards Developing Biomarkers of Subjective Cognitive Decline and Progression to Dementia</t>
-        </is>
-      </c>
-      <c r="L63" s="3" t="inlineStr">
-        <is>
-          <t>An Inclusive Approach Towards Developing Biomarkers of Subjective Cognitive Decline and Progression to Dementia</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr">
-        <is>
-          <t>Invecchiamento</t>
-        </is>
-      </c>
-      <c r="N63" s="2" t="inlineStr">
-        <is>
-          <t>dementi, alzheimer, cognitive decline, older adults, neurodegenerat</t>
-        </is>
-      </c>
-      <c r="O63" s="3" t="n"/>
-      <c r="P63" s="6" t="n">
-        <v>200000</v>
-      </c>
-      <c r="Q63" s="6" t="n"/>
-      <c r="R63" s="2" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="S63" s="2" t="n"/>
-      <c r="T63" s="3" t="inlineStr">
-        <is>
-          <t>Non stimabile – dati insufficienti</t>
-        </is>
-      </c>
-      <c r="U63" s="3" t="inlineStr">
-        <is>
-          <t>Non indicato</t>
-        </is>
-      </c>
-      <c r="V63" s="4" t="n"/>
-      <c r="W63" s="2" t="n"/>
-      <c r="X63" s="2" t="n"/>
-      <c r="Y63" s="3" t="n"/>
-      <c r="Z63" s="3" t="n"/>
-      <c r="AA63" s="2" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="AB63" s="2" t="inlineStr">
-        <is>
-          <t>Inglese</t>
-        </is>
-      </c>
-      <c r="AC63" s="7" t="inlineStr">
-        <is>
-          <t>https://braincanada.ca/funded-grants/an-inclusive-approach-towards-developing-biomarkers-of-subjective-cognitive-decline-and-progression-to-dementia</t>
-        </is>
-      </c>
-      <c r="AD63" s="3" t="n"/>
-      <c r="AE63" s="4" t="n">
-        <v>46313</v>
-      </c>
-      <c r="AF63" s="4" t="n">
-        <v>46312</v>
-      </c>
-      <c r="AG63" s="2" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>WEB-a0ead6d80832</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>Da verificare</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>Non analizzato</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="n"/>
-      <c r="E64" s="3" t="inlineStr">
-        <is>
-          <t>Fuel for Thoughts: The effect of exercise and ketone supplementation on brain and muscle function in subjective cognitive decline</t>
-        </is>
-      </c>
-      <c r="F64" s="4" t="n"/>
-      <c r="G64" s="5">
-        <f>IF(F64="","",F64-TODAY())</f>
-        <v/>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>Scadenza da verificare</t>
-        </is>
-      </c>
-      <c r="I64" s="2" t="inlineStr">
-        <is>
-          <t>Brain Canada</t>
-        </is>
-      </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>Brain Canada</t>
-        </is>
-      </c>
-      <c r="K64" s="2" t="inlineStr">
-        <is>
-          <t>Fuel for Thoughts: The effect of exercise and ketone supplementation on brain and muscle function in subjective cognitive decline</t>
-        </is>
-      </c>
-      <c r="L64" s="3" t="inlineStr">
-        <is>
-          <t>Fuel for Thoughts: The effect of exercise and ketone supplementation on brain and muscle function in subjective cognitive decline</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr">
-        <is>
-          <t>Invecchiamento</t>
-        </is>
-      </c>
-      <c r="N64" s="2" t="inlineStr">
-        <is>
-          <t>dementi, alzheimer, cognitive decline, aging, neurodegenerat</t>
-        </is>
-      </c>
-      <c r="O64" s="3" t="n"/>
-      <c r="P64" s="6" t="n">
-        <v>100000</v>
-      </c>
-      <c r="Q64" s="6" t="n"/>
-      <c r="R64" s="2" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="S64" s="2" t="n"/>
-      <c r="T64" s="3" t="inlineStr">
-        <is>
-          <t>Non stimabile – dati insufficienti</t>
-        </is>
-      </c>
-      <c r="U64" s="3" t="inlineStr">
-        <is>
-          <t>Non indicato</t>
-        </is>
-      </c>
-      <c r="V64" s="4" t="n"/>
-      <c r="W64" s="2" t="n"/>
-      <c r="X64" s="2" t="n"/>
-      <c r="Y64" s="3" t="n"/>
-      <c r="Z64" s="3" t="n"/>
-      <c r="AA64" s="2" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="AB64" s="2" t="inlineStr">
-        <is>
-          <t>Inglese</t>
-        </is>
-      </c>
-      <c r="AC64" s="7" t="inlineStr">
-        <is>
-          <t>https://braincanada.ca/funded-grants/fuel-for-thoughts-the-effect-of-exercise-and-ketone-supplementation-on-brain-and-muscle-function-in-subjective-cognitive-decline</t>
-        </is>
-      </c>
-      <c r="AD64" s="3" t="n"/>
-      <c r="AE64" s="4" t="n">
-        <v>46313</v>
-      </c>
-      <c r="AF64" s="4" t="n">
-        <v>46312</v>
-      </c>
-      <c r="AG64" s="2" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>WEB-8dd2c47bc95e</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>Da verificare</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>Non analizzato</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="n"/>
-      <c r="E65" s="3" t="inlineStr">
-        <is>
-          <t>Music-Based Interventions to Engage Memory in Individuals Living with Dementia</t>
-        </is>
-      </c>
-      <c r="F65" s="4" t="n"/>
-      <c r="G65" s="5">
-        <f>IF(F65="","",F65-TODAY())</f>
-        <v/>
-      </c>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t>Scadenza da verificare</t>
-        </is>
-      </c>
-      <c r="I65" s="2" t="inlineStr">
-        <is>
-          <t>Brain Canada</t>
-        </is>
-      </c>
-      <c r="J65" s="2" t="inlineStr">
-        <is>
-          <t>Brain Canada</t>
-        </is>
-      </c>
-      <c r="K65" s="2" t="inlineStr">
-        <is>
-          <t>Music-Based Interventions to Engage Memory in Individuals Living with Dementia</t>
-        </is>
-      </c>
-      <c r="L65" s="3" t="inlineStr">
-        <is>
-          <t>Music-Based Interventions to Engage Memory in Individuals Living with Dementia</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr">
-        <is>
-          <t>Invecchiamento</t>
-        </is>
-      </c>
-      <c r="N65" s="2" t="inlineStr">
-        <is>
-          <t>dementi, alzheimer, neurodegenerat</t>
-        </is>
-      </c>
-      <c r="O65" s="3" t="n"/>
-      <c r="P65" s="6" t="n">
-        <v>100000</v>
-      </c>
-      <c r="Q65" s="6" t="n"/>
-      <c r="R65" s="2" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="S65" s="2" t="n"/>
-      <c r="T65" s="3" t="inlineStr">
-        <is>
-          <t>Non stimabile – dati insufficienti</t>
-        </is>
-      </c>
-      <c r="U65" s="3" t="inlineStr">
-        <is>
-          <t>Non indicato</t>
-        </is>
-      </c>
-      <c r="V65" s="4" t="n"/>
-      <c r="W65" s="2" t="n"/>
-      <c r="X65" s="2" t="n"/>
-      <c r="Y65" s="3" t="n"/>
-      <c r="Z65" s="3" t="n"/>
-      <c r="AA65" s="2" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="AB65" s="2" t="inlineStr">
-        <is>
-          <t>Inglese</t>
-        </is>
-      </c>
-      <c r="AC65" s="7" t="inlineStr">
-        <is>
-          <t>https://braincanada.ca/funded-grants/music-based-interventions-to-engage-memory-in-individuals-living-with-dementia</t>
-        </is>
-      </c>
-      <c r="AD65" s="3" t="n"/>
-      <c r="AE65" s="4" t="n">
-        <v>46313</v>
-      </c>
-      <c r="AF65" s="4" t="n">
-        <v>46312</v>
-      </c>
-      <c r="AG65" s="2" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>WEB-4e64a8c55083</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>Da verificare</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>Non analizzato</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="n"/>
-      <c r="E66" s="3" t="inlineStr">
-        <is>
-          <t>ALS and Medical Assistance in Dying</t>
-        </is>
-      </c>
-      <c r="F66" s="4" t="n"/>
-      <c r="G66" s="5">
-        <f>IF(F66="","",F66-TODAY())</f>
-        <v/>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>Scadenza da verificare</t>
-        </is>
-      </c>
-      <c r="I66" s="2" t="inlineStr">
-        <is>
-          <t>Brain Canada</t>
-        </is>
-      </c>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>Brain Canada</t>
-        </is>
-      </c>
-      <c r="K66" s="2" t="inlineStr">
-        <is>
-          <t>ALS and Medical Assistance in Dying</t>
-        </is>
-      </c>
-      <c r="L66" s="3" t="inlineStr">
-        <is>
-          <t>ALS and Medical Assistance in Dying</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr">
-        <is>
-          <t>Altre malattie e riabilitazione</t>
-        </is>
-      </c>
-      <c r="N66" s="2" t="inlineStr">
-        <is>
-          <t>amyotrophic lateral sclerosis, neurodegenerat</t>
-        </is>
-      </c>
-      <c r="O66" s="3" t="n"/>
-      <c r="P66" s="6" t="n">
-        <v>100000</v>
-      </c>
-      <c r="Q66" s="6" t="n"/>
-      <c r="R66" s="2" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="S66" s="2" t="n"/>
-      <c r="T66" s="3" t="inlineStr">
-        <is>
-          <t>Non stimabile – dati insufficienti</t>
-        </is>
-      </c>
-      <c r="U66" s="3" t="inlineStr">
-        <is>
-          <t>Non indicato</t>
-        </is>
-      </c>
-      <c r="V66" s="4" t="n"/>
-      <c r="W66" s="2" t="n"/>
-      <c r="X66" s="2" t="n"/>
-      <c r="Y66" s="3" t="n"/>
-      <c r="Z66" s="3" t="n"/>
-      <c r="AA66" s="2" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="AB66" s="2" t="inlineStr">
-        <is>
-          <t>Inglese</t>
-        </is>
-      </c>
-      <c r="AC66" s="7" t="inlineStr">
-        <is>
-          <t>https://braincanada.ca/funded-grants/als-and-medical-assistance-in-dying</t>
-        </is>
-      </c>
-      <c r="AD66" s="3" t="n"/>
-      <c r="AE66" s="4" t="n">
-        <v>46313</v>
-      </c>
-      <c r="AF66" s="4" t="n">
-        <v>46312</v>
-      </c>
-      <c r="AG66" s="2" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>WEB-4430e9cb97bd</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>Da verificare</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>Non analizzato</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="n"/>
-      <c r="E67" s="3" t="inlineStr">
-        <is>
-          <t>Understanding how microglia repair the injured spinal cord</t>
-        </is>
-      </c>
-      <c r="F67" s="4" t="n"/>
-      <c r="G67" s="5">
-        <f>IF(F67="","",F67-TODAY())</f>
-        <v/>
-      </c>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t>Scadenza da verificare</t>
-        </is>
-      </c>
-      <c r="I67" s="2" t="inlineStr">
-        <is>
-          <t>Brain Canada</t>
-        </is>
-      </c>
-      <c r="J67" s="2" t="inlineStr">
-        <is>
-          <t>Brain Canada</t>
-        </is>
-      </c>
-      <c r="K67" s="2" t="inlineStr">
-        <is>
-          <t>Understanding how microglia repair the injured spinal cord</t>
-        </is>
-      </c>
-      <c r="L67" s="3" t="inlineStr">
-        <is>
-          <t>Understanding how microglia repair the injured spinal cord</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr">
-        <is>
-          <t>Altre malattie e riabilitazione</t>
-        </is>
-      </c>
-      <c r="N67" s="2" t="inlineStr">
-        <is>
-          <t>spinal cord injur, neurological condition</t>
-        </is>
-      </c>
-      <c r="O67" s="3" t="n"/>
-      <c r="P67" s="6" t="n">
-        <v>100000</v>
-      </c>
-      <c r="Q67" s="6" t="n"/>
-      <c r="R67" s="2" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="S67" s="2" t="n"/>
-      <c r="T67" s="3" t="inlineStr">
-        <is>
-          <t>Non stimabile – dati insufficienti</t>
-        </is>
-      </c>
-      <c r="U67" s="3" t="inlineStr">
-        <is>
-          <t>Non indicato</t>
-        </is>
-      </c>
-      <c r="V67" s="4" t="n"/>
-      <c r="W67" s="2" t="n"/>
-      <c r="X67" s="2" t="n"/>
-      <c r="Y67" s="3" t="n"/>
-      <c r="Z67" s="3" t="n"/>
-      <c r="AA67" s="2" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="AB67" s="2" t="inlineStr">
-        <is>
-          <t>Inglese</t>
-        </is>
-      </c>
-      <c r="AC67" s="7" t="inlineStr">
-        <is>
-          <t>https://braincanada.ca/funded-grants/understanding-how-microglia-repair-the-injured-spinal-cord</t>
-        </is>
-      </c>
-      <c r="AD67" s="3" t="n"/>
-      <c r="AE67" s="4" t="n">
-        <v>46313</v>
-      </c>
-      <c r="AF67" s="4" t="n">
-        <v>46313</v>
-      </c>
-      <c r="AG67" s="2" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>WEB-890640ec53cd</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>Da verificare</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>Non analizzato</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="n"/>
-      <c r="E68" s="3" t="inlineStr">
-        <is>
-          <t>Telomerase Reverse Transcriptase as a Neuroprotective Factor in Progressive Multiple Sclerosis</t>
-        </is>
-      </c>
-      <c r="F68" s="4" t="n"/>
-      <c r="G68" s="5">
-        <f>IF(F68="","",F68-TODAY())</f>
-        <v/>
-      </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>Scadenza da verificare</t>
-        </is>
-      </c>
-      <c r="I68" s="2" t="inlineStr">
-        <is>
-          <t>Brain Canada</t>
-        </is>
-      </c>
-      <c r="J68" s="2" t="inlineStr">
-        <is>
-          <t>Brain Canada</t>
-        </is>
-      </c>
-      <c r="K68" s="2" t="inlineStr">
-        <is>
-          <t>Telomerase Reverse Transcriptase as a Neuroprotective Factor in Progressive Multiple Sclerosis</t>
-        </is>
-      </c>
-      <c r="L68" s="3" t="inlineStr">
-        <is>
-          <t>Telomerase Reverse Transcriptase as a Neuroprotective Factor in Progressive Multiple Sclerosis</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr">
-        <is>
-          <t>Altre malattie e riabilitazione</t>
-        </is>
-      </c>
-      <c r="N68" s="2" t="inlineStr">
-        <is>
-          <t>multiple sclerosis, neurodegenerat, disabilit</t>
-        </is>
-      </c>
-      <c r="O68" s="3" t="n"/>
-      <c r="P68" s="6" t="n">
-        <v>100000</v>
-      </c>
-      <c r="Q68" s="6" t="n"/>
-      <c r="R68" s="2" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="S68" s="2" t="n"/>
-      <c r="T68" s="3" t="inlineStr">
-        <is>
-          <t>Non stimabile – dati insufficienti</t>
-        </is>
-      </c>
-      <c r="U68" s="3" t="inlineStr">
-        <is>
-          <t>Non indicato</t>
-        </is>
-      </c>
-      <c r="V68" s="4" t="n"/>
-      <c r="W68" s="2" t="n"/>
-      <c r="X68" s="2" t="n"/>
-      <c r="Y68" s="3" t="n"/>
-      <c r="Z68" s="3" t="n"/>
-      <c r="AA68" s="2" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="AB68" s="2" t="inlineStr">
-        <is>
-          <t>Inglese</t>
-        </is>
-      </c>
-      <c r="AC68" s="7" t="inlineStr">
-        <is>
-          <t>https://braincanada.ca/funded-grants/telomerase-reverse-transcriptase-as-a-neuroprotective-factor-in-progressive-multiple-sclerosis</t>
-        </is>
-      </c>
-      <c r="AD68" s="3" t="n"/>
-      <c r="AE68" s="4" t="n">
-        <v>46313</v>
-      </c>
-      <c r="AF68" s="4" t="n">
-        <v>46312</v>
-      </c>
-      <c r="AG68" s="2" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>WEB-21455809207b</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>Da verificare</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>Non analizzato</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="n"/>
-      <c r="E69" s="3" t="inlineStr">
-        <is>
-          <t>La douleur chronique, un chaînon manquant dans la prédiction du risque cérébrovasculaire</t>
-        </is>
-      </c>
-      <c r="F69" s="4" t="n"/>
-      <c r="G69" s="5">
-        <f>IF(F69="","",F69-TODAY())</f>
-        <v/>
-      </c>
-      <c r="H69" s="2" t="inlineStr">
-        <is>
-          <t>Scadenza da verificare</t>
-        </is>
-      </c>
-      <c r="I69" s="2" t="inlineStr">
-        <is>
-          <t>Brain Canada</t>
-        </is>
-      </c>
-      <c r="J69" s="2" t="inlineStr">
-        <is>
-          <t>Brain Canada</t>
-        </is>
-      </c>
-      <c r="K69" s="2" t="inlineStr">
-        <is>
-          <t>La douleur chronique, un chaînon manquant dans la prédiction du risque cérébrovasculaire</t>
-        </is>
-      </c>
-      <c r="L69" s="3" t="inlineStr">
-        <is>
-          <t>La douleur chronique, un chaînon manquant dans la prédiction du risque cérébrovasculaire</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr">
-        <is>
-          <t>Ictus</t>
-        </is>
-      </c>
-      <c r="N69" s="2" t="inlineStr">
-        <is>
-          <t>stroke, cerebrovascula</t>
-        </is>
-      </c>
-      <c r="O69" s="3" t="n"/>
-      <c r="P69" s="6" t="n">
-        <v>100000</v>
-      </c>
-      <c r="Q69" s="6" t="n"/>
-      <c r="R69" s="2" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="S69" s="2" t="n"/>
-      <c r="T69" s="3" t="inlineStr">
-        <is>
-          <t>Non stimabile – dati insufficienti</t>
-        </is>
-      </c>
-      <c r="U69" s="3" t="inlineStr">
-        <is>
-          <t>Non indicato</t>
-        </is>
-      </c>
-      <c r="V69" s="4" t="n"/>
-      <c r="W69" s="2" t="n"/>
-      <c r="X69" s="2" t="n"/>
-      <c r="Y69" s="3" t="n"/>
-      <c r="Z69" s="3" t="n"/>
-      <c r="AA69" s="2" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="AB69" s="2" t="inlineStr">
-        <is>
-          <t>Inglese</t>
-        </is>
-      </c>
-      <c r="AC69" s="7" t="inlineStr">
-        <is>
-          <t>https://braincanada.ca/funded-grants/la-douleur-chronique-un-chaînon-manquant-dans-la-prédiction-du-risque-cérébrovasculaire</t>
-        </is>
-      </c>
-      <c r="AD69" s="3" t="n"/>
-      <c r="AE69" s="4" t="n">
-        <v>46313</v>
-      </c>
-      <c r="AF69" s="4" t="n">
-        <v>46312</v>
-      </c>
-      <c r="AG69" s="2" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>WEB-8b08f4b95c82</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>Da verificare</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>Non analizzato</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="n"/>
-      <c r="E70" s="3" t="inlineStr">
-        <is>
-          <t>Counteracting Refractory Alcohol-Use-Disorder Via Electrostimulation (CRAVE): Deep Brain Stimulation for Treatment-Refractory Alcohol Use Disorder</t>
-        </is>
-      </c>
-      <c r="F70" s="4" t="n"/>
-      <c r="G70" s="5">
-        <f>IF(F70="","",F70-TODAY())</f>
-        <v/>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>Scadenza da verificare</t>
-        </is>
-      </c>
-      <c r="I70" s="2" t="inlineStr">
-        <is>
-          <t>Brain Canada</t>
-        </is>
-      </c>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>Brain Canada</t>
-        </is>
-      </c>
-      <c r="K70" s="2" t="inlineStr">
-        <is>
-          <t>Counteracting Refractory Alcohol-Use-Disorder Via Electrostimulation (CRAVE): Deep Brain Stimulation for Treatment-Refractory Alcohol Use Disorder</t>
-        </is>
-      </c>
-      <c r="L70" s="3" t="inlineStr">
-        <is>
-          <t>Counteracting Refractory Alcohol-Use-Disorder Via Electrostimulation (CRAVE): Deep Brain Stimulation for Treatment-Refractory Alcohol Use Disorder</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr">
-        <is>
-          <t>Parkinson</t>
-        </is>
-      </c>
-      <c r="N70" s="2" t="inlineStr">
-        <is>
-          <t>deep brain stimulation</t>
-        </is>
-      </c>
-      <c r="O70" s="3" t="n"/>
-      <c r="P70" s="6" t="n">
-        <v>100000</v>
-      </c>
-      <c r="Q70" s="6" t="n"/>
-      <c r="R70" s="2" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="S70" s="2" t="n"/>
-      <c r="T70" s="3" t="inlineStr">
-        <is>
-          <t>Non stimabile – dati insufficienti</t>
-        </is>
-      </c>
-      <c r="U70" s="3" t="inlineStr">
-        <is>
-          <t>Non indicato</t>
-        </is>
-      </c>
-      <c r="V70" s="4" t="n"/>
-      <c r="W70" s="2" t="n"/>
-      <c r="X70" s="2" t="n"/>
-      <c r="Y70" s="3" t="n"/>
-      <c r="Z70" s="3" t="n"/>
-      <c r="AA70" s="2" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="AB70" s="2" t="inlineStr">
-        <is>
-          <t>Inglese</t>
-        </is>
-      </c>
-      <c r="AC70" s="7" t="inlineStr">
-        <is>
-          <t>https://braincanada.ca/funded-grants/counteracting-refractory-alcohol-use-disorder-via-electrostimulation-crave-deep-brain-stimulation-for-treatment-refractory-alcohol-use-disorder</t>
-        </is>
-      </c>
-      <c r="AD70" s="3" t="n"/>
-      <c r="AE70" s="4" t="n">
-        <v>46313</v>
-      </c>
-      <c r="AF70" s="4" t="n">
-        <v>46312</v>
-      </c>
-      <c r="AG70" s="2" t="n"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:AG70"/>
-  <conditionalFormatting sqref="G2:G70">
+  <autoFilter ref="A1:AG38"/>
+  <conditionalFormatting sqref="G2:G38">
     <cfRule type="cellIs" priority="1" operator="between" dxfId="0">
       <formula>0</formula>
       <formula>30</formula>
@@ -9093,38 +5911,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC36" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC37" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC38" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC39" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC40" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC41" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC42" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC43" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC44" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC45" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC46" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC47" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC48" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC49" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC50" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC51" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC52" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC53" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC54" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC55" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC56" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC57" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC58" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC59" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC60" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC61" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC62" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC63" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC64" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC65" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC66" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC67" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC68" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC69" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC70" r:id="rId69"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -9226,11 +6012,11 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>21/10/2026 06:06</t>
+          <t>21/10/2026 12:13</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>107</v>
+        <v>142</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>0</v>
@@ -9269,11 +6055,11 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>21/10/2026 06:15</t>
+          <t>21/10/2026 12:23</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>21</v>
@@ -9312,18 +6098,18 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18/10/2026 01:41</t>
+          <t>21/10/2026 12:22</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Saltata: non aperta a enti italiani (colonna 'italia' di fonti_web.csv)</t>
+          <t>Ultima esecuzione: 22 elementi esaminati, 0 pertinenti</t>
         </is>
       </c>
     </row>
@@ -9355,18 +6141,18 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18/10/2026 01:40</t>
+          <t>21/10/2026 12:21</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>5</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Saltata: non aperta a enti italiani (colonna 'italia' di fonti_web.csv)</t>
+          <t>Ultima esecuzione: 2 elementi esaminati, 0 pertinenti</t>
         </is>
       </c>
     </row>
@@ -9398,18 +6184,18 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18/10/2026 01:43</t>
+          <t>21/10/2026 12:24</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Saltata: non aperta a enti italiani (colonna 'italia' di fonti_web.csv)</t>
+          <t>Ultima esecuzione: 29 elementi esaminati, 0 pertinenti</t>
         </is>
       </c>
     </row>
@@ -9441,14 +6227,14 @@
       </c>
       <c r="F7" s="2" t="n"/>
       <c r="G7" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Saltata: non aperta a enti italiani (colonna 'italia' di fonti_web.csv)</t>
+          <t>Ultimo errore 21/10/2026: HTTP 403</t>
         </is>
       </c>
     </row>
@@ -9480,18 +6266,18 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18/10/2026 01:45</t>
+          <t>21/10/2026 12:24</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>10</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Saltata: non aperta a enti italiani (colonna 'italia' di fonti_web.csv)</t>
+          <t>Ultima esecuzione: 20 elementi esaminati, 1 pertinenti</t>
         </is>
       </c>
     </row>
@@ -9523,18 +6309,18 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18/10/2026 01:45</t>
+          <t>21/10/2026 12:24</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Saltata: non aperta a enti italiani (colonna 'italia' di fonti_web.csv)</t>
+          <t>Ultima esecuzione: 1 elementi esaminati, 0 pertinenti</t>
         </is>
       </c>
     </row>
@@ -9566,11 +6352,11 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21/10/2026 05:59</t>
+          <t>21/10/2026 12:05</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>175</v>
+        <v>210</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>1</v>
@@ -9609,18 +6395,18 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18/10/2026 01:41</t>
+          <t>21/10/2026 12:22</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>70</v>
+        <v>105</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>9</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Saltata: non aperta a enti italiani (colonna 'italia' di fonti_web.csv)</t>
+          <t>Ultima esecuzione: 35 elementi esaminati, 0 pertinenti</t>
         </is>
       </c>
     </row>
@@ -9652,11 +6438,11 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21/10/2026 06:06</t>
+          <t>21/10/2026 12:13</t>
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>175</v>
+        <v>210</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>0</v>
@@ -9695,11 +6481,11 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21/10/2026 06:13</t>
+          <t>21/10/2026 12:19</t>
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>175</v>
+        <v>210</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>0</v>
@@ -9738,18 +6524,18 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21/10/2026 05:49</t>
+          <t>21/10/2026 11:55</t>
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>5984</v>
+        <v>7187</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>77</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Ultima esecuzione: 1203 elementi esaminati, 10 pertinenti</t>
+          <t>Ultima esecuzione: 1203 elementi esaminati, 8 pertinenti</t>
         </is>
       </c>
     </row>
@@ -9781,18 +6567,18 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>21/10/2026 06:01</t>
+          <t>21/10/2026 12:08</t>
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>174</v>
+        <v>207</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>3</v>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Ultima esecuzione: 34 elementi esaminati, 0 pertinenti</t>
+          <t>Ultima esecuzione: 33 elementi esaminati, 0 pertinenti</t>
         </is>
       </c>
     </row>
@@ -9824,11 +6610,11 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21/10/2026 06:00</t>
+          <t>21/10/2026 12:07</t>
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>175</v>
+        <v>210</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>3</v>
@@ -9867,11 +6653,11 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21/10/2026 06:04</t>
+          <t>21/10/2026 12:11</t>
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>175</v>
+        <v>210</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>2</v>
@@ -9910,11 +6696,11 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>21/10/2026 05:58</t>
+          <t>21/10/2026 12:03</t>
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>175</v>
+        <v>210</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>2</v>
@@ -9953,11 +6739,11 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21/10/2026 06:05</t>
+          <t>21/10/2026 12:11</t>
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>175</v>
+        <v>210</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>0</v>
@@ -9996,11 +6782,11 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>21/10/2026 06:05</t>
+          <t>21/10/2026 12:12</t>
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>175</v>
+        <v>210</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>0</v>
@@ -10039,18 +6825,18 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>18/10/2026 01:45</t>
+          <t>21/10/2026 12:24</t>
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>16</v>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>Saltata: non aperta a enti italiani (colonna 'italia' di fonti_web.csv)</t>
+          <t>Ultima esecuzione: 19 elementi esaminati, 1 pertinenti</t>
         </is>
       </c>
     </row>
@@ -10082,11 +6868,11 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>21/10/2026 05:54</t>
+          <t>21/10/2026 12:00</t>
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>4236</v>
+        <v>5090</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>116</v>
@@ -10125,11 +6911,11 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>21/10/2026 05:56</t>
+          <t>21/10/2026 12:01</t>
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>175</v>
+        <v>210</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>0</v>
@@ -10168,11 +6954,11 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>21/10/2026 06:07</t>
+          <t>21/10/2026 12:13</t>
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>0</v>
@@ -10211,11 +6997,11 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>21/10/2026 05:57</t>
+          <t>21/10/2026 12:03</t>
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>175</v>
+        <v>210</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>0</v>
@@ -10254,11 +7040,11 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>21/10/2026 06:14</t>
+          <t>21/10/2026 12:23</t>
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>21</v>
@@ -10297,11 +7083,11 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>21/10/2026 05:55</t>
+          <t>21/10/2026 12:01</t>
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>175</v>
+        <v>210</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>0</v>
@@ -10340,11 +7126,11 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>21/10/2026 05:54</t>
+          <t>21/10/2026 12:00</t>
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H28" s="2" t="n">
         <v>0</v>
@@ -10390,7 +7176,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>Saltata: non aperta a enti italiani (colonna 'italia' di fonti_web.csv)</t>
+          <t>Ultimo errore 21/10/2026: irraggiungibile: HTTPSConnectionPool(host='www.nhmrc.gov.au', port=443): Read timed out. (read timeout=45)</t>
         </is>
       </c>
     </row>
@@ -10422,14 +7208,14 @@
       </c>
       <c r="F30" s="2" t="n"/>
       <c r="G30" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Saltata: non aperta a enti italiani (colonna 'italia' di fonti_web.csv)</t>
+          <t>Ultimo errore 21/10/2026: HTTP 403</t>
         </is>
       </c>
     </row>
@@ -10461,18 +7247,18 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>21/10/2026 06:16</t>
+          <t>21/10/2026 12:24</t>
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Ultima esecuzione: 35 elementi esaminati, 0 pertinenti</t>
+          <t>Ultima esecuzione: 1 elementi esaminati, 0 pertinenti</t>
         </is>
       </c>
     </row>
@@ -10504,11 +7290,11 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>21/10/2026 06:15</t>
+          <t>21/10/2026 12:23</t>
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="H32" s="2" t="n">
         <v>8</v>
@@ -10547,18 +7333,18 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>18/10/2026 01:40</t>
+          <t>21/10/2026 12:21</t>
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>6</v>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>Saltata: non aperta a enti italiani (colonna 'italia' di fonti_web.csv)</t>
+          <t>Ultima esecuzione: 12 elementi esaminati, 1 pertinenti</t>
         </is>
       </c>
     </row>
@@ -10590,11 +7376,11 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>21/10/2026 05:56</t>
+          <t>21/10/2026 12:01</t>
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>0</v>
@@ -10633,11 +7419,11 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>21/10/2026 05:56</t>
+          <t>21/10/2026 12:02</t>
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>175</v>
+        <v>210</v>
       </c>
       <c r="H35" s="2" t="n">
         <v>0</v>
@@ -10676,14 +7462,14 @@
       </c>
       <c r="F36" s="2" t="n"/>
       <c r="G36" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Saltata: non aperta a enti italiani (colonna 'italia' di fonti_web.csv)</t>
+          <t>Ultimo errore 21/10/2026: HTTP 403</t>
         </is>
       </c>
     </row>
@@ -10715,11 +7501,11 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>21/10/2026 06:13</t>
+          <t>21/10/2026 12:19</t>
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>0</v>
@@ -10758,11 +7544,11 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>21/10/2026 06:13</t>
+          <t>21/10/2026 12:20</t>
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>175</v>
+        <v>210</v>
       </c>
       <c r="H38" s="2" t="n">
         <v>0</v>
@@ -10801,11 +7587,11 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>21/10/2026 06:14</t>
+          <t>21/10/2026 12:21</t>
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>175</v>
+        <v>210</v>
       </c>
       <c r="H39" s="2" t="n">
         <v>0</v>
@@ -10827,7 +7613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -10885,43 +7671,43 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-21 06:19</t>
+          <t>2026-10-21 12:31</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2731</v>
+        <v>2839</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>35 non aperti all'Italia, 3 di infrastruttura, 3 preclinici, 2 non pertinenti alla riabilitazione, 1 servizi o programmi sociali</t>
+          <t>12 di infrastruttura, 7 servizi o programmi sociali, 6 preclinici, 4 non pertinenti alla riabilitazione, 1 chiusi, 1 pagine che non sono bandi</t>
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>Nessuno</t>
+          <t>NIHR: HTTP 403; Stroke Association: HTTP 403; American Heart Association – Research: HTTP 403; NHMRC: irraggiungibile: HTTPSConnectionPool(host='www.nhmrc.gov.au', port=443): Read timed out. (read timeout=45)</t>
         </is>
       </c>
       <c r="H2" s="3" t="n">
-        <v>30</v>
+        <v>36.7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-19 07:49</t>
+          <t>2026-10-21 06:19</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2686</v>
+        <v>2731</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>0</v>
@@ -10931,11 +7717,11 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>32 non aperti all'Italia, 3 di infrastruttura, 3 preclinici, 2 non pertinenti alla riabilitazione, 1 servizi o programmi sociali</t>
+          <t>35 non aperti all'Italia, 3 di infrastruttura, 3 preclinici, 2 non pertinenti alla riabilitazione, 1 servizi o programmi sociali</t>
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -10943,31 +7729,31 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>24.1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-18 14:17</t>
+          <t>2026-10-19 07:49</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>2720</v>
+        <v>2686</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>32 non aperti all'Italia, 3 di infrastruttura, 3 preclinici, 3 non pertinenti alla riabilitazione, 1 servizi o programmi sociali</t>
+          <t>32 non aperti all'Italia, 3 di infrastruttura, 3 preclinici, 2 non pertinenti alla riabilitazione, 1 servizi o programmi sociali</t>
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
@@ -10975,62 +7761,94 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>29.3</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-18 02:48</t>
+          <t>2026-10-18 14:17</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>2925</v>
+        <v>2720</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>107</v>
-      </c>
-      <c r="E5" s="3" t="n"/>
+        <v>112</v>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>32 non aperti all'Italia, 3 di infrastruttura, 3 preclinici, 3 non pertinenti alla riabilitazione, 1 servizi o programmi sociali</t>
+        </is>
+      </c>
       <c r="F5" s="3" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>NIHR: HTTP 403; Stroke Association: HTTP 403; American Heart Association – Research: HTTP 403; NHMRC: irraggiungibile: HTTPSConnectionPool(host='www.nhmrc.gov.au', port=443): Read timed out. (read timeout=45)</t>
+          <t>Nessuno</t>
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>92.5</v>
+        <v>29.3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-10-17 15:58</t>
+          <t>2026-10-18 02:48</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>2819</v>
+        <v>2925</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>266</v>
+        <v>20</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="E6" s="3" t="n"/>
       <c r="F6" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>NIHR: HTTP 403; Stroke Association: HTTP 403; American Heart Association – Research: HTTP 403; NHMRC: irraggiungibile: HTTPSConnectionPool(host='www.nhmrc.gov.au', port=443): Read timed out. (read timeout=45)</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>92.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-17 15:58</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>2819</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>266</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3" t="n">
         <v>44</v>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>NIHR: HTTP 403; Stroke Association: HTTP 403; American Heart Association – Research: HTTP 403; NHMRC: irraggiungibile: HTTPSConnectionPool(host='www.nhmrc.gov.au', port=443): Read timed out. (read timeout=45)</t>
         </is>
       </c>
-      <c r="H6" s="3" t="n">
+      <c r="H7" s="3" t="n">
         <v>76.5</v>
       </c>
     </row>

--- a/report/NeuroGrant_ultimo.xlsx
+++ b/report/NeuroGrant_ultimo.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LOG" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BANDI'!$A$1:$AG$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BANDI'!$A$1:$AG$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -492,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG38"/>
+  <dimension ref="A1:AG41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -834,7 +834,7 @@
         </is>
       </c>
       <c r="AE2" s="4" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="AF2" s="4" t="n">
         <v>46312</v>
@@ -844,7 +844,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>GG-PAR-25-124</t>
+          <t>EU-HORIZON-HLTH-2027-01-STAYHLTH-01</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -864,11 +864,11 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Finanziamento di ricerca per ricercatori a inizio carriera NCMRR (R03 Clinical Trial facoltativo)</t>
+          <t>Affrontare le disabilità lungo l'arco della vita per favorire la vita indipendente e l'inclusione</t>
         </is>
       </c>
       <c r="F3" s="4" t="n">
-        <v>46759</v>
+        <v>46435</v>
       </c>
       <c r="G3" s="5">
         <f>IF(F3="","",F3-TODAY())</f>
@@ -876,61 +876,61 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Aperto</t>
+          <t>In apertura</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>National Institutes of Health</t>
+          <t>Commissione europea</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Grants.gov</t>
+          <t>EU Funding &amp; Tenders Portal</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>National Institutes of Health – PAR-25-124</t>
+          <t>Horizon Europe – HORIZON  Research and Innovation Actions</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>NCMRR Early Career Research Award (R03 Clinical Trial Optional)</t>
+          <t>Addressing disabilities through the life course to support independent living and inclusion</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Altre malattie e riabilitazione</t>
+          <t>Invecchiamento, Tecnologie riabilitazione, Altre malattie e riabilitazione</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>rehabilitat</t>
+          <t>frailty, older persons, assistive technolog, rehabilitat, disabilit, cardiovascular, obesit</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>Bando dedicato specificamente alla ricerca di base e clinica in riabilitazione promosso dal NCMRR per ricercatori a inizio carriera.</t>
+          <t>Bando dedicato all'accesso a servizi di riabilitazione innovativa con tecnologie assistive e al supporto dell'autonomia nelle disabilità a lungo termine.</t>
         </is>
       </c>
       <c r="P3" s="6" t="n">
-        <v>200000</v>
+        <v>39300000</v>
       </c>
       <c r="Q3" s="6" t="n">
-        <v>200000</v>
+        <v>8000000</v>
       </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="S3" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T3" s="3" t="inlineStr">
         <is>
-          <t>Bassa – 1 progetti finanziabili (stima: tasso storico non disponibile)</t>
+          <t>Media – 5 progetti finanziabili (stima: tasso storico non disponibile)</t>
         </is>
       </c>
       <c r="U3" s="3" t="inlineStr">
@@ -939,7 +939,7 @@
         </is>
       </c>
       <c r="V3" s="4" t="n">
-        <v>45614</v>
+        <v>46324</v>
       </c>
       <c r="W3" s="2" t="n"/>
       <c r="X3" s="2" t="inlineStr">
@@ -947,15 +947,15 @@
           <t>Ricerca</t>
         </is>
       </c>
-      <c r="Y3" s="3" t="inlineStr">
-        <is>
-          <t>State governments; Nonprofits having a 501(c)(3) status with the IRS, other than institutions of higher education; Others (see text field entitled "Additional Information on Eligibility" for clarification); City or township governments; Nonprofits that do not have a 501(c)(3) status with the IRS, other than institutions of higher education; Private institutions of higher education; Native American</t>
-        </is>
-      </c>
-      <c r="Z3" s="3" t="n"/>
+      <c r="Y3" s="3" t="n"/>
+      <c r="Z3" s="3" t="inlineStr">
+        <is>
+          <t>Consorzio: min. 3 enti indipendenti da 3 paesi UE/associati (regola standard, verificare il topic)</t>
+        </is>
+      </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>Ammessi anche enti non statunitensi (call NIH completa)</t>
+          <t>Stati membri UE e paesi associati (altri paesi secondo le condizioni del topic)</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
@@ -965,26 +965,26 @@
       </c>
       <c r="AC3" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/357206</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-HLTH-2027-01-STAYHLTH-01</t>
         </is>
       </c>
       <c r="AD3" s="3" t="inlineStr">
         <is>
-          <t>Il bando NCMRR Early Career Research Award (R03), promosso dal National Institutes of Health (NIH), sostiene ricercatori a inizio carriera che intendono consolidare un percorso scientifico indipendente nel campo della riabilitazione medica. L'iniziativa finanzia progetti di ricerca clinica e di base allineati al Piano di Ricerca sulla Riabilitazione del NIH, con l'obiettivo di raccogliere dati preliminari sufficienti per future proposte R01. Sono ammissibili analisi secondarie di dati preesistenti, studi pilota indipendenti, sviluppo di metodologie di ricerca, studi traslazionali, ricerca sugli esiti e lo sviluppo di nuove tecnologie. Possono candidarsi istituzioni accademiche e di ricerca, comprese organizzazioni non profit ed enti stranieri con sede al di fuori degli Stati Uniti.</t>
+          <t>Questo bando Horizon Europe mira a promuovere la vita indipendente e l'inclusione sociale delle persone con disabilità a lungo termine lungo tutto l'arco dell'esistenza. Le proposte devono affrontare almeno tre aree tematiche tra cui: ricerca sanitaria sulle patologie causa di disabilità; percorsi di transizione verso l'autonomia per minori o anziani; accesso a servizi di abilitazione e riabilitazione, compresa la riabilitazione psicologica e l'impiego di tecnologie assistive; prevenzione dei fattori di rischio secondari; transizione dall'istituzionalizzazione alla comunità e sviluppo di modelli assistenziali centrati sulla persona. L'obiettivo è rimuovere le barriere fisiche, sociali e relazionali, fornendo servizi integrati sociosanitari di supporto e autosufficienza per le persone disabili e le loro famiglie.</t>
         </is>
       </c>
       <c r="AE3" s="4" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="AF3" s="4" t="n">
-        <v>46312</v>
+        <v>46317</v>
       </c>
       <c r="AG3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>WEB-00773cbd93aa</t>
+          <t>GG-PAR-25-124</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1004,11 +1004,11 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Finanziamento ponte per la ricerca interrotta sulle malattie neurodegenerative (BFDN)</t>
+          <t>Finanziamento di ricerca per ricercatori a inizio carriera NCMRR (R03 Clinical Trial facoltativo)</t>
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>46325</v>
+        <v>46759</v>
       </c>
       <c r="G4" s="5">
         <f>IF(F4="","",F4-TODAY())</f>
@@ -1016,49 +1016,49 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>In scadenza (≤30 gg)</t>
+          <t>Aperto</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Michael J. Fox Foundation</t>
+          <t>National Institutes of Health</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Michael J. Fox Foundation</t>
+          <t>Grants.gov</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>Bridge Funding for Disrupted Neurodegenerative Research Grant Program (BFDN) Powering the Next Generation of Research</t>
+          <t>National Institutes of Health – PAR-25-124</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>Bridge Funding for Disrupted Neurodegenerative Research Grant Program (BFDN) Powering the Next Generation of Research</t>
+          <t>NCMRR Early Career Research Award (R03 Clinical Trial Optional)</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Parkinson, Invecchiamento, Altre malattie e riabilitazione</t>
+          <t>Altre malattie e riabilitazione</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>parkinson, dementi, alzheimer, neurodegenerat, neurological disease</t>
+          <t>rehabilitat</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>Finanzia la continuità di progetti di ricerca su Parkinson, Alzheimer e demenze, senza una focalizzazione specifica sulla riabilitazione.</t>
+          <t>Bando dedicato specificamente alla ricerca di base e clinica in riabilitazione promosso dal NCMRR per ricercatori a inizio carriera.</t>
         </is>
       </c>
       <c r="P4" s="6" t="n">
-        <v>250000</v>
+        <v>200000</v>
       </c>
       <c r="Q4" s="6" t="n">
-        <v>250000</v>
+        <v>200000</v>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
@@ -1075,15 +1075,13 @@
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t>Co-finanziamento richiesto (25% a carico del beneficiario)</t>
-        </is>
-      </c>
-      <c r="V4" s="4" t="n"/>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>12 mesi</t>
-        </is>
-      </c>
+          <t>Interamente finanziato</t>
+        </is>
+      </c>
+      <c r="V4" s="4" t="n">
+        <v>45614</v>
+      </c>
+      <c r="W4" s="2" t="n"/>
       <c r="X4" s="2" t="inlineStr">
         <is>
           <t>Ricerca</t>
@@ -1091,13 +1089,13 @@
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t>Ricercatori principali a inizio carriera (Early Stage Investigator secondo i criteri NIH o entro 7 anni dalla qualifica) titolari di grant federali statunitensi interrotti</t>
+          <t>Nonprofits having a 501(c)(3) status with the IRS, other than institutions of higher education; State governments; Public housing authorities/Indian housing authorities; Nonprofits that do not have a 501(c)(3) status with the IRS, other than institutions of higher education; Private institutions of higher education; For profit organizations other than small businesses; Special district governments</t>
         </is>
       </c>
       <c r="Z4" s="3" t="n"/>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>Mondiale</t>
+          <t>Ammessi anche enti non statunitensi (call NIH completa)</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
@@ -1107,16 +1105,16 @@
       </c>
       <c r="AC4" s="7" t="inlineStr">
         <is>
-          <t>https://www.michaeljfox.org/grant/bridge-funding-disrupted-neurodegenerative-research-grant-program-bfdn-powering-next</t>
+          <t>https://www.grants.gov/search-results-detail/357206</t>
         </is>
       </c>
       <c r="AD4" s="3" t="inlineStr">
         <is>
-          <t>Il programma congiunto promosso da Alzheimer's Association, The Michael J. Fox Foundation e Robertson Foundation fornisce finanziamenti ponte per garantire la continuità a progetti di ricerca sulle malattie neurodegenerative (morbo di Parkinson, malattia di Alzheimer, demenza frontotemporale, demenza a corpi di Lewy e parkinsonismi atipici). L'iniziativa è specificamente rivolta a ricercatori a inizio carriera (Early Stage Investigator secondo i criteri NIH o entro 7 anni da tale qualifica) i cui finanziamenti federali statunitensi abbiano subito interruzioni, ritardi o tagli per cambiamenti operativi o di priorità. Il contributo, fino a un massimo di 250.000 dollari per una durata compresa tra 3 e 12 mesi, copre stipendi e costi diretti, richiedendo un cofinanziamento istituzionale fino al 25%.</t>
+          <t>Il bando NCMRR Early Career Research Award (R03), promosso dal National Institutes of Health (NIH), sostiene ricercatori a inizio carriera che intendono consolidare un percorso scientifico indipendente nel campo della riabilitazione medica. L'iniziativa finanzia progetti di ricerca clinica e di base allineati al Piano di Ricerca sulla Riabilitazione del NIH, con l'obiettivo di raccogliere dati preliminari sufficienti per future proposte R01. Sono ammissibili analisi secondarie di dati preesistenti, studi pilota indipendenti, sviluppo di metodologie di ricerca, studi traslazionali, ricerca sugli esiti e lo sviluppo di nuove tecnologie. Possono candidarsi istituzioni accademiche e di ricerca, comprese organizzazioni non profit ed enti stranieri con sede al di fuori degli Stati Uniti.</t>
         </is>
       </c>
       <c r="AE4" s="4" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="AF4" s="4" t="n">
         <v>46312</v>
@@ -1126,7 +1124,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>GG-PAR-25-226</t>
+          <t>WEB-00773cbd93aa</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -1146,11 +1144,11 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Sviluppo clinico precoce integrato (fase 1-2a) di nuovi agenti terapeutici per l'Alzheimer e le demenze correlate (UG3/UH3)</t>
+          <t>Finanziamento ponte per la ricerca interrotta sulle malattie neurodegenerative (BFDN)</t>
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>46345</v>
+        <v>46325</v>
       </c>
       <c r="G5" s="5">
         <f>IF(F5="","",F5-TODAY())</f>
@@ -1163,61 +1161,69 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>National Institutes of Health</t>
+          <t>Michael J. Fox Foundation</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>Grants.gov</t>
+          <t>Michael J. Fox Foundation</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>National Institutes of Health – PAR-25-226</t>
+          <t>Bridge Funding for Disrupted Neurodegenerative Research Grant Program (BFDN) Powering the Next Generation of Research</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>Seamless Early-Stage Clinical Drug Development (Phase 1 to 2a) for Novel therapeutic Agents for the Spectrum of Alzheimer's Disease (AD) and AD-related Dementias (ADRD) (UG3/UH3 Clinical Trial Required)</t>
+          <t>Bridge Funding for Disrupted Neurodegenerative Research Grant Program (BFDN) Powering the Next Generation of Research</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Invecchiamento</t>
+          <t>Parkinson, Invecchiamento, Altre malattie e riabilitazione</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>dementi, alzheimer</t>
+          <t>parkinson, dementi, alzheimer, neurodegenerat, neurological disease</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>Riguarda la malattia di Alzheimer e le demenze correlate, ma è incentrato sullo sviluppo farmacologico precoce e non su interventi riabilitativi.</t>
-        </is>
-      </c>
-      <c r="P5" s="6" t="n"/>
-      <c r="Q5" s="6" t="n"/>
+          <t>Finanzia la continuità di progetti di ricerca su Parkinson, Alzheimer e demenze, senza una focalizzazione specifica sulla riabilitazione.</t>
+        </is>
+      </c>
+      <c r="P5" s="6" t="n">
+        <v>250000</v>
+      </c>
+      <c r="Q5" s="6" t="n">
+        <v>250000</v>
+      </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="S5" s="2" t="n"/>
+      <c r="S5" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t>Non stimabile – dati insufficienti</t>
+          <t>Bassa – 1 progetti finanziabili (stima: tasso storico non disponibile)</t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t>Interamente finanziato</t>
-        </is>
-      </c>
-      <c r="V5" s="4" t="n">
-        <v>45618</v>
-      </c>
-      <c r="W5" s="2" t="n"/>
+          <t>Co-finanziamento richiesto (25% a carico del beneficiario)</t>
+        </is>
+      </c>
+      <c r="V5" s="4" t="n"/>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
+          <t>12 mesi</t>
+        </is>
+      </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
           <t>Ricerca</t>
@@ -1225,13 +1231,13 @@
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t>Nonprofits that do not have a 501(c)(3) status with the IRS, other than institutions of higher education; County governments; City or township governments; Independent school districts; Public housing authorities/Indian housing authorities; Private institutions of higher education; For profit organizations other than small businesses; Nonprofits having a 501(c)(3) status with the IRS, other than i</t>
+          <t>Ricercatori principali a inizio carriera (Early Stage Investigator secondo i criteri NIH o entro 7 anni dalla qualifica) titolari di grant federali statunitensi interrotti</t>
         </is>
       </c>
       <c r="Z5" s="3" t="n"/>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>Ammessi anche enti non statunitensi (call NIH completa)</t>
+          <t>Mondiale</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
@@ -1241,16 +1247,16 @@
       </c>
       <c r="AC5" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/357343</t>
+          <t>https://www.michaeljfox.org/grant/bridge-funding-disrupted-neurodegenerative-research-grant-program-bfdn-powering-next</t>
         </is>
       </c>
       <c r="AD5" s="3" t="inlineStr">
         <is>
-          <t>Il bando invita a presentare proposte per lo sviluppo clinico precoce di nuovi agenti farmacologici non amiloidi e non tau per la malattia di Alzheimer e le demenze correlate. Tramite il meccanismo a fasi UG3/UH3, il bando unisce protocolli di sperimentazione di fase 1 con fasi 1b/2a per valutare sicurezza, tollerabilità ed efficacia su sintomi cognitivi o neuropsichiatrici in diversi stadi di malattia. L'avanzamento tra le fasi è subordinato a traguardi predefiniti. Possono partecipare istituti accademici, organizzazioni sanitarie, enti di ricerca pubblici e privati e istituzioni straniere non statunitensi.</t>
+          <t>Il programma congiunto promosso da Alzheimer's Association, The Michael J. Fox Foundation e Robertson Foundation fornisce finanziamenti ponte per garantire la continuità a progetti di ricerca sulle malattie neurodegenerative (morbo di Parkinson, malattia di Alzheimer, demenza frontotemporale, demenza a corpi di Lewy e parkinsonismi atipici). L'iniziativa è specificamente rivolta a ricercatori a inizio carriera (Early Stage Investigator secondo i criteri NIH o entro 7 anni da tale qualifica) i cui finanziamenti federali statunitensi abbiano subito interruzioni, ritardi o tagli per cambiamenti operativi o di priorità. Il contributo, fino a un massimo di 250.000 dollari per una durata compresa tra 3 e 12 mesi, copre stipendi e costi diretti, richiedendo un cofinanziamento istituzionale fino al 25%.</t>
         </is>
       </c>
       <c r="AE5" s="4" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="AF5" s="4" t="n">
         <v>46312</v>
@@ -1260,7 +1266,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>EU-HORIZON-HLTH-2027-02-DISEASE-01-two-stage</t>
+          <t>GG-PAR-25-226</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -1280,11 +1286,11 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Interventi sanitari innovativi per le malattie non trasmissibili</t>
+          <t>Sviluppo clinico precoce integrato (fase 1-2a) di nuovi agenti terapeutici per l'Alzheimer e le demenze correlate (UG3/UH3)</t>
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>46435</v>
+        <v>46345</v>
       </c>
       <c r="G6" s="5">
         <f>IF(F6="","",F6-TODAY())</f>
@@ -1292,61 +1298,55 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>In apertura</t>
+          <t>In scadenza (≤30 gg)</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Commissione europea</t>
+          <t>National Institutes of Health</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>EU Funding &amp; Tenders Portal</t>
+          <t>Grants.gov</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>Horizon Europe – HORIZON  Research and Innovation Actions</t>
+          <t>National Institutes of Health – PAR-25-226</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>Innovative healthcare interventions for non-communicable diseases</t>
+          <t>Seamless Early-Stage Clinical Drug Development (Phase 1 to 2a) for Novel therapeutic Agents for the Spectrum of Alzheimer's Disease (AD) and AD-related Dementias (ADRD) (UG3/UH3 Clinical Trial Required)</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Tecnologie riabilitazione, Altre malattie e riabilitazione</t>
+          <t>Invecchiamento</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>wearable, disabilit</t>
+          <t>dementi, alzheimer</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>Bando incentrato su interventi innovativi e gestione clinica di patologie croniche cardiache e respiratorie, senza focus esclusivo sulla riabilitazione.</t>
-        </is>
-      </c>
-      <c r="P6" s="6" t="n">
-        <v>63800000</v>
-      </c>
-      <c r="Q6" s="6" t="n">
-        <v>8000000</v>
-      </c>
+          <t>Riguarda la malattia di Alzheimer e le demenze correlate, ma è incentrato sullo sviluppo farmacologico precoce e non su interventi riabilitativi.</t>
+        </is>
+      </c>
+      <c r="P6" s="6" t="n"/>
+      <c r="Q6" s="6" t="n"/>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="n">
-        <v>8</v>
-      </c>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="n"/>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t>Media – 8 progetti finanziabili (stima: tasso storico non disponibile)</t>
+          <t>Non stimabile – dati insufficienti</t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
@@ -1355,7 +1355,7 @@
         </is>
       </c>
       <c r="V6" s="4" t="n">
-        <v>46324</v>
+        <v>45618</v>
       </c>
       <c r="W6" s="2" t="n"/>
       <c r="X6" s="2" t="inlineStr">
@@ -1365,17 +1365,13 @@
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t>Enti di ricerca, università, strutture sanitarie, PMI, startup, autorità regolatorie e organizzazioni di pazienti.</t>
-        </is>
-      </c>
-      <c r="Z6" s="3" t="inlineStr">
-        <is>
-          <t>Consorzio: min. 3 enti indipendenti da 3 paesi UE/associati (regola standard, verificare il topic)</t>
-        </is>
-      </c>
+          <t>Public housing authorities/Indian housing authorities; Public and State controlled institutions of higher education; Special district governments; Independent school districts; State governments; Native American tribal governments (Federally recognized); County governments; Nonprofits that do not have a 501(c)(3) status with the IRS, other than institutions of higher education; Private institution</t>
+        </is>
+      </c>
+      <c r="Z6" s="3" t="n"/>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>Stati membri UE e paesi associati (altri paesi secondo le condizioni del topic)</t>
+          <t>Ammessi anche enti non statunitensi (call NIH completa)</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
@@ -1385,16 +1381,16 @@
       </c>
       <c r="AC6" s="7" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-HLTH-2027-02-DISEASE-01-two-stage</t>
+          <t>https://www.grants.gov/search-results-detail/357343</t>
         </is>
       </c>
       <c r="AD6" s="3" t="inlineStr">
         <is>
-          <t>Il bando punta a ridurre l'impatto di specifiche malattie croniche non trasmissibili, tra cui patologie cardiovascolari, diabete, malattie respiratorie e renali croniche. Si finanzia la realizzazione di studi clinici in fase precoce per validare interventi terapeutici o di gestione della patologia innovativi o perfezionati, supportati da prove di concetto su sicurezza ed efficacia clinica. Le proposte devono integrare tecnologie digitali (come intelligenza artificiale o dispositivi indossabili) per il monitoraggio a lungo termine a domicilio. Possono partecipare consorzi internazionali composti da università, enti di ricerca clinica, ospedali, piccole e medie imprese, startup e organizzazioni di pazienti, promuovendo anche l'inclusione di competenze socio-umanistiche e l'interazione con autorità regolatorie per favorire la futura scalabilità degli interventi.</t>
+          <t>Il bando invita a presentare proposte per lo sviluppo clinico precoce di nuovi agenti farmacologici non amiloidi e non tau per la malattia di Alzheimer e le demenze correlate. Tramite il meccanismo a fasi UG3/UH3, il bando unisce protocolli di sperimentazione di fase 1 con fasi 1b/2a per valutare sicurezza, tollerabilità ed efficacia su sintomi cognitivi o neuropsichiatrici in diversi stadi di malattia. L'avanzamento tra le fasi è subordinato a traguardi predefiniti. Possono partecipare istituti accademici, organizzazioni sanitarie, enti di ricerca pubblici e privati e istituzioni straniere non statunitensi.</t>
         </is>
       </c>
       <c r="AE6" s="4" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="AF6" s="4" t="n">
         <v>46312</v>
@@ -1404,7 +1400,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>EU-HORIZON-HLTH-2027-01-DISEASE-10</t>
+          <t>EU-HORIZON-HLTH-2027-02-DISEASE-01-two-stage</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -1424,7 +1420,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Prevenzione e gestione delle malattie croniche non trasmissibili nei bambini e nei giovani (GACD)</t>
+          <t>Interventi sanitari innovativi per le malattie non trasmissibili</t>
         </is>
       </c>
       <c r="F7" s="4" t="n">
@@ -1456,29 +1452,29 @@
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>Prevention and management of chronic non-communicable diseases in children and young people (GACD)</t>
+          <t>Innovative healthcare interventions for non-communicable diseases</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Altre malattie e riabilitazione</t>
+          <t>Tecnologie riabilitazione, Altre malattie e riabilitazione</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>neurological disorder, disabilit</t>
+          <t>wearable, disabilit</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>Finanzia la ricerca sull'implementazione per la gestione di patologie croniche non trasmissibili nei giovani, ambito che include percorsi di cura complessi ma non esclusivamente riabilitativi.</t>
+          <t>Bando incentrato su interventi innovativi e gestione clinica di patologie croniche cardiache e respiratorie, senza focus esclusivo sulla riabilitazione.</t>
         </is>
       </c>
       <c r="P7" s="6" t="n">
-        <v>11800000</v>
+        <v>63800000</v>
       </c>
       <c r="Q7" s="6" t="n">
-        <v>4000000</v>
+        <v>8000000</v>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
@@ -1486,11 +1482,11 @@
         </is>
       </c>
       <c r="S7" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t>Bassa – 3 progetti finanziabili (stima: tasso storico non disponibile)</t>
+          <t>Media – 8 progetti finanziabili (stima: tasso storico non disponibile)</t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
@@ -1509,7 +1505,7 @@
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t>Ricercatori, professionisti sanitari, erogatori di servizi, decisori politici e stakeholder locali</t>
+          <t>Enti di ricerca, università, strutture sanitarie, PMI, startup, autorità regolatorie e organizzazioni di pazienti.</t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
@@ -1529,26 +1525,26 @@
       </c>
       <c r="AC7" s="7" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-HLTH-2027-01-DISEASE-10</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-HLTH-2027-02-DISEASE-01-two-stage</t>
         </is>
       </c>
       <c r="AD7" s="3" t="inlineStr">
         <is>
-          <t>In collaborazione con la Global Alliance for Chronic Diseases (GACD), il bando sostiene la ricerca sull'implementazione di interventi evidence-based per la prevenzione, la diagnosi precoce e la gestione a lungo termine delle malattie croniche non trasmissibili in soggetti tra 1 e 24 anni. Il focus riguarda popolazioni vulnerabili in paesi a basso e medio reddito o comunità svantaggiate in paesi ad alto reddito. Si finanziano modelli di cura integrati, percorsi di transizione dall'assistenza pediatrica a quella per adulti, supporto ai caregiver e strategie costo-efficaci. Possono partecipare ricercatori, operatori sanitari e istituzioni di ricerca appartenenti a consorzi eleggibili secondo le regole di Horizon Europe.</t>
+          <t>Il bando punta a ridurre l'impatto di specifiche malattie croniche non trasmissibili, tra cui patologie cardiovascolari, diabete, malattie respiratorie e renali croniche. Si finanzia la realizzazione di studi clinici in fase precoce per validare interventi terapeutici o di gestione della patologia innovativi o perfezionati, supportati da prove di concetto su sicurezza ed efficacia clinica. Le proposte devono integrare tecnologie digitali (come intelligenza artificiale o dispositivi indossabili) per il monitoraggio a lungo termine a domicilio. Possono partecipare consorzi internazionali composti da università, enti di ricerca clinica, ospedali, piccole e medie imprese, startup e organizzazioni di pazienti, promuovendo anche l'inclusione di competenze socio-umanistiche e l'interazione con autorità regolatorie per favorire la futura scalabilità degli interventi.</t>
         </is>
       </c>
       <c r="AE7" s="4" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="AF7" s="4" t="n">
-        <v>46313</v>
+        <v>46312</v>
       </c>
       <c r="AG7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>WEB-6768384ca0cb</t>
+          <t>EU-HORIZON-HLTH-2027-01-DISEASE-10</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -1568,82 +1564,84 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Programma per lo sviluppo della pipeline terapeutica nella malattia di Parkinson</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="n"/>
+          <t>Prevenzione e gestione delle malattie croniche non trasmissibili nei bambini e nei giovani (GACD)</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>46435</v>
+      </c>
       <c r="G8" s="5">
         <f>IF(F8="","",F8-TODAY())</f>
         <v/>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Scadenza da verificare</t>
+          <t>In apertura</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Michael J. Fox Foundation</t>
+          <t>Commissione europea</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>Michael J. Fox Foundation</t>
+          <t>EU Funding &amp; Tenders Portal</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>Parkinson's Disease Therapeutics Pipeline Program</t>
+          <t>Horizon Europe – HORIZON  Research and Innovation Actions</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>Parkinson's Disease Therapeutics Pipeline Program</t>
+          <t>Prevention and management of chronic non-communicable diseases in children and young people (GACD)</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Parkinson</t>
+          <t>Altre malattie e riabilitazione</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>parkinson</t>
+          <t>neurological disorder, disabilit</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>Focalizzato sullo sviluppo terapeutico e farmacologico preclinico e clinico per il Parkinson, senza un focus specifico sulla riabilitazione.</t>
+          <t>Finanzia la ricerca sull'implementazione per la gestione di patologie croniche non trasmissibili nei giovani, ambito che include percorsi di cura complessi ma non esclusivamente riabilitativi.</t>
         </is>
       </c>
       <c r="P8" s="6" t="n">
-        <v>250000</v>
+        <v>11800000</v>
       </c>
       <c r="Q8" s="6" t="n">
-        <v>5000000</v>
+        <v>4000000</v>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="n"/>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t>Non stimabile – dati insufficienti</t>
+          <t>Bassa – 3 progetti finanziabili (stima: tasso storico non disponibile)</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t>Non indicato</t>
-        </is>
-      </c>
-      <c r="V8" s="4" t="n"/>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>36 mesi</t>
-        </is>
-      </c>
+          <t>Interamente finanziato</t>
+        </is>
+      </c>
+      <c r="V8" s="4" t="n">
+        <v>46324</v>
+      </c>
+      <c r="W8" s="2" t="n"/>
       <c r="X8" s="2" t="inlineStr">
         <is>
           <t>Ricerca</t>
@@ -1651,17 +1649,17 @@
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t>Imprese biotech/pharma, partenariati accademia-industria e istituti accademici</t>
+          <t>Ricercatori, professionisti sanitari, erogatori di servizi, decisori politici e stakeholder locali</t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t>Aperto a collaborazioni accademia-industria, singole aziende o progetti a guida accademica</t>
+          <t>Consorzio: min. 3 enti indipendenti da 3 paesi UE/associati (regola standard, verificare il topic)</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>Mondiale</t>
+          <t>Stati membri UE e paesi associati (altri paesi secondo le condizioni del topic)</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
@@ -1671,119 +1669,121 @@
       </c>
       <c r="AC8" s="7" t="inlineStr">
         <is>
-          <t>https://www.michaeljfox.org/grant/parkinsons-disease-therapeutics-pipeline-program</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-HLTH-2027-01-DISEASE-10</t>
         </is>
       </c>
       <c r="AD8" s="3" t="inlineStr">
         <is>
-          <t>Il Therapeutics Pipeline Program della Michael J. Fox Foundation finanzia lo sviluppo preclinico e clinico di interventi terapeutici modificanti la malattia o mirati al controllo sintomatico del Parkinson, integrando strumenti biomarcatori decisionali. Il programma supporta progetti da uno a tre anni con contributi compresi generalmente tra 250.000 e oltre 5 milioni di dollari, a seconda della fase di avanzamento. La candidatura è aperta a imprese biotech, collaborazioni accademia-industria e, in casi specifici, a gruppi esclusivamente accademici. Il processo di selezione è strutturato in due fasi: invio continuo di pre-proposte e, su invito, presentazione della proposta completa secondo scadenze cicliche periodiche. Sono esclusi studi su integratori alimentari o scoperta di target precoci.</t>
+          <t>In collaborazione con la Global Alliance for Chronic Diseases (GACD), il bando sostiene la ricerca sull'implementazione di interventi evidence-based per la prevenzione, la diagnosi precoce e la gestione a lungo termine delle malattie croniche non trasmissibili in soggetti tra 1 e 24 anni. Il focus riguarda popolazioni vulnerabili in paesi a basso e medio reddito o comunità svantaggiate in paesi ad alto reddito. Si finanziano modelli di cura integrati, percorsi di transizione dall'assistenza pediatrica a quella per adulti, supporto ai caregiver e strategie costo-efficaci. Possono partecipare ricercatori, operatori sanitari e istituzioni di ricerca appartenenti a consorzi eleggibili secondo le regole di Horizon Europe.</t>
         </is>
       </c>
       <c r="AE8" s="4" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="AF8" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AG8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>GG-RFA-NS-26-028</t>
+          <t>WEB-6768384ca0cb</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Da verificare</t>
+          <t>Sì</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Tecnologia / innovazione</t>
+          <t>Ricerca clinica</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Iniziativa HEAL: ottimizzazione dei dispositivi medici terapeutici attraverso la ricerca meccanicistica interdisciplinare (RM1)</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>46325</v>
-      </c>
+          <t>Programma per lo sviluppo della pipeline terapeutica nella malattia di Parkinson</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="n"/>
       <c r="G9" s="5">
         <f>IF(F9="","",F9-TODAY())</f>
         <v/>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>In scadenza (≤30 gg)</t>
+          <t>Scadenza da verificare</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>National Institutes of Health</t>
+          <t>Michael J. Fox Foundation</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>Grants.gov</t>
+          <t>Michael J. Fox Foundation</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>National Institutes of Health – RFA-NS-26-028</t>
+          <t>Parkinson's Disease Therapeutics Pipeline Program</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>HEAL Initiative: Optimization of Therapeutic Medical Devices through Team Science Mechanistic Research (RM1)</t>
+          <t>Parkinson's Disease Therapeutics Pipeline Program</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Ictus, Altre malattie e riabilitazione</t>
+          <t>Parkinson</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>stroke, neurological disorder</t>
+          <t>parkinson</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>Supporta la ricerca sui meccanismi d'azione di dispositivi medici terapeutici per patologie neurologiche e dolore cronico, altamente rilevanti per la neuroriabilitazione.</t>
-        </is>
-      </c>
-      <c r="P9" s="6" t="n"/>
-      <c r="Q9" s="6" t="n"/>
+          <t>Focalizzato sullo sviluppo terapeutico e farmacologico preclinico e clinico per il Parkinson, senza un focus specifico sulla riabilitazione.</t>
+        </is>
+      </c>
+      <c r="P9" s="6" t="n">
+        <v>250000</v>
+      </c>
+      <c r="Q9" s="6" t="n">
+        <v>5000000</v>
+      </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="S9" s="2" t="n">
-        <v>4</v>
-      </c>
+      <c r="S9" s="2" t="n"/>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t>Bassa – 4 progetti finanziabili (stima: tasso storico non disponibile)</t>
+          <t>Non stimabile – dati insufficienti</t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t>Interamente finanziato</t>
-        </is>
-      </c>
-      <c r="V9" s="4" t="n">
-        <v>46097</v>
-      </c>
-      <c r="W9" s="2" t="n"/>
+          <t>Non indicato</t>
+        </is>
+      </c>
+      <c r="V9" s="4" t="n"/>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>36 mesi</t>
+        </is>
+      </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
           <t>Ricerca</t>
@@ -1791,17 +1791,17 @@
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t>For profit organizations other than small businesses; Public housing authorities/Indian housing authorities; Independent school districts; Small businesses; County governments; Private institutions of higher education; Others (see text field entitled "Additional Information on Eligibility" for clarification); Nonprofits having a 501(c)(3) status with the IRS, other than institutions of higher educ</t>
+          <t>Imprese biotech/pharma, partenariati accademia-industria e istituti accademici</t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t>Team scientifici interdisciplinari comprendenti competenze ingegneristiche, biologiche, computazionali e cliniche</t>
+          <t>Aperto a collaborazioni accademia-industria, singole aziende o progetti a guida accademica</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>Enti esteri: da verificare nel bando</t>
+          <t>Mondiale</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
@@ -1811,16 +1811,16 @@
       </c>
       <c r="AC9" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/361520</t>
+          <t>https://www.michaeljfox.org/grant/parkinsons-disease-therapeutics-pipeline-program</t>
         </is>
       </c>
       <c r="AD9" s="3" t="inlineStr">
         <is>
-          <t>Il National Institute of Neurological Disorders and Stroke (NINDS), nell'ambito dell'iniziativa NIH HEAL, preannuncia un'opportunità di finanziamento destinata a indagare i meccanismi d'azione dei dispositivi medici terapeutici per ottimizzare i risultati clinici nelle patologie neurologiche e nel trattamento del dolore. La call intende finanziare team scientifici altamente interdisciplinari (con competenze che spaziano dall'ingegneria e biologia alla clinica, biostatistica, intelligenza artificiale e sperimentazioni cliniche). Le attività ammissibili comprendono studi clinici meccanicistici, modelli computazionali o simulazioni e ricerche precliniche su modelli animali, applicabili sia a dispositivi sperimentali sia a tecnologie già approvate dalla FDA e impiegate nella pratica clinica. La partecipazione è aperta anche a istituzioni di ricerca estere non statunitensi.</t>
+          <t>Il Therapeutics Pipeline Program della Michael J. Fox Foundation finanzia lo sviluppo preclinico e clinico di interventi terapeutici modificanti la malattia o mirati al controllo sintomatico del Parkinson, integrando strumenti biomarcatori decisionali. Il programma supporta progetti da uno a tre anni con contributi compresi generalmente tra 250.000 e oltre 5 milioni di dollari, a seconda della fase di avanzamento. La candidatura è aperta a imprese biotech, collaborazioni accademia-industria e, in casi specifici, a gruppi esclusivamente accademici. Il processo di selezione è strutturato in due fasi: invio continuo di pre-proposte e, su invito, presentazione della proposta completa secondo scadenze cicliche periodiche. Sono esclusi studi su integratori alimentari o scoperta di target precoci.</t>
         </is>
       </c>
       <c r="AE9" s="4" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="AF9" s="4" t="n">
         <v>46312</v>
@@ -1830,7 +1830,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>GG-HT942526SCIRPTRA</t>
+          <t>GG-RFA-NS-26-028</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -1845,16 +1845,16 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Ricerca clinica</t>
+          <t>Tecnologia / innovazione</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Programma di ricerca sulle lesioni del midollo spinale del Dipartimento della Difesa: finanziamento per la ricerca traslazionale</t>
+          <t>Iniziativa HEAL: ottimizzazione dei dispositivi medici terapeutici attraverso la ricerca meccanicistica interdisciplinare (RM1)</t>
         </is>
       </c>
       <c r="F10" s="4" t="n">
-        <v>46338</v>
+        <v>46325</v>
       </c>
       <c r="G10" s="5">
         <f>IF(F10="","",F10-TODAY())</f>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Defense Health Agency Contracting Activity - DHACA</t>
+          <t>National Institutes of Health</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1877,32 +1877,30 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>Defense Health Agency Contracting Activity - DHACA – HT942526SCIRPTRA</t>
+          <t>National Institutes of Health – RFA-NS-26-028</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>DoW Spinal Cord Injury, Translational Research Award</t>
+          <t>HEAL Initiative: Optimization of Therapeutic Medical Devices through Team Science Mechanistic Research (RM1)</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Altre malattie e riabilitazione</t>
+          <t>Ictus, Altre malattie e riabilitazione</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>spinal cord injur</t>
+          <t>stroke, neurological disorder</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>Dedicato alla ricerca traslazionale per l'applicazione clinica nelle lesioni del midollo spinale, patologia cardine della riabilitazione neurologica.</t>
-        </is>
-      </c>
-      <c r="P10" s="6" t="n">
-        <v>8320000</v>
-      </c>
+          <t>Supporta la ricerca sui meccanismi d'azione di dispositivi medici terapeutici per patologie neurologiche e dolore cronico, altamente rilevanti per la neuroriabilitazione.</t>
+        </is>
+      </c>
+      <c r="P10" s="6" t="n"/>
       <c r="Q10" s="6" t="n"/>
       <c r="R10" s="2" t="inlineStr">
         <is>
@@ -1923,7 +1921,7 @@
         </is>
       </c>
       <c r="V10" s="4" t="n">
-        <v>46147</v>
+        <v>46097</v>
       </c>
       <c r="W10" s="2" t="n"/>
       <c r="X10" s="2" t="inlineStr">
@@ -1933,12 +1931,12 @@
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t>Unrestricted (i.e., open to any type of entity above), subject to any clarification in text field entitled "Additional Information on Eligibility"</t>
+          <t>Nonprofits having a 501(c)(3) status with the IRS, other than institutions of higher education; Native American tribal organizations (other than Federally recognized tribal governments); State governments; Special district governments; For profit organizations other than small businesses; Public and State controlled institutions of higher education; Independent school districts; City or township g</t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t>Obbligatorio almeno un partner comunitario esperto per esperienza diretta di lesione midollare; ammessa opzione a due PI con ricercatore junior.</t>
+          <t>Team scientifici interdisciplinari comprendenti competenze ingegneristiche, biologiche, computazionali e cliniche</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1953,26 +1951,26 @@
       </c>
       <c r="AC10" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/362222</t>
+          <t>https://www.grants.gov/search-results-detail/361520</t>
         </is>
       </c>
       <c r="AD10" s="3" t="inlineStr">
         <is>
-          <t>Il Translational Research Award, nell'ambito del programma di ricerca sulle lesioni del midollo spinale (SCIRP), sostiene progetti di ricerca traslazionale mirati ad accelerare il passaggio di idee e interventi innovativi dal laboratorio alle applicazioni cliniche per pazienti con lesioni midollari. Le proposte devono includere obbligatoriamente come partner almeno un membro o consulente della comunità con lesione spinale vissuta in prima persona o un rappresentante di organizzazioni attive nel settore. È prevista l'opzione di collaborazione paritaria che consente a un ricercatore esperto di affiancare un ricercatore a inizio carriera nella guida del progetto. Possono partecipare atenei, enti ospedalieri, istituti di ricerca pubblici o privati e organizzazioni specializzate.</t>
+          <t>Il National Institute of Neurological Disorders and Stroke (NINDS), nell'ambito dell'iniziativa NIH HEAL, preannuncia un'opportunità di finanziamento destinata a indagare i meccanismi d'azione dei dispositivi medici terapeutici per ottimizzare i risultati clinici nelle patologie neurologiche e nel trattamento del dolore. La call intende finanziare team scientifici altamente interdisciplinari (con competenze che spaziano dall'ingegneria e biologia alla clinica, biostatistica, intelligenza artificiale e sperimentazioni cliniche). Le attività ammissibili comprendono studi clinici meccanicistici, modelli computazionali o simulazioni e ricerche precliniche su modelli animali, applicabili sia a dispositivi sperimentali sia a tecnologie già approvate dalla FDA e impiegate nella pratica clinica. La partecipazione è aperta anche a istituzioni di ricerca estere non statunitensi.</t>
         </is>
       </c>
       <c r="AE10" s="4" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="AF10" s="4" t="n">
-        <v>46313</v>
+        <v>46312</v>
       </c>
       <c r="AG10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>GG-HT942526SCIRPCTA</t>
+          <t>WEB-eb079c6b7229</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -1987,16 +1985,16 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Ricerca clinica</t>
+          <t>Tecnologia / innovazione</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>DoW Ricerca sulle lesioni del midollo spinale, finanziamento per trial clinici</t>
+          <t>Finanziamenti per le tecnologie assistive nella sclerosi laterale amiotrofica (SLA)</t>
         </is>
       </c>
       <c r="F11" s="4" t="n">
-        <v>46338</v>
+        <v>46329</v>
       </c>
       <c r="G11" s="5">
         <f>IF(F11="","",F11-TODAY())</f>
@@ -2009,83 +2007,79 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Defense Health Agency Contracting Activity - DHACA</t>
+          <t>ALS Association</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>Grants.gov</t>
+          <t>ALS Association</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>Defense Health Agency Contracting Activity - DHACA – HT942526SCIRPCTA</t>
+          <t>AssistiveTech2026</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>DoW Spinal Cord Injury, Clinical Trial Award</t>
+          <t>AssistiveTech2026</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Altre malattie e riabilitazione</t>
+          <t>Tecnologie riabilitazione</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>spinal cord injur</t>
+          <t>assistive technolog, brain-computer interface, robot, mobility aid, disabilit</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>Finanzia trial clinici focalizzati sul trattamento e sulla gestione funzionale delle lesioni del midollo spinale.</t>
+          <t>Finanzia lo sviluppo e l'adattamento di tecnologie assistive per migliorare l'autonomia e la qualità della vita di persone affette da SLA.</t>
         </is>
       </c>
       <c r="P11" s="6" t="n">
-        <v>9760000</v>
-      </c>
-      <c r="Q11" s="6" t="n"/>
+        <v>400000</v>
+      </c>
+      <c r="Q11" s="6" t="n">
+        <v>400000</v>
+      </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="S11" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t>Bassa – 2 progetti finanziabili (stima: tasso storico non disponibile)</t>
+          <t>Bassa – 1 progetti finanziabili (stima: tasso storico non disponibile)</t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t>Interamente finanziato</t>
-        </is>
-      </c>
-      <c r="V11" s="4" t="n">
-        <v>46147</v>
-      </c>
-      <c r="W11" s="2" t="n"/>
+          <t>Non indicato</t>
+        </is>
+      </c>
+      <c r="V11" s="4" t="n"/>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>24 mesi</t>
+        </is>
+      </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>Ricerca</t>
-        </is>
-      </c>
-      <c r="Y11" s="3" t="inlineStr">
-        <is>
-          <t>Unrestricted (i.e., open to any type of entity above), subject to any clarification in text field entitled "Additional Information on Eligibility"</t>
-        </is>
-      </c>
-      <c r="Z11" s="3" t="inlineStr">
-        <is>
-          <t>Obbligatori almeno 2 partner della comunità con esperienza di lesione midollare; possibile collaborazione tra 2 PI</t>
-        </is>
-      </c>
+          <t>Innovazione</t>
+        </is>
+      </c>
+      <c r="Y11" s="3" t="n"/>
+      <c r="Z11" s="3" t="n"/>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>Enti esteri: da verificare nel bando</t>
+          <t>Mondiale</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
@@ -2095,26 +2089,26 @@
       </c>
       <c r="AC11" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/362224</t>
+          <t>http://www.als.org/AssistiveTech2026</t>
         </is>
       </c>
       <c r="AD11" s="3" t="inlineStr">
         <is>
-          <t>Il bando Clinical Trial Award del programma SCIRP (anno fiscale 2026) finanzia la rapida attuazione di studi clinici con un potenziale impatto significativo sul trattamento o sulla gestione delle persone con lesione del midollo spinale. L'opportunità include un'opzione di partenariato per ricercatori all'inizio della carriera (Early-Career Partnership Option), che consente la partecipazione di due Principal Investigator, purché almeno uno sia un ricercatore junior. Le proposte devono obbligatoriamente coinvolgere almeno due rappresentanti o partner della comunità con esperienza diretta di lesione midollare, che collaboreranno attivamente fornendo consulenza durante l'intera pianificazione e implementazione dello studio clinico.</t>
+          <t>Questo programma di finanziamento promosso dalla ALS Association sostiene la ricerca e lo sviluppo di tecnologie assistive dedicate alle persone affette da sclerosi laterale amiotrofica (SLA). L'obiettivo è accelerare la realizzazione di soluzioni tecnologiche innovative o l'adattamento di ausili esistenti per facilitare la comunicazione, la mobilità, la respirazione e la gestione delle attività della vita quotidiana, migliorando la qualità di vita e l'autonomia dei pazienti e riducendo il carico dei caregiver. Il bando finanzia progetti che abbiano già superato la fase iniziale di scoperta, con l'aspettativa che il dispositivo raggiunga la disponibilità commerciale entro 3-5 anni dal termine dello studio. È richiesta una lettera di intenti preliminare.</t>
         </is>
       </c>
       <c r="AE11" s="4" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="AF11" s="4" t="n">
-        <v>46313</v>
+        <v>46317</v>
       </c>
       <c r="AG11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>GG-HT942526SCIRPCTRA</t>
+          <t>GG-HT942526SCIRPTRA</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -2134,7 +2128,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>DoW Ricerca sulle lesioni del midollo spinale, finanziamento per la ricerca clinica traslazionale</t>
+          <t>Programma di ricerca sulle lesioni del midollo spinale del Dipartimento della Difesa: finanziamento per la ricerca traslazionale</t>
         </is>
       </c>
       <c r="F12" s="4" t="n">
@@ -2161,12 +2155,12 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>Defense Health Agency Contracting Activity - DHACA – HT942526SCIRPCTRA</t>
+          <t>Defense Health Agency Contracting Activity - DHACA – HT942526SCIRPTRA</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>DoW Spinal Cord Injury, Clinical Translation Research Award</t>
+          <t>DoW Spinal Cord Injury, Translational Research Award</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -2176,16 +2170,16 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>rehabilitat, spinal cord injur</t>
+          <t>spinal cord injur</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>Finanzia ricerca clinica traslazionale volta a identificare le opzioni più efficaci di riabilitazione e trattamento nelle lesioni midollari.</t>
+          <t>Dedicato alla ricerca traslazionale per l'applicazione clinica nelle lesioni del midollo spinale, patologia cardine della riabilitazione neurologica.</t>
         </is>
       </c>
       <c r="P12" s="6" t="n">
-        <v>6120000</v>
+        <v>8320000</v>
       </c>
       <c r="Q12" s="6" t="n"/>
       <c r="R12" s="2" t="inlineStr">
@@ -2194,11 +2188,11 @@
         </is>
       </c>
       <c r="S12" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t>Bassa – 3 progetti finanziabili (stima: tasso storico non disponibile)</t>
+          <t>Bassa – 4 progetti finanziabili (stima: tasso storico non disponibile)</t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
@@ -2222,7 +2216,7 @@
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t>Obbligatori almeno due partner della comunità di pazienti; opzione con due PI di cui uno a inizio carriera</t>
+          <t>Obbligatorio almeno un partner comunitario esperto per esperienza diretta di lesione midollare; ammessa opzione a due PI con ricercatore junior.</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -2237,26 +2231,26 @@
       </c>
       <c r="AC12" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/362225</t>
+          <t>https://www.grants.gov/search-results-detail/362222</t>
         </is>
       </c>
       <c r="AD12" s="3" t="inlineStr">
         <is>
-          <t>Il bando Clinical Translation Research Award dello SCIRP per l'anno fiscale 2026 promuove ricerche cliniche emergenti o ad alto impatto che necessitano di studi preliminari, di fattibilità o di ottimizzazione per preparare futuri trial clinici definitivi. Tra gli obiettivi principali rientrano l'accelerazione del trasferimento clinico di nuove tecniche o interventi e l'identificazione delle migliori opzioni diagnostiche, terapeutiche e riabilitative per supportare le decisioni di pazienti e clinici nell'ambito delle lesioni del midollo spinale. Il bando include un'opzione per due Principal Investigator (con almeno un ricercatore junior) e impone il coinvolgimento di almeno due partner della comunità di pazienti come consulenti del progetto.</t>
+          <t>Il Translational Research Award, nell'ambito del programma di ricerca sulle lesioni del midollo spinale (SCIRP), sostiene progetti di ricerca traslazionale mirati ad accelerare il passaggio di idee e interventi innovativi dal laboratorio alle applicazioni cliniche per pazienti con lesioni midollari. Le proposte devono includere obbligatoriamente come partner almeno un membro o consulente della comunità con lesione spinale vissuta in prima persona o un rappresentante di organizzazioni attive nel settore. È prevista l'opzione di collaborazione paritaria che consente a un ricercatore esperto di affiancare un ricercatore a inizio carriera nella guida del progetto. Possono partecipare atenei, enti ospedalieri, istituti di ricerca pubblici o privati e organizzazioni specializzate.</t>
         </is>
       </c>
       <c r="AE12" s="4" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="AF12" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AG12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>GG-HT942526SCIRPIIRA</t>
+          <t>GG-HT942526SCIRPCTA</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -2276,7 +2270,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>DoW Ricerca sulle lesioni del midollo spinale, finanziamento per la ricerca promossa dal ricercatore</t>
+          <t>DoW Ricerca sulle lesioni del midollo spinale, finanziamento per trial clinici</t>
         </is>
       </c>
       <c r="F13" s="4" t="n">
@@ -2303,12 +2297,12 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Defense Health Agency Contracting Activity - DHACA – HT942526SCIRPIIRA</t>
+          <t>Defense Health Agency Contracting Activity - DHACA – HT942526SCIRPCTA</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>DoW Spinal Cord Injury, Investigator-Initiated Research Award</t>
+          <t>DoW Spinal Cord Injury, Clinical Trial Award</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -2323,11 +2317,11 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>Supporta la ricerca traslazionale e clinica mirata a migliorare l'assistenza e la qualità di vita nelle lesioni midollari.</t>
+          <t>Finanzia trial clinici focalizzati sul trattamento e sulla gestione funzionale delle lesioni del midollo spinale.</t>
         </is>
       </c>
       <c r="P13" s="6" t="n">
-        <v>4960000</v>
+        <v>9760000</v>
       </c>
       <c r="Q13" s="6" t="n"/>
       <c r="R13" s="2" t="inlineStr">
@@ -2336,11 +2330,11 @@
         </is>
       </c>
       <c r="S13" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t>Media – 6 progetti finanziabili (stima: tasso storico non disponibile)</t>
+          <t>Bassa – 2 progetti finanziabili (stima: tasso storico non disponibile)</t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
@@ -2364,7 +2358,7 @@
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t>Opzione per due Principal Investigator (di cui almeno uno a inizio carriera)</t>
+          <t>Obbligatori almeno 2 partner della comunità con esperienza di lesione midollare; possibile collaborazione tra 2 PI</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2379,16 +2373,16 @@
       </c>
       <c r="AC13" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/362226</t>
+          <t>https://www.grants.gov/search-results-detail/362224</t>
         </is>
       </c>
       <c r="AD13" s="3" t="inlineStr">
         <is>
-          <t>Il bando Investigator-Initiated Research Award (IIRA) per l'anno fiscale 2026, promosso dal programma SCIRP, supporta studi con un impatto rilevante sulla ricerca, sulla cura clinica e sulla qualità della vita delle persone con lesioni del midollo spinale. L'opportunità finanzia progetti che spaziano dalla ricerca fondamentale alle scienze traslazionali, scoraggiando gli studi focalizzati esclusivamente sull'identificazione di bersagli farmacologici o biologici. Il bando contempla una modalità opzionale di partenariato che permette a due Principal Investigator di fare domanda congiunta con premi separati, a condizione che almeno uno dei due sia un ricercatore a inizio carriera.</t>
+          <t>Il bando Clinical Trial Award del programma SCIRP (anno fiscale 2026) finanzia la rapida attuazione di studi clinici con un potenziale impatto significativo sul trattamento o sulla gestione delle persone con lesione del midollo spinale. L'opportunità include un'opzione di partenariato per ricercatori all'inizio della carriera (Early-Career Partnership Option), che consente la partecipazione di due Principal Investigator, purché almeno uno sia un ricercatore junior. Le proposte devono obbligatoriamente coinvolgere almeno due rappresentanti o partner della comunità con esperienza diretta di lesione midollare, che collaboreranno attivamente fornendo consulenza durante l'intera pianificazione e implementazione dello studio clinico.</t>
         </is>
       </c>
       <c r="AE13" s="4" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="AF13" s="4" t="n">
         <v>46313</v>
@@ -2398,7 +2392,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>GG-RFA-DA-28-011</t>
+          <t>GG-HT942526SCIRPCTRA</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -2418,11 +2412,11 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Iniziativa HEAL: gestione integrata del dolore cronico e del disturbo da uso di oppioidi (IMPOWR) - Centri di ricerca (RM1)</t>
+          <t>DoW Ricerca sulle lesioni del midollo spinale, finanziamento per la ricerca clinica traslazionale</t>
         </is>
       </c>
       <c r="F14" s="4" t="n">
-        <v>46413</v>
+        <v>46338</v>
       </c>
       <c r="G14" s="5">
         <f>IF(F14="","",F14-TODAY())</f>
@@ -2430,12 +2424,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Aperto</t>
+          <t>In scadenza (≤30 gg)</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>National Institutes of Health</t>
+          <t>Defense Health Agency Contracting Activity - DHACA</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -2445,12 +2439,12 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>National Institutes of Health – RFA-DA-28-011</t>
+          <t>Defense Health Agency Contracting Activity - DHACA – HT942526SCIRPCTRA</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>HEAL Initiative: Integrative Management of Chronic Pain and OUD for Whole Recovery (IMPOWR): Research Centers (RM1 Clinical Trial Required)</t>
+          <t>DoW Spinal Cord Injury, Clinical Translation Research Award</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -2460,25 +2454,29 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>chronic pain</t>
+          <t>rehabilitat, spinal cord injur</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>È dedicato alla gestione integrata a lungo termine del dolore cronico e al recupero funzionale dei pazienti.</t>
-        </is>
-      </c>
-      <c r="P14" s="6" t="n"/>
+          <t>Finanzia ricerca clinica traslazionale volta a identificare le opzioni più efficaci di riabilitazione e trattamento nelle lesioni midollari.</t>
+        </is>
+      </c>
+      <c r="P14" s="6" t="n">
+        <v>6120000</v>
+      </c>
       <c r="Q14" s="6" t="n"/>
       <c r="R14" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="S14" s="2" t="n"/>
+      <c r="S14" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t>Non stimabile – dati insufficienti</t>
+          <t>Bassa – 3 progetti finanziabili (stima: tasso storico non disponibile)</t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr">
@@ -2487,7 +2485,7 @@
         </is>
       </c>
       <c r="V14" s="4" t="n">
-        <v>46301</v>
+        <v>46147</v>
       </c>
       <c r="W14" s="2" t="n"/>
       <c r="X14" s="2" t="inlineStr">
@@ -2497,10 +2495,14 @@
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t>Special district governments; Nonprofits that do not have a 501(c)(3) status with the IRS, other than institutions of higher education; State governments; Public and State controlled institutions of higher education; Native American tribal governments (Federally recognized); Public housing authorities/Indian housing authorities; Independent school districts; Private institutions of higher educatio</t>
-        </is>
-      </c>
-      <c r="Z14" s="3" t="n"/>
+          <t>Unrestricted (i.e., open to any type of entity above), subject to any clarification in text field entitled "Additional Information on Eligibility"</t>
+        </is>
+      </c>
+      <c r="Z14" s="3" t="inlineStr">
+        <is>
+          <t>Obbligatori almeno due partner della comunità di pazienti; opzione con due PI di cui uno a inizio carriera</t>
+        </is>
+      </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
           <t>Enti esteri: da verificare nel bando</t>
@@ -2513,26 +2515,26 @@
       </c>
       <c r="AC14" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/360048</t>
+          <t>https://www.grants.gov/search-results-detail/362225</t>
         </is>
       </c>
       <c r="AD14" s="3" t="inlineStr">
         <is>
-          <t>L'avviso anticipa il rinnovo della rete di ricerca IMPOWR, parte dell'iniziativa NIH HEAL, finalizzata allo sviluppo e alla validazione di modelli integrati per la gestione del dolore cronico e del disturbo da uso di oppioidi. Il network comprenderà molteplici progetti di ricerca coordinati da un centro centrale, con l'obiettivo di condurre studi clinici per testare approcci assistenziali innovativi in grado di migliorare significativamente l'erogazione delle cure nei sistemi sanitari. Possono partecipare istituzioni universitarie, ospedaliere, enti di ricerca no-profit o profit e organizzazioni estere non statunitensi.</t>
+          <t>Il bando Clinical Translation Research Award dello SCIRP per l'anno fiscale 2026 promuove ricerche cliniche emergenti o ad alto impatto che necessitano di studi preliminari, di fattibilità o di ottimizzazione per preparare futuri trial clinici definitivi. Tra gli obiettivi principali rientrano l'accelerazione del trasferimento clinico di nuove tecniche o interventi e l'identificazione delle migliori opzioni diagnostiche, terapeutiche e riabilitative per supportare le decisioni di pazienti e clinici nell'ambito delle lesioni del midollo spinale. Il bando include un'opzione per due Principal Investigator (con almeno un ricercatore junior) e impone il coinvolgimento di almeno due partner della comunità di pazienti come consulenti del progetto.</t>
         </is>
       </c>
       <c r="AE14" s="4" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="AF14" s="4" t="n">
-        <v>46313</v>
+        <v>46312</v>
       </c>
       <c r="AG14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>GG-PAR-27-065</t>
+          <t>GG-HT942526SCIRPIIRA</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -2552,11 +2554,11 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Trial clinici esplorativi e di efficacia del NINDS (UG3/UH3 - Clinical Trial obbligatorio)</t>
+          <t>DoW Ricerca sulle lesioni del midollo spinale, finanziamento per la ricerca promossa dal ricercatore</t>
         </is>
       </c>
       <c r="F15" s="4" t="n">
-        <v>47186</v>
+        <v>46338</v>
       </c>
       <c r="G15" s="5">
         <f>IF(F15="","",F15-TODAY())</f>
@@ -2564,12 +2566,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Aperto</t>
+          <t>In scadenza (≤30 gg)</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>National Institutes of Health</t>
+          <t>Defense Health Agency Contracting Activity - DHACA</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2579,40 +2581,44 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>National Institutes of Health – PAR-27-065</t>
+          <t>Defense Health Agency Contracting Activity - DHACA – HT942526SCIRPIIRA</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>NINDS Efficacy and Exploratory Clinical Trials (UG3/UH3 - Clinical Trial Required)</t>
+          <t>DoW Spinal Cord Injury, Investigator-Initiated Research Award</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Ictus, Altre malattie e riabilitazione</t>
+          <t>Altre malattie e riabilitazione</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>stroke, rehabilitat, neurological disorder</t>
+          <t>spinal cord injur</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>Finanzia trial clinici neurologici e ammette esplicitamente terapie e interventi di riabilitazione lungo tutto l'arco della vita.</t>
-        </is>
-      </c>
-      <c r="P15" s="6" t="n"/>
+          <t>Supporta la ricerca traslazionale e clinica mirata a migliorare l'assistenza e la qualità di vita nelle lesioni midollari.</t>
+        </is>
+      </c>
+      <c r="P15" s="6" t="n">
+        <v>4960000</v>
+      </c>
       <c r="Q15" s="6" t="n"/>
       <c r="R15" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="S15" s="2" t="n"/>
+      <c r="S15" s="2" t="n">
+        <v>6</v>
+      </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t>Non stimabile – dati insufficienti</t>
+          <t>Media – 6 progetti finanziabili (stima: tasso storico non disponibile)</t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
@@ -2621,7 +2627,7 @@
         </is>
       </c>
       <c r="V15" s="4" t="n">
-        <v>46265</v>
+        <v>46147</v>
       </c>
       <c r="W15" s="2" t="n"/>
       <c r="X15" s="2" t="inlineStr">
@@ -2631,12 +2637,12 @@
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t>Small businesses; Private institutions of higher education; Public and State controlled institutions of higher education; Native American tribal governments (Federally recognized); State governments; City or township governments; Independent school districts; Nonprofits having a 501(c)(3) status with the IRS, other than institutions of higher education; Nonprofits that do not have a 501(c)(3) stat</t>
+          <t>Unrestricted (i.e., open to any type of entity above), subject to any clarification in text field entitled "Additional Information on Eligibility"</t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t>Non sono ammessi sub-accordi o subappalti a entità estere; le organizzazioni estere possono candidarsi direttamente come capofila</t>
+          <t>Opzione per due Principal Investigator (di cui almeno uno a inizio carriera)</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2651,26 +2657,26 @@
       </c>
       <c r="AC15" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/360404</t>
+          <t>https://www.grants.gov/search-results-detail/362226</t>
         </is>
       </c>
       <c r="AD15" s="3" t="inlineStr">
         <is>
-          <t>Questa opportunità di finanziamento (UG3/UH3) promossa dal National Institute of Neurological Disorders and Stroke (NINDS) sostiene trial clinici proposti da ricercatori per affrontare quesiti coerenti con la missione dell'istituto. Il bando finanzia sperimentazioni cliniche precoci, intermedie o confermative di fase 3 e studi di efficacia comparativa su molecole, farmaci biologici, dispositivi medici o interventi chirurgici, comportamentali, dietetici e terapie riabilitative, per tutte le età. Possono partecipare enti accademici, ospedalieri e organizzazioni di ricerca, incluse entità straniere non statunitensi come capofila. Non sono tuttavia consentiti subappalti o sub-accordi finanziari internazionali verso altre entità estere nell'ambito dello stesso progetto.</t>
+          <t>Il bando Investigator-Initiated Research Award (IIRA) per l'anno fiscale 2026, promosso dal programma SCIRP, supporta studi con un impatto rilevante sulla ricerca, sulla cura clinica e sulla qualità della vita delle persone con lesioni del midollo spinale. L'opportunità finanzia progetti che spaziano dalla ricerca fondamentale alle scienze traslazionali, scoraggiando gli studi focalizzati esclusivamente sull'identificazione di bersagli farmacologici o biologici. Il bando contempla una modalità opzionale di partenariato che permette a due Principal Investigator di fare domanda congiunta con premi separati, a condizione che almeno uno dei due sia un ricercatore a inizio carriera.</t>
         </is>
       </c>
       <c r="AE15" s="4" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="AF15" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AG15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>GG-PD-26-369Y</t>
+          <t>GG-RFA-DA-28-011</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -2685,27 +2691,29 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Tecnologia / innovazione</t>
+          <t>Ricerca clinica</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Ingegneria dei sistemi biologici e biomedici (EBBS)</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="n"/>
+          <t>Iniziativa HEAL: gestione integrata del dolore cronico e del disturbo da uso di oppioidi (IMPOWR) - Centri di ricerca (RM1)</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>46413</v>
+      </c>
       <c r="G16" s="5">
         <f>IF(F16="","",F16-TODAY())</f>
         <v/>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Scadenza da verificare</t>
+          <t>Aperto</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>U.S. National Science Foundation</t>
+          <t>National Institutes of Health</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2715,27 +2723,27 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>U.S. National Science Foundation – PD-26-369Y</t>
+          <t>National Institutes of Health – RFA-DA-28-011</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>Engineering Biological and Biomedical Systems (EBBS)</t>
+          <t>HEAL Initiative: Integrative Management of Chronic Pain and OUD for Whole Recovery (IMPOWR): Research Centers (RM1 Clinical Trial Required)</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Tecnologie riabilitazione, Altre malattie e riabilitazione</t>
+          <t>Altre malattie e riabilitazione</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>rehabilitation engineering, rehabilitat, persons with disabilities</t>
+          <t>chronic pain</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>Supporta esplicitamente la ricerca fondamentale in ingegneria della riabilitazione e tecnologie per il ripristino delle funzioni e la disabilità.</t>
+          <t>È dedicato alla gestione integrata a lungo termine del dolore cronico e al recupero funzionale dei pazienti.</t>
         </is>
       </c>
       <c r="P16" s="6" t="n"/>
@@ -2757,7 +2765,7 @@
         </is>
       </c>
       <c r="V16" s="4" t="n">
-        <v>46136</v>
+        <v>46301</v>
       </c>
       <c r="W16" s="2" t="n"/>
       <c r="X16" s="2" t="inlineStr">
@@ -2767,7 +2775,7 @@
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t>Unrestricted (i.e., open to any type of entity above), subject to any clarification in text field entitled "Additional Information on Eligibility"</t>
+          <t>Native American tribal organizations (other than Federally recognized tribal governments); City or township governments; For profit organizations other than small businesses; Small businesses; Independent school districts; Nonprofits that do not have a 501(c)(3) status with the IRS, other than institutions of higher education; State governments; Nonprofits having a 501(c)(3) status with the IRS, o</t>
         </is>
       </c>
       <c r="Z16" s="3" t="n"/>
@@ -2783,26 +2791,26 @@
       </c>
       <c r="AC16" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/362062</t>
+          <t>https://www.grants.gov/search-results-detail/360048</t>
         </is>
       </c>
       <c r="AD16" s="3" t="inlineStr">
         <is>
-          <t>Il programma Engineering Biological and Biomedical Systems (EBBS) della National Science Foundation statunitense sostiene progetti di ricerca ingegneristica fondamentale volti a comprendere e controllare i sistemi biologici e fisiologici per migliorare la salute umana. L'iniziativa finanzia in particolare lo sviluppo di piattaforme di biosensing, metodologie di imaging ottico, sistemi per imitare o ripristinare le funzioni di tessuti e organi, nonché progetti innovativi di ingegneria della riabilitazione guidati dalle esigenze delle persone con disabilità. Non sono supportati trial clinici né progetti dedicati unicamente alla progettazione di farmaci o alla commercializzazione immediata. Il bando incoraggia approcci interdisciplinari e collaborazioni, ma non specifica restrizioni geografiche per la candidatura diretta.</t>
+          <t>L'avviso anticipa il rinnovo della rete di ricerca IMPOWR, parte dell'iniziativa NIH HEAL, finalizzata allo sviluppo e alla validazione di modelli integrati per la gestione del dolore cronico e del disturbo da uso di oppioidi. Il network comprenderà molteplici progetti di ricerca coordinati da un centro centrale, con l'obiettivo di condurre studi clinici per testare approcci assistenziali innovativi in grado di migliorare significativamente l'erogazione delle cure nei sistemi sanitari. Possono partecipare istituzioni universitarie, ospedaliere, enti di ricerca no-profit o profit e organizzazioni estere non statunitensi.</t>
         </is>
       </c>
       <c r="AE16" s="4" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="AF16" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AG16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>GG-HT942526PRPEIRA</t>
+          <t>GG-PAR-27-065</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -2812,21 +2820,21 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Formazione / fellowship</t>
+          <t>Ricerca clinica</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Programma di ricerca sul Parkinson del Dipartimento della Difesa: bando per ricercatori a inizio carriera</t>
+          <t>Trial clinici esplorativi e di efficacia del NINDS (UG3/UH3 - Clinical Trial obbligatorio)</t>
         </is>
       </c>
       <c r="F17" s="4" t="n">
-        <v>46332</v>
+        <v>47186</v>
       </c>
       <c r="G17" s="5">
         <f>IF(F17="","",F17-TODAY())</f>
@@ -2834,12 +2842,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>In scadenza (≤30 gg)</t>
+          <t>Aperto</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Defense Health Agency Contracting Activity - DHACA</t>
+          <t>National Institutes of Health</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2849,44 +2857,40 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>Defense Health Agency Contracting Activity - DHACA – HT942526PRPEIRA</t>
+          <t>National Institutes of Health – PAR-27-065</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>DoW Parkinson’s, Early Investigator Research Award</t>
+          <t>NINDS Efficacy and Exploratory Clinical Trials (UG3/UH3 - Clinical Trial Required)</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Parkinson</t>
+          <t>Ictus, Altre malattie e riabilitazione</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>parkinson</t>
+          <t>stroke, rehabilitat, neurological disorder</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>Finanzia la ricerca sul morbo di Parkinson per ricercatori a inizio carriera, ma esclude i trial clinici e non è mirato alla riabilitazione.</t>
-        </is>
-      </c>
-      <c r="P17" s="6" t="n">
-        <v>4200000</v>
-      </c>
+          <t>Finanzia trial clinici neurologici e ammette esplicitamente terapie e interventi di riabilitazione lungo tutto l'arco della vita.</t>
+        </is>
+      </c>
+      <c r="P17" s="6" t="n"/>
       <c r="Q17" s="6" t="n"/>
       <c r="R17" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="S17" s="2" t="n">
-        <v>7</v>
-      </c>
+      <c r="S17" s="2" t="n"/>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t>Media – 7 progetti finanziabili (stima: tasso storico non disponibile)</t>
+          <t>Non stimabile – dati insufficienti</t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
@@ -2895,22 +2899,22 @@
         </is>
       </c>
       <c r="V17" s="4" t="n">
-        <v>46191</v>
+        <v>46265</v>
       </c>
       <c r="W17" s="2" t="n"/>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>Dottorato / formazione / mobilità</t>
+          <t>Ricerca</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t>Unrestricted (i.e., open to any type of entity above), subject to any clarification in text field entitled "Additional Information on Eligibility"</t>
+          <t>Special district governments; Public housing authorities/Indian housing authorities; Nonprofits that do not have a 501(c)(3) status with the IRS, other than institutions of higher education; Private institutions of higher education; Native American tribal governments (Federally recognized); Nonprofits having a 501(c)(3) status with the IRS, other than institutions of higher education; Public and S</t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t>Per il Livello 1 è obbligatoria la designazione di almeno un mentore con esperienza documentata nella ricerca su Parkinson.</t>
+          <t>Non sono ammessi sub-accordi o subappalti a entità estere; le organizzazioni estere possono candidarsi direttamente come capofila</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2925,16 +2929,16 @@
       </c>
       <c r="AC17" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/362866</t>
+          <t>https://www.grants.gov/search-results-detail/360404</t>
         </is>
       </c>
       <c r="AD17" s="3" t="inlineStr">
         <is>
-          <t>Il bando Early Investigator Research Award, promosso nell'ambito del Parkinson’s Research Program dell'agenzia di difesa statunitense, sostiene la formazione e l'avvio di carriera di ricercatori promettenti dedicati alla ricerca sulla malattia di Parkinson. L'iniziativa prevede due livelli: il primo è destinato a borsisti o assegnisti (fellows) e richiede l'affiancamento obbligatorio di un mentore esperto per garantire un solido percorso verso l'indipendenza scientifica; il secondo è rivolto a ricercatori indipendenti junior e richiede dati preliminari comprovati. Le ricerche proposte devono rientrare nelle aree prioritarie del programma e non possono includere sperimentazioni cliniche. Possono candidarsi ricercatori a inizio carriera sostenuti dalle proprie organizzazioni di ricerca o accademiche.</t>
+          <t>Questa opportunità di finanziamento (UG3/UH3) promossa dal National Institute of Neurological Disorders and Stroke (NINDS) sostiene trial clinici proposti da ricercatori per affrontare quesiti coerenti con la missione dell'istituto. Il bando finanzia sperimentazioni cliniche precoci, intermedie o confermative di fase 3 e studi di efficacia comparativa su molecole, farmaci biologici, dispositivi medici o interventi chirurgici, comportamentali, dietetici e terapie riabilitative, per tutte le età. Possono partecipare enti accademici, ospedalieri e organizzazioni di ricerca, incluse entità straniere non statunitensi come capofila. Non sono tuttavia consentiti subappalti o sub-accordi finanziari internazionali verso altre entità estere nell'ambito dello stesso progetto.</t>
         </is>
       </c>
       <c r="AE17" s="4" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="AF17" s="4" t="n">
         <v>46312</v>
@@ -2944,7 +2948,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>GG-HT942526PRPIIRA</t>
+          <t>GG-PD-26-369Y</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -2954,34 +2958,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Ricerca clinica</t>
+          <t>Tecnologia / innovazione</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Programma di ricerca sul Parkinson del Dipartimento della Difesa: bando di ricerca promosso dal ricercatore</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="n">
-        <v>46332</v>
-      </c>
+          <t>Ingegneria dei sistemi biologici e biomedici (EBBS)</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="n"/>
       <c r="G18" s="5">
         <f>IF(F18="","",F18-TODAY())</f>
         <v/>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>In scadenza (≤30 gg)</t>
+          <t>Scadenza da verificare</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Defense Health Agency Contracting Activity - DHACA</t>
+          <t>U.S. National Science Foundation</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2991,44 +2993,40 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>Defense Health Agency Contracting Activity - DHACA – HT942526PRPIIRA</t>
+          <t>U.S. National Science Foundation – PD-26-369Y</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>DoW Parkinson’s, Investigator-Initiated Research Award</t>
+          <t>Engineering Biological and Biomedical Systems (EBBS)</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Parkinson</t>
+          <t>Tecnologie riabilitazione, Altre malattie e riabilitazione</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>parkinson</t>
+          <t>rehabilitation engineering, rehabilitat, persons with disabilities</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>Bando dedicato alla malattia di Parkinson che ammette trial clinici, pur senza essere focalizzato specificamente sulla riabilitazione.</t>
-        </is>
-      </c>
-      <c r="P18" s="6" t="n">
-        <v>10000000</v>
-      </c>
+          <t>Supporta esplicitamente la ricerca fondamentale in ingegneria della riabilitazione e tecnologie per il ripristino delle funzioni e la disabilità.</t>
+        </is>
+      </c>
+      <c r="P18" s="6" t="n"/>
       <c r="Q18" s="6" t="n"/>
       <c r="R18" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="S18" s="2" t="n">
-        <v>5</v>
-      </c>
+      <c r="S18" s="2" t="n"/>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t>Media – 5 progetti finanziabili (stima: tasso storico non disponibile)</t>
+          <t>Non stimabile – dati insufficienti</t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
@@ -3037,7 +3035,7 @@
         </is>
       </c>
       <c r="V18" s="4" t="n">
-        <v>46191</v>
+        <v>46136</v>
       </c>
       <c r="W18" s="2" t="n"/>
       <c r="X18" s="2" t="inlineStr">
@@ -3050,11 +3048,7 @@
           <t>Unrestricted (i.e., open to any type of entity above), subject to any clarification in text field entitled "Additional Information on Eligibility"</t>
         </is>
       </c>
-      <c r="Z18" s="3" t="inlineStr">
-        <is>
-          <t>Possibilità di consorzio con un Initiating PI e fino a due Partnering PI multidisciplinari.</t>
-        </is>
-      </c>
+      <c r="Z18" s="3" t="n"/>
       <c r="AA18" s="2" t="inlineStr">
         <is>
           <t>Enti esteri: da verificare nel bando</t>
@@ -3067,16 +3061,16 @@
       </c>
       <c r="AC18" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/362868</t>
+          <t>https://www.grants.gov/search-results-detail/362062</t>
         </is>
       </c>
       <c r="AD18" s="3" t="inlineStr">
         <is>
-          <t>L'Investigator-Initiated Research Award, gestito dal programma di ricerca sul Parkinson (PRP), mira a finanziare progetti di ricerca rigorosi, multidisciplinari e ad alto impatto con un rilevante potenziale innovativo nella lotta al morbo di Parkinson. Le proposte devono concentrarsi su una delle aree prioritarie stabilite per l'anno fiscale 2026 e devono essere obbligatoriamente supportate da solidi dati preliminari. A differenza di altre linee di finanziamento, questo bando consente esplicitamente la conduzione di studi clinici. È inoltre prevista un'opzione di partenariato che permette la collaborazione formale tra un ricercatore principale capofila e fino a due Principal Investigator partner. Possono candidarsi istituti universitari, centri di ricerca e organizzazioni cliniche qualificate.</t>
+          <t>Il programma Engineering Biological and Biomedical Systems (EBBS) della National Science Foundation statunitense sostiene progetti di ricerca ingegneristica fondamentale volti a comprendere e controllare i sistemi biologici e fisiologici per migliorare la salute umana. L'iniziativa finanzia in particolare lo sviluppo di piattaforme di biosensing, metodologie di imaging ottico, sistemi per imitare o ripristinare le funzioni di tessuti e organi, nonché progetti innovativi di ingegneria della riabilitazione guidati dalle esigenze delle persone con disabilità. Non sono supportati trial clinici né progetti dedicati unicamente alla progettazione di farmaci o alla commercializzazione immediata. Il bando incoraggia approcci interdisciplinari e collaborazioni, ma non specifica restrizioni geografiche per la candidatura diretta.</t>
         </is>
       </c>
       <c r="AE18" s="4" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="AF18" s="4" t="n">
         <v>46312</v>
@@ -3086,7 +3080,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>GG-PAR-27-007</t>
+          <t>GG-HT942526PRPEIRA</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -3101,16 +3095,16 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Ricerca clinica</t>
+          <t>Formazione / fellowship</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Trial clinici e studi ancillari condotti all'interno delle reti di ricerca clinica finanziate dal NIH (UG3/UH3)</t>
+          <t>Programma di ricerca sul Parkinson del Dipartimento della Difesa: bando per ricercatori a inizio carriera</t>
         </is>
       </c>
       <c r="F19" s="4" t="n">
-        <v>46336</v>
+        <v>46332</v>
       </c>
       <c r="G19" s="5">
         <f>IF(F19="","",F19-TODAY())</f>
@@ -3123,7 +3117,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>National Institutes of Health</t>
+          <t>Defense Health Agency Contracting Activity - DHACA</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -3133,40 +3127,44 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>National Institutes of Health – PAR-27-007</t>
+          <t>Defense Health Agency Contracting Activity - DHACA – HT942526PRPEIRA</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>Clinical Trials and Ancillary Studies Conducted within NIH-Funded Clinical Trial Research Networks (UG3/UH3 - Clinical Trial Required)</t>
+          <t>DoW Parkinson’s, Early Investigator Research Award</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>Ictus, Altre malattie e riabilitazione</t>
+          <t>Parkinson</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>stroke, neurological disorder</t>
+          <t>parkinson</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>Finanzia trial clinici in reti neurologiche che possono comprendere patologie di interesse riabilitativo come l'ictus, pur non focalizzandosi sulla riabilitazione.</t>
-        </is>
-      </c>
-      <c r="P19" s="6" t="n"/>
+          <t>Finanzia la ricerca sul morbo di Parkinson per ricercatori a inizio carriera, ma esclude i trial clinici e non è mirato alla riabilitazione.</t>
+        </is>
+      </c>
+      <c r="P19" s="6" t="n">
+        <v>4200000</v>
+      </c>
       <c r="Q19" s="6" t="n"/>
       <c r="R19" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="S19" s="2" t="n"/>
+      <c r="S19" s="2" t="n">
+        <v>7</v>
+      </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t>Non stimabile – dati insufficienti</t>
+          <t>Media – 7 progetti finanziabili (stima: tasso storico non disponibile)</t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
@@ -3175,24 +3173,24 @@
         </is>
       </c>
       <c r="V19" s="4" t="n">
-        <v>46097</v>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>84 mesi</t>
-        </is>
-      </c>
+        <v>46191</v>
+      </c>
+      <c r="W19" s="2" t="n"/>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>Ricerca</t>
+          <t>Dottorato / formazione / mobilità</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t>Public housing authorities/Indian housing authorities; State governments; Special district governments; Private institutions of higher education; Independent school districts; City or township governments; Nonprofits having a 501(c)(3) status with the IRS, other than institutions of higher education; Public and State controlled institutions of higher education; Small businesses; Nonprofits that do</t>
-        </is>
-      </c>
-      <c r="Z19" s="3" t="n"/>
+          <t>Unrestricted (i.e., open to any type of entity above), subject to any clarification in text field entitled "Additional Information on Eligibility"</t>
+        </is>
+      </c>
+      <c r="Z19" s="3" t="inlineStr">
+        <is>
+          <t>Per il Livello 1 è obbligatoria la designazione di almeno un mentore con esperienza documentata nella ricerca su Parkinson.</t>
+        </is>
+      </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
           <t>Enti esteri: da verificare nel bando</t>
@@ -3205,16 +3203,16 @@
       </c>
       <c r="AC19" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/361522</t>
+          <t>https://www.grants.gov/search-results-detail/362866</t>
         </is>
       </c>
       <c r="AD19" s="3" t="inlineStr">
         <is>
-          <t>Il bando, promosso dal NINDS insieme ad altri istituti del NIH tramite lo schema cooperativo a due fasi UG3/UH3, intende sostenere la conduzione di studi clinici multicentrici e studi ancillari all'interno delle reti di ricerca clinica già finanziate e attive del NIH. Il programma prevede una fase iniziale di pianificazione e avvio fino a due anni (UG3), con possibile passaggio a una fase operativa fino a ulteriori cinque anni (UH3) al raggiungimento di specifici traguardi. Possono candidarsi enti di ricerca, università, organizzazioni pubbliche o private ed enti stranieri non statunitensi per testare interventi diagnostici e terapeutici in ambito neurologico.</t>
+          <t>Il bando Early Investigator Research Award, promosso nell'ambito del Parkinson’s Research Program dell'agenzia di difesa statunitense, sostiene la formazione e l'avvio di carriera di ricercatori promettenti dedicati alla ricerca sulla malattia di Parkinson. L'iniziativa prevede due livelli: il primo è destinato a borsisti o assegnisti (fellows) e richiede l'affiancamento obbligatorio di un mentore esperto per garantire un solido percorso verso l'indipendenza scientifica; il secondo è rivolto a ricercatori indipendenti junior e richiede dati preliminari comprovati. Le ricerche proposte devono rientrare nelle aree prioritarie del programma e non possono includere sperimentazioni cliniche. Possono candidarsi ricercatori a inizio carriera sostenuti dalle proprie organizzazioni di ricerca o accademiche.</t>
         </is>
       </c>
       <c r="AE19" s="4" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="AF19" s="4" t="n">
         <v>46312</v>
@@ -3224,7 +3222,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>GG-RFA-TS-27-018</t>
+          <t>GG-HT942526PRPIIRA</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -3244,11 +3242,11 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Identificazione e valutazione dei potenziali fattori di rischio per la sclerosi laterale amiotrofica (SLA)</t>
+          <t>Programma di ricerca sul Parkinson del Dipartimento della Difesa: bando di ricerca promosso dal ricercatore</t>
         </is>
       </c>
       <c r="F20" s="4" t="n">
-        <v>46357</v>
+        <v>46332</v>
       </c>
       <c r="G20" s="5">
         <f>IF(F20="","",F20-TODAY())</f>
@@ -3256,12 +3254,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Aperto</t>
+          <t>In scadenza (≤30 gg)</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Centers for Disease Control and Prevention - ERA</t>
+          <t>Defense Health Agency Contracting Activity - DHACA</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -3271,46 +3269,44 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>Centers for Disease Control and Prevention - ERA – RFA-TS-27-018</t>
+          <t>Defense Health Agency Contracting Activity - DHACA – HT942526PRPIIRA</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>Identify and Evaluate Potential Risk Factors for Amyotrophic Lateral Sclerosis (ALS)</t>
+          <t>DoW Parkinson’s, Investigator-Initiated Research Award</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Altre malattie e riabilitazione</t>
+          <t>Parkinson</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>amyotrophic lateral sclerosis, traumatic brain injur</t>
+          <t>parkinson</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>Riguarda la sclerosi laterale amiotrofica (SLA) ma è incentrato sullo studio dei fattori di rischio eziologici e non sulla riabilitazione.</t>
+          <t>Bando dedicato alla malattia di Parkinson che ammette trial clinici, pur senza essere focalizzato specificamente sulla riabilitazione.</t>
         </is>
       </c>
       <c r="P20" s="6" t="n">
-        <v>4500000</v>
-      </c>
-      <c r="Q20" s="6" t="n">
-        <v>500000</v>
-      </c>
+        <v>10000000</v>
+      </c>
+      <c r="Q20" s="6" t="n"/>
       <c r="R20" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="S20" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t>Bassa – 3 progetti finanziabili (stima: tasso storico non disponibile)</t>
+          <t>Media – 5 progetti finanziabili (stima: tasso storico non disponibile)</t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
@@ -3319,7 +3315,7 @@
         </is>
       </c>
       <c r="V20" s="4" t="n">
-        <v>46211</v>
+        <v>46191</v>
       </c>
       <c r="W20" s="2" t="n"/>
       <c r="X20" s="2" t="inlineStr">
@@ -3329,10 +3325,14 @@
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t>City or township governments; Public and State controlled institutions of higher education; Native American tribal organizations (other than Federally recognized tribal governments); Nonprofits that do not have a 501(c)(3) status with the IRS, other than institutions of higher education; Public housing authorities/Indian housing authorities; County governments; Private institutions of higher educa</t>
-        </is>
-      </c>
-      <c r="Z20" s="3" t="n"/>
+          <t>Unrestricted (i.e., open to any type of entity above), subject to any clarification in text field entitled "Additional Information on Eligibility"</t>
+        </is>
+      </c>
+      <c r="Z20" s="3" t="inlineStr">
+        <is>
+          <t>Possibilità di consorzio con un Initiating PI e fino a due Partnering PI multidisciplinari.</t>
+        </is>
+      </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
           <t>Enti esteri: da verificare nel bando</t>
@@ -3345,16 +3345,16 @@
       </c>
       <c r="AC20" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/363115</t>
+          <t>https://www.grants.gov/search-results-detail/362868</t>
         </is>
       </c>
       <c r="AD20" s="3" t="inlineStr">
         <is>
-          <t>Il CDC e l'ATSDR finanziano progetti di ricerca dedicati all'identificazione e alla valutazione dei fattori di rischio per la sclerosi laterale amiotrofica (SLA), incoraggiando studi su servizio militare, sport di contatto, traumi cranici, neuroinfiammazione ed esposizioni ad agenti infettivi o ambientali. Il bando prevede quattro opzioni tematiche: ricerca supportata da evidenze consolidate e legami tra fattori di rischio, diagnosi e cura; studi esplorativi e innovativi su nuovi fattori; analisi del rischio in popolazioni specifiche, come i veterani militari; studio di campioni biologici del cluster di Guam per chiarire i meccanismi patologici, biomarcatori e approcci di prevenzione.</t>
+          <t>L'Investigator-Initiated Research Award, gestito dal programma di ricerca sul Parkinson (PRP), mira a finanziare progetti di ricerca rigorosi, multidisciplinari e ad alto impatto con un rilevante potenziale innovativo nella lotta al morbo di Parkinson. Le proposte devono concentrarsi su una delle aree prioritarie stabilite per l'anno fiscale 2026 e devono essere obbligatoriamente supportate da solidi dati preliminari. A differenza di altre linee di finanziamento, questo bando consente esplicitamente la conduzione di studi clinici. È inoltre prevista un'opzione di partenariato che permette la collaborazione formale tra un ricercatore principale capofila e fino a due Principal Investigator partner. Possono candidarsi istituti universitari, centri di ricerca e organizzazioni cliniche qualificate.</t>
         </is>
       </c>
       <c r="AE20" s="4" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="AF20" s="4" t="n">
         <v>46312</v>
@@ -3364,7 +3364,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>GG-FOR-FD-25-001</t>
+          <t>GG-PAR-27-007</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -3384,22 +3384,24 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Trial clinici per i bisogni insoddisfatti nelle malattie neurodegenerative rare (R01 - Clinical Trial obbligatorio)</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="n"/>
+          <t>Trial clinici e studi ancillari condotti all'interno delle reti di ricerca clinica finanziate dal NIH (UG3/UH3)</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>46336</v>
+      </c>
       <c r="G21" s="5">
         <f>IF(F21="","",F21-TODAY())</f>
         <v/>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>In apertura</t>
+          <t>In scadenza (≤30 gg)</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>Food and Drug Administration</t>
+          <t>National Institutes of Health</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -3409,33 +3411,31 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>Food and Drug Administration – FOR-FD-25-001</t>
+          <t>National Institutes of Health – PAR-27-007</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>Clinical Trials Addressing Unmet Needs of Rare Neurodegenerative Diseases (R01) Clinical Trials Required</t>
+          <t>Clinical Trials and Ancillary Studies Conducted within NIH-Funded Clinical Trial Research Networks (UG3/UH3 - Clinical Trial Required)</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Altre malattie e riabilitazione</t>
+          <t>Ictus, Altre malattie e riabilitazione</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>neurodegenerat</t>
+          <t>stroke, neurological disorder</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>Riguarda le malattie neurodegenerative rare, ma è finalizzato a trial clinici regolatori per l'approvazione o rietichettatura di farmaci.</t>
+          <t>Finanzia trial clinici in reti neurologiche che possono comprendere patologie di interesse riabilitativo come l'ictus, pur non focalizzandosi sulla riabilitazione.</t>
         </is>
       </c>
       <c r="P21" s="6" t="n"/>
-      <c r="Q21" s="6" t="n">
-        <v>900000</v>
-      </c>
+      <c r="Q21" s="6" t="n"/>
       <c r="R21" s="2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3453,9 +3453,13 @@
         </is>
       </c>
       <c r="V21" s="4" t="n">
-        <v>45518</v>
-      </c>
-      <c r="W21" s="2" t="n"/>
+        <v>46097</v>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>84 mesi</t>
+        </is>
+      </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
           <t>Ricerca</t>
@@ -3463,7 +3467,7 @@
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t>Public and State controlled institutions of higher education; Nonprofits that do not have a 501(c)(3) status with the IRS, other than institutions of higher education; For profit organizations other than small businesses; State governments; Small businesses; Native American tribal governments (Federally recognized); County governments; Special district governments; City or township governments; No</t>
+          <t>Independent school districts; Special district governments; Public and State controlled institutions of higher education; State governments; Public housing authorities/Indian housing authorities; For profit organizations other than small businesses; Native American tribal governments (Federally recognized); Small businesses; Native American tribal organizations (other than Federally recognized tri</t>
         </is>
       </c>
       <c r="Z21" s="3" t="n"/>
@@ -3479,16 +3483,16 @@
       </c>
       <c r="AC21" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/356054</t>
+          <t>https://www.grants.gov/search-results-detail/361522</t>
         </is>
       </c>
       <c r="AD21" s="3" t="inlineStr">
         <is>
-          <t>Questo bando promosso dalla Food and Drug Administration (FDA) tramite il meccanismo R01 è destinato a finanziare trial clinici dedicati a rispondere ai bisogni insoddisfatti nell'ambito delle malattie neurodegenerative rare, sia pediatriche che dell'età adulta. I progetti devono valutare l'efficacia e la sicurezza di prodotti terapeutici a supporto di nuove indicazioni cliniche o di modifiche delle indicazioni di etichettatura (labeling). L'obiettivo primario è incrementare il numero di trattamenti approvati dalle autorità regolatorie e favorire un impatto positivo e duraturo sullo sviluppo clinico di terapie per patologie rare. La presentazione di un trial clinico è requisito obbligatorio per accedere al finanziamento.</t>
+          <t>Il bando, promosso dal NINDS insieme ad altri istituti del NIH tramite lo schema cooperativo a due fasi UG3/UH3, intende sostenere la conduzione di studi clinici multicentrici e studi ancillari all'interno delle reti di ricerca clinica già finanziate e attive del NIH. Il programma prevede una fase iniziale di pianificazione e avvio fino a due anni (UG3), con possibile passaggio a una fase operativa fino a ulteriori cinque anni (UH3) al raggiungimento di specifici traguardi. Possono candidarsi enti di ricerca, università, organizzazioni pubbliche o private ed enti stranieri non statunitensi per testare interventi diagnostici e terapeutici in ambito neurologico.</t>
         </is>
       </c>
       <c r="AE21" s="4" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="AF21" s="4" t="n">
         <v>46312</v>
@@ -3498,7 +3502,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>GG-FOR-FD-25-006</t>
+          <t>GG-RFA-TS-27-018</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -3518,22 +3522,24 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Studi rivolti alle malattie neurodegenerative rare, inclusa la SLA</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="n"/>
+          <t>Identificazione e valutazione dei potenziali fattori di rischio per la sclerosi laterale amiotrofica (SLA)</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>46357</v>
+      </c>
       <c r="G22" s="5">
         <f>IF(F22="","",F22-TODAY())</f>
         <v/>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>In apertura</t>
+          <t>Aperto</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Food and Drug Administration</t>
+          <t>Centers for Disease Control and Prevention - ERA</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -3543,12 +3549,12 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>Food and Drug Administration – FOR-FD-25-006</t>
+          <t>Centers for Disease Control and Prevention - ERA – RFA-TS-27-018</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>Studies Addressing Rare Neurodegenerative Diseases including ALS</t>
+          <t>Identify and Evaluate Potential Risk Factors for Amyotrophic Lateral Sclerosis (ALS)</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -3558,27 +3564,31 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>neurodegenerat</t>
+          <t>amyotrophic lateral sclerosis, traumatic brain injur</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>Riguarda la SLA e le malattie neurodegenerative rare, ma è focalizzato sullo sviluppo di prodotti medici anziché su interventi riabilitativi specifici.</t>
-        </is>
-      </c>
-      <c r="P22" s="6" t="n"/>
-      <c r="Q22" s="6" t="n"/>
+          <t>Riguarda la sclerosi laterale amiotrofica (SLA) ma è incentrato sullo studio dei fattori di rischio eziologici e non sulla riabilitazione.</t>
+        </is>
+      </c>
+      <c r="P22" s="6" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="Q22" s="6" t="n">
+        <v>500000</v>
+      </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="S22" s="2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t>Media – 10 progetti finanziabili (stima: tasso storico non disponibile)</t>
+          <t>Bassa – 3 progetti finanziabili (stima: tasso storico non disponibile)</t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
@@ -3587,7 +3597,7 @@
         </is>
       </c>
       <c r="V22" s="4" t="n">
-        <v>45518</v>
+        <v>46211</v>
       </c>
       <c r="W22" s="2" t="n"/>
       <c r="X22" s="2" t="inlineStr">
@@ -3597,7 +3607,7 @@
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Public and State controlled institutions of higher education; Unrestricted (i.e., open to any type of entity above), subject to any clarification in text field entitled "Additional Information on Eligibility"; County governments; Public housing authorities/Indian housing authorities; Native American tribal organizations (other than Federally recognized tribal governments); Private institutions of </t>
+          <t>Independent school districts; Nonprofits that do not have a 501(c)(3) status with the IRS, other than institutions of higher education; Private institutions of higher education; City or township governments; Public housing authorities/Indian housing authorities; Nonprofits having a 501(c)(3) status with the IRS, other than institutions of higher education; State governments; Public and State contr</t>
         </is>
       </c>
       <c r="Z22" s="3" t="n"/>
@@ -3613,16 +3623,16 @@
       </c>
       <c r="AC22" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/356046</t>
+          <t>https://www.grants.gov/search-results-detail/363115</t>
         </is>
       </c>
       <c r="AD22" s="3" t="inlineStr">
         <is>
-          <t>Il bando, promosso dalla Food and Drug Administration (FDA), mira a sostenere studi scientifici per far progredire lo sviluppo di prodotti medici destinati a prevenire, diagnosticare, mitigare, trattare o curare la sclerosi laterale amiotrofica (SLA) e altre malattie neurodegenerative rare, sia negli adulti che nei bambini. Attraverso questo programma, l’ente intende colmare lacune conoscitive critiche, generare un impatto significativo sulla gestione delle patologie neurodegenerative rare e fornire dati essenziali per orientare lo sviluppo regolatorio e industriale di interventi innovativi attuali e futuri. Il bando finanzia attività di ricerca volte all'avanzamento di candidati terapeutici e strumenti diagnostici. I dettagli relativi a requisiti specifici di partecipazione e contributi economici sono definiti nella documentazione ufficiale.</t>
+          <t>Il CDC e l'ATSDR finanziano progetti di ricerca dedicati all'identificazione e alla valutazione dei fattori di rischio per la sclerosi laterale amiotrofica (SLA), incoraggiando studi su servizio militare, sport di contatto, traumi cranici, neuroinfiammazione ed esposizioni ad agenti infettivi o ambientali. Il bando prevede quattro opzioni tematiche: ricerca supportata da evidenze consolidate e legami tra fattori di rischio, diagnosi e cura; studi esplorativi e innovativi su nuovi fattori; analisi del rischio in popolazioni specifiche, come i veterani militari; studio di campioni biologici del cluster di Guam per chiarire i meccanismi patologici, biomarcatori e approcci di prevenzione.</t>
         </is>
       </c>
       <c r="AE22" s="4" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="AF22" s="4" t="n">
         <v>46312</v>
@@ -3632,7 +3642,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>WEB-be57b3f2011d</t>
+          <t>GG-FOR-FD-25-001</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -3647,12 +3657,12 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Formazione / fellowship</t>
+          <t>Ricerca clinica</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Bandi per la formazione clinica della Parkinson's Foundation</t>
+          <t>Trial clinici per i bisogni insoddisfatti nelle malattie neurodegenerative rare (R01 - Clinical Trial obbligatorio)</t>
         </is>
       </c>
       <c r="F23" s="4" t="n"/>
@@ -3662,88 +3672,82 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Scadenza da verificare</t>
+          <t>In apertura</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Parkinson's Foundation</t>
+          <t>Food and Drug Administration</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>Parkinson's Foundation</t>
+          <t>Grants.gov</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>Clinical Training Awards</t>
+          <t>Food and Drug Administration – FOR-FD-25-001</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>Clinical Training Awards</t>
+          <t>Clinical Trials Addressing Unmet Needs of Rare Neurodegenerative Diseases (R01) Clinical Trials Required</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>Parkinson, Invecchiamento</t>
+          <t>Altre malattie e riabilitazione</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>parkinson, movement disorder, aging</t>
+          <t>neurodegenerat</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>Finanzia la formazione clinica avanzata e la ricerca nella malattia di Parkinson e disturbi del movimento, ma non è focalizzato specificamente sulla riabilitazione.</t>
-        </is>
-      </c>
-      <c r="P23" s="6" t="n">
-        <v>50000</v>
-      </c>
+          <t>Riguarda le malattie neurodegenerative rare, ma è finalizzato a trial clinici regolatori per l'approvazione o rietichettatura di farmaci.</t>
+        </is>
+      </c>
+      <c r="P23" s="6" t="n"/>
       <c r="Q23" s="6" t="n">
-        <v>103800</v>
+        <v>900000</v>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="S23" s="2" t="n">
-        <v>4</v>
-      </c>
+      <c r="S23" s="2" t="n"/>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t>Bassa – 4 progetti finanziabili (stima: tasso storico non disponibile)</t>
+          <t>Non stimabile – dati insufficienti</t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t>Non indicato</t>
-        </is>
-      </c>
-      <c r="V23" s="4" t="n"/>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>24 mesi</t>
-        </is>
-      </c>
+          <t>Interamente finanziato</t>
+        </is>
+      </c>
+      <c r="V23" s="4" t="n">
+        <v>45518</v>
+      </c>
+      <c r="W23" s="2" t="n"/>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>Dottorato / formazione / mobilità</t>
+          <t>Ricerca</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t>Istituzioni accademiche/ospedaliere, giovani ricercatori e clinici entro 5 anni dal titolo, docenti di scienze infermieristiche</t>
+          <t>Independent school districts; State governments; Public and State controlled institutions of higher education; City or township governments; Private institutions of higher education; Public housing authorities/Indian housing authorities; Native American tribal organizations (other than Federally recognized tribal governments); Nonprofits that do not have a 501(c)(3) status with the IRS, other than</t>
         </is>
       </c>
       <c r="Z23" s="3" t="n"/>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>Mondiale</t>
+          <t>Enti esteri: da verificare nel bando</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
@@ -3753,16 +3757,16 @@
       </c>
       <c r="AC23" s="7" t="inlineStr">
         <is>
-          <t>https://www.parkinson.org/resources-support/professionals/clinical-training-awards</t>
+          <t>https://www.grants.gov/search-results-detail/356054</t>
         </is>
       </c>
       <c r="AD23" s="3" t="inlineStr">
         <is>
-          <t>La Parkinson's Foundation offre diversi programmi di finanziamento alla formazione per migliorare l'assistenza a persone affette da malattia di Parkinson e disturbi del movimento. Le opportunità includono borse biennali per istituzioni volte alla formazione specialistica di nuovi neurologi clinici (fino a 103.800 dollari/anno), il Mentored Clinical Research Award da 50.000 dollari in collaborazione con il Parkinson Study Group per giovani ricercatori entro cinque anni dal termine della specializzazione, e il Nurse Faculty Award (fino a 10.000 dollari) per docenti infermieri. I contributi coprono stipendi, costi diretti di ricerca e attività di sviluppo accademico e clinico.</t>
+          <t>Questo bando promosso dalla Food and Drug Administration (FDA) tramite il meccanismo R01 è destinato a finanziare trial clinici dedicati a rispondere ai bisogni insoddisfatti nell'ambito delle malattie neurodegenerative rare, sia pediatriche che dell'età adulta. I progetti devono valutare l'efficacia e la sicurezza di prodotti terapeutici a supporto di nuove indicazioni cliniche o di modifiche delle indicazioni di etichettatura (labeling). L'obiettivo primario è incrementare il numero di trattamenti approvati dalle autorità regolatorie e favorire un impatto positivo e duraturo sullo sviluppo clinico di terapie per patologie rare. La presentazione di un trial clinico è requisito obbligatorio per accedere al finanziamento.</t>
         </is>
       </c>
       <c r="AE23" s="4" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="AF23" s="4" t="n">
         <v>46312</v>
@@ -3772,17 +3776,17 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>GG-PAR-25-052</t>
+          <t>GG-FOR-FD-25-006</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Da verificare</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -3792,24 +3796,22 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Studi clinici e studi sui biomarcatori NIH StrokeNet per il trattamento, il recupero e la prevenzione dell'ictus (UG3/UH3)</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="n">
-        <v>46345</v>
-      </c>
+          <t>Studi rivolti alle malattie neurodegenerative rare, inclusa la SLA</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="n"/>
       <c r="G24" s="5">
         <f>IF(F24="","",F24-TODAY())</f>
         <v/>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>In scadenza (≤30 gg)</t>
+          <t>In apertura</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>National Institutes of Health</t>
+          <t>Food and Drug Administration</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3819,27 +3821,27 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>National Institutes of Health – PAR-25-052</t>
+          <t>Food and Drug Administration – FOR-FD-25-006</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>NIH StrokeNet Clinical Trials and Biomarker Studies for Stroke Treatment, Recovery, and Prevention (UG3/UH3 Clinical Trial Optional)</t>
+          <t>Studies Addressing Rare Neurodegenerative Diseases including ALS</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>Ictus</t>
+          <t>Altre malattie e riabilitazione</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>stroke</t>
+          <t>neurodegenerat</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>Il bando finanzia trial clinici e studi di biomarcatori dedicati al trattamento, al recupero funzionale e alla prevenzione dell'ictus.</t>
+          <t>Riguarda la SLA e le malattie neurodegenerative rare, ma è focalizzato sullo sviluppo di prodotti medici anziché su interventi riabilitativi specifici.</t>
         </is>
       </c>
       <c r="P24" s="6" t="n"/>
@@ -3849,10 +3851,12 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="S24" s="2" t="n"/>
+      <c r="S24" s="2" t="n">
+        <v>10</v>
+      </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t>Non stimabile – dati insufficienti</t>
+          <t>Media – 10 progetti finanziabili (stima: tasso storico non disponibile)</t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
@@ -3861,7 +3865,7 @@
         </is>
       </c>
       <c r="V24" s="4" t="n">
-        <v>45616</v>
+        <v>45518</v>
       </c>
       <c r="W24" s="2" t="n"/>
       <c r="X24" s="2" t="inlineStr">
@@ -3871,17 +3875,13 @@
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t>State governments; City or township governments; County governments; Native American tribal organizations (other than Federally recognized tribal governments); Public housing authorities/Indian housing authorities; Nonprofits having a 501(c)(3) status with the IRS, other than institutions of higher education; Nonprofits that do not have a 501(c)(3) status with the IRS, other than institutions of h</t>
-        </is>
-      </c>
-      <c r="Z24" s="3" t="inlineStr">
-        <is>
-          <t>Collaborazione obbligatoria all'interno della rete NIH StrokeNet con il National Coordinating Center e i siti clinici affiliati.</t>
-        </is>
-      </c>
+          <t>Nonprofits that do not have a 501(c)(3) status with the IRS, other than institutions of higher education; Public and State controlled institutions of higher education; Native American tribal organizations (other than Federally recognized tribal governments); Independent school districts; Small businesses; Nonprofits having a 501(c)(3) status with the IRS, other than institutions of higher educatio</t>
+        </is>
+      </c>
+      <c r="Z24" s="3" t="n"/>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>Enti esteri non ammessi (call NIH completa)</t>
+          <t>Enti esteri: da verificare nel bando</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
@@ -3891,26 +3891,26 @@
       </c>
       <c r="AC24" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/357256</t>
+          <t>https://www.grants.gov/search-results-detail/356046</t>
         </is>
       </c>
       <c r="AD24" s="3" t="inlineStr">
         <is>
-          <t>Il bando promosso dal National Institutes of Health (NIH/NINDS) sostiene la realizzazione di studi clinici multicentrici esplorativi e di conferma focalizzati su interventi terapeutici promettenti, oltre a studi di validazione di biomarcatori o misure di esito funzionale propedeutici a trial clinici nell'ambito della prevenzione, del trattamento acuto e del recupero post-ictus. I progetti selezionati saranno integrati e condotti all'interno dell'infrastruttura della rete NIH StrokeNet, collaborando con i centri nazionali di coordinamento e gestione dei dati per il reclutamento e l'implementazione del protocollo. Possono candidarsi enti statunitensi come università, istituti di ricerca, ospedali e agenzie governative ammissibili, mentre gli enti esteri non residenti negli Stati Uniti sono esplicitamente esclusi come capofila.</t>
+          <t>Il bando, promosso dalla Food and Drug Administration (FDA), mira a sostenere studi scientifici per far progredire lo sviluppo di prodotti medici destinati a prevenire, diagnosticare, mitigare, trattare o curare la sclerosi laterale amiotrofica (SLA) e altre malattie neurodegenerative rare, sia negli adulti che nei bambini. Attraverso questo programma, l’ente intende colmare lacune conoscitive critiche, generare un impatto significativo sulla gestione delle patologie neurodegenerative rare e fornire dati essenziali per orientare lo sviluppo regolatorio e industriale di interventi innovativi attuali e futuri. Il bando finanzia attività di ricerca volte all'avanzamento di candidati terapeutici e strumenti diagnostici. I dettagli relativi a requisiti specifici di partecipazione e contributi economici sono definiti nella documentazione ufficiale.</t>
         </is>
       </c>
       <c r="AE24" s="4" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="AF24" s="4" t="n">
-        <v>46316</v>
+        <v>46312</v>
       </c>
       <c r="AG24" s="2" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>GG-HHS-2027-ACL-NIDILRR-ARCP-0300</t>
+          <t>GG-PAR-25-052</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -3925,16 +3925,16 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Formazione / fellowship</t>
+          <t>Ricerca clinica</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Programma di formazione avanzata nella ricerca riabilitativa (ARRT) - Vita nella comunità e partecipazione</t>
+          <t>Studi clinici e studi sui biomarcatori NIH StrokeNet per il trattamento, il recupero e la prevenzione dell'ictus (UG3/UH3)</t>
         </is>
       </c>
       <c r="F25" s="4" t="n">
-        <v>46363</v>
+        <v>46345</v>
       </c>
       <c r="G25" s="5">
         <f>IF(F25="","",F25-TODAY())</f>
@@ -3942,12 +3942,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Aperto</t>
+          <t>In scadenza (≤30 gg)</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Administration for Community Living</t>
+          <t>National Institutes of Health</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3957,46 +3957,40 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>Administration for Community Living – HHS-2027-ACL-NIDILRR-ARCP-0300</t>
+          <t>National Institutes of Health – PAR-25-052</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>Advanced Rehabilitation Research Training (ARRT) Program - Community Living and Participation</t>
+          <t>NIH StrokeNet Clinical Trials and Biomarker Studies for Stroke Treatment, Recovery, and Prevention (UG3/UH3 Clinical Trial Optional)</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>Altre malattie e riabilitazione</t>
+          <t>Ictus</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>rehabilitat</t>
+          <t>stroke</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>Finanzia programmi di formazione avanzata per ricercatori nell'ambito della riabilitazione e della disabilità.</t>
-        </is>
-      </c>
-      <c r="P25" s="6" t="n">
-        <v>250000</v>
-      </c>
-      <c r="Q25" s="6" t="n">
-        <v>250000</v>
-      </c>
+          <t>Il bando finanzia trial clinici e studi di biomarcatori dedicati al trattamento, al recupero funzionale e alla prevenzione dell'ictus.</t>
+        </is>
+      </c>
+      <c r="P25" s="6" t="n"/>
+      <c r="Q25" s="6" t="n"/>
       <c r="R25" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="S25" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="S25" s="2" t="n"/>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t>Bassa – 1 progetti finanziabili (stima: tasso storico non disponibile)</t>
+          <t>Non stimabile – dati insufficienti</t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
@@ -4005,13 +3999,9 @@
         </is>
       </c>
       <c r="V25" s="4" t="n">
-        <v>46290</v>
-      </c>
-      <c r="W25" s="2" t="inlineStr">
-        <is>
-          <t>36 mesi</t>
-        </is>
-      </c>
+        <v>45616</v>
+      </c>
+      <c r="W25" s="2" t="n"/>
       <c r="X25" s="2" t="inlineStr">
         <is>
           <t>Ricerca</t>
@@ -4019,13 +4009,17 @@
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t>Private institutions of higher education; Public and State controlled institutions of higher education</t>
-        </is>
-      </c>
-      <c r="Z25" s="3" t="n"/>
+          <t>Special district governments; State governments; Independent school districts; Public and State controlled institutions of higher education; Small businesses; Nonprofits that do not have a 501(c)(3) status with the IRS, other than institutions of higher education; For profit organizations other than small businesses; Public housing authorities/Indian housing authorities; Others (see text field ent</t>
+        </is>
+      </c>
+      <c r="Z25" s="3" t="inlineStr">
+        <is>
+          <t>Collaborazione obbligatoria all'interno della rete NIH StrokeNet con il National Coordinating Center e i siti clinici affiliati.</t>
+        </is>
+      </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>Solo enti statunitensi</t>
+          <t>Enti esteri non ammessi (call NIH completa)</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
@@ -4035,16 +4029,16 @@
       </c>
       <c r="AC25" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/363963</t>
+          <t>https://www.grants.gov/search-results-detail/357256</t>
         </is>
       </c>
       <c r="AD25" s="3" t="inlineStr">
         <is>
-          <t>Il programma Advanced Rehabilitation Research Training (ARRT), gestito dal NIDILRR presso l'Administration for Community Living, si propone di fornire formazione avanzata ed esperienza scientifica a ricercatori post-dottorato nel settore della riabilitazione, compresi ricercatori con disabilità. L'obiettivo del bando è rafforzare la capacità di condurre ricerche multidisciplinari di elevata qualità focalizzate sul miglioramento della vita autonoma nella comunità e sulla partecipazione sociale delle persone con disabilità. Il finanziamento sostiene un singolo progetto triennale articolato in tre periodi di budget annuali. La candidatura è aperta esclusivamente a istituti di istruzione superiore pubblici, statali o privati con sede negli Stati Uniti, mentre gli enti stranieri non sono ammessi a partecipare né a ricevere fondi.</t>
+          <t>Il bando promosso dal National Institutes of Health (NIH/NINDS) sostiene la realizzazione di studi clinici multicentrici esplorativi e di conferma focalizzati su interventi terapeutici promettenti, oltre a studi di validazione di biomarcatori o misure di esito funzionale propedeutici a trial clinici nell'ambito della prevenzione, del trattamento acuto e del recupero post-ictus. I progetti selezionati saranno integrati e condotti all'interno dell'infrastruttura della rete NIH StrokeNet, collaborando con i centri nazionali di coordinamento e gestione dei dati per il reclutamento e l'implementazione del protocollo. Possono candidarsi enti statunitensi come università, istituti di ricerca, ospedali e agenzie governative ammissibili, mentre gli enti esteri non residenti negli Stati Uniti sono esplicitamente esclusi come capofila.</t>
         </is>
       </c>
       <c r="AE25" s="4" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="AF25" s="4" t="n">
         <v>46316</v>
@@ -4054,7 +4048,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>GG-HHS-2027-ACL-NIDILRR-AREM-0301</t>
+          <t>GG-HHS-2027-ACL-NIDILRR-ARCP-0300</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -4074,7 +4068,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Programma di formazione avanzata nella ricerca riabilitativa (ARRT) - Occupazione</t>
+          <t>Programma di formazione avanzata nella ricerca riabilitativa (ARRT) - Vita nella comunità e partecipazione</t>
         </is>
       </c>
       <c r="F26" s="4" t="n">
@@ -4101,12 +4095,12 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>Administration for Community Living – HHS-2027-ACL-NIDILRR-AREM-0301</t>
+          <t>Administration for Community Living – HHS-2027-ACL-NIDILRR-ARCP-0300</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>Advanced Rehabilitation Research Training (ARRT) Program - Employment</t>
+          <t>Advanced Rehabilitation Research Training (ARRT) Program - Community Living and Participation</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -4121,7 +4115,7 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>Finanzia la formazione avanzata di ricercatori nel campo della riabilitazione e disabilità con focus sull'occupazione.</t>
+          <t>Finanzia programmi di formazione avanzata per ricercatori nell'ambito della riabilitazione e della disabilità.</t>
         </is>
       </c>
       <c r="P26" s="6" t="n">
@@ -4163,7 +4157,7 @@
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t>Private institutions of higher education; Public and State controlled institutions of higher education</t>
+          <t>Public and State controlled institutions of higher education; Private institutions of higher education</t>
         </is>
       </c>
       <c r="Z26" s="3" t="n"/>
@@ -4179,16 +4173,16 @@
       </c>
       <c r="AC26" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/363964</t>
+          <t>https://www.grants.gov/search-results-detail/363963</t>
         </is>
       </c>
       <c r="AD26" s="3" t="inlineStr">
         <is>
-          <t>Il programma ARRT promosso dal NIDILRR (Administration for Community Living) è finalizzato a erogare formazione avanzata ed esperienza scientifica a professionisti in possesso di dottorato o titoli equivalenti nel settore della riabilitazione, incentivando la partecipazione di ricercatori con disabilità. Questa specifica opportunità si concentra sul potenziamento delle competenze per condurre studi multidisciplinari incentrati sugli esiti lavorativi e sull'inclusione occupazionale delle persone con disabilità. L'iniziativa prevede l'assegnazione di un unico finanziamento per una durata complessiva di 36 mesi, suddiviso in tre annualità di budget. Possono concorrere unicamente istituzioni di istruzione superiore pubbliche, statali o private statunitensi, mentre gli enti esteri sono esplicitamente esclusi dalla competizione e dall'assegnazione del contributo.</t>
+          <t>Il programma Advanced Rehabilitation Research Training (ARRT), gestito dal NIDILRR presso l'Administration for Community Living, si propone di fornire formazione avanzata ed esperienza scientifica a ricercatori post-dottorato nel settore della riabilitazione, compresi ricercatori con disabilità. L'obiettivo del bando è rafforzare la capacità di condurre ricerche multidisciplinari di elevata qualità focalizzate sul miglioramento della vita autonoma nella comunità e sulla partecipazione sociale delle persone con disabilità. Il finanziamento sostiene un singolo progetto triennale articolato in tre periodi di budget annuali. La candidatura è aperta esclusivamente a istituti di istruzione superiore pubblici, statali o privati con sede negli Stati Uniti, mentre gli enti stranieri non sono ammessi a partecipare né a ricevere fondi.</t>
         </is>
       </c>
       <c r="AE26" s="4" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="AF26" s="4" t="n">
         <v>46316</v>
@@ -4198,7 +4192,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>GG-HHS-2027-ACL-NIDILRR-ARHF-0302</t>
+          <t>GG-HHS-2027-ACL-NIDILRR-AREM-0301</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -4218,7 +4212,7 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Programma di formazione avanzata nella ricerca riabilitativa (ARRT) - Salute e funzionalità</t>
+          <t>Programma di formazione avanzata nella ricerca riabilitativa (ARRT) - Occupazione</t>
         </is>
       </c>
       <c r="F27" s="4" t="n">
@@ -4245,12 +4239,12 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>Administration for Community Living – HHS-2027-ACL-NIDILRR-ARHF-0302</t>
+          <t>Administration for Community Living – HHS-2027-ACL-NIDILRR-AREM-0301</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>Advanced Rehabilitation Research Training (ARRT) Program - Health and Function</t>
+          <t>Advanced Rehabilitation Research Training (ARRT) Program - Employment</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -4265,7 +4259,7 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>Finanzia programmi di formazione avanzata per ricercatori nell'ambito della riabilitazione focalizzati su salute e funzionalità.</t>
+          <t>Finanzia la formazione avanzata di ricercatori nel campo della riabilitazione e disabilità con focus sull'occupazione.</t>
         </is>
       </c>
       <c r="P27" s="6" t="n">
@@ -4302,7 +4296,7 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>Ricerca</t>
+          <t>Dottorato / formazione / mobilità</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
@@ -4323,16 +4317,16 @@
       </c>
       <c r="AC27" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/363965</t>
+          <t>https://www.grants.gov/search-results-detail/363964</t>
         </is>
       </c>
       <c r="AD27" s="3" t="inlineStr">
         <is>
-          <t>L'iniziativa ARRT promossa dal National Institute on Disability, Independent Living, and Rehabilitation Research (NIDILRR) sostiene programmi formativi avanzati destinati a ricercatori post-dottorato nel campo della riabilitazione, inclusi studiosi con disabilità. L'obiettivo consiste nell'accrescere le competenze metodologiche e scientifiche per sviluppare ricerche multidisciplinari mirate al miglioramento della salute, del recupero funzionale e del benessere delle persone con disabilità fisiche o cognitive. È prevista l'assegnazione di un solo finanziamento della durata di 36 mesi, articolato su tre cicli annuali di spesa. La partecipazione è riservata esclusivamente a istituti di istruzione superiore pubblici, statali o privati statunitensi; gli enti internazionali e stranieri non sono ammessi a concorrere né a ricevere il finanziamento.</t>
+          <t>Il programma ARRT promosso dal NIDILRR (Administration for Community Living) è finalizzato a erogare formazione avanzata ed esperienza scientifica a professionisti in possesso di dottorato o titoli equivalenti nel settore della riabilitazione, incentivando la partecipazione di ricercatori con disabilità. Questa specifica opportunità si concentra sul potenziamento delle competenze per condurre studi multidisciplinari incentrati sugli esiti lavorativi e sull'inclusione occupazionale delle persone con disabilità. L'iniziativa prevede l'assegnazione di un unico finanziamento per una durata complessiva di 36 mesi, suddiviso in tre annualità di budget. Possono concorrere unicamente istituzioni di istruzione superiore pubbliche, statali o private statunitensi, mentre gli enti esteri sono esplicitamente esclusi dalla competizione e dall'assegnazione del contributo.</t>
         </is>
       </c>
       <c r="AE27" s="4" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="AF27" s="4" t="n">
         <v>46316</v>
@@ -4342,7 +4336,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>WEB-14a8635c6be7</t>
+          <t>GG-HHS-2027-ACL-NIDILRR-ARHF-0302</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -4362,11 +4356,11 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Borse di studio per la promozione degli studi di dottorato (PODS)</t>
+          <t>Programma di formazione avanzata nella ricerca riabilitativa (ARRT) - Salute e funzionalità</t>
         </is>
       </c>
       <c r="F28" s="4" t="n">
-        <v>46407</v>
+        <v>46363</v>
       </c>
       <c r="G28" s="5">
         <f>IF(F28="","",F28-TODAY())</f>
@@ -4379,44 +4373,44 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Foundation for Physical Therapy Research</t>
+          <t>Administration for Community Living</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>Foundation for Physical Therapy Research</t>
+          <t>Grants.gov</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>Promotion of Doctoral Studies Scholarships</t>
+          <t>Administration for Community Living – HHS-2027-ACL-NIDILRR-ARHF-0302</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>Promotion of Doctoral Studies Scholarships</t>
+          <t>Advanced Rehabilitation Research Training (ARRT) Program - Health and Function</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>Invecchiamento, Altre malattie e riabilitazione</t>
+          <t>Altre malattie e riabilitazione</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>geriatr, physical therap, cardiovascular, pulmonary</t>
+          <t>rehabilitat</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>Finanzia borse di studio dottorali per fisioterapisti impegnati nella ricerca riabilitativa clinica e applicata.</t>
+          <t>Finanzia programmi di formazione avanzata per ricercatori nell'ambito della riabilitazione focalizzati su salute e funzionalità.</t>
         </is>
       </c>
       <c r="P28" s="6" t="n">
-        <v>7500</v>
+        <v>250000</v>
       </c>
       <c r="Q28" s="6" t="n">
-        <v>15000</v>
+        <v>250000</v>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
@@ -4424,22 +4418,24 @@
         </is>
       </c>
       <c r="S28" s="2" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t>Alta – 22 progetti finanziabili (stima: tasso storico non disponibile)</t>
+          <t>Bassa – 1 progetti finanziabili (stima: tasso storico non disponibile)</t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t>Non indicato</t>
-        </is>
-      </c>
-      <c r="V28" s="4" t="n"/>
+          <t>Interamente finanziato</t>
+        </is>
+      </c>
+      <c r="V28" s="4" t="n">
+        <v>46290</v>
+      </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>12 mesi</t>
+          <t>36 mesi</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
@@ -4449,13 +4445,13 @@
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t>Fisioterapisti e fisioterapeuti assistenti APTA membri</t>
+          <t>Private institutions of higher education; Public and State controlled institutions of higher education</t>
         </is>
       </c>
       <c r="Z28" s="3" t="n"/>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Solo enti statunitensi</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
@@ -4465,26 +4461,26 @@
       </c>
       <c r="AC28" s="7" t="inlineStr">
         <is>
-          <t>https://foundation4pt.org/foundation-funding-opportunities/scholarships/</t>
+          <t>https://www.grants.gov/search-results-detail/363965</t>
         </is>
       </c>
       <c r="AD28" s="3" t="inlineStr">
         <is>
-          <t>La Foundation for Physical Therapy Research offre borse di studio a supporto dei fisioterapisti abilitati e assistenti di fisioterapia, iscritti all'APTA, che frequentano un programma di dottorato di ricerca (PhD, EdD, DSc) con l'intento di intraprendere una carriera scientifica nella riabilitazione. Il bando prevede due fasi: pre-candidatura (PODSI), con borse annuali di 7.500 dollari per il percorso di corsi preliminari, e candidatura dottorale (PODSII), con borse annuali di 15.000 dollari per la fase di tesi e ricerca. Sono previsti finanziamenti generali e su aree specialistiche quali neurologia, geriatria, riabilitazione cardiovascolare e polmonare, pediatria e ricerca sui servizi sanitari, con un totale stimato di circa 22 borse disponibili.</t>
+          <t>L'iniziativa ARRT promossa dal National Institute on Disability, Independent Living, and Rehabilitation Research (NIDILRR) sostiene programmi formativi avanzati destinati a ricercatori post-dottorato nel campo della riabilitazione, inclusi studiosi con disabilità. L'obiettivo consiste nell'accrescere le competenze metodologiche e scientifiche per sviluppare ricerche multidisciplinari mirate al miglioramento della salute, del recupero funzionale e del benessere delle persone con disabilità fisiche o cognitive. È prevista l'assegnazione di un solo finanziamento della durata di 36 mesi, articolato su tre cicli annuali di spesa. La partecipazione è riservata esclusivamente a istituti di istruzione superiore pubblici, statali o privati statunitensi; gli enti internazionali e stranieri non sono ammessi a concorrere né a ricevere il finanziamento.</t>
         </is>
       </c>
       <c r="AE28" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="AF28" s="4" t="n">
         <v>46316</v>
-      </c>
-      <c r="AF28" s="4" t="n">
-        <v>46312</v>
       </c>
       <c r="AG28" s="2" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>GG-HHS-2027-ACL-NIDILRR-DPTB-0311</t>
+          <t>WEB-14a8635c6be7</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -4499,16 +4495,16 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Ricerca clinica</t>
+          <t>Formazione / fellowship</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Centri modello per il sistema di cura e riabilitazione del trauma cranico encefalico</t>
+          <t>Borse di studio per la promozione degli studi di dottorato (PODS)</t>
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>46478</v>
+        <v>46407</v>
       </c>
       <c r="G29" s="5">
         <f>IF(F29="","",F29-TODAY())</f>
@@ -4521,44 +4517,44 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>Administration for Community Living</t>
+          <t>Foundation for Physical Therapy Research</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>Grants.gov</t>
+          <t>Foundation for Physical Therapy Research</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>Administration for Community Living – HHS-2027-ACL-NIDILRR-DPTB-0311</t>
+          <t>Promotion of Doctoral Studies Scholarships</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>Traumatic Brain Injury Model Systems Centers</t>
+          <t>Promotion of Doctoral Studies Scholarships</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>Altre malattie e riabilitazione</t>
+          <t>Invecchiamento, Altre malattie e riabilitazione</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>rehabilitat, traumatic brain injur</t>
+          <t>geriatr, physical therap, cardiovascular, pulmonary</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>Focalizzato specificamente sulla riabilitazione clinica evidence-based e il recupero funzionale nei pazienti con trauma cranico (TBI).</t>
+          <t>Finanzia borse di studio dottorali per fisioterapisti impegnati nella ricerca riabilitativa clinica e applicata.</t>
         </is>
       </c>
       <c r="P29" s="6" t="n">
-        <v>8450000</v>
+        <v>7500</v>
       </c>
       <c r="Q29" s="6" t="n">
-        <v>640000</v>
+        <v>15000</v>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
@@ -4566,40 +4562,38 @@
         </is>
       </c>
       <c r="S29" s="2" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t>Media – 14 progetti finanziabili (stima: tasso storico non disponibile)</t>
+          <t>Alta – 22 progetti finanziabili (stima: tasso storico non disponibile)</t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t>Interamente finanziato</t>
-        </is>
-      </c>
-      <c r="V29" s="4" t="n">
-        <v>46290</v>
-      </c>
+          <t>Non indicato</t>
+        </is>
+      </c>
+      <c r="V29" s="4" t="n"/>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>60 mesi</t>
+          <t>12 mesi</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>Ricerca</t>
+          <t>Dottorato / formazione / mobilità</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t>City or township governments; Small businesses; State governments; Special district governments; Nonprofits that do not have a 501(c)(3) status with the IRS, other than institutions of higher education; Nonprofits having a 501(c)(3) status with the IRS, other than institutions of higher education; County governments; Public and State controlled institutions of higher education; Native American tri</t>
+          <t>Fisioterapisti e assistenti fisioterapisti abilitati, membri APTA, iscritti a un programma di dottorato di ricerca accademico.</t>
         </is>
       </c>
       <c r="Z29" s="3" t="n"/>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>Solo enti statunitensi</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
@@ -4609,26 +4603,26 @@
       </c>
       <c r="AC29" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/363970</t>
+          <t>https://foundation4pt.org/foundation-funding-opportunities/scholarships/</t>
         </is>
       </c>
       <c r="AD29" s="3" t="inlineStr">
         <is>
-          <t>L'iniziativa finanzia i centri TBI Model Systems (TBIMS) con lo scopo di condurre ricerche cliniche per lo sviluppo e l'accesso alla riabilitazione evidence-based nei traumi cranio-encefalici. I centri devono generare nuova conoscenza per migliorare gli esiti funzionali, l'inclusione nella comunità e l'occupazione, oltre a contribuire al database longitudinale TBIMS. Possono candidarsi esclusivamente enti dotati di un continuum multidisciplinare di cura (dall'emergenza alla riabilitazione post-acuta). Le entità estere sono escluse. Il progetto prevede una durata di 60 mesi.</t>
+          <t>La Foundation for Physical Therapy Research offre borse di studio a supporto dei fisioterapisti abilitati e assistenti di fisioterapia, iscritti all'APTA, che frequentano un programma di dottorato di ricerca (PhD, EdD, DSc) con l'intento di intraprendere una carriera scientifica nella riabilitazione. Il bando prevede due fasi: pre-candidatura (PODSI), con borse annuali di 7.500 dollari per il percorso di corsi preliminari, e candidatura dottorale (PODSII), con borse annuali di 15.000 dollari per la fase di tesi e ricerca. Sono previsti finanziamenti generali e su aree specialistiche quali neurologia, geriatria, riabilitazione cardiovascolare e polmonare, pediatria e ricerca sui servizi sanitari, con un totale stimato di circa 22 borse disponibili.</t>
         </is>
       </c>
       <c r="AE29" s="4" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="AF29" s="4" t="n">
-        <v>46316</v>
+        <v>46312</v>
       </c>
       <c r="AG29" s="2" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>GG-HHS-2027-ACL-NIDILRR-REGE-0312</t>
+          <t>GG-HHS-2027-ACL-NIDILRR-DPTB-0311</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -4643,16 +4637,16 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Tecnologia / innovazione</t>
+          <t>Ricerca clinica</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Centro di ricerca ingegneristica per la riabilitazione sulle tecnologie per ricreazione, sport ed esercizio nelle disabilità</t>
+          <t>Centri modello per il sistema di cura e riabilitazione del trauma cranico encefalico</t>
         </is>
       </c>
       <c r="F30" s="4" t="n">
-        <v>46492</v>
+        <v>46478</v>
       </c>
       <c r="G30" s="5">
         <f>IF(F30="","",F30-TODAY())</f>
@@ -4675,34 +4669,34 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>Administration for Community Living – HHS-2027-ACL-NIDILRR-REGE-0312</t>
+          <t>Administration for Community Living – HHS-2027-ACL-NIDILRR-DPTB-0311</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>Rehabilitation Engineering Research Center on Recreational, Sport, and Exercise Technologies for People with Disabilities</t>
+          <t>Traumatic Brain Injury Model Systems Centers</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>Tecnologie riabilitazione, Altre malattie e riabilitazione</t>
+          <t>Altre malattie e riabilitazione</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>rehabilitation engineering, rehabilitat</t>
+          <t>rehabilitat, traumatic brain injur</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>Finanzia ricerca ingegneristica e sviluppo tecnologico per l'esercizio, lo sport e la riabilitazione di persone con disabilità.</t>
+          <t>Focalizzato specificamente sulla riabilitazione clinica evidence-based e il recupero funzionale nei pazienti con trauma cranico (TBI).</t>
         </is>
       </c>
       <c r="P30" s="6" t="n">
-        <v>975000</v>
+        <v>8450000</v>
       </c>
       <c r="Q30" s="6" t="n">
-        <v>975000</v>
+        <v>640000</v>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
@@ -4710,11 +4704,11 @@
         </is>
       </c>
       <c r="S30" s="2" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t>Bassa – 1 progetti finanziabili (stima: tasso storico non disponibile)</t>
+          <t>Media – 14 progetti finanziabili (stima: tasso storico non disponibile)</t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
@@ -4737,7 +4731,7 @@
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nonprofits that do not have a 501(c)(3) status with the IRS, other than institutions of higher education; Nonprofits having a 501(c)(3) status with the IRS, other than institutions of higher education; Public and State controlled institutions of higher education; Small businesses; State governments; County governments; Private institutions of higher education; City or township governments; Others </t>
+          <t>Small businesses; State governments; County governments; City or township governments; Nonprofits that do not have a 501(c)(3) status with the IRS, other than institutions of higher education; Public and State controlled institutions of higher education; Others (see text field entitled "Additional Information on Eligibility" for clarification); Nonprofits having a 501(c)(3) status with the IRS, ot</t>
         </is>
       </c>
       <c r="Z30" s="3" t="n"/>
@@ -4753,16 +4747,16 @@
       </c>
       <c r="AC30" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/363973</t>
+          <t>https://www.grants.gov/search-results-detail/363970</t>
         </is>
       </c>
       <c r="AD30" s="3" t="inlineStr">
         <is>
-          <t>Il bando finanzia un Rehabilitation Engineering Research Center (RERC) per condurre ricerca ingegneristica avanzata e sviluppo di tecnologie innovative dedicate a promuovere l'esercizio fisico, lo sport e la salute in persone con disabilità, eliminando le barriere ambientali. NIDILRR intende assegnare un singolo finanziamento della durata complessiva di 60 mesi (5 periodi di bilancio da 12 mesi). Possono candidarsi stati, enti pubblici e privati (compresi for-profit), atenei e organizzazioni comunitarie statunitensi; le organizzazioni estere non sono ammesse al bando.</t>
+          <t>L'iniziativa finanzia i centri TBI Model Systems (TBIMS) con lo scopo di condurre ricerche cliniche per lo sviluppo e l'accesso alla riabilitazione evidence-based nei traumi cranio-encefalici. I centri devono generare nuova conoscenza per migliorare gli esiti funzionali, l'inclusione nella comunità e l'occupazione, oltre a contribuire al database longitudinale TBIMS. Possono candidarsi esclusivamente enti dotati di un continuum multidisciplinare di cura (dall'emergenza alla riabilitazione post-acuta). Le entità estere sono escluse. Il progetto prevede una durata di 60 mesi.</t>
         </is>
       </c>
       <c r="AE30" s="4" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="AF30" s="4" t="n">
         <v>46316</v>
@@ -4772,7 +4766,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>GG-HHS-2027-ACL-NIDILRR-REGE-0313</t>
+          <t>GG-HHS-2027-ACL-NIDILRR-REGE-0312</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -4792,11 +4786,11 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Centro di ricerca ingegneristica per la riabilitazione sulle tecnologie per persone non vedenti o ipovedenti</t>
+          <t>Centro di ricerca ingegneristica per la riabilitazione sulle tecnologie per ricreazione, sport ed esercizio nelle disabilità</t>
         </is>
       </c>
       <c r="F31" s="4" t="n">
-        <v>46499</v>
+        <v>46492</v>
       </c>
       <c r="G31" s="5">
         <f>IF(F31="","",F31-TODAY())</f>
@@ -4819,27 +4813,27 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>Administration for Community Living – HHS-2027-ACL-NIDILRR-REGE-0313</t>
+          <t>Administration for Community Living – HHS-2027-ACL-NIDILRR-REGE-0312</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>Rehabilitation Engineering Research Center on Technologies for People Who are Blind or have Low Vision</t>
+          <t>Rehabilitation Engineering Research Center on Recreational, Sport, and Exercise Technologies for People with Disabilities</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>Tecnologie riabilitazione</t>
+          <t>Tecnologie riabilitazione, Altre malattie e riabilitazione</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>rehabilitation engineering</t>
+          <t>rehabilitation engineering, rehabilitat</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>Dedicato allo sviluppo di tecnologie e ausili per l'autonomia e la riabilitazione visiva in persone non vedenti o ipovedenti.</t>
+          <t>Finanzia ricerca ingegneristica e sviluppo tecnologico per l'esercizio, lo sport e la riabilitazione di persone con disabilità.</t>
         </is>
       </c>
       <c r="P31" s="6" t="n">
@@ -4876,12 +4870,12 @@
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>Ricerca</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t>Nonprofits having a 501(c)(3) status with the IRS, other than institutions of higher education; For profit organizations other than small businesses; Public and State controlled institutions of higher education; Native American tribal organizations (other than Federally recognized tribal governments); State governments; County governments; Nonprofits that do not have a 501(c)(3) status with the IR</t>
+          <t>For profit organizations other than small businesses; City or township governments; Private institutions of higher education; Public and State controlled institutions of higher education; Nonprofits that do not have a 501(c)(3) status with the IRS, other than institutions of higher education; Special district governments; State governments; Small businesses; Native American tribal organizations (o</t>
         </is>
       </c>
       <c r="Z31" s="3" t="n"/>
@@ -4897,16 +4891,16 @@
       </c>
       <c r="AC31" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/363974</t>
+          <t>https://www.grants.gov/search-results-detail/363973</t>
         </is>
       </c>
       <c r="AD31" s="3" t="inlineStr">
         <is>
-          <t>Il programma Rehabilitation Engineering Research Centers (RERC) intende finanziare un centro focalizzato sulla ricerca ingegneristica e sullo sviluppo di tecnologie assistive avanzate volte a promuovere l'indipendenza funzionale e la vita nella comunità per individui non vedenti o ipovedenti. È previsto il finanziamento di un unico progetto della durata di 60 mesi. Possono partecipare atenei, enti pubblici o privati profit e no-profit con sede negli Stati Uniti. Le entità straniere non sono idonee alla candidatura né alla ricezione dei fondi.</t>
+          <t>Il bando finanzia un Rehabilitation Engineering Research Center (RERC) per condurre ricerca ingegneristica avanzata e sviluppo di tecnologie innovative dedicate a promuovere l'esercizio fisico, lo sport e la salute in persone con disabilità, eliminando le barriere ambientali. NIDILRR intende assegnare un singolo finanziamento della durata complessiva di 60 mesi (5 periodi di bilancio da 12 mesi). Possono candidarsi stati, enti pubblici e privati (compresi for-profit), atenei e organizzazioni comunitarie statunitensi; le organizzazioni estere non sono ammesse al bando.</t>
         </is>
       </c>
       <c r="AE31" s="4" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="AF31" s="4" t="n">
         <v>46316</v>
@@ -4916,7 +4910,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>GG-RFA-NS-26-001</t>
+          <t>GG-HHS-2027-ACL-NIDILRR-REGE-0313</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -4926,21 +4920,21 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Ricerca clinica</t>
+          <t>Tecnologia / innovazione</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Accesso allargato a popolazioni intermedie di pazienti con sclerosi laterale amiotrofica (U01)</t>
+          <t>Centro di ricerca ingegneristica per la riabilitazione sulle tecnologie per persone non vedenti o ipovedenti</t>
         </is>
       </c>
       <c r="F32" s="4" t="n">
-        <v>46336</v>
+        <v>46499</v>
       </c>
       <c r="G32" s="5">
         <f>IF(F32="","",F32-TODAY())</f>
@@ -4948,12 +4942,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>In scadenza (≤30 gg)</t>
+          <t>Aperto</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>National Institutes of Health</t>
+          <t>Administration for Community Living</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -4963,44 +4957,46 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>National Institutes of Health – RFA-NS-26-001</t>
+          <t>Administration for Community Living – HHS-2027-ACL-NIDILRR-REGE-0313</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>Amyotrophic Lateral Sclerosis (ALS) Intermediate Patient Population Expanded Access (U01 Clinical Trial Required)</t>
+          <t>Rehabilitation Engineering Research Center on Technologies for People Who are Blind or have Low Vision</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>Altre malattie e riabilitazione</t>
+          <t>Tecnologie riabilitazione</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>amyotrophic lateral sclerosis</t>
+          <t>rehabilitation engineering</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>Riguarda la sclerosi laterale amiotrofica (SLA) nell'ambito di farmaci sperimentali in accesso allargato, non la riabilitazione.</t>
+          <t>Dedicato allo sviluppo di tecnologie e ausili per l'autonomia e la riabilitazione visiva in persone non vedenti o ipovedenti.</t>
         </is>
       </c>
       <c r="P32" s="6" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="Q32" s="6" t="n"/>
+        <v>975000</v>
+      </c>
+      <c r="Q32" s="6" t="n">
+        <v>975000</v>
+      </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="S32" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t>Bassa – 4 progetti finanziabili (stima: tasso storico non disponibile)</t>
+          <t>Bassa – 1 progetti finanziabili (stima: tasso storico non disponibile)</t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
@@ -5009,24 +5005,24 @@
         </is>
       </c>
       <c r="V32" s="4" t="n">
-        <v>46146</v>
-      </c>
-      <c r="W32" s="2" t="n"/>
+        <v>46290</v>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>60 mesi</t>
+        </is>
+      </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>Ricerca</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nonprofits having a 501(c)(3) status with the IRS, other than institutions of higher education; Nonprofits that do not have a 501(c)(3) status with the IRS, other than institutions of higher education; Native American tribal governments (Federally recognized); For profit organizations other than small businesses; Public housing authorities/Indian housing authorities; Special district governments; </t>
-        </is>
-      </c>
-      <c r="Z32" s="3" t="inlineStr">
-        <is>
-          <t>Centri di sperimentazione clinica collegati a trial di fase 2/3 o 3 con sponsor di piccola impresa</t>
-        </is>
-      </c>
+          <t>Private institutions of higher education; Native American tribal organizations (other than Federally recognized tribal governments); County governments; Public and State controlled institutions of higher education; Native American tribal governments (Federally recognized); Nonprofits that do not have a 501(c)(3) status with the IRS, other than institutions of higher education; City or township gov</t>
+        </is>
+      </c>
+      <c r="Z32" s="3" t="n"/>
       <c r="AA32" s="2" t="inlineStr">
         <is>
           <t>Solo enti statunitensi</t>
@@ -5039,16 +5035,16 @@
       </c>
       <c r="AC32" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/360400</t>
+          <t>https://www.grants.gov/search-results-detail/363974</t>
         </is>
       </c>
       <c r="AD32" s="3" t="inlineStr">
         <is>
-          <t>Bando promosso dal NINDS per condurre attività di ricerca clinica che utilizzano dati derivanti da programmi di accesso allargato (Expanded Access) a farmaci o prodotti biologici sperimentali per la sclerosi laterale amiotrofica (SLA). L'opportunità è indirizzata a popolazioni di pazienti di dimensioni intermedie che non risultano idonei all'arruolamento nei trial clinici convenzionali per il trattamento o la prevenzione della SLA. Possono partecipare unicamente centri clinici già coinvolti in trial registrativi di fase 2/3 o 3 sponsorizzati da piccole imprese in possesso di IND approvato dalla FDA. Il bando esclude categoricamente gli enti non statunitensi e le collaborazioni con componenti estere.</t>
+          <t>Il programma Rehabilitation Engineering Research Centers (RERC) intende finanziare un centro focalizzato sulla ricerca ingegneristica e sullo sviluppo di tecnologie assistive avanzate volte a promuovere l'indipendenza funzionale e la vita nella comunità per individui non vedenti o ipovedenti. È previsto il finanziamento di un unico progetto della durata di 60 mesi. Possono partecipare atenei, enti pubblici o privati profit e no-profit con sede negli Stati Uniti. Le entità straniere non sono idonee alla candidatura né alla ricezione dei fondi.</t>
         </is>
       </c>
       <c r="AE32" s="4" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="AF32" s="4" t="n">
         <v>46316</v>
@@ -5058,7 +5054,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>GG-RFA-NS-28-009</t>
+          <t>WEB-c6a9b085a5f9</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -5068,7 +5064,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -5078,57 +5074,57 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Accesso allargato a popolazioni intermedie di pazienti con sclerosi laterale amiotrofica (SLA) (U01)</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="n">
-        <v>46532</v>
-      </c>
+          <t>Bandi di ricerca su implementazione, interventi e coinvolgimento comunitario in terapia occupazionale 2026-2027</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="n"/>
       <c r="G33" s="5">
         <f>IF(F33="","",F33-TODAY())</f>
         <v/>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Aperto</t>
+          <t>Scadenza da verificare</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>National Institutes of Health</t>
+          <t>American Occupational Therapy Foundation</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>Grants.gov</t>
+          <t>American Occupational Therapy Foundation</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>National Institutes of Health – RFA-NS-28-009</t>
+          <t>Grant Award Guidelines 2026 2027 Final</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>Amyotrophic Lateral Sclerosis (ALS) Intermediate Patient Population Expanded Access (U01 Clinical Trial Required)</t>
+          <t>Grant Award Guidelines 2026 2027 Final</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>Ictus, Altre malattie e riabilitazione</t>
+          <t>Ictus, Invecchiamento, Altre malattie e riabilitazione</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>stroke, amyotrophic lateral sclerosis, neurological disorder</t>
+          <t>stroke, dementi, cognitive impairment, occupational therap, spinal cord injur, traumatic brain injur, cerebral palsy, disabilit</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>Riguarda la SLA ma è focalizzato su protocolli di accesso allargato a farmaci sperimentali e biomarcatori.</t>
-        </is>
-      </c>
-      <c r="P33" s="6" t="n"/>
+          <t>Bando focalizzato sulla ricerca clinica di intervento e implementazione in terapia occupazionale, centrale per il recupero funzionale e l'autonomia.</t>
+        </is>
+      </c>
+      <c r="P33" s="6" t="n">
+        <v>100000</v>
+      </c>
       <c r="Q33" s="6" t="n"/>
       <c r="R33" s="2" t="inlineStr">
         <is>
@@ -5143,27 +5139,25 @@
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t>Interamente finanziato</t>
-        </is>
-      </c>
-      <c r="V33" s="4" t="n">
-        <v>46288</v>
-      </c>
+          <t>Co-finanziamento da verificare</t>
+        </is>
+      </c>
+      <c r="V33" s="4" t="n"/>
       <c r="W33" s="2" t="n"/>
       <c r="X33" s="2" t="inlineStr">
         <is>
           <t>Ricerca</t>
         </is>
       </c>
-      <c r="Y33" s="3" t="inlineStr">
-        <is>
-          <t>Native American tribal governments (Federally recognized); County governments; Small businesses; State governments; Nonprofits having a 501(c)(3) status with the IRS, other than institutions of higher education; Special district governments; For profit organizations other than small businesses; Others (see text field entitled "Additional Information on Eligibility" for clarification); Private inst</t>
-        </is>
-      </c>
-      <c r="Z33" s="3" t="n"/>
+      <c r="Y33" s="3" t="n"/>
+      <c r="Z33" s="3" t="inlineStr">
+        <is>
+          <t>Prevista collaborazione attiva tra ricercatori, organizzazioni e partner di comunità per il bando CERG</t>
+        </is>
+      </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>Solo enti statunitensi</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
@@ -5173,26 +5167,26 @@
       </c>
       <c r="AC33" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/363926</t>
+          <t>https://www.aotf.org/wp-content/uploads/2026/10/Grant_Award-Guidelines_2026-2027_Final.pdf</t>
         </is>
       </c>
       <c r="AD33" s="3" t="inlineStr">
         <is>
-          <t>Il National Institute of Neurological Disorders and Stroke (NINDS) intende sostenere la ricerca scientifica basata sui dati derivanti da protocolli di accesso allargato di dimensioni intermedie per la sclerosi laterale amiotrofica (SLA). I protocolli ammissibili devono fornire accesso a farmaci o prodotti biologici sperimentali e generare dati a supporto della ricerca su prevenzione, diagnosi o trattamento della SLA, inclusi effetti su biomarcatori, sicurezza, sopravvivenza o esiti clinici rilevanti (es. ospedalizzazione o ventilazione assistita). Possono candidarsi centri clinici partecipanti a trial di fase 2/3 o fase 3 promossi da una piccola impresa statunitense titolare dell'IND presso la FDA. Non sono ammesse organizzazioni né componenti non statunitensi.</t>
+          <t>Linee guida per i bandi di ricerca 2026-2027 della American Occupational Therapy Foundation (AOTF), articolati in tre tipologie di finanziamento: Implementation Research (IR), Intervention Research (IRG) e Community-Engaged Research (CERG). I programmi mirano a costruire una solida base di evidenze scientifiche per la terapia occupazionale, sostenendo lo sviluppo e la validazione di interventi manualizzati centrati sul paziente, la traslazione dei risultati nella pratica clinica e partenariati inclusivi con le comunità. I temi prioritari includono la gestione dei comportamenti di salute nelle malattie croniche, la salute mentale, il supporto ambientale e tecnologico, la resilienza dei caregiver e l'accesso equo ai servizi sanitari per popolazioni vulnerabili con disabilità fisiche o cognitive.</t>
         </is>
       </c>
       <c r="AE33" s="4" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="AF33" s="4" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="AG33" s="2" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>GG-RFA-AG-26-011</t>
+          <t>WEB-3e0abf79b1c9</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -5202,104 +5196,108 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Formazione / fellowship</t>
+          <t>Ricerca clinica</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Programma estivo di formazione alla ricerca NIA per espandere gli studi su Alzheimer e demenze (R25)</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="n">
-        <v>46533</v>
-      </c>
+          <t>Bando di ricerca Hand in Hand 2026-2027 per la riabilitazione della mano e dell'arto superiore</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="n"/>
       <c r="G34" s="5">
         <f>IF(F34="","",F34-TODAY())</f>
         <v/>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Aperto</t>
+          <t>Scadenza da verificare</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>National Institutes of Health</t>
+          <t>American Occupational Therapy Foundation</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>Grants.gov</t>
+          <t>American Occupational Therapy Foundation</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>National Institutes of Health – RFA-AG-26-011</t>
+          <t>HiHRG Award Guidelines 2026 2027</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>NIA Expanding Research in AD/ADRD (ERA) Summer Research Education Program (R25 Independent Clinical Trial Not Allowed)</t>
+          <t>HiHRG Award Guidelines 2026 2027</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>Invecchiamento</t>
+          <t>Ictus, Invecchiamento, Altre malattie e riabilitazione</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>dementi, alzheimer</t>
+          <t>stroke, dementi, cognitive impairment, rehabilitat, physical therap, occupational therap, spinal cord injur, traumatic brain injur, cerebral palsy, disabilit, chronic condition, obesit</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>Riguarda l'Alzheimer e le demenze correlate, ma è incentrato sulla formazione estiva alla ricerca per studenti.</t>
-        </is>
-      </c>
-      <c r="P34" s="6" t="n"/>
+          <t>Bando interamente incentrato sulla riabilitazione della mano e dell'arto superiore per lesioni tendinee, ictus, lesioni midollari e dolore cronico.</t>
+        </is>
+      </c>
+      <c r="P34" s="6" t="n">
+        <v>50000</v>
+      </c>
       <c r="Q34" s="6" t="n">
-        <v>200000</v>
+        <v>50000</v>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="S34" s="2" t="n"/>
+      <c r="S34" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t>Non stimabile – dati insufficienti</t>
+          <t>Bassa – 1 progetti finanziabili (stima: tasso storico non disponibile)</t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t>Interamente finanziato</t>
-        </is>
-      </c>
-      <c r="V34" s="4" t="n">
-        <v>45902</v>
-      </c>
-      <c r="W34" s="2" t="n"/>
+          <t>Non indicato</t>
+        </is>
+      </c>
+      <c r="V34" s="4" t="n"/>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>12 mesi</t>
+        </is>
+      </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>Dottorato / formazione / mobilità</t>
-        </is>
-      </c>
-      <c r="Y34" s="3" t="inlineStr">
-        <is>
-          <t>Special district governments; For profit organizations other than small businesses; State governments; Others (see text field entitled "Additional Information on Eligibility" for clarification); Native American tribal governments (Federally recognized); Native American tribal organizations (other than Federally recognized tribal governments); Small businesses; Public housing authorities/Indian hou</t>
-        </is>
-      </c>
-      <c r="Z34" s="3" t="n"/>
+          <t>Ricerca</t>
+        </is>
+      </c>
+      <c r="Y34" s="3" t="n"/>
+      <c r="Z34" s="3" t="inlineStr">
+        <is>
+          <t>Richiesta la collaborazione tra partner comunitari e ricercatori o istituzioni accademiche</t>
+        </is>
+      </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>Enti esteri non ammessi (call NIH completa)</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
@@ -5309,26 +5307,26 @@
       </c>
       <c r="AC34" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/359655</t>
+          <t>https://www.aotf.org/wp-content/uploads/2026/08/HiHRG_-Award-Guidelines-2026-2027.pdf</t>
         </is>
       </c>
       <c r="AD34" s="3" t="inlineStr">
         <is>
-          <t>Il National Institute on Aging (NIA) promuove lo sviluppo e l'attuazione di programmi estivi di educazione alla ricerca incentrati sulla malattia di Alzheimer e sulle demenze correlate (AD/ADRD). Il bando è rivolto a studenti delle scuole superiori, universitari o docenti di scienze, incoraggiando la partecipazione di gruppi sottorappresentati nelle scienze biomediche e comportamentali. L'obiettivo è ampliare il bacino di ricercatori qualificati fornendo esperienze intensive di ricerca estiva per favorire percorsi accademici avanzati nelle demenze. I partecipanti non possono condurre trial clinici indipendenti, ma possono maturare esperienza all'interno di sperimentazioni cliniche guidate da tutor. Le organizzazioni estere e i componenti stranieri sono esclusi.</t>
+          <t>Il bando Hand in Hand Research Grant 2026-2027 nasce dalla collaborazione tra AOTF, ASHT e AHTF per sostenere progetti pilota di ricerca clinica con forte coinvolgimento della comunità nella terapia della mano e dell'arto superiore. Il finanziamento è destinato a studi preliminari volti a gettare le basi per future sperimentazioni su larga scala, valutando interventi riabilitativi, disparità sanitarie, efficacia comparativa e validazione degli esiti terapeutici. Le aree di interesse clinico prioritario includono le lesioni dei tendini, l'epicondilite laterale, le sindromi dolorose complesse (CRPS), l'uso di ortesi e agenti biofisici, con particolare attenzione a popolazioni con lesioni traumatiche, ictus o lesioni del midollo spinale.</t>
         </is>
       </c>
       <c r="AE34" s="4" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="AF34" s="4" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="AG34" s="2" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>GG-RFA-AG-26-010</t>
+          <t>GG-RFA-NS-26-001</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -5343,16 +5341,16 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Formazione / fellowship</t>
+          <t>Ricerca clinica</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>Programma post-laurea NIA di formazione alla ricerca per ampliare gli studi su Alzheimer e demenze (R25)</t>
+          <t>Accesso allargato a popolazioni intermedie di pazienti con sclerosi laterale amiotrofica (U01)</t>
         </is>
       </c>
       <c r="F35" s="4" t="n">
-        <v>46533</v>
+        <v>46336</v>
       </c>
       <c r="G35" s="5">
         <f>IF(F35="","",F35-TODAY())</f>
@@ -5360,7 +5358,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Aperto</t>
+          <t>In scadenza (≤30 gg)</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -5375,42 +5373,44 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>National Institutes of Health – RFA-AG-26-010</t>
+          <t>National Institutes of Health – RFA-NS-26-001</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>NIA Expanding Research in AD/ADRD (ERA) Postbaccalaureate Research Education Program (R25 Independent Clinical Trial Not Allowed)</t>
+          <t>Amyotrophic Lateral Sclerosis (ALS) Intermediate Patient Population Expanded Access (U01 Clinical Trial Required)</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>Invecchiamento</t>
+          <t>Altre malattie e riabilitazione</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>dementi, alzheimer</t>
+          <t>amyotrophic lateral sclerosis</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>Riguarda l'Alzheimer e le demenze correlate, ma è dedicato alla formazione post-laurea triennale.</t>
-        </is>
-      </c>
-      <c r="P35" s="6" t="n"/>
-      <c r="Q35" s="6" t="n">
-        <v>400000</v>
-      </c>
+          <t>Riguarda la sclerosi laterale amiotrofica (SLA) nell'ambito di farmaci sperimentali in accesso allargato, non la riabilitazione.</t>
+        </is>
+      </c>
+      <c r="P35" s="6" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="Q35" s="6" t="n"/>
       <c r="R35" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="S35" s="2" t="n"/>
+      <c r="S35" s="2" t="n">
+        <v>4</v>
+      </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t>Non stimabile – dati insufficienti</t>
+          <t>Bassa – 4 progetti finanziabili (stima: tasso storico non disponibile)</t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
@@ -5419,23 +5419,27 @@
         </is>
       </c>
       <c r="V35" s="4" t="n">
-        <v>45902</v>
+        <v>46146</v>
       </c>
       <c r="W35" s="2" t="n"/>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>Dottorato / formazione / mobilità</t>
+          <t>Ricerca</t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t>County governments; Special district governments; Native American tribal governments (Federally recognized); Native American tribal organizations (other than Federally recognized tribal governments); City or township governments; Nonprofits that do not have a 501(c)(3) status with the IRS, other than institutions of higher education; For profit organizations other than small businesses; Independen</t>
-        </is>
-      </c>
-      <c r="Z35" s="3" t="n"/>
+          <t>City or township governments; For profit organizations other than small businesses; Others (see text field entitled "Additional Information on Eligibility" for clarification); County governments; Public housing authorities/Indian housing authorities; Nonprofits having a 501(c)(3) status with the IRS, other than institutions of higher education; Small businesses; Private institutions of higher educ</t>
+        </is>
+      </c>
+      <c r="Z35" s="3" t="inlineStr">
+        <is>
+          <t>Centri di sperimentazione clinica collegati a trial di fase 2/3 o 3 con sponsor di piccola impresa</t>
+        </is>
+      </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>Enti esteri non ammessi (call NIH completa)</t>
+          <t>Solo enti statunitensi</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
@@ -5445,16 +5449,16 @@
       </c>
       <c r="AC35" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/359653</t>
+          <t>https://www.grants.gov/search-results-detail/360400</t>
         </is>
       </c>
       <c r="AD35" s="3" t="inlineStr">
         <is>
-          <t>Il National Institute on Aging (NIA) finanzia programmi di formazione alla ricerca per neolaureati (baccalaureate) incentrati sulla malattia di Alzheimer e sulle demenze correlate (AD/ADRD). L'iniziativa mira ad ampliare la comunità di ricercatori qualificati, includendo individui provenienti da contesti sottorappresentati nelle scienze biomediche e comportamentali, e fornendo un'esperienza precoce di ricerca nel settore. I percorsi educativi proposti dovranno offrire esperienze intensive per preparare i partecipanti al passaggio verso corsi di laurea magistrale, dottorati focalizzati sulla ricerca o carriere scientifiche nel settore privato. Non è consentito condurre trial clinici indipendenti. Le entità e le componenti estere non sono ammesse al bando.</t>
+          <t>Bando promosso dal NINDS per condurre attività di ricerca clinica che utilizzano dati derivanti da programmi di accesso allargato (Expanded Access) a farmaci o prodotti biologici sperimentali per la sclerosi laterale amiotrofica (SLA). L'opportunità è indirizzata a popolazioni di pazienti di dimensioni intermedie che non risultano idonei all'arruolamento nei trial clinici convenzionali per il trattamento o la prevenzione della SLA. Possono partecipare unicamente centri clinici già coinvolti in trial registrativi di fase 2/3 o 3 sponsorizzati da piccole imprese in possesso di IND approvato dalla FDA. Il bando esclude categoricamente gli enti non statunitensi e le collaborazioni con componenti estere.</t>
         </is>
       </c>
       <c r="AE35" s="4" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="AF35" s="4" t="n">
         <v>46316</v>
@@ -5464,7 +5468,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>GG-PAR-24-321</t>
+          <t>GG-RFA-NS-28-009</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -5479,16 +5483,16 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Formazione / fellowship</t>
+          <t>Ricerca clinica</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Finanziamento NIA per la leadership accademica e lo sviluppo di carriera (K07)</t>
+          <t>Accesso allargato a popolazioni intermedie di pazienti con sclerosi laterale amiotrofica (SLA) (U01)</t>
         </is>
       </c>
       <c r="F36" s="4" t="n">
-        <v>46703</v>
+        <v>46532</v>
       </c>
       <c r="G36" s="5">
         <f>IF(F36="","",F36-TODAY())</f>
@@ -5511,27 +5515,27 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>National Institutes of Health – PAR-24-321</t>
+          <t>National Institutes of Health – RFA-NS-28-009</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>NIA Academic Leadership Career Award (K07 Independent Clinical Trial Not Allowed)</t>
+          <t>Amyotrophic Lateral Sclerosis (ALS) Intermediate Patient Population Expanded Access (U01 Clinical Trial Required)</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>Invecchiamento</t>
+          <t>Ictus, Altre malattie e riabilitazione</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>dementi, alzheimer, aging</t>
+          <t>stroke, amyotrophic lateral sclerosis, neurological disorder</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>Tratta l'invecchiamento e le demenze ma si focalizza sullo sviluppo accademico, la mentorship e le capacità istituzionali di ricerca, non sulla riabilitazione.</t>
+          <t>Riguarda la SLA ma è focalizzato su protocolli di accesso allargato a farmaci sperimentali e biomarcatori.</t>
         </is>
       </c>
       <c r="P36" s="6" t="n"/>
@@ -5553,23 +5557,23 @@
         </is>
       </c>
       <c r="V36" s="4" t="n">
-        <v>45602</v>
+        <v>46288</v>
       </c>
       <c r="W36" s="2" t="n"/>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>Dottorato / formazione / mobilità</t>
+          <t>Ricerca</t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t>State governments; Independent school districts; Others (see text field entitled "Additional Information on Eligibility" for clarification); Native American tribal governments (Federally recognized); Nonprofits having a 501(c)(3) status with the IRS, other than institutions of higher education; Nonprofits that do not have a 501(c)(3) status with the IRS, other than institutions of higher education</t>
+          <t>Special district governments; Public and State controlled institutions of higher education; City or township governments; Nonprofits having a 501(c)(3) status with the IRS, other than institutions of higher education; Others (see text field entitled "Additional Information on Eligibility" for clarification); Native American tribal organizations (other than Federally recognized tribal governments);</t>
         </is>
       </c>
       <c r="Z36" s="3" t="n"/>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>Enti esteri non ammessi (call NIH completa)</t>
+          <t>Solo enti statunitensi</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
@@ -5579,16 +5583,16 @@
       </c>
       <c r="AC36" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/357000</t>
+          <t>https://www.grants.gov/search-results-detail/363926</t>
         </is>
       </c>
       <c r="AD36" s="3" t="inlineStr">
         <is>
-          <t>Il National Institute on Aging mette a disposizione fondi attraverso il meccanismo K07 per supportare ricercatori affermati dotati di comprovata esperienza e capacità di leadership, al fine di rafforzare la capacità di ricerca sull'invecchiamento, sulla malattia di Alzheimer e sulle demenze correlate all'interno delle loro istituzioni accademiche. Il finanziamento supporta lo sviluppo di infrastrutture formative e di ricerca, attività di mentorship, nuovi corsi curriculari e programmi pilota. Non è consentito condurre trial clinici indipendenti con questo bando. La partecipazione è riservata a docenti e ricercatori di istituzioni universitarie ed enti di ricerca situati negli Stati Uniti; le organizzazioni non statunitensi sono escluse.</t>
+          <t>Il National Institute of Neurological Disorders and Stroke (NINDS) intende sostenere la ricerca scientifica basata sui dati derivanti da protocolli di accesso allargato di dimensioni intermedie per la sclerosi laterale amiotrofica (SLA). I protocolli ammissibili devono fornire accesso a farmaci o prodotti biologici sperimentali e generare dati a supporto della ricerca su prevenzione, diagnosi o trattamento della SLA, inclusi effetti su biomarcatori, sicurezza, sopravvivenza o esiti clinici rilevanti (es. ospedalizzazione o ventilazione assistita). Possono candidarsi centri clinici partecipanti a trial di fase 2/3 o fase 3 promossi da una piccola impresa statunitense titolare dell'IND presso la FDA. Non sono ammesse organizzazioni né componenti non statunitensi.</t>
         </is>
       </c>
       <c r="AE36" s="4" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="AF36" s="4" t="n">
         <v>46316</v>
@@ -5598,7 +5602,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>GG-PAR-25-024</t>
+          <t>GG-RFA-AG-26-011</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -5613,16 +5617,16 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Ricerca clinica</t>
+          <t>Formazione / fellowship</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Sviluppo di biomarcatori o combinazioni di biomarcatori per patologie neurologiche e neuromuscolari (R61/R33)</t>
+          <t>Programma estivo di formazione alla ricerca NIA per espandere gli studi su Alzheimer e demenze (R25)</t>
         </is>
       </c>
       <c r="F37" s="4" t="n">
-        <v>46759</v>
+        <v>46533</v>
       </c>
       <c r="G37" s="5">
         <f>IF(F37="","",F37-TODAY())</f>
@@ -5645,31 +5649,33 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>National Institutes of Health – PAR-25-024</t>
+          <t>National Institutes of Health – RFA-AG-26-011</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>Development of Biomarkers or Composite Biomarkers for Neurological and Neuromuscular Disorders (R61/R33 - Clinical Trial Optional)</t>
+          <t>NIA Expanding Research in AD/ADRD (ERA) Summer Research Education Program (R25 Independent Clinical Trial Not Allowed)</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>Altre malattie e riabilitazione</t>
+          <t>Invecchiamento</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>neuromuscular</t>
+          <t>dementi, alzheimer</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>Il bando finanzia la ricerca di biomarcatori per patologie neurologiche e neuromuscolari senza un focus diretto su interventi di riabilitazione.</t>
+          <t>Riguarda l'Alzheimer e le demenze correlate, ma è incentrato sulla formazione estiva alla ricerca per studenti.</t>
         </is>
       </c>
       <c r="P37" s="6" t="n"/>
-      <c r="Q37" s="6" t="n"/>
+      <c r="Q37" s="6" t="n">
+        <v>200000</v>
+      </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5687,17 +5693,17 @@
         </is>
       </c>
       <c r="V37" s="4" t="n">
-        <v>45593</v>
+        <v>45902</v>
       </c>
       <c r="W37" s="2" t="n"/>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>Ricerca</t>
+          <t>Dottorato / formazione / mobilità</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Native American tribal governments (Federally recognized); Public housing authorities/Indian housing authorities; Private institutions of higher education; Small businesses; City or township governments; Special district governments; Independent school districts; County governments; Native American tribal organizations (other than Federally recognized tribal governments); For profit organizations </t>
+          <t xml:space="preserve">Private institutions of higher education; County governments; City or township governments; State governments; Nonprofits having a 501(c)(3) status with the IRS, other than institutions of higher education; Special district governments; Native American tribal organizations (other than Federally recognized tribal governments); Nonprofits that do not have a 501(c)(3) status with the IRS, other than </t>
         </is>
       </c>
       <c r="Z37" s="3" t="n"/>
@@ -5713,16 +5719,16 @@
       </c>
       <c r="AC37" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/356874</t>
+          <t>https://www.grants.gov/search-results-detail/359655</t>
         </is>
       </c>
       <c r="AD37" s="3" t="inlineStr">
         <is>
-          <t>Questa opportunità promossa dal NIH supporta la scoperta e la valutazione preliminare di solidi biomarcatori o firme di biomarcatori mirati a facilitare lo sviluppo clinico di terapie neurologiche e il loro impiego nella pratica clinica. La call si focalizza sulla caratterizzazione biologica, analitica e clinica iniziale di marcatori per patologie neurologiche e neuromuscolari. I progetti possono includere modelli animali, ma devono obbligatoriamente prevedere una prima validazione su campioni o dataset clinici umani standardizzati. Possono concorrere università, ospedali, centri di ricerca e imprese commerciali con sede negli Stati Uniti. I soggetti esteri sono esclusi dalla candidatura come enti proponenti.</t>
+          <t>Il National Institute on Aging (NIA) promuove lo sviluppo e l'attuazione di programmi estivi di educazione alla ricerca incentrati sulla malattia di Alzheimer e sulle demenze correlate (AD/ADRD). Il bando è rivolto a studenti delle scuole superiori, universitari o docenti di scienze, incoraggiando la partecipazione di gruppi sottorappresentati nelle scienze biomediche e comportamentali. L'obiettivo è ampliare il bacino di ricercatori qualificati fornendo esperienze intensive di ricerca estiva per favorire percorsi accademici avanzati nelle demenze. I partecipanti non possono condurre trial clinici indipendenti, ma possono maturare esperienza all'interno di sperimentazioni cliniche guidate da tutor. Le organizzazioni estere e i componenti stranieri sono esclusi.</t>
         </is>
       </c>
       <c r="AE37" s="4" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="AF37" s="4" t="n">
         <v>46316</v>
@@ -5732,7 +5738,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>GG-PAR-27-096</t>
+          <t>GG-RFA-AG-26-010</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -5747,16 +5753,16 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Ricerca clinica</t>
+          <t>Formazione / fellowship</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Finanziamenti per la transizione alla ricerca sull'invecchiamento per specialisti medici e chirurgici a inizio carriera (GEMSSTAR R03)</t>
+          <t>Programma post-laurea NIA di formazione alla ricerca per ampliare gli studi su Alzheimer e demenze (R25)</t>
         </is>
       </c>
       <c r="F38" s="4" t="n">
-        <v>46950</v>
+        <v>46533</v>
       </c>
       <c r="G38" s="5">
         <f>IF(F38="","",F38-TODAY())</f>
@@ -5779,12 +5785,12 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>National Institutes of Health – PAR-27-096</t>
+          <t>National Institutes of Health – RFA-AG-26-010</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>Grants for Early Medical/Surgical Specialists' Transition to Aging Research (GEMSSTAR) (R03 Clinical Trial Optional)</t>
+          <t>NIA Expanding Research in AD/ADRD (ERA) Postbaccalaureate Research Education Program (R25 Independent Clinical Trial Not Allowed)</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
@@ -5794,17 +5800,17 @@
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>geriatr, aging</t>
+          <t>dementi, alzheimer</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>Bando generale sulla ricerca geriatrica e sull'invecchiamento rivolto a medici specialisti, che può includere la riabilitazione ma non vi è specificamente dedicato.</t>
+          <t>Riguarda l'Alzheimer e le demenze correlate, ma è dedicato alla formazione post-laurea triennale.</t>
         </is>
       </c>
       <c r="P38" s="6" t="n"/>
       <c r="Q38" s="6" t="n">
-        <v>125000</v>
+        <v>400000</v>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
@@ -5823,23 +5829,23 @@
         </is>
       </c>
       <c r="V38" s="4" t="n">
-        <v>46266</v>
+        <v>45902</v>
       </c>
       <c r="W38" s="2" t="n"/>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>Ricerca</t>
+          <t>Dottorato / formazione / mobilità</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t>Native American tribal organizations (other than Federally recognized tribal governments); County governments; For profit organizations other than small businesses; State governments; Special district governments; Others (see text field entitled "Additional Information on Eligibility" for clarification); Private institutions of higher education; Native American tribal governments (Federally recogn</t>
+          <t>City or township governments; For profit organizations other than small businesses; Independent school districts; Native American tribal organizations (other than Federally recognized tribal governments); County governments; Native American tribal governments (Federally recognized); Nonprofits having a 501(c)(3) status with the IRS, other than institutions of higher education; State governments; P</t>
         </is>
       </c>
       <c r="Z38" s="3" t="n"/>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>Solo enti statunitensi</t>
+          <t>Enti esteri non ammessi (call NIH completa)</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
@@ -5849,25 +5855,429 @@
       </c>
       <c r="AC38" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/359940</t>
+          <t>https://www.grants.gov/search-results-detail/359653</t>
         </is>
       </c>
       <c r="AD38" s="3" t="inlineStr">
         <is>
-          <t>Il programma GEMSSTAR del National Institute on Aging intende supportare medici-ricercatori a inizio carriera operanti in discipline mediche o chirurgiche per avviarli a ruoli di leadership nella ricerca sull'invecchiamento e geriatrica. Il bando finanzia progetti pilota transdisciplinari volti a generare dati preliminari per successive linee di ricerca, integrati con un piano formale di sviluppo professionale e mentorship. I candidati devono operare in un contesto clinico-accademico favorevole alla ricerca geriatrica. Possono presentare domanda esclusivamente istituzioni con sede negli Stati Uniti; le organizzazioni straniere e i sub-appalti finanziari verso istituzioni estere non sono ammessi.</t>
+          <t>Il National Institute on Aging (NIA) finanzia programmi di formazione alla ricerca per neolaureati (baccalaureate) incentrati sulla malattia di Alzheimer e sulle demenze correlate (AD/ADRD). L'iniziativa mira ad ampliare la comunità di ricercatori qualificati, includendo individui provenienti da contesti sottorappresentati nelle scienze biomediche e comportamentali, e fornendo un'esperienza precoce di ricerca nel settore. I percorsi educativi proposti dovranno offrire esperienze intensive per preparare i partecipanti al passaggio verso corsi di laurea magistrale, dottorati focalizzati sulla ricerca o carriere scientifiche nel settore privato. Non è consentito condurre trial clinici indipendenti. Le entità e le componenti estere non sono ammesse al bando.</t>
         </is>
       </c>
       <c r="AE38" s="4" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="AF38" s="4" t="n">
         <v>46316</v>
       </c>
       <c r="AG38" s="2" t="n"/>
     </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>GG-PAR-24-321</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Formazione / fellowship</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Finanziamento NIA per la leadership accademica e lo sviluppo di carriera (K07)</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>46703</v>
+      </c>
+      <c r="G39" s="5">
+        <f>IF(F39="","",F39-TODAY())</f>
+        <v/>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>Aperto</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>National Institutes of Health</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>Grants.gov</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>National Institutes of Health – PAR-24-321</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>NIA Academic Leadership Career Award (K07 Independent Clinical Trial Not Allowed)</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>Invecchiamento</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>dementi, alzheimer, aging</t>
+        </is>
+      </c>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t>Tratta l'invecchiamento e le demenze ma si focalizza sullo sviluppo accademico, la mentorship e le capacità istituzionali di ricerca, non sulla riabilitazione.</t>
+        </is>
+      </c>
+      <c r="P39" s="6" t="n"/>
+      <c r="Q39" s="6" t="n"/>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="S39" s="2" t="n"/>
+      <c r="T39" s="3" t="inlineStr">
+        <is>
+          <t>Non stimabile – dati insufficienti</t>
+        </is>
+      </c>
+      <c r="U39" s="3" t="inlineStr">
+        <is>
+          <t>Interamente finanziato</t>
+        </is>
+      </c>
+      <c r="V39" s="4" t="n">
+        <v>45602</v>
+      </c>
+      <c r="W39" s="2" t="n"/>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>Dottorato / formazione / mobilità</t>
+        </is>
+      </c>
+      <c r="Y39" s="3" t="inlineStr">
+        <is>
+          <t>Special district governments; Independent school districts; Others (see text field entitled "Additional Information on Eligibility" for clarification); Native American tribal organizations (other than Federally recognized tribal governments); Private institutions of higher education; Public housing authorities/Indian housing authorities; Nonprofits that do not have a 501(c)(3) status with the IRS,</t>
+        </is>
+      </c>
+      <c r="Z39" s="3" t="n"/>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>Enti esteri non ammessi (call NIH completa)</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>Inglese</t>
+        </is>
+      </c>
+      <c r="AC39" s="7" t="inlineStr">
+        <is>
+          <t>https://www.grants.gov/search-results-detail/357000</t>
+        </is>
+      </c>
+      <c r="AD39" s="3" t="inlineStr">
+        <is>
+          <t>Il National Institute on Aging mette a disposizione fondi attraverso il meccanismo K07 per supportare ricercatori affermati dotati di comprovata esperienza e capacità di leadership, al fine di rafforzare la capacità di ricerca sull'invecchiamento, sulla malattia di Alzheimer e sulle demenze correlate all'interno delle loro istituzioni accademiche. Il finanziamento supporta lo sviluppo di infrastrutture formative e di ricerca, attività di mentorship, nuovi corsi curriculari e programmi pilota. Non è consentito condurre trial clinici indipendenti con questo bando. La partecipazione è riservata a docenti e ricercatori di istituzioni universitarie ed enti di ricerca situati negli Stati Uniti; le organizzazioni non statunitensi sono escluse.</t>
+        </is>
+      </c>
+      <c r="AE39" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="AF39" s="4" t="n">
+        <v>46316</v>
+      </c>
+      <c r="AG39" s="2" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>GG-PAR-25-024</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Ricerca clinica</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Sviluppo di biomarcatori o combinazioni di biomarcatori per patologie neurologiche e neuromuscolari (R61/R33)</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="n">
+        <v>46759</v>
+      </c>
+      <c r="G40" s="5">
+        <f>IF(F40="","",F40-TODAY())</f>
+        <v/>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>Aperto</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>National Institutes of Health</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>Grants.gov</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>National Institutes of Health – PAR-25-024</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>Development of Biomarkers or Composite Biomarkers for Neurological and Neuromuscular Disorders (R61/R33 - Clinical Trial Optional)</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>Altre malattie e riabilitazione</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>neuromuscular</t>
+        </is>
+      </c>
+      <c r="O40" s="3" t="inlineStr">
+        <is>
+          <t>Il bando finanzia la ricerca di biomarcatori per patologie neurologiche e neuromuscolari senza un focus diretto su interventi di riabilitazione.</t>
+        </is>
+      </c>
+      <c r="P40" s="6" t="n"/>
+      <c r="Q40" s="6" t="n"/>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="n"/>
+      <c r="T40" s="3" t="inlineStr">
+        <is>
+          <t>Non stimabile – dati insufficienti</t>
+        </is>
+      </c>
+      <c r="U40" s="3" t="inlineStr">
+        <is>
+          <t>Interamente finanziato</t>
+        </is>
+      </c>
+      <c r="V40" s="4" t="n">
+        <v>45593</v>
+      </c>
+      <c r="W40" s="2" t="n"/>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>Ricerca</t>
+        </is>
+      </c>
+      <c r="Y40" s="3" t="inlineStr">
+        <is>
+          <t>City or township governments; For profit organizations other than small businesses; Private institutions of higher education; Special district governments; Public and State controlled institutions of higher education; Native American tribal governments (Federally recognized); State governments; Nonprofits that do not have a 501(c)(3) status with the IRS, other than institutions of higher education</t>
+        </is>
+      </c>
+      <c r="Z40" s="3" t="n"/>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>Enti esteri non ammessi (call NIH completa)</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>Inglese</t>
+        </is>
+      </c>
+      <c r="AC40" s="7" t="inlineStr">
+        <is>
+          <t>https://www.grants.gov/search-results-detail/356874</t>
+        </is>
+      </c>
+      <c r="AD40" s="3" t="inlineStr">
+        <is>
+          <t>Questa opportunità promossa dal NIH supporta la scoperta e la valutazione preliminare di solidi biomarcatori o firme di biomarcatori mirati a facilitare lo sviluppo clinico di terapie neurologiche e il loro impiego nella pratica clinica. La call si focalizza sulla caratterizzazione biologica, analitica e clinica iniziale di marcatori per patologie neurologiche e neuromuscolari. I progetti possono includere modelli animali, ma devono obbligatoriamente prevedere una prima validazione su campioni o dataset clinici umani standardizzati. Possono concorrere università, ospedali, centri di ricerca e imprese commerciali con sede negli Stati Uniti. I soggetti esteri sono esclusi dalla candidatura come enti proponenti.</t>
+        </is>
+      </c>
+      <c r="AE40" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="AF40" s="4" t="n">
+        <v>46316</v>
+      </c>
+      <c r="AG40" s="2" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>GG-PAR-27-096</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Ricerca clinica</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>Finanziamenti per la transizione alla ricerca sull'invecchiamento per specialisti medici e chirurgici a inizio carriera (GEMSSTAR R03)</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="n">
+        <v>46950</v>
+      </c>
+      <c r="G41" s="5">
+        <f>IF(F41="","",F41-TODAY())</f>
+        <v/>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>Aperto</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>National Institutes of Health</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>Grants.gov</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>National Institutes of Health – PAR-27-096</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>Grants for Early Medical/Surgical Specialists' Transition to Aging Research (GEMSSTAR) (R03 Clinical Trial Optional)</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>Invecchiamento</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>geriatr, aging</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="inlineStr">
+        <is>
+          <t>Bando generale sulla ricerca geriatrica e sull'invecchiamento rivolto a medici specialisti, che può includere la riabilitazione ma non vi è specificamente dedicato.</t>
+        </is>
+      </c>
+      <c r="P41" s="6" t="n"/>
+      <c r="Q41" s="6" t="n">
+        <v>125000</v>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="n"/>
+      <c r="T41" s="3" t="inlineStr">
+        <is>
+          <t>Non stimabile – dati insufficienti</t>
+        </is>
+      </c>
+      <c r="U41" s="3" t="inlineStr">
+        <is>
+          <t>Interamente finanziato</t>
+        </is>
+      </c>
+      <c r="V41" s="4" t="n">
+        <v>46266</v>
+      </c>
+      <c r="W41" s="2" t="n"/>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>Ricerca</t>
+        </is>
+      </c>
+      <c r="Y41" s="3" t="inlineStr">
+        <is>
+          <t>Nonprofits having a 501(c)(3) status with the IRS, other than institutions of higher education; Special district governments; Native American tribal organizations (other than Federally recognized tribal governments); State governments; County governments; Small businesses; Public housing authorities/Indian housing authorities; Independent school districts; Private institutions of higher education;</t>
+        </is>
+      </c>
+      <c r="Z41" s="3" t="n"/>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>Solo enti statunitensi</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>Inglese</t>
+        </is>
+      </c>
+      <c r="AC41" s="7" t="inlineStr">
+        <is>
+          <t>https://www.grants.gov/search-results-detail/359940</t>
+        </is>
+      </c>
+      <c r="AD41" s="3" t="inlineStr">
+        <is>
+          <t>Il programma GEMSSTAR del National Institute on Aging intende supportare medici-ricercatori a inizio carriera operanti in discipline mediche o chirurgiche per avviarli a ruoli di leadership nella ricerca sull'invecchiamento e geriatrica. Il bando finanzia progetti pilota transdisciplinari volti a generare dati preliminari per successive linee di ricerca, integrati con un piano formale di sviluppo professionale e mentorship. I candidati devono operare in un contesto clinico-accademico favorevole alla ricerca geriatrica. Possono presentare domanda esclusivamente istituzioni con sede negli Stati Uniti; le organizzazioni straniere e i sub-appalti finanziari verso istituzioni estere non sono ammessi.</t>
+        </is>
+      </c>
+      <c r="AE41" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="AF41" s="4" t="n">
+        <v>46316</v>
+      </c>
+      <c r="AG41" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AG38"/>
-  <conditionalFormatting sqref="G2:G38">
+  <autoFilter ref="A1:AG41"/>
+  <conditionalFormatting sqref="G2:G41">
     <cfRule type="cellIs" priority="1" operator="between" dxfId="0">
       <formula>0</formula>
       <formula>30</formula>
@@ -5911,6 +6321,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC36" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC37" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC41" r:id="rId40"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -5923,7 +6336,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -6012,11 +6425,11 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>21/10/2026 12:13</t>
+          <t>22/10/2026 22:18</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>142</v>
+        <v>177</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>0</v>
@@ -6030,7 +6443,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Alzheimer's Association</t>
+          <t>ALS Association</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -6050,30 +6463,30 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>https://www.alz.org/research</t>
+          <t>https://www.als.org/research/for-researchers</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>21/10/2026 12:23</t>
+          <t>22/10/2026 22:44</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>122</v>
+        <v>26</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Ultima esecuzione: 13 elementi esaminati, 0 pertinenti</t>
+          <t>Ultima esecuzione: 26 elementi esaminati, 1 pertinenti</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Alzheimer's Research UK</t>
+          <t>AMED – Japan Agency for Medical Research and Development</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -6083,40 +6496,36 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Regno Unito</t>
+          <t>Giappone</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Charity</t>
+          <t>Pubblico estero</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>https://www.alzheimersresearchuk.org/</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>21/10/2026 12:22</t>
-        </is>
-      </c>
+          <t>https://www.amed.go.jp/en/koubo/</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="n">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Ultima esecuzione: 22 elementi esaminati, 0 pertinenti</t>
+          <t>Ultimo errore 22/10/2026: HTTP 404</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Alzheimer's Society</t>
+          <t>ANID Chile</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -6126,40 +6535,36 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Regno Unito</t>
+          <t>Cile</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Charity</t>
+          <t>Pubblico estero</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>https://www.alzheimers.org.uk/research</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>21/10/2026 12:21</t>
-        </is>
-      </c>
+          <t>https://anid.cl/concursos/</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Ultima esecuzione: 2 elementi esaminati, 0 pertinenti</t>
+          <t>Ultimo errore 22/10/2026: HTTP 403</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>American Federation for Aging Research (AFAR)</t>
+          <t>ANR – Agence Nationale de la Recherche</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -6169,40 +6574,40 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Francia</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Fondazione privata</t>
+          <t>Pubblico estero</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>https://www.afar.org/</t>
+          <t>https://anr.fr/en/open-calls-and-preannouncements/</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>21/10/2026 12:24</t>
+          <t>22/10/2026 22:35</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Ultima esecuzione: 29 elementi esaminati, 0 pertinenti</t>
+          <t>Ultima esecuzione: 35 elementi esaminati, 0 pertinenti</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>American Heart Association – Research</t>
+          <t>Alzheimer's Association</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -6212,7 +6617,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Mondiale</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -6222,26 +6627,30 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>https://professional.heart.org/</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="n"/>
+          <t>https://www.alz.org/research</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>22/10/2026 22:30</t>
+        </is>
+      </c>
       <c r="G7" s="2" t="n">
-        <v>3</v>
+        <v>150</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Ultimo errore 21/10/2026: HTTP 403</t>
+          <t>Ultima esecuzione: 28 elementi esaminati, 0 pertinenti</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Brain Canada</t>
+          <t>Alzheimer's Drug Discovery Foundation</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -6251,7 +6660,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Mondiale</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -6261,30 +6670,30 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>https://braincanada.ca/</t>
+          <t>https://www.alzdiscovery.org/research-and-grants/funding-opportunities</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>21/10/2026 12:24</t>
+          <t>22/10/2026 22:43</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Ultima esecuzione: 20 elementi esaminati, 1 pertinenti</t>
+          <t>Ultima esecuzione: 29 elementi esaminati, 0 pertinenti</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Canadian Institutes of Health Research</t>
+          <t>Alzheimer's Research UK</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -6294,40 +6703,40 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Regno Unito</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Pubblico estero</t>
+          <t>Charity</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>https://cihr-irsc.gc.ca/</t>
+          <t>https://www.alzheimersresearchuk.org/</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21/10/2026 12:24</t>
+          <t>22/10/2026 22:28</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>3</v>
+        <v>67</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Ultima esecuzione: 1 elementi esaminati, 0 pertinenti</t>
+          <t>Ultima esecuzione: 22 elementi esaminati, 0 pertinenti</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Compagnia di San Paolo</t>
+          <t>Alzheimer's Society</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -6337,29 +6746,29 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Italia (Piemonte, Liguria)</t>
+          <t>Regno Unito</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Fondazione bancaria</t>
+          <t>Charity</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>https://www.compagniadisanpaolo.it/</t>
+          <t>https://www.alzheimers.org.uk/research</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21/10/2026 12:05</t>
+          <t>22/10/2026 22:27</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>210</v>
+        <v>57</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
@@ -6370,7 +6779,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Dunhill Medical Trust</t>
+          <t>American Federation for Aging Research (AFAR)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -6380,7 +6789,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Regno Unito</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -6390,19 +6799,19 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>https://dunhillmedical.org.uk/</t>
+          <t>https://www.afar.org/</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>21/10/2026 12:22</t>
+          <t>22/10/2026 22:31</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
@@ -6413,7 +6822,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>EIT Health</t>
+          <t>American Heart Association – Research</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -6423,40 +6832,36 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Europa</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Pubblico europeo</t>
+          <t>Charity</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>https://eithealth.eu/</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>21/10/2026 12:13</t>
-        </is>
-      </c>
+          <t>https://professional.heart.org/</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="n"/>
       <c r="G12" s="2" t="n">
-        <v>210</v>
+        <v>4</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Ultima esecuzione: 35 elementi esaminati, 0 pertinenti</t>
+          <t>Ultimo errore 22/10/2026: HTTP 403</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>ERA4Health</t>
+          <t>American Occupational Therapy Foundation</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -6466,83 +6871,79 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Europa</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Pubblico europeo</t>
+          <t>Fondazione privata</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>https://era4health.eu/</t>
+          <t>https://www.aotf.org/</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21/10/2026 12:19</t>
+          <t>22/10/2026 22:45</t>
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>210</v>
+        <v>28</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Ultima esecuzione: 35 elementi esaminati, 0 pertinenti</t>
+          <t>Ultima esecuzione: 28 elementi esaminati, 2 pertinenti</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>EU Funding &amp; Tenders Portal</t>
+          <t>BMBF – Gesundheitsforschung (bandi)</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>API</t>
+          <t>Lettura pagine web</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>UE e paesi associati</t>
+          <t>Germania</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Pubblico</t>
+          <t>Pubblico estero</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>21/10/2026 11:55</t>
-        </is>
-      </c>
+          <t>https://www.gesundheitsforschung-bmbf.de/de/bekanntmachungen.php</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="n"/>
       <c r="G14" s="2" t="n">
-        <v>7187</v>
+        <v>1</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Ultima esecuzione: 1203 elementi esaminati, 8 pertinenti</t>
+          <t>Ultimo errore 22/10/2026: HTTP 404</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Fondazione CR Firenze</t>
+          <t>Brain Canada</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -6552,40 +6953,40 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Italia (Toscana)</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Fondazione bancaria</t>
+          <t>Fondazione privata</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>https://www.fondazionecrfirenze.it/</t>
+          <t>https://braincanada.ca/</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>21/10/2026 12:08</t>
+          <t>22/10/2026 22:32</t>
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>207</v>
+        <v>80</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Ultima esecuzione: 33 elementi esaminati, 0 pertinenti</t>
+          <t>Ultima esecuzione: 20 elementi esaminati, 1 pertinenti</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Fondazione CRT</t>
+          <t>CNPq</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -6595,40 +6996,40 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Italia (Piemonte, Valle d'Aosta)</t>
+          <t>Brasile</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Fondazione bancaria</t>
+          <t>Pubblico estero</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>https://www.fondazionecrt.it/</t>
+          <t>https://www.gov.br/cnpq/pt-br</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21/10/2026 12:07</t>
+          <t>22/10/2026 22:49</t>
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>210</v>
+        <v>35</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Ultima esecuzione: 35 elementi esaminati, 1 pertinenti</t>
+          <t>Ultima esecuzione: 35 elementi esaminati, 0 pertinenti</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Fondazione Cariparo</t>
+          <t>CONICET</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -6638,29 +7039,29 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Italia (Veneto)</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Fondazione bancaria</t>
+          <t>Pubblico estero</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>https://www.fondazionecariparo.it/</t>
+          <t>https://convocatorias.conicet.gov.ar/</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21/10/2026 12:11</t>
+          <t>22/10/2026 22:50</t>
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>210</v>
+        <v>35</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
@@ -6671,7 +7072,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Fondazione Cariplo</t>
+          <t>Canadian Institutes of Health Research</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -6681,40 +7082,40 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Italia (Lombardia)</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Fondazione bancaria</t>
+          <t>Pubblico estero</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>https://www.fondazionecariplo.it/</t>
+          <t>https://cihr-irsc.gc.ca/</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>21/10/2026 12:03</t>
+          <t>22/10/2026 22:31</t>
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>210</v>
+        <v>4</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Ultima esecuzione: 35 elementi esaminati, 0 pertinenti</t>
+          <t>Ultima esecuzione: 1 elementi esaminati, 0 pertinenti</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Fondazione Cariverona</t>
+          <t>Chan Zuckerberg Initiative</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -6724,40 +7125,36 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Italia (Veneto, Lombardia)</t>
+          <t>Mondiale</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Fondazione bancaria</t>
+          <t>Fondazione privata</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>https://www.fondazionecariverona.org/</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>21/10/2026 12:11</t>
-        </is>
-      </c>
+          <t>https://chanzuckerberg.com/rfa/</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="n"/>
       <c r="G19" s="2" t="n">
-        <v>210</v>
+        <v>1</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Ultima esecuzione: 35 elementi esaminati, 0 pertinenti</t>
+          <t>Ultimo errore 22/10/2026: HTTP 404</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Fondazione Umberto Veronesi</t>
+          <t>Compagnia di San Paolo</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -6767,29 +7164,29 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Italia</t>
+          <t>Italia (Piemonte, Liguria)</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Fondazione privata</t>
+          <t>Fondazione bancaria</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>https://www.fondazioneveronesi.it/</t>
+          <t>https://www.compagniadisanpaolo.it/</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>21/10/2026 12:12</t>
+          <t>22/10/2026 22:11</t>
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>210</v>
+        <v>245</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
@@ -6800,7 +7197,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Foundation for Physical Therapy Research</t>
+          <t>Craig H. Neilsen Foundation</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -6810,7 +7207,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>USA e Canada</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -6820,73 +7217,65 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>https://foundation4pt.org/</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>21/10/2026 12:24</t>
-        </is>
-      </c>
+          <t>https://chnfoundation.org/grants/</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="n"/>
       <c r="G21" s="2" t="n">
-        <v>81</v>
+        <v>1</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>Ultima esecuzione: 19 elementi esaminati, 1 pertinenti</t>
+          <t>Ultimo errore 22/10/2026: HTTP 404</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Grants.gov (USA, incluso NIH)</t>
+          <t>Cure Parkinson's</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>API</t>
+          <t>Lettura pagine web</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>USA (alcuni aperti a enti esteri)</t>
+          <t>Mondiale</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Pubblico</t>
+          <t>Charity</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>https://www.grants.gov</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>21/10/2026 12:00</t>
-        </is>
-      </c>
+          <t>https://cureparkinsons.org.uk/research/</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="n"/>
       <c r="G22" s="2" t="n">
-        <v>5090</v>
+        <v>1</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Ultima esecuzione: 854 elementi esaminati, 58 pertinenti</t>
+          <t>Ultimo errore 22/10/2026: HTTP 403</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>INAIL – Ricerca</t>
+          <t>DFG – Deutsche Forschungsgemeinschaft</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -6896,26 +7285,26 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Italia</t>
+          <t>Germania</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Pubblico nazionale</t>
+          <t>Pubblico estero</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>https://www.inail.it/</t>
+          <t>https://www.dfg.de/en/research-funding/funding-opportunities</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>21/10/2026 12:01</t>
+          <t>22/10/2026 22:35</t>
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>210</v>
+        <v>35</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>0</v>
@@ -6929,7 +7318,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>JPND – EU Joint Programme Neurodegenerative Disease</t>
+          <t>Dunhill Medical Trust</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -6939,40 +7328,40 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Europa</t>
+          <t>Regno Unito</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Pubblico europeo</t>
+          <t>Fondazione privata</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>https://neurodegenerationresearch.eu/</t>
+          <t>https://dunhillmedical.org.uk/</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>21/10/2026 12:13</t>
+          <t>22/10/2026 22:29</t>
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>54</v>
+        <v>140</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Ultima esecuzione: 9 elementi esaminati, 0 pertinenti</t>
+          <t>Ultima esecuzione: 35 elementi esaminati, 0 pertinenti</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Lazio Innova – Bandi</t>
+          <t>EIT Health</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -6982,26 +7371,26 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Europa</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Pubblico regionale</t>
+          <t>Pubblico europeo</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>https://www.lazioinnova.it/</t>
+          <t>https://eithealth.eu/</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>21/10/2026 12:03</t>
+          <t>22/10/2026 22:19</t>
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>210</v>
+        <v>245</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>0</v>
@@ -7015,7 +7404,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Michael J. Fox Foundation</t>
+          <t>ERA4Health</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -7025,83 +7414,83 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Mondiale</t>
+          <t>Europa</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Fondazione privata</t>
+          <t>Pubblico europeo</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://www.michaeljfox.org/</t>
+          <t>https://era4health.eu/</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>21/10/2026 12:23</t>
+          <t>22/10/2026 22:25</t>
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>190</v>
+        <v>245</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Ultima esecuzione: 30 elementi esaminati, 2 pertinenti</t>
+          <t>Ultima esecuzione: 35 elementi esaminati, 0 pertinenti</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Ministero dell'Università e della Ricerca</t>
+          <t>EU Funding &amp; Tenders Portal</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Lettura pagine web</t>
+          <t>API</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Italia</t>
+          <t>UE e paesi associati</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Pubblico nazionale</t>
+          <t>Pubblico</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>https://www.mur.gov.it/</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>21/10/2026 12:01</t>
+          <t>22/10/2026 22:02</t>
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>210</v>
+        <v>8395</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Ultima esecuzione: 35 elementi esaminati, 0 pertinenti</t>
+          <t>Ultima esecuzione: 1208 elementi esaminati, 10 pertinenti</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Ministero della Salute – Ricerca sanitaria</t>
+          <t>FAPESP</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -7111,40 +7500,40 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Italia</t>
+          <t>Brasile</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Pubblico nazionale</t>
+          <t>Pubblico estero</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>https://www.salute.gov.it/</t>
+          <t>https://fapesp.br/en/calls</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>21/10/2026 12:00</t>
+          <t>22/10/2026 22:48</t>
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="H28" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Ultima esecuzione: 1 elementi esaminati, 0 pertinenti</t>
+          <t>Ultima esecuzione: 35 elementi esaminati, 0 pertinenti</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>NHMRC</t>
+          <t>FCT – Fundação para a Ciência e a Tecnologia</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -7154,7 +7543,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Portogallo</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -7164,26 +7553,30 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>https://www.nhmrc.gov.au/funding</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="n"/>
+          <t>https://www.fct.pt/en/funding/</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>22/10/2026 22:40</t>
+        </is>
+      </c>
       <c r="G29" s="2" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>Ultimo errore 21/10/2026: irraggiungibile: HTTPSConnectionPool(host='www.nhmrc.gov.au', port=443): Read timed out. (read timeout=45)</t>
+          <t>Ultima esecuzione: 35 elementi esaminati, 0 pertinenti</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>NIHR</t>
+          <t>FWF – Austrian Science Fund</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -7193,7 +7586,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Regno Unito</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -7203,26 +7596,30 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>https://www.nihr.ac.uk/</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="n"/>
+          <t>https://www.fwf.ac.at/en/funding</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>22/10/2026 22:37</t>
+        </is>
+      </c>
       <c r="G30" s="2" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Ultimo errore 21/10/2026: HTTP 403</t>
+          <t>Ultima esecuzione: 35 elementi esaminati, 0 pertinenti</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>PCORI</t>
+          <t>FWO – Research Foundation Flanders</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -7232,40 +7629,36 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Belgio</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Fondazione privata</t>
+          <t>Pubblico estero</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>https://www.pcori.org/funding-opportunities</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>21/10/2026 12:24</t>
-        </is>
-      </c>
+          <t>https://www.fwo.be/en/fellowships-funding/</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="n"/>
       <c r="G31" s="2" t="n">
-        <v>176</v>
+        <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Ultima esecuzione: 1 elementi esaminati, 0 pertinenti</t>
+          <t>Ultimo errore 22/10/2026: irraggiungibile: HTTPSConnectionPool(host='www.fwo.be', port=443): Max retries exceeded with url: /en/fellowships-funding/ (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_s</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Parkinson's Foundation</t>
+          <t>Fondazione CR Firenze</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -7275,40 +7668,40 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Mondiale</t>
+          <t>Italia (Toscana)</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Fondazione privata</t>
+          <t>Fondazione bancaria</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://www.parkinson.org/research</t>
+          <t>https://www.fondazionecrfirenze.it/</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>21/10/2026 12:23</t>
+          <t>22/10/2026 22:13</t>
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>86</v>
+        <v>239</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Ultima esecuzione: 12 elementi esaminati, 1 pertinenti</t>
+          <t>Ultima esecuzione: 32 elementi esaminati, 0 pertinenti</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Parkinson's UK</t>
+          <t>Fondazione CRT</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -7318,40 +7711,40 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Regno Unito</t>
+          <t>Italia (Piemonte, Valle d'Aosta)</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Charity</t>
+          <t>Fondazione bancaria</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://www.parkinsons.org.uk/research</t>
+          <t>https://www.fondazionecrt.it/</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>21/10/2026 12:21</t>
+          <t>22/10/2026 22:12</t>
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>40</v>
+        <v>245</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>Ultima esecuzione: 12 elementi esaminati, 1 pertinenti</t>
+          <t>Ultima esecuzione: 35 elementi esaminati, 1 pertinenti</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Regione Lombardia – Bandi</t>
+          <t>Fondazione Cariparo</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -7361,40 +7754,40 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Lombardia</t>
+          <t>Italia (Veneto)</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Pubblico regionale</t>
+          <t>Fondazione bancaria</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://www.bandi.regione.lombardia.it/</t>
+          <t>https://www.fondazionecariparo.it/</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>21/10/2026 12:01</t>
+          <t>22/10/2026 22:16</t>
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>6</v>
+        <v>245</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Ultima esecuzione: 1 elementi esaminati, 0 pertinenti</t>
+          <t>Ultima esecuzione: 35 elementi esaminati, 0 pertinenti</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Regione Toscana – Bandi</t>
+          <t>Fondazione Cariplo</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -7404,29 +7797,29 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Toscana</t>
+          <t>Italia (Lombardia)</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Pubblico regionale</t>
+          <t>Fondazione bancaria</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://www.regione.toscana.it/</t>
+          <t>https://www.fondazionecariplo.it/</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>21/10/2026 12:02</t>
+          <t>22/10/2026 22:10</t>
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>210</v>
+        <v>245</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
@@ -7437,7 +7830,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Stroke Association</t>
+          <t>Fondazione Cariverona</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -7447,36 +7840,40 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Regno Unito</t>
+          <t>Italia (Veneto, Lombardia)</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Charity</t>
+          <t>Fondazione bancaria</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://www.stroke.org.uk/</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="n"/>
+          <t>https://www.fondazionecariverona.org/</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>22/10/2026 22:17</t>
+        </is>
+      </c>
       <c r="G36" s="2" t="n">
-        <v>3</v>
+        <v>245</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Ultimo errore 21/10/2026: HTTP 403</t>
+          <t>Ultima esecuzione: 35 elementi esaminati, 0 pertinenti</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Transforming Health and Care Systems (THCS)</t>
+          <t>Fondazione Umberto Veronesi</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -7486,40 +7883,40 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Europa</t>
+          <t>Italia</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Pubblico europeo</t>
+          <t>Fondazione privata</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://www.thcspartnership.eu/</t>
+          <t>https://www.fondazioneveronesi.it/</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>21/10/2026 12:19</t>
+          <t>22/10/2026 22:18</t>
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>84</v>
+        <v>245</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>Ultima esecuzione: 14 elementi esaminati, 0 pertinenti</t>
+          <t>Ultima esecuzione: 35 elementi esaminati, 0 pertinenti</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>UKRI – Funding opportunities</t>
+          <t>Foundation for Physical Therapy Research</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -7529,40 +7926,40 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Regno Unito (alcuni aperti a enti esteri)</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Pubblico estero</t>
+          <t>Fondazione privata</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://www.ukri.org/opportunity/</t>
+          <t>https://foundation4pt.org/</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>21/10/2026 12:20</t>
+          <t>22/10/2026 22:31</t>
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>210</v>
+        <v>100</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>Ultima esecuzione: 35 elementi esaminati, 0 pertinenti</t>
+          <t>Ultima esecuzione: 19 elementi esaminati, 1 pertinenti</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Wellcome</t>
+          <t>Gates Foundation – Grand Challenges</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -7582,23 +7979,2168 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://wellcome.org/research-funding</t>
+          <t>https://gcgh.grandchallenges.org/challenges</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>21/10/2026 12:21</t>
+          <t>22/10/2026 22:43</t>
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>210</v>
+        <v>21</v>
       </c>
       <c r="H39" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
+          <t>Ultima esecuzione: 21 elementi esaminati, 0 pertinenti</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Global Health EDCTP3</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Lettura pagine web</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Europa e Africa</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Pubblico europeo</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.global-health-edctp3.europa.eu/funding-calls_en</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="n"/>
+      <c r="G40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>Ultimo errore 22/10/2026: HTTP 404</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Grants.gov (USA, incluso NIH)</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>USA (alcuni aperti a enti esteri)</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Pubblico</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.grants.gov</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>22/10/2026 22:07</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>5942</v>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>116</v>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>Ultima esecuzione: 852 elementi esaminati, 58 pertinenti</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Health Research Board Ireland</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Lettura pagine web</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Irlanda</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Pubblico estero</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hrb.ie/funding/</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="n"/>
+      <c r="G42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>Ultimo errore 22/10/2026: HTTP 403</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Health Research Council of New Zealand</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Lettura pagine web</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Nuova Zelanda</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Pubblico estero</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hrc.govt.nz/funding-opportunities</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>22/10/2026 22:52</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
           <t>Ultima esecuzione: 35 elementi esaminati, 0 pertinenti</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Hertie Foundation</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Lettura pagine web</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Germania</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Fondazione privata</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ghst.de/en/</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>22/10/2026 22:41</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>Ultima esecuzione: 5 elementi esaminati, 0 pertinenti</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Human Frontier Science Program</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Lettura pagine web</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Mondiale</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Pubblico internazionale</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hfsp.org/funding</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="n"/>
+      <c r="G45" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>Ultimo errore 22/10/2026: HTTP 403</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>IBRO – International Brain Research Organization</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Lettura pagine web</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Mondiale</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Pubblico internazionale</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>https://ibro.org/grants/</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>22/10/2026 22:43</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>Ultima esecuzione: 35 elementi esaminati, 0 pertinenti</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>IBRO – International Brain Research Organization grants</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Lettura pagine web</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Internazionale</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Fondazione internazionale</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>https://ibro.org/grants/</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>22/10/2026 22:56</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>Ultima esecuzione: 35 elementi esaminati, 0 pertinenti</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>ICMR – Indian Council of Medical Research</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Lettura pagine web</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Pubblico estero</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.icmr.gov.in/</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>22/10/2026 22:47</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>Ultima esecuzione: 35 elementi esaminati, 1 pertinenti</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>INAIL – Ricerca</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Lettura pagine web</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Italia</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Pubblico nazionale</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>https://www.inail.it/</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>22/10/2026 22:08</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>245</v>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>Ultima esecuzione: 35 elementi esaminati, 0 pertinenti</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>ISCIII – Instituto de Salud Carlos III</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Lettura pagine web</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Spagna</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Pubblico estero</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>https://www.isciii.es/financiacion</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>22/10/2026 22:40</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>Ultima esecuzione: 35 elementi esaminati, 0 pertinenti</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Independent Research Fund Denmark</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Lettura pagine web</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Danimarca</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Pubblico estero</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>https://dff.dk/en</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>22/10/2026 22:38</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>Ultima esecuzione: 35 elementi esaminati, 0 pertinenti</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>India Alliance (DBT/Wellcome)</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Lettura pagine web</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Fondazione privata</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>https://www.indiaalliance.org/</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>22/10/2026 22:47</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>Ultima esecuzione: 1 elementi esaminati, 0 pertinenti</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>International Spinal Research Trust</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Lettura pagine web</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Mondiale</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Charity</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>https://spinal-research.org/research/</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>22/10/2026 22:44</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>Ultima esecuzione: 2 elementi esaminati, 0 pertinenti</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>JPND – EU Joint Programme Neurodegenerative Disease</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Lettura pagine web</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Pubblico europeo</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>https://neurodegenerationresearch.eu/</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>22/10/2026 22:19</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>Ultima esecuzione: 9 elementi esaminati, 0 pertinenti</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>JSPS – Japan Society for the Promotion of Science</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Lettura pagine web</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Giappone</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Pubblico estero</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>https://www.jsps.go.jp/english/</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>22/10/2026 22:46</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>Ultima esecuzione: 35 elementi esaminati, 0 pertinenti</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>JSPS – Postdoctoral Fellowships for Research in Japan</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Lettura pagine web</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Giappone (ricercatori stranieri)</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Pubblico estero</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>https://www.jsps.go.jp/english/e-fellow/</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>22/10/2026 22:55</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>Ultima esecuzione: 35 elementi esaminati, 0 pertinenti</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Lazio Innova – Bandi</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Lettura pagine web</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Pubblico regionale</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lazioinnova.it/</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>22/10/2026 22:09</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>245</v>
+      </c>
+      <c r="H57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>Ultima esecuzione: 35 elementi esaminati, 0 pertinenti</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Lundbeck Foundation</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Lettura pagine web</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Danimarca</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Fondazione privata</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>https://lundbeckfonden.com/en/research</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="n"/>
+      <c r="G58" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>Ultimo errore 22/10/2026: HTTP 404</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>MRFF – Medical Research Future Fund</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Lettura pagine web</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Pubblico estero</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/our-work/medical-research-future-fund</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="n"/>
+      <c r="G59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>Ultimo errore 22/10/2026: irraggiungibile: HTTPSConnectionPool(host='www.health.gov.au', port=443): Read timed out. (read timeout=45)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>MS International Federation</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Lettura pagine web</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Mondiale</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Charity</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>https://www.msif.org/research/</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>22/10/2026 22:44</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="H60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>Ultima esecuzione: 22 elementi esaminati, 0 pertinenti</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Michael J. Fox Foundation</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Lettura pagine web</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Mondiale</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Fondazione privata</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaeljfox.org/</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>22/10/2026 22:29</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>220</v>
+      </c>
+      <c r="H61" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>Ultima esecuzione: 30 elementi esaminati, 2 pertinenti</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Minciencias Colombia</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Lettura pagine web</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Pubblico estero</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>https://minciencias.gov.co/convocatorias</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>22/10/2026 22:50</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>Ultima esecuzione: 35 elementi esaminati, 0 pertinenti</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Ministero dell'Università e della Ricerca</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Lettura pagine web</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Italia</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Pubblico nazionale</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mur.gov.it/</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>22/10/2026 22:07</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>245</v>
+      </c>
+      <c r="H63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>Ultima esecuzione: 35 elementi esaminati, 0 pertinenti</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Ministero della Salute – Ricerca sanitaria</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Lettura pagine web</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Italia</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Pubblico nazionale</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>https://www.salute.gov.it/</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>22/10/2026 22:07</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>Ultima esecuzione: 1 elementi esaminati, 0 pertinenti</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>NCN – National Science Centre Poland</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Lettura pagine web</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Polonia</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Pubblico estero</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ncn.gov.pl/en</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>22/10/2026 22:41</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="H65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>Ultima esecuzione: 35 elementi esaminati, 0 pertinenti</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>NHMRC</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Lettura pagine web</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Pubblico estero</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>https://www.nhmrc.gov.au/funding</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="n"/>
+      <c r="G66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>Ultimo errore 22/10/2026: irraggiungibile: HTTPSConnectionPool(host='www.nhmrc.gov.au', port=443): Read timed out. (read timeout=45)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>NIHR</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Lettura pagine web</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Regno Unito</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Pubblico estero</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>https://www.nihr.ac.uk/</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="n"/>
+      <c r="G67" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>Ultimo errore 22/10/2026: HTTP 403</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>NMRC Singapore</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Lettura pagine web</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Pubblico estero</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>https://www.nmrc.gov.sg/grants/</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="n"/>
+      <c r="G68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>Ultimo errore 22/10/2026: irraggiungibile: HTTPSConnectionPool(host='www.nmrc.gov.sg', port=443): Max retries exceeded with url: /grants/ (Caused by NameResolutionError("HTTPSConnection(host='www.nmrc.gov.sg', port=443): Failed to resolve 'www.nmrc.gov.sg' ([Errno -2] Name or service not known)"))</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>NRF South Africa</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Lettura pagine web</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Sudafrica</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Pubblico estero</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>https://www.nrf.ac.za/funding/</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>22/10/2026 22:51</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="H69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>Ultima esecuzione: 35 elementi esaminati, 0 pertinenti</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>NSFC – National Natural Science Foundation of China</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Lettura pagine web</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Cina</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Pubblico estero</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>https://www.nsfc.gov.cn/english/site_1/index.html</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>22/10/2026 22:46</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="H70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>Ultima esecuzione: 14 elementi esaminati, 0 pertinenti</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>National MS Society</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Lettura pagine web</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Mondiale</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Charity</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>https://www.nationalmssociety.org/research</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>22/10/2026 22:44</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>Ultima esecuzione: 1 elementi esaminati, 0 pertinenti</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Novo Nordisk Foundation</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Lettura pagine web</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Danimarca</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Fondazione privata</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>https://novonordiskfonden.dk/en/grants/</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>22/10/2026 22:41</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="H72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>Ultima esecuzione: 13 elementi esaminati, 0 pertinenti</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>PCORI</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Lettura pagine web</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Fondazione privata</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>https://www.pcori.org/funding-opportunities</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>22/10/2026 22:31</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="n">
+        <v>211</v>
+      </c>
+      <c r="H73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>Ultima esecuzione: 35 elementi esaminati, 0 pertinenti</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Parkinson's Foundation</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Lettura pagine web</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Mondiale</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Fondazione privata</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>https://www.parkinson.org/research</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>22/10/2026 22:29</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="n">
+        <v>104</v>
+      </c>
+      <c r="H74" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>Ultima esecuzione: 18 elementi esaminati, 0 pertinenti</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>Parkinson's UK</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Lettura pagine web</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Regno Unito</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Charity</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>https://www.parkinsons.org.uk/research</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>22/10/2026 22:27</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="H75" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>Ultima esecuzione: 12 elementi esaminati, 1 pertinenti</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Regione Lombardia – Bandi</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Lettura pagine web</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Lombardia</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Pubblico regionale</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bandi.regione.lombardia.it/</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>22/10/2026 22:08</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="H76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>Ultima esecuzione: 1 elementi esaminati, 0 pertinenti</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>Regione Toscana – Bandi</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Lettura pagine web</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Toscana</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Pubblico regionale</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>https://www.regione.toscana.it/</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>22/10/2026 22:09</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="n">
+        <v>245</v>
+      </c>
+      <c r="H77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>Ultima esecuzione: 35 elementi esaminati, 0 pertinenti</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Research Council of Finland</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Lettura pagine web</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Finlandia</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Pubblico estero</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aka.fi/en/research-funding/apply-for-funding/calls-for-applications/</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>22/10/2026 22:39</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="H78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>Ultima esecuzione: 35 elementi esaminati, 0 pertinenti</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>Research Council of Norway</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Lettura pagine web</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Norvegia</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Pubblico estero</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>https://www.forskningsradet.no/en/call-for-proposals/</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>22/10/2026 22:38</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="H79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>Ultima esecuzione: 35 elementi esaminati, 0 pertinenti</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>SAMRC – South African Medical Research Council</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Lettura pagine web</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Sudafrica</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Pubblico estero</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>https://www.samrc.ac.za/funding</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="n"/>
+      <c r="G80" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>Ultimo errore 22/10/2026: HTTP 404</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>SNSF – Swiss National Science Foundation</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Lettura pagine web</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Svizzera</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Pubblico estero</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>https://www.snf.ch/en</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>22/10/2026 22:36</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="H81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>Ultima esecuzione: 35 elementi esaminati, 0 pertinenti</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Science for Africa Foundation</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Lettura pagine web</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Africa</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Fondazione privata</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>https://scienceforafrica.foundation/funding</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>22/10/2026 22:51</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="H82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>Ultima esecuzione: 16 elementi esaminati, 0 pertinenti</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>Stroke Association</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Lettura pagine web</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Regno Unito</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Charity</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>https://www.stroke.org.uk/</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="n"/>
+      <c r="G83" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>Ultimo errore 22/10/2026: HTTP 403</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Swedish Research Council</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Lettura pagine web</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Svezia</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Pubblico estero</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vr.se/english/applying-for-funding/calls.html</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="n"/>
+      <c r="G84" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>Ultimo errore 22/10/2026: HTTP 404</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>Transforming Health and Care Systems (THCS)</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>Lettura pagine web</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Pubblico europeo</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>https://www.thcspartnership.eu/</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>22/10/2026 22:25</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="H85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>Ultima esecuzione: 14 elementi esaminati, 0 pertinenti</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>UKRI – Funding opportunities</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Lettura pagine web</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Regno Unito (alcuni aperti a enti esteri)</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Pubblico estero</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ukri.org/opportunity/</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>22/10/2026 22:26</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="n">
+        <v>245</v>
+      </c>
+      <c r="H86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>Ultima esecuzione: 35 elementi esaminati, 0 pertinenti</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>VolkswagenStiftung</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>Lettura pagine web</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Germania</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Fondazione privata</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>https://www.volkswagenstiftung.de/en/funding</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>22/10/2026 22:42</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="H87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>Ultima esecuzione: 35 elementi esaminati, 0 pertinenti</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Wellcome</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>Lettura pagine web</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Mondiale</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Fondazione privata</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>https://wellcome.org/research-funding</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>22/10/2026 22:26</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="n">
+        <v>245</v>
+      </c>
+      <c r="H88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>Ultima esecuzione: 35 elementi esaminati, 0 pertinenti</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>Wings for Life</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>Lettura pagine web</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Mondiale</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Fondazione privata</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wingsforlife.com/en/research/</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>22/10/2026 22:42</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>Ultima esecuzione: 1 elementi esaminati, 0 pertinenti</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>ZonMw</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>Lettura pagine web</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Paesi Bassi</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Pubblico estero</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>https://www.zonmw.nl/en</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="n"/>
+      <c r="G90" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>Ultimo errore 22/10/2026: HTTP 403</t>
         </is>
       </c>
     </row>
@@ -7613,7 +10155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -7671,75 +10213,75 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-21 12:31</t>
+          <t>2026-10-22 22:58</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2839</v>
+        <v>3897</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>12 di infrastruttura, 7 servizi o programmi sociali, 6 preclinici, 4 non pertinenti alla riabilitazione, 1 chiusi, 1 pagine che non sono bandi</t>
+          <t>12 di infrastruttura, 7 preclinici, 7 servizi o programmi sociali, 5 non pertinenti alla riabilitazione, 1 chiusi, 1 pagine che non sono bandi</t>
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>NIHR: HTTP 403; Stroke Association: HTTP 403; American Heart Association – Research: HTTP 403; NHMRC: irraggiungibile: HTTPSConnectionPool(host='www.nhmrc.gov.au', port=443): Read timed out. (read timeout=45)</t>
+          <t>NIHR: HTTP 403; Stroke Association: HTTP 403; American Heart Association – Research: HTTP 403; NHMRC: irraggiungibile: HTTPSConnectionPool(host='www.nhmrc.gov.au', port=443): Read timed out. (read timeout=45); BMBF – Gesundheitsforschung (bandi): HTTP 404; ZonMw: HTTP 403; FWO – Research Foundation Flanders: irraggiungibile: HTTPSConnectionPool(host='www.fwo.be', port=443): Max retries exceeded with url: /en/fellowships-funding/ (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1010)'))); Swedish Research Council: HTTP 404; Health Research Board Ireland: HTTP 403; Lundbeck Foundation: HTTP 404; Global Health EDCTP3: HTTP 404; Human Frontier Science Program: HTTP 403; Chan Zuckerberg Initiative: HTTP 404; Cure Parkinson's: HTTP 403; Craig H. Neilsen Foundation: HTTP 404; AMED – Japan Agency for Medical Research and Development: HTTP 404; NMRC Singapore: irraggiungibile: HTTPSConnectionPool(host='www.nmrc.gov.sg', port=443): Max retries exceeded with url: /grants/ (Caused by NameResolutionError("HTTPSConnection(host='www.nmrc.gov.sg', port=443): Failed to resolve 'www.nmrc.gov.sg' ([Errno -2] Name or service not known)")); ANID Chile: HTTP 403; SAMRC – South African Medical Research Council: HTTP 404; MRFF – Medical Research Future Fund: irraggiungibile: HTTPSConnectionPool(host='www.health.gov.au', port=443): Read timed out. (read timeout=45)</t>
         </is>
       </c>
       <c r="H2" s="3" t="n">
-        <v>36.7</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-21 06:19</t>
+          <t>2026-10-21 12:31</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2731</v>
+        <v>2839</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>35 non aperti all'Italia, 3 di infrastruttura, 3 preclinici, 2 non pertinenti alla riabilitazione, 1 servizi o programmi sociali</t>
+          <t>12 di infrastruttura, 7 servizi o programmi sociali, 6 preclinici, 4 non pertinenti alla riabilitazione, 1 chiusi, 1 pagine che non sono bandi</t>
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Nessuno</t>
+          <t>NIHR: HTTP 403; Stroke Association: HTTP 403; American Heart Association – Research: HTTP 403; NHMRC: irraggiungibile: HTTPSConnectionPool(host='www.nhmrc.gov.au', port=443): Read timed out. (read timeout=45)</t>
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>30</v>
+        <v>36.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-19 07:49</t>
+          <t>2026-10-21 06:19</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>2686</v>
+        <v>2731</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>0</v>
@@ -7749,11 +10291,11 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>32 non aperti all'Italia, 3 di infrastruttura, 3 preclinici, 2 non pertinenti alla riabilitazione, 1 servizi o programmi sociali</t>
+          <t>35 non aperti all'Italia, 3 di infrastruttura, 3 preclinici, 2 non pertinenti alla riabilitazione, 1 servizi o programmi sociali</t>
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
@@ -7761,31 +10303,31 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>24.1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-18 14:17</t>
+          <t>2026-10-19 07:49</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>2720</v>
+        <v>2686</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>32 non aperti all'Italia, 3 di infrastruttura, 3 preclinici, 3 non pertinenti alla riabilitazione, 1 servizi o programmi sociali</t>
+          <t>32 non aperti all'Italia, 3 di infrastruttura, 3 preclinici, 2 non pertinenti alla riabilitazione, 1 servizi o programmi sociali</t>
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -7793,62 +10335,94 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>29.3</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-10-18 02:48</t>
+          <t>2026-10-18 14:17</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>2925</v>
+        <v>2720</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>107</v>
-      </c>
-      <c r="E6" s="3" t="n"/>
+        <v>112</v>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>32 non aperti all'Italia, 3 di infrastruttura, 3 preclinici, 3 non pertinenti alla riabilitazione, 1 servizi o programmi sociali</t>
+        </is>
+      </c>
       <c r="F6" s="3" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>NIHR: HTTP 403; Stroke Association: HTTP 403; American Heart Association – Research: HTTP 403; NHMRC: irraggiungibile: HTTPSConnectionPool(host='www.nhmrc.gov.au', port=443): Read timed out. (read timeout=45)</t>
+          <t>Nessuno</t>
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>92.5</v>
+        <v>29.3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-10-17 15:58</t>
+          <t>2026-10-18 02:48</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>2819</v>
+        <v>2925</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>266</v>
+        <v>20</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="E7" s="3" t="n"/>
       <c r="F7" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>NIHR: HTTP 403; Stroke Association: HTTP 403; American Heart Association – Research: HTTP 403; NHMRC: irraggiungibile: HTTPSConnectionPool(host='www.nhmrc.gov.au', port=443): Read timed out. (read timeout=45)</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>92.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-17 15:58</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>2819</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>266</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3" t="n"/>
+      <c r="F8" s="3" t="n">
         <v>44</v>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>NIHR: HTTP 403; Stroke Association: HTTP 403; American Heart Association – Research: HTTP 403; NHMRC: irraggiungibile: HTTPSConnectionPool(host='www.nhmrc.gov.au', port=443): Read timed out. (read timeout=45)</t>
         </is>
       </c>
-      <c r="H7" s="3" t="n">
+      <c r="H8" s="3" t="n">
         <v>76.5</v>
       </c>
     </row>

--- a/report/NeuroGrant_ultimo.xlsx
+++ b/report/NeuroGrant_ultimo.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LOG" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BANDI'!$A$1:$AG$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BANDI'!$A$1:$AG$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -492,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG41"/>
+  <dimension ref="A1:AG39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -700,7 +700,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>EU-HORIZON-HLTH-2027-02-DISEASE-14-two-stage</t>
+          <t>GG-RFA-DA-28-011</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -720,11 +720,11 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Sperimentazioni cliniche per promuovere interventi innovativi nelle malattie neurodegenerative</t>
+          <t>Iniziativa HEAL: Centri di ricerca per la gestione integrata del dolore cronico e del disturbo da uso di oppioidi (RM1)</t>
         </is>
       </c>
       <c r="F2" s="4" t="n">
-        <v>46435</v>
+        <v>46413</v>
       </c>
       <c r="G2" s="5">
         <f>IF(F2="","",F2-TODAY())</f>
@@ -732,61 +732,55 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>In apertura</t>
+          <t>Aperto</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Commissione europea</t>
+          <t>National Institutes of Health</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>EU Funding &amp; Tenders Portal</t>
+          <t>Grants.gov</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>Horizon Europe – HORIZON  Research and Innovation Actions</t>
+          <t>National Institutes of Health – RFA-DA-28-011</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>Clinical trials for advancing innovative interventions for neurodegenerative diseases</t>
+          <t>HEAL Initiative: Integrative Management of Chronic Pain and OUD for Whole Recovery (IMPOWR): Research Centers (RM1 Clinical Trial Required)</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Parkinson, Invecchiamento, Tecnologie riabilitazione, Altre malattie e riabilitazione</t>
+          <t>Altre malattie e riabilitazione</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>parkinson, dementi, alzheimer, aging, wearable, rehabilitat, neurodegenerat, huntington, neurological disorder</t>
+          <t>chronic pain</t>
         </is>
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>Richiede esplicitamente l'integrazione di terapie riabilitative e training cognitivo in trial clinici per malattie neurodegenerative come Alzheimer e Parkinson.</t>
-        </is>
-      </c>
-      <c r="P2" s="6" t="n">
-        <v>39300000</v>
-      </c>
-      <c r="Q2" s="6" t="n">
-        <v>10000000</v>
-      </c>
+          <t>Focalizzato su studi clinici e approcci integrati per la gestione del dolore cronico e del disturbo da uso di oppioidi.</t>
+        </is>
+      </c>
+      <c r="P2" s="6" t="n"/>
+      <c r="Q2" s="6" t="n"/>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="S2" s="2" t="n">
-        <v>4</v>
-      </c>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="n"/>
       <c r="T2" s="3" t="inlineStr">
         <is>
-          <t>Bassa – 4 progetti finanziabili (stima: tasso storico non disponibile)</t>
+          <t>Non stimabile – dati insufficienti</t>
         </is>
       </c>
       <c r="U2" s="3" t="inlineStr">
@@ -795,7 +789,7 @@
         </is>
       </c>
       <c r="V2" s="4" t="n">
-        <v>46324</v>
+        <v>46301</v>
       </c>
       <c r="W2" s="2" t="n"/>
       <c r="X2" s="2" t="inlineStr">
@@ -805,17 +799,13 @@
       </c>
       <c r="Y2" s="3" t="inlineStr">
         <is>
-          <t>Università, centri di ricerca, ospedali, PMI, start-up, organizzazioni di pazienti e autorità sanitarie</t>
-        </is>
-      </c>
-      <c r="Z2" s="3" t="inlineStr">
-        <is>
-          <t>Consorzio: min. 3 enti indipendenti da 3 paesi UE/associati (regola standard, verificare il topic)</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Private institutions of higher education; For profit organizations other than small businesses; Native American tribal organizations (other than Federally recognized tribal governments); Native American tribal governments (Federally recognized); Small businesses; Public and State controlled institutions of higher education; Independent school districts; County governments; State governments; City </t>
+        </is>
+      </c>
+      <c r="Z2" s="3" t="n"/>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>Stati membri UE e paesi associati (altri paesi secondo le condizioni del topic)</t>
+          <t>Enti esteri: da verificare nel bando</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
@@ -825,26 +815,26 @@
       </c>
       <c r="AC2" s="7" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-HLTH-2027-02-DISEASE-14-two-stage</t>
+          <t>https://www.grants.gov/search-results-detail/360048</t>
         </is>
       </c>
       <c r="AD2" s="3" t="inlineStr">
         <is>
-          <t>Il bando di Horizon Europe finanzia la realizzazione di studi clinici precoci volti a verificare sicurezza ed efficacia di interventi innovativi per malattie neurodegenerative non rare come Parkinson e Alzheimer. Le proposte devono combinare un principio attivo terapeutico con approcci multidisciplinari complementari, inclusi esplicitamente terapie riabilitative, modifiche dello stile di vita e training cognitivo, oltre all'uso di tecnologie digitali per il monitoraggio a lungo termine. Possono partecipare consorzi internazionali composti da università, centri clinici, PMI, associazioni di pazienti e altri enti stabiliti negli Stati membri dell'UE o nei Paesi associati.</t>
+          <t>Nell'ambito dell'iniziativa NIH HEAL, il bando finanzia centri di ricerca (meccanismo RM1) dedicati alla gestione integrata del dolore cronico e del disturbo da uso di oppioidi (OUD). L'obiettivo della rete di ricerca IMPOWR è sperimentare, mediante trial clinici obbligatori, modelli e approcci assistenziali innovativi in grado di ottimizzare la gestione del dolore cronico e migliorare i percorsi di recupero nei sistemi sanitari. Possono candidarsi istituzioni accademiche, organizzazioni di ricerca e sanitarie, inclusi espressamente enti non statunitensi (istituzioni straniere), consentendo la partecipazione di centri di ricerca italiani. Il bando finanzia progetti di ricerca clinica collaborativi supportati da un centro di coordinamento dedicato, promuovendo soluzioni efficaci e applicabili nella pratica clinica.</t>
         </is>
       </c>
       <c r="AE2" s="4" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="AF2" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AG2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>EU-HORIZON-HLTH-2027-01-STAYHLTH-01</t>
+          <t>EU-HORIZON-HLTH-2027-02-DISEASE-14-two-stage</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -864,7 +854,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Affrontare le disabilità lungo l'arco della vita per favorire la vita indipendente e l'inclusione</t>
+          <t>Trial clinici per far progredire interventi innovativi nelle malattie neurodegenerative</t>
         </is>
       </c>
       <c r="F3" s="4" t="n">
@@ -896,29 +886,29 @@
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>Addressing disabilities through the life course to support independent living and inclusion</t>
+          <t>Clinical trials for advancing innovative interventions for neurodegenerative diseases</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Invecchiamento, Tecnologie riabilitazione, Altre malattie e riabilitazione</t>
+          <t>Parkinson, Invecchiamento, Tecnologie riabilitazione, Altre malattie e riabilitazione</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>frailty, older persons, assistive technolog, rehabilitat, disabilit, cardiovascular, obesit</t>
+          <t>parkinson, dementi, alzheimer, aging, wearable, rehabilitat, neurodegenerat, huntington, neurological disorder</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>Bando dedicato all'accesso a servizi di riabilitazione innovativa con tecnologie assistive e al supporto dell'autonomia nelle disabilità a lungo termine.</t>
+          <t>Prevede trial clinici su malattie neurodegenerative in cui le terapie attive devono integrarsi con approcci multidisciplinari inclusi interventi di riabilitazione e training cognitivo.</t>
         </is>
       </c>
       <c r="P3" s="6" t="n">
         <v>39300000</v>
       </c>
       <c r="Q3" s="6" t="n">
-        <v>8000000</v>
+        <v>10000000</v>
       </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
@@ -926,11 +916,11 @@
         </is>
       </c>
       <c r="S3" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T3" s="3" t="inlineStr">
         <is>
-          <t>Media – 5 progetti finanziabili (stima: tasso storico non disponibile)</t>
+          <t>Bassa – 4 progetti finanziabili (stima: tasso storico non disponibile)</t>
         </is>
       </c>
       <c r="U3" s="3" t="inlineStr">
@@ -947,7 +937,11 @@
           <t>Ricerca</t>
         </is>
       </c>
-      <c r="Y3" s="3" t="n"/>
+      <c r="Y3" s="3" t="inlineStr">
+        <is>
+          <t>Università, centri di ricerca, ospedali, PMI, start-up, organizzazioni di pazienti e autorità sanitarie</t>
+        </is>
+      </c>
       <c r="Z3" s="3" t="inlineStr">
         <is>
           <t>Consorzio: min. 3 enti indipendenti da 3 paesi UE/associati (regola standard, verificare il topic)</t>
@@ -965,26 +959,26 @@
       </c>
       <c r="AC3" s="7" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-HLTH-2027-01-STAYHLTH-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-HLTH-2027-02-DISEASE-14-two-stage</t>
         </is>
       </c>
       <c r="AD3" s="3" t="inlineStr">
         <is>
-          <t>Questo bando Horizon Europe mira a promuovere la vita indipendente e l'inclusione sociale delle persone con disabilità a lungo termine lungo tutto l'arco dell'esistenza. Le proposte devono affrontare almeno tre aree tematiche tra cui: ricerca sanitaria sulle patologie causa di disabilità; percorsi di transizione verso l'autonomia per minori o anziani; accesso a servizi di abilitazione e riabilitazione, compresa la riabilitazione psicologica e l'impiego di tecnologie assistive; prevenzione dei fattori di rischio secondari; transizione dall'istituzionalizzazione alla comunità e sviluppo di modelli assistenziali centrati sulla persona. L'obiettivo è rimuovere le barriere fisiche, sociali e relazionali, fornendo servizi integrati sociosanitari di supporto e autosufficienza per le persone disabili e le loro famiglie.</t>
+          <t>Il bando di Horizon Europe finanzia trial clinici in fase precoce dedicati allo sviluppo e alla validazione di interventi terapeutici innovativi per le malattie neurodegenerative (come Alzheimer e Parkinson, escludendo le malattie rare). Le soluzioni terapeutiche devono combinare principi attivi con approcci multidisciplinari complementari, inclusi terapie riabilitative, modifiche dello stile di vita o stimolazione cognitiva, al fine di migliorare la qualità di vita dei pazienti. Le proposte devono prevedere la valutazione dell'efficacia, dei meccanismi d'azione anche tramite biomarcatori e imaging, e l'impiego di tecnologie digitali o indossabili per il monitoraggio. È fortemente incoraggiata la partecipazione di PMI e il coinvolgimento attivo di pazienti e caregiver.</t>
         </is>
       </c>
       <c r="AE3" s="4" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="AF3" s="4" t="n">
-        <v>46317</v>
+        <v>46312</v>
       </c>
       <c r="AG3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>GG-PAR-25-124</t>
+          <t>EU-HORIZON-HLTH-2027-01-STAYHLTH-01</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -1004,11 +998,11 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Finanziamento di ricerca per ricercatori a inizio carriera NCMRR (R03 Clinical Trial facoltativo)</t>
+          <t>Affrontare le disabilità lungo l'arco della vita per favorire la vita indipendente e l'inclusione</t>
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>46759</v>
+        <v>46435</v>
       </c>
       <c r="G4" s="5">
         <f>IF(F4="","",F4-TODAY())</f>
@@ -1016,61 +1010,61 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Aperto</t>
+          <t>In apertura</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>National Institutes of Health</t>
+          <t>Commissione europea</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Grants.gov</t>
+          <t>EU Funding &amp; Tenders Portal</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>National Institutes of Health – PAR-25-124</t>
+          <t>Horizon Europe – HORIZON  Research and Innovation Actions</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>NCMRR Early Career Research Award (R03 Clinical Trial Optional)</t>
+          <t>Addressing disabilities through the life course to support independent living and inclusion</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Altre malattie e riabilitazione</t>
+          <t>Invecchiamento, Tecnologie riabilitazione, Altre malattie e riabilitazione</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>rehabilitat</t>
+          <t>frailty, older persons, assistive technolog, rehabilitat, disabilit, cardiovascular, obesit</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>Bando dedicato specificamente alla ricerca di base e clinica in riabilitazione promosso dal NCMRR per ricercatori a inizio carriera.</t>
+          <t>Pone al centro la disabilità a lungo termine e include specificamente la ricerca su percorsi di abilitazione, riabilitazione e tecnologie assistive per favorire la vita indipendente.</t>
         </is>
       </c>
       <c r="P4" s="6" t="n">
-        <v>200000</v>
+        <v>39300000</v>
       </c>
       <c r="Q4" s="6" t="n">
-        <v>200000</v>
+        <v>8000000</v>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="S4" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t>Bassa – 1 progetti finanziabili (stima: tasso storico non disponibile)</t>
+          <t>Media – 5 progetti finanziabili (stima: tasso storico non disponibile)</t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr">
@@ -1079,7 +1073,7 @@
         </is>
       </c>
       <c r="V4" s="4" t="n">
-        <v>45614</v>
+        <v>46324</v>
       </c>
       <c r="W4" s="2" t="n"/>
       <c r="X4" s="2" t="inlineStr">
@@ -1087,15 +1081,15 @@
           <t>Ricerca</t>
         </is>
       </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t>Nonprofits having a 501(c)(3) status with the IRS, other than institutions of higher education; State governments; Public housing authorities/Indian housing authorities; Nonprofits that do not have a 501(c)(3) status with the IRS, other than institutions of higher education; Private institutions of higher education; For profit organizations other than small businesses; Special district governments</t>
-        </is>
-      </c>
-      <c r="Z4" s="3" t="n"/>
+      <c r="Y4" s="3" t="n"/>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>Consorzio: min. 3 enti indipendenti da 3 paesi UE/associati (regola standard, verificare il topic)</t>
+        </is>
+      </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>Ammessi anche enti non statunitensi (call NIH completa)</t>
+          <t>Stati membri UE e paesi associati (altri paesi secondo le condizioni del topic)</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
@@ -1105,26 +1099,26 @@
       </c>
       <c r="AC4" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/357206</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-HLTH-2027-01-STAYHLTH-01</t>
         </is>
       </c>
       <c r="AD4" s="3" t="inlineStr">
         <is>
-          <t>Il bando NCMRR Early Career Research Award (R03), promosso dal National Institutes of Health (NIH), sostiene ricercatori a inizio carriera che intendono consolidare un percorso scientifico indipendente nel campo della riabilitazione medica. L'iniziativa finanzia progetti di ricerca clinica e di base allineati al Piano di Ricerca sulla Riabilitazione del NIH, con l'obiettivo di raccogliere dati preliminari sufficienti per future proposte R01. Sono ammissibili analisi secondarie di dati preesistenti, studi pilota indipendenti, sviluppo di metodologie di ricerca, studi traslazionali, ricerca sugli esiti e lo sviluppo di nuove tecnologie. Possono candidarsi istituzioni accademiche e di ricerca, comprese organizzazioni non profit ed enti stranieri con sede al di fuori degli Stati Uniti.</t>
+          <t>Il bando promosso nell'ambito di Horizon Europe sostiene progetti di ricerca finalizzati a favorire l'inclusione sociale e la vita indipendente di persone con disabilità a lungo termine (fisiche, mentali, intellettive o sensoriali). Gli ambiti di ricerca ammessi includono lo studio delle cause della disabilità, soluzioni diagnostiche e terapeutiche innovative, l'accesso a servizi di abilitazione e riabilitazione integrati con tecnologie assistive, modelli per la transizione dalla residenzialità istituzionale al domicilio e la prevenzione delle disabilità durante l'intero arco vitale. I progetti devono proporre modelli assistenziali incentrati sulla persona, con servizi sanitari e sociali accessibili, e favorire il coinvolgimento diretto di utenti, famiglie e organizzazioni di rappresentanza.</t>
         </is>
       </c>
       <c r="AE4" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="AF4" s="4" t="n">
         <v>46317</v>
-      </c>
-      <c r="AF4" s="4" t="n">
-        <v>46312</v>
       </c>
       <c r="AG4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>WEB-00773cbd93aa</t>
+          <t>GG-PAR-25-124</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -1134,7 +1128,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1144,11 +1138,11 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Finanziamento ponte per la ricerca interrotta sulle malattie neurodegenerative (BFDN)</t>
+          <t>Finanziamento NCMRR per ricercatori a inizio carriera (R03 Clinical Trial opzionale)</t>
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>46325</v>
+        <v>46759</v>
       </c>
       <c r="G5" s="5">
         <f>IF(F5="","",F5-TODAY())</f>
@@ -1156,49 +1150,49 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>In scadenza (≤30 gg)</t>
+          <t>Aperto</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Michael J. Fox Foundation</t>
+          <t>National Institutes of Health</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>Michael J. Fox Foundation</t>
+          <t>Grants.gov</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>Bridge Funding for Disrupted Neurodegenerative Research Grant Program (BFDN) Powering the Next Generation of Research</t>
+          <t>National Institutes of Health – PAR-25-124</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>Bridge Funding for Disrupted Neurodegenerative Research Grant Program (BFDN) Powering the Next Generation of Research</t>
+          <t>NCMRR Early Career Research Award (R03 Clinical Trial Optional)</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Parkinson, Invecchiamento, Altre malattie e riabilitazione</t>
+          <t>Altre malattie e riabilitazione</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>parkinson, dementi, alzheimer, neurodegenerat, neurological disease</t>
+          <t>rehabilitat</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>Finanzia la continuità di progetti di ricerca su Parkinson, Alzheimer e demenze, senza una focalizzazione specifica sulla riabilitazione.</t>
+          <t>Il bando finanzia specificamente ricercatori a inizio carriera nell'ambito della riabilitazione medica su tematiche coerenti con la missione dell'NCMRR.</t>
         </is>
       </c>
       <c r="P5" s="6" t="n">
-        <v>250000</v>
+        <v>200000</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>250000</v>
+        <v>200000</v>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
@@ -1215,15 +1209,13 @@
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t>Co-finanziamento richiesto (25% a carico del beneficiario)</t>
-        </is>
-      </c>
-      <c r="V5" s="4" t="n"/>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>12 mesi</t>
-        </is>
-      </c>
+          <t>Interamente finanziato</t>
+        </is>
+      </c>
+      <c r="V5" s="4" t="n">
+        <v>45614</v>
+      </c>
+      <c r="W5" s="2" t="n"/>
       <c r="X5" s="2" t="inlineStr">
         <is>
           <t>Ricerca</t>
@@ -1231,13 +1223,13 @@
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t>Ricercatori principali a inizio carriera (Early Stage Investigator secondo i criteri NIH o entro 7 anni dalla qualifica) titolari di grant federali statunitensi interrotti</t>
+          <t>Special district governments; Native American tribal organizations (other than Federally recognized tribal governments); City or township governments; Independent school districts; Private institutions of higher education; Native American tribal governments (Federally recognized); Nonprofits having a 501(c)(3) status with the IRS, other than institutions of higher education; Others (see text field</t>
         </is>
       </c>
       <c r="Z5" s="3" t="n"/>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>Mondiale</t>
+          <t>Ammessi anche enti non statunitensi (call NIH completa)</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
@@ -1247,16 +1239,16 @@
       </c>
       <c r="AC5" s="7" t="inlineStr">
         <is>
-          <t>https://www.michaeljfox.org/grant/bridge-funding-disrupted-neurodegenerative-research-grant-program-bfdn-powering-next</t>
+          <t>https://www.grants.gov/search-results-detail/357206</t>
         </is>
       </c>
       <c r="AD5" s="3" t="inlineStr">
         <is>
-          <t>Il programma congiunto promosso da Alzheimer's Association, The Michael J. Fox Foundation e Robertson Foundation fornisce finanziamenti ponte per garantire la continuità a progetti di ricerca sulle malattie neurodegenerative (morbo di Parkinson, malattia di Alzheimer, demenza frontotemporale, demenza a corpi di Lewy e parkinsonismi atipici). L'iniziativa è specificamente rivolta a ricercatori a inizio carriera (Early Stage Investigator secondo i criteri NIH o entro 7 anni da tale qualifica) i cui finanziamenti federali statunitensi abbiano subito interruzioni, ritardi o tagli per cambiamenti operativi o di priorità. Il contributo, fino a un massimo di 250.000 dollari per una durata compresa tra 3 e 12 mesi, copre stipendi e costi diretti, richiedendo un cofinanziamento istituzionale fino al 25%.</t>
+          <t>Il bando NCMRR Early Career Research Award (R03), promosso dal National Center for Medical Rehabilitation Research degli NIH, sostiene la ricerca di base e clinica condotta da ricercatori nel campo della riabilitazione che stanno avviando una carriera indipendente. L'obiettivo primario è consentire ai Principal Investigator di raccogliere dati preliminari sufficienti per una successiva domanda di finanziamento R01. Sono ammessi progetti di analisi secondaria di dati, piccoli studi di ricerca autonomi, sviluppo di metodologie, ricerca traslazionale, outcomes research e sviluppo di nuove tecnologie. Possono candidarsi istituzioni accademiche e di ricerca idonee, comprese organizzazioni non statunitensi ed enti internazionali.</t>
         </is>
       </c>
       <c r="AE5" s="4" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="AF5" s="4" t="n">
         <v>46312</v>
@@ -1266,7 +1258,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>GG-PAR-25-226</t>
+          <t>GG-PAR-27-065</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -1276,7 +1268,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1286,11 +1278,11 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Sviluppo clinico precoce integrato (fase 1-2a) di nuovi agenti terapeutici per l'Alzheimer e le demenze correlate (UG3/UH3)</t>
+          <t>Trial clinici esplorativi ed di efficacia del NINDS</t>
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>46345</v>
+        <v>47186</v>
       </c>
       <c r="G6" s="5">
         <f>IF(F6="","",F6-TODAY())</f>
@@ -1298,7 +1290,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>In scadenza (≤30 gg)</t>
+          <t>Aperto</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1313,27 +1305,27 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>National Institutes of Health – PAR-25-226</t>
+          <t>National Institutes of Health – PAR-27-065</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>Seamless Early-Stage Clinical Drug Development (Phase 1 to 2a) for Novel therapeutic Agents for the Spectrum of Alzheimer's Disease (AD) and AD-related Dementias (ADRD) (UG3/UH3 Clinical Trial Required)</t>
+          <t>NINDS Efficacy and Exploratory Clinical Trials (UG3/UH3 - Clinical Trial Required)</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Invecchiamento</t>
+          <t>Ictus, Altre malattie e riabilitazione</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>dementi, alzheimer</t>
+          <t>stroke, rehabilitat, neurological disorder</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>Riguarda la malattia di Alzheimer e le demenze correlate, ma è incentrato sullo sviluppo farmacologico precoce e non su interventi riabilitativi.</t>
+          <t>Il bando finanzia trial clinici anche su terapie riabilitative per malattie neurologiche, ammettendo enti italiani.</t>
         </is>
       </c>
       <c r="P6" s="6" t="n"/>
@@ -1355,7 +1347,7 @@
         </is>
       </c>
       <c r="V6" s="4" t="n">
-        <v>45618</v>
+        <v>46265</v>
       </c>
       <c r="W6" s="2" t="n"/>
       <c r="X6" s="2" t="inlineStr">
@@ -1365,13 +1357,17 @@
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t>Public housing authorities/Indian housing authorities; Public and State controlled institutions of higher education; Special district governments; Independent school districts; State governments; Native American tribal governments (Federally recognized); County governments; Nonprofits that do not have a 501(c)(3) status with the IRS, other than institutions of higher education; Private institution</t>
-        </is>
-      </c>
-      <c r="Z6" s="3" t="n"/>
+          <t xml:space="preserve">Native American tribal governments (Federally recognized); Others (see text field entitled "Additional Information on Eligibility" for clarification); Public housing authorities/Indian housing authorities; Native American tribal organizations (other than Federally recognized tribal governments); Independent school districts; State governments; For profit organizations other than small businesses; </t>
+        </is>
+      </c>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t>Non sono ammessi sub-accordi o subappalti a entità estere; le organizzazioni estere possono candidarsi direttamente come capofila</t>
+        </is>
+      </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>Ammessi anche enti non statunitensi (call NIH completa)</t>
+          <t>Enti esteri: da verificare nel bando</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
@@ -1381,16 +1377,16 @@
       </c>
       <c r="AC6" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/357343</t>
+          <t>https://www.grants.gov/search-results-detail/360404</t>
         </is>
       </c>
       <c r="AD6" s="3" t="inlineStr">
         <is>
-          <t>Il bando invita a presentare proposte per lo sviluppo clinico precoce di nuovi agenti farmacologici non amiloidi e non tau per la malattia di Alzheimer e le demenze correlate. Tramite il meccanismo a fasi UG3/UH3, il bando unisce protocolli di sperimentazione di fase 1 con fasi 1b/2a per valutare sicurezza, tollerabilità ed efficacia su sintomi cognitivi o neuropsichiatrici in diversi stadi di malattia. L'avanzamento tra le fasi è subordinato a traguardi predefiniti. Possono partecipare istituti accademici, organizzazioni sanitarie, enti di ricerca pubblici e privati e istituzioni straniere non statunitensi.</t>
+          <t>Il bando incoraggia domande per studi clinici promossi da ricercatori e finanziati dal National Institute of Neurological Disorders and Stroke (NINDS). Vengono finanziati studi su piccole molecole, prodotti biologici, dispositivi, nonché interventi chirurgici, comportamentali, dietetici o terapie riabilitative. Sono particolarmente incoraggiati studi su malattie e cure neurologiche lungo tutto l'arco della vita, che spaziano da trial clinici esplorativi di fase precoce e intermedia fino a trial di conferma di fase 3 o di efficacia comparativa. Possono partecipare organizzazioni ed enti di ricerca nazionali e internazionali, inclusi quelli non statunitensi. Il finanziamento copre lo sviluppo di studi clinici mirati.</t>
         </is>
       </c>
       <c r="AE6" s="4" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="AF6" s="4" t="n">
         <v>46312</v>
@@ -1400,7 +1396,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>EU-HORIZON-HLTH-2027-02-DISEASE-01-two-stage</t>
+          <t>GG-RFA-NS-26-028</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -1415,16 +1411,16 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Ricerca clinica</t>
+          <t>Tecnologia / innovazione</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Interventi sanitari innovativi per le malattie non trasmissibili</t>
+          <t>Iniziativa HEAL: ottimizzazione di dispositivi medici terapeutici mediante ricerca meccanicistica di team science (RM1)</t>
         </is>
       </c>
       <c r="F7" s="4" t="n">
-        <v>46435</v>
+        <v>46325</v>
       </c>
       <c r="G7" s="5">
         <f>IF(F7="","",F7-TODAY())</f>
@@ -1432,61 +1428,57 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>In apertura</t>
+          <t>In scadenza (≤30 gg)</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Commissione europea</t>
+          <t>National Institutes of Health</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>EU Funding &amp; Tenders Portal</t>
+          <t>Grants.gov</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>Horizon Europe – HORIZON  Research and Innovation Actions</t>
+          <t>National Institutes of Health – RFA-NS-26-028</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>Innovative healthcare interventions for non-communicable diseases</t>
+          <t>HEAL Initiative: Optimization of Therapeutic Medical Devices through Team Science Mechanistic Research (RM1)</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Tecnologie riabilitazione, Altre malattie e riabilitazione</t>
+          <t>Ictus, Altre malattie e riabilitazione</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>wearable, disabilit</t>
+          <t>stroke, neurological disorder</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>Bando incentrato su interventi innovativi e gestione clinica di patologie croniche cardiache e respiratorie, senza focus esclusivo sulla riabilitazione.</t>
-        </is>
-      </c>
-      <c r="P7" s="6" t="n">
-        <v>63800000</v>
-      </c>
-      <c r="Q7" s="6" t="n">
-        <v>8000000</v>
-      </c>
+          <t>Riguarda l'ottimizzazione e i meccanismi di dispositivi medici terapeutici per patologie neurologiche e dolore (iniziativa HEAL), ambiti di forte interesse riabilitativo.</t>
+        </is>
+      </c>
+      <c r="P7" s="6" t="n"/>
+      <c r="Q7" s="6" t="n"/>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="S7" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t>Media – 8 progetti finanziabili (stima: tasso storico non disponibile)</t>
+          <t>Bassa – 4 progetti finanziabili (stima: tasso storico non disponibile)</t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
@@ -1495,7 +1487,7 @@
         </is>
       </c>
       <c r="V7" s="4" t="n">
-        <v>46324</v>
+        <v>46097</v>
       </c>
       <c r="W7" s="2" t="n"/>
       <c r="X7" s="2" t="inlineStr">
@@ -1505,17 +1497,17 @@
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t>Enti di ricerca, università, strutture sanitarie, PMI, startup, autorità regolatorie e organizzazioni di pazienti.</t>
+          <t>Independent school districts; Public and State controlled institutions of higher education; Native American tribal organizations (other than Federally recognized tribal governments); City or township governments; Small businesses; For profit organizations other than small businesses; Nonprofits that do not have a 501(c)(3) status with the IRS, other than institutions of higher education; Public ho</t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t>Consorzio: min. 3 enti indipendenti da 3 paesi UE/associati (regola standard, verificare il topic)</t>
+          <t>Team scientifici interdisciplinari comprendenti competenze ingegneristiche, biologiche, computazionali e cliniche</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>Stati membri UE e paesi associati (altri paesi secondo le condizioni del topic)</t>
+          <t>Enti esteri: da verificare nel bando</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
@@ -1525,16 +1517,16 @@
       </c>
       <c r="AC7" s="7" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-HLTH-2027-02-DISEASE-01-two-stage</t>
+          <t>https://www.grants.gov/search-results-detail/361520</t>
         </is>
       </c>
       <c r="AD7" s="3" t="inlineStr">
         <is>
-          <t>Il bando punta a ridurre l'impatto di specifiche malattie croniche non trasmissibili, tra cui patologie cardiovascolari, diabete, malattie respiratorie e renali croniche. Si finanzia la realizzazione di studi clinici in fase precoce per validare interventi terapeutici o di gestione della patologia innovativi o perfezionati, supportati da prove di concetto su sicurezza ed efficacia clinica. Le proposte devono integrare tecnologie digitali (come intelligenza artificiale o dispositivi indossabili) per il monitoraggio a lungo termine a domicilio. Possono partecipare consorzi internazionali composti da università, enti di ricerca clinica, ospedali, piccole e medie imprese, startup e organizzazioni di pazienti, promuovendo anche l'inclusione di competenze socio-umanistiche e l'interazione con autorità regolatorie per favorire la futura scalabilità degli interventi.</t>
+          <t>Questo preavviso di bando (NOFO) dell'iniziativa HEAL, coordinato dal NINDS e da altri istituti degli NIH, finanzierà ricerche interdisciplinari volte a chiarire i meccanismi d'azione dei dispositivi medici terapeutici per migliorare gli esiti clinici nelle patologie neurologiche e nel dolore. L'obiettivo è comprendere come tali dispositivi producano effetti terapeutici e modulino marcatori fisiologici, ottimizzando gli interventi basati su dispositivi già approvati dalla FDA o sperimentali. I progetti potranno comprendere trial clinici meccanicistici, modelli computazionali o studi su animali. Possono candidarsi consorzi interdisciplinari che associno competenze in ingegneria, biologia, clinica e intelligenza artificiale, inclusi istituti accademici e di ricerca esteri non statunitensi.</t>
         </is>
       </c>
       <c r="AE7" s="4" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="AF7" s="4" t="n">
         <v>46312</v>
@@ -1544,7 +1536,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>EU-HORIZON-HLTH-2027-01-DISEASE-10</t>
+          <t>WEB-00773cbd93aa</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -1564,11 +1556,11 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Prevenzione e gestione delle malattie croniche non trasmissibili nei bambini e nei giovani (GACD)</t>
+          <t>Programma di finanziamento ponte BFDN per la ricerca interrotta sulle malattie neurodegenerative</t>
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>46435</v>
+        <v>46325</v>
       </c>
       <c r="G8" s="5">
         <f>IF(F8="","",F8-TODAY())</f>
@@ -1576,72 +1568,74 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>In apertura</t>
+          <t>In scadenza (≤30 gg)</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Commissione europea</t>
+          <t>Michael J. Fox Foundation</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>EU Funding &amp; Tenders Portal</t>
+          <t>Michael J. Fox Foundation</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>Horizon Europe – HORIZON  Research and Innovation Actions</t>
+          <t>Bridge Funding for Disrupted Neurodegenerative Research Grant Program (BFDN) Powering the Next Generation of Research</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>Prevention and management of chronic non-communicable diseases in children and young people (GACD)</t>
+          <t>Bridge Funding for Disrupted Neurodegenerative Research Grant Program (BFDN) Powering the Next Generation of Research</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Altre malattie e riabilitazione</t>
+          <t>Parkinson, Invecchiamento, Altre malattie e riabilitazione</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>neurological disorder, disabilit</t>
+          <t>parkinson, dementi, alzheimer, neurodegenerat, neurological disease</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>Finanzia la ricerca sull'implementazione per la gestione di patologie croniche non trasmissibili nei giovani, ambito che include percorsi di cura complessi ma non esclusivamente riabilitativi.</t>
+          <t>Offre finanziamenti ponte per progetti di ricerca su Parkinson, Alzheimer e demenze colpite da tagli ai fondi federali USA, senza focus primario sulla riabilitazione.</t>
         </is>
       </c>
       <c r="P8" s="6" t="n">
-        <v>11800000</v>
+        <v>250000</v>
       </c>
       <c r="Q8" s="6" t="n">
-        <v>4000000</v>
+        <v>250000</v>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="S8" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t>Bassa – 3 progetti finanziabili (stima: tasso storico non disponibile)</t>
+          <t>Bassa – 1 progetti finanziabili (stima: tasso storico non disponibile)</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t>Interamente finanziato</t>
-        </is>
-      </c>
-      <c r="V8" s="4" t="n">
-        <v>46324</v>
-      </c>
-      <c r="W8" s="2" t="n"/>
+          <t>Co-finanziamento richiesto (25% a carico del beneficiario)</t>
+        </is>
+      </c>
+      <c r="V8" s="4" t="n"/>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>12 mesi</t>
+        </is>
+      </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
           <t>Ricerca</t>
@@ -1649,17 +1643,13 @@
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t>Ricercatori, professionisti sanitari, erogatori di servizi, decisori politici e stakeholder locali</t>
-        </is>
-      </c>
-      <c r="Z8" s="3" t="inlineStr">
-        <is>
-          <t>Consorzio: min. 3 enti indipendenti da 3 paesi UE/associati (regola standard, verificare il topic)</t>
-        </is>
-      </c>
+          <t>Ricercatori principali a inizio carriera (Early Stage Investigator secondo i criteri NIH o entro 7 anni dalla qualifica) titolari di grant federali statunitensi interrotti</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="n"/>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>Stati membri UE e paesi associati (altri paesi secondo le condizioni del topic)</t>
+          <t>Mondiale</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
@@ -1669,26 +1659,26 @@
       </c>
       <c r="AC8" s="7" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-HLTH-2027-01-DISEASE-10</t>
+          <t>https://www.michaeljfox.org/grant/bridge-funding-disrupted-neurodegenerative-research-grant-program-bfdn-powering-next</t>
         </is>
       </c>
       <c r="AD8" s="3" t="inlineStr">
         <is>
-          <t>In collaborazione con la Global Alliance for Chronic Diseases (GACD), il bando sostiene la ricerca sull'implementazione di interventi evidence-based per la prevenzione, la diagnosi precoce e la gestione a lungo termine delle malattie croniche non trasmissibili in soggetti tra 1 e 24 anni. Il focus riguarda popolazioni vulnerabili in paesi a basso e medio reddito o comunità svantaggiate in paesi ad alto reddito. Si finanziano modelli di cura integrati, percorsi di transizione dall'assistenza pediatrica a quella per adulti, supporto ai caregiver e strategie costo-efficaci. Possono partecipare ricercatori, operatori sanitari e istituzioni di ricerca appartenenti a consorzi eleggibili secondo le regole di Horizon Europe.</t>
+          <t>Il programma promosso congiuntamente da Alzheimer's Association e Michael J. Fox Foundation offre finanziamenti ponte per sostenere la continuità della ricerca su Alzheimer, Parkinson, demenza frontotemporale, demenza a corpi di Lewy e disturbi correlati. L'iniziativa si rivolge a ricercatori a inizio carriera (Early Stage Investigator) i cui progetti abbiano subito interruzioni o riduzioni a causa di cambiamenti nelle priorità e nei processi dei finanziamenti federali statunitensi (NIH). I fondi finanziano stipendi e costi diretti della ricerca per una durata compresa tra 3 e 12 mesi, con un contributo massimo di 250.000 dollari. È richiesta una quota di cofinanziamento istituzionale pari ad almeno il 25% del budget richiesto.</t>
         </is>
       </c>
       <c r="AE8" s="4" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="AF8" s="4" t="n">
-        <v>46313</v>
+        <v>46312</v>
       </c>
       <c r="AG8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>WEB-6768384ca0cb</t>
+          <t>GG-PAR-25-226</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -1708,60 +1698,58 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Programma per lo sviluppo della pipeline terapeutica nella malattia di Parkinson</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="n"/>
+          <t>Sviluppo clinico precoce integrato (Fase 1-2a) di nuovi agenti terapeutici per l'Alzheimer e le demenze correlate (UG3/UH3)</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>46345</v>
+      </c>
       <c r="G9" s="5">
         <f>IF(F9="","",F9-TODAY())</f>
         <v/>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Scadenza da verificare</t>
+          <t>In scadenza (≤30 gg)</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Michael J. Fox Foundation</t>
+          <t>National Institutes of Health</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>Michael J. Fox Foundation</t>
+          <t>Grants.gov</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>Parkinson's Disease Therapeutics Pipeline Program</t>
+          <t>National Institutes of Health – PAR-25-226</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>Parkinson's Disease Therapeutics Pipeline Program</t>
+          <t>Seamless Early-Stage Clinical Drug Development (Phase 1 to 2a) for Novel therapeutic Agents for the Spectrum of Alzheimer's Disease (AD) and AD-related Dementias (ADRD) (UG3/UH3 Clinical Trial Required)</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Parkinson</t>
+          <t>Invecchiamento</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>parkinson</t>
+          <t>dementi, alzheimer</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>Focalizzato sullo sviluppo terapeutico e farmacologico preclinico e clinico per il Parkinson, senza un focus specifico sulla riabilitazione.</t>
-        </is>
-      </c>
-      <c r="P9" s="6" t="n">
-        <v>250000</v>
-      </c>
-      <c r="Q9" s="6" t="n">
-        <v>5000000</v>
-      </c>
+          <t>Si concentra sullo sviluppo clinico di fase precoce di farmaci per Alzheimer e demenze correlate, senza una componente di riabilitazione.</t>
+        </is>
+      </c>
+      <c r="P9" s="6" t="n"/>
+      <c r="Q9" s="6" t="n"/>
       <c r="R9" s="2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1775,15 +1763,13 @@
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t>Non indicato</t>
-        </is>
-      </c>
-      <c r="V9" s="4" t="n"/>
-      <c r="W9" s="2" t="inlineStr">
-        <is>
-          <t>36 mesi</t>
-        </is>
-      </c>
+          <t>Interamente finanziato</t>
+        </is>
+      </c>
+      <c r="V9" s="4" t="n">
+        <v>45618</v>
+      </c>
+      <c r="W9" s="2" t="n"/>
       <c r="X9" s="2" t="inlineStr">
         <is>
           <t>Ricerca</t>
@@ -1791,17 +1777,13 @@
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t>Imprese biotech/pharma, partenariati accademia-industria e istituti accademici</t>
-        </is>
-      </c>
-      <c r="Z9" s="3" t="inlineStr">
-        <is>
-          <t>Aperto a collaborazioni accademia-industria, singole aziende o progetti a guida accademica</t>
-        </is>
-      </c>
+          <t>Special district governments; County governments; Public housing authorities/Indian housing authorities; Private institutions of higher education; Native American tribal organizations (other than Federally recognized tribal governments); For profit organizations other than small businesses; Nonprofits having a 501(c)(3) status with the IRS, other than institutions of higher education; Native Ameri</t>
+        </is>
+      </c>
+      <c r="Z9" s="3" t="n"/>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>Mondiale</t>
+          <t>Ammessi anche enti non statunitensi (call NIH completa)</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
@@ -1811,16 +1793,16 @@
       </c>
       <c r="AC9" s="7" t="inlineStr">
         <is>
-          <t>https://www.michaeljfox.org/grant/parkinsons-disease-therapeutics-pipeline-program</t>
+          <t>https://www.grants.gov/search-results-detail/357343</t>
         </is>
       </c>
       <c r="AD9" s="3" t="inlineStr">
         <is>
-          <t>Il Therapeutics Pipeline Program della Michael J. Fox Foundation finanzia lo sviluppo preclinico e clinico di interventi terapeutici modificanti la malattia o mirati al controllo sintomatico del Parkinson, integrando strumenti biomarcatori decisionali. Il programma supporta progetti da uno a tre anni con contributi compresi generalmente tra 250.000 e oltre 5 milioni di dollari, a seconda della fase di avanzamento. La candidatura è aperta a imprese biotech, collaborazioni accademia-industria e, in casi specifici, a gruppi esclusivamente accademici. Il processo di selezione è strutturato in due fasi: invio continuo di pre-proposte e, su invito, presentazione della proposta completa secondo scadenze cicliche periodiche. Sono esclusi studi su integratori alimentari o scoperta di target precoci.</t>
+          <t>L'avviso di finanziamento dei National Institutes of Health (NIH) mira a sostenere studi clinici precoci integrati che combinano protocolli di fase 1 con trial di fase 1b/2a per la sperimentazione di nuovi agenti farmacologici per la malattia di Alzheimer e le demenze correlate (ADRD). I candidati terapeutici, comprese piccole molecole e biologici, devono agire su meccanismi diversi da amiloide e tau per trattare sintomi cognitivi e neuropsichiatrici. Possono partecipare istituti accademici, enti di ricerca e organizzazioni non statunitensi (straniere). L'avviso adotta il meccanismo a fasi UG3/UH3, richiedendo tappe intermedie rigorose di sicurezza e tollerabilità per autorizzare il passaggio alla fase successiva.</t>
         </is>
       </c>
       <c r="AE9" s="4" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="AF9" s="4" t="n">
         <v>46312</v>
@@ -1830,31 +1812,31 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>GG-RFA-NS-26-028</t>
+          <t>EU-HORIZON-HLTH-2027-02-DISEASE-01-two-stage</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Da verificare</t>
+          <t>Sì</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Tecnologia / innovazione</t>
+          <t>Ricerca clinica</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Iniziativa HEAL: ottimizzazione dei dispositivi medici terapeutici attraverso la ricerca meccanicistica interdisciplinare (RM1)</t>
+          <t>Interventi sanitari innovativi per le malattie non trasmissibili</t>
         </is>
       </c>
       <c r="F10" s="4" t="n">
-        <v>46325</v>
+        <v>46435</v>
       </c>
       <c r="G10" s="5">
         <f>IF(F10="","",F10-TODAY())</f>
@@ -1862,57 +1844,61 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>In scadenza (≤30 gg)</t>
+          <t>In apertura</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>National Institutes of Health</t>
+          <t>Commissione europea</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Grants.gov</t>
+          <t>EU Funding &amp; Tenders Portal</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>National Institutes of Health – RFA-NS-26-028</t>
+          <t>Horizon Europe – HORIZON  Research and Innovation Actions</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>HEAL Initiative: Optimization of Therapeutic Medical Devices through Team Science Mechanistic Research (RM1)</t>
+          <t>Innovative healthcare interventions for non-communicable diseases</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Ictus, Altre malattie e riabilitazione</t>
+          <t>Tecnologie riabilitazione, Altre malattie e riabilitazione</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>stroke, neurological disorder</t>
+          <t>wearable, disabilit</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>Supporta la ricerca sui meccanismi d'azione di dispositivi medici terapeutici per patologie neurologiche e dolore cronico, altamente rilevanti per la neuroriabilitazione.</t>
-        </is>
-      </c>
-      <c r="P10" s="6" t="n"/>
-      <c r="Q10" s="6" t="n"/>
+          <t>Finanzia trial clinici su interventi sanitari per malattie croniche tra cui cardiovascolari e respiratorie, contesti rilevanti per la riabilitazione ma non dedicati esclusivamente ad essa.</t>
+        </is>
+      </c>
+      <c r="P10" s="6" t="n">
+        <v>63800000</v>
+      </c>
+      <c r="Q10" s="6" t="n">
+        <v>8000000</v>
+      </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="S10" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t>Bassa – 4 progetti finanziabili (stima: tasso storico non disponibile)</t>
+          <t>Media – 8 progetti finanziabili (stima: tasso storico non disponibile)</t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
@@ -1921,7 +1907,7 @@
         </is>
       </c>
       <c r="V10" s="4" t="n">
-        <v>46097</v>
+        <v>46324</v>
       </c>
       <c r="W10" s="2" t="n"/>
       <c r="X10" s="2" t="inlineStr">
@@ -1931,17 +1917,17 @@
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t>Nonprofits having a 501(c)(3) status with the IRS, other than institutions of higher education; Native American tribal organizations (other than Federally recognized tribal governments); State governments; Special district governments; For profit organizations other than small businesses; Public and State controlled institutions of higher education; Independent school districts; City or township g</t>
+          <t>Enti di ricerca, università, strutture sanitarie, PMI, startup, autorità regolatorie e organizzazioni di pazienti.</t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t>Team scientifici interdisciplinari comprendenti competenze ingegneristiche, biologiche, computazionali e cliniche</t>
+          <t>Consorzio: min. 3 enti indipendenti da 3 paesi UE/associati (regola standard, verificare il topic)</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>Enti esteri: da verificare nel bando</t>
+          <t>Stati membri UE e paesi associati (altri paesi secondo le condizioni del topic)</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
@@ -1951,16 +1937,16 @@
       </c>
       <c r="AC10" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/361520</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-HLTH-2027-02-DISEASE-01-two-stage</t>
         </is>
       </c>
       <c r="AD10" s="3" t="inlineStr">
         <is>
-          <t>Il National Institute of Neurological Disorders and Stroke (NINDS), nell'ambito dell'iniziativa NIH HEAL, preannuncia un'opportunità di finanziamento destinata a indagare i meccanismi d'azione dei dispositivi medici terapeutici per ottimizzare i risultati clinici nelle patologie neurologiche e nel trattamento del dolore. La call intende finanziare team scientifici altamente interdisciplinari (con competenze che spaziano dall'ingegneria e biologia alla clinica, biostatistica, intelligenza artificiale e sperimentazioni cliniche). Le attività ammissibili comprendono studi clinici meccanicistici, modelli computazionali o simulazioni e ricerche precliniche su modelli animali, applicabili sia a dispositivi sperimentali sia a tecnologie già approvate dalla FDA e impiegate nella pratica clinica. La partecipazione è aperta anche a istituzioni di ricerca estere non statunitensi.</t>
+          <t>Il bando Horizon Europe finanzia la conduzione di trial clinici in fase precoce per validare interventi sanitari innovativi finalizzati al trattamento e alla gestione clinica di specifiche malattie non trasmissibili: patologie cardiovascolari, diabete, malattie respiratorie croniche o nefropatie croniche. I progetti devono basarsi su una solida prova di concetto preclinica e clinica di sicurezza ed efficacia. Si richiede l'integrazione di tecnologie digitali o indossabili per monitorare a lungo termine i pazienti a domicilio, analisi di dati del mondo reale (RWD) e valutazioni di impatto farmaco-economico. È incoraggiata la partecipazione di piccole e medie imprese, esperti in scienze sociali e umanistiche e organizzazioni dei pazienti.</t>
         </is>
       </c>
       <c r="AE10" s="4" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="AF10" s="4" t="n">
         <v>46312</v>
@@ -1970,93 +1956,89 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>WEB-eb079c6b7229</t>
+          <t>WEB-6768384ca0cb</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Da verificare</t>
+          <t>Sì</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Tecnologia / innovazione</t>
+          <t>Ricerca clinica</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Finanziamenti per le tecnologie assistive nella sclerosi laterale amiotrofica (SLA)</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="n">
-        <v>46329</v>
-      </c>
+          <t>Programma della pipeline di sviluppo terapeutico per la malattia di Parkinson</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="n"/>
       <c r="G11" s="5">
         <f>IF(F11="","",F11-TODAY())</f>
         <v/>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>In scadenza (≤30 gg)</t>
+          <t>Scadenza da verificare</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>ALS Association</t>
+          <t>Michael J. Fox Foundation</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>ALS Association</t>
+          <t>Michael J. Fox Foundation</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>AssistiveTech2026</t>
+          <t>Parkinson's Disease Therapeutics Pipeline Program</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>AssistiveTech2026</t>
+          <t>Parkinson's Disease Therapeutics Pipeline Program</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Tecnologie riabilitazione</t>
+          <t>Parkinson</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>assistive technolog, brain-computer interface, robot, mobility aid, disabilit</t>
+          <t>parkinson</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>Finanzia lo sviluppo e l'adattamento di tecnologie assistive per migliorare l'autonomia e la qualità della vita di persone affette da SLA.</t>
+          <t>Il bando riguarda il morbo di Parkinson, patologia di rilievo riabilitativo, ma è incentrato sullo sviluppo di terapie farmacologiche e sintomatiche e relativi biomarcatori.</t>
         </is>
       </c>
       <c r="P11" s="6" t="n">
-        <v>400000</v>
+        <v>250000</v>
       </c>
       <c r="Q11" s="6" t="n">
-        <v>400000</v>
+        <v>5000000</v>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="S11" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="S11" s="2" t="n"/>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t>Bassa – 1 progetti finanziabili (stima: tasso storico non disponibile)</t>
+          <t>Non stimabile – dati insufficienti</t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
@@ -2067,16 +2049,24 @@
       <c r="V11" s="4" t="n"/>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>24 mesi</t>
+          <t>36 mesi</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
-        </is>
-      </c>
-      <c r="Y11" s="3" t="n"/>
-      <c r="Z11" s="3" t="n"/>
+          <t>Ricerca</t>
+        </is>
+      </c>
+      <c r="Y11" s="3" t="inlineStr">
+        <is>
+          <t>Imprese biotech/pharma, partenariati accademia-industria e istituti accademici</t>
+        </is>
+      </c>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
+          <t>Aperto a collaborazioni accademia-industria, singole aziende o progetti a guida accademica</t>
+        </is>
+      </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
           <t>Mondiale</t>
@@ -2089,26 +2079,26 @@
       </c>
       <c r="AC11" s="7" t="inlineStr">
         <is>
-          <t>http://www.als.org/AssistiveTech2026</t>
+          <t>https://www.michaeljfox.org/grant/parkinsons-disease-therapeutics-pipeline-program</t>
         </is>
       </c>
       <c r="AD11" s="3" t="inlineStr">
         <is>
-          <t>Questo programma di finanziamento promosso dalla ALS Association sostiene la ricerca e lo sviluppo di tecnologie assistive dedicate alle persone affette da sclerosi laterale amiotrofica (SLA). L'obiettivo è accelerare la realizzazione di soluzioni tecnologiche innovative o l'adattamento di ausili esistenti per facilitare la comunicazione, la mobilità, la respirazione e la gestione delle attività della vita quotidiana, migliorando la qualità di vita e l'autonomia dei pazienti e riducendo il carico dei caregiver. Il bando finanzia progetti che abbiano già superato la fase iniziale di scoperta, con l'aspettativa che il dispositivo raggiunga la disponibilità commerciale entro 3-5 anni dal termine dello studio. È richiesta una lettera di intenti preliminare.</t>
+          <t>Il programma Therapeutics Pipeline Program della Michael J. Fox Foundation accelera lo sviluppo di terapie per la malattia di Parkinson, finanziando la produzione di evidenze a supporto di traguardi critici di sviluppo preclinico e clinico. Il bando supporta interventi disease-modifying o sintomatici e l'integrazione di biomarcatori decisionali, escludendo la scoperta di bersagli precoci o integratori alimentari. Il finanziamento varia da 250.000 a oltre 5 milioni di dollari, con una durata di 1-2 anni per studi preclinici e 2-3 anni per programmi clinici. Possono candidarsi imprese, partenariati accademico-industriali e, in casi specifici, enti accademici. La presentazione delle pre-proposte avviene su base continua con scadenze multiple per le proposte complete.</t>
         </is>
       </c>
       <c r="AE11" s="4" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="AF11" s="4" t="n">
-        <v>46317</v>
+        <v>46312</v>
       </c>
       <c r="AG11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>GG-HT942526SCIRPTRA</t>
+          <t>WEB-eb079c6b7229</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -2123,16 +2113,16 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Ricerca clinica</t>
+          <t>Tecnologia / innovazione</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Programma di ricerca sulle lesioni del midollo spinale del Dipartimento della Difesa: finanziamento per la ricerca traslazionale</t>
+          <t>Bandi per tecnologie assistive 2026 per la sclerosi laterale amiotrofica (SLA)</t>
         </is>
       </c>
       <c r="F12" s="4" t="n">
-        <v>46338</v>
+        <v>46329</v>
       </c>
       <c r="G12" s="5">
         <f>IF(F12="","",F12-TODAY())</f>
@@ -2145,83 +2135,79 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Defense Health Agency Contracting Activity - DHACA</t>
+          <t>ALS Association</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>Grants.gov</t>
+          <t>ALS Association</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>Defense Health Agency Contracting Activity - DHACA – HT942526SCIRPTRA</t>
+          <t>AssistiveTech2026</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>DoW Spinal Cord Injury, Translational Research Award</t>
+          <t>AssistiveTech2026</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Altre malattie e riabilitazione</t>
+          <t>Tecnologie riabilitazione</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>spinal cord injur</t>
+          <t>assistive technolog, brain-computer interface, robot, mobility aid, disabilit</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>Dedicato alla ricerca traslazionale per l'applicazione clinica nelle lesioni del midollo spinale, patologia cardine della riabilitazione neurologica.</t>
+          <t>Finanzia lo sviluppo e l'adattamento di tecnologie assistive e ausili per migliorare l'autonomia, il movimento e la respirazione nella SLA.</t>
         </is>
       </c>
       <c r="P12" s="6" t="n">
-        <v>8320000</v>
-      </c>
-      <c r="Q12" s="6" t="n"/>
+        <v>400000</v>
+      </c>
+      <c r="Q12" s="6" t="n">
+        <v>400000</v>
+      </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="S12" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t>Bassa – 4 progetti finanziabili (stima: tasso storico non disponibile)</t>
+          <t>Bassa – 1 progetti finanziabili (stima: tasso storico non disponibile)</t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t>Interamente finanziato</t>
-        </is>
-      </c>
-      <c r="V12" s="4" t="n">
-        <v>46147</v>
-      </c>
-      <c r="W12" s="2" t="n"/>
+          <t>Non indicato</t>
+        </is>
+      </c>
+      <c r="V12" s="4" t="n"/>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>24 mesi</t>
+        </is>
+      </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>Ricerca</t>
-        </is>
-      </c>
-      <c r="Y12" s="3" t="inlineStr">
-        <is>
-          <t>Unrestricted (i.e., open to any type of entity above), subject to any clarification in text field entitled "Additional Information on Eligibility"</t>
-        </is>
-      </c>
-      <c r="Z12" s="3" t="inlineStr">
-        <is>
-          <t>Obbligatorio almeno un partner comunitario esperto per esperienza diretta di lesione midollare; ammessa opzione a due PI con ricercatore junior.</t>
-        </is>
-      </c>
+          <t>Innovazione</t>
+        </is>
+      </c>
+      <c r="Y12" s="3" t="n"/>
+      <c r="Z12" s="3" t="n"/>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>Enti esteri: da verificare nel bando</t>
+          <t>Mondiale</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
@@ -2231,26 +2217,26 @@
       </c>
       <c r="AC12" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/362222</t>
+          <t>http://www.als.org/AssistiveTech2026</t>
         </is>
       </c>
       <c r="AD12" s="3" t="inlineStr">
         <is>
-          <t>Il Translational Research Award, nell'ambito del programma di ricerca sulle lesioni del midollo spinale (SCIRP), sostiene progetti di ricerca traslazionale mirati ad accelerare il passaggio di idee e interventi innovativi dal laboratorio alle applicazioni cliniche per pazienti con lesioni midollari. Le proposte devono includere obbligatoriamente come partner almeno un membro o consulente della comunità con lesione spinale vissuta in prima persona o un rappresentante di organizzazioni attive nel settore. È prevista l'opzione di collaborazione paritaria che consente a un ricercatore esperto di affiancare un ricercatore a inizio carriera nella guida del progetto. Possono partecipare atenei, enti ospedalieri, istituti di ricerca pubblici o privati e organizzazioni specializzate.</t>
+          <t>L'Associazione SLA promuove il programma Assistive Technology Grants per finanziare lo sviluppo di tecnologie innovative e l'adattamento di ausili già esistenti destinati alle persone affette da sclerosi laterale amiotrofica (SLA). L'obiettivo è migliorare l'autonomia, la comunicazione, la mobilità, la respirazione e la qualità di vita dei pazienti e dei loro caregiver, sostenendo soluzioni con elevato potenziale di impatto che possano raggiungere il mercato entro 3-5 anni dal termine del progetto. Possono candidarsi ricercatori e team che propongano progetti successivi alla fase esplorativa, con una solida base scientifica e fattibilità tecnica. Il bando assegna fino a 400.000 dollari per progetti biennali.</t>
         </is>
       </c>
       <c r="AE12" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="AF12" s="4" t="n">
         <v>46317</v>
-      </c>
-      <c r="AF12" s="4" t="n">
-        <v>46313</v>
       </c>
       <c r="AG12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>GG-HT942526SCIRPCTA</t>
+          <t>GG-HT942526SCIRPTRA</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -2270,7 +2256,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>DoW Ricerca sulle lesioni del midollo spinale, finanziamento per trial clinici</t>
+          <t>Programma di ricerca sulle lesioni del midollo spinale del Dipartimento della Difesa: finanziamento per la ricerca traslazionale</t>
         </is>
       </c>
       <c r="F13" s="4" t="n">
@@ -2297,12 +2283,12 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Defense Health Agency Contracting Activity - DHACA – HT942526SCIRPCTA</t>
+          <t>Defense Health Agency Contracting Activity - DHACA – HT942526SCIRPTRA</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>DoW Spinal Cord Injury, Clinical Trial Award</t>
+          <t>DoW Spinal Cord Injury, Translational Research Award</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -2317,11 +2303,11 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>Finanzia trial clinici focalizzati sul trattamento e sulla gestione funzionale delle lesioni del midollo spinale.</t>
+          <t>Dedicato alla ricerca traslazionale per l'applicazione clinica nelle lesioni del midollo spinale, patologia cardine della riabilitazione neurologica.</t>
         </is>
       </c>
       <c r="P13" s="6" t="n">
-        <v>9760000</v>
+        <v>8320000</v>
       </c>
       <c r="Q13" s="6" t="n"/>
       <c r="R13" s="2" t="inlineStr">
@@ -2330,11 +2316,11 @@
         </is>
       </c>
       <c r="S13" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t>Bassa – 2 progetti finanziabili (stima: tasso storico non disponibile)</t>
+          <t>Bassa – 4 progetti finanziabili (stima: tasso storico non disponibile)</t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
@@ -2358,7 +2344,7 @@
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t>Obbligatori almeno 2 partner della comunità con esperienza di lesione midollare; possibile collaborazione tra 2 PI</t>
+          <t>Obbligatorio almeno un partner comunitario esperto per esperienza diretta di lesione midollare; ammessa opzione a due PI con ricercatore junior.</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2373,16 +2359,16 @@
       </c>
       <c r="AC13" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/362224</t>
+          <t>https://www.grants.gov/search-results-detail/362222</t>
         </is>
       </c>
       <c r="AD13" s="3" t="inlineStr">
         <is>
-          <t>Il bando Clinical Trial Award del programma SCIRP (anno fiscale 2026) finanzia la rapida attuazione di studi clinici con un potenziale impatto significativo sul trattamento o sulla gestione delle persone con lesione del midollo spinale. L'opportunità include un'opzione di partenariato per ricercatori all'inizio della carriera (Early-Career Partnership Option), che consente la partecipazione di due Principal Investigator, purché almeno uno sia un ricercatore junior. Le proposte devono obbligatoriamente coinvolgere almeno due rappresentanti o partner della comunità con esperienza diretta di lesione midollare, che collaboreranno attivamente fornendo consulenza durante l'intera pianificazione e implementazione dello studio clinico.</t>
+          <t>Il Translational Research Award, nell'ambito del programma di ricerca sulle lesioni del midollo spinale (SCIRP), sostiene progetti di ricerca traslazionale mirati ad accelerare il passaggio di idee e interventi innovativi dal laboratorio alle applicazioni cliniche per pazienti con lesioni midollari. Le proposte devono includere obbligatoriamente come partner almeno un membro o consulente della comunità con lesione spinale vissuta in prima persona o un rappresentante di organizzazioni attive nel settore. È prevista l'opzione di collaborazione paritaria che consente a un ricercatore esperto di affiancare un ricercatore a inizio carriera nella guida del progetto. Possono partecipare atenei, enti ospedalieri, istituti di ricerca pubblici o privati e organizzazioni specializzate.</t>
         </is>
       </c>
       <c r="AE13" s="4" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="AF13" s="4" t="n">
         <v>46313</v>
@@ -2392,7 +2378,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>GG-HT942526SCIRPCTRA</t>
+          <t>GG-HT942526SCIRPCTA</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -2412,7 +2398,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>DoW Ricerca sulle lesioni del midollo spinale, finanziamento per la ricerca clinica traslazionale</t>
+          <t>DoW Ricerca sulle lesioni del midollo spinale, finanziamento per trial clinici</t>
         </is>
       </c>
       <c r="F14" s="4" t="n">
@@ -2439,12 +2425,12 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>Defense Health Agency Contracting Activity - DHACA – HT942526SCIRPCTRA</t>
+          <t>Defense Health Agency Contracting Activity - DHACA – HT942526SCIRPCTA</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>DoW Spinal Cord Injury, Clinical Translation Research Award</t>
+          <t>DoW Spinal Cord Injury, Clinical Trial Award</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -2454,16 +2440,16 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>rehabilitat, spinal cord injur</t>
+          <t>spinal cord injur</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>Finanzia ricerca clinica traslazionale volta a identificare le opzioni più efficaci di riabilitazione e trattamento nelle lesioni midollari.</t>
+          <t>Finanzia trial clinici focalizzati sul trattamento e sulla gestione funzionale delle lesioni del midollo spinale.</t>
         </is>
       </c>
       <c r="P14" s="6" t="n">
-        <v>6120000</v>
+        <v>9760000</v>
       </c>
       <c r="Q14" s="6" t="n"/>
       <c r="R14" s="2" t="inlineStr">
@@ -2472,11 +2458,11 @@
         </is>
       </c>
       <c r="S14" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t>Bassa – 3 progetti finanziabili (stima: tasso storico non disponibile)</t>
+          <t>Bassa – 2 progetti finanziabili (stima: tasso storico non disponibile)</t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr">
@@ -2500,7 +2486,7 @@
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t>Obbligatori almeno due partner della comunità di pazienti; opzione con due PI di cui uno a inizio carriera</t>
+          <t>Obbligatori almeno 2 partner della comunità con esperienza di lesione midollare; possibile collaborazione tra 2 PI</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2515,26 +2501,26 @@
       </c>
       <c r="AC14" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/362225</t>
+          <t>https://www.grants.gov/search-results-detail/362224</t>
         </is>
       </c>
       <c r="AD14" s="3" t="inlineStr">
         <is>
-          <t>Il bando Clinical Translation Research Award dello SCIRP per l'anno fiscale 2026 promuove ricerche cliniche emergenti o ad alto impatto che necessitano di studi preliminari, di fattibilità o di ottimizzazione per preparare futuri trial clinici definitivi. Tra gli obiettivi principali rientrano l'accelerazione del trasferimento clinico di nuove tecniche o interventi e l'identificazione delle migliori opzioni diagnostiche, terapeutiche e riabilitative per supportare le decisioni di pazienti e clinici nell'ambito delle lesioni del midollo spinale. Il bando include un'opzione per due Principal Investigator (con almeno un ricercatore junior) e impone il coinvolgimento di almeno due partner della comunità di pazienti come consulenti del progetto.</t>
+          <t>Il bando Clinical Trial Award del programma SCIRP (anno fiscale 2026) finanzia la rapida attuazione di studi clinici con un potenziale impatto significativo sul trattamento o sulla gestione delle persone con lesione del midollo spinale. L'opportunità include un'opzione di partenariato per ricercatori all'inizio della carriera (Early-Career Partnership Option), che consente la partecipazione di due Principal Investigator, purché almeno uno sia un ricercatore junior. Le proposte devono obbligatoriamente coinvolgere almeno due rappresentanti o partner della comunità con esperienza diretta di lesione midollare, che collaboreranno attivamente fornendo consulenza durante l'intera pianificazione e implementazione dello studio clinico.</t>
         </is>
       </c>
       <c r="AE14" s="4" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="AF14" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AG14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>GG-HT942526SCIRPIIRA</t>
+          <t>GG-HT942526SCIRPCTRA</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -2554,7 +2540,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>DoW Ricerca sulle lesioni del midollo spinale, finanziamento per la ricerca promossa dal ricercatore</t>
+          <t>Premio per la ricerca di traslazione clinica sulle lesioni del midollo spinale (SCIRP CTRA)</t>
         </is>
       </c>
       <c r="F15" s="4" t="n">
@@ -2581,12 +2567,12 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>Defense Health Agency Contracting Activity - DHACA – HT942526SCIRPIIRA</t>
+          <t>Defense Health Agency Contracting Activity - DHACA – HT942526SCIRPCTRA</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>DoW Spinal Cord Injury, Investigator-Initiated Research Award</t>
+          <t>DoW Spinal Cord Injury, Clinical Translation Research Award</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -2596,16 +2582,16 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>spinal cord injur</t>
+          <t>rehabilitat, spinal cord injur</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>Supporta la ricerca traslazionale e clinica mirata a migliorare l'assistenza e la qualità di vita nelle lesioni midollari.</t>
+          <t>Finanzia studi clinici pilota e di fattibilità mirati a ottimizzare opzioni di trattamento e riabilitazione nelle lesioni del midollo spinale.</t>
         </is>
       </c>
       <c r="P15" s="6" t="n">
-        <v>4960000</v>
+        <v>6120000</v>
       </c>
       <c r="Q15" s="6" t="n"/>
       <c r="R15" s="2" t="inlineStr">
@@ -2614,11 +2600,11 @@
         </is>
       </c>
       <c r="S15" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t>Media – 6 progetti finanziabili (stima: tasso storico non disponibile)</t>
+          <t>Bassa – 3 progetti finanziabili (stima: tasso storico non disponibile)</t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
@@ -2642,7 +2628,7 @@
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t>Opzione per due Principal Investigator (di cui almeno uno a inizio carriera)</t>
+          <t>Obbligatori almeno due partner della comunità di pazienti; opzione con due PI di cui uno a inizio carriera</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2657,26 +2643,26 @@
       </c>
       <c r="AC15" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/362226</t>
+          <t>https://www.grants.gov/search-results-detail/362225</t>
         </is>
       </c>
       <c r="AD15" s="3" t="inlineStr">
         <is>
-          <t>Il bando Investigator-Initiated Research Award (IIRA) per l'anno fiscale 2026, promosso dal programma SCIRP, supporta studi con un impatto rilevante sulla ricerca, sulla cura clinica e sulla qualità della vita delle persone con lesioni del midollo spinale. L'opportunità finanzia progetti che spaziano dalla ricerca fondamentale alle scienze traslazionali, scoraggiando gli studi focalizzati esclusivamente sull'identificazione di bersagli farmacologici o biologici. Il bando contempla una modalità opzionale di partenariato che permette a due Principal Investigator di fare domanda congiunta con premi separati, a condizione che almeno uno dei due sia un ricercatore a inizio carriera.</t>
+          <t>Il bando SCIRP Clinical Translation Research Award, promosso dal Dipartimento della Difesa USA, finanzia progetti di ricerca clinica innovativi o emergenti che richiedono studi preliminari (fattibilità, piloti, ottimizzazione) per preparare trial clinici su larga scala nelle lesioni del midollo spinale. Gli obiettivi primari includono l'accelerazione del trasferimento clinico di interventi promettenti e l'individuazione di efficaci opzioni di diagnosi, trattamento e riabilitazione per migliorare il processo decisionale clinico. È prevista un'opzione di partenariato per ricercatori all'inizio della carriera (Early-Career Partnership) ed è obbligatorio coinvolgere almeno due partner della comunità di persone con lesione midollare a supporto della pianificazione e realizzazione.</t>
         </is>
       </c>
       <c r="AE15" s="4" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="AF15" s="4" t="n">
-        <v>46313</v>
+        <v>46312</v>
       </c>
       <c r="AG15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>GG-RFA-DA-28-011</t>
+          <t>GG-PD-26-369Y</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -2691,29 +2677,27 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Ricerca clinica</t>
+          <t>Tecnologia / innovazione</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Iniziativa HEAL: gestione integrata del dolore cronico e del disturbo da uso di oppioidi (IMPOWR) - Centri di ricerca (RM1)</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="n">
-        <v>46413</v>
-      </c>
+          <t>Ingegneria dei sistemi biologici e biomedici</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="n"/>
       <c r="G16" s="5">
         <f>IF(F16="","",F16-TODAY())</f>
         <v/>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Aperto</t>
+          <t>Scadenza da verificare</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>National Institutes of Health</t>
+          <t>U.S. National Science Foundation</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2723,27 +2707,27 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>National Institutes of Health – RFA-DA-28-011</t>
+          <t>U.S. National Science Foundation – PD-26-369Y</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>HEAL Initiative: Integrative Management of Chronic Pain and OUD for Whole Recovery (IMPOWR): Research Centers (RM1 Clinical Trial Required)</t>
+          <t>Engineering Biological and Biomedical Systems (EBBS)</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Altre malattie e riabilitazione</t>
+          <t>Tecnologie riabilitazione, Altre malattie e riabilitazione</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>chronic pain</t>
+          <t>rehabilitation engineering, rehabilitat, persons with disabilities</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>È dedicato alla gestione integrata a lungo termine del dolore cronico e al recupero funzionale dei pazienti.</t>
+          <t>Il testo descrive un programma di ricerca permanente e le sue linee generali senza indicare una call aperta con scadenze o budget.</t>
         </is>
       </c>
       <c r="P16" s="6" t="n"/>
@@ -2765,7 +2749,7 @@
         </is>
       </c>
       <c r="V16" s="4" t="n">
-        <v>46301</v>
+        <v>46136</v>
       </c>
       <c r="W16" s="2" t="n"/>
       <c r="X16" s="2" t="inlineStr">
@@ -2775,7 +2759,7 @@
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t>Native American tribal organizations (other than Federally recognized tribal governments); City or township governments; For profit organizations other than small businesses; Small businesses; Independent school districts; Nonprofits that do not have a 501(c)(3) status with the IRS, other than institutions of higher education; State governments; Nonprofits having a 501(c)(3) status with the IRS, o</t>
+          <t>Unrestricted (i.e., open to any type of entity above), subject to any clarification in text field entitled "Additional Information on Eligibility"</t>
         </is>
       </c>
       <c r="Z16" s="3" t="n"/>
@@ -2791,26 +2775,26 @@
       </c>
       <c r="AC16" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/360048</t>
+          <t>https://www.grants.gov/search-results-detail/362062</t>
         </is>
       </c>
       <c r="AD16" s="3" t="inlineStr">
         <is>
-          <t>L'avviso anticipa il rinnovo della rete di ricerca IMPOWR, parte dell'iniziativa NIH HEAL, finalizzata allo sviluppo e alla validazione di modelli integrati per la gestione del dolore cronico e del disturbo da uso di oppioidi. Il network comprenderà molteplici progetti di ricerca coordinati da un centro centrale, con l'obiettivo di condurre studi clinici per testare approcci assistenziali innovativi in grado di migliorare significativamente l'erogazione delle cure nei sistemi sanitari. Possono partecipare istituzioni universitarie, ospedaliere, enti di ricerca no-profit o profit e organizzazioni estere non statunitensi.</t>
+          <t>Il programma sostiene la comprensione e il miglioramento dei sistemi biologici e fisiologici per la salute umana attraverso l'ingegneria, combinando intuizioni meccanicistiche con tecniche sperimentali e computazionali. Si finanziano piattaforme, dispositivi, tessuti e processi per ripristinare le funzioni corporee, inclusi progetti che fanno avanzare l'ingegneria riabilitativa tramite nuove teorie e approcci. Il programma è rivolto a ricercatori e accademici per studi fondamentali e di ingegneria tissutale o biosensori. Non sono supportati trial clinici o progetti focalizzati sulla commercializzazione o sullo sviluppo di farmaci.</t>
         </is>
       </c>
       <c r="AE16" s="4" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="AF16" s="4" t="n">
-        <v>46313</v>
+        <v>46312</v>
       </c>
       <c r="AG16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>GG-PAR-27-065</t>
+          <t>GG-FOR-FD-25-006</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -2830,24 +2814,22 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Trial clinici esplorativi e di efficacia del NINDS (UG3/UH3 - Clinical Trial obbligatorio)</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="n">
-        <v>47186</v>
-      </c>
+          <t>Studi sulle malattie neurodegenerative rare inclusa la SLA</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="n"/>
       <c r="G17" s="5">
         <f>IF(F17="","",F17-TODAY())</f>
         <v/>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Aperto</t>
+          <t>In apertura</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>National Institutes of Health</t>
+          <t>Food and Drug Administration</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2857,27 +2839,27 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>National Institutes of Health – PAR-27-065</t>
+          <t>Food and Drug Administration – FOR-FD-25-006</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>NINDS Efficacy and Exploratory Clinical Trials (UG3/UH3 - Clinical Trial Required)</t>
+          <t>Studies Addressing Rare Neurodegenerative Diseases including ALS</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Ictus, Altre malattie e riabilitazione</t>
+          <t>Altre malattie e riabilitazione</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>stroke, rehabilitat, neurological disorder</t>
+          <t>neurodegenerat</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>Finanzia trial clinici neurologici e ammette esplicitamente terapie e interventi di riabilitazione lungo tutto l'arco della vita.</t>
+          <t>Il bando finanzia studi sulla SLA e altre malattie neurodegenerative rare, ma non specifica se l'Italia sia ammessa.</t>
         </is>
       </c>
       <c r="P17" s="6" t="n"/>
@@ -2887,10 +2869,12 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="S17" s="2" t="n"/>
+      <c r="S17" s="2" t="n">
+        <v>10</v>
+      </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t>Non stimabile – dati insufficienti</t>
+          <t>Media – 10 progetti finanziabili (stima: tasso storico non disponibile)</t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
@@ -2899,7 +2883,7 @@
         </is>
       </c>
       <c r="V17" s="4" t="n">
-        <v>46265</v>
+        <v>45518</v>
       </c>
       <c r="W17" s="2" t="n"/>
       <c r="X17" s="2" t="inlineStr">
@@ -2909,14 +2893,10 @@
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t>Special district governments; Public housing authorities/Indian housing authorities; Nonprofits that do not have a 501(c)(3) status with the IRS, other than institutions of higher education; Private institutions of higher education; Native American tribal governments (Federally recognized); Nonprofits having a 501(c)(3) status with the IRS, other than institutions of higher education; Public and S</t>
-        </is>
-      </c>
-      <c r="Z17" s="3" t="inlineStr">
-        <is>
-          <t>Non sono ammessi sub-accordi o subappalti a entità estere; le organizzazioni estere possono candidarsi direttamente come capofila</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Unrestricted (i.e., open to any type of entity above), subject to any clarification in text field entitled "Additional Information on Eligibility"; County governments; Independent school districts; Small businesses; Nonprofits that do not have a 501(c)(3) status with the IRS, other than institutions of higher education; Nonprofits having a 501(c)(3) status with the IRS, other than institutions of </t>
+        </is>
+      </c>
+      <c r="Z17" s="3" t="n"/>
       <c r="AA17" s="2" t="inlineStr">
         <is>
           <t>Enti esteri: da verificare nel bando</t>
@@ -2929,16 +2909,16 @@
       </c>
       <c r="AC17" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/360404</t>
+          <t>https://www.grants.gov/search-results-detail/356046</t>
         </is>
       </c>
       <c r="AD17" s="3" t="inlineStr">
         <is>
-          <t>Questa opportunità di finanziamento (UG3/UH3) promossa dal National Institute of Neurological Disorders and Stroke (NINDS) sostiene trial clinici proposti da ricercatori per affrontare quesiti coerenti con la missione dell'istituto. Il bando finanzia sperimentazioni cliniche precoci, intermedie o confermative di fase 3 e studi di efficacia comparativa su molecole, farmaci biologici, dispositivi medici o interventi chirurgici, comportamentali, dietetici e terapie riabilitative, per tutte le età. Possono partecipare enti accademici, ospedalieri e organizzazioni di ricerca, incluse entità straniere non statunitensi come capofila. Non sono tuttavia consentiti subappalti o sub-accordi finanziari internazionali verso altre entità estere nell'ambito dello stesso progetto.</t>
+          <t>Lo scopo di questa opportunità di finanziamento è sostenere studi che promuovono lo sviluppo di prodotti medici, interventi di prevenzione, diagnosi, attenuazione, trattamento o cura della SLA e di altre malattie neurodegenerative rare in adulti e bambini. Attraverso questi studi si punta a colmare lacune conoscitive critiche e a indirizzare lo sviluppo attuale e futuro di prodotti terapeutici. Possono candidarsi ricercatori e organizzazioni qualificate nella ricerca clinica o biomedica. Il bando finanzia attività di ricerca e sviluppo finalizzate a interventi terapeutici per patologie neurodegenerative rare.</t>
         </is>
       </c>
       <c r="AE17" s="4" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="AF17" s="4" t="n">
         <v>46312</v>
@@ -2948,7 +2928,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>GG-PD-26-369Y</t>
+          <t>GG-HT942526PRPEIRA</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -2958,32 +2938,34 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Tecnologia / innovazione</t>
+          <t>Formazione / fellowship</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Ingegneria dei sistemi biologici e biomedici (EBBS)</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="n"/>
+          <t>Programma di ricerca sul Parkinson - Finanziamento per giovani ricercatori (EIRA)</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>46332</v>
+      </c>
       <c r="G18" s="5">
         <f>IF(F18="","",F18-TODAY())</f>
         <v/>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Scadenza da verificare</t>
+          <t>In scadenza (≤30 gg)</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>U.S. National Science Foundation</t>
+          <t>Defense Health Agency Contracting Activity - DHACA</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2993,40 +2975,44 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>U.S. National Science Foundation – PD-26-369Y</t>
+          <t>Defense Health Agency Contracting Activity - DHACA – HT942526PRPEIRA</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>Engineering Biological and Biomedical Systems (EBBS)</t>
+          <t>DoW Parkinson’s, Early Investigator Research Award</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Tecnologie riabilitazione, Altre malattie e riabilitazione</t>
+          <t>Parkinson</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>rehabilitation engineering, rehabilitat, persons with disabilities</t>
+          <t>parkinson</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>Supporta esplicitamente la ricerca fondamentale in ingegneria della riabilitazione e tecnologie per il ripristino delle funzioni e la disabilità.</t>
-        </is>
-      </c>
-      <c r="P18" s="6" t="n"/>
+          <t>Finanzia la ricerca sulla malattia di Parkinson per ricercatori a inizio carriera, ma esclude esplicitamente i trial clinici.</t>
+        </is>
+      </c>
+      <c r="P18" s="6" t="n">
+        <v>4200000</v>
+      </c>
       <c r="Q18" s="6" t="n"/>
       <c r="R18" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="S18" s="2" t="n"/>
+      <c r="S18" s="2" t="n">
+        <v>7</v>
+      </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t>Non stimabile – dati insufficienti</t>
+          <t>Media – 7 progetti finanziabili (stima: tasso storico non disponibile)</t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
@@ -3035,12 +3021,12 @@
         </is>
       </c>
       <c r="V18" s="4" t="n">
-        <v>46136</v>
+        <v>46191</v>
       </c>
       <c r="W18" s="2" t="n"/>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>Ricerca</t>
+          <t>Dottorato / formazione / mobilità</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
@@ -3048,7 +3034,11 @@
           <t>Unrestricted (i.e., open to any type of entity above), subject to any clarification in text field entitled "Additional Information on Eligibility"</t>
         </is>
       </c>
-      <c r="Z18" s="3" t="n"/>
+      <c r="Z18" s="3" t="inlineStr">
+        <is>
+          <t>Per il Livello 1 è obbligatoria la designazione di almeno un mentore con esperienza documentata nella ricerca su Parkinson.</t>
+        </is>
+      </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
           <t>Enti esteri: da verificare nel bando</t>
@@ -3061,16 +3051,16 @@
       </c>
       <c r="AC18" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/362062</t>
+          <t>https://www.grants.gov/search-results-detail/362866</t>
         </is>
       </c>
       <c r="AD18" s="3" t="inlineStr">
         <is>
-          <t>Il programma Engineering Biological and Biomedical Systems (EBBS) della National Science Foundation statunitense sostiene progetti di ricerca ingegneristica fondamentale volti a comprendere e controllare i sistemi biologici e fisiologici per migliorare la salute umana. L'iniziativa finanzia in particolare lo sviluppo di piattaforme di biosensing, metodologie di imaging ottico, sistemi per imitare o ripristinare le funzioni di tessuti e organi, nonché progetti innovativi di ingegneria della riabilitazione guidati dalle esigenze delle persone con disabilità. Non sono supportati trial clinici né progetti dedicati unicamente alla progettazione di farmaci o alla commercializzazione immediata. Il bando incoraggia approcci interdisciplinari e collaborazioni, ma non specifica restrizioni geografiche per la candidatura diretta.</t>
+          <t>Il programma di ricerca sul Parkinson del Dipartimento della Difesa statunitense (DoD PRP) promuove l'Early Investigator Research Award (EIRA) per sostenere scienziati nelle prime fasi della loro carriera dedicati allo studio della malattia di Parkinson. Il bando prevede due livelli di finanziamento: il Livello 1 è riservato a borsisti/fellow e richiede la presenza obbligatoria di un mentore esperto nella patologia, mentre il Livello 2 si rivolge a ricercatori indipendenti di inizio carriera e richiede dati preliminari. Le proposte devono allinearsi alle aree prioritarie del programma e non possono includere sperimentazioni cliniche (trial clinici non ammessi).</t>
         </is>
       </c>
       <c r="AE18" s="4" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="AF18" s="4" t="n">
         <v>46312</v>
@@ -3080,7 +3070,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>GG-HT942526PRPEIRA</t>
+          <t>GG-HT942526PRPIIRA</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -3095,12 +3085,12 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Formazione / fellowship</t>
+          <t>Ricerca clinica</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Programma di ricerca sul Parkinson del Dipartimento della Difesa: bando per ricercatori a inizio carriera</t>
+          <t>Programma di ricerca sul Parkinson del Dipartimento della Difesa: bando di ricerca promosso dal ricercatore</t>
         </is>
       </c>
       <c r="F19" s="4" t="n">
@@ -3127,12 +3117,12 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>Defense Health Agency Contracting Activity - DHACA – HT942526PRPEIRA</t>
+          <t>Defense Health Agency Contracting Activity - DHACA – HT942526PRPIIRA</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>DoW Parkinson’s, Early Investigator Research Award</t>
+          <t>DoW Parkinson’s, Investigator-Initiated Research Award</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -3147,11 +3137,11 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>Finanzia la ricerca sul morbo di Parkinson per ricercatori a inizio carriera, ma esclude i trial clinici e non è mirato alla riabilitazione.</t>
+          <t>Bando dedicato alla malattia di Parkinson che ammette trial clinici, pur senza essere focalizzato specificamente sulla riabilitazione.</t>
         </is>
       </c>
       <c r="P19" s="6" t="n">
-        <v>4200000</v>
+        <v>10000000</v>
       </c>
       <c r="Q19" s="6" t="n"/>
       <c r="R19" s="2" t="inlineStr">
@@ -3160,11 +3150,11 @@
         </is>
       </c>
       <c r="S19" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t>Media – 7 progetti finanziabili (stima: tasso storico non disponibile)</t>
+          <t>Media – 5 progetti finanziabili (stima: tasso storico non disponibile)</t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
@@ -3178,7 +3168,7 @@
       <c r="W19" s="2" t="n"/>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>Dottorato / formazione / mobilità</t>
+          <t>Ricerca</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
@@ -3188,7 +3178,7 @@
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t>Per il Livello 1 è obbligatoria la designazione di almeno un mentore con esperienza documentata nella ricerca su Parkinson.</t>
+          <t>Possibilità di consorzio con un Initiating PI e fino a due Partnering PI multidisciplinari.</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -3203,16 +3193,16 @@
       </c>
       <c r="AC19" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/362866</t>
+          <t>https://www.grants.gov/search-results-detail/362868</t>
         </is>
       </c>
       <c r="AD19" s="3" t="inlineStr">
         <is>
-          <t>Il bando Early Investigator Research Award, promosso nell'ambito del Parkinson’s Research Program dell'agenzia di difesa statunitense, sostiene la formazione e l'avvio di carriera di ricercatori promettenti dedicati alla ricerca sulla malattia di Parkinson. L'iniziativa prevede due livelli: il primo è destinato a borsisti o assegnisti (fellows) e richiede l'affiancamento obbligatorio di un mentore esperto per garantire un solido percorso verso l'indipendenza scientifica; il secondo è rivolto a ricercatori indipendenti junior e richiede dati preliminari comprovati. Le ricerche proposte devono rientrare nelle aree prioritarie del programma e non possono includere sperimentazioni cliniche. Possono candidarsi ricercatori a inizio carriera sostenuti dalle proprie organizzazioni di ricerca o accademiche.</t>
+          <t>L'Investigator-Initiated Research Award, gestito dal programma di ricerca sul Parkinson (PRP), mira a finanziare progetti di ricerca rigorosi, multidisciplinari e ad alto impatto con un rilevante potenziale innovativo nella lotta al morbo di Parkinson. Le proposte devono concentrarsi su una delle aree prioritarie stabilite per l'anno fiscale 2026 e devono essere obbligatoriamente supportate da solidi dati preliminari. A differenza di altre linee di finanziamento, questo bando consente esplicitamente la conduzione di studi clinici. È inoltre prevista un'opzione di partenariato che permette la collaborazione formale tra un ricercatore principale capofila e fino a due Principal Investigator partner. Possono candidarsi istituti universitari, centri di ricerca e organizzazioni cliniche qualificate.</t>
         </is>
       </c>
       <c r="AE19" s="4" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="AF19" s="4" t="n">
         <v>46312</v>
@@ -3222,7 +3212,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>GG-HT942526PRPIIRA</t>
+          <t>GG-PAR-27-007</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -3242,11 +3232,11 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Programma di ricerca sul Parkinson del Dipartimento della Difesa: bando di ricerca promosso dal ricercatore</t>
+          <t>Trial clinici e studi ancillari condotti all'interno delle reti di ricerca clinica finanziate dal NIH (UG3/UH3)</t>
         </is>
       </c>
       <c r="F20" s="4" t="n">
-        <v>46332</v>
+        <v>46336</v>
       </c>
       <c r="G20" s="5">
         <f>IF(F20="","",F20-TODAY())</f>
@@ -3259,7 +3249,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Defense Health Agency Contracting Activity - DHACA</t>
+          <t>National Institutes of Health</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -3269,44 +3259,40 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>Defense Health Agency Contracting Activity - DHACA – HT942526PRPIIRA</t>
+          <t>National Institutes of Health – PAR-27-007</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>DoW Parkinson’s, Investigator-Initiated Research Award</t>
+          <t>Clinical Trials and Ancillary Studies Conducted within NIH-Funded Clinical Trial Research Networks (UG3/UH3 - Clinical Trial Required)</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Parkinson</t>
+          <t>Ictus, Altre malattie e riabilitazione</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>parkinson</t>
+          <t>stroke, neurological disorder</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>Bando dedicato alla malattia di Parkinson che ammette trial clinici, pur senza essere focalizzato specificamente sulla riabilitazione.</t>
-        </is>
-      </c>
-      <c r="P20" s="6" t="n">
-        <v>10000000</v>
-      </c>
+          <t>Finanzia trial clinici in reti neurologiche che possono comprendere patologie di interesse riabilitativo come l'ictus, pur non focalizzandosi sulla riabilitazione.</t>
+        </is>
+      </c>
+      <c r="P20" s="6" t="n"/>
       <c r="Q20" s="6" t="n"/>
       <c r="R20" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="S20" s="2" t="n">
-        <v>5</v>
-      </c>
+      <c r="S20" s="2" t="n"/>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t>Media – 5 progetti finanziabili (stima: tasso storico non disponibile)</t>
+          <t>Non stimabile – dati insufficienti</t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
@@ -3315,9 +3301,13 @@
         </is>
       </c>
       <c r="V20" s="4" t="n">
-        <v>46191</v>
-      </c>
-      <c r="W20" s="2" t="n"/>
+        <v>46097</v>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>84 mesi</t>
+        </is>
+      </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
           <t>Ricerca</t>
@@ -3325,14 +3315,10 @@
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t>Unrestricted (i.e., open to any type of entity above), subject to any clarification in text field entitled "Additional Information on Eligibility"</t>
-        </is>
-      </c>
-      <c r="Z20" s="3" t="inlineStr">
-        <is>
-          <t>Possibilità di consorzio con un Initiating PI e fino a due Partnering PI multidisciplinari.</t>
-        </is>
-      </c>
+          <t>City or township governments; Independent school districts; Private institutions of higher education; Special district governments; Others (see text field entitled "Additional Information on Eligibility" for clarification); Native American tribal organizations (other than Federally recognized tribal governments); Small businesses; Public and State controlled institutions of higher education; Count</t>
+        </is>
+      </c>
+      <c r="Z20" s="3" t="n"/>
       <c r="AA20" s="2" t="inlineStr">
         <is>
           <t>Enti esteri: da verificare nel bando</t>
@@ -3345,16 +3331,16 @@
       </c>
       <c r="AC20" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/362868</t>
+          <t>https://www.grants.gov/search-results-detail/361522</t>
         </is>
       </c>
       <c r="AD20" s="3" t="inlineStr">
         <is>
-          <t>L'Investigator-Initiated Research Award, gestito dal programma di ricerca sul Parkinson (PRP), mira a finanziare progetti di ricerca rigorosi, multidisciplinari e ad alto impatto con un rilevante potenziale innovativo nella lotta al morbo di Parkinson. Le proposte devono concentrarsi su una delle aree prioritarie stabilite per l'anno fiscale 2026 e devono essere obbligatoriamente supportate da solidi dati preliminari. A differenza di altre linee di finanziamento, questo bando consente esplicitamente la conduzione di studi clinici. È inoltre prevista un'opzione di partenariato che permette la collaborazione formale tra un ricercatore principale capofila e fino a due Principal Investigator partner. Possono candidarsi istituti universitari, centri di ricerca e organizzazioni cliniche qualificate.</t>
+          <t>Il bando, promosso dal NINDS insieme ad altri istituti del NIH tramite lo schema cooperativo a due fasi UG3/UH3, intende sostenere la conduzione di studi clinici multicentrici e studi ancillari all'interno delle reti di ricerca clinica già finanziate e attive del NIH. Il programma prevede una fase iniziale di pianificazione e avvio fino a due anni (UG3), con possibile passaggio a una fase operativa fino a ulteriori cinque anni (UH3) al raggiungimento di specifici traguardi. Possono candidarsi enti di ricerca, università, organizzazioni pubbliche o private ed enti stranieri non statunitensi per testare interventi diagnostici e terapeutici in ambito neurologico.</t>
         </is>
       </c>
       <c r="AE20" s="4" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="AF20" s="4" t="n">
         <v>46312</v>
@@ -3364,7 +3350,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>GG-PAR-27-007</t>
+          <t>GG-RFA-TS-27-018</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -3384,11 +3370,11 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Trial clinici e studi ancillari condotti all'interno delle reti di ricerca clinica finanziate dal NIH (UG3/UH3)</t>
+          <t>Identificazione e valutazione dei potenziali fattori di rischio per la sclerosi laterale amiotrofica (SLA)</t>
         </is>
       </c>
       <c r="F21" s="4" t="n">
-        <v>46336</v>
+        <v>46357</v>
       </c>
       <c r="G21" s="5">
         <f>IF(F21="","",F21-TODAY())</f>
@@ -3396,12 +3382,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>In scadenza (≤30 gg)</t>
+          <t>Aperto</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>National Institutes of Health</t>
+          <t>Centers for Disease Control and Prevention - ERA</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -3411,40 +3397,46 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>National Institutes of Health – PAR-27-007</t>
+          <t>Centers for Disease Control and Prevention - ERA – RFA-TS-27-018</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>Clinical Trials and Ancillary Studies Conducted within NIH-Funded Clinical Trial Research Networks (UG3/UH3 - Clinical Trial Required)</t>
+          <t>Identify and Evaluate Potential Risk Factors for Amyotrophic Lateral Sclerosis (ALS)</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Ictus, Altre malattie e riabilitazione</t>
+          <t>Altre malattie e riabilitazione</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>stroke, neurological disorder</t>
+          <t>amyotrophic lateral sclerosis, traumatic brain injur</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>Finanzia trial clinici in reti neurologiche che possono comprendere patologie di interesse riabilitativo come l'ictus, pur non focalizzandosi sulla riabilitazione.</t>
-        </is>
-      </c>
-      <c r="P21" s="6" t="n"/>
-      <c r="Q21" s="6" t="n"/>
+          <t>Focalizzato sui fattori di rischio e sull'eziologia della sclerosi laterale amiotrofica (SLA) piuttosto che sulla riabilitazione.</t>
+        </is>
+      </c>
+      <c r="P21" s="6" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="Q21" s="6" t="n">
+        <v>500000</v>
+      </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="S21" s="2" t="n"/>
+      <c r="S21" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t>Non stimabile – dati insufficienti</t>
+          <t>Bassa – 3 progetti finanziabili (stima: tasso storico non disponibile)</t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
@@ -3453,13 +3445,9 @@
         </is>
       </c>
       <c r="V21" s="4" t="n">
-        <v>46097</v>
-      </c>
-      <c r="W21" s="2" t="inlineStr">
-        <is>
-          <t>84 mesi</t>
-        </is>
-      </c>
+        <v>46211</v>
+      </c>
+      <c r="W21" s="2" t="n"/>
       <c r="X21" s="2" t="inlineStr">
         <is>
           <t>Ricerca</t>
@@ -3467,7 +3455,7 @@
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t>Independent school districts; Special district governments; Public and State controlled institutions of higher education; State governments; Public housing authorities/Indian housing authorities; For profit organizations other than small businesses; Native American tribal governments (Federally recognized); Small businesses; Native American tribal organizations (other than Federally recognized tri</t>
+          <t>Native American tribal organizations (other than Federally recognized tribal governments); Nonprofits that do not have a 501(c)(3) status with the IRS, other than institutions of higher education; Private institutions of higher education; State governments; Native American tribal governments (Federally recognized); Unrestricted (i.e., open to any type of entity above), subject to any clarification</t>
         </is>
       </c>
       <c r="Z21" s="3" t="n"/>
@@ -3483,16 +3471,16 @@
       </c>
       <c r="AC21" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/361522</t>
+          <t>https://www.grants.gov/search-results-detail/363115</t>
         </is>
       </c>
       <c r="AD21" s="3" t="inlineStr">
         <is>
-          <t>Il bando, promosso dal NINDS insieme ad altri istituti del NIH tramite lo schema cooperativo a due fasi UG3/UH3, intende sostenere la conduzione di studi clinici multicentrici e studi ancillari all'interno delle reti di ricerca clinica già finanziate e attive del NIH. Il programma prevede una fase iniziale di pianificazione e avvio fino a due anni (UG3), con possibile passaggio a una fase operativa fino a ulteriori cinque anni (UH3) al raggiungimento di specifici traguardi. Possono candidarsi enti di ricerca, università, organizzazioni pubbliche o private ed enti stranieri non statunitensi per testare interventi diagnostici e terapeutici in ambito neurologico.</t>
+          <t>Il bando promosso da CDC e ATSDR finanzia progetti di ricerca volti a identificare e valutare i fattori di rischio ambientali, occupazionali e genetici per la sclerosi laterale amiotrofica (SLA). Sono incoraggiati studi su servizio militare, sport di contatto, lesioni cerebrali traumatiche e neuroinfiammazione. Il programma prevede quattro opzioni di finanziamento che supportano ricerche su fattori con prove consolidate, studi esplorativi e innovativi, valutazioni in popolazioni specifiche come i veterani militari e analisi di campioni biologici provenienti dal cluster di SLA di Guam per chiarire meccanismi patologici e biomarker. I criteri di ammissibilità completi saranno dettagliati nel testo integrale del bando.</t>
         </is>
       </c>
       <c r="AE21" s="4" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="AF21" s="4" t="n">
         <v>46312</v>
@@ -3502,7 +3490,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>GG-RFA-TS-27-018</t>
+          <t>GG-FOR-FD-25-001</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -3522,24 +3510,22 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Identificazione e valutazione dei potenziali fattori di rischio per la sclerosi laterale amiotrofica (SLA)</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="n">
-        <v>46357</v>
-      </c>
+          <t>Trial clinici per le esigenze non soddisfatte nelle malattie neurodegenerative rare</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="n"/>
       <c r="G22" s="5">
         <f>IF(F22="","",F22-TODAY())</f>
         <v/>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Aperto</t>
+          <t>In apertura</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Centers for Disease Control and Prevention - ERA</t>
+          <t>Food and Drug Administration</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -3549,12 +3535,12 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>Centers for Disease Control and Prevention - ERA – RFA-TS-27-018</t>
+          <t>Food and Drug Administration – FOR-FD-25-001</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>Identify and Evaluate Potential Risk Factors for Amyotrophic Lateral Sclerosis (ALS)</t>
+          <t>Clinical Trials Addressing Unmet Needs of Rare Neurodegenerative Diseases (R01) Clinical Trials Required</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -3564,31 +3550,27 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>amyotrophic lateral sclerosis, traumatic brain injur</t>
+          <t>neurodegenerat</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>Riguarda la sclerosi laterale amiotrofica (SLA) ma è incentrato sullo studio dei fattori di rischio eziologici e non sulla riabilitazione.</t>
-        </is>
-      </c>
-      <c r="P22" s="6" t="n">
-        <v>4500000</v>
-      </c>
+          <t>Il bando finanzia trial clinici per malattie neurodegenerative rare, ma non fornisce informazioni sull'ammissibilità dell'Italia.</t>
+        </is>
+      </c>
+      <c r="P22" s="6" t="n"/>
       <c r="Q22" s="6" t="n">
-        <v>500000</v>
+        <v>900000</v>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="S22" s="2" t="n">
-        <v>3</v>
-      </c>
+      <c r="S22" s="2" t="n"/>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t>Bassa – 3 progetti finanziabili (stima: tasso storico non disponibile)</t>
+          <t>Non stimabile – dati insufficienti</t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
@@ -3597,7 +3579,7 @@
         </is>
       </c>
       <c r="V22" s="4" t="n">
-        <v>46211</v>
+        <v>45518</v>
       </c>
       <c r="W22" s="2" t="n"/>
       <c r="X22" s="2" t="inlineStr">
@@ -3607,7 +3589,7 @@
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t>Independent school districts; Nonprofits that do not have a 501(c)(3) status with the IRS, other than institutions of higher education; Private institutions of higher education; City or township governments; Public housing authorities/Indian housing authorities; Nonprofits having a 501(c)(3) status with the IRS, other than institutions of higher education; State governments; Public and State contr</t>
+          <t>Nonprofits having a 501(c)(3) status with the IRS, other than institutions of higher education; Public and State controlled institutions of higher education; Unrestricted (i.e., open to any type of entity above), subject to any clarification in text field entitled "Additional Information on Eligibility"; Independent school districts; Native American tribal organizations (other than Federally recog</t>
         </is>
       </c>
       <c r="Z22" s="3" t="n"/>
@@ -3623,16 +3605,16 @@
       </c>
       <c r="AC22" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/363115</t>
+          <t>https://www.grants.gov/search-results-detail/356054</t>
         </is>
       </c>
       <c r="AD22" s="3" t="inlineStr">
         <is>
-          <t>Il CDC e l'ATSDR finanziano progetti di ricerca dedicati all'identificazione e alla valutazione dei fattori di rischio per la sclerosi laterale amiotrofica (SLA), incoraggiando studi su servizio militare, sport di contatto, traumi cranici, neuroinfiammazione ed esposizioni ad agenti infettivi o ambientali. Il bando prevede quattro opzioni tematiche: ricerca supportata da evidenze consolidate e legami tra fattori di rischio, diagnosi e cura; studi esplorativi e innovativi su nuovi fattori; analisi del rischio in popolazioni specifiche, come i veterani militari; studio di campioni biologici del cluster di Guam per chiarire i meccanismi patologici, biomarcatori e approcci di prevenzione.</t>
+          <t>L'obiettivo del bando è finanziare trial clinici di prodotti che valutano l'efficacia e/o la sicurezza a supporto di nuove indicazioni o etichettature per soddisfare bisogni non soddisfatti in pazienti pediatrici e adulti affetti da malattie neurodegenerative rare. Tramite il supporto a studi clinici collaborativi, efficienti e innovativi, l'ente finanziatore intende aumentare il numero di trattamenti approvati e avere un impatto positivo sullo sviluppo di farmaci per malattie rare. Possono partecipare enti di ricerca idonei a condurre trial clinici su tali patologie. Il finanziamento sostiene la conduzione di studi clinici mirati.</t>
         </is>
       </c>
       <c r="AE22" s="4" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="AF22" s="4" t="n">
         <v>46312</v>
@@ -3642,17 +3624,17 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>GG-FOR-FD-25-001</t>
+          <t>GG-PAR-25-052</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Da verificare</t>
+          <t>No</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -3662,22 +3644,24 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Trial clinici per i bisogni insoddisfatti nelle malattie neurodegenerative rare (R01 - Clinical Trial obbligatorio)</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="n"/>
+          <t>Trial clinici e studi su biomarcatori NIH StrokeNet per trattamento, recupero e prevenzione dell'ictus (UG3/UH3)</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>46345</v>
+      </c>
       <c r="G23" s="5">
         <f>IF(F23="","",F23-TODAY())</f>
         <v/>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>In apertura</t>
+          <t>In scadenza (≤30 gg)</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Food and Drug Administration</t>
+          <t>National Institutes of Health</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -3687,33 +3671,31 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>Food and Drug Administration – FOR-FD-25-001</t>
+          <t>National Institutes of Health – PAR-25-052</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>Clinical Trials Addressing Unmet Needs of Rare Neurodegenerative Diseases (R01) Clinical Trials Required</t>
+          <t>NIH StrokeNet Clinical Trials and Biomarker Studies for Stroke Treatment, Recovery, and Prevention (UG3/UH3 Clinical Trial Optional)</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>Altre malattie e riabilitazione</t>
+          <t>Ictus</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>neurodegenerat</t>
+          <t>stroke</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>Riguarda le malattie neurodegenerative rare, ma è finalizzato a trial clinici regolatori per l'approvazione o rietichettatura di farmaci.</t>
+          <t>Bando dedicato a trial clinici e studi di biomarcatori per il trattamento, la prevenzione e il recupero nell'ictus all'interno della rete StrokeNet.</t>
         </is>
       </c>
       <c r="P23" s="6" t="n"/>
-      <c r="Q23" s="6" t="n">
-        <v>900000</v>
-      </c>
+      <c r="Q23" s="6" t="n"/>
       <c r="R23" s="2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3731,7 +3713,7 @@
         </is>
       </c>
       <c r="V23" s="4" t="n">
-        <v>45518</v>
+        <v>45616</v>
       </c>
       <c r="W23" s="2" t="n"/>
       <c r="X23" s="2" t="inlineStr">
@@ -3741,13 +3723,17 @@
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t>Independent school districts; State governments; Public and State controlled institutions of higher education; City or township governments; Private institutions of higher education; Public housing authorities/Indian housing authorities; Native American tribal organizations (other than Federally recognized tribal governments); Nonprofits that do not have a 501(c)(3) status with the IRS, other than</t>
-        </is>
-      </c>
-      <c r="Z23" s="3" t="n"/>
+          <t>City or township governments; Public housing authorities/Indian housing authorities; For profit organizations other than small businesses; Nonprofits having a 501(c)(3) status with the IRS, other than institutions of higher education; Independent school districts; State governments; County governments; Native American tribal organizations (other than Federally recognized tribal governments); Priva</t>
+        </is>
+      </c>
+      <c r="Z23" s="3" t="inlineStr">
+        <is>
+          <t>Collaborazione obbligatoria all'interno della rete NIH StrokeNet con il National Coordinating Center e i siti clinici affiliati.</t>
+        </is>
+      </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>Enti esteri: da verificare nel bando</t>
+          <t>Enti esteri non ammessi (call NIH completa)</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
@@ -3757,61 +3743,63 @@
       </c>
       <c r="AC23" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/356054</t>
+          <t>https://www.grants.gov/search-results-detail/357256</t>
         </is>
       </c>
       <c r="AD23" s="3" t="inlineStr">
         <is>
-          <t>Questo bando promosso dalla Food and Drug Administration (FDA) tramite il meccanismo R01 è destinato a finanziare trial clinici dedicati a rispondere ai bisogni insoddisfatti nell'ambito delle malattie neurodegenerative rare, sia pediatriche che dell'età adulta. I progetti devono valutare l'efficacia e la sicurezza di prodotti terapeutici a supporto di nuove indicazioni cliniche o di modifiche delle indicazioni di etichettatura (labeling). L'obiettivo primario è incrementare il numero di trattamenti approvati dalle autorità regolatorie e favorire un impatto positivo e duraturo sullo sviluppo clinico di terapie per patologie rare. La presentazione di un trial clinico è requisito obbligatorio per accedere al finanziamento.</t>
+          <t>L'avviso NIH finanzia studi clinici multicentrici esplorativi e confermativi, studi di validazione di biomarcatori o misure di esito, e studi ancillari all'interno della rete StrokeNet, mirati a promuovere interventi per la prevenzione, il trattamento e il recupero post-ictus. I progetti approvati utilizzeranno l'infrastruttura di StrokeNet collaborando con il National Coordinating Center e il National Data Management Center per la gestione statistica e l'arruolamento dei pazienti. Possono candidarsi enti statunitensi pubblici o privati, comprese università e organizzazioni comunitarie, mentre gli enti esteri non sono ammessi a presentare domanda come capofila.</t>
         </is>
       </c>
       <c r="AE23" s="4" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="AF23" s="4" t="n">
-        <v>46312</v>
+        <v>46316</v>
       </c>
       <c r="AG23" s="2" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>GG-FOR-FD-25-006</t>
+          <t>GG-HHS-2027-ACL-NIDILRR-ARCP-0300</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Da verificare</t>
+          <t>No</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Ricerca clinica</t>
+          <t>Formazione / fellowship</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Studi rivolti alle malattie neurodegenerative rare, inclusa la SLA</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="n"/>
+          <t>Programma di formazione avanzata nella ricerca riabilitativa (ARRT) - Vita di comunità e partecipazione</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>46363</v>
+      </c>
       <c r="G24" s="5">
         <f>IF(F24="","",F24-TODAY())</f>
         <v/>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>In apertura</t>
+          <t>Aperto</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Food and Drug Administration</t>
+          <t>Administration for Community Living</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3821,12 +3809,12 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>Food and Drug Administration – FOR-FD-25-006</t>
+          <t>Administration for Community Living – HHS-2027-ACL-NIDILRR-ARCP-0300</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>Studies Addressing Rare Neurodegenerative Diseases including ALS</t>
+          <t>Advanced Rehabilitation Research Training (ARRT) Program - Community Living and Participation</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -3836,27 +3824,31 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>neurodegenerat</t>
+          <t>rehabilitat</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>Riguarda la SLA e le malattie neurodegenerative rare, ma è focalizzato sullo sviluppo di prodotti medici anziché su interventi riabilitativi specifici.</t>
-        </is>
-      </c>
-      <c r="P24" s="6" t="n"/>
-      <c r="Q24" s="6" t="n"/>
+          <t>Bando esplicitamente dedicato alla formazione avanzata di ricercatori nel campo della disabilità e della riabilitazione.</t>
+        </is>
+      </c>
+      <c r="P24" s="6" t="n">
+        <v>250000</v>
+      </c>
+      <c r="Q24" s="6" t="n">
+        <v>250000</v>
+      </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="S24" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t>Media – 10 progetti finanziabili (stima: tasso storico non disponibile)</t>
+          <t>Bassa – 1 progetti finanziabili (stima: tasso storico non disponibile)</t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
@@ -3865,23 +3857,27 @@
         </is>
       </c>
       <c r="V24" s="4" t="n">
-        <v>45518</v>
-      </c>
-      <c r="W24" s="2" t="n"/>
+        <v>46290</v>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>36 mesi</t>
+        </is>
+      </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>Ricerca</t>
+          <t>Dottorato / formazione / mobilità</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t>Nonprofits that do not have a 501(c)(3) status with the IRS, other than institutions of higher education; Public and State controlled institutions of higher education; Native American tribal organizations (other than Federally recognized tribal governments); Independent school districts; Small businesses; Nonprofits having a 501(c)(3) status with the IRS, other than institutions of higher educatio</t>
+          <t>Private institutions of higher education; Public and State controlled institutions of higher education</t>
         </is>
       </c>
       <c r="Z24" s="3" t="n"/>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>Enti esteri: da verificare nel bando</t>
+          <t>Solo enti statunitensi</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
@@ -3891,26 +3887,26 @@
       </c>
       <c r="AC24" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/356046</t>
+          <t>https://www.grants.gov/search-results-detail/363963</t>
         </is>
       </c>
       <c r="AD24" s="3" t="inlineStr">
         <is>
-          <t>Il bando, promosso dalla Food and Drug Administration (FDA), mira a sostenere studi scientifici per far progredire lo sviluppo di prodotti medici destinati a prevenire, diagnosticare, mitigare, trattare o curare la sclerosi laterale amiotrofica (SLA) e altre malattie neurodegenerative rare, sia negli adulti che nei bambini. Attraverso questo programma, l’ente intende colmare lacune conoscitive critiche, generare un impatto significativo sulla gestione delle patologie neurodegenerative rare e fornire dati essenziali per orientare lo sviluppo regolatorio e industriale di interventi innovativi attuali e futuri. Il bando finanzia attività di ricerca volte all'avanzamento di candidati terapeutici e strumenti diagnostici. I dettagli relativi a requisiti specifici di partecipazione e contributi economici sono definiti nella documentazione ufficiale.</t>
+          <t>Il programma ARRT del NIDILRR sostiene percorsi di formazione avanzata alla ricerca ed esperienza post-dottorato a favore di ricercatori nell'ambito della riabilitazione, compresi ricercatori con disabilità. L'obiettivo è potenziare la capacità di condurre ricerche multidisciplinari di elevata qualità sulla disabilità e sulla riabilitazione, focalizzandosi su esiti legati alla vita comunitaria e alla partecipazione sociale delle persone con disabilità. Il finanziamento è destinato a istituzioni universitarie pubbliche o private statunitensi per un singolo progetto della durata di 36 mesi articolato in tre periodi di budget annuali; gli enti stranieri non possono partecipare né ricevere fondi.</t>
         </is>
       </c>
       <c r="AE24" s="4" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="AF24" s="4" t="n">
-        <v>46312</v>
+        <v>46316</v>
       </c>
       <c r="AG24" s="2" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>GG-PAR-25-052</t>
+          <t>GG-HHS-2027-ACL-NIDILRR-AREM-0301</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -3925,16 +3921,16 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Ricerca clinica</t>
+          <t>Formazione / fellowship</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Studi clinici e studi sui biomarcatori NIH StrokeNet per il trattamento, il recupero e la prevenzione dell'ictus (UG3/UH3)</t>
+          <t>Programma avanzato di formazione alla ricerca riabilitativa (ARRT) - Occupazione</t>
         </is>
       </c>
       <c r="F25" s="4" t="n">
-        <v>46345</v>
+        <v>46363</v>
       </c>
       <c r="G25" s="5">
         <f>IF(F25="","",F25-TODAY())</f>
@@ -3942,12 +3938,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>In scadenza (≤30 gg)</t>
+          <t>Aperto</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>National Institutes of Health</t>
+          <t>Administration for Community Living</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3957,40 +3953,46 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>National Institutes of Health – PAR-25-052</t>
+          <t>Administration for Community Living – HHS-2027-ACL-NIDILRR-AREM-0301</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>NIH StrokeNet Clinical Trials and Biomarker Studies for Stroke Treatment, Recovery, and Prevention (UG3/UH3 Clinical Trial Optional)</t>
+          <t>Advanced Rehabilitation Research Training (ARRT) Program - Employment</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>Ictus</t>
+          <t>Altre malattie e riabilitazione</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>stroke</t>
+          <t>rehabilitat</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>Il bando finanzia trial clinici e studi di biomarcatori dedicati al trattamento, al recupero funzionale e alla prevenzione dell'ictus.</t>
-        </is>
-      </c>
-      <c r="P25" s="6" t="n"/>
-      <c r="Q25" s="6" t="n"/>
+          <t>Finanzia programmi avanzati di formazione alla ricerca multidisciplinare per la disabilità e la riabilitazione occupazionale.</t>
+        </is>
+      </c>
+      <c r="P25" s="6" t="n">
+        <v>250000</v>
+      </c>
+      <c r="Q25" s="6" t="n">
+        <v>250000</v>
+      </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="S25" s="2" t="n"/>
+      <c r="S25" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t>Non stimabile – dati insufficienti</t>
+          <t>Bassa – 1 progetti finanziabili (stima: tasso storico non disponibile)</t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
@@ -3999,27 +4001,27 @@
         </is>
       </c>
       <c r="V25" s="4" t="n">
-        <v>45616</v>
-      </c>
-      <c r="W25" s="2" t="n"/>
+        <v>46290</v>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>36 mesi</t>
+        </is>
+      </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>Ricerca</t>
+          <t>Dottorato / formazione / mobilità</t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t>Special district governments; State governments; Independent school districts; Public and State controlled institutions of higher education; Small businesses; Nonprofits that do not have a 501(c)(3) status with the IRS, other than institutions of higher education; For profit organizations other than small businesses; Public housing authorities/Indian housing authorities; Others (see text field ent</t>
-        </is>
-      </c>
-      <c r="Z25" s="3" t="inlineStr">
-        <is>
-          <t>Collaborazione obbligatoria all'interno della rete NIH StrokeNet con il National Coordinating Center e i siti clinici affiliati.</t>
-        </is>
-      </c>
+          <t>Public and State controlled institutions of higher education; Private institutions of higher education</t>
+        </is>
+      </c>
+      <c r="Z25" s="3" t="n"/>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>Enti esteri non ammessi (call NIH completa)</t>
+          <t>Solo enti statunitensi</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
@@ -4029,16 +4031,16 @@
       </c>
       <c r="AC25" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/357256</t>
+          <t>https://www.grants.gov/search-results-detail/363964</t>
         </is>
       </c>
       <c r="AD25" s="3" t="inlineStr">
         <is>
-          <t>Il bando promosso dal National Institutes of Health (NIH/NINDS) sostiene la realizzazione di studi clinici multicentrici esplorativi e di conferma focalizzati su interventi terapeutici promettenti, oltre a studi di validazione di biomarcatori o misure di esito funzionale propedeutici a trial clinici nell'ambito della prevenzione, del trattamento acuto e del recupero post-ictus. I progetti selezionati saranno integrati e condotti all'interno dell'infrastruttura della rete NIH StrokeNet, collaborando con i centri nazionali di coordinamento e gestione dei dati per il reclutamento e l'implementazione del protocollo. Possono candidarsi enti statunitensi come università, istituti di ricerca, ospedali e agenzie governative ammissibili, mentre gli enti esteri non residenti negli Stati Uniti sono esplicitamente esclusi come capofila.</t>
+          <t>Il bando Advanced Rehabilitation Research Training (ARRT) Program, promosso dal National Institute on Disability, Independent Living, and Rehabilitation Research (NIDILRR), mira a finanziare un progetto triennale dedicato alla formazione avanzata di ricercatori post-dottorato nell'ambito della disabilità e della riabilitazione. L'obiettivo primario è sviluppare competenze multidisciplinari di alto livello incentrate sul miglioramento dei risultati occupazionali per le persone con disabilità, incoraggiando anche la partecipazione di ricercatori con disabilità. Possono candidarsi esclusivamente istituti di istruzione superiore statunitensi, sia pubblici che privati, mentre gli enti stranieri sono espressamente esclusi dalla partecipazione. Il programma copre le attività di formazione e ricerca avanzata nell'arco di tre periodi di budget annuali consecutivi.</t>
         </is>
       </c>
       <c r="AE25" s="4" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="AF25" s="4" t="n">
         <v>46316</v>
@@ -4048,7 +4050,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>GG-HHS-2027-ACL-NIDILRR-ARCP-0300</t>
+          <t>GG-HHS-2027-ACL-NIDILRR-ARHF-0302</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -4068,7 +4070,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Programma di formazione avanzata nella ricerca riabilitativa (ARRT) - Vita nella comunità e partecipazione</t>
+          <t>Programma avanzato di formazione alla ricerca riabilitativa (ARRT) - Salute e funzione</t>
         </is>
       </c>
       <c r="F26" s="4" t="n">
@@ -4095,12 +4097,12 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>Administration for Community Living – HHS-2027-ACL-NIDILRR-ARCP-0300</t>
+          <t>Administration for Community Living – HHS-2027-ACL-NIDILRR-ARHF-0302</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>Advanced Rehabilitation Research Training (ARRT) Program - Community Living and Participation</t>
+          <t>Advanced Rehabilitation Research Training (ARRT) Program - Health and Function</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -4115,7 +4117,7 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>Finanzia programmi di formazione avanzata per ricercatori nell'ambito della riabilitazione e della disabilità.</t>
+          <t>Supporta la formazione avanzata di ricercatori nella riabilitazione focalizzata su esiti di salute e funzionalità nelle persone con disabilità.</t>
         </is>
       </c>
       <c r="P26" s="6" t="n">
@@ -4157,7 +4159,7 @@
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t>Public and State controlled institutions of higher education; Private institutions of higher education</t>
+          <t>Private institutions of higher education; Public and State controlled institutions of higher education</t>
         </is>
       </c>
       <c r="Z26" s="3" t="n"/>
@@ -4173,16 +4175,16 @@
       </c>
       <c r="AC26" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/363963</t>
+          <t>https://www.grants.gov/search-results-detail/363965</t>
         </is>
       </c>
       <c r="AD26" s="3" t="inlineStr">
         <is>
-          <t>Il programma Advanced Rehabilitation Research Training (ARRT), gestito dal NIDILRR presso l'Administration for Community Living, si propone di fornire formazione avanzata ed esperienza scientifica a ricercatori post-dottorato nel settore della riabilitazione, compresi ricercatori con disabilità. L'obiettivo del bando è rafforzare la capacità di condurre ricerche multidisciplinari di elevata qualità focalizzate sul miglioramento della vita autonoma nella comunità e sulla partecipazione sociale delle persone con disabilità. Il finanziamento sostiene un singolo progetto triennale articolato in tre periodi di budget annuali. La candidatura è aperta esclusivamente a istituti di istruzione superiore pubblici, statali o privati con sede negli Stati Uniti, mentre gli enti stranieri non sono ammessi a partecipare né a ricevere fondi.</t>
+          <t>Il bando Advanced Rehabilitation Research Training (ARRT) Program – Health and Function, promosso dal National Institute on Disability, Independent Living, and Rehabilitation Research (NIDILRR), finanzia un progetto per sostenere la formazione avanzata alla ricerca di figure con titolo di dottorato o equivalente. L'obiettivo dell'iniziativa è accrescere la capacità di condurre ricerca multidisciplinare di eccellenza nel settore della riabilitazione e della disabilità, focalizzandosi in particolare sul miglioramento degli esiti di salute e funzionalità delle persone con disabilità. Possono partecipare istituzioni di istruzione superiore pubbliche o private con sede negli Stati Uniti; gli enti esteri non sono ammessi a presentare domanda o ricevere fondi. Il finanziamento prevede una durata complessiva di 36 mesi.</t>
         </is>
       </c>
       <c r="AE26" s="4" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="AF26" s="4" t="n">
         <v>46316</v>
@@ -4192,7 +4194,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>GG-HHS-2027-ACL-NIDILRR-AREM-0301</t>
+          <t>WEB-14a8635c6be7</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -4212,11 +4214,11 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Programma di formazione avanzata nella ricerca riabilitativa (ARRT) - Occupazione</t>
+          <t>Borse di studio per la promozione degli studi dottorali (PODS)</t>
         </is>
       </c>
       <c r="F27" s="4" t="n">
-        <v>46363</v>
+        <v>46407</v>
       </c>
       <c r="G27" s="5">
         <f>IF(F27="","",F27-TODAY())</f>
@@ -4229,44 +4231,44 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Administration for Community Living</t>
+          <t>Foundation for Physical Therapy Research</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>Grants.gov</t>
+          <t>Foundation for Physical Therapy Research</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>Administration for Community Living – HHS-2027-ACL-NIDILRR-AREM-0301</t>
+          <t>Promotion of Doctoral Studies Scholarships</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>Advanced Rehabilitation Research Training (ARRT) Program - Employment</t>
+          <t>Promotion of Doctoral Studies Scholarships</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>Altre malattie e riabilitazione</t>
+          <t>Invecchiamento, Altre malattie e riabilitazione</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>rehabilitat</t>
+          <t>geriatr, physical therap, cardiovascular, pulmonary</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>Finanzia la formazione avanzata di ricercatori nel campo della riabilitazione e disabilità con focus sull'occupazione.</t>
+          <t>Finanzia borse di studio dottorali per fisioterapisti impegnati nella ricerca in fisioterapia e riabilitazione.</t>
         </is>
       </c>
       <c r="P27" s="6" t="n">
-        <v>250000</v>
+        <v>7500</v>
       </c>
       <c r="Q27" s="6" t="n">
-        <v>250000</v>
+        <v>15000</v>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
@@ -4274,24 +4276,22 @@
         </is>
       </c>
       <c r="S27" s="2" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t>Bassa – 1 progetti finanziabili (stima: tasso storico non disponibile)</t>
+          <t>Alta – 22 progetti finanziabili (stima: tasso storico non disponibile)</t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t>Interamente finanziato</t>
-        </is>
-      </c>
-      <c r="V27" s="4" t="n">
-        <v>46290</v>
-      </c>
+          <t>Non indicato</t>
+        </is>
+      </c>
+      <c r="V27" s="4" t="n"/>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>36 mesi</t>
+          <t>12 mesi</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
@@ -4301,13 +4301,13 @@
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t>Public and State controlled institutions of higher education; Private institutions of higher education</t>
+          <t>Fisioterapisti e assistenti fisioterapisti abilitati, membri APTA, iscritti a un programma di dottorato di ricerca accademico.</t>
         </is>
       </c>
       <c r="Z27" s="3" t="n"/>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>Solo enti statunitensi</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
@@ -4317,26 +4317,26 @@
       </c>
       <c r="AC27" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/363964</t>
+          <t>https://foundation4pt.org/foundation-funding-opportunities/scholarships/</t>
         </is>
       </c>
       <c r="AD27" s="3" t="inlineStr">
         <is>
-          <t>Il programma ARRT promosso dal NIDILRR (Administration for Community Living) è finalizzato a erogare formazione avanzata ed esperienza scientifica a professionisti in possesso di dottorato o titoli equivalenti nel settore della riabilitazione, incentivando la partecipazione di ricercatori con disabilità. Questa specifica opportunità si concentra sul potenziamento delle competenze per condurre studi multidisciplinari incentrati sugli esiti lavorativi e sull'inclusione occupazionale delle persone con disabilità. L'iniziativa prevede l'assegnazione di un unico finanziamento per una durata complessiva di 36 mesi, suddiviso in tre annualità di budget. Possono concorrere unicamente istituzioni di istruzione superiore pubbliche, statali o private statunitensi, mentre gli enti esteri sono esplicitamente esclusi dalla competizione e dall'assegnazione del contributo.</t>
+          <t>Il programma Promotion of Doctoral Studies (PODS) Scholarships, promosso dalla Foundation for Physical Therapy Research, offre borse di studio per sostenere la formazione dottorale di fisioterapisti e assistenti fisioterapisti iscritti all'APTA che intendono intraprendere una carriera nella ricerca in fisioterapia e riabilitazione. Il bando prevede due linee: la fase pre-candidatura (PODSI), con contributi annuali di 7.500 dollari per il percorso di corsi propedeutici, e la fase di candidatura dottorale (PODSII), con borse annuali di 15.000 dollari per il completamento della tesi di ricerca. Sono previsti premi generali e premi mirati ad aree specialistiche quali neurologia, geriatria, pediatria e apparato cardiovascolare e polmonare, con circa 22 borse complessive disponibili.</t>
         </is>
       </c>
       <c r="AE27" s="4" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="AF27" s="4" t="n">
-        <v>46316</v>
+        <v>46312</v>
       </c>
       <c r="AG27" s="2" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>GG-HHS-2027-ACL-NIDILRR-ARHF-0302</t>
+          <t>GG-HHS-2027-ACL-NIDILRR-DPTB-0311</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -4351,16 +4351,16 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Formazione / fellowship</t>
+          <t>Ricerca clinica</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Programma di formazione avanzata nella ricerca riabilitativa (ARRT) - Salute e funzionalità</t>
+          <t>Centri per il sistema modello per le lesioni cerebrali traumatiche (TBIMS)</t>
         </is>
       </c>
       <c r="F28" s="4" t="n">
-        <v>46363</v>
+        <v>46478</v>
       </c>
       <c r="G28" s="5">
         <f>IF(F28="","",F28-TODAY())</f>
@@ -4383,12 +4383,12 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>Administration for Community Living – HHS-2027-ACL-NIDILRR-ARHF-0302</t>
+          <t>Administration for Community Living – HHS-2027-ACL-NIDILRR-DPTB-0311</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>Advanced Rehabilitation Research Training (ARRT) Program - Health and Function</t>
+          <t>Traumatic Brain Injury Model Systems Centers</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -4398,19 +4398,19 @@
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>rehabilitat</t>
+          <t>rehabilitat, traumatic brain injur</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>Finanzia programmi di formazione avanzata per ricercatori nell'ambito della riabilitazione focalizzati su salute e funzionalità.</t>
+          <t>È interamente dedicato alla ricerca clinica e alla riabilitazione nei pazienti con lesioni cerebrali traumatiche.</t>
         </is>
       </c>
       <c r="P28" s="6" t="n">
-        <v>250000</v>
+        <v>8450000</v>
       </c>
       <c r="Q28" s="6" t="n">
-        <v>250000</v>
+        <v>640000</v>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
@@ -4418,11 +4418,11 @@
         </is>
       </c>
       <c r="S28" s="2" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t>Bassa – 1 progetti finanziabili (stima: tasso storico non disponibile)</t>
+          <t>Media – 14 progetti finanziabili (stima: tasso storico non disponibile)</t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
@@ -4435,17 +4435,17 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>36 mesi</t>
+          <t>60 mesi</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>Dottorato / formazione / mobilità</t>
+          <t>Ricerca</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t>Private institutions of higher education; Public and State controlled institutions of higher education</t>
+          <t>Special district governments; For profit organizations other than small businesses; Public and State controlled institutions of higher education; Nonprofits that do not have a 501(c)(3) status with the IRS, other than institutions of higher education; Native American tribal governments (Federally recognized); Native American tribal organizations (other than Federally recognized tribal governments)</t>
         </is>
       </c>
       <c r="Z28" s="3" t="n"/>
@@ -4461,16 +4461,16 @@
       </c>
       <c r="AC28" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/363965</t>
+          <t>https://www.grants.gov/search-results-detail/363970</t>
         </is>
       </c>
       <c r="AD28" s="3" t="inlineStr">
         <is>
-          <t>L'iniziativa ARRT promossa dal National Institute on Disability, Independent Living, and Rehabilitation Research (NIDILRR) sostiene programmi formativi avanzati destinati a ricercatori post-dottorato nel campo della riabilitazione, inclusi studiosi con disabilità. L'obiettivo consiste nell'accrescere le competenze metodologiche e scientifiche per sviluppare ricerche multidisciplinari mirate al miglioramento della salute, del recupero funzionale e del benessere delle persone con disabilità fisiche o cognitive. È prevista l'assegnazione di un solo finanziamento della durata di 36 mesi, articolato su tre cicli annuali di spesa. La partecipazione è riservata esclusivamente a istituti di istruzione superiore pubblici, statali o privati statunitensi; gli enti internazionali e stranieri non sono ammessi a concorrere né a ricevere il finanziamento.</t>
+          <t>Il bando sostiene i Traumatic Brain Injury Model Systems Centers (TBIMS) con l'obiettivo di sviluppare e migliorare l'accesso a percorsi di riabilitazione basati sull'evidenza per persone con lesione cerebrale traumatica (TBI). I centri finanziati devono generare nuove conoscenze per migliorare gli esiti funzionali, la partecipazione comunitaria e l'occupazione, conducendo studi clinici multicentrici e contribuendo alla banca dati longitudinale TBIMS. Possono partecipare stati, università, enti pubblici e privati che garantiscano una continuità assistenziale multidisciplinare completa (emergenza, cure acute, riabilitazione medica acuta e post-acuta). Gli enti esteri sono esclusi. I finanziamenti hanno una durata di 60 mesi, con importi commisurati al numero di partecipanti seguiti nel database.</t>
         </is>
       </c>
       <c r="AE28" s="4" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="AF28" s="4" t="n">
         <v>46316</v>
@@ -4480,7 +4480,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>WEB-14a8635c6be7</t>
+          <t>GG-HHS-2027-ACL-NIDILRR-REGE-0312</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -4495,16 +4495,16 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Formazione / fellowship</t>
+          <t>Tecnologia / innovazione</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Borse di studio per la promozione degli studi di dottorato (PODS)</t>
+          <t>Centro di ricerca di ingegneria della riabilitazione sulle tecnologie ricreative, sportive e di esercizio per persone con disabilità</t>
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>46407</v>
+        <v>46492</v>
       </c>
       <c r="G29" s="5">
         <f>IF(F29="","",F29-TODAY())</f>
@@ -4517,44 +4517,44 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>Foundation for Physical Therapy Research</t>
+          <t>Administration for Community Living</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>Foundation for Physical Therapy Research</t>
+          <t>Grants.gov</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>Promotion of Doctoral Studies Scholarships</t>
+          <t>Administration for Community Living – HHS-2027-ACL-NIDILRR-REGE-0312</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>Promotion of Doctoral Studies Scholarships</t>
+          <t>Rehabilitation Engineering Research Center on Recreational, Sport, and Exercise Technologies for People with Disabilities</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>Invecchiamento, Altre malattie e riabilitazione</t>
+          <t>Tecnologie riabilitazione, Altre malattie e riabilitazione</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>geriatr, physical therap, cardiovascular, pulmonary</t>
+          <t>rehabilitation engineering, rehabilitat</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>Finanzia borse di studio dottorali per fisioterapisti impegnati nella ricerca riabilitativa clinica e applicata.</t>
+          <t>Finanzia lo sviluppo di tecnologie ingegneristiche e ausili per promuovere l'esercizio e la salute in persone con disabilità.</t>
         </is>
       </c>
       <c r="P29" s="6" t="n">
-        <v>7500</v>
+        <v>975000</v>
       </c>
       <c r="Q29" s="6" t="n">
-        <v>15000</v>
+        <v>975000</v>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
@@ -4562,38 +4562,40 @@
         </is>
       </c>
       <c r="S29" s="2" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t>Alta – 22 progetti finanziabili (stima: tasso storico non disponibile)</t>
+          <t>Bassa – 1 progetti finanziabili (stima: tasso storico non disponibile)</t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t>Non indicato</t>
-        </is>
-      </c>
-      <c r="V29" s="4" t="n"/>
+          <t>Interamente finanziato</t>
+        </is>
+      </c>
+      <c r="V29" s="4" t="n">
+        <v>46290</v>
+      </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>12 mesi</t>
+          <t>60 mesi</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>Dottorato / formazione / mobilità</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t>Fisioterapisti e assistenti fisioterapisti abilitati, membri APTA, iscritti a un programma di dottorato di ricerca accademico.</t>
+          <t>County governments; City or township governments; Small businesses; Special district governments; Nonprofits having a 501(c)(3) status with the IRS, other than institutions of higher education; Native American tribal organizations (other than Federally recognized tribal governments); For profit organizations other than small businesses; Public and State controlled institutions of higher education;</t>
         </is>
       </c>
       <c r="Z29" s="3" t="n"/>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Solo enti statunitensi</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
@@ -4603,26 +4605,26 @@
       </c>
       <c r="AC29" s="7" t="inlineStr">
         <is>
-          <t>https://foundation4pt.org/foundation-funding-opportunities/scholarships/</t>
+          <t>https://www.grants.gov/search-results-detail/363973</t>
         </is>
       </c>
       <c r="AD29" s="3" t="inlineStr">
         <is>
-          <t>La Foundation for Physical Therapy Research offre borse di studio a supporto dei fisioterapisti abilitati e assistenti di fisioterapia, iscritti all'APTA, che frequentano un programma di dottorato di ricerca (PhD, EdD, DSc) con l'intento di intraprendere una carriera scientifica nella riabilitazione. Il bando prevede due fasi: pre-candidatura (PODSI), con borse annuali di 7.500 dollari per il percorso di corsi preliminari, e candidatura dottorale (PODSII), con borse annuali di 15.000 dollari per la fase di tesi e ricerca. Sono previsti finanziamenti generali e su aree specialistiche quali neurologia, geriatria, riabilitazione cardiovascolare e polmonare, pediatria e ricerca sui servizi sanitari, con un totale stimato di circa 22 borse disponibili.</t>
+          <t>L'iniziativa finanzia un centro RERC (Rehabilitation Engineering Research Center) per promuovere la ricerca ingegneristica avanzata e lo sviluppo di tecnologie innovative volte a risolvere specifici problemi riabilitativi o rimuovere barriere ambientali. Nello specifico, il centro dovrà dedicarsi a soluzioni tecnologiche, ausili e dispositivi che incoraggino l'esercizio fisico, la pratica sportiva, le attività ricreative e la salute nelle persone con disabilità. Possono candidarsi istituzioni accademiche, agenzie e organizzazioni pubbliche o private statunitensi, mentre le entità estere sono escluse. Verrà selezionato un singolo progetto della durata di 60 mesi, articolato in cinque periodi di bilancio annuali.</t>
         </is>
       </c>
       <c r="AE29" s="4" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="AF29" s="4" t="n">
-        <v>46312</v>
+        <v>46316</v>
       </c>
       <c r="AG29" s="2" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>GG-HHS-2027-ACL-NIDILRR-DPTB-0311</t>
+          <t>GG-HHS-2027-ACL-NIDILRR-REGE-0313</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -4637,16 +4639,16 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Ricerca clinica</t>
+          <t>Tecnologia / innovazione</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Centri modello per il sistema di cura e riabilitazione del trauma cranico encefalico</t>
+          <t>Centro di ricerca di ingegneria della riabilitazione sulle tecnologie per persone cieche o ipovedenti</t>
         </is>
       </c>
       <c r="F30" s="4" t="n">
-        <v>46478</v>
+        <v>46499</v>
       </c>
       <c r="G30" s="5">
         <f>IF(F30="","",F30-TODAY())</f>
@@ -4669,34 +4671,34 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>Administration for Community Living – HHS-2027-ACL-NIDILRR-DPTB-0311</t>
+          <t>Administration for Community Living – HHS-2027-ACL-NIDILRR-REGE-0313</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>Traumatic Brain Injury Model Systems Centers</t>
+          <t>Rehabilitation Engineering Research Center on Technologies for People Who are Blind or have Low Vision</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>Altre malattie e riabilitazione</t>
+          <t>Tecnologie riabilitazione</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>rehabilitat, traumatic brain injur</t>
+          <t>rehabilitation engineering</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>Focalizzato specificamente sulla riabilitazione clinica evidence-based e il recupero funzionale nei pazienti con trauma cranico (TBI).</t>
+          <t>È incentrato sulla ricerca e sviluppo di tecnologie assistive per promuovere l'indipendenza di persone con cecità o ipovisione.</t>
         </is>
       </c>
       <c r="P30" s="6" t="n">
-        <v>8450000</v>
+        <v>975000</v>
       </c>
       <c r="Q30" s="6" t="n">
-        <v>640000</v>
+        <v>975000</v>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
@@ -4704,11 +4706,11 @@
         </is>
       </c>
       <c r="S30" s="2" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t>Media – 14 progetti finanziabili (stima: tasso storico non disponibile)</t>
+          <t>Bassa – 1 progetti finanziabili (stima: tasso storico non disponibile)</t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
@@ -4726,12 +4728,12 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>Ricerca</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t>Small businesses; State governments; County governments; City or township governments; Nonprofits that do not have a 501(c)(3) status with the IRS, other than institutions of higher education; Public and State controlled institutions of higher education; Others (see text field entitled "Additional Information on Eligibility" for clarification); Nonprofits having a 501(c)(3) status with the IRS, ot</t>
+          <t>Special district governments; Public and State controlled institutions of higher education; Nonprofits having a 501(c)(3) status with the IRS, other than institutions of higher education; Native American tribal governments (Federally recognized); For profit organizations other than small businesses; Native American tribal organizations (other than Federally recognized tribal governments); County g</t>
         </is>
       </c>
       <c r="Z30" s="3" t="n"/>
@@ -4747,16 +4749,16 @@
       </c>
       <c r="AC30" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/363970</t>
+          <t>https://www.grants.gov/search-results-detail/363974</t>
         </is>
       </c>
       <c r="AD30" s="3" t="inlineStr">
         <is>
-          <t>L'iniziativa finanzia i centri TBI Model Systems (TBIMS) con lo scopo di condurre ricerche cliniche per lo sviluppo e l'accesso alla riabilitazione evidence-based nei traumi cranio-encefalici. I centri devono generare nuova conoscenza per migliorare gli esiti funzionali, l'inclusione nella comunità e l'occupazione, oltre a contribuire al database longitudinale TBIMS. Possono candidarsi esclusivamente enti dotati di un continuum multidisciplinare di cura (dall'emergenza alla riabilitazione post-acuta). Le entità estere sono escluse. Il progetto prevede una durata di 60 mesi.</t>
+          <t>Il bando finanzia un Rehabilitation Engineering Research Center (RERC) mirato a migliorare l'efficacia dei servizi riabilitativi attraverso la ricerca ingegneristica e lo sviluppo tecnologico avanzato. Il centro dovrà realizzare e validare tecnologie e ausili innovativi destinati a promuovere l'indipendenza, la mobilità e la vita comunitaria delle persone non vedenti o con ipovisione. Il bando è aperto a stati, istituti di istruzione superiore, agenzie e organizzazioni pubbliche o private (anche a scopo di lucro) con sede negli Stati Uniti; le organizzazioni estere non sono ammesse a concorrere o ricevere fondi. È prevista l'assegnazione di un solo finanziamento per una durata di 60 mesi.</t>
         </is>
       </c>
       <c r="AE30" s="4" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="AF30" s="4" t="n">
         <v>46316</v>
@@ -4766,7 +4768,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>GG-HHS-2027-ACL-NIDILRR-REGE-0312</t>
+          <t>GG-RFA-AG-26-010</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -4781,16 +4783,16 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Tecnologia / innovazione</t>
+          <t>Formazione / fellowship</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Centro di ricerca ingegneristica per la riabilitazione sulle tecnologie per ricreazione, sport ed esercizio nelle disabilità</t>
+          <t>Programma di educazione alla ricerca post-laurea NIA per l'espansione della ricerca su AD/ADRD</t>
         </is>
       </c>
       <c r="F31" s="4" t="n">
-        <v>46492</v>
+        <v>46533</v>
       </c>
       <c r="G31" s="5">
         <f>IF(F31="","",F31-TODAY())</f>
@@ -4803,7 +4805,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Administration for Community Living</t>
+          <t>National Institutes of Health</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -4813,46 +4815,42 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>Administration for Community Living – HHS-2027-ACL-NIDILRR-REGE-0312</t>
+          <t>National Institutes of Health – RFA-AG-26-010</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>Rehabilitation Engineering Research Center on Recreational, Sport, and Exercise Technologies for People with Disabilities</t>
+          <t>NIA Expanding Research in AD/ADRD (ERA) Postbaccalaureate Research Education Program (R25 Independent Clinical Trial Not Allowed)</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>Tecnologie riabilitazione, Altre malattie e riabilitazione</t>
+          <t>Invecchiamento</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>rehabilitation engineering, rehabilitat</t>
+          <t>dementi, alzheimer</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>Finanzia ricerca ingegneristica e sviluppo tecnologico per l'esercizio, lo sport e la riabilitazione di persone con disabilità.</t>
-        </is>
-      </c>
-      <c r="P31" s="6" t="n">
-        <v>975000</v>
-      </c>
+          <t>Finanzia programmi di formazione alla ricerca nell'ambito della malattia di Alzheimer e delle demenze correlate.</t>
+        </is>
+      </c>
+      <c r="P31" s="6" t="n"/>
       <c r="Q31" s="6" t="n">
-        <v>975000</v>
+        <v>400000</v>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="S31" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="S31" s="2" t="n"/>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t>Bassa – 1 progetti finanziabili (stima: tasso storico non disponibile)</t>
+          <t>Non stimabile – dati insufficienti</t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
@@ -4861,27 +4859,23 @@
         </is>
       </c>
       <c r="V31" s="4" t="n">
-        <v>46290</v>
-      </c>
-      <c r="W31" s="2" t="inlineStr">
-        <is>
-          <t>60 mesi</t>
-        </is>
-      </c>
+        <v>45902</v>
+      </c>
+      <c r="W31" s="2" t="n"/>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Dottorato / formazione / mobilità</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t>For profit organizations other than small businesses; City or township governments; Private institutions of higher education; Public and State controlled institutions of higher education; Nonprofits that do not have a 501(c)(3) status with the IRS, other than institutions of higher education; Special district governments; State governments; Small businesses; Native American tribal organizations (o</t>
+          <t>Independent school districts; For profit organizations other than small businesses; State governments; City or township governments; Public housing authorities/Indian housing authorities; Special district governments; Native American tribal governments (Federally recognized); Others (see text field entitled "Additional Information on Eligibility" for clarification); Small businesses; Native Americ</t>
         </is>
       </c>
       <c r="Z31" s="3" t="n"/>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>Solo enti statunitensi</t>
+          <t>Enti esteri non ammessi (call NIH completa)</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
@@ -4891,16 +4885,16 @@
       </c>
       <c r="AC31" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/363973</t>
+          <t>https://www.grants.gov/search-results-detail/359653</t>
         </is>
       </c>
       <c r="AD31" s="3" t="inlineStr">
         <is>
-          <t>Il bando finanzia un Rehabilitation Engineering Research Center (RERC) per condurre ricerca ingegneristica avanzata e sviluppo di tecnologie innovative dedicate a promuovere l'esercizio fisico, lo sport e la salute in persone con disabilità, eliminando le barriere ambientali. NIDILRR intende assegnare un singolo finanziamento della durata complessiva di 60 mesi (5 periodi di bilancio da 12 mesi). Possono candidarsi stati, enti pubblici e privati (compresi for-profit), atenei e organizzazioni comunitarie statunitensi; le organizzazioni estere non sono ammesse al bando.</t>
+          <t>Questo bando sostiene lo sviluppo e l'implementazione di programmi di educazione alla ricerca per recenti laureati, inclusi gruppi sottorappresentati, per ampliare la forza lavoro qualificata nella ricerca sulla malattia di Alzheimer (AD) e sulle demenze correlate (ADRD). L'obiettivo è fornire esperienze di ricerca intensive nel campo dell'Alzheimer per preparare i partecipanti a intraprendere programmi di dottorato avanzati orientati alla ricerca o carriere competitive nel settore privato. Possono partecipare diverse organizzazioni statunitensi, tra cui enti comunitari e tribali. Il finanziamento supporta attività educative e di ricerca pratica, ma esclude esplicitamente le organizzazioni straniere e non ammette sperimentazioni cliniche indipendenti.</t>
         </is>
       </c>
       <c r="AE31" s="4" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="AF31" s="4" t="n">
         <v>46316</v>
@@ -4910,7 +4904,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>GG-HHS-2027-ACL-NIDILRR-REGE-0313</t>
+          <t>GG-PAR-24-321</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -4925,16 +4919,16 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Tecnologia / innovazione</t>
+          <t>Formazione / fellowship</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Centro di ricerca ingegneristica per la riabilitazione sulle tecnologie per persone non vedenti o ipovedenti</t>
+          <t>Premio alla carriera per la leadership accademica NIA</t>
         </is>
       </c>
       <c r="F32" s="4" t="n">
-        <v>46499</v>
+        <v>46703</v>
       </c>
       <c r="G32" s="5">
         <f>IF(F32="","",F32-TODAY())</f>
@@ -4947,7 +4941,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Administration for Community Living</t>
+          <t>National Institutes of Health</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -4957,46 +4951,40 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>Administration for Community Living – HHS-2027-ACL-NIDILRR-REGE-0313</t>
+          <t>National Institutes of Health – PAR-24-321</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>Rehabilitation Engineering Research Center on Technologies for People Who are Blind or have Low Vision</t>
+          <t>NIA Academic Leadership Career Award (K07 Independent Clinical Trial Not Allowed)</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>Tecnologie riabilitazione</t>
+          <t>Invecchiamento</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>rehabilitation engineering</t>
+          <t>dementi, alzheimer, aging</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>Dedicato allo sviluppo di tecnologie e ausili per l'autonomia e la riabilitazione visiva in persone non vedenti o ipovedenti.</t>
-        </is>
-      </c>
-      <c r="P32" s="6" t="n">
-        <v>975000</v>
-      </c>
-      <c r="Q32" s="6" t="n">
-        <v>975000</v>
-      </c>
+          <t>Finanzia leader di ricerca accademica per potenziare le capacità di ricerca sull'invecchiamento e sulla demenza e Alzheimer.</t>
+        </is>
+      </c>
+      <c r="P32" s="6" t="n"/>
+      <c r="Q32" s="6" t="n"/>
       <c r="R32" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="S32" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="S32" s="2" t="n"/>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t>Bassa – 1 progetti finanziabili (stima: tasso storico non disponibile)</t>
+          <t>Non stimabile – dati insufficienti</t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
@@ -5005,27 +4993,23 @@
         </is>
       </c>
       <c r="V32" s="4" t="n">
-        <v>46290</v>
-      </c>
-      <c r="W32" s="2" t="inlineStr">
-        <is>
-          <t>60 mesi</t>
-        </is>
-      </c>
+        <v>45602</v>
+      </c>
+      <c r="W32" s="2" t="n"/>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Dottorato / formazione / mobilità</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t>Private institutions of higher education; Native American tribal organizations (other than Federally recognized tribal governments); County governments; Public and State controlled institutions of higher education; Native American tribal governments (Federally recognized); Nonprofits that do not have a 501(c)(3) status with the IRS, other than institutions of higher education; City or township gov</t>
+          <t>Others (see text field entitled "Additional Information on Eligibility" for clarification); Special district governments; Public housing authorities/Indian housing authorities; Small businesses; Nonprofits that do not have a 501(c)(3) status with the IRS, other than institutions of higher education; Private institutions of higher education; For profit organizations other than small businesses; Pub</t>
         </is>
       </c>
       <c r="Z32" s="3" t="n"/>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>Solo enti statunitensi</t>
+          <t>Enti esteri non ammessi (call NIH completa)</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
@@ -5035,16 +5019,16 @@
       </c>
       <c r="AC32" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/363974</t>
+          <t>https://www.grants.gov/search-results-detail/357000</t>
         </is>
       </c>
       <c r="AD32" s="3" t="inlineStr">
         <is>
-          <t>Il programma Rehabilitation Engineering Research Centers (RERC) intende finanziare un centro focalizzato sulla ricerca ingegneristica e sullo sviluppo di tecnologie assistive avanzate volte a promuovere l'indipendenza funzionale e la vita nella comunità per individui non vedenti o ipovedenti. È previsto il finanziamento di un unico progetto della durata di 60 mesi. Possono partecipare atenei, enti pubblici o privati profit e no-profit con sede negli Stati Uniti. Le entità straniere non sono idonee alla candidatura né alla ricezione dei fondi.</t>
+          <t>Il bando offre supporto a ricercatori affermati con competenze e doti di leadership per potenziare la capacità di ricerca sull'invecchiamento, sulla malattia di Alzheimer e sulle demenze correlate (ADRD) all'interno delle loro istituzioni accademiche. I beneficiari si dedicheranno allo sviluppo di infrastrutture di ricerca ed educative, tutoraggio e attività di sviluppo di carriera, inclusi corsi, curricula, supporto alla ricerca, finanziamenti pilota e borse di viaggio. L'avviso è destinato a candidati la cui ricerca non prevede la conduzione di trial clinici indipendenti. Possono partecipare istituzioni e agenzie idonee negli Stati Uniti, escludendo le organizzazioni straniere.</t>
         </is>
       </c>
       <c r="AE32" s="4" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="AF32" s="4" t="n">
         <v>46316</v>
@@ -5054,7 +5038,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>WEB-c6a9b085a5f9</t>
+          <t>GG-PAR-25-024</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -5074,57 +5058,57 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Bandi di ricerca su implementazione, interventi e coinvolgimento comunitario in terapia occupazionale 2026-2027</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="n"/>
+          <t>Sviluppo di biomarcatori o biomarcatori compositi per disturbi neurologici e neuromuscolari</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>46759</v>
+      </c>
       <c r="G33" s="5">
         <f>IF(F33="","",F33-TODAY())</f>
         <v/>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Scadenza da verificare</t>
+          <t>Aperto</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>American Occupational Therapy Foundation</t>
+          <t>National Institutes of Health</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>American Occupational Therapy Foundation</t>
+          <t>Grants.gov</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>Grant Award Guidelines 2026 2027 Final</t>
+          <t>National Institutes of Health – PAR-25-024</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>Grant Award Guidelines 2026 2027 Final</t>
+          <t>Development of Biomarkers or Composite Biomarkers for Neurological and Neuromuscular Disorders (R61/R33 - Clinical Trial Optional)</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>Ictus, Invecchiamento, Altre malattie e riabilitazione</t>
+          <t>Altre malattie e riabilitazione</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>stroke, dementi, cognitive impairment, occupational therap, spinal cord injur, traumatic brain injur, cerebral palsy, disabilit</t>
+          <t>neuromuscular</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>Bando focalizzato sulla ricerca clinica di intervento e implementazione in terapia occupazionale, centrale per il recupero funzionale e l'autonomia.</t>
-        </is>
-      </c>
-      <c r="P33" s="6" t="n">
-        <v>100000</v>
-      </c>
+          <t>Promuove la scoperta e la valutazione di biomarcatori per disturbi neurologici e neuromuscolari.</t>
+        </is>
+      </c>
+      <c r="P33" s="6" t="n"/>
       <c r="Q33" s="6" t="n"/>
       <c r="R33" s="2" t="inlineStr">
         <is>
@@ -5139,25 +5123,27 @@
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t>Co-finanziamento da verificare</t>
-        </is>
-      </c>
-      <c r="V33" s="4" t="n"/>
+          <t>Interamente finanziato</t>
+        </is>
+      </c>
+      <c r="V33" s="4" t="n">
+        <v>45593</v>
+      </c>
       <c r="W33" s="2" t="n"/>
       <c r="X33" s="2" t="inlineStr">
         <is>
           <t>Ricerca</t>
         </is>
       </c>
-      <c r="Y33" s="3" t="n"/>
-      <c r="Z33" s="3" t="inlineStr">
-        <is>
-          <t>Prevista collaborazione attiva tra ricercatori, organizzazioni e partner di comunità per il bando CERG</t>
-        </is>
-      </c>
+      <c r="Y33" s="3" t="inlineStr">
+        <is>
+          <t>Small businesses; State governments; Native American tribal governments (Federally recognized); Public and State controlled institutions of higher education; Nonprofits having a 501(c)(3) status with the IRS, other than institutions of higher education; Others (see text field entitled "Additional Information on Eligibility" for clarification); Independent school districts; Public housing authoriti</t>
+        </is>
+      </c>
+      <c r="Z33" s="3" t="n"/>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Enti esteri non ammessi (call NIH completa)</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
@@ -5167,19 +5153,19 @@
       </c>
       <c r="AC33" s="7" t="inlineStr">
         <is>
-          <t>https://www.aotf.org/wp-content/uploads/2026/10/Grant_Award-Guidelines_2026-2027_Final.pdf</t>
+          <t>https://www.grants.gov/search-results-detail/356874</t>
         </is>
       </c>
       <c r="AD33" s="3" t="inlineStr">
         <is>
-          <t>Linee guida per i bandi di ricerca 2026-2027 della American Occupational Therapy Foundation (AOTF), articolati in tre tipologie di finanziamento: Implementation Research (IR), Intervention Research (IRG) e Community-Engaged Research (CERG). I programmi mirano a costruire una solida base di evidenze scientifiche per la terapia occupazionale, sostenendo lo sviluppo e la validazione di interventi manualizzati centrati sul paziente, la traslazione dei risultati nella pratica clinica e partenariati inclusivi con le comunità. I temi prioritari includono la gestione dei comportamenti di salute nelle malattie croniche, la salute mentale, il supporto ambientale e tecnologico, la resilienza dei caregiver e l'accesso equo ai servizi sanitari per popolazioni vulnerabili con disabilità fisiche o cognitive.</t>
+          <t>L'iniziativa promuove la scoperta e la valutazione precoce di candidati biomarcatori e firme di biomarcatori da utilizzare come strumenti per facilitare lo sviluppo clinico di neuroterapeutici e la pratica clinica per disturbi neurologici e neuromuscolari. Il bando si concentra sull'identificazione e sulla valutazione biologica, analitica e clinica iniziale di biomarcatori utilizzando campioni o set di dati umani standardizzati, eventualmente affiancati da studi su animali. L'obiettivo è fornire biomarcatori pronti per studi definitivi di validazione clinica. Possono candidarsi enti di ricerca statunitensi idonei, mentre le organizzazioni straniere sono escluse.</t>
         </is>
       </c>
       <c r="AE33" s="4" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="AF33" s="4" t="n">
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="AG33" s="2" t="n"/>
     </row>
@@ -5206,7 +5192,7 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Bando di ricerca Hand in Hand 2026-2027 per la riabilitazione della mano e dell'arto superiore</t>
+          <t>Bando di ricerca Hand in Hand</t>
         </is>
       </c>
       <c r="F34" s="4" t="n"/>
@@ -5251,7 +5237,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>Bando interamente incentrato sulla riabilitazione della mano e dell'arto superiore per lesioni tendinee, ictus, lesioni midollari e dolore cronico.</t>
+          <t>Finanzia progetti di ricerca precoce nella riabilitazione della mano e degli arti superiori e in popolazioni con menomazioni fisiche come l'ictus e le lesioni midollari.</t>
         </is>
       </c>
       <c r="P34" s="6" t="n">
@@ -5275,7 +5261,7 @@
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t>Non indicato</t>
+          <t>Interamente finanziato</t>
         </is>
       </c>
       <c r="V34" s="4" t="n"/>
@@ -5289,7 +5275,11 @@
           <t>Ricerca</t>
         </is>
       </c>
-      <c r="Y34" s="3" t="n"/>
+      <c r="Y34" s="3" t="inlineStr">
+        <is>
+          <t>Ricercatori e organizzazioni idonee</t>
+        </is>
+      </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
           <t>Richiesta la collaborazione tra partner comunitari e ricercatori o istituzioni accademiche</t>
@@ -5312,11 +5302,11 @@
       </c>
       <c r="AD34" s="3" t="inlineStr">
         <is>
-          <t>Il bando Hand in Hand Research Grant 2026-2027 nasce dalla collaborazione tra AOTF, ASHT e AHTF per sostenere progetti pilota di ricerca clinica con forte coinvolgimento della comunità nella terapia della mano e dell'arto superiore. Il finanziamento è destinato a studi preliminari volti a gettare le basi per future sperimentazioni su larga scala, valutando interventi riabilitativi, disparità sanitarie, efficacia comparativa e validazione degli esiti terapeutici. Le aree di interesse clinico prioritario includono le lesioni dei tendini, l'epicondilite laterale, le sindromi dolorose complesse (CRPS), l'uso di ortesi e agenti biofisici, con particolare attenzione a popolazioni con lesioni traumatiche, ictus o lesioni del midollo spinale.</t>
+          <t>Il bando Hand in Hand Research Grant, promosso da AOTF, ASHT e AHTF, sostiene progetti di ricerca in fase iniziale fortemente incentrati sul coinvolgimento della comunità nella terapia della mano e degli arti superiori. L'obiettivo è gettare le basi per studi futuri su larga scala, esaminando interventi terapeutici, accesso ai servizi sanitari e implementazione dell'evidenza nella pratica clinica. Le aree prioritarie includono le disparità sanitarie, l'efficacia comparativa, la convalida degli esiti clinici nella riabilitazione della mano (tra cui lesioni tendinee, epicondilite laterale, dolore e sindrome da dolore regionale complesso) e l'uso di ortesi. Il contributo massimo è di 50.000 dollari per la durata di un anno.</t>
         </is>
       </c>
       <c r="AE34" s="4" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="AF34" s="4" t="n">
         <v>46317</v>
@@ -5429,7 +5419,7 @@
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t>City or township governments; For profit organizations other than small businesses; Others (see text field entitled "Additional Information on Eligibility" for clarification); County governments; Public housing authorities/Indian housing authorities; Nonprofits having a 501(c)(3) status with the IRS, other than institutions of higher education; Small businesses; Private institutions of higher educ</t>
+          <t>Public and State controlled institutions of higher education; Independent school districts; Others (see text field entitled "Additional Information on Eligibility" for clarification); Private institutions of higher education; Small businesses; State governments; Public housing authorities/Indian housing authorities; For profit organizations other than small businesses; City or township governments</t>
         </is>
       </c>
       <c r="Z35" s="3" t="inlineStr">
@@ -5458,7 +5448,7 @@
         </is>
       </c>
       <c r="AE35" s="4" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="AF35" s="4" t="n">
         <v>46316</v>
@@ -5488,7 +5478,7 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Accesso allargato a popolazioni intermedie di pazienti con sclerosi laterale amiotrofica (SLA) (U01)</t>
+          <t>Accesso allargato per popolazioni intermedie di pazienti con sclerosi laterale amiotrofica (U01)</t>
         </is>
       </c>
       <c r="F36" s="4" t="n">
@@ -5535,7 +5525,7 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>Riguarda la SLA ma è focalizzato su protocolli di accesso allargato a farmaci sperimentali e biomarcatori.</t>
+          <t>Riguarda la SLA ma è focalizzato sulla sperimentazione e accesso allargato a farmaci o prodotti biologici.</t>
         </is>
       </c>
       <c r="P36" s="6" t="n"/>
@@ -5567,7 +5557,7 @@
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t>Special district governments; Public and State controlled institutions of higher education; City or township governments; Nonprofits having a 501(c)(3) status with the IRS, other than institutions of higher education; Others (see text field entitled "Additional Information on Eligibility" for clarification); Native American tribal organizations (other than Federally recognized tribal governments);</t>
+          <t>For profit organizations other than small businesses; Nonprofits that do not have a 501(c)(3) status with the IRS, other than institutions of higher education; Native American tribal organizations (other than Federally recognized tribal governments); Native American tribal governments (Federally recognized); Special district governments; City or township governments; County governments; State gove</t>
         </is>
       </c>
       <c r="Z36" s="3" t="n"/>
@@ -5588,11 +5578,11 @@
       </c>
       <c r="AD36" s="3" t="inlineStr">
         <is>
-          <t>Il National Institute of Neurological Disorders and Stroke (NINDS) intende sostenere la ricerca scientifica basata sui dati derivanti da protocolli di accesso allargato di dimensioni intermedie per la sclerosi laterale amiotrofica (SLA). I protocolli ammissibili devono fornire accesso a farmaci o prodotti biologici sperimentali e generare dati a supporto della ricerca su prevenzione, diagnosi o trattamento della SLA, inclusi effetti su biomarcatori, sicurezza, sopravvivenza o esiti clinici rilevanti (es. ospedalizzazione o ventilazione assistita). Possono candidarsi centri clinici partecipanti a trial di fase 2/3 o fase 3 promossi da una piccola impresa statunitense titolare dell'IND presso la FDA. Non sono ammesse organizzazioni né componenti non statunitensi.</t>
+          <t>Il National Institute of Neurological Disorders and Stroke (NINDS) intende finanziare la ricerca scientifica basata su protocolli di accesso allargato a popolazioni intermedie per la sclerosi laterale amiotrofica (SLA). I protocolli ammissibili devono fornire l'accesso a un farmaco o prodotto biologico sperimentale e generare dati utili per prevenzione, diagnosi, trattamento o cura della patologia, inclusi effetti su biomarcatori, sicurezza, esiti clinici (ospedalizzazione, necessità di ventilazione assistita) o esperienza del paziente. Possono candidarsi esclusivamente centri di sperimentazione clinica che partecipano a trial di fase 2/3 o fase 3 sponsorizzati da piccole imprese statunitensi titolari di IND. Gli enti stranieri e le collaborazioni internazionali con componenti estere non sono ammessi.</t>
         </is>
       </c>
       <c r="AE36" s="4" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="AF36" s="4" t="n">
         <v>46316</v>
@@ -5622,7 +5612,7 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Programma estivo di formazione alla ricerca NIA per espandere gli studi su Alzheimer e demenze (R25)</t>
+          <t>Programma estivo NIA di formazione alla ricerca su Alzheimer e demenze correlate (R25)</t>
         </is>
       </c>
       <c r="F37" s="4" t="n">
@@ -5669,7 +5659,7 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>Riguarda l'Alzheimer e le demenze correlate, ma è incentrato sulla formazione estiva alla ricerca per studenti.</t>
+          <t>Programma di formazione alla ricerca su Alzheimer e demenze correlate, senza focus specifico sulla riabilitazione.</t>
         </is>
       </c>
       <c r="P37" s="6" t="n"/>
@@ -5703,7 +5693,7 @@
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Private institutions of higher education; County governments; City or township governments; State governments; Nonprofits having a 501(c)(3) status with the IRS, other than institutions of higher education; Special district governments; Native American tribal organizations (other than Federally recognized tribal governments); Nonprofits that do not have a 501(c)(3) status with the IRS, other than </t>
+          <t>Others (see text field entitled "Additional Information on Eligibility" for clarification); Independent school districts; Public and State controlled institutions of higher education; Special district governments; County governments; Nonprofits that do not have a 501(c)(3) status with the IRS, other than institutions of higher education; Private institutions of higher education; City or township g</t>
         </is>
       </c>
       <c r="Z37" s="3" t="n"/>
@@ -5724,11 +5714,11 @@
       </c>
       <c r="AD37" s="3" t="inlineStr">
         <is>
-          <t>Il National Institute on Aging (NIA) promuove lo sviluppo e l'attuazione di programmi estivi di educazione alla ricerca incentrati sulla malattia di Alzheimer e sulle demenze correlate (AD/ADRD). Il bando è rivolto a studenti delle scuole superiori, universitari o docenti di scienze, incoraggiando la partecipazione di gruppi sottorappresentati nelle scienze biomediche e comportamentali. L'obiettivo è ampliare il bacino di ricercatori qualificati fornendo esperienze intensive di ricerca estiva per favorire percorsi accademici avanzati nelle demenze. I partecipanti non possono condurre trial clinici indipendenti, ma possono maturare esperienza all'interno di sperimentazioni cliniche guidate da tutor. Le organizzazioni estere e i componenti stranieri sono esclusi.</t>
+          <t>Il National Institute on Aging (NIA) promuove questo bando R25 per finanziare lo sviluppo e l'attuazione di programmi estivi di formazione alla ricerca rivolti a studenti delle scuole superiori, studenti universitari o docenti di materie scientifiche. L'obiettivo consiste nell'ampliare e diversificare la forza lavoro qualificata nel settore della malattia di Alzheimer e delle demenze correlate (ADRD), offrendo esperienze intensive per incoraggiare percorsi di carriera nella ricerca biomedica e comportamentale. I partecipanti possono acquisire esperienza nell'ambito di trial clinici guidati da mentori, pur senza poter condurre trial in modo indipendente. Le istituzioni non statunitensi e i componenti esteri di enti USA non sono ammessi a partecipare.</t>
         </is>
       </c>
       <c r="AE37" s="4" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="AF37" s="4" t="n">
         <v>46316</v>
@@ -5738,7 +5728,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>GG-RFA-AG-26-010</t>
+          <t>GG-PAR-27-096</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -5758,11 +5748,11 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Programma post-laurea NIA di formazione alla ricerca per ampliare gli studi su Alzheimer e demenze (R25)</t>
+          <t>Finanziamenti per la transizione di specialisti medici e chirurgici emergenti alla ricerca sull'invecchiamento</t>
         </is>
       </c>
       <c r="F38" s="4" t="n">
-        <v>46533</v>
+        <v>46950</v>
       </c>
       <c r="G38" s="5">
         <f>IF(F38="","",F38-TODAY())</f>
@@ -5785,12 +5775,12 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>National Institutes of Health – RFA-AG-26-010</t>
+          <t>National Institutes of Health – PAR-27-096</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>NIA Expanding Research in AD/ADRD (ERA) Postbaccalaureate Research Education Program (R25 Independent Clinical Trial Not Allowed)</t>
+          <t>Grants for Early Medical/Surgical Specialists' Transition to Aging Research (GEMSSTAR) (R03 Clinical Trial Optional)</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
@@ -5800,17 +5790,17 @@
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>dementi, alzheimer</t>
+          <t>geriatr, aging</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>Riguarda l'Alzheimer e le demenze correlate, ma è dedicato alla formazione post-laurea triennale.</t>
+          <t>Il bando finanzia ricercatori all'inizio della carriera nella ricerca sull'invecchiamento e geriatria, ma esclude enti non statunitensi.</t>
         </is>
       </c>
       <c r="P38" s="6" t="n"/>
       <c r="Q38" s="6" t="n">
-        <v>400000</v>
+        <v>125000</v>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
@@ -5829,23 +5819,23 @@
         </is>
       </c>
       <c r="V38" s="4" t="n">
-        <v>45902</v>
+        <v>46266</v>
       </c>
       <c r="W38" s="2" t="n"/>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>Dottorato / formazione / mobilità</t>
+          <t>Ricerca</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t>City or township governments; For profit organizations other than small businesses; Independent school districts; Native American tribal organizations (other than Federally recognized tribal governments); County governments; Native American tribal governments (Federally recognized); Nonprofits having a 501(c)(3) status with the IRS, other than institutions of higher education; State governments; P</t>
+          <t>Nonprofits having a 501(c)(3) status with the IRS, other than institutions of higher education; County governments; For profit organizations other than small businesses; Native American tribal organizations (other than Federally recognized tribal governments); Public and State controlled institutions of higher education; Others (see text field entitled "Additional Information on Eligibility" for c</t>
         </is>
       </c>
       <c r="Z38" s="3" t="n"/>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>Enti esteri non ammessi (call NIH completa)</t>
+          <t>Solo enti statunitensi</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
@@ -5855,16 +5845,16 @@
       </c>
       <c r="AC38" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/359653</t>
+          <t>https://www.grants.gov/search-results-detail/359940</t>
         </is>
       </c>
       <c r="AD38" s="3" t="inlineStr">
         <is>
-          <t>Il National Institute on Aging (NIA) finanzia programmi di formazione alla ricerca per neolaureati (baccalaureate) incentrati sulla malattia di Alzheimer e sulle demenze correlate (AD/ADRD). L'iniziativa mira ad ampliare la comunità di ricercatori qualificati, includendo individui provenienti da contesti sottorappresentati nelle scienze biomediche e comportamentali, e fornendo un'esperienza precoce di ricerca nel settore. I percorsi educativi proposti dovranno offrire esperienze intensive per preparare i partecipanti al passaggio verso corsi di laurea magistrale, dottorati focalizzati sulla ricerca o carriere scientifiche nel settore privato. Non è consentito condurre trial clinici indipendenti. Le entità e le componenti estere non sono ammesse al bando.</t>
+          <t>Questo programma offre supporto a specialisti medici e chirurgici all'inizio della carriera clinico-scientifica per avviare carriere come futuri leader nella ricerca focalizzata sull'invecchiamento o sulla geriatria. L'iniziativa incoraggia la ricerca transdisciplinare per produrre dati pilota ed esperienze utili a successivi progetti di ricerca. I candidati devono includere un piano di sviluppo professionale che rifletta un ambiente di ricerca di supporto. Possono partecipare ricercatori clinici inseriti in contesti idonei, mentre sono escluse le organizzazioni non statunitensi. Si finanziano progetti di ricerca pilota e attività di sviluppo professionale in ambito geriatrico e dell'invecchiamento.</t>
         </is>
       </c>
       <c r="AE38" s="4" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="AF38" s="4" t="n">
         <v>46316</v>
@@ -5874,7 +5864,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>GG-PAR-24-321</t>
+          <t>WEB-c6a9b085a5f9</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -5889,62 +5879,62 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Formazione / fellowship</t>
+          <t>Ricerca clinica</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Finanziamento NIA per la leadership accademica e lo sviluppo di carriera (K07)</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="n">
-        <v>46703</v>
-      </c>
+          <t>Finanziamenti per la ricerca sull'implementazione, sugli interventi e con il coinvolgimento della comunità</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="n"/>
       <c r="G39" s="5">
         <f>IF(F39="","",F39-TODAY())</f>
         <v/>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>Aperto</t>
+          <t>Scadenza da verificare</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>National Institutes of Health</t>
+          <t>American Occupational Therapy Foundation</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>Grants.gov</t>
+          <t>American Occupational Therapy Foundation</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>National Institutes of Health – PAR-24-321</t>
+          <t>Grant Award Guidelines 2026 2027 Final</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>NIA Academic Leadership Career Award (K07 Independent Clinical Trial Not Allowed)</t>
+          <t>Grant Award Guidelines 2026 2027 Final</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>Invecchiamento</t>
+          <t>Ictus, Invecchiamento, Altre malattie e riabilitazione</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>dementi, alzheimer, aging</t>
+          <t>stroke, dementi, cognitive impairment, occupational therap, spinal cord injur, traumatic brain injur, cerebral palsy, disabilit</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>Tratta l'invecchiamento e le demenze ma si focalizza sullo sviluppo accademico, la mentorship e le capacità istituzionali di ricerca, non sulla riabilitazione.</t>
-        </is>
-      </c>
-      <c r="P39" s="6" t="n"/>
+          <t>Finanzia la ricerca clinica e l'implementazione in terapia occupazionale, area correlata alla riabilitazione ma focalizzata sull'occupazione e il benessere generale.</t>
+        </is>
+      </c>
+      <c r="P39" s="6" t="n">
+        <v>100000</v>
+      </c>
       <c r="Q39" s="6" t="n"/>
       <c r="R39" s="2" t="inlineStr">
         <is>
@@ -5959,27 +5949,29 @@
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t>Interamente finanziato</t>
-        </is>
-      </c>
-      <c r="V39" s="4" t="n">
-        <v>45602</v>
-      </c>
+          <t>Co-finanziamento da verificare</t>
+        </is>
+      </c>
+      <c r="V39" s="4" t="n"/>
       <c r="W39" s="2" t="n"/>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>Dottorato / formazione / mobilità</t>
+          <t>Ricerca</t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t>Special district governments; Independent school districts; Others (see text field entitled "Additional Information on Eligibility" for clarification); Native American tribal organizations (other than Federally recognized tribal governments); Private institutions of higher education; Public housing authorities/Indian housing authorities; Nonprofits that do not have a 501(c)(3) status with the IRS,</t>
-        </is>
-      </c>
-      <c r="Z39" s="3" t="n"/>
+          <t>Ricercatori e organizzazioni idonee</t>
+        </is>
+      </c>
+      <c r="Z39" s="3" t="inlineStr">
+        <is>
+          <t>Prevista collaborazione attiva tra ricercatori, organizzazioni e partner di comunità per il bando CERG</t>
+        </is>
+      </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>Enti esteri non ammessi (call NIH completa)</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
@@ -5989,295 +5981,25 @@
       </c>
       <c r="AC39" s="7" t="inlineStr">
         <is>
-          <t>https://www.grants.gov/search-results-detail/357000</t>
+          <t>https://www.aotf.org/wp-content/uploads/2026/10/Grant_Award-Guidelines_2026-2027_Final.pdf</t>
         </is>
       </c>
       <c r="AD39" s="3" t="inlineStr">
         <is>
-          <t>Il National Institute on Aging mette a disposizione fondi attraverso il meccanismo K07 per supportare ricercatori affermati dotati di comprovata esperienza e capacità di leadership, al fine di rafforzare la capacità di ricerca sull'invecchiamento, sulla malattia di Alzheimer e sulle demenze correlate all'interno delle loro istituzioni accademiche. Il finanziamento supporta lo sviluppo di infrastrutture formative e di ricerca, attività di mentorship, nuovi corsi curriculari e programmi pilota. Non è consentito condurre trial clinici indipendenti con questo bando. La partecipazione è riservata a docenti e ricercatori di istituzioni universitarie ed enti di ricerca situati negli Stati Uniti; le organizzazioni non statunitensi sono escluse.</t>
+          <t>Il bando della American Occupational Therapy Foundation sostiene programmi di ricerca focalizzati sull'implementazione, sugli interventi e sul coinvolgimento della comunità nell'ambito della terapia occupazionale. Gli obiettivi includono lo sviluppo di metodi per integrare servizi basati sull'evidenza nella pratica clinica, la valutazione dell'efficacia degli interventi terapeutici sulla partecipazione e sulla salute, e la promozione di collaborazioni di ricerca radicate nelle comunità. Le aree prioritarie comprendono la gestione delle condizioni croniche, la salute mentale, il supporto tecnologico e ambientale, lo sviluppo e le transizioni familiari, l'accesso equo ai servizi, il supporto ai caregiver e i nuovi approcci di erogazione dei servizi. Possono partecipare ricercatori e organizzazioni idonee secondo le linee guida.</t>
         </is>
       </c>
       <c r="AE39" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="AF39" s="4" t="n">
         <v>46317</v>
       </c>
-      <c r="AF39" s="4" t="n">
-        <v>46316</v>
-      </c>
       <c r="AG39" s="2" t="n"/>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>GG-PAR-25-024</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>Ricerca clinica</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="inlineStr">
-        <is>
-          <t>Sviluppo di biomarcatori o combinazioni di biomarcatori per patologie neurologiche e neuromuscolari (R61/R33)</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="n">
-        <v>46759</v>
-      </c>
-      <c r="G40" s="5">
-        <f>IF(F40="","",F40-TODAY())</f>
-        <v/>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>Aperto</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>National Institutes of Health</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>Grants.gov</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>National Institutes of Health – PAR-25-024</t>
-        </is>
-      </c>
-      <c r="L40" s="3" t="inlineStr">
-        <is>
-          <t>Development of Biomarkers or Composite Biomarkers for Neurological and Neuromuscular Disorders (R61/R33 - Clinical Trial Optional)</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>Altre malattie e riabilitazione</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>neuromuscular</t>
-        </is>
-      </c>
-      <c r="O40" s="3" t="inlineStr">
-        <is>
-          <t>Il bando finanzia la ricerca di biomarcatori per patologie neurologiche e neuromuscolari senza un focus diretto su interventi di riabilitazione.</t>
-        </is>
-      </c>
-      <c r="P40" s="6" t="n"/>
-      <c r="Q40" s="6" t="n"/>
-      <c r="R40" s="2" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="S40" s="2" t="n"/>
-      <c r="T40" s="3" t="inlineStr">
-        <is>
-          <t>Non stimabile – dati insufficienti</t>
-        </is>
-      </c>
-      <c r="U40" s="3" t="inlineStr">
-        <is>
-          <t>Interamente finanziato</t>
-        </is>
-      </c>
-      <c r="V40" s="4" t="n">
-        <v>45593</v>
-      </c>
-      <c r="W40" s="2" t="n"/>
-      <c r="X40" s="2" t="inlineStr">
-        <is>
-          <t>Ricerca</t>
-        </is>
-      </c>
-      <c r="Y40" s="3" t="inlineStr">
-        <is>
-          <t>City or township governments; For profit organizations other than small businesses; Private institutions of higher education; Special district governments; Public and State controlled institutions of higher education; Native American tribal governments (Federally recognized); State governments; Nonprofits that do not have a 501(c)(3) status with the IRS, other than institutions of higher education</t>
-        </is>
-      </c>
-      <c r="Z40" s="3" t="n"/>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>Enti esteri non ammessi (call NIH completa)</t>
-        </is>
-      </c>
-      <c r="AB40" s="2" t="inlineStr">
-        <is>
-          <t>Inglese</t>
-        </is>
-      </c>
-      <c r="AC40" s="7" t="inlineStr">
-        <is>
-          <t>https://www.grants.gov/search-results-detail/356874</t>
-        </is>
-      </c>
-      <c r="AD40" s="3" t="inlineStr">
-        <is>
-          <t>Questa opportunità promossa dal NIH supporta la scoperta e la valutazione preliminare di solidi biomarcatori o firme di biomarcatori mirati a facilitare lo sviluppo clinico di terapie neurologiche e il loro impiego nella pratica clinica. La call si focalizza sulla caratterizzazione biologica, analitica e clinica iniziale di marcatori per patologie neurologiche e neuromuscolari. I progetti possono includere modelli animali, ma devono obbligatoriamente prevedere una prima validazione su campioni o dataset clinici umani standardizzati. Possono concorrere università, ospedali, centri di ricerca e imprese commerciali con sede negli Stati Uniti. I soggetti esteri sono esclusi dalla candidatura come enti proponenti.</t>
-        </is>
-      </c>
-      <c r="AE40" s="4" t="n">
-        <v>46317</v>
-      </c>
-      <c r="AF40" s="4" t="n">
-        <v>46316</v>
-      </c>
-      <c r="AG40" s="2" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>GG-PAR-27-096</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>Ricerca clinica</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>Finanziamenti per la transizione alla ricerca sull'invecchiamento per specialisti medici e chirurgici a inizio carriera (GEMSSTAR R03)</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="n">
-        <v>46950</v>
-      </c>
-      <c r="G41" s="5">
-        <f>IF(F41="","",F41-TODAY())</f>
-        <v/>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>Aperto</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>National Institutes of Health</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>Grants.gov</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>National Institutes of Health – PAR-27-096</t>
-        </is>
-      </c>
-      <c r="L41" s="3" t="inlineStr">
-        <is>
-          <t>Grants for Early Medical/Surgical Specialists' Transition to Aging Research (GEMSSTAR) (R03 Clinical Trial Optional)</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>Invecchiamento</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>geriatr, aging</t>
-        </is>
-      </c>
-      <c r="O41" s="3" t="inlineStr">
-        <is>
-          <t>Bando generale sulla ricerca geriatrica e sull'invecchiamento rivolto a medici specialisti, che può includere la riabilitazione ma non vi è specificamente dedicato.</t>
-        </is>
-      </c>
-      <c r="P41" s="6" t="n"/>
-      <c r="Q41" s="6" t="n">
-        <v>125000</v>
-      </c>
-      <c r="R41" s="2" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="S41" s="2" t="n"/>
-      <c r="T41" s="3" t="inlineStr">
-        <is>
-          <t>Non stimabile – dati insufficienti</t>
-        </is>
-      </c>
-      <c r="U41" s="3" t="inlineStr">
-        <is>
-          <t>Interamente finanziato</t>
-        </is>
-      </c>
-      <c r="V41" s="4" t="n">
-        <v>46266</v>
-      </c>
-      <c r="W41" s="2" t="n"/>
-      <c r="X41" s="2" t="inlineStr">
-        <is>
-          <t>Ricerca</t>
-        </is>
-      </c>
-      <c r="Y41" s="3" t="inlineStr">
-        <is>
-          <t>Nonprofits having a 501(c)(3) status with the IRS, other than institutions of higher education; Special district governments; Native American tribal organizations (other than Federally recognized tribal governments); State governments; County governments; Small businesses; Public housing authorities/Indian housing authorities; Independent school districts; Private institutions of higher education;</t>
-        </is>
-      </c>
-      <c r="Z41" s="3" t="n"/>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>Solo enti statunitensi</t>
-        </is>
-      </c>
-      <c r="AB41" s="2" t="inlineStr">
-        <is>
-          <t>Inglese</t>
-        </is>
-      </c>
-      <c r="AC41" s="7" t="inlineStr">
-        <is>
-          <t>https://www.grants.gov/search-results-detail/359940</t>
-        </is>
-      </c>
-      <c r="AD41" s="3" t="inlineStr">
-        <is>
-          <t>Il programma GEMSSTAR del National Institute on Aging intende supportare medici-ricercatori a inizio carriera operanti in discipline mediche o chirurgiche per avviarli a ruoli di leadership nella ricerca sull'invecchiamento e geriatrica. Il bando finanzia progetti pilota transdisciplinari volti a generare dati preliminari per successive linee di ricerca, integrati con un piano formale di sviluppo professionale e mentorship. I candidati devono operare in un contesto clinico-accademico favorevole alla ricerca geriatrica. Possono presentare domanda esclusivamente istituzioni con sede negli Stati Uniti; le organizzazioni straniere e i sub-appalti finanziari verso istituzioni estere non sono ammessi.</t>
-        </is>
-      </c>
-      <c r="AE41" s="4" t="n">
-        <v>46317</v>
-      </c>
-      <c r="AF41" s="4" t="n">
-        <v>46316</v>
-      </c>
-      <c r="AG41" s="2" t="n"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:AG41"/>
-  <conditionalFormatting sqref="G2:G41">
+  <autoFilter ref="A1:AG39"/>
+  <conditionalFormatting sqref="G2:G39">
     <cfRule type="cellIs" priority="1" operator="between" dxfId="0">
       <formula>0</formula>
       <formula>30</formula>
@@ -6322,8 +6044,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC37" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC38" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC39" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC40" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC41" r:id="rId40"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -6425,11 +6145,11 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>22/10/2026 22:18</t>
+          <t>23/10/2026 11:28</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>177</v>
+        <v>212</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>0</v>
@@ -6468,11 +6188,11 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>22/10/2026 22:44</t>
+          <t>23/10/2026 11:54</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>1</v>
@@ -6506,19 +6226,23 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>https://www.amed.go.jp/en/koubo/</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="n"/>
+          <t>https://www.amed.go.jp/koubo/bunya_index.html</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>23/10/2026 11:55</t>
+        </is>
+      </c>
       <c r="G4" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Ultimo errore 22/10/2026: HTTP 404</t>
+          <t>Ultima esecuzione: 1 elementi esaminati, 0 pertinenti</t>
         </is>
       </c>
     </row>
@@ -6550,14 +6274,14 @@
       </c>
       <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Ultimo errore 22/10/2026: HTTP 403</t>
+          <t>Ultimo errore 23/10/2026: HTTP 403</t>
         </is>
       </c>
     </row>
@@ -6589,11 +6313,11 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22/10/2026 22:35</t>
+          <t>23/10/2026 11:45</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>0</v>
@@ -6632,11 +6356,11 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22/10/2026 22:30</t>
+          <t>23/10/2026 11:39</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>150</v>
+        <v>178</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>21</v>
@@ -6675,11 +6399,11 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>22/10/2026 22:43</t>
+          <t>23/10/2026 11:53</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>0</v>
@@ -6718,11 +6442,11 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22/10/2026 22:28</t>
+          <t>23/10/2026 11:38</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>2</v>
@@ -6761,11 +6485,11 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22/10/2026 22:27</t>
+          <t>23/10/2026 11:37</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>57</v>
+        <v>92</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>5</v>
@@ -6804,11 +6528,11 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22/10/2026 22:31</t>
+          <t>23/10/2026 11:40</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>100</v>
+        <v>135</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>0</v>
@@ -6847,14 +6571,14 @@
       </c>
       <c r="F12" s="2" t="n"/>
       <c r="G12" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Ultimo errore 22/10/2026: HTTP 403</t>
+          <t>Ultimo errore 23/10/2026: HTTP 403</t>
         </is>
       </c>
     </row>
@@ -6886,11 +6610,11 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22/10/2026 22:45</t>
+          <t>23/10/2026 11:55</t>
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>2</v>
@@ -6929,14 +6653,14 @@
       </c>
       <c r="F14" s="2" t="n"/>
       <c r="G14" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Ultimo errore 22/10/2026: HTTP 404</t>
+          <t>Ultimo errore 23/10/2026: HTTP 404</t>
         </is>
       </c>
     </row>
@@ -6968,11 +6692,11 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>22/10/2026 22:32</t>
+          <t>23/10/2026 11:41</t>
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>10</v>
@@ -7011,11 +6735,11 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22/10/2026 22:49</t>
+          <t>23/10/2026 11:58</t>
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>0</v>
@@ -7054,11 +6778,11 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22/10/2026 22:50</t>
+          <t>23/10/2026 11:59</t>
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>0</v>
@@ -7097,11 +6821,11 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>22/10/2026 22:31</t>
+          <t>23/10/2026 11:41</t>
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>0</v>
@@ -7140,14 +6864,14 @@
       </c>
       <c r="F19" s="2" t="n"/>
       <c r="G19" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Ultimo errore 22/10/2026: HTTP 404</t>
+          <t>Ultimo errore 23/10/2026: HTTP 404</t>
         </is>
       </c>
     </row>
@@ -7179,11 +6903,11 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>22/10/2026 22:11</t>
+          <t>23/10/2026 11:20</t>
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>245</v>
+        <v>280</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>1</v>
@@ -7222,14 +6946,14 @@
       </c>
       <c r="F21" s="2" t="n"/>
       <c r="G21" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>Ultimo errore 22/10/2026: HTTP 404</t>
+          <t>Ultimo errore 23/10/2026: HTTP 404</t>
         </is>
       </c>
     </row>
@@ -7261,14 +6985,14 @@
       </c>
       <c r="F22" s="2" t="n"/>
       <c r="G22" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Ultimo errore 22/10/2026: HTTP 403</t>
+          <t>Ultimo errore 23/10/2026: HTTP 403</t>
         </is>
       </c>
     </row>
@@ -7300,11 +7024,11 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>22/10/2026 22:35</t>
+          <t>23/10/2026 11:44</t>
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>0</v>
@@ -7343,11 +7067,11 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>22/10/2026 22:29</t>
+          <t>23/10/2026 11:38</t>
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>140</v>
+        <v>175</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>9</v>
@@ -7386,11 +7110,11 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>22/10/2026 22:19</t>
+          <t>23/10/2026 11:28</t>
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>245</v>
+        <v>280</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>0</v>
@@ -7429,11 +7153,11 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>22/10/2026 22:25</t>
+          <t>23/10/2026 11:34</t>
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>245</v>
+        <v>280</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>0</v>
@@ -7472,18 +7196,18 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>22/10/2026 22:02</t>
+          <t>23/10/2026 11:11</t>
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>8395</v>
+        <v>9602</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>77</v>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Ultima esecuzione: 1208 elementi esaminati, 10 pertinenti</t>
+          <t>Ultima esecuzione: 1207 elementi esaminati, 8 pertinenti</t>
         </is>
       </c>
     </row>
@@ -7515,18 +7239,18 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>22/10/2026 22:48</t>
+          <t>23/10/2026 11:57</t>
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Ultima esecuzione: 35 elementi esaminati, 0 pertinenti</t>
+          <t>Ultima esecuzione: 35 elementi esaminati, 1 pertinenti</t>
         </is>
       </c>
     </row>
@@ -7558,11 +7282,11 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>22/10/2026 22:40</t>
+          <t>23/10/2026 11:50</t>
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>0</v>
@@ -7601,11 +7325,11 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>22/10/2026 22:37</t>
+          <t>23/10/2026 11:47</t>
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>0</v>
@@ -7651,7 +7375,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Ultimo errore 22/10/2026: irraggiungibile: HTTPSConnectionPool(host='www.fwo.be', port=443): Max retries exceeded with url: /en/fellowships-funding/ (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_s</t>
+          <t>Ultimo errore 23/10/2026: irraggiungibile: HTTPSConnectionPool(host='www.fwo.be', port=443): Max retries exceeded with url: /en/fellowships-funding/ (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_s</t>
         </is>
       </c>
     </row>
@@ -7683,11 +7407,11 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>22/10/2026 22:13</t>
+          <t>23/10/2026 11:22</t>
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>239</v>
+        <v>271</v>
       </c>
       <c r="H32" s="2" t="n">
         <v>3</v>
@@ -7726,11 +7450,11 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>22/10/2026 22:12</t>
+          <t>23/10/2026 11:21</t>
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>245</v>
+        <v>280</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>3</v>
@@ -7769,11 +7493,11 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>22/10/2026 22:16</t>
+          <t>23/10/2026 11:26</t>
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>245</v>
+        <v>280</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>2</v>
@@ -7812,11 +7536,11 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>22/10/2026 22:10</t>
+          <t>23/10/2026 11:19</t>
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>245</v>
+        <v>280</v>
       </c>
       <c r="H35" s="2" t="n">
         <v>2</v>
@@ -7855,11 +7579,11 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>22/10/2026 22:17</t>
+          <t>23/10/2026 11:26</t>
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>245</v>
+        <v>280</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>0</v>
@@ -7898,11 +7622,11 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>22/10/2026 22:18</t>
+          <t>23/10/2026 11:27</t>
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>245</v>
+        <v>280</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>0</v>
@@ -7941,11 +7665,11 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>22/10/2026 22:31</t>
+          <t>23/10/2026 11:41</t>
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="H38" s="2" t="n">
         <v>16</v>
@@ -7984,11 +7708,11 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>22/10/2026 22:43</t>
+          <t>23/10/2026 11:53</t>
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="H39" s="2" t="n">
         <v>0</v>
@@ -8027,14 +7751,14 @@
       </c>
       <c r="F40" s="2" t="n"/>
       <c r="G40" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H40" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Ultimo errore 22/10/2026: HTTP 404</t>
+          <t>Ultimo errore 23/10/2026: HTTP 404</t>
         </is>
       </c>
     </row>
@@ -8066,18 +7790,18 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>22/10/2026 22:07</t>
+          <t>23/10/2026 11:16</t>
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>5942</v>
+        <v>6786</v>
       </c>
       <c r="H41" s="2" t="n">
         <v>116</v>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>Ultima esecuzione: 852 elementi esaminati, 58 pertinenti</t>
+          <t>Ultima esecuzione: 844 elementi esaminati, 58 pertinenti</t>
         </is>
       </c>
     </row>
@@ -8109,14 +7833,14 @@
       </c>
       <c r="F42" s="2" t="n"/>
       <c r="G42" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H42" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>Ultimo errore 22/10/2026: HTTP 403</t>
+          <t>Ultimo errore 23/10/2026: HTTP 403</t>
         </is>
       </c>
     </row>
@@ -8148,11 +7872,11 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>22/10/2026 22:52</t>
+          <t>23/10/2026 12:02</t>
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="H43" s="2" t="n">
         <v>0</v>
@@ -8191,11 +7915,11 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>22/10/2026 22:41</t>
+          <t>23/10/2026 11:51</t>
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H44" s="2" t="n">
         <v>0</v>
@@ -8234,14 +7958,14 @@
       </c>
       <c r="F45" s="2" t="n"/>
       <c r="G45" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H45" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>Ultimo errore 22/10/2026: HTTP 403</t>
+          <t>Ultimo errore 23/10/2026: HTTP 403</t>
         </is>
       </c>
     </row>
@@ -8273,18 +7997,18 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>22/10/2026 22:43</t>
+          <t>23/10/2026 11:53</t>
         </is>
       </c>
       <c r="G46" s="2" t="n">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>Ultima esecuzione: 35 elementi esaminati, 0 pertinenti</t>
+          <t>Ultima esecuzione: 35 elementi esaminati, 1 pertinenti</t>
         </is>
       </c>
     </row>
@@ -8359,11 +8083,11 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>22/10/2026 22:47</t>
+          <t>23/10/2026 11:57</t>
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="H48" s="2" t="n">
         <v>1</v>
@@ -8402,11 +8126,11 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>22/10/2026 22:08</t>
+          <t>23/10/2026 11:17</t>
         </is>
       </c>
       <c r="G49" s="2" t="n">
-        <v>245</v>
+        <v>280</v>
       </c>
       <c r="H49" s="2" t="n">
         <v>0</v>
@@ -8445,11 +8169,11 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>22/10/2026 22:40</t>
+          <t>23/10/2026 11:50</t>
         </is>
       </c>
       <c r="G50" s="2" t="n">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="H50" s="2" t="n">
         <v>0</v>
@@ -8488,11 +8212,11 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>22/10/2026 22:38</t>
+          <t>23/10/2026 11:49</t>
         </is>
       </c>
       <c r="G51" s="2" t="n">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="H51" s="2" t="n">
         <v>0</v>
@@ -8531,11 +8255,11 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>22/10/2026 22:47</t>
+          <t>23/10/2026 11:57</t>
         </is>
       </c>
       <c r="G52" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H52" s="2" t="n">
         <v>0</v>
@@ -8574,11 +8298,11 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>22/10/2026 22:44</t>
+          <t>23/10/2026 11:54</t>
         </is>
       </c>
       <c r="G53" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H53" s="2" t="n">
         <v>0</v>
@@ -8617,11 +8341,11 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>22/10/2026 22:19</t>
+          <t>23/10/2026 11:28</t>
         </is>
       </c>
       <c r="G54" s="2" t="n">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="H54" s="2" t="n">
         <v>0</v>
@@ -8660,11 +8384,11 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>22/10/2026 22:46</t>
+          <t>23/10/2026 11:56</t>
         </is>
       </c>
       <c r="G55" s="2" t="n">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="H55" s="2" t="n">
         <v>0</v>
@@ -8703,11 +8427,11 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>22/10/2026 22:55</t>
+          <t>23/10/2026 12:05</t>
         </is>
       </c>
       <c r="G56" s="2" t="n">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="H56" s="2" t="n">
         <v>0</v>
@@ -8746,11 +8470,11 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>22/10/2026 22:09</t>
+          <t>23/10/2026 11:18</t>
         </is>
       </c>
       <c r="G57" s="2" t="n">
-        <v>245</v>
+        <v>280</v>
       </c>
       <c r="H57" s="2" t="n">
         <v>0</v>
@@ -8789,14 +8513,14 @@
       </c>
       <c r="F58" s="2" t="n"/>
       <c r="G58" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H58" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>Ultimo errore 22/10/2026: HTTP 404</t>
+          <t>Ultimo errore 23/10/2026: HTTP 404</t>
         </is>
       </c>
     </row>
@@ -8835,7 +8559,7 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>Ultimo errore 22/10/2026: irraggiungibile: HTTPSConnectionPool(host='www.health.gov.au', port=443): Read timed out. (read timeout=45)</t>
+          <t>Ultimo errore 23/10/2026: irraggiungibile: HTTPSConnectionPool(host='www.health.gov.au', port=443): Read timed out. (read timeout=45)</t>
         </is>
       </c>
     </row>
@@ -8867,11 +8591,11 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>22/10/2026 22:44</t>
+          <t>23/10/2026 11:54</t>
         </is>
       </c>
       <c r="G60" s="2" t="n">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="H60" s="2" t="n">
         <v>0</v>
@@ -8910,11 +8634,11 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>22/10/2026 22:29</t>
+          <t>23/10/2026 11:39</t>
         </is>
       </c>
       <c r="G61" s="2" t="n">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="H61" s="2" t="n">
         <v>21</v>
@@ -8953,11 +8677,11 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>22/10/2026 22:50</t>
+          <t>23/10/2026 12:00</t>
         </is>
       </c>
       <c r="G62" s="2" t="n">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="H62" s="2" t="n">
         <v>0</v>
@@ -8996,11 +8720,11 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>22/10/2026 22:07</t>
+          <t>23/10/2026 11:17</t>
         </is>
       </c>
       <c r="G63" s="2" t="n">
-        <v>245</v>
+        <v>280</v>
       </c>
       <c r="H63" s="2" t="n">
         <v>0</v>
@@ -9039,11 +8763,11 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>22/10/2026 22:07</t>
+          <t>23/10/2026 11:16</t>
         </is>
       </c>
       <c r="G64" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H64" s="2" t="n">
         <v>0</v>
@@ -9082,11 +8806,11 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>22/10/2026 22:41</t>
+          <t>23/10/2026 11:51</t>
         </is>
       </c>
       <c r="G65" s="2" t="n">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="H65" s="2" t="n">
         <v>0</v>
@@ -9132,7 +8856,7 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>Ultimo errore 22/10/2026: irraggiungibile: HTTPSConnectionPool(host='www.nhmrc.gov.au', port=443): Read timed out. (read timeout=45)</t>
+          <t>Ultimo errore 23/10/2026: irraggiungibile: HTTPSConnectionPool(host='www.nhmrc.gov.au', port=443): Read timed out. (read timeout=45)</t>
         </is>
       </c>
     </row>
@@ -9164,14 +8888,14 @@
       </c>
       <c r="F67" s="2" t="n"/>
       <c r="G67" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H67" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>Ultimo errore 22/10/2026: HTTP 403</t>
+          <t>Ultimo errore 23/10/2026: HTTP 403</t>
         </is>
       </c>
     </row>
@@ -9242,11 +8966,11 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>22/10/2026 22:51</t>
+          <t>23/10/2026 12:01</t>
         </is>
       </c>
       <c r="G69" s="2" t="n">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="H69" s="2" t="n">
         <v>0</v>
@@ -9285,11 +9009,11 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>22/10/2026 22:46</t>
+          <t>23/10/2026 11:56</t>
         </is>
       </c>
       <c r="G70" s="2" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="H70" s="2" t="n">
         <v>0</v>
@@ -9328,11 +9052,11 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>22/10/2026 22:44</t>
+          <t>23/10/2026 11:54</t>
         </is>
       </c>
       <c r="G71" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H71" s="2" t="n">
         <v>0</v>
@@ -9371,11 +9095,11 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>22/10/2026 22:41</t>
+          <t>23/10/2026 11:51</t>
         </is>
       </c>
       <c r="G72" s="2" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="H72" s="2" t="n">
         <v>0</v>
@@ -9414,18 +9138,18 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>22/10/2026 22:31</t>
+          <t>23/10/2026 11:40</t>
         </is>
       </c>
       <c r="G73" s="2" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>Ultima esecuzione: 35 elementi esaminati, 0 pertinenti</t>
+          <t>Ultima esecuzione: 1 elementi esaminati, 0 pertinenti</t>
         </is>
       </c>
     </row>
@@ -9457,11 +9181,11 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>22/10/2026 22:29</t>
+          <t>23/10/2026 11:39</t>
         </is>
       </c>
       <c r="G74" s="2" t="n">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="H74" s="2" t="n">
         <v>8</v>
@@ -9500,11 +9224,11 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>22/10/2026 22:27</t>
+          <t>23/10/2026 11:36</t>
         </is>
       </c>
       <c r="G75" s="2" t="n">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="H75" s="2" t="n">
         <v>6</v>
@@ -9543,11 +9267,11 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>22/10/2026 22:08</t>
+          <t>23/10/2026 11:17</t>
         </is>
       </c>
       <c r="G76" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H76" s="2" t="n">
         <v>0</v>
@@ -9586,11 +9310,11 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>22/10/2026 22:09</t>
+          <t>23/10/2026 11:18</t>
         </is>
       </c>
       <c r="G77" s="2" t="n">
-        <v>245</v>
+        <v>280</v>
       </c>
       <c r="H77" s="2" t="n">
         <v>0</v>
@@ -9629,11 +9353,11 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>22/10/2026 22:39</t>
+          <t>23/10/2026 11:49</t>
         </is>
       </c>
       <c r="G78" s="2" t="n">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="H78" s="2" t="n">
         <v>0</v>
@@ -9672,11 +9396,11 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>22/10/2026 22:38</t>
+          <t>23/10/2026 11:47</t>
         </is>
       </c>
       <c r="G79" s="2" t="n">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="H79" s="2" t="n">
         <v>0</v>
@@ -9715,14 +9439,14 @@
       </c>
       <c r="F80" s="2" t="n"/>
       <c r="G80" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H80" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>Ultimo errore 22/10/2026: HTTP 404</t>
+          <t>Ultimo errore 23/10/2026: HTTP 404</t>
         </is>
       </c>
     </row>
@@ -9754,11 +9478,11 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>22/10/2026 22:36</t>
+          <t>23/10/2026 11:46</t>
         </is>
       </c>
       <c r="G81" s="2" t="n">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="H81" s="2" t="n">
         <v>0</v>
@@ -9797,11 +9521,11 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>22/10/2026 22:51</t>
+          <t>23/10/2026 12:01</t>
         </is>
       </c>
       <c r="G82" s="2" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="H82" s="2" t="n">
         <v>0</v>
@@ -9840,14 +9564,14 @@
       </c>
       <c r="F83" s="2" t="n"/>
       <c r="G83" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H83" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>Ultimo errore 22/10/2026: HTTP 403</t>
+          <t>Ultimo errore 23/10/2026: HTTP 403</t>
         </is>
       </c>
     </row>
@@ -9874,19 +9598,23 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>https://www.vr.se/english/applying-for-funding/calls.html</t>
-        </is>
-      </c>
-      <c r="F84" s="2" t="n"/>
+          <t>https://www.vr.se/english/applying-for-funding/calls-and-decisions.html</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>23/10/2026 11:48</t>
+        </is>
+      </c>
       <c r="G84" s="2" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="H84" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>Ultimo errore 22/10/2026: HTTP 404</t>
+          <t>Ultima esecuzione: 35 elementi esaminati, 0 pertinenti</t>
         </is>
       </c>
     </row>
@@ -9918,11 +9646,11 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>22/10/2026 22:25</t>
+          <t>23/10/2026 11:35</t>
         </is>
       </c>
       <c r="G85" s="2" t="n">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="H85" s="2" t="n">
         <v>0</v>
@@ -9961,11 +9689,11 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>22/10/2026 22:26</t>
+          <t>23/10/2026 11:35</t>
         </is>
       </c>
       <c r="G86" s="2" t="n">
-        <v>245</v>
+        <v>280</v>
       </c>
       <c r="H86" s="2" t="n">
         <v>0</v>
@@ -10004,11 +9732,11 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>22/10/2026 22:42</t>
+          <t>23/10/2026 11:52</t>
         </is>
       </c>
       <c r="G87" s="2" t="n">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="H87" s="2" t="n">
         <v>0</v>
@@ -10047,11 +9775,11 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>22/10/2026 22:26</t>
+          <t>23/10/2026 11:36</t>
         </is>
       </c>
       <c r="G88" s="2" t="n">
-        <v>245</v>
+        <v>280</v>
       </c>
       <c r="H88" s="2" t="n">
         <v>0</v>
@@ -10090,11 +9818,11 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>22/10/2026 22:42</t>
+          <t>23/10/2026 11:52</t>
         </is>
       </c>
       <c r="G89" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H89" s="2" t="n">
         <v>0</v>
@@ -10133,14 +9861,14 @@
       </c>
       <c r="F90" s="2" t="n"/>
       <c r="G90" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H90" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>Ultimo errore 22/10/2026: HTTP 403</t>
+          <t>Ultimo errore 23/10/2026: HTTP 403</t>
         </is>
       </c>
     </row>
@@ -10155,7 +9883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -10213,107 +9941,107 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22 22:58</t>
+          <t>2026-10-23 12:48</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3897</v>
+        <v>3853</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>12 di infrastruttura, 7 preclinici, 7 servizi o programmi sociali, 5 non pertinenti alla riabilitazione, 1 chiusi, 1 pagine che non sono bandi</t>
+          <t>12 di infrastruttura, 8 preclinici, 7 non pertinenti alla riabilitazione, 7 servizi o programmi sociali, 2 pagine che non sono bandi, 1 chiusi</t>
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>6</v>
+        <v>61</v>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>NIHR: HTTP 403; Stroke Association: HTTP 403; American Heart Association – Research: HTTP 403; NHMRC: irraggiungibile: HTTPSConnectionPool(host='www.nhmrc.gov.au', port=443): Read timed out. (read timeout=45); BMBF – Gesundheitsforschung (bandi): HTTP 404; ZonMw: HTTP 403; FWO – Research Foundation Flanders: irraggiungibile: HTTPSConnectionPool(host='www.fwo.be', port=443): Max retries exceeded with url: /en/fellowships-funding/ (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1010)'))); Swedish Research Council: HTTP 404; Health Research Board Ireland: HTTP 403; Lundbeck Foundation: HTTP 404; Global Health EDCTP3: HTTP 404; Human Frontier Science Program: HTTP 403; Chan Zuckerberg Initiative: HTTP 404; Cure Parkinson's: HTTP 403; Craig H. Neilsen Foundation: HTTP 404; AMED – Japan Agency for Medical Research and Development: HTTP 404; NMRC Singapore: irraggiungibile: HTTPSConnectionPool(host='www.nmrc.gov.sg', port=443): Max retries exceeded with url: /grants/ (Caused by NameResolutionError("HTTPSConnection(host='www.nmrc.gov.sg', port=443): Failed to resolve 'www.nmrc.gov.sg' ([Errno -2] Name or service not known)")); ANID Chile: HTTP 403; SAMRC – South African Medical Research Council: HTTP 404; MRFF – Medical Research Future Fund: irraggiungibile: HTTPSConnectionPool(host='www.health.gov.au', port=443): Read timed out. (read timeout=45)</t>
+          <t>NIHR: HTTP 403; Stroke Association: HTTP 403; American Heart Association – Research: HTTP 403; NHMRC: irraggiungibile: HTTPSConnectionPool(host='www.nhmrc.gov.au', port=443): Read timed out. (read timeout=45); BMBF – Gesundheitsforschung (bandi): HTTP 404; ZonMw: HTTP 403; FWO – Research Foundation Flanders: irraggiungibile: HTTPSConnectionPool(host='www.fwo.be', port=443): Max retries exceeded with url: /en/fellowships-funding/ (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1010)'))); Health Research Board Ireland: HTTP 403; Lundbeck Foundation: HTTP 404; Global Health EDCTP3: HTTP 404; Human Frontier Science Program: HTTP 403; Chan Zuckerberg Initiative: HTTP 404; Cure Parkinson's: HTTP 403; Craig H. Neilsen Foundation: HTTP 404; ANID Chile: HTTP 403; SAMRC – South African Medical Research Council: HTTP 404; MRFF – Medical Research Future Fund: irraggiungibile: HTTPSConnectionPool(host='www.health.gov.au', port=443): Read timed out. (read timeout=45)</t>
         </is>
       </c>
       <c r="H2" s="3" t="n">
-        <v>56.7</v>
+        <v>97.7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-21 12:31</t>
+          <t>2026-10-22 22:58</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2839</v>
+        <v>3897</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>12 di infrastruttura, 7 servizi o programmi sociali, 6 preclinici, 4 non pertinenti alla riabilitazione, 1 chiusi, 1 pagine che non sono bandi</t>
+          <t>12 di infrastruttura, 7 preclinici, 7 servizi o programmi sociali, 5 non pertinenti alla riabilitazione, 1 chiusi, 1 pagine che non sono bandi</t>
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>NIHR: HTTP 403; Stroke Association: HTTP 403; American Heart Association – Research: HTTP 403; NHMRC: irraggiungibile: HTTPSConnectionPool(host='www.nhmrc.gov.au', port=443): Read timed out. (read timeout=45)</t>
+          <t>NIHR: HTTP 403; Stroke Association: HTTP 403; American Heart Association – Research: HTTP 403; NHMRC: irraggiungibile: HTTPSConnectionPool(host='www.nhmrc.gov.au', port=443): Read timed out. (read timeout=45); BMBF – Gesundheitsforschung (bandi): HTTP 404; ZonMw: HTTP 403; FWO – Research Foundation Flanders: irraggiungibile: HTTPSConnectionPool(host='www.fwo.be', port=443): Max retries exceeded with url: /en/fellowships-funding/ (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1010)'))); Swedish Research Council: HTTP 404; Health Research Board Ireland: HTTP 403; Lundbeck Foundation: HTTP 404; Global Health EDCTP3: HTTP 404; Human Frontier Science Program: HTTP 403; Chan Zuckerberg Initiative: HTTP 404; Cure Parkinson's: HTTP 403; Craig H. Neilsen Foundation: HTTP 404; AMED – Japan Agency for Medical Research and Development: HTTP 404; NMRC Singapore: irraggiungibile: HTTPSConnectionPool(host='www.nmrc.gov.sg', port=443): Max retries exceeded with url: /grants/ (Caused by NameResolutionError("HTTPSConnection(host='www.nmrc.gov.sg', port=443): Failed to resolve 'www.nmrc.gov.sg' ([Errno -2] Name or service not known)")); ANID Chile: HTTP 403; SAMRC – South African Medical Research Council: HTTP 404; MRFF – Medical Research Future Fund: irraggiungibile: HTTPSConnectionPool(host='www.health.gov.au', port=443): Read timed out. (read timeout=45)</t>
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>36.7</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-21 06:19</t>
+          <t>2026-10-21 12:31</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>2731</v>
+        <v>2839</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>35 non aperti all'Italia, 3 di infrastruttura, 3 preclinici, 2 non pertinenti alla riabilitazione, 1 servizi o programmi sociali</t>
+          <t>12 di infrastruttura, 7 servizi o programmi sociali, 6 preclinici, 4 non pertinenti alla riabilitazione, 1 chiusi, 1 pagine che non sono bandi</t>
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Nessuno</t>
+          <t>NIHR: HTTP 403; Stroke Association: HTTP 403; American Heart Association – Research: HTTP 403; NHMRC: irraggiungibile: HTTPSConnectionPool(host='www.nhmrc.gov.au', port=443): Read timed out. (read timeout=45)</t>
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>30</v>
+        <v>36.7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-19 07:49</t>
+          <t>2026-10-21 06:19</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>2686</v>
+        <v>2731</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>0</v>
@@ -10323,11 +10051,11 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>32 non aperti all'Italia, 3 di infrastruttura, 3 preclinici, 2 non pertinenti alla riabilitazione, 1 servizi o programmi sociali</t>
+          <t>35 non aperti all'Italia, 3 di infrastruttura, 3 preclinici, 2 non pertinenti alla riabilitazione, 1 servizi o programmi sociali</t>
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -10335,31 +10063,31 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>24.1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-10-18 14:17</t>
+          <t>2026-10-19 07:49</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>2720</v>
+        <v>2686</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>32 non aperti all'Italia, 3 di infrastruttura, 3 preclinici, 3 non pertinenti alla riabilitazione, 1 servizi o programmi sociali</t>
+          <t>32 non aperti all'Italia, 3 di infrastruttura, 3 preclinici, 2 non pertinenti alla riabilitazione, 1 servizi o programmi sociali</t>
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
@@ -10367,62 +10095,94 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>29.3</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-10-18 02:48</t>
+          <t>2026-10-18 14:17</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>2925</v>
+        <v>2720</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>107</v>
-      </c>
-      <c r="E7" s="3" t="n"/>
+        <v>112</v>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>32 non aperti all'Italia, 3 di infrastruttura, 3 preclinici, 3 non pertinenti alla riabilitazione, 1 servizi o programmi sociali</t>
+        </is>
+      </c>
       <c r="F7" s="3" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>NIHR: HTTP 403; Stroke Association: HTTP 403; American Heart Association – Research: HTTP 403; NHMRC: irraggiungibile: HTTPSConnectionPool(host='www.nhmrc.gov.au', port=443): Read timed out. (read timeout=45)</t>
+          <t>Nessuno</t>
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>92.5</v>
+        <v>29.3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-10-17 15:58</t>
+          <t>2026-10-18 02:48</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>2819</v>
+        <v>2925</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>266</v>
+        <v>20</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="E8" s="3" t="n"/>
       <c r="F8" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>NIHR: HTTP 403; Stroke Association: HTTP 403; American Heart Association – Research: HTTP 403; NHMRC: irraggiungibile: HTTPSConnectionPool(host='www.nhmrc.gov.au', port=443): Read timed out. (read timeout=45)</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>92.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-17 15:58</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>2819</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>266</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="n"/>
+      <c r="F9" s="3" t="n">
         <v>44</v>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>NIHR: HTTP 403; Stroke Association: HTTP 403; American Heart Association – Research: HTTP 403; NHMRC: irraggiungibile: HTTPSConnectionPool(host='www.nhmrc.gov.au', port=443): Read timed out. (read timeout=45)</t>
         </is>
       </c>
-      <c r="H8" s="3" t="n">
+      <c r="H9" s="3" t="n">
         <v>76.5</v>
       </c>
     </row>
